--- a/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
+++ b/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP121" headerRowCount="1">
-  <autoFilter ref="A1:EP121"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP125" headerRowCount="1">
+  <autoFilter ref="A1:EP125"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP121"/>
+  <dimension ref="A1:EP125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.8" customWidth="1" min="1" max="1"/>
@@ -1797,7 +1797,7 @@
         <v>1.13</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -2242,7 +2242,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="DE3" t="n">
         <v>0.63</v>
@@ -2685,7 +2685,7 @@
         <v>2.43</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE5" t="n">
         <v>0.29</v>
@@ -4583,7 +4583,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5022,10 +5022,10 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5055,7 +5055,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP9" t="b">
         <v>0</v>
@@ -5914,10 +5914,10 @@
         <v>100</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="DF11" t="n">
         <v>3</v>
@@ -5947,7 +5947,7 @@
         <v>2.56</v>
       </c>
       <c r="DO11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -7343,7 +7343,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7757,7 +7757,7 @@
         <v>2.75</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DF15" t="n">
         <v>0</v>
@@ -7787,7 +7787,7 @@
         <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8242,7 +8242,7 @@
         <v>50</v>
       </c>
       <c r="DD16" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DE16" t="n">
         <v>0.29</v>
@@ -8714,7 +8714,7 @@
         <v>0</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DE17" t="n">
         <v>1.38</v>
@@ -10526,7 +10526,7 @@
         <v>50</v>
       </c>
       <c r="DD21" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="DE21" t="n">
         <v>1.14</v>
@@ -10559,7 +10559,7 @@
         <v>1.95</v>
       </c>
       <c r="DO21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11019,7 +11019,7 @@
         <v>0</v>
       </c>
       <c r="DO22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11449,7 +11449,7 @@
         <v>2.71</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DF23" t="n">
         <v>3</v>
@@ -11921,7 +11921,7 @@
         <v>1.5</v>
       </c>
       <c r="DE24" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DF24" t="n">
         <v>0</v>
@@ -12362,10 +12362,10 @@
         <v>50</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DE25" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF25" t="n">
         <v>1</v>
@@ -12395,7 +12395,7 @@
         <v>2.16</v>
       </c>
       <c r="DO25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13333,7 +13333,7 @@
         <v>1.29</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="DF27" t="n">
         <v>3</v>
@@ -13811,7 +13811,7 @@
         <v>2.04</v>
       </c>
       <c r="DO28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -15178,7 +15178,7 @@
         <v>50</v>
       </c>
       <c r="DD31" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DE31" t="n">
         <v>2.14</v>
@@ -16982,7 +16982,7 @@
         <v>75</v>
       </c>
       <c r="DD35" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE35" t="n">
         <v>1.38</v>
@@ -17934,7 +17934,7 @@
         <v>75</v>
       </c>
       <c r="DD37" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="DE37" t="n">
         <v>0.57</v>
@@ -17967,7 +17967,7 @@
         <v>2.97</v>
       </c>
       <c r="DO37" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18378,7 +18378,7 @@
         <v>100</v>
       </c>
       <c r="DD38" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DE38" t="n">
         <v>1.13</v>
@@ -18845,7 +18845,7 @@
         <v>1.13</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DF39" t="n">
         <v>2</v>
@@ -19301,7 +19301,7 @@
         <v>2.25</v>
       </c>
       <c r="DE40" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF40" t="n">
         <v>1.5</v>
@@ -20218,10 +20218,10 @@
         <v>50</v>
       </c>
       <c r="DD42" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DE42" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DF42" t="n">
         <v>0.67</v>
@@ -20251,7 +20251,7 @@
         <v>2.35</v>
       </c>
       <c r="DO42" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -20690,7 +20690,7 @@
         <v>59</v>
       </c>
       <c r="DD43" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DE43" t="n">
         <v>1.14</v>
@@ -20723,7 +20723,7 @@
         <v>2.55</v>
       </c>
       <c r="DO43" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -23039,7 +23039,7 @@
         <v>3.02</v>
       </c>
       <c r="DO48" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -23465,7 +23465,7 @@
         <v>0.57</v>
       </c>
       <c r="DE49" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="DF49" t="n">
         <v>0.5</v>
@@ -23495,7 +23495,7 @@
         <v>2.7</v>
       </c>
       <c r="DO49" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -23934,7 +23934,7 @@
         <v>63</v>
       </c>
       <c r="DD50" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DE50" t="n">
         <v>0.86</v>
@@ -23967,7 +23967,7 @@
         <v>2.38</v>
       </c>
       <c r="DO50" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24846,10 +24846,10 @@
         <v>50</v>
       </c>
       <c r="DD52" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE52" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF52" t="n">
         <v>1.33</v>
@@ -24879,7 +24879,7 @@
         <v>2</v>
       </c>
       <c r="DO52" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25305,7 +25305,7 @@
         <v>1.29</v>
       </c>
       <c r="DE53" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DF53" t="n">
         <v>1.5</v>
@@ -25750,10 +25750,10 @@
         <v>71</v>
       </c>
       <c r="DD54" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="DE54" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="DF54" t="n">
         <v>0.67</v>
@@ -25783,7 +25783,7 @@
         <v>3.31</v>
       </c>
       <c r="DO54" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -27606,7 +27606,7 @@
         <v>63</v>
       </c>
       <c r="DD58" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DE58" t="n">
         <v>0.29</v>
@@ -29901,7 +29901,7 @@
         <v>1.29</v>
       </c>
       <c r="DE63" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF63" t="n">
         <v>1.33</v>
@@ -30849,7 +30849,7 @@
         <v>1.29</v>
       </c>
       <c r="DE65" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DF65" t="n">
         <v>1.33</v>
@@ -31305,7 +31305,7 @@
         <v>1</v>
       </c>
       <c r="DE66" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DF66" t="n">
         <v>1.5</v>
@@ -31754,7 +31754,7 @@
         <v>88</v>
       </c>
       <c r="DD67" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="DE67" t="n">
         <v>0.86</v>
@@ -31787,7 +31787,7 @@
         <v>3</v>
       </c>
       <c r="DO67" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -32686,7 +32686,7 @@
         <v>37</v>
       </c>
       <c r="DD69" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DE69" t="n">
         <v>1.14</v>
@@ -33130,7 +33130,7 @@
         <v>88</v>
       </c>
       <c r="DD70" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE70" t="n">
         <v>0.63</v>
@@ -34537,7 +34537,7 @@
         <v>0.57</v>
       </c>
       <c r="DE73" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DF73" t="n">
         <v>0.33</v>
@@ -34567,7 +34567,7 @@
         <v>2.46</v>
       </c>
       <c r="DO73" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -35507,7 +35507,7 @@
         <v>2.91</v>
       </c>
       <c r="DO75" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -37329,7 +37329,7 @@
         <v>2.75</v>
       </c>
       <c r="DE79" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="DF79" t="n">
         <v>2.5</v>
@@ -37359,7 +37359,7 @@
         <v>3.14</v>
       </c>
       <c r="DO79" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -37785,7 +37785,7 @@
         <v>1.5</v>
       </c>
       <c r="DE80" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF80" t="n">
         <v>2</v>
@@ -38254,7 +38254,7 @@
         <v>53</v>
       </c>
       <c r="DD81" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE81" t="n">
         <v>0</v>
@@ -38690,7 +38690,7 @@
         <v>70</v>
       </c>
       <c r="DD82" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="DE82" t="n">
         <v>1.38</v>
@@ -39142,7 +39142,7 @@
         <v>80</v>
       </c>
       <c r="DD83" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DE83" t="n">
         <v>0.63</v>
@@ -39601,7 +39601,7 @@
         <v>2.25</v>
       </c>
       <c r="DE84" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DF84" t="n">
         <v>1.8</v>
@@ -40522,7 +40522,7 @@
         <v>47</v>
       </c>
       <c r="DD86" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DE86" t="n">
         <v>1.13</v>
@@ -41499,7 +41499,7 @@
         <v>3.03</v>
       </c>
       <c r="DO88" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -42091,162 +42091,170 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
         <v>45948.41666666666</v>
       </c>
       <c r="G90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
         <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K90" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L90" t="n">
+        <v>9</v>
+      </c>
+      <c r="M90" t="n">
+        <v>2</v>
+      </c>
+      <c r="N90" t="n">
+        <v>2</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
         <v>11</v>
       </c>
-      <c r="M90" t="n">
-        <v>1</v>
-      </c>
-      <c r="N90" t="n">
-        <v>2</v>
-      </c>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>3</v>
-      </c>
       <c r="R90" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T90" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="U90" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="V90" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W90" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="X90" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Y90" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="Z90" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA90" t="inlineStr"/>
-      <c r="AB90" t="inlineStr"/>
+        <v>35</v>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>Stadion Nizhny Novgorod</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>ul. Dolzhanskaya, Nizhniy Novgorod</t>
+        </is>
+      </c>
       <c r="AC90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD90" t="n">
         <v>2</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.9</v>
+        <v>2.29</v>
       </c>
       <c r="AF90" t="n">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="AG90" t="n">
-        <v>3.28</v>
+        <v>2.57</v>
       </c>
       <c r="AH90" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AI90" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AJ90" t="n">
-        <v>3.08</v>
+        <v>2.66</v>
       </c>
       <c r="AK90" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AL90" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="AM90" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AN90" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AO90" t="n">
-        <v>2.62</v>
+        <v>2.16</v>
       </c>
       <c r="AP90" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR90" t="n">
-        <v>2.74</v>
+        <v>2.51</v>
       </c>
       <c r="AS90" t="n">
-        <v>3.04</v>
+        <v>3.32</v>
       </c>
       <c r="AT90" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AU90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV90" t="n">
         <v>0</v>
       </c>
       <c r="AW90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ90" t="n">
         <v>1</v>
       </c>
       <c r="BA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB90" t="n">
-        <v>-1</v>
+        <v>668270</v>
       </c>
       <c r="BC90" t="n">
         <v>0</v>
       </c>
       <c r="BD90" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BE90" t="n">
         <v>0</v>
@@ -42279,7 +42287,7 @@
         <v>-1</v>
       </c>
       <c r="BO90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP90" t="n">
         <v>0</v>
@@ -42291,7 +42299,7 @@
         <v>2</v>
       </c>
       <c r="BS90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT90" t="n">
         <v>3</v>
@@ -42300,25 +42308,25 @@
         <v>1</v>
       </c>
       <c r="BV90" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="BW90" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="BX90" t="n">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="BY90" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BZ90" t="n">
-        <v>1.44</v>
+        <v>2.76</v>
       </c>
       <c r="CA90" t="n">
-        <v>1.34</v>
+        <v>1.09</v>
       </c>
       <c r="CB90" t="n">
-        <v>2.78</v>
+        <v>3.85</v>
       </c>
       <c r="CC90" t="n">
         <v>0</v>
@@ -42366,73 +42374,73 @@
         <v>1</v>
       </c>
       <c r="CR90" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS90" t="n">
         <v>21</v>
       </c>
-      <c r="CS90" t="n">
-        <v>23</v>
-      </c>
       <c r="CT90" t="n">
         <v>1</v>
       </c>
       <c r="CU90" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="CV90" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CW90" t="n">
         <v>1</v>
       </c>
       <c r="CX90" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="CY90" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="CZ90" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="DA90" t="n">
         <v>100</v>
       </c>
       <c r="DB90" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="DC90" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="DD90" t="n">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="DE90" t="n">
-        <v>0.57</v>
+        <v>1.63</v>
       </c>
       <c r="DF90" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="DG90" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="DH90" t="n">
-        <v>1.09</v>
+        <v>0.55</v>
       </c>
       <c r="DI90" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="DJ90" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="DK90" t="n">
         <v>0</v>
       </c>
       <c r="DL90" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DM90" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="DN90" t="n">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="DO90" t="n">
         <v>15</v>
@@ -42441,7 +42449,7 @@
         <v>1</v>
       </c>
       <c r="DQ90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR90" t="b">
         <v>0</v>
@@ -42456,70 +42464,82 @@
         <v>0</v>
       </c>
       <c r="DV90" t="b">
-        <v>1</v>
-      </c>
-      <c r="DW90" t="inlineStr"/>
-      <c r="DX90" t="inlineStr"/>
-      <c r="DY90" t="inlineStr"/>
-      <c r="DZ90" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="DW90" t="n">
+        <v>8</v>
+      </c>
+      <c r="DX90" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="DY90" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="DZ90" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
       <c r="EA90" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EB90" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="EC90" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="ED90" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EE90" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EF90" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="EG90" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="EH90" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="EI90" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="EJ90" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="EK90" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EL90" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="EM90" t="inlineStr"/>
@@ -42543,170 +42563,162 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F91" s="2" t="n">
         <v>45948.41666666666</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91" t="n">
         <v>1</v>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J91" t="n">
+        <v>5</v>
+      </c>
+      <c r="K91" t="n">
         <v>6</v>
       </c>
-      <c r="K91" t="n">
+      <c r="L91" t="n">
+        <v>11</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1</v>
+      </c>
+      <c r="N91" t="n">
+        <v>2</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
         <v>3</v>
       </c>
-      <c r="L91" t="n">
-        <v>9</v>
-      </c>
-      <c r="M91" t="n">
-        <v>2</v>
-      </c>
-      <c r="N91" t="n">
-        <v>2</v>
-      </c>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>11</v>
-      </c>
       <c r="R91" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S91" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T91" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="U91" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="V91" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W91" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X91" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Y91" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Z91" t="n">
-        <v>35</v>
-      </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>Stadion Nizhny Novgorod</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>ul. Dolzhanskaya, Nizhniy Novgorod</t>
-        </is>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="AA91" t="inlineStr"/>
+      <c r="AB91" t="inlineStr"/>
       <c r="AC91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD91" t="n">
         <v>2</v>
       </c>
       <c r="AE91" t="n">
-        <v>2.29</v>
+        <v>1.9</v>
       </c>
       <c r="AF91" t="n">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
       <c r="AG91" t="n">
-        <v>2.57</v>
+        <v>3.28</v>
       </c>
       <c r="AH91" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AI91" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AJ91" t="n">
-        <v>2.66</v>
+        <v>3.08</v>
       </c>
       <c r="AK91" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="AL91" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="AM91" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AN91" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AO91" t="n">
-        <v>2.16</v>
+        <v>2.62</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AR91" t="n">
-        <v>2.51</v>
+        <v>2.74</v>
       </c>
       <c r="AS91" t="n">
-        <v>3.32</v>
+        <v>3.04</v>
       </c>
       <c r="AT91" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AU91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV91" t="n">
         <v>0</v>
       </c>
       <c r="AW91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ91" t="n">
         <v>1</v>
       </c>
       <c r="BA91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB91" t="n">
-        <v>668270</v>
+        <v>-1</v>
       </c>
       <c r="BC91" t="n">
         <v>0</v>
       </c>
       <c r="BD91" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BE91" t="n">
         <v>0</v>
@@ -42739,7 +42751,7 @@
         <v>-1</v>
       </c>
       <c r="BO91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP91" t="n">
         <v>0</v>
@@ -42751,7 +42763,7 @@
         <v>2</v>
       </c>
       <c r="BS91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT91" t="n">
         <v>3</v>
@@ -42760,25 +42772,25 @@
         <v>1</v>
       </c>
       <c r="BV91" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="BW91" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="BX91" t="n">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="BY91" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="BZ91" t="n">
-        <v>2.76</v>
+        <v>1.44</v>
       </c>
       <c r="CA91" t="n">
-        <v>1.09</v>
+        <v>1.34</v>
       </c>
       <c r="CB91" t="n">
-        <v>3.85</v>
+        <v>2.78</v>
       </c>
       <c r="CC91" t="n">
         <v>0</v>
@@ -42826,73 +42838,73 @@
         <v>1</v>
       </c>
       <c r="CR91" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CS91" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CT91" t="n">
         <v>1</v>
       </c>
       <c r="CU91" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="CV91" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CW91" t="n">
         <v>1</v>
       </c>
       <c r="CX91" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="CY91" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="CZ91" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="DA91" t="n">
         <v>100</v>
       </c>
       <c r="DB91" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="DC91" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="DD91" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="DE91" t="n">
-        <v>1.63</v>
+        <v>0.57</v>
       </c>
       <c r="DF91" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="DG91" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="DH91" t="n">
-        <v>0.55</v>
+        <v>1.09</v>
       </c>
       <c r="DI91" t="n">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="DJ91" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="DK91" t="n">
         <v>0</v>
       </c>
       <c r="DL91" t="n">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="DM91" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="DN91" t="n">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="DO91" t="n">
         <v>15</v>
@@ -42901,7 +42913,7 @@
         <v>1</v>
       </c>
       <c r="DQ91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR91" t="b">
         <v>0</v>
@@ -42916,82 +42928,70 @@
         <v>0</v>
       </c>
       <c r="DV91" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW91" t="n">
-        <v>8</v>
-      </c>
-      <c r="DX91" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="DY91" t="inlineStr">
-        <is>
-          <t>80%</t>
-        </is>
-      </c>
-      <c r="DZ91" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="DW91" t="inlineStr"/>
+      <c r="DX91" t="inlineStr"/>
+      <c r="DY91" t="inlineStr"/>
+      <c r="DZ91" t="inlineStr"/>
       <c r="EA91" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EB91" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="EC91" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="ED91" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EE91" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EF91" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="EG91" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="EH91" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="EI91" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EJ91" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="EK91" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="EL91" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EM91" t="inlineStr"/>
@@ -43334,7 +43334,7 @@
         <v>67</v>
       </c>
       <c r="DD92" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE92" t="n">
         <v>1.13</v>
@@ -44277,7 +44277,7 @@
         <v>2.43</v>
       </c>
       <c r="DE94" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DF94" t="n">
         <v>2.2</v>
@@ -45206,10 +45206,10 @@
         <v>67</v>
       </c>
       <c r="DD96" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DE96" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="DF96" t="n">
         <v>2.17</v>
@@ -45239,7 +45239,7 @@
         <v>2.71</v>
       </c>
       <c r="DO96" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -45657,7 +45657,7 @@
         <v>1.13</v>
       </c>
       <c r="DE97" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DF97" t="n">
         <v>1.33</v>
@@ -46126,7 +46126,7 @@
         <v>86</v>
       </c>
       <c r="DD98" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE98" t="n">
         <v>0.57</v>
@@ -46159,7 +46159,7 @@
         <v>2.97</v>
       </c>
       <c r="DO98" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -47486,7 +47486,7 @@
         <v>75</v>
       </c>
       <c r="DD101" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="DE101" t="n">
         <v>1.63</v>
@@ -47961,7 +47961,7 @@
         <v>1</v>
       </c>
       <c r="DE102" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="DF102" t="n">
         <v>1</v>
@@ -49325,7 +49325,7 @@
         <v>1.43</v>
       </c>
       <c r="DE105" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF105" t="n">
         <v>2</v>
@@ -49355,7 +49355,7 @@
         <v>2.37</v>
       </c>
       <c r="DO105" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -50230,7 +50230,7 @@
         <v>61</v>
       </c>
       <c r="DD107" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DE107" t="n">
         <v>1.14</v>
@@ -52102,10 +52102,10 @@
         <v>36</v>
       </c>
       <c r="DD111" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DE111" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF111" t="n">
         <v>0.57</v>
@@ -52135,7 +52135,7 @@
         <v>2.03</v>
       </c>
       <c r="DO111" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -52561,7 +52561,7 @@
         <v>1.86</v>
       </c>
       <c r="DE112" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DF112" t="n">
         <v>1.8</v>
@@ -52591,7 +52591,7 @@
         <v>2.57</v>
       </c>
       <c r="DO112" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -53941,7 +53941,7 @@
         <v>1.5</v>
       </c>
       <c r="DE115" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DF115" t="n">
         <v>1.71</v>
@@ -56239,7 +56239,7 @@
         <v>3.17</v>
       </c>
       <c r="DO120" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -56834,6 +56834,1802 @@
           <t>2.31</t>
         </is>
       </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>16</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Akron</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>FK Sochi</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>45982.64583333334</v>
+      </c>
+      <c r="G122" t="n">
+        <v>3</v>
+      </c>
+      <c r="H122" t="n">
+        <v>2</v>
+      </c>
+      <c r="I122" t="n">
+        <v>5</v>
+      </c>
+      <c r="J122" t="n">
+        <v>1</v>
+      </c>
+      <c r="K122" t="n">
+        <v>3</v>
+      </c>
+      <c r="L122" t="n">
+        <v>4</v>
+      </c>
+      <c r="M122" t="n">
+        <v>1</v>
+      </c>
+      <c r="N122" t="n">
+        <v>1</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>7</v>
+      </c>
+      <c r="R122" t="n">
+        <v>4</v>
+      </c>
+      <c r="S122" t="n">
+        <v>3</v>
+      </c>
+      <c r="T122" t="n">
+        <v>9</v>
+      </c>
+      <c r="U122" t="n">
+        <v>10</v>
+      </c>
+      <c r="V122" t="n">
+        <v>13</v>
+      </c>
+      <c r="W122" t="n">
+        <v>14</v>
+      </c>
+      <c r="X122" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA122" t="inlineStr"/>
+      <c r="AB122" t="inlineStr"/>
+      <c r="AC122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>668270</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>75</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>53</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>45</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>119</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>95</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU122" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV122" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX122" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY122" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ122" t="n">
+        <v>52</v>
+      </c>
+      <c r="DA122" t="n">
+        <v>94</v>
+      </c>
+      <c r="DB122" t="n">
+        <v>34</v>
+      </c>
+      <c r="DC122" t="n">
+        <v>68</v>
+      </c>
+      <c r="DD122" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE122" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="DF122" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DG122" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH122" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DI122" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="DJ122" t="n">
+        <v>48</v>
+      </c>
+      <c r="DK122" t="n">
+        <v>7</v>
+      </c>
+      <c r="DL122" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DM122" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="DN122" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DO122" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP122" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ122" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR122" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS122" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT122" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU122" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV122" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW122" t="inlineStr"/>
+      <c r="DX122" t="inlineStr"/>
+      <c r="DY122" t="inlineStr"/>
+      <c r="DZ122" t="inlineStr"/>
+      <c r="EA122" t="inlineStr"/>
+      <c r="EB122" t="inlineStr"/>
+      <c r="EC122" t="inlineStr"/>
+      <c r="ED122" t="inlineStr"/>
+      <c r="EE122" t="inlineStr"/>
+      <c r="EF122" t="inlineStr"/>
+      <c r="EG122" t="inlineStr"/>
+      <c r="EH122" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EI122" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="EJ122" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="EK122" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EL122" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EM122" t="inlineStr"/>
+      <c r="EN122" t="inlineStr"/>
+      <c r="EO122" t="inlineStr"/>
+      <c r="EP122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>16</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Orenburg</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Baltika</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>45983.45833333334</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>7</v>
+      </c>
+      <c r="K123" t="n">
+        <v>3</v>
+      </c>
+      <c r="L123" t="n">
+        <v>10</v>
+      </c>
+      <c r="M123" t="n">
+        <v>3</v>
+      </c>
+      <c r="N123" t="n">
+        <v>3</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>4</v>
+      </c>
+      <c r="R123" t="n">
+        <v>2</v>
+      </c>
+      <c r="S123" t="n">
+        <v>7</v>
+      </c>
+      <c r="T123" t="n">
+        <v>6</v>
+      </c>
+      <c r="U123" t="n">
+        <v>11</v>
+      </c>
+      <c r="V123" t="n">
+        <v>8</v>
+      </c>
+      <c r="W123" t="n">
+        <v>13</v>
+      </c>
+      <c r="X123" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>Stadion Gazovik</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>Tsvetnoy bulvar' 31, Rostoshi</t>
+        </is>
+      </c>
+      <c r="AC123" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>47</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>72</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>92</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>32</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>33</v>
+      </c>
+      <c r="CT123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU123" t="n">
+        <v>26</v>
+      </c>
+      <c r="CV123" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX123" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY123" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ123" t="n">
+        <v>38</v>
+      </c>
+      <c r="DA123" t="n">
+        <v>69</v>
+      </c>
+      <c r="DB123" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC123" t="n">
+        <v>51</v>
+      </c>
+      <c r="DD123" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DE123" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DF123" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DG123" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DH123" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="DI123" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="DJ123" t="n">
+        <v>63</v>
+      </c>
+      <c r="DK123" t="n">
+        <v>32</v>
+      </c>
+      <c r="DL123" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DM123" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DN123" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DO123" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP123" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ123" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR123" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS123" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT123" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU123" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV123" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW123" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="DX123" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="DY123" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="DZ123" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA123" t="inlineStr"/>
+      <c r="EB123" t="inlineStr"/>
+      <c r="EC123" t="inlineStr"/>
+      <c r="ED123" t="inlineStr"/>
+      <c r="EE123" t="inlineStr"/>
+      <c r="EF123" t="inlineStr"/>
+      <c r="EG123" t="inlineStr"/>
+      <c r="EH123" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="EI123" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EJ123" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="EK123" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EL123" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EM123" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EN123" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EO123" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EP123" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>16</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Spartak Moskva</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>CSKA Moskva</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>45983.57291666666</v>
+      </c>
+      <c r="G124" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>1</v>
+      </c>
+      <c r="J124" t="n">
+        <v>2</v>
+      </c>
+      <c r="K124" t="n">
+        <v>4</v>
+      </c>
+      <c r="L124" t="n">
+        <v>6</v>
+      </c>
+      <c r="M124" t="n">
+        <v>2</v>
+      </c>
+      <c r="N124" t="n">
+        <v>2</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>1</v>
+      </c>
+      <c r="R124" t="n">
+        <v>1</v>
+      </c>
+      <c r="S124" t="n">
+        <v>9</v>
+      </c>
+      <c r="T124" t="n">
+        <v>9</v>
+      </c>
+      <c r="U124" t="n">
+        <v>10</v>
+      </c>
+      <c r="V124" t="n">
+        <v>10</v>
+      </c>
+      <c r="W124" t="n">
+        <v>20</v>
+      </c>
+      <c r="X124" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>Otkrytiye Arena</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>Volokolamskoye shosse, Tushino, Moskva</t>
+        </is>
+      </c>
+      <c r="AC124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>924</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>47</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>27</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>31</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>61</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>60</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU124" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV124" t="n">
+        <v>20</v>
+      </c>
+      <c r="CW124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX124" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY124" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ124" t="n">
+        <v>53</v>
+      </c>
+      <c r="DA124" t="n">
+        <v>66</v>
+      </c>
+      <c r="DB124" t="n">
+        <v>34</v>
+      </c>
+      <c r="DC124" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD124" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DE124" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DF124" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DG124" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DH124" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DI124" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DJ124" t="n">
+        <v>48</v>
+      </c>
+      <c r="DK124" t="n">
+        <v>34</v>
+      </c>
+      <c r="DL124" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DM124" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="DN124" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="DO124" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP124" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ124" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR124" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS124" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT124" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU124" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV124" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW124" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="DX124" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="DY124" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="DZ124" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA124" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EB124" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="EC124" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="ED124" t="inlineStr"/>
+      <c r="EE124" t="inlineStr"/>
+      <c r="EF124" t="inlineStr"/>
+      <c r="EG124" t="inlineStr"/>
+      <c r="EH124" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EI124" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="EJ124" t="inlineStr">
+        <is>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="EK124" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EL124" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EM124" t="inlineStr"/>
+      <c r="EN124" t="inlineStr"/>
+      <c r="EO124" t="inlineStr"/>
+      <c r="EP124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>16</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Akhmat Grozny</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>45983.6875</v>
+      </c>
+      <c r="G125" t="n">
+        <v>1</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>1</v>
+      </c>
+      <c r="J125" t="n">
+        <v>3</v>
+      </c>
+      <c r="K125" t="n">
+        <v>3</v>
+      </c>
+      <c r="L125" t="n">
+        <v>6</v>
+      </c>
+      <c r="M125" t="n">
+        <v>2</v>
+      </c>
+      <c r="N125" t="n">
+        <v>1</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>3</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="n">
+        <v>6</v>
+      </c>
+      <c r="T125" t="n">
+        <v>7</v>
+      </c>
+      <c r="U125" t="n">
+        <v>9</v>
+      </c>
+      <c r="V125" t="n">
+        <v>7</v>
+      </c>
+      <c r="W125" t="n">
+        <v>14</v>
+      </c>
+      <c r="X125" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>47</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>53</v>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>Kazan' Arena</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>Prospekt Husaina Yamasheva 115a, Kazan'</t>
+        </is>
+      </c>
+      <c r="AC125" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>932</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>23</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>13</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>78</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>79</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU125" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV125" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX125" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY125" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ125" t="n">
+        <v>44</v>
+      </c>
+      <c r="DA125" t="n">
+        <v>76</v>
+      </c>
+      <c r="DB125" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC125" t="n">
+        <v>82</v>
+      </c>
+      <c r="DD125" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DE125" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DF125" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DG125" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DH125" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DI125" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="DJ125" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK125" t="n">
+        <v>26</v>
+      </c>
+      <c r="DL125" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DM125" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DN125" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="DO125" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP125" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ125" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR125" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS125" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT125" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU125" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV125" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW125" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="DX125" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="DY125" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="DZ125" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA125" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EB125" t="inlineStr">
+        <is>
+          <t>3.99</t>
+        </is>
+      </c>
+      <c r="EC125" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="ED125" t="inlineStr"/>
+      <c r="EE125" t="inlineStr"/>
+      <c r="EF125" t="inlineStr"/>
+      <c r="EG125" t="inlineStr"/>
+      <c r="EH125" t="inlineStr">
+        <is>
+          <t>2.73</t>
+        </is>
+      </c>
+      <c r="EI125" t="inlineStr">
+        <is>
+          <t>2.78</t>
+        </is>
+      </c>
+      <c r="EJ125" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="EK125" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EL125" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EM125" t="inlineStr"/>
+      <c r="EN125" t="inlineStr"/>
+      <c r="EO125" t="inlineStr"/>
+      <c r="EP125" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
+++ b/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP125" headerRowCount="1">
-  <autoFilter ref="A1:EP125"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP129" headerRowCount="1">
+  <autoFilter ref="A1:EP129"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP125"/>
+  <dimension ref="A1:EP129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.8" customWidth="1" min="1" max="1"/>
@@ -1794,7 +1794,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DE2" t="n">
         <v>1.78</v>
@@ -1827,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2682,7 +2682,7 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="DE4" t="n">
         <v>0.44</v>
@@ -2715,7 +2715,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3149,7 +3149,7 @@
         <v>2.22</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3179,7 +3179,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DE6" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3659,7 +3659,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4109,7 +4109,7 @@
         <v>2.71</v>
       </c>
       <c r="DE7" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -5470,7 +5470,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
@@ -5503,7 +5503,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6378,10 +6378,10 @@
         <v>100</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DE12" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DF12" t="n">
         <v>1</v>
@@ -6411,7 +6411,7 @@
         <v>2.72</v>
       </c>
       <c r="DO12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6863,7 +6863,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -8245,7 +8245,7 @@
         <v>0.89</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DF16" t="n">
         <v>1</v>
@@ -8275,7 +8275,7 @@
         <v>1.72</v>
       </c>
       <c r="DO16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8717,7 +8717,7 @@
         <v>1.89</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -8747,7 +8747,7 @@
         <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9203,7 +9203,7 @@
         <v>1.28</v>
       </c>
       <c r="DO18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9675,7 +9675,7 @@
         <v>1.82</v>
       </c>
       <c r="DO19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10098,7 +10098,7 @@
         <v>100</v>
       </c>
       <c r="DD20" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DE20" t="n">
         <v>1.63</v>
@@ -10131,7 +10131,7 @@
         <v>2.42</v>
       </c>
       <c r="DO20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -11479,7 +11479,7 @@
         <v>3.96</v>
       </c>
       <c r="DO23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -11951,7 +11951,7 @@
         <v>1.08</v>
       </c>
       <c r="DO24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12883,7 +12883,7 @@
         <v>1.97</v>
       </c>
       <c r="DO26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13330,7 +13330,7 @@
         <v>25</v>
       </c>
       <c r="DD27" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="DE27" t="n">
         <v>1.78</v>
@@ -13363,7 +13363,7 @@
         <v>3.01</v>
       </c>
       <c r="DO27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14246,7 +14246,7 @@
         <v>0</v>
       </c>
       <c r="DD29" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="DE29" t="n">
         <v>1.14</v>
@@ -14279,7 +14279,7 @@
         <v>3.23</v>
       </c>
       <c r="DO29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14721,7 +14721,7 @@
         <v>1.43</v>
       </c>
       <c r="DE30" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DF30" t="n">
         <v>0</v>
@@ -14751,7 +14751,7 @@
         <v>3.75</v>
       </c>
       <c r="DO30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15181,7 +15181,7 @@
         <v>0.89</v>
       </c>
       <c r="DE31" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="DF31" t="n">
         <v>1</v>
@@ -15211,7 +15211,7 @@
         <v>2.03</v>
       </c>
       <c r="DO31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15667,7 +15667,7 @@
         <v>1.95</v>
       </c>
       <c r="DO32" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16135,7 +16135,7 @@
         <v>3.03</v>
       </c>
       <c r="DO33" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16579,7 +16579,7 @@
         <v>2.73</v>
       </c>
       <c r="DO34" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -16985,7 +16985,7 @@
         <v>2.22</v>
       </c>
       <c r="DE35" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DF35" t="n">
         <v>1.5</v>
@@ -17015,7 +17015,7 @@
         <v>2.48</v>
       </c>
       <c r="DO35" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17503,7 +17503,7 @@
         <v>2.73</v>
       </c>
       <c r="DO36" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18381,7 +18381,7 @@
         <v>1.89</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DF38" t="n">
         <v>2</v>
@@ -18411,7 +18411,7 @@
         <v>2.06</v>
       </c>
       <c r="DO38" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -18842,7 +18842,7 @@
         <v>75</v>
       </c>
       <c r="DD39" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DE39" t="n">
         <v>1.38</v>
@@ -18875,7 +18875,7 @@
         <v>2.78</v>
       </c>
       <c r="DO39" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19331,7 +19331,7 @@
         <v>2.87</v>
       </c>
       <c r="DO40" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -19754,10 +19754,10 @@
         <v>75</v>
       </c>
       <c r="DD41" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DE41" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DF41" t="n">
         <v>0</v>
@@ -19787,7 +19787,7 @@
         <v>2.54</v>
       </c>
       <c r="DO41" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -21157,7 +21157,7 @@
         <v>2.71</v>
       </c>
       <c r="DE44" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DF44" t="n">
         <v>2</v>
@@ -21187,7 +21187,7 @@
         <v>3.11</v>
       </c>
       <c r="DO44" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -21618,10 +21618,10 @@
         <v>59</v>
       </c>
       <c r="DD45" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="DE45" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DF45" t="n">
         <v>3</v>
@@ -21651,7 +21651,7 @@
         <v>2.4</v>
       </c>
       <c r="DO45" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22098,7 +22098,7 @@
         <v>50</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DE46" t="n">
         <v>0</v>
@@ -22131,7 +22131,7 @@
         <v>2.53</v>
       </c>
       <c r="DO46" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22546,10 +22546,10 @@
         <v>50</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="DE47" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="DF47" t="n">
         <v>2</v>
@@ -22579,7 +22579,7 @@
         <v>2.33</v>
       </c>
       <c r="DO47" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -24415,7 +24415,7 @@
         <v>2.54</v>
       </c>
       <c r="DO51" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25335,7 +25335,7 @@
         <v>3.04</v>
       </c>
       <c r="DO53" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -26202,7 +26202,7 @@
         <v>84</v>
       </c>
       <c r="DD55" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="DE55" t="n">
         <v>0.63</v>
@@ -26235,7 +26235,7 @@
         <v>2.77</v>
       </c>
       <c r="DO55" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -26665,7 +26665,7 @@
         <v>2.75</v>
       </c>
       <c r="DE56" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="DF56" t="n">
         <v>3</v>
@@ -26695,7 +26695,7 @@
         <v>3.14</v>
       </c>
       <c r="DO56" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27167,7 +27167,7 @@
         <v>2.24</v>
       </c>
       <c r="DO57" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -27609,7 +27609,7 @@
         <v>1.89</v>
       </c>
       <c r="DE58" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DF58" t="n">
         <v>1.75</v>
@@ -27639,7 +27639,7 @@
         <v>2.53</v>
       </c>
       <c r="DO58" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -28078,7 +28078,7 @@
         <v>100</v>
       </c>
       <c r="DD59" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DE59" t="n">
         <v>0.57</v>
@@ -28111,7 +28111,7 @@
         <v>2.96</v>
       </c>
       <c r="DO59" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -28215,37 +28215,37 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
         <v>45913.57291666666</v>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K60" t="n">
         <v>5</v>
       </c>
       <c r="L60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N60" t="n">
         <v>4</v>
@@ -28257,7 +28257,7 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R60" t="n">
         <v>4</v>
@@ -28266,110 +28266,102 @@
         <v>9</v>
       </c>
       <c r="T60" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="U60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V60" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="W60" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="X60" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y60" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="Z60" t="n">
-        <v>62</v>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>Akhmat Arena</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
-        </is>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD60" t="n">
         <v>4</v>
       </c>
       <c r="AE60" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="AF60" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="AG60" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AI60" t="n">
         <v>1.77</v>
       </c>
       <c r="AJ60" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="AK60" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AL60" t="n">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="AM60" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="AN60" t="n">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AO60" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AQ60" t="n">
         <v>1.38</v>
       </c>
       <c r="AR60" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="AS60" t="n">
-        <v>2.88</v>
+        <v>3.07</v>
       </c>
       <c r="AT60" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AU60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY60" t="n">
         <v>1</v>
       </c>
       <c r="AZ60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB60" t="n">
         <v>-1</v>
@@ -28378,7 +28370,7 @@
         <v>0</v>
       </c>
       <c r="BD60" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="BE60" t="n">
         <v>0</v>
@@ -28414,43 +28406,43 @@
         <v>0</v>
       </c>
       <c r="BP60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BQ60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR60" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS60" t="n">
         <v>3</v>
       </c>
-      <c r="BS60" t="n">
-        <v>1</v>
-      </c>
       <c r="BT60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BU60" t="n">
         <v>1</v>
       </c>
       <c r="BV60" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="BW60" t="n">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="BX60" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="BY60" t="n">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="BZ60" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="CA60" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="CB60" t="n">
-        <v>3.11</v>
+        <v>2.81</v>
       </c>
       <c r="CC60" t="n">
         <v>0</v>
@@ -28498,19 +28490,19 @@
         <v>1</v>
       </c>
       <c r="CR60" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="CS60" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CT60" t="n">
         <v>1</v>
       </c>
       <c r="CU60" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="CV60" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="CW60" t="n">
         <v>1</v>
@@ -28519,55 +28511,55 @@
         <v>4</v>
       </c>
       <c r="CY60" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CZ60" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="DA60" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="DB60" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="DC60" t="n">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="DD60" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.63</v>
+        <v>1.14</v>
       </c>
       <c r="DF60" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DG60" t="n">
-        <v>2.33</v>
+        <v>1.33</v>
       </c>
       <c r="DH60" t="n">
         <v>1.14</v>
       </c>
       <c r="DI60" t="n">
-        <v>2.14</v>
+        <v>1.57</v>
       </c>
       <c r="DJ60" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="DK60" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="DL60" t="n">
-        <v>1.47</v>
+        <v>1.97</v>
       </c>
       <c r="DM60" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="DN60" t="n">
-        <v>2.92</v>
+        <v>3.31</v>
       </c>
       <c r="DO60" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -28576,10 +28568,10 @@
         <v>1</v>
       </c>
       <c r="DR60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT60" t="b">
         <v>0</v>
@@ -28591,34 +28583,34 @@
         <v>1</v>
       </c>
       <c r="DW60" t="n">
-        <v>19.43</v>
+        <v>16.47</v>
       </c>
       <c r="DX60" t="n">
-        <v>3.41</v>
+        <v>2.44</v>
       </c>
       <c r="DY60" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="DZ60" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="EA60" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EB60" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="EC60" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="ED60" t="inlineStr"/>
@@ -28627,41 +28619,49 @@
       <c r="EG60" t="inlineStr"/>
       <c r="EH60" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="EI60" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="EJ60" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EK60" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="EL60" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="EM60" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EN60" t="inlineStr">
         <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="EO60" t="inlineStr"/>
-      <c r="EP60" t="inlineStr"/>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EO60" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EP60" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -28679,37 +28679,37 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F61" s="2" t="n">
         <v>45913.57291666666</v>
       </c>
       <c r="G61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K61" t="n">
         <v>5</v>
       </c>
       <c r="L61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
         <v>4</v>
@@ -28721,7 +28721,7 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R61" t="n">
         <v>4</v>
@@ -28730,183 +28730,191 @@
         <v>9</v>
       </c>
       <c r="T61" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="U61" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V61" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W61" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="X61" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y61" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="Z61" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA61" t="inlineStr"/>
-      <c r="AB61" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>Akhmat Arena</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
+        </is>
+      </c>
       <c r="AC61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD61" t="n">
         <v>4</v>
       </c>
       <c r="AE61" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="AF61" t="n">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="AG61" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AI61" t="n">
         <v>1.77</v>
       </c>
       <c r="AJ61" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="AK61" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AL61" t="n">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="AM61" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="AN61" t="n">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AO61" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AQ61" t="n">
         <v>1.38</v>
       </c>
       <c r="AR61" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="AS61" t="n">
-        <v>3.07</v>
+        <v>2.88</v>
       </c>
       <c r="AT61" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AU61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY61" t="n">
         <v>1</v>
       </c>
       <c r="AZ61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD61" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH61" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP61" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR61" t="n">
         <v>3</v>
       </c>
-      <c r="BB61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BC61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD61" t="n">
-        <v>59</v>
-      </c>
-      <c r="BE61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BG61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BH61" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BJ61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BK61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BL61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BM61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BN61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BO61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP61" t="n">
+      <c r="BS61" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT61" t="n">
         <v>3</v>
       </c>
-      <c r="BQ61" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR61" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS61" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT61" t="n">
-        <v>2</v>
-      </c>
       <c r="BU61" t="n">
         <v>1</v>
       </c>
       <c r="BV61" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="BW61" t="n">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="BX61" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="BY61" t="n">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="BZ61" t="n">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="CA61" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="CB61" t="n">
-        <v>2.81</v>
+        <v>3.11</v>
       </c>
       <c r="CC61" t="n">
         <v>0</v>
@@ -28954,19 +28962,19 @@
         <v>1</v>
       </c>
       <c r="CR61" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="CS61" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT61" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU61" t="n">
         <v>17</v>
       </c>
-      <c r="CT61" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU61" t="n">
-        <v>21</v>
-      </c>
       <c r="CV61" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="CW61" t="n">
         <v>1</v>
@@ -28975,55 +28983,55 @@
         <v>4</v>
       </c>
       <c r="CY61" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CZ61" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="DA61" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="DB61" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="DC61" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.13</v>
+        <v>1.43</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.14</v>
+        <v>1.63</v>
       </c>
       <c r="DF61" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="DG61" t="n">
-        <v>1.33</v>
+        <v>2.33</v>
       </c>
       <c r="DH61" t="n">
         <v>1.14</v>
       </c>
       <c r="DI61" t="n">
-        <v>1.57</v>
+        <v>2.14</v>
       </c>
       <c r="DJ61" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="DK61" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="DL61" t="n">
-        <v>1.97</v>
+        <v>1.47</v>
       </c>
       <c r="DM61" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="DN61" t="n">
-        <v>3.31</v>
+        <v>2.92</v>
       </c>
       <c r="DO61" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -29032,10 +29040,10 @@
         <v>1</v>
       </c>
       <c r="DR61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT61" t="b">
         <v>0</v>
@@ -29047,34 +29055,34 @@
         <v>1</v>
       </c>
       <c r="DW61" t="n">
-        <v>16.47</v>
+        <v>19.43</v>
       </c>
       <c r="DX61" t="n">
-        <v>2.44</v>
+        <v>3.41</v>
       </c>
       <c r="DY61" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="DZ61" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA61" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EB61" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EC61" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="ED61" t="inlineStr"/>
@@ -29083,49 +29091,41 @@
       <c r="EG61" t="inlineStr"/>
       <c r="EH61" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="EI61" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="EJ61" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="EK61" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="EL61" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EM61" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EN61" t="inlineStr">
         <is>
-          <t>1.99</t>
-        </is>
-      </c>
-      <c r="EO61" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EP61" t="inlineStr">
-        <is>
-          <t>2.58</t>
-        </is>
-      </c>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EO61" t="inlineStr"/>
+      <c r="EP61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -29495,7 +29495,7 @@
         <v>3.61</v>
       </c>
       <c r="DO62" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -29898,7 +29898,7 @@
         <v>59</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="DE63" t="n">
         <v>0.44</v>
@@ -29931,7 +29931,7 @@
         <v>1.8</v>
       </c>
       <c r="DO63" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -30361,7 +30361,7 @@
         <v>1.86</v>
       </c>
       <c r="DE64" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DF64" t="n">
         <v>2</v>
@@ -30391,7 +30391,7 @@
         <v>2.75</v>
       </c>
       <c r="DO64" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP64" t="b">
         <v>0</v>
@@ -30879,7 +30879,7 @@
         <v>3.14</v>
       </c>
       <c r="DO65" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -31302,7 +31302,7 @@
         <v>100</v>
       </c>
       <c r="DD66" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DE66" t="n">
         <v>0.67</v>
@@ -31335,7 +31335,7 @@
         <v>2.54</v>
       </c>
       <c r="DO66" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -32247,7 +32247,7 @@
         <v>2.38</v>
       </c>
       <c r="DO68" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -32719,7 +32719,7 @@
         <v>2.57</v>
       </c>
       <c r="DO69" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -33163,7 +33163,7 @@
         <v>2.43</v>
       </c>
       <c r="DO70" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -33593,7 +33593,7 @@
         <v>1.86</v>
       </c>
       <c r="DE71" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DF71" t="n">
         <v>1.67</v>
@@ -33623,7 +33623,7 @@
         <v>2.46</v>
       </c>
       <c r="DO71" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP71" t="b">
         <v>0</v>
@@ -34065,7 +34065,7 @@
         <v>2.25</v>
       </c>
       <c r="DE72" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DF72" t="n">
         <v>2.25</v>
@@ -34095,7 +34095,7 @@
         <v>3.42</v>
       </c>
       <c r="DO72" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35014,7 +35014,7 @@
         <v>38</v>
       </c>
       <c r="DD74" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="DE74" t="n">
         <v>1.14</v>
@@ -35047,7 +35047,7 @@
         <v>2.54</v>
       </c>
       <c r="DO74" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -35926,7 +35926,7 @@
         <v>88</v>
       </c>
       <c r="DD76" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="DE76" t="n">
         <v>0.86</v>
@@ -35959,7 +35959,7 @@
         <v>3.09</v>
       </c>
       <c r="DO76" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -36417,7 +36417,7 @@
         <v>1.29</v>
       </c>
       <c r="DE77" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="DF77" t="n">
         <v>1.75</v>
@@ -36447,7 +36447,7 @@
         <v>2.97</v>
       </c>
       <c r="DO77" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP77" t="b">
         <v>0</v>
@@ -36895,7 +36895,7 @@
         <v>3.2</v>
       </c>
       <c r="DO78" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -37815,7 +37815,7 @@
         <v>1.87</v>
       </c>
       <c r="DO80" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP80" t="b">
         <v>0</v>
@@ -38287,7 +38287,7 @@
         <v>2.45</v>
       </c>
       <c r="DO81" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -38693,7 +38693,7 @@
         <v>1</v>
       </c>
       <c r="DE82" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DF82" t="n">
         <v>0.6</v>
@@ -38723,7 +38723,7 @@
         <v>2.79</v>
       </c>
       <c r="DO82" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -39175,7 +39175,7 @@
         <v>2.19</v>
       </c>
       <c r="DO83" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -39631,7 +39631,7 @@
         <v>3.27</v>
       </c>
       <c r="DO84" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -40046,7 +40046,7 @@
         <v>80</v>
       </c>
       <c r="DD85" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DE85" t="n">
         <v>1.63</v>
@@ -40079,7 +40079,7 @@
         <v>3.26</v>
       </c>
       <c r="DO85" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -40525,7 +40525,7 @@
         <v>0.89</v>
       </c>
       <c r="DE86" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DF86" t="n">
         <v>0.67</v>
@@ -40555,7 +40555,7 @@
         <v>2.29</v>
       </c>
       <c r="DO86" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -41027,7 +41027,7 @@
         <v>1.93</v>
       </c>
       <c r="DO87" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -41941,7 +41941,7 @@
         <v>1.86</v>
       </c>
       <c r="DE89" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DF89" t="n">
         <v>1.5</v>
@@ -41971,7 +41971,7 @@
         <v>2.67</v>
       </c>
       <c r="DO89" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -42410,7 +42410,7 @@
         <v>100</v>
       </c>
       <c r="DD90" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DE90" t="n">
         <v>1.63</v>
@@ -42443,7 +42443,7 @@
         <v>2.66</v>
       </c>
       <c r="DO90" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -42874,7 +42874,7 @@
         <v>80</v>
       </c>
       <c r="DD91" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="DE91" t="n">
         <v>0.57</v>
@@ -42907,7 +42907,7 @@
         <v>2.46</v>
       </c>
       <c r="DO91" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -43337,7 +43337,7 @@
         <v>2.22</v>
       </c>
       <c r="DE92" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DF92" t="n">
         <v>2.17</v>
@@ -43367,7 +43367,7 @@
         <v>2.78</v>
       </c>
       <c r="DO92" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -43797,7 +43797,7 @@
         <v>1.5</v>
       </c>
       <c r="DE93" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="DF93" t="n">
         <v>1.8</v>
@@ -43827,7 +43827,7 @@
         <v>2.49</v>
       </c>
       <c r="DO93" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -44274,7 +44274,7 @@
         <v>70</v>
       </c>
       <c r="DD94" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="DE94" t="n">
         <v>1.38</v>
@@ -44307,7 +44307,7 @@
         <v>3.2</v>
       </c>
       <c r="DO94" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -44749,7 +44749,7 @@
         <v>0.57</v>
       </c>
       <c r="DE95" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DF95" t="n">
         <v>0.8</v>
@@ -44779,7 +44779,7 @@
         <v>2.32</v>
       </c>
       <c r="DO95" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -45654,7 +45654,7 @@
         <v>100</v>
       </c>
       <c r="DD97" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DE97" t="n">
         <v>0.67</v>
@@ -45687,7 +45687,7 @@
         <v>3.18</v>
       </c>
       <c r="DO97" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -46589,7 +46589,7 @@
         <v>1.29</v>
       </c>
       <c r="DE99" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DF99" t="n">
         <v>1.6</v>
@@ -46619,7 +46619,7 @@
         <v>2.84</v>
       </c>
       <c r="DO99" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -47063,7 +47063,7 @@
         <v>2.59</v>
       </c>
       <c r="DO100" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -47519,7 +47519,7 @@
         <v>2.97</v>
       </c>
       <c r="DO101" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -47958,7 +47958,7 @@
         <v>77</v>
       </c>
       <c r="DD102" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DE102" t="n">
         <v>1.78</v>
@@ -47991,7 +47991,7 @@
         <v>3.06</v>
       </c>
       <c r="DO102" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP102" t="b">
         <v>0</v>
@@ -48427,7 +48427,7 @@
         <v>3.41</v>
       </c>
       <c r="DO103" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -48899,7 +48899,7 @@
         <v>3.31</v>
       </c>
       <c r="DO104" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -49811,7 +49811,7 @@
         <v>2.66</v>
       </c>
       <c r="DO106" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -50263,7 +50263,7 @@
         <v>2.61</v>
       </c>
       <c r="DO107" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP107" t="b">
         <v>0</v>
@@ -50751,7 +50751,7 @@
         <v>2.09</v>
       </c>
       <c r="DO108" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -50863,25 +50863,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F109" s="2" t="n">
         <v>45962.71875</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J109" t="n">
         <v>6</v>
@@ -50896,137 +50896,129 @@
         <v>2</v>
       </c>
       <c r="N109" t="n">
+        <v>1</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>6</v>
+      </c>
+      <c r="R109" t="n">
+        <v>2</v>
+      </c>
+      <c r="S109" t="n">
         <v>5</v>
-      </c>
-      <c r="O109" t="n">
-        <v>1</v>
-      </c>
-      <c r="P109" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q109" t="n">
-        <v>3</v>
-      </c>
-      <c r="R109" t="n">
-        <v>2</v>
-      </c>
-      <c r="S109" t="n">
-        <v>10</v>
       </c>
       <c r="T109" t="n">
         <v>6</v>
       </c>
       <c r="U109" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V109" t="n">
         <v>8</v>
       </c>
       <c r="W109" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X109" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Y109" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Z109" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA109" t="inlineStr">
-        <is>
-          <t>Stadion Central’nyj im. I.P. Chayka</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>ul. Suvorova, Peschanokopskoye</t>
-        </is>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="AA109" t="inlineStr"/>
+      <c r="AB109" t="inlineStr"/>
       <c r="AC109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD109" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE109" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AF109" t="n">
-        <v>3.47</v>
+        <v>3.9</v>
       </c>
       <c r="AG109" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AH109" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AI109" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AJ109" t="n">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="AK109" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AL109" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AM109" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="AN109" t="n">
-        <v>2.23</v>
+        <v>1.92</v>
       </c>
       <c r="AO109" t="n">
-        <v>2.32</v>
+        <v>2.65</v>
       </c>
       <c r="AP109" t="n">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AR109" t="n">
-        <v>2.77</v>
+        <v>2.6</v>
       </c>
       <c r="AS109" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="AT109" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AU109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW109" t="n">
         <v>0</v>
       </c>
       <c r="AX109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ109" t="n">
         <v>1</v>
       </c>
       <c r="BA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB109" t="n">
-        <v>668270</v>
+        <v>921</v>
       </c>
       <c r="BC109" t="n">
         <v>0</v>
       </c>
       <c r="BD109" t="n">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="BE109" t="n">
         <v>0</v>
@@ -51059,58 +51051,58 @@
         <v>-1</v>
       </c>
       <c r="BO109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ109" t="n">
         <v>1</v>
       </c>
       <c r="BR109" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BS109" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BT109" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BU109" t="n">
         <v>1</v>
       </c>
       <c r="BV109" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="BW109" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="BX109" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="BY109" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="BZ109" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="CA109" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="CB109" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="CC109" t="n">
         <v>0</v>
       </c>
       <c r="CD109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE109" t="n">
         <v>0</v>
       </c>
       <c r="CF109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG109" t="n">
         <v>0</v>
@@ -51125,7 +51117,7 @@
         <v>1</v>
       </c>
       <c r="CK109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL109" t="n">
         <v>0</v>
@@ -51146,82 +51138,82 @@
         <v>1</v>
       </c>
       <c r="CR109" t="n">
+        <v>28</v>
+      </c>
+      <c r="CS109" t="n">
+        <v>8</v>
+      </c>
+      <c r="CT109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU109" t="n">
         <v>20</v>
       </c>
-      <c r="CS109" t="n">
-        <v>15</v>
-      </c>
-      <c r="CT109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU109" t="n">
-        <v>15</v>
-      </c>
       <c r="CV109" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="CW109" t="n">
         <v>1</v>
       </c>
       <c r="CX109" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY109" t="n">
         <v>6</v>
       </c>
-      <c r="CY109" t="n">
-        <v>15</v>
-      </c>
       <c r="CZ109" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="DA109" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="DB109" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="DC109" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="DD109" t="n">
-        <v>1.29</v>
+        <v>2.71</v>
       </c>
       <c r="DE109" t="n">
         <v>1.63</v>
       </c>
       <c r="DF109" t="n">
-        <v>1.5</v>
+        <v>2.67</v>
       </c>
       <c r="DG109" t="n">
-        <v>1.17</v>
+        <v>1.86</v>
       </c>
       <c r="DH109" t="n">
-        <v>1.15</v>
+        <v>2</v>
       </c>
       <c r="DI109" t="n">
-        <v>0.92</v>
+        <v>2.08</v>
       </c>
       <c r="DJ109" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="DK109" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="DL109" t="n">
-        <v>1.47</v>
+        <v>1.9</v>
       </c>
       <c r="DM109" t="n">
-        <v>1.34</v>
+        <v>1.54</v>
       </c>
       <c r="DN109" t="n">
-        <v>2.81</v>
+        <v>3.44</v>
       </c>
       <c r="DO109" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
       </c>
       <c r="DQ109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR109" t="b">
         <v>0</v>
@@ -51239,79 +51231,63 @@
         <v>0</v>
       </c>
       <c r="DW109" t="n">
-        <v>5.41</v>
+        <v>14.13</v>
       </c>
       <c r="DX109" t="n">
-        <v>4.99</v>
+        <v>9.24</v>
       </c>
       <c r="DY109" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="DZ109" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="EA109" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EB109" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="EC109" t="inlineStr">
         <is>
-          <t>1.28</t>
-        </is>
-      </c>
-      <c r="ED109" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EE109" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="EF109" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="EG109" t="inlineStr">
-        <is>
-          <t>2.79</t>
-        </is>
-      </c>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="ED109" t="inlineStr"/>
+      <c r="EE109" t="inlineStr"/>
+      <c r="EF109" t="inlineStr"/>
+      <c r="EG109" t="inlineStr"/>
       <c r="EH109" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="EI109" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="EJ109" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="EK109" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="EL109" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EM109" t="inlineStr"/>
@@ -51335,25 +51311,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F110" s="2" t="n">
         <v>45962.71875</v>
       </c>
       <c r="G110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J110" t="n">
         <v>6</v>
@@ -51368,129 +51344,137 @@
         <v>2</v>
       </c>
       <c r="N110" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P110" t="n">
         <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R110" t="n">
         <v>2</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T110" t="n">
         <v>6</v>
       </c>
       <c r="U110" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V110" t="n">
         <v>8</v>
       </c>
       <c r="W110" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="X110" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Y110" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Z110" t="n">
-        <v>51</v>
-      </c>
-      <c r="AA110" t="inlineStr"/>
-      <c r="AB110" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>Stadion Central’nyj im. I.P. Chayka</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>ul. Suvorova, Peschanokopskoye</t>
+        </is>
+      </c>
       <c r="AC110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD110" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE110" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AF110" t="n">
-        <v>3.9</v>
+        <v>3.47</v>
       </c>
       <c r="AG110" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AH110" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AI110" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AJ110" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="AK110" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AL110" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AM110" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="AN110" t="n">
-        <v>1.92</v>
+        <v>2.23</v>
       </c>
       <c r="AO110" t="n">
-        <v>2.65</v>
+        <v>2.32</v>
       </c>
       <c r="AP110" t="n">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AR110" t="n">
-        <v>2.6</v>
+        <v>2.77</v>
       </c>
       <c r="AS110" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="AT110" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AU110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW110" t="n">
         <v>0</v>
       </c>
       <c r="AX110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ110" t="n">
         <v>1</v>
       </c>
       <c r="BA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB110" t="n">
-        <v>921</v>
+        <v>668270</v>
       </c>
       <c r="BC110" t="n">
         <v>0</v>
       </c>
       <c r="BD110" t="n">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="BE110" t="n">
         <v>0</v>
@@ -51523,58 +51507,58 @@
         <v>-1</v>
       </c>
       <c r="BO110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ110" t="n">
         <v>1</v>
       </c>
       <c r="BR110" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BS110" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BT110" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BU110" t="n">
         <v>1</v>
       </c>
       <c r="BV110" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="BW110" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="BX110" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="BY110" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="BZ110" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="CA110" t="n">
-        <v>0.98</v>
+        <v>0.91</v>
       </c>
       <c r="CB110" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="CC110" t="n">
         <v>0</v>
       </c>
       <c r="CD110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE110" t="n">
         <v>0</v>
       </c>
       <c r="CF110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG110" t="n">
         <v>0</v>
@@ -51589,7 +51573,7 @@
         <v>1</v>
       </c>
       <c r="CK110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL110" t="n">
         <v>0</v>
@@ -51610,82 +51594,82 @@
         <v>1</v>
       </c>
       <c r="CR110" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="CS110" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="CT110" t="n">
         <v>1</v>
       </c>
       <c r="CU110" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="CV110" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="CW110" t="n">
         <v>1</v>
       </c>
       <c r="CX110" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CY110" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="CZ110" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="DA110" t="n">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="DB110" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="DC110" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="DD110" t="n">
-        <v>2.71</v>
+        <v>1.29</v>
       </c>
       <c r="DE110" t="n">
         <v>1.63</v>
       </c>
       <c r="DF110" t="n">
-        <v>2.67</v>
+        <v>1.5</v>
       </c>
       <c r="DG110" t="n">
-        <v>1.86</v>
+        <v>1.17</v>
       </c>
       <c r="DH110" t="n">
-        <v>2</v>
+        <v>1.15</v>
       </c>
       <c r="DI110" t="n">
-        <v>2.08</v>
+        <v>0.92</v>
       </c>
       <c r="DJ110" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="DK110" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="DL110" t="n">
-        <v>1.9</v>
+        <v>1.47</v>
       </c>
       <c r="DM110" t="n">
-        <v>1.54</v>
+        <v>1.34</v>
       </c>
       <c r="DN110" t="n">
-        <v>3.44</v>
+        <v>2.81</v>
       </c>
       <c r="DO110" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
       </c>
       <c r="DQ110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR110" t="b">
         <v>0</v>
@@ -51703,63 +51687,79 @@
         <v>0</v>
       </c>
       <c r="DW110" t="n">
-        <v>14.13</v>
+        <v>5.41</v>
       </c>
       <c r="DX110" t="n">
-        <v>9.24</v>
+        <v>4.99</v>
       </c>
       <c r="DY110" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="DZ110" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA110" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EB110" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="EC110" t="inlineStr">
         <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="ED110" t="inlineStr"/>
-      <c r="EE110" t="inlineStr"/>
-      <c r="EF110" t="inlineStr"/>
-      <c r="EG110" t="inlineStr"/>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="ED110" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EE110" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EF110" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="EG110" t="inlineStr">
+        <is>
+          <t>2.79</t>
+        </is>
+      </c>
       <c r="EH110" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EI110" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="EJ110" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="EK110" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="EL110" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EM110" t="inlineStr"/>
@@ -53063,7 +53063,7 @@
         <v>3.33</v>
       </c>
       <c r="DO113" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -53494,7 +53494,7 @@
         <v>86</v>
       </c>
       <c r="DD114" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DE114" t="n">
         <v>1.63</v>
@@ -53527,7 +53527,7 @@
         <v>3.16</v>
       </c>
       <c r="DO114" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP114" t="b">
         <v>1</v>
@@ -53619,12 +53619,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F115" s="2" t="n">
@@ -53634,128 +53634,128 @@
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J115" t="n">
+        <v>2</v>
+      </c>
+      <c r="K115" t="n">
+        <v>10</v>
+      </c>
+      <c r="L115" t="n">
+        <v>12</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1</v>
+      </c>
+      <c r="N115" t="n">
+        <v>3</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" t="n">
+        <v>2</v>
+      </c>
+      <c r="S115" t="n">
         <v>7</v>
       </c>
-      <c r="K115" t="n">
-        <v>6</v>
-      </c>
-      <c r="L115" t="n">
+      <c r="T115" t="n">
         <v>13</v>
       </c>
-      <c r="M115" t="n">
-        <v>1</v>
-      </c>
-      <c r="N115" t="n">
-        <v>1</v>
-      </c>
-      <c r="O115" t="n">
-        <v>0</v>
-      </c>
-      <c r="P115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q115" t="n">
-        <v>3</v>
-      </c>
-      <c r="R115" t="n">
-        <v>2</v>
-      </c>
-      <c r="S115" t="n">
-        <v>12</v>
-      </c>
-      <c r="T115" t="n">
-        <v>9</v>
-      </c>
       <c r="U115" t="n">
+        <v>7</v>
+      </c>
+      <c r="V115" t="n">
         <v>15</v>
-      </c>
-      <c r="V115" t="n">
-        <v>11</v>
       </c>
       <c r="W115" t="n">
         <v>12</v>
       </c>
       <c r="X115" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y115" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="Z115" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>Anzhi-Arena</t>
+          <t>Stadion Nizhny Novgorod</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>, Kaspiysk</t>
+          <t>ul. Dolzhanskaya, Nizhniy Novgorod</t>
         </is>
       </c>
       <c r="AC115" t="n">
         <v>1</v>
       </c>
       <c r="AD115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE115" t="n">
-        <v>3.83</v>
+        <v>2.8</v>
       </c>
       <c r="AF115" t="n">
-        <v>3.03</v>
+        <v>3.1</v>
       </c>
       <c r="AG115" t="n">
-        <v>2.09</v>
+        <v>2.56</v>
       </c>
       <c r="AH115" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AI115" t="n">
         <v>2.2</v>
       </c>
       <c r="AJ115" t="n">
-        <v>4.55</v>
+        <v>3.84</v>
       </c>
       <c r="AK115" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AL115" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AM115" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AN115" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="AO115" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AR115" t="n">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="AS115" t="n">
-        <v>2.43</v>
+        <v>2.73</v>
       </c>
       <c r="AT115" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AU115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV115" t="n">
         <v>0</v>
@@ -53767,22 +53767,22 @@
         <v>0</v>
       </c>
       <c r="AY115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA115" t="n">
         <v>0</v>
       </c>
       <c r="BB115" t="n">
-        <v>101</v>
+        <v>-1</v>
       </c>
       <c r="BC115" t="n">
         <v>0</v>
       </c>
       <c r="BD115" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="BE115" t="n">
         <v>0</v>
@@ -53818,7 +53818,7 @@
         <v>0</v>
       </c>
       <c r="BP115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ115" t="n">
         <v>1</v>
@@ -53827,7 +53827,7 @@
         <v>1</v>
       </c>
       <c r="BS115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT115" t="n">
         <v>2</v>
@@ -53836,145 +53836,145 @@
         <v>1</v>
       </c>
       <c r="BV115" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW115" t="n">
+        <v>43</v>
+      </c>
+      <c r="BX115" t="n">
+        <v>80</v>
+      </c>
+      <c r="BY115" t="n">
+        <v>78</v>
+      </c>
+      <c r="BZ115" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="CA115" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CB115" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="CC115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR115" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS115" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU115" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV115" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX115" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY115" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ115" t="n">
         <v>54</v>
       </c>
-      <c r="BW115" t="n">
-        <v>45</v>
-      </c>
-      <c r="BX115" t="n">
-        <v>96</v>
-      </c>
-      <c r="BY115" t="n">
-        <v>88</v>
-      </c>
-      <c r="BZ115" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="CA115" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="CB115" t="n">
+      <c r="DA115" t="n">
+        <v>69</v>
+      </c>
+      <c r="DB115" t="n">
+        <v>31</v>
+      </c>
+      <c r="DC115" t="n">
+        <v>77</v>
+      </c>
+      <c r="DD115" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DE115" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DF115" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG115" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DH115" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DI115" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DJ115" t="n">
+        <v>47</v>
+      </c>
+      <c r="DK115" t="n">
+        <v>31</v>
+      </c>
+      <c r="DL115" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DM115" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DN115" t="n">
         <v>2.71</v>
       </c>
-      <c r="CC115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI115" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ115" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM115" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CN115" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CO115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ115" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR115" t="n">
-        <v>26</v>
-      </c>
-      <c r="CS115" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT115" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU115" t="n">
-        <v>13</v>
-      </c>
-      <c r="CV115" t="n">
-        <v>12</v>
-      </c>
-      <c r="CW115" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX115" t="n">
-        <v>13</v>
-      </c>
-      <c r="CY115" t="n">
-        <v>12</v>
-      </c>
-      <c r="CZ115" t="n">
-        <v>25</v>
-      </c>
-      <c r="DA115" t="n">
-        <v>62</v>
-      </c>
-      <c r="DB115" t="n">
-        <v>17</v>
-      </c>
-      <c r="DC115" t="n">
-        <v>70</v>
-      </c>
-      <c r="DD115" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DE115" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="DF115" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DG115" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DH115" t="n">
-        <v>1</v>
-      </c>
-      <c r="DI115" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="DJ115" t="n">
-        <v>75</v>
-      </c>
-      <c r="DK115" t="n">
-        <v>38</v>
-      </c>
-      <c r="DL115" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="DM115" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="DN115" t="n">
-        <v>2.75</v>
-      </c>
       <c r="DO115" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ115" t="b">
         <v>0</v>
@@ -53995,59 +53995,63 @@
         <v>0</v>
       </c>
       <c r="DW115" t="n">
-        <v>14.21</v>
+        <v>8.43</v>
       </c>
       <c r="DX115" t="n">
-        <v>4.28</v>
+        <v>6.4</v>
       </c>
       <c r="DY115" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="DZ115" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="EA115" t="inlineStr"/>
-      <c r="EB115" t="inlineStr"/>
-      <c r="EC115" t="inlineStr"/>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA115" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EB115" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="EC115" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
       <c r="ED115" t="inlineStr"/>
-      <c r="EE115" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EF115" t="inlineStr">
-        <is>
-          <t>2.62</t>
-        </is>
-      </c>
+      <c r="EE115" t="inlineStr"/>
+      <c r="EF115" t="inlineStr"/>
       <c r="EG115" t="inlineStr"/>
       <c r="EH115" t="inlineStr">
         <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="EI115" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EJ115" t="inlineStr">
+        <is>
           <t>3.30</t>
         </is>
       </c>
-      <c r="EI115" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="EJ115" t="inlineStr">
-        <is>
-          <t>3.23</t>
-        </is>
-      </c>
       <c r="EK115" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EL115" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EM115" t="inlineStr"/>
@@ -54071,12 +54075,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F116" s="2" t="n">
@@ -54086,347 +54090,347 @@
         <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J116" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K116" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L116" t="n">
+        <v>13</v>
+      </c>
+      <c r="M116" t="n">
+        <v>1</v>
+      </c>
+      <c r="N116" t="n">
+        <v>1</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>3</v>
+      </c>
+      <c r="R116" t="n">
+        <v>2</v>
+      </c>
+      <c r="S116" t="n">
         <v>12</v>
       </c>
-      <c r="M116" t="n">
-        <v>1</v>
-      </c>
-      <c r="N116" t="n">
-        <v>3</v>
-      </c>
-      <c r="O116" t="n">
-        <v>0</v>
-      </c>
-      <c r="P116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
-      <c r="R116" t="n">
-        <v>2</v>
-      </c>
-      <c r="S116" t="n">
-        <v>7</v>
-      </c>
       <c r="T116" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="U116" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="V116" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="W116" t="n">
         <v>12</v>
       </c>
       <c r="X116" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y116" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="Z116" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>Stadion Nizhny Novgorod</t>
+          <t>Anzhi-Arena</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>ul. Dolzhanskaya, Nizhniy Novgorod</t>
+          <t>, Kaspiysk</t>
         </is>
       </c>
       <c r="AC116" t="n">
         <v>1</v>
       </c>
       <c r="AD116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE116" t="n">
-        <v>2.8</v>
+        <v>3.83</v>
       </c>
       <c r="AF116" t="n">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="AG116" t="n">
-        <v>2.56</v>
+        <v>2.09</v>
       </c>
       <c r="AH116" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AI116" t="n">
         <v>2.2</v>
       </c>
       <c r="AJ116" t="n">
-        <v>3.84</v>
+        <v>4.55</v>
       </c>
       <c r="AK116" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AL116" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AM116" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AN116" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="AO116" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AR116" t="n">
-        <v>3.2</v>
+        <v>3.52</v>
       </c>
       <c r="AS116" t="n">
-        <v>2.73</v>
+        <v>2.43</v>
       </c>
       <c r="AT116" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AU116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB116" t="n">
+        <v>101</v>
+      </c>
+      <c r="BC116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD116" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT116" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV116" t="n">
+        <v>54</v>
+      </c>
+      <c r="BW116" t="n">
+        <v>45</v>
+      </c>
+      <c r="BX116" t="n">
+        <v>96</v>
+      </c>
+      <c r="BY116" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ116" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CA116" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="CB116" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="CC116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR116" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS116" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU116" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV116" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX116" t="n">
+        <v>13</v>
+      </c>
+      <c r="CY116" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ116" t="n">
+        <v>25</v>
+      </c>
+      <c r="DA116" t="n">
+        <v>62</v>
+      </c>
+      <c r="DB116" t="n">
+        <v>17</v>
+      </c>
+      <c r="DC116" t="n">
+        <v>70</v>
+      </c>
+      <c r="DD116" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE116" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DF116" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DG116" t="n">
         <v>1.33</v>
       </c>
-      <c r="AU116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB116" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BC116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD116" t="n">
-        <v>47</v>
-      </c>
-      <c r="BE116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF116" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BG116" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BH116" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI116" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BJ116" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BK116" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BL116" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BM116" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BN116" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BO116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP116" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ116" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR116" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS116" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT116" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU116" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV116" t="n">
-        <v>46</v>
-      </c>
-      <c r="BW116" t="n">
-        <v>43</v>
-      </c>
-      <c r="BX116" t="n">
-        <v>80</v>
-      </c>
-      <c r="BY116" t="n">
-        <v>78</v>
-      </c>
-      <c r="BZ116" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="CA116" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="CB116" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="CC116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM116" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CN116" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CO116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR116" t="n">
+      <c r="DH116" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI116" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DJ116" t="n">
+        <v>75</v>
+      </c>
+      <c r="DK116" t="n">
+        <v>38</v>
+      </c>
+      <c r="DL116" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DM116" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DN116" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DO116" t="n">
         <v>16</v>
       </c>
-      <c r="CS116" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU116" t="n">
-        <v>14</v>
-      </c>
-      <c r="CV116" t="n">
-        <v>15</v>
-      </c>
-      <c r="CW116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX116" t="n">
-        <v>5</v>
-      </c>
-      <c r="CY116" t="n">
-        <v>6</v>
-      </c>
-      <c r="CZ116" t="n">
-        <v>54</v>
-      </c>
-      <c r="DA116" t="n">
-        <v>69</v>
-      </c>
-      <c r="DB116" t="n">
-        <v>31</v>
-      </c>
-      <c r="DC116" t="n">
-        <v>77</v>
-      </c>
-      <c r="DD116" t="n">
-        <v>1</v>
-      </c>
-      <c r="DE116" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="DF116" t="n">
-        <v>1</v>
-      </c>
-      <c r="DG116" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="DH116" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DI116" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="DJ116" t="n">
-        <v>47</v>
-      </c>
-      <c r="DK116" t="n">
-        <v>31</v>
-      </c>
-      <c r="DL116" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="DM116" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="DN116" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="DO116" t="n">
-        <v>15</v>
-      </c>
       <c r="DP116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ116" t="b">
         <v>0</v>
@@ -54447,63 +54451,59 @@
         <v>0</v>
       </c>
       <c r="DW116" t="n">
-        <v>8.43</v>
+        <v>14.21</v>
       </c>
       <c r="DX116" t="n">
-        <v>6.4</v>
+        <v>4.28</v>
       </c>
       <c r="DY116" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="DZ116" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="EA116" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="EB116" t="inlineStr">
-        <is>
-          <t>4.02</t>
-        </is>
-      </c>
-      <c r="EC116" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="EA116" t="inlineStr"/>
+      <c r="EB116" t="inlineStr"/>
+      <c r="EC116" t="inlineStr"/>
       <c r="ED116" t="inlineStr"/>
-      <c r="EE116" t="inlineStr"/>
-      <c r="EF116" t="inlineStr"/>
+      <c r="EE116" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EF116" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
       <c r="EG116" t="inlineStr"/>
       <c r="EH116" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="EI116" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EJ116" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="EK116" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EL116" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EM116" t="inlineStr"/>
@@ -54849,7 +54849,7 @@
         <v>0.57</v>
       </c>
       <c r="DE117" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DF117" t="n">
         <v>0.67</v>
@@ -54879,7 +54879,7 @@
         <v>2.24</v>
       </c>
       <c r="DO117" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -55310,10 +55310,10 @@
         <v>69</v>
       </c>
       <c r="DD118" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="DE118" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DF118" t="n">
         <v>1.33</v>
@@ -55343,7 +55343,7 @@
         <v>2.53</v>
       </c>
       <c r="DO118" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -55750,7 +55750,7 @@
         <v>75</v>
       </c>
       <c r="DD119" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="DE119" t="n">
         <v>0.57</v>
@@ -55783,7 +55783,7 @@
         <v>3.04</v>
       </c>
       <c r="DO119" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -56697,7 +56697,7 @@
         <v>1.86</v>
       </c>
       <c r="DE121" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="DF121" t="n">
         <v>2</v>
@@ -56727,7 +56727,7 @@
         <v>2.71</v>
       </c>
       <c r="DO121" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -57666,36 +57666,48 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="EA123" t="inlineStr"/>
-      <c r="EB123" t="inlineStr"/>
-      <c r="EC123" t="inlineStr"/>
+      <c r="EA123" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EB123" t="inlineStr">
+        <is>
+          <t>3.97</t>
+        </is>
+      </c>
+      <c r="EC123" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
       <c r="ED123" t="inlineStr"/>
       <c r="EE123" t="inlineStr"/>
       <c r="EF123" t="inlineStr"/>
       <c r="EG123" t="inlineStr"/>
       <c r="EH123" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="EI123" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="EJ123" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="EK123" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EL123" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EM123" t="inlineStr">
@@ -57705,17 +57717,17 @@
       </c>
       <c r="EN123" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="EO123" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EP123" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.49</t>
         </is>
       </c>
     </row>
@@ -57952,25 +57964,25 @@
         <v>1</v>
       </c>
       <c r="BV124" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="BW124" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="BX124" t="n">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="BY124" t="n">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="BZ124" t="n">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="CA124" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="CB124" t="n">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="CC124" t="n">
         <v>0</v>
@@ -58030,7 +58042,7 @@
         <v>14</v>
       </c>
       <c r="CV124" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CW124" t="n">
         <v>1</v>
@@ -58128,46 +58140,62 @@
       </c>
       <c r="EA124" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EB124" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="EC124" t="inlineStr">
         <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="ED124" t="inlineStr"/>
-      <c r="EE124" t="inlineStr"/>
-      <c r="EF124" t="inlineStr"/>
-      <c r="EG124" t="inlineStr"/>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="ED124" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EE124" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EF124" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="EG124" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
       <c r="EH124" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="EI124" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="EJ124" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="EK124" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EL124" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EM124" t="inlineStr"/>
@@ -58239,13 +58267,13 @@
         <v>0</v>
       </c>
       <c r="S125" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T125" t="n">
         <v>7</v>
       </c>
       <c r="U125" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V125" t="n">
         <v>7</v>
@@ -58408,25 +58436,25 @@
         <v>1</v>
       </c>
       <c r="BV125" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="BW125" t="n">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="BX125" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="BY125" t="n">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="BZ125" t="n">
-        <v>0.95</v>
+        <v>1.18</v>
       </c>
       <c r="CA125" t="n">
-        <v>0.55</v>
+        <v>0.78</v>
       </c>
       <c r="CB125" t="n">
-        <v>1.5</v>
+        <v>1.96</v>
       </c>
       <c r="CC125" t="n">
         <v>0</v>
@@ -58483,10 +58511,10 @@
         <v>1</v>
       </c>
       <c r="CU125" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="CV125" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="CW125" t="n">
         <v>1</v>
@@ -58584,17 +58612,17 @@
       </c>
       <c r="EA125" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="EB125" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="EC125" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="ED125" t="inlineStr"/>
@@ -58603,33 +58631,1877 @@
       <c r="EG125" t="inlineStr"/>
       <c r="EH125" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="EI125" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="EJ125" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="EK125" t="inlineStr">
         <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EL125" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EM125" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EN125" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="EO125" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EP125" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>16</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Krylya Sovetov</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Rostov</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>45984.41666666666</v>
+      </c>
+      <c r="G126" t="n">
+        <v>2</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>2</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
+        <v>5</v>
+      </c>
+      <c r="L126" t="n">
+        <v>5</v>
+      </c>
+      <c r="M126" t="n">
+        <v>2</v>
+      </c>
+      <c r="N126" t="n">
+        <v>1</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>3</v>
+      </c>
+      <c r="R126" t="n">
+        <v>4</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0</v>
+      </c>
+      <c r="T126" t="n">
+        <v>13</v>
+      </c>
+      <c r="U126" t="n">
+        <v>3</v>
+      </c>
+      <c r="V126" t="n">
+        <v>17</v>
+      </c>
+      <c r="W126" t="n">
+        <v>18</v>
+      </c>
+      <c r="X126" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>62</v>
+      </c>
+      <c r="AA126" t="inlineStr"/>
+      <c r="AB126" t="inlineStr"/>
+      <c r="AC126" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>928</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>22</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>78</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>72</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>113</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU126" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV126" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX126" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY126" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ126" t="n">
+        <v>27</v>
+      </c>
+      <c r="DA126" t="n">
+        <v>69</v>
+      </c>
+      <c r="DB126" t="n">
+        <v>21</v>
+      </c>
+      <c r="DC126" t="n">
+        <v>54</v>
+      </c>
+      <c r="DD126" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE126" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF126" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DG126" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DH126" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="DI126" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DJ126" t="n">
+        <v>73</v>
+      </c>
+      <c r="DK126" t="n">
+        <v>32</v>
+      </c>
+      <c r="DL126" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DM126" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DN126" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="DO126" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP126" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ126" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW126" t="inlineStr"/>
+      <c r="DX126" t="inlineStr"/>
+      <c r="DY126" t="inlineStr"/>
+      <c r="DZ126" t="inlineStr"/>
+      <c r="EA126" t="inlineStr"/>
+      <c r="EB126" t="inlineStr"/>
+      <c r="EC126" t="inlineStr"/>
+      <c r="ED126" t="inlineStr"/>
+      <c r="EE126" t="inlineStr"/>
+      <c r="EF126" t="inlineStr"/>
+      <c r="EG126" t="inlineStr"/>
+      <c r="EH126" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="EI126" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EJ126" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="EK126" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EL126" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EM126" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EN126" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EO126" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EP126" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>16</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Olimpiyets</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Zenit</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>45984.51041666666</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>2</v>
+      </c>
+      <c r="I127" t="n">
+        <v>2</v>
+      </c>
+      <c r="J127" t="n">
+        <v>7</v>
+      </c>
+      <c r="K127" t="n">
+        <v>4</v>
+      </c>
+      <c r="L127" t="n">
+        <v>11</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" t="n">
+        <v>2</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>3</v>
+      </c>
+      <c r="R127" t="n">
+        <v>4</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="n">
+        <v>3</v>
+      </c>
+      <c r="U127" t="n">
+        <v>13</v>
+      </c>
+      <c r="V127" t="n">
+        <v>7</v>
+      </c>
+      <c r="W127" t="n">
+        <v>22</v>
+      </c>
+      <c r="X127" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>35</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>Stadion Nizhny Novgorod</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>ul. Dolzhanskaya, Nizhniy Novgorod</t>
+        </is>
+      </c>
+      <c r="AC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>921</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>53</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>49</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>82</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>109</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU127" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV127" t="n">
+        <v>25</v>
+      </c>
+      <c r="CW127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX127" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY127" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ127" t="n">
+        <v>44</v>
+      </c>
+      <c r="DA127" t="n">
+        <v>69</v>
+      </c>
+      <c r="DB127" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC127" t="n">
+        <v>63</v>
+      </c>
+      <c r="DD127" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DE127" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DF127" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG127" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DH127" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="DI127" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ127" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK127" t="n">
+        <v>32</v>
+      </c>
+      <c r="DL127" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DM127" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DN127" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="DO127" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP127" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ127" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW127" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DX127" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="DY127" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="DZ127" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="EA127" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EB127" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="EC127" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="ED127" t="inlineStr"/>
+      <c r="EE127" t="inlineStr"/>
+      <c r="EF127" t="inlineStr"/>
+      <c r="EG127" t="inlineStr"/>
+      <c r="EH127" t="inlineStr">
+        <is>
+          <t>8.92</t>
+        </is>
+      </c>
+      <c r="EI127" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EJ127" t="inlineStr">
+        <is>
+          <t>4.93</t>
+        </is>
+      </c>
+      <c r="EK127" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EL127" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EM127" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EN127" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EO127" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EP127" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>16</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Dinamo Moskva</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Makhachkala</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>45984.60416666666</v>
+      </c>
+      <c r="G128" t="n">
+        <v>3</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>3</v>
+      </c>
+      <c r="J128" t="n">
+        <v>4</v>
+      </c>
+      <c r="K128" t="n">
+        <v>3</v>
+      </c>
+      <c r="L128" t="n">
+        <v>7</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" t="n">
+        <v>2</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>5</v>
+      </c>
+      <c r="R128" t="n">
+        <v>1</v>
+      </c>
+      <c r="S128" t="n">
+        <v>4</v>
+      </c>
+      <c r="T128" t="n">
+        <v>3</v>
+      </c>
+      <c r="U128" t="n">
+        <v>9</v>
+      </c>
+      <c r="V128" t="n">
+        <v>4</v>
+      </c>
+      <c r="W128" t="n">
+        <v>13</v>
+      </c>
+      <c r="X128" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA128" t="inlineStr"/>
+      <c r="AB128" t="inlineStr"/>
+      <c r="AC128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>935</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>52</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>51</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>51</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>95</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>99</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>2</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU128" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV128" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX128" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY128" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ128" t="n">
+        <v>45</v>
+      </c>
+      <c r="DA128" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB128" t="n">
+        <v>40</v>
+      </c>
+      <c r="DC128" t="n">
+        <v>87</v>
+      </c>
+      <c r="DD128" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DE128" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DF128" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DG128" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="DH128" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DI128" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="DJ128" t="n">
+        <v>56</v>
+      </c>
+      <c r="DK128" t="n">
+        <v>21</v>
+      </c>
+      <c r="DL128" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DM128" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DN128" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="DO128" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP128" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ128" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR128" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW128" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="DX128" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="DY128" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="DZ128" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="EA128" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EB128" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="EC128" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="ED128" t="inlineStr"/>
+      <c r="EE128" t="inlineStr"/>
+      <c r="EF128" t="inlineStr"/>
+      <c r="EG128" t="inlineStr"/>
+      <c r="EH128" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EI128" t="inlineStr">
+        <is>
+          <t>5.58</t>
+        </is>
+      </c>
+      <c r="EJ128" t="inlineStr">
+        <is>
+          <t>4.14</t>
+        </is>
+      </c>
+      <c r="EK128" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EL128" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EM128" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EN128" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EO128" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EP128" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>16</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Lokomotiv Moskva</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Krasnodar</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>45984.69791666666</v>
+      </c>
+      <c r="G129" t="n">
+        <v>1</v>
+      </c>
+      <c r="H129" t="n">
+        <v>1</v>
+      </c>
+      <c r="I129" t="n">
+        <v>2</v>
+      </c>
+      <c r="J129" t="n">
+        <v>1</v>
+      </c>
+      <c r="K129" t="n">
+        <v>4</v>
+      </c>
+      <c r="L129" t="n">
+        <v>5</v>
+      </c>
+      <c r="M129" t="n">
+        <v>2</v>
+      </c>
+      <c r="N129" t="n">
+        <v>1</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>2</v>
+      </c>
+      <c r="R129" t="n">
+        <v>9</v>
+      </c>
+      <c r="S129" t="n">
+        <v>13</v>
+      </c>
+      <c r="T129" t="n">
+        <v>13</v>
+      </c>
+      <c r="U129" t="n">
+        <v>15</v>
+      </c>
+      <c r="V129" t="n">
+        <v>22</v>
+      </c>
+      <c r="W129" t="n">
+        <v>25</v>
+      </c>
+      <c r="X129" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>37</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>63</v>
+      </c>
+      <c r="AA129" t="inlineStr"/>
+      <c r="AB129" t="inlineStr"/>
+      <c r="AC129" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>53</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>46</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>83</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>93</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU129" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV129" t="n">
+        <v>26</v>
+      </c>
+      <c r="CW129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX129" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY129" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ129" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA129" t="n">
+        <v>71</v>
+      </c>
+      <c r="DB129" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC129" t="n">
+        <v>64</v>
+      </c>
+      <c r="DD129" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DE129" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF129" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="DG129" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DH129" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI129" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DJ129" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK129" t="n">
+        <v>29</v>
+      </c>
+      <c r="DL129" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="DM129" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DN129" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="DO129" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP129" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ129" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR129" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS129" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT129" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU129" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV129" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW129" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DX129" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="DY129" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="DZ129" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="EA129" t="inlineStr"/>
+      <c r="EB129" t="inlineStr"/>
+      <c r="EC129" t="inlineStr"/>
+      <c r="ED129" t="inlineStr"/>
+      <c r="EE129" t="inlineStr"/>
+      <c r="EF129" t="inlineStr"/>
+      <c r="EG129" t="inlineStr"/>
+      <c r="EH129" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="EI129" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="EJ129" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="EK129" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="EL129" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EM129" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EN129" t="inlineStr">
+        <is>
           <t>1.93</t>
         </is>
       </c>
-      <c r="EL125" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EM125" t="inlineStr"/>
-      <c r="EN125" t="inlineStr"/>
-      <c r="EO125" t="inlineStr"/>
-      <c r="EP125" t="inlineStr"/>
+      <c r="EO129" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EP129" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
+++ b/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP129" headerRowCount="1">
-  <autoFilter ref="A1:EP129"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP131" headerRowCount="1">
+  <autoFilter ref="A1:EP131"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP129"/>
+  <dimension ref="A1:EP131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.8" customWidth="1" min="1" max="1"/>
@@ -2242,7 +2242,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DE3" t="n">
         <v>0.63</v>
@@ -5055,7 +5055,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP9" t="b">
         <v>0</v>
@@ -5473,7 +5473,7 @@
         <v>1.5</v>
       </c>
       <c r="DE10" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -7754,7 +7754,7 @@
         <v>0</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE15" t="n">
         <v>0.67</v>
@@ -9323,70 +9323,70 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
         <v>45871.72916666666</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>7</v>
+      </c>
+      <c r="L19" t="n">
+        <v>11</v>
+      </c>
+      <c r="M19" t="n">
         <v>5</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>5</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>4</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>10</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6</v>
+      </c>
+      <c r="S19" t="n">
         <v>3</v>
       </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>5</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
+        <v>8</v>
+      </c>
+      <c r="U19" t="n">
         <v>13</v>
       </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>18</v>
-      </c>
       <c r="V19" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="W19" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="X19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y19" t="n">
         <v>56</v>
@@ -9396,91 +9396,91 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Stadion FK Krasnodar</t>
+          <t>Akhmat Arena</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>ul. Vostochno-Kruglikovskaya 126, Krasnodar</t>
+          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
         </is>
       </c>
       <c r="AC19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD19" t="n">
         <v>4</v>
       </c>
-      <c r="AD19" t="n">
-        <v>3</v>
-      </c>
       <c r="AE19" t="n">
-        <v>1.81</v>
+        <v>5.84</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.54</v>
+        <v>1.65</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB19" t="n">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="BC19" t="n">
         <v>0</v>
@@ -9519,46 +9519,46 @@
         <v>-1</v>
       </c>
       <c r="BO19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ19" t="n">
         <v>3</v>
       </c>
       <c r="BR19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BS19" t="n">
         <v>3</v>
       </c>
       <c r="BT19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BU19" t="n">
         <v>1</v>
       </c>
       <c r="BV19" t="n">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="BW19" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="BX19" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="BY19" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="CA19" t="n">
-        <v>0.45</v>
+        <v>1.54</v>
       </c>
       <c r="CB19" t="n">
-        <v>2.43</v>
+        <v>3.43</v>
       </c>
       <c r="CC19" t="n">
         <v>0</v>
@@ -9600,64 +9600,64 @@
         <v>0</v>
       </c>
       <c r="CP19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ19" t="n">
         <v>1</v>
       </c>
       <c r="CR19" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="CS19" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="CT19" t="n">
         <v>1</v>
       </c>
       <c r="CU19" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="CV19" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="CW19" t="n">
         <v>1</v>
       </c>
       <c r="CX19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="CY19" t="n">
         <v>7</v>
       </c>
       <c r="CZ19" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DA19" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DB19" t="n">
         <v>0</v>
       </c>
       <c r="DC19" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.25</v>
+        <v>0.89</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.14</v>
+        <v>1.63</v>
       </c>
       <c r="DF19" t="n">
         <v>0</v>
       </c>
       <c r="DG19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DH19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="DI19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DJ19" t="n">
         <v>0</v>
@@ -9666,13 +9666,13 @@
         <v>0</v>
       </c>
       <c r="DL19" t="n">
-        <v>1.82</v>
+        <v>1.17</v>
       </c>
       <c r="DM19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.82</v>
+        <v>2.42</v>
       </c>
       <c r="DO19" t="n">
         <v>16</v>
@@ -9681,83 +9681,63 @@
         <v>1</v>
       </c>
       <c r="DQ19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU19" t="b">
         <v>0</v>
       </c>
       <c r="DV19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW19" t="n">
-        <v>31.6</v>
+        <v>37.47</v>
       </c>
       <c r="DX19" t="n">
-        <v>4.87</v>
+        <v>6.85</v>
       </c>
       <c r="DY19" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="DZ19" t="inlineStr">
         <is>
-          <t>96%</t>
-        </is>
-      </c>
-      <c r="EA19" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="EB19" t="inlineStr">
-        <is>
-          <t>2.82</t>
-        </is>
-      </c>
-      <c r="EC19" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="EA19" t="inlineStr"/>
+      <c r="EB19" t="inlineStr"/>
+      <c r="EC19" t="inlineStr"/>
       <c r="ED19" t="inlineStr"/>
       <c r="EE19" t="inlineStr"/>
       <c r="EF19" t="inlineStr"/>
       <c r="EG19" t="inlineStr"/>
       <c r="EH19" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="EI19" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EJ19" t="inlineStr">
         <is>
-          <t>3.69</t>
-        </is>
-      </c>
-      <c r="EK19" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
-      <c r="EL19" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
+          <t>4.32</t>
+        </is>
+      </c>
+      <c r="EK19" t="inlineStr"/>
+      <c r="EL19" t="inlineStr"/>
       <c r="EM19" t="inlineStr"/>
       <c r="EN19" t="inlineStr"/>
       <c r="EO19" t="inlineStr"/>
@@ -9779,70 +9759,70 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
         <v>45871.72916666666</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>5</v>
+      </c>
+      <c r="M20" t="n">
+        <v>4</v>
+      </c>
+      <c r="N20" t="n">
         <v>3</v>
       </c>
-      <c r="I20" t="n">
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>5</v>
       </c>
-      <c r="J20" t="n">
-        <v>4</v>
-      </c>
-      <c r="K20" t="n">
-        <v>7</v>
-      </c>
-      <c r="L20" t="n">
-        <v>11</v>
-      </c>
-      <c r="M20" t="n">
-        <v>5</v>
-      </c>
-      <c r="N20" t="n">
-        <v>4</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>10</v>
-      </c>
       <c r="R20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
+        <v>13</v>
+      </c>
+      <c r="T20" t="n">
         <v>3</v>
       </c>
-      <c r="T20" t="n">
-        <v>8</v>
-      </c>
       <c r="U20" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="V20" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="W20" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="X20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y20" t="n">
         <v>56</v>
@@ -9852,91 +9832,91 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Akhmat Arena</t>
+          <t>Stadion FK Krasnodar</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
+          <t>ul. Vostochno-Kruglikovskaya 126, Krasnodar</t>
         </is>
       </c>
       <c r="AC20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE20" t="n">
-        <v>5.84</v>
+        <v>1.81</v>
       </c>
       <c r="AF20" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.65</v>
+        <v>3.54</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AU20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AV20" t="n">
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="BC20" t="n">
         <v>0</v>
@@ -9975,46 +9955,46 @@
         <v>-1</v>
       </c>
       <c r="BO20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ20" t="n">
         <v>3</v>
       </c>
       <c r="BR20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BS20" t="n">
         <v>3</v>
       </c>
       <c r="BT20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BU20" t="n">
         <v>1</v>
       </c>
       <c r="BV20" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="BW20" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="BX20" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="BY20" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.54</v>
+        <v>0.45</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.43</v>
+        <v>2.43</v>
       </c>
       <c r="CC20" t="n">
         <v>0</v>
@@ -10056,64 +10036,64 @@
         <v>0</v>
       </c>
       <c r="CP20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ20" t="n">
         <v>1</v>
       </c>
       <c r="CR20" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="CS20" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="CT20" t="n">
         <v>1</v>
       </c>
       <c r="CU20" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="CV20" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="CW20" t="n">
         <v>1</v>
       </c>
       <c r="CX20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CY20" t="n">
         <v>7</v>
       </c>
       <c r="CZ20" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DA20" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DB20" t="n">
         <v>0</v>
       </c>
       <c r="DC20" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DD20" t="n">
-        <v>0.89</v>
+        <v>2.25</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.63</v>
+        <v>1.14</v>
       </c>
       <c r="DF20" t="n">
         <v>0</v>
       </c>
       <c r="DG20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DH20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="DI20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DJ20" t="n">
         <v>0</v>
@@ -10122,13 +10102,13 @@
         <v>0</v>
       </c>
       <c r="DL20" t="n">
-        <v>1.17</v>
+        <v>1.82</v>
       </c>
       <c r="DM20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="DN20" t="n">
-        <v>2.42</v>
+        <v>1.82</v>
       </c>
       <c r="DO20" t="n">
         <v>16</v>
@@ -10137,63 +10117,83 @@
         <v>1</v>
       </c>
       <c r="DQ20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU20" t="b">
         <v>0</v>
       </c>
       <c r="DV20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW20" t="n">
-        <v>37.47</v>
+        <v>31.6</v>
       </c>
       <c r="DX20" t="n">
-        <v>6.85</v>
+        <v>4.87</v>
       </c>
       <c r="DY20" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="DZ20" t="inlineStr">
         <is>
-          <t>60%</t>
-        </is>
-      </c>
-      <c r="EA20" t="inlineStr"/>
-      <c r="EB20" t="inlineStr"/>
-      <c r="EC20" t="inlineStr"/>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="EA20" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EB20" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="EC20" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
       <c r="ED20" t="inlineStr"/>
       <c r="EE20" t="inlineStr"/>
       <c r="EF20" t="inlineStr"/>
       <c r="EG20" t="inlineStr"/>
       <c r="EH20" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="EI20" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="EJ20" t="inlineStr">
         <is>
-          <t>4.32</t>
-        </is>
-      </c>
-      <c r="EK20" t="inlineStr"/>
-      <c r="EL20" t="inlineStr"/>
+          <t>3.69</t>
+        </is>
+      </c>
+      <c r="EK20" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EL20" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
       <c r="EM20" t="inlineStr"/>
       <c r="EN20" t="inlineStr"/>
       <c r="EO20" t="inlineStr"/>
@@ -10526,7 +10526,7 @@
         <v>50</v>
       </c>
       <c r="DD21" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DE21" t="n">
         <v>1.14</v>
@@ -10989,7 +10989,7 @@
         <v>1.86</v>
       </c>
       <c r="DE22" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF22" t="n">
         <v>0</v>
@@ -13778,7 +13778,7 @@
         <v>100</v>
       </c>
       <c r="DD28" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE28" t="n">
         <v>0.86</v>
@@ -16105,7 +16105,7 @@
         <v>1.29</v>
       </c>
       <c r="DE33" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="DF33" t="n">
         <v>0</v>
@@ -17934,10 +17934,10 @@
         <v>75</v>
       </c>
       <c r="DD37" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DE37" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF37" t="n">
         <v>1</v>
@@ -17967,7 +17967,7 @@
         <v>2.97</v>
       </c>
       <c r="DO37" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -22101,7 +22101,7 @@
         <v>1.33</v>
       </c>
       <c r="DE46" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="DF46" t="n">
         <v>1.33</v>
@@ -23006,7 +23006,7 @@
         <v>100</v>
       </c>
       <c r="DD48" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE48" t="n">
         <v>1.63</v>
@@ -23039,7 +23039,7 @@
         <v>3.02</v>
       </c>
       <c r="DO48" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -24385,7 +24385,7 @@
         <v>2.71</v>
       </c>
       <c r="DE51" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="DF51" t="n">
         <v>2.33</v>
@@ -25750,7 +25750,7 @@
         <v>71</v>
       </c>
       <c r="DD54" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DE54" t="n">
         <v>1.78</v>
@@ -26662,7 +26662,7 @@
         <v>84</v>
       </c>
       <c r="DD56" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE56" t="n">
         <v>2</v>
@@ -28081,7 +28081,7 @@
         <v>0.89</v>
       </c>
       <c r="DE59" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF59" t="n">
         <v>1</v>
@@ -28111,7 +28111,7 @@
         <v>2.96</v>
       </c>
       <c r="DO59" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -28215,37 +28215,37 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
         <v>45913.57291666666</v>
       </c>
       <c r="G60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I60" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K60" t="n">
         <v>5</v>
       </c>
       <c r="L60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
         <v>4</v>
@@ -28257,7 +28257,7 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R60" t="n">
         <v>4</v>
@@ -28266,183 +28266,191 @@
         <v>9</v>
       </c>
       <c r="T60" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="U60" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V60" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W60" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="X60" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y60" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="Z60" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA60" t="inlineStr"/>
-      <c r="AB60" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>Akhmat Arena</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
+        </is>
+      </c>
       <c r="AC60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
         <v>4</v>
       </c>
       <c r="AE60" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="AF60" t="n">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="AG60" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AI60" t="n">
         <v>1.77</v>
       </c>
       <c r="AJ60" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="AK60" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AL60" t="n">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="AM60" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="AN60" t="n">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AO60" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AQ60" t="n">
         <v>1.38</v>
       </c>
       <c r="AR60" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="AS60" t="n">
-        <v>3.07</v>
+        <v>2.88</v>
       </c>
       <c r="AT60" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AU60" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY60" t="n">
         <v>1</v>
       </c>
       <c r="AZ60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD60" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH60" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP60" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR60" t="n">
         <v>3</v>
       </c>
-      <c r="BB60" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BC60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD60" t="n">
-        <v>59</v>
-      </c>
-      <c r="BE60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF60" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BG60" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BH60" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI60" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BJ60" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BK60" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BL60" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BM60" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BN60" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BO60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP60" t="n">
+      <c r="BS60" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT60" t="n">
         <v>3</v>
       </c>
-      <c r="BQ60" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR60" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS60" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT60" t="n">
-        <v>2</v>
-      </c>
       <c r="BU60" t="n">
         <v>1</v>
       </c>
       <c r="BV60" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="BW60" t="n">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="BX60" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="BY60" t="n">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="BZ60" t="n">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="CA60" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="CB60" t="n">
-        <v>2.81</v>
+        <v>3.11</v>
       </c>
       <c r="CC60" t="n">
         <v>0</v>
@@ -28490,19 +28498,19 @@
         <v>1</v>
       </c>
       <c r="CR60" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="CS60" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT60" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU60" t="n">
         <v>17</v>
       </c>
-      <c r="CT60" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU60" t="n">
-        <v>21</v>
-      </c>
       <c r="CV60" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="CW60" t="n">
         <v>1</v>
@@ -28511,52 +28519,52 @@
         <v>4</v>
       </c>
       <c r="CY60" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CZ60" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="DA60" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="DB60" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="DC60" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="DD60" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.14</v>
+        <v>1.63</v>
       </c>
       <c r="DF60" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="DG60" t="n">
-        <v>1.33</v>
+        <v>2.33</v>
       </c>
       <c r="DH60" t="n">
         <v>1.14</v>
       </c>
       <c r="DI60" t="n">
-        <v>1.57</v>
+        <v>2.14</v>
       </c>
       <c r="DJ60" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="DK60" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="DL60" t="n">
-        <v>1.97</v>
+        <v>1.47</v>
       </c>
       <c r="DM60" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="DN60" t="n">
-        <v>3.31</v>
+        <v>2.92</v>
       </c>
       <c r="DO60" t="n">
         <v>16</v>
@@ -28568,10 +28576,10 @@
         <v>1</v>
       </c>
       <c r="DR60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT60" t="b">
         <v>0</v>
@@ -28583,34 +28591,34 @@
         <v>1</v>
       </c>
       <c r="DW60" t="n">
-        <v>16.47</v>
+        <v>19.43</v>
       </c>
       <c r="DX60" t="n">
-        <v>2.44</v>
+        <v>3.41</v>
       </c>
       <c r="DY60" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="DZ60" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA60" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EB60" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EC60" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="ED60" t="inlineStr"/>
@@ -28619,49 +28627,41 @@
       <c r="EG60" t="inlineStr"/>
       <c r="EH60" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="EI60" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="EJ60" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="EK60" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="EL60" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EM60" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EN60" t="inlineStr">
         <is>
-          <t>1.99</t>
-        </is>
-      </c>
-      <c r="EO60" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EP60" t="inlineStr">
-        <is>
-          <t>2.58</t>
-        </is>
-      </c>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EO60" t="inlineStr"/>
+      <c r="EP60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -28679,37 +28679,37 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F61" s="2" t="n">
         <v>45913.57291666666</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K61" t="n">
         <v>5</v>
       </c>
       <c r="L61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N61" t="n">
         <v>4</v>
@@ -28721,7 +28721,7 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R61" t="n">
         <v>4</v>
@@ -28730,110 +28730,102 @@
         <v>9</v>
       </c>
       <c r="T61" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="U61" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V61" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="W61" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="X61" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y61" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="Z61" t="n">
-        <v>62</v>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>Akhmat Arena</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
-        </is>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD61" t="n">
         <v>4</v>
       </c>
       <c r="AE61" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="AF61" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="AG61" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AI61" t="n">
         <v>1.77</v>
       </c>
       <c r="AJ61" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="AK61" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AL61" t="n">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="AM61" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="AN61" t="n">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AO61" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AQ61" t="n">
         <v>1.38</v>
       </c>
       <c r="AR61" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="AS61" t="n">
-        <v>2.88</v>
+        <v>3.07</v>
       </c>
       <c r="AT61" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AU61" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY61" t="n">
         <v>1</v>
       </c>
       <c r="AZ61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB61" t="n">
         <v>-1</v>
@@ -28842,7 +28834,7 @@
         <v>0</v>
       </c>
       <c r="BD61" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="BE61" t="n">
         <v>0</v>
@@ -28878,43 +28870,43 @@
         <v>0</v>
       </c>
       <c r="BP61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BQ61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR61" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS61" t="n">
         <v>3</v>
       </c>
-      <c r="BS61" t="n">
-        <v>1</v>
-      </c>
       <c r="BT61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BU61" t="n">
         <v>1</v>
       </c>
       <c r="BV61" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="BW61" t="n">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="BX61" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="BY61" t="n">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="BZ61" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="CA61" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="CB61" t="n">
-        <v>3.11</v>
+        <v>2.81</v>
       </c>
       <c r="CC61" t="n">
         <v>0</v>
@@ -28962,19 +28954,19 @@
         <v>1</v>
       </c>
       <c r="CR61" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="CS61" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CT61" t="n">
         <v>1</v>
       </c>
       <c r="CU61" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="CV61" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="CW61" t="n">
         <v>1</v>
@@ -28983,52 +28975,52 @@
         <v>4</v>
       </c>
       <c r="CY61" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CZ61" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="DA61" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="DB61" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="DC61" t="n">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.63</v>
+        <v>1.14</v>
       </c>
       <c r="DF61" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DG61" t="n">
-        <v>2.33</v>
+        <v>1.33</v>
       </c>
       <c r="DH61" t="n">
         <v>1.14</v>
       </c>
       <c r="DI61" t="n">
-        <v>2.14</v>
+        <v>1.57</v>
       </c>
       <c r="DJ61" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="DK61" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="DL61" t="n">
-        <v>1.47</v>
+        <v>1.97</v>
       </c>
       <c r="DM61" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="DN61" t="n">
-        <v>2.92</v>
+        <v>3.31</v>
       </c>
       <c r="DO61" t="n">
         <v>16</v>
@@ -29040,10 +29032,10 @@
         <v>1</v>
       </c>
       <c r="DR61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT61" t="b">
         <v>0</v>
@@ -29055,34 +29047,34 @@
         <v>1</v>
       </c>
       <c r="DW61" t="n">
-        <v>19.43</v>
+        <v>16.47</v>
       </c>
       <c r="DX61" t="n">
-        <v>3.41</v>
+        <v>2.44</v>
       </c>
       <c r="DY61" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="DZ61" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="EA61" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EB61" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="EC61" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="ED61" t="inlineStr"/>
@@ -29091,41 +29083,49 @@
       <c r="EG61" t="inlineStr"/>
       <c r="EH61" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="EI61" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="EJ61" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EK61" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="EL61" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="EM61" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EN61" t="inlineStr">
         <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="EO61" t="inlineStr"/>
-      <c r="EP61" t="inlineStr"/>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EO61" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EP61" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -31754,7 +31754,7 @@
         <v>88</v>
       </c>
       <c r="DD67" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DE67" t="n">
         <v>0.86</v>
@@ -36865,7 +36865,7 @@
         <v>2.71</v>
       </c>
       <c r="DE78" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF78" t="n">
         <v>2.5</v>
@@ -37326,7 +37326,7 @@
         <v>90</v>
       </c>
       <c r="DD79" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE79" t="n">
         <v>1.78</v>
@@ -38257,7 +38257,7 @@
         <v>2.22</v>
       </c>
       <c r="DE81" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="DF81" t="n">
         <v>2</v>
@@ -38690,7 +38690,7 @@
         <v>70</v>
       </c>
       <c r="DD82" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DE82" t="n">
         <v>1.56</v>
@@ -40997,7 +40997,7 @@
         <v>0.57</v>
       </c>
       <c r="DE87" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="DF87" t="n">
         <v>0.25</v>
@@ -41466,7 +41466,7 @@
         <v>65</v>
       </c>
       <c r="DD88" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE88" t="n">
         <v>1.14</v>
@@ -42091,170 +42091,162 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
         <v>45948.41666666666</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" t="n">
         <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J90" t="n">
+        <v>5</v>
+      </c>
+      <c r="K90" t="n">
         <v>6</v>
       </c>
-      <c r="K90" t="n">
+      <c r="L90" t="n">
+        <v>11</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1</v>
+      </c>
+      <c r="N90" t="n">
+        <v>2</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
         <v>3</v>
       </c>
-      <c r="L90" t="n">
-        <v>9</v>
-      </c>
-      <c r="M90" t="n">
-        <v>2</v>
-      </c>
-      <c r="N90" t="n">
-        <v>2</v>
-      </c>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>11</v>
-      </c>
       <c r="R90" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S90" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T90" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="U90" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="V90" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W90" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X90" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Y90" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Z90" t="n">
-        <v>35</v>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>Stadion Nizhny Novgorod</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>ul. Dolzhanskaya, Nizhniy Novgorod</t>
-        </is>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="AA90" t="inlineStr"/>
+      <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD90" t="n">
         <v>2</v>
       </c>
       <c r="AE90" t="n">
-        <v>2.29</v>
+        <v>1.9</v>
       </c>
       <c r="AF90" t="n">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
       <c r="AG90" t="n">
-        <v>2.57</v>
+        <v>3.28</v>
       </c>
       <c r="AH90" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AI90" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AJ90" t="n">
-        <v>2.66</v>
+        <v>3.08</v>
       </c>
       <c r="AK90" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="AL90" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="AM90" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AN90" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AO90" t="n">
-        <v>2.16</v>
+        <v>2.62</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AR90" t="n">
-        <v>2.51</v>
+        <v>2.74</v>
       </c>
       <c r="AS90" t="n">
-        <v>3.32</v>
+        <v>3.04</v>
       </c>
       <c r="AT90" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AU90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV90" t="n">
         <v>0</v>
       </c>
       <c r="AW90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ90" t="n">
         <v>1</v>
       </c>
       <c r="BA90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB90" t="n">
-        <v>668270</v>
+        <v>-1</v>
       </c>
       <c r="BC90" t="n">
         <v>0</v>
       </c>
       <c r="BD90" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BE90" t="n">
         <v>0</v>
@@ -42287,7 +42279,7 @@
         <v>-1</v>
       </c>
       <c r="BO90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP90" t="n">
         <v>0</v>
@@ -42299,7 +42291,7 @@
         <v>2</v>
       </c>
       <c r="BS90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT90" t="n">
         <v>3</v>
@@ -42308,25 +42300,25 @@
         <v>1</v>
       </c>
       <c r="BV90" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="BW90" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="BX90" t="n">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="BY90" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="BZ90" t="n">
-        <v>2.76</v>
+        <v>1.44</v>
       </c>
       <c r="CA90" t="n">
-        <v>1.09</v>
+        <v>1.34</v>
       </c>
       <c r="CB90" t="n">
-        <v>3.85</v>
+        <v>2.78</v>
       </c>
       <c r="CC90" t="n">
         <v>0</v>
@@ -42374,73 +42366,73 @@
         <v>1</v>
       </c>
       <c r="CR90" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CS90" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CT90" t="n">
         <v>1</v>
       </c>
       <c r="CU90" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="CV90" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CW90" t="n">
         <v>1</v>
       </c>
       <c r="CX90" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="CY90" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="CZ90" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="DA90" t="n">
         <v>100</v>
       </c>
       <c r="DB90" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="DC90" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="DD90" t="n">
-        <v>0.89</v>
+        <v>1.5</v>
       </c>
       <c r="DE90" t="n">
-        <v>1.63</v>
+        <v>0.5</v>
       </c>
       <c r="DF90" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="DG90" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="DH90" t="n">
-        <v>0.55</v>
+        <v>1.09</v>
       </c>
       <c r="DI90" t="n">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="DJ90" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="DK90" t="n">
         <v>0</v>
       </c>
       <c r="DL90" t="n">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="DM90" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="DN90" t="n">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="DO90" t="n">
         <v>16</v>
@@ -42449,7 +42441,7 @@
         <v>1</v>
       </c>
       <c r="DQ90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR90" t="b">
         <v>0</v>
@@ -42464,82 +42456,70 @@
         <v>0</v>
       </c>
       <c r="DV90" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW90" t="n">
-        <v>8</v>
-      </c>
-      <c r="DX90" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="DY90" t="inlineStr">
-        <is>
-          <t>80%</t>
-        </is>
-      </c>
-      <c r="DZ90" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="DW90" t="inlineStr"/>
+      <c r="DX90" t="inlineStr"/>
+      <c r="DY90" t="inlineStr"/>
+      <c r="DZ90" t="inlineStr"/>
       <c r="EA90" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EB90" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="EC90" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="ED90" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EE90" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EF90" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="EG90" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="EH90" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="EI90" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EJ90" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="EK90" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="EL90" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EM90" t="inlineStr"/>
@@ -42563,162 +42543,170 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F91" s="2" t="n">
         <v>45948.41666666666</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
         <v>1</v>
       </c>
       <c r="I91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K91" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L91" t="n">
+        <v>9</v>
+      </c>
+      <c r="M91" t="n">
+        <v>2</v>
+      </c>
+      <c r="N91" t="n">
+        <v>2</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
         <v>11</v>
       </c>
-      <c r="M91" t="n">
-        <v>1</v>
-      </c>
-      <c r="N91" t="n">
-        <v>2</v>
-      </c>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>3</v>
-      </c>
       <c r="R91" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T91" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="U91" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="V91" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W91" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="X91" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Y91" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="Z91" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA91" t="inlineStr"/>
-      <c r="AB91" t="inlineStr"/>
+        <v>35</v>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>Stadion Nizhny Novgorod</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>ul. Dolzhanskaya, Nizhniy Novgorod</t>
+        </is>
+      </c>
       <c r="AC91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD91" t="n">
         <v>2</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.9</v>
+        <v>2.29</v>
       </c>
       <c r="AF91" t="n">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="AG91" t="n">
-        <v>3.28</v>
+        <v>2.57</v>
       </c>
       <c r="AH91" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AI91" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AJ91" t="n">
-        <v>3.08</v>
+        <v>2.66</v>
       </c>
       <c r="AK91" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AL91" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="AM91" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AN91" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AO91" t="n">
-        <v>2.62</v>
+        <v>2.16</v>
       </c>
       <c r="AP91" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR91" t="n">
-        <v>2.74</v>
+        <v>2.51</v>
       </c>
       <c r="AS91" t="n">
-        <v>3.04</v>
+        <v>3.32</v>
       </c>
       <c r="AT91" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AU91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV91" t="n">
         <v>0</v>
       </c>
       <c r="AW91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ91" t="n">
         <v>1</v>
       </c>
       <c r="BA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB91" t="n">
-        <v>-1</v>
+        <v>668270</v>
       </c>
       <c r="BC91" t="n">
         <v>0</v>
       </c>
       <c r="BD91" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BE91" t="n">
         <v>0</v>
@@ -42751,7 +42739,7 @@
         <v>-1</v>
       </c>
       <c r="BO91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP91" t="n">
         <v>0</v>
@@ -42763,7 +42751,7 @@
         <v>2</v>
       </c>
       <c r="BS91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT91" t="n">
         <v>3</v>
@@ -42772,25 +42760,25 @@
         <v>1</v>
       </c>
       <c r="BV91" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="BW91" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="BX91" t="n">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="BY91" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BZ91" t="n">
-        <v>1.44</v>
+        <v>2.76</v>
       </c>
       <c r="CA91" t="n">
-        <v>1.34</v>
+        <v>1.09</v>
       </c>
       <c r="CB91" t="n">
-        <v>2.78</v>
+        <v>3.85</v>
       </c>
       <c r="CC91" t="n">
         <v>0</v>
@@ -42838,82 +42826,82 @@
         <v>1</v>
       </c>
       <c r="CR91" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS91" t="n">
         <v>21</v>
       </c>
-      <c r="CS91" t="n">
-        <v>23</v>
-      </c>
       <c r="CT91" t="n">
         <v>1</v>
       </c>
       <c r="CU91" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="CV91" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CW91" t="n">
         <v>1</v>
       </c>
       <c r="CX91" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="CY91" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="CZ91" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="DA91" t="n">
         <v>100</v>
       </c>
       <c r="DB91" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="DC91" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="DD91" t="n">
-        <v>1.5</v>
+        <v>0.89</v>
       </c>
       <c r="DE91" t="n">
-        <v>0.57</v>
+        <v>1.63</v>
       </c>
       <c r="DF91" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="DG91" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="DH91" t="n">
-        <v>1.09</v>
+        <v>0.55</v>
       </c>
       <c r="DI91" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="DJ91" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="DK91" t="n">
         <v>0</v>
       </c>
       <c r="DL91" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DM91" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="DN91" t="n">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="DO91" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
       </c>
       <c r="DQ91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR91" t="b">
         <v>0</v>
@@ -42928,70 +42916,82 @@
         <v>0</v>
       </c>
       <c r="DV91" t="b">
-        <v>1</v>
-      </c>
-      <c r="DW91" t="inlineStr"/>
-      <c r="DX91" t="inlineStr"/>
-      <c r="DY91" t="inlineStr"/>
-      <c r="DZ91" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="DW91" t="n">
+        <v>8</v>
+      </c>
+      <c r="DX91" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="DY91" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="DZ91" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
       <c r="EA91" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EB91" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="EC91" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="ED91" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EE91" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EF91" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="EG91" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="EH91" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="EI91" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="EJ91" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="EK91" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EL91" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="EM91" t="inlineStr"/>
@@ -46129,7 +46129,7 @@
         <v>2.22</v>
       </c>
       <c r="DE98" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF98" t="n">
         <v>2</v>
@@ -47030,7 +47030,7 @@
         <v>92</v>
       </c>
       <c r="DD100" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE100" t="n">
         <v>0.63</v>
@@ -47486,7 +47486,7 @@
         <v>75</v>
       </c>
       <c r="DD101" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DE101" t="n">
         <v>1.63</v>
@@ -49778,10 +49778,10 @@
         <v>61</v>
       </c>
       <c r="DD106" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE106" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="DF106" t="n">
         <v>2.71</v>
@@ -49811,7 +49811,7 @@
         <v>2.66</v>
       </c>
       <c r="DO106" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -49911,170 +49911,170 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F107" s="2" t="n">
         <v>45962.61458333334</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J107" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K107" t="n">
+        <v>2</v>
+      </c>
+      <c r="L107" t="n">
+        <v>11</v>
+      </c>
+      <c r="M107" t="n">
+        <v>2</v>
+      </c>
+      <c r="N107" t="n">
+        <v>2</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>6</v>
+      </c>
+      <c r="R107" t="n">
+        <v>1</v>
+      </c>
+      <c r="S107" t="n">
+        <v>7</v>
+      </c>
+      <c r="T107" t="n">
         <v>5</v>
       </c>
-      <c r="L107" t="n">
-        <v>8</v>
-      </c>
-      <c r="M107" t="n">
-        <v>3</v>
-      </c>
-      <c r="N107" t="n">
-        <v>3</v>
-      </c>
-      <c r="O107" t="n">
-        <v>1</v>
-      </c>
-      <c r="P107" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>2</v>
-      </c>
-      <c r="R107" t="n">
-        <v>3</v>
-      </c>
-      <c r="S107" t="n">
-        <v>5</v>
-      </c>
-      <c r="T107" t="n">
-        <v>11</v>
-      </c>
       <c r="U107" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="V107" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="W107" t="n">
         <v>16</v>
       </c>
       <c r="X107" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="Y107" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="Z107" t="n">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>Kazan' Arena</t>
+          <t>Anzhi-Arena</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>Prospekt Husaina Yamasheva 115a, Kazan'</t>
+          <t>, Kaspiysk</t>
         </is>
       </c>
       <c r="AC107" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AD107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE107" t="n">
-        <v>3.1</v>
+        <v>2.03</v>
       </c>
       <c r="AF107" t="n">
         <v>3.2</v>
       </c>
       <c r="AG107" t="n">
-        <v>2.2</v>
+        <v>3.95</v>
       </c>
       <c r="AH107" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AI107" t="n">
-        <v>1.91</v>
+        <v>2.48</v>
       </c>
       <c r="AJ107" t="n">
-        <v>2.9</v>
+        <v>4.65</v>
       </c>
       <c r="AK107" t="n">
-        <v>1.66</v>
+        <v>2.14</v>
       </c>
       <c r="AL107" t="n">
-        <v>2.29</v>
+        <v>1.64</v>
       </c>
       <c r="AM107" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="AN107" t="n">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="AO107" t="n">
-        <v>2.36</v>
+        <v>2.06</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="AR107" t="n">
-        <v>2.68</v>
+        <v>3.54</v>
       </c>
       <c r="AS107" t="n">
-        <v>2.89</v>
+        <v>2.4</v>
       </c>
       <c r="AT107" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AU107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW107" t="n">
         <v>0</v>
       </c>
       <c r="AX107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY107" t="n">
         <v>0</v>
       </c>
       <c r="AZ107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB107" t="n">
-        <v>-1</v>
+        <v>668267</v>
       </c>
       <c r="BC107" t="n">
         <v>0</v>
       </c>
       <c r="BD107" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="BE107" t="n">
         <v>0</v>
@@ -50107,169 +50107,169 @@
         <v>-1</v>
       </c>
       <c r="BO107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BR107" t="n">
         <v>2</v>
       </c>
       <c r="BS107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT107" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV107" t="n">
+        <v>53</v>
+      </c>
+      <c r="BW107" t="n">
+        <v>26</v>
+      </c>
+      <c r="BX107" t="n">
+        <v>126</v>
+      </c>
+      <c r="BY107" t="n">
+        <v>75</v>
+      </c>
+      <c r="BZ107" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="CA107" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="CB107" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="CC107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM107" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN107" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR107" t="n">
+        <v>29</v>
+      </c>
+      <c r="CS107" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU107" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV107" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX107" t="n">
         <v>5</v>
       </c>
-      <c r="BU107" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV107" t="n">
-        <v>39</v>
-      </c>
-      <c r="BW107" t="n">
-        <v>66</v>
-      </c>
-      <c r="BX107" t="n">
-        <v>101</v>
-      </c>
-      <c r="BY107" t="n">
-        <v>121</v>
-      </c>
-      <c r="BZ107" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="CA107" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CB107" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="CC107" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD107" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE107" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF107" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG107" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH107" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI107" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ107" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK107" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL107" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM107" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CN107" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CO107" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP107" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ107" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR107" t="n">
-        <v>18</v>
-      </c>
-      <c r="CS107" t="n">
-        <v>15</v>
-      </c>
-      <c r="CT107" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU107" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV107" t="n">
-        <v>17</v>
-      </c>
-      <c r="CW107" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX107" t="n">
-        <v>10</v>
-      </c>
       <c r="CY107" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="CZ107" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="DA107" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="DB107" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="DC107" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="DD107" t="n">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="DE107" t="n">
-        <v>1.14</v>
+        <v>0.63</v>
       </c>
       <c r="DF107" t="n">
-        <v>1.86</v>
+        <v>1.5</v>
       </c>
       <c r="DG107" t="n">
-        <v>1.17</v>
+        <v>0.71</v>
       </c>
       <c r="DH107" t="n">
-        <v>1.38</v>
+        <v>0.85</v>
       </c>
       <c r="DI107" t="n">
-        <v>1.23</v>
+        <v>1</v>
       </c>
       <c r="DJ107" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="DK107" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="DL107" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="DM107" t="n">
-        <v>1.4</v>
+        <v>0.97</v>
       </c>
       <c r="DN107" t="n">
-        <v>2.61</v>
+        <v>2.09</v>
       </c>
       <c r="DO107" t="n">
         <v>16</v>
       </c>
       <c r="DP107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR107" t="b">
         <v>0</v>
@@ -50287,101 +50287,77 @@
         <v>0</v>
       </c>
       <c r="DW107" t="n">
-        <v>6.32</v>
+        <v>16.76</v>
       </c>
       <c r="DX107" t="n">
-        <v>3.69</v>
+        <v>8.27</v>
       </c>
       <c r="DY107" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="DZ107" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="EA107" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EB107" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="EC107" t="inlineStr">
         <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="ED107" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="ED107" t="inlineStr"/>
       <c r="EE107" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EF107" t="inlineStr">
         <is>
-          <t>3.19</t>
-        </is>
-      </c>
-      <c r="EG107" t="inlineStr">
-        <is>
-          <t>2.76</t>
-        </is>
-      </c>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EG107" t="inlineStr"/>
       <c r="EH107" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EI107" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="EJ107" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="EK107" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EL107" t="inlineStr">
         <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="EM107" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
-      </c>
-      <c r="EN107" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EO107" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="EP107" t="inlineStr">
-        <is>
-          <t>2.44</t>
-        </is>
-      </c>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EM107" t="inlineStr"/>
+      <c r="EN107" t="inlineStr"/>
+      <c r="EO107" t="inlineStr"/>
+      <c r="EP107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -50399,170 +50375,170 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F108" s="2" t="n">
         <v>45962.61458333334</v>
       </c>
       <c r="G108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K108" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L108" t="n">
+        <v>8</v>
+      </c>
+      <c r="M108" t="n">
+        <v>3</v>
+      </c>
+      <c r="N108" t="n">
+        <v>3</v>
+      </c>
+      <c r="O108" t="n">
+        <v>1</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>2</v>
+      </c>
+      <c r="R108" t="n">
+        <v>3</v>
+      </c>
+      <c r="S108" t="n">
+        <v>5</v>
+      </c>
+      <c r="T108" t="n">
         <v>11</v>
       </c>
-      <c r="M108" t="n">
-        <v>2</v>
-      </c>
-      <c r="N108" t="n">
-        <v>2</v>
-      </c>
-      <c r="O108" t="n">
-        <v>0</v>
-      </c>
-      <c r="P108" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q108" t="n">
-        <v>6</v>
-      </c>
-      <c r="R108" t="n">
-        <v>1</v>
-      </c>
-      <c r="S108" t="n">
+      <c r="U108" t="n">
         <v>7</v>
       </c>
-      <c r="T108" t="n">
-        <v>5</v>
-      </c>
-      <c r="U108" t="n">
-        <v>13</v>
-      </c>
       <c r="V108" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="W108" t="n">
         <v>16</v>
       </c>
       <c r="X108" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Y108" t="n">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="Z108" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>Anzhi-Arena</t>
+          <t>Kazan' Arena</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>, Kaspiysk</t>
+          <t>Prospekt Husaina Yamasheva 115a, Kazan'</t>
         </is>
       </c>
       <c r="AC108" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE108" t="n">
-        <v>2.03</v>
+        <v>3.1</v>
       </c>
       <c r="AF108" t="n">
         <v>3.2</v>
       </c>
       <c r="AG108" t="n">
-        <v>3.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH108" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AI108" t="n">
-        <v>2.48</v>
+        <v>1.91</v>
       </c>
       <c r="AJ108" t="n">
-        <v>4.65</v>
+        <v>2.9</v>
       </c>
       <c r="AK108" t="n">
-        <v>2.14</v>
+        <v>1.66</v>
       </c>
       <c r="AL108" t="n">
-        <v>1.64</v>
+        <v>2.29</v>
       </c>
       <c r="AM108" t="n">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="AN108" t="n">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="AO108" t="n">
-        <v>2.06</v>
+        <v>2.36</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="AR108" t="n">
-        <v>3.54</v>
+        <v>2.68</v>
       </c>
       <c r="AS108" t="n">
-        <v>2.4</v>
+        <v>2.89</v>
       </c>
       <c r="AT108" t="n">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AU108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW108" t="n">
         <v>0</v>
       </c>
       <c r="AX108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY108" t="n">
         <v>0</v>
       </c>
       <c r="AZ108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB108" t="n">
-        <v>668267</v>
+        <v>-1</v>
       </c>
       <c r="BC108" t="n">
         <v>0</v>
       </c>
       <c r="BD108" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="BE108" t="n">
         <v>0</v>
@@ -50595,46 +50571,46 @@
         <v>-1</v>
       </c>
       <c r="BO108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BR108" t="n">
         <v>2</v>
       </c>
       <c r="BS108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT108" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BU108" t="n">
         <v>1</v>
       </c>
       <c r="BV108" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="BW108" t="n">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="BX108" t="n">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="BY108" t="n">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="BZ108" t="n">
-        <v>1.63</v>
+        <v>0.88</v>
       </c>
       <c r="CA108" t="n">
-        <v>0.65</v>
+        <v>1.58</v>
       </c>
       <c r="CB108" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="CC108" t="n">
         <v>0</v>
@@ -50661,7 +50637,7 @@
         <v>1</v>
       </c>
       <c r="CK108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL108" t="n">
         <v>0</v>
@@ -50682,82 +50658,82 @@
         <v>1</v>
       </c>
       <c r="CR108" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="CS108" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="CT108" t="n">
         <v>1</v>
       </c>
       <c r="CU108" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="CV108" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CW108" t="n">
         <v>1</v>
       </c>
       <c r="CX108" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="CY108" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="CZ108" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="DA108" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="DB108" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="DC108" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="DD108" t="n">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="DE108" t="n">
-        <v>0.63</v>
+        <v>1.14</v>
       </c>
       <c r="DF108" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="DG108" t="n">
-        <v>0.71</v>
+        <v>1.17</v>
       </c>
       <c r="DH108" t="n">
-        <v>0.85</v>
+        <v>1.38</v>
       </c>
       <c r="DI108" t="n">
-        <v>1</v>
+        <v>1.23</v>
       </c>
       <c r="DJ108" t="n">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="DK108" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="DL108" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="DM108" t="n">
-        <v>0.97</v>
+        <v>1.4</v>
       </c>
       <c r="DN108" t="n">
-        <v>2.09</v>
+        <v>2.61</v>
       </c>
       <c r="DO108" t="n">
         <v>16</v>
       </c>
       <c r="DP108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR108" t="b">
         <v>0</v>
@@ -50775,77 +50751,101 @@
         <v>0</v>
       </c>
       <c r="DW108" t="n">
-        <v>16.76</v>
+        <v>6.32</v>
       </c>
       <c r="DX108" t="n">
-        <v>8.27</v>
+        <v>3.69</v>
       </c>
       <c r="DY108" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="DZ108" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="EA108" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EB108" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="EC108" t="inlineStr">
         <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="ED108" t="inlineStr"/>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="ED108" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
       <c r="EE108" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EF108" t="inlineStr">
         <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="EG108" t="inlineStr"/>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="EG108" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
       <c r="EH108" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="EI108" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="EJ108" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="EK108" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="EL108" t="inlineStr">
         <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="EM108" t="inlineStr"/>
-      <c r="EN108" t="inlineStr"/>
-      <c r="EO108" t="inlineStr"/>
-      <c r="EP108" t="inlineStr"/>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EM108" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EN108" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EO108" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EP108" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -50863,25 +50863,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F109" s="2" t="n">
         <v>45962.71875</v>
       </c>
       <c r="G109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J109" t="n">
         <v>6</v>
@@ -50896,129 +50896,137 @@
         <v>2</v>
       </c>
       <c r="N109" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P109" t="n">
         <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R109" t="n">
         <v>2</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T109" t="n">
         <v>6</v>
       </c>
       <c r="U109" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V109" t="n">
         <v>8</v>
       </c>
       <c r="W109" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="X109" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Y109" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Z109" t="n">
-        <v>51</v>
-      </c>
-      <c r="AA109" t="inlineStr"/>
-      <c r="AB109" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>Stadion Central’nyj im. I.P. Chayka</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>ul. Suvorova, Peschanokopskoye</t>
+        </is>
+      </c>
       <c r="AC109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD109" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE109" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AF109" t="n">
-        <v>3.9</v>
+        <v>3.47</v>
       </c>
       <c r="AG109" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AH109" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AI109" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AJ109" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="AK109" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AL109" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AM109" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="AN109" t="n">
-        <v>1.92</v>
+        <v>2.23</v>
       </c>
       <c r="AO109" t="n">
-        <v>2.65</v>
+        <v>2.32</v>
       </c>
       <c r="AP109" t="n">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AR109" t="n">
-        <v>2.6</v>
+        <v>2.77</v>
       </c>
       <c r="AS109" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="AT109" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AU109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW109" t="n">
         <v>0</v>
       </c>
       <c r="AX109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ109" t="n">
         <v>1</v>
       </c>
       <c r="BA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB109" t="n">
-        <v>921</v>
+        <v>668270</v>
       </c>
       <c r="BC109" t="n">
         <v>0</v>
       </c>
       <c r="BD109" t="n">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="BE109" t="n">
         <v>0</v>
@@ -51051,58 +51059,58 @@
         <v>-1</v>
       </c>
       <c r="BO109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ109" t="n">
         <v>1</v>
       </c>
       <c r="BR109" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BS109" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BT109" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BU109" t="n">
         <v>1</v>
       </c>
       <c r="BV109" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="BW109" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="BX109" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="BY109" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="BZ109" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="CA109" t="n">
-        <v>0.98</v>
+        <v>0.91</v>
       </c>
       <c r="CB109" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="CC109" t="n">
         <v>0</v>
       </c>
       <c r="CD109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE109" t="n">
         <v>0</v>
       </c>
       <c r="CF109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG109" t="n">
         <v>0</v>
@@ -51117,7 +51125,7 @@
         <v>1</v>
       </c>
       <c r="CK109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL109" t="n">
         <v>0</v>
@@ -51138,73 +51146,73 @@
         <v>1</v>
       </c>
       <c r="CR109" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="CS109" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="CT109" t="n">
         <v>1</v>
       </c>
       <c r="CU109" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="CV109" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="CW109" t="n">
         <v>1</v>
       </c>
       <c r="CX109" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CY109" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="CZ109" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="DA109" t="n">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="DB109" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="DC109" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="DD109" t="n">
-        <v>2.71</v>
+        <v>1.29</v>
       </c>
       <c r="DE109" t="n">
         <v>1.63</v>
       </c>
       <c r="DF109" t="n">
-        <v>2.67</v>
+        <v>1.5</v>
       </c>
       <c r="DG109" t="n">
-        <v>1.86</v>
+        <v>1.17</v>
       </c>
       <c r="DH109" t="n">
-        <v>2</v>
+        <v>1.15</v>
       </c>
       <c r="DI109" t="n">
-        <v>2.08</v>
+        <v>0.92</v>
       </c>
       <c r="DJ109" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="DK109" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="DL109" t="n">
-        <v>1.9</v>
+        <v>1.47</v>
       </c>
       <c r="DM109" t="n">
-        <v>1.54</v>
+        <v>1.34</v>
       </c>
       <c r="DN109" t="n">
-        <v>3.44</v>
+        <v>2.81</v>
       </c>
       <c r="DO109" t="n">
         <v>16</v>
@@ -51213,7 +51221,7 @@
         <v>1</v>
       </c>
       <c r="DQ109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR109" t="b">
         <v>0</v>
@@ -51231,63 +51239,79 @@
         <v>0</v>
       </c>
       <c r="DW109" t="n">
-        <v>14.13</v>
+        <v>5.41</v>
       </c>
       <c r="DX109" t="n">
-        <v>9.24</v>
+        <v>4.99</v>
       </c>
       <c r="DY109" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="DZ109" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA109" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EB109" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="EC109" t="inlineStr">
         <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="ED109" t="inlineStr"/>
-      <c r="EE109" t="inlineStr"/>
-      <c r="EF109" t="inlineStr"/>
-      <c r="EG109" t="inlineStr"/>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="ED109" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EE109" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EF109" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="EG109" t="inlineStr">
+        <is>
+          <t>2.79</t>
+        </is>
+      </c>
       <c r="EH109" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EI109" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="EJ109" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="EK109" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="EL109" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EM109" t="inlineStr"/>
@@ -51311,25 +51335,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F110" s="2" t="n">
         <v>45962.71875</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J110" t="n">
         <v>6</v>
@@ -51344,137 +51368,129 @@
         <v>2</v>
       </c>
       <c r="N110" t="n">
+        <v>1</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>6</v>
+      </c>
+      <c r="R110" t="n">
+        <v>2</v>
+      </c>
+      <c r="S110" t="n">
         <v>5</v>
-      </c>
-      <c r="O110" t="n">
-        <v>1</v>
-      </c>
-      <c r="P110" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q110" t="n">
-        <v>3</v>
-      </c>
-      <c r="R110" t="n">
-        <v>2</v>
-      </c>
-      <c r="S110" t="n">
-        <v>10</v>
       </c>
       <c r="T110" t="n">
         <v>6</v>
       </c>
       <c r="U110" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V110" t="n">
         <v>8</v>
       </c>
       <c r="W110" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X110" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Y110" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Z110" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA110" t="inlineStr">
-        <is>
-          <t>Stadion Central’nyj im. I.P. Chayka</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>ul. Suvorova, Peschanokopskoye</t>
-        </is>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="AA110" t="inlineStr"/>
+      <c r="AB110" t="inlineStr"/>
       <c r="AC110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD110" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE110" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AF110" t="n">
-        <v>3.47</v>
+        <v>3.9</v>
       </c>
       <c r="AG110" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AH110" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AI110" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AJ110" t="n">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="AK110" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AL110" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AM110" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="AN110" t="n">
-        <v>2.23</v>
+        <v>1.92</v>
       </c>
       <c r="AO110" t="n">
-        <v>2.32</v>
+        <v>2.65</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AR110" t="n">
-        <v>2.77</v>
+        <v>2.6</v>
       </c>
       <c r="AS110" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="AT110" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AU110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW110" t="n">
         <v>0</v>
       </c>
       <c r="AX110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ110" t="n">
         <v>1</v>
       </c>
       <c r="BA110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB110" t="n">
-        <v>668270</v>
+        <v>921</v>
       </c>
       <c r="BC110" t="n">
         <v>0</v>
       </c>
       <c r="BD110" t="n">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="BE110" t="n">
         <v>0</v>
@@ -51507,58 +51523,58 @@
         <v>-1</v>
       </c>
       <c r="BO110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ110" t="n">
         <v>1</v>
       </c>
       <c r="BR110" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BS110" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BT110" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BU110" t="n">
         <v>1</v>
       </c>
       <c r="BV110" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="BW110" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="BX110" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="BY110" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="BZ110" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="CA110" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="CB110" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="CC110" t="n">
         <v>0</v>
       </c>
       <c r="CD110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE110" t="n">
         <v>0</v>
       </c>
       <c r="CF110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG110" t="n">
         <v>0</v>
@@ -51573,7 +51589,7 @@
         <v>1</v>
       </c>
       <c r="CK110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL110" t="n">
         <v>0</v>
@@ -51594,73 +51610,73 @@
         <v>1</v>
       </c>
       <c r="CR110" t="n">
+        <v>28</v>
+      </c>
+      <c r="CS110" t="n">
+        <v>8</v>
+      </c>
+      <c r="CT110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU110" t="n">
         <v>20</v>
       </c>
-      <c r="CS110" t="n">
-        <v>15</v>
-      </c>
-      <c r="CT110" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU110" t="n">
-        <v>15</v>
-      </c>
       <c r="CV110" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="CW110" t="n">
         <v>1</v>
       </c>
       <c r="CX110" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY110" t="n">
         <v>6</v>
       </c>
-      <c r="CY110" t="n">
-        <v>15</v>
-      </c>
       <c r="CZ110" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="DA110" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="DB110" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="DC110" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="DD110" t="n">
-        <v>1.29</v>
+        <v>2.71</v>
       </c>
       <c r="DE110" t="n">
         <v>1.63</v>
       </c>
       <c r="DF110" t="n">
-        <v>1.5</v>
+        <v>2.67</v>
       </c>
       <c r="DG110" t="n">
-        <v>1.17</v>
+        <v>1.86</v>
       </c>
       <c r="DH110" t="n">
-        <v>1.15</v>
+        <v>2</v>
       </c>
       <c r="DI110" t="n">
-        <v>0.92</v>
+        <v>2.08</v>
       </c>
       <c r="DJ110" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="DK110" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="DL110" t="n">
-        <v>1.47</v>
+        <v>1.9</v>
       </c>
       <c r="DM110" t="n">
-        <v>1.34</v>
+        <v>1.54</v>
       </c>
       <c r="DN110" t="n">
-        <v>2.81</v>
+        <v>3.44</v>
       </c>
       <c r="DO110" t="n">
         <v>16</v>
@@ -51669,7 +51685,7 @@
         <v>1</v>
       </c>
       <c r="DQ110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR110" t="b">
         <v>0</v>
@@ -51687,79 +51703,63 @@
         <v>0</v>
       </c>
       <c r="DW110" t="n">
-        <v>5.41</v>
+        <v>14.13</v>
       </c>
       <c r="DX110" t="n">
-        <v>4.99</v>
+        <v>9.24</v>
       </c>
       <c r="DY110" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="DZ110" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="EA110" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EB110" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="EC110" t="inlineStr">
         <is>
-          <t>1.28</t>
-        </is>
-      </c>
-      <c r="ED110" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EE110" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="EF110" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="EG110" t="inlineStr">
-        <is>
-          <t>2.79</t>
-        </is>
-      </c>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="ED110" t="inlineStr"/>
+      <c r="EE110" t="inlineStr"/>
+      <c r="EF110" t="inlineStr"/>
+      <c r="EG110" t="inlineStr"/>
       <c r="EH110" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="EI110" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="EJ110" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="EK110" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="EL110" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EM110" t="inlineStr"/>
@@ -55753,7 +55753,7 @@
         <v>2.25</v>
       </c>
       <c r="DE119" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF119" t="n">
         <v>2.33</v>
@@ -57162,7 +57162,7 @@
         <v>68</v>
       </c>
       <c r="DD122" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DE122" t="n">
         <v>0.44</v>
@@ -60503,6 +60503,854 @@
         </is>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>17</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Akron</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Olimpiyets</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>45990.45833333334</v>
+      </c>
+      <c r="G130" t="n">
+        <v>1</v>
+      </c>
+      <c r="H130" t="n">
+        <v>2</v>
+      </c>
+      <c r="I130" t="n">
+        <v>3</v>
+      </c>
+      <c r="J130" t="n">
+        <v>10</v>
+      </c>
+      <c r="K130" t="n">
+        <v>3</v>
+      </c>
+      <c r="L130" t="n">
+        <v>13</v>
+      </c>
+      <c r="M130" t="n">
+        <v>1</v>
+      </c>
+      <c r="N130" t="n">
+        <v>2</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>6</v>
+      </c>
+      <c r="R130" t="n">
+        <v>5</v>
+      </c>
+      <c r="S130" t="n">
+        <v>7</v>
+      </c>
+      <c r="T130" t="n">
+        <v>11</v>
+      </c>
+      <c r="U130" t="n">
+        <v>13</v>
+      </c>
+      <c r="V130" t="n">
+        <v>16</v>
+      </c>
+      <c r="W130" t="n">
+        <v>13</v>
+      </c>
+      <c r="X130" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>56</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA130" t="inlineStr"/>
+      <c r="AB130" t="inlineStr"/>
+      <c r="AC130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>1482</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>51</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>56</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>35</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>103</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>73</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU130" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV130" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX130" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY130" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ130" t="n">
+        <v>41</v>
+      </c>
+      <c r="DA130" t="n">
+        <v>93</v>
+      </c>
+      <c r="DB130" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC130" t="n">
+        <v>73</v>
+      </c>
+      <c r="DD130" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DE130" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="DF130" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG130" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH130" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DI130" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DJ130" t="n">
+        <v>60</v>
+      </c>
+      <c r="DK130" t="n">
+        <v>7</v>
+      </c>
+      <c r="DL130" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DM130" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="DN130" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="DO130" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP130" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ130" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR130" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS130" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT130" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU130" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV130" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW130" t="inlineStr"/>
+      <c r="DX130" t="inlineStr"/>
+      <c r="DY130" t="inlineStr"/>
+      <c r="DZ130" t="inlineStr"/>
+      <c r="EA130" t="inlineStr"/>
+      <c r="EB130" t="inlineStr"/>
+      <c r="EC130" t="inlineStr"/>
+      <c r="ED130" t="inlineStr"/>
+      <c r="EE130" t="inlineStr"/>
+      <c r="EF130" t="inlineStr"/>
+      <c r="EG130" t="inlineStr"/>
+      <c r="EH130" t="inlineStr"/>
+      <c r="EI130" t="inlineStr"/>
+      <c r="EJ130" t="inlineStr"/>
+      <c r="EK130" t="inlineStr"/>
+      <c r="EL130" t="inlineStr"/>
+      <c r="EM130" t="inlineStr"/>
+      <c r="EN130" t="inlineStr"/>
+      <c r="EO130" t="inlineStr"/>
+      <c r="EP130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>17</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>CSKA Moskva</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Orenburg</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>45990.5625</v>
+      </c>
+      <c r="G131" t="n">
+        <v>2</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" t="n">
+        <v>2</v>
+      </c>
+      <c r="J131" t="n">
+        <v>5</v>
+      </c>
+      <c r="K131" t="n">
+        <v>10</v>
+      </c>
+      <c r="L131" t="n">
+        <v>15</v>
+      </c>
+      <c r="M131" t="n">
+        <v>2</v>
+      </c>
+      <c r="N131" t="n">
+        <v>2</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>6</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6</v>
+      </c>
+      <c r="S131" t="n">
+        <v>7</v>
+      </c>
+      <c r="T131" t="n">
+        <v>11</v>
+      </c>
+      <c r="U131" t="n">
+        <v>13</v>
+      </c>
+      <c r="V131" t="n">
+        <v>17</v>
+      </c>
+      <c r="W131" t="n">
+        <v>11</v>
+      </c>
+      <c r="X131" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>62</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>VEB Arena</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>3-ya Peschanaya ul., Moskva</t>
+        </is>
+      </c>
+      <c r="AC131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>101</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU131" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV131" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX131" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY131" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ131" t="n">
+        <v>54</v>
+      </c>
+      <c r="DA131" t="n">
+        <v>73</v>
+      </c>
+      <c r="DB131" t="n">
+        <v>46</v>
+      </c>
+      <c r="DC131" t="n">
+        <v>73</v>
+      </c>
+      <c r="DD131" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="DE131" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF131" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DG131" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DH131" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="DI131" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DJ131" t="n">
+        <v>47</v>
+      </c>
+      <c r="DK131" t="n">
+        <v>27</v>
+      </c>
+      <c r="DL131" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DM131" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DN131" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="DO131" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP131" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ131" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW131" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="DX131" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="DY131" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="DZ131" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="EA131" t="inlineStr"/>
+      <c r="EB131" t="inlineStr"/>
+      <c r="EC131" t="inlineStr"/>
+      <c r="ED131" t="inlineStr"/>
+      <c r="EE131" t="inlineStr"/>
+      <c r="EF131" t="inlineStr"/>
+      <c r="EG131" t="inlineStr"/>
+      <c r="EH131" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EI131" t="inlineStr">
+        <is>
+          <t>7.53</t>
+        </is>
+      </c>
+      <c r="EJ131" t="inlineStr">
+        <is>
+          <t>4.86</t>
+        </is>
+      </c>
+      <c r="EK131" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EL131" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EM131" t="inlineStr"/>
+      <c r="EN131" t="inlineStr"/>
+      <c r="EO131" t="inlineStr"/>
+      <c r="EP131" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
+++ b/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP131" headerRowCount="1">
-  <autoFilter ref="A1:EP131"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP136" headerRowCount="1">
+  <autoFilter ref="A1:EP136"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP131"/>
+  <dimension ref="A1:EP136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.8" customWidth="1" min="1" max="1"/>
@@ -1827,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2245,7 +2245,7 @@
         <v>0.89</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -3659,7 +3659,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4106,7 +4106,7 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DE7" t="n">
         <v>1</v>
@@ -4139,7 +4139,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4583,7 +4583,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5503,7 +5503,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5947,7 +5947,7 @@
         <v>2.56</v>
       </c>
       <c r="DO11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6411,7 +6411,7 @@
         <v>2.72</v>
       </c>
       <c r="DO12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6830,10 +6830,10 @@
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DE13" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DF13" t="n">
         <v>0</v>
@@ -6863,7 +6863,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7787,7 +7787,7 @@
         <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8747,7 +8747,7 @@
         <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9170,10 +9170,10 @@
         <v>50</v>
       </c>
       <c r="DD18" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DF18" t="n">
         <v>0</v>
@@ -9203,7 +9203,7 @@
         <v>1.28</v>
       </c>
       <c r="DO18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9645,7 +9645,7 @@
         <v>0.89</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DF19" t="n">
         <v>0</v>
@@ -9675,7 +9675,7 @@
         <v>2.42</v>
       </c>
       <c r="DO19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10078,10 +10078,10 @@
         <v>50</v>
       </c>
       <c r="DD20" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF20" t="n">
         <v>0</v>
@@ -10111,7 +10111,7 @@
         <v>1.82</v>
       </c>
       <c r="DO20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10529,7 +10529,7 @@
         <v>0.89</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF21" t="n">
         <v>1</v>
@@ -10559,7 +10559,7 @@
         <v>1.95</v>
       </c>
       <c r="DO21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -10986,7 +10986,7 @@
         <v>0</v>
       </c>
       <c r="DD22" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE22" t="n">
         <v>0.5</v>
@@ -11019,7 +11019,7 @@
         <v>0</v>
       </c>
       <c r="DO22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11446,7 +11446,7 @@
         <v>50</v>
       </c>
       <c r="DD23" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DE23" t="n">
         <v>1.38</v>
@@ -11479,7 +11479,7 @@
         <v>3.96</v>
       </c>
       <c r="DO23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -13363,7 +13363,7 @@
         <v>3.01</v>
       </c>
       <c r="DO27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13781,7 +13781,7 @@
         <v>2.78</v>
       </c>
       <c r="DE28" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DF28" t="n">
         <v>3</v>
@@ -13811,7 +13811,7 @@
         <v>2.04</v>
       </c>
       <c r="DO28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14249,7 +14249,7 @@
         <v>2.25</v>
       </c>
       <c r="DE29" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF29" t="n">
         <v>3</v>
@@ -14279,7 +14279,7 @@
         <v>3.23</v>
       </c>
       <c r="DO29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14718,7 +14718,7 @@
         <v>100</v>
       </c>
       <c r="DD30" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DE30" t="n">
         <v>1.56</v>
@@ -14751,7 +14751,7 @@
         <v>3.75</v>
       </c>
       <c r="DO30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15211,7 +15211,7 @@
         <v>2.03</v>
       </c>
       <c r="DO31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15637,7 +15637,7 @@
         <v>0.57</v>
       </c>
       <c r="DE32" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF32" t="n">
         <v>0</v>
@@ -16102,7 +16102,7 @@
         <v>50</v>
       </c>
       <c r="DD33" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DE33" t="n">
         <v>0.38</v>
@@ -16135,7 +16135,7 @@
         <v>3.03</v>
       </c>
       <c r="DO33" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16546,10 +16546,10 @@
         <v>100</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE34" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DF34" t="n">
         <v>3</v>
@@ -16579,7 +16579,7 @@
         <v>2.73</v>
       </c>
       <c r="DO34" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17015,7 +17015,7 @@
         <v>2.48</v>
       </c>
       <c r="DO35" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17470,10 +17470,10 @@
         <v>100</v>
       </c>
       <c r="DD36" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DE36" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DF36" t="n">
         <v>1.5</v>
@@ -17503,7 +17503,7 @@
         <v>2.73</v>
       </c>
       <c r="DO36" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18411,7 +18411,7 @@
         <v>2.06</v>
       </c>
       <c r="DO38" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -18875,7 +18875,7 @@
         <v>2.78</v>
       </c>
       <c r="DO39" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19298,7 +19298,7 @@
         <v>50</v>
       </c>
       <c r="DD40" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DE40" t="n">
         <v>0.44</v>
@@ -20251,7 +20251,7 @@
         <v>2.35</v>
       </c>
       <c r="DO42" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -20693,7 +20693,7 @@
         <v>1.89</v>
       </c>
       <c r="DE43" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF43" t="n">
         <v>2.33</v>
@@ -20723,7 +20723,7 @@
         <v>2.55</v>
       </c>
       <c r="DO43" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21154,7 +21154,7 @@
         <v>84</v>
       </c>
       <c r="DD44" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DE44" t="n">
         <v>0.25</v>
@@ -21651,7 +21651,7 @@
         <v>2.4</v>
       </c>
       <c r="DO45" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22131,7 +22131,7 @@
         <v>2.53</v>
       </c>
       <c r="DO46" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22579,7 +22579,7 @@
         <v>2.33</v>
       </c>
       <c r="DO47" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23937,7 +23937,7 @@
         <v>0.89</v>
       </c>
       <c r="DE50" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DF50" t="n">
         <v>0.75</v>
@@ -23967,7 +23967,7 @@
         <v>2.38</v>
       </c>
       <c r="DO50" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24382,7 +24382,7 @@
         <v>67</v>
       </c>
       <c r="DD51" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DE51" t="n">
         <v>0.38</v>
@@ -24415,7 +24415,7 @@
         <v>2.54</v>
       </c>
       <c r="DO51" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25302,7 +25302,7 @@
         <v>75</v>
       </c>
       <c r="DD53" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DE53" t="n">
         <v>0.67</v>
@@ -25335,7 +25335,7 @@
         <v>3.04</v>
       </c>
       <c r="DO53" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -25783,7 +25783,7 @@
         <v>3.31</v>
       </c>
       <c r="DO54" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26205,7 +26205,7 @@
         <v>2.25</v>
       </c>
       <c r="DE55" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DF55" t="n">
         <v>2.33</v>
@@ -26235,7 +26235,7 @@
         <v>2.77</v>
       </c>
       <c r="DO55" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -26695,7 +26695,7 @@
         <v>3.14</v>
       </c>
       <c r="DO56" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27137,7 +27137,7 @@
         <v>1.5</v>
       </c>
       <c r="DE57" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF57" t="n">
         <v>2</v>
@@ -28534,10 +28534,10 @@
         <v>100</v>
       </c>
       <c r="DD60" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DF60" t="n">
         <v>2</v>
@@ -28567,7 +28567,7 @@
         <v>2.92</v>
       </c>
       <c r="DO60" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -28993,7 +28993,7 @@
         <v>1.33</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF61" t="n">
         <v>1.75</v>
@@ -29023,7 +29023,7 @@
         <v>3.31</v>
       </c>
       <c r="DO61" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -29462,7 +29462,7 @@
         <v>67</v>
       </c>
       <c r="DD62" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DE62" t="n">
         <v>1.63</v>
@@ -29495,7 +29495,7 @@
         <v>3.61</v>
       </c>
       <c r="DO62" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -30358,7 +30358,7 @@
         <v>100</v>
       </c>
       <c r="DD64" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE64" t="n">
         <v>1.56</v>
@@ -30391,7 +30391,7 @@
         <v>2.75</v>
       </c>
       <c r="DO64" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP64" t="b">
         <v>0</v>
@@ -30846,7 +30846,7 @@
         <v>67</v>
       </c>
       <c r="DD65" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DE65" t="n">
         <v>1.38</v>
@@ -30879,7 +30879,7 @@
         <v>3.14</v>
       </c>
       <c r="DO65" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -31335,7 +31335,7 @@
         <v>2.54</v>
       </c>
       <c r="DO66" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -31757,7 +31757,7 @@
         <v>0.89</v>
       </c>
       <c r="DE67" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DF67" t="n">
         <v>0.5</v>
@@ -31787,7 +31787,7 @@
         <v>3</v>
       </c>
       <c r="DO67" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -32217,7 +32217,7 @@
         <v>1.5</v>
       </c>
       <c r="DE68" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DF68" t="n">
         <v>2.33</v>
@@ -32689,7 +32689,7 @@
         <v>0.89</v>
       </c>
       <c r="DE69" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF69" t="n">
         <v>0.8</v>
@@ -32719,7 +32719,7 @@
         <v>2.57</v>
       </c>
       <c r="DO69" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -33133,7 +33133,7 @@
         <v>2.22</v>
       </c>
       <c r="DE70" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DF70" t="n">
         <v>1.75</v>
@@ -33163,7 +33163,7 @@
         <v>2.43</v>
       </c>
       <c r="DO70" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -33590,7 +33590,7 @@
         <v>71</v>
       </c>
       <c r="DD71" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE71" t="n">
         <v>1</v>
@@ -33623,7 +33623,7 @@
         <v>2.46</v>
       </c>
       <c r="DO71" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP71" t="b">
         <v>0</v>
@@ -34062,7 +34062,7 @@
         <v>63</v>
       </c>
       <c r="DD72" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DE72" t="n">
         <v>1.56</v>
@@ -34095,7 +34095,7 @@
         <v>3.42</v>
       </c>
       <c r="DO72" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35017,7 +35017,7 @@
         <v>1.5</v>
       </c>
       <c r="DE74" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF74" t="n">
         <v>1.75</v>
@@ -35047,7 +35047,7 @@
         <v>2.54</v>
       </c>
       <c r="DO74" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -35474,7 +35474,7 @@
         <v>88</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DE75" t="n">
         <v>1.63</v>
@@ -35507,7 +35507,7 @@
         <v>2.91</v>
       </c>
       <c r="DO75" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -35929,7 +35929,7 @@
         <v>2.25</v>
       </c>
       <c r="DE76" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DF76" t="n">
         <v>2</v>
@@ -35959,7 +35959,7 @@
         <v>3.09</v>
       </c>
       <c r="DO76" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -36414,7 +36414,7 @@
         <v>75</v>
       </c>
       <c r="DD77" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DE77" t="n">
         <v>2</v>
@@ -36447,7 +36447,7 @@
         <v>2.97</v>
       </c>
       <c r="DO77" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP77" t="b">
         <v>0</v>
@@ -36862,7 +36862,7 @@
         <v>88</v>
       </c>
       <c r="DD78" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DE78" t="n">
         <v>0.5</v>
@@ -36895,7 +36895,7 @@
         <v>3.2</v>
       </c>
       <c r="DO78" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -37359,7 +37359,7 @@
         <v>3.14</v>
       </c>
       <c r="DO79" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -38287,7 +38287,7 @@
         <v>2.45</v>
       </c>
       <c r="DO81" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -38723,7 +38723,7 @@
         <v>2.79</v>
       </c>
       <c r="DO82" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -39145,7 +39145,7 @@
         <v>1.89</v>
       </c>
       <c r="DE83" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DF83" t="n">
         <v>2</v>
@@ -39175,7 +39175,7 @@
         <v>2.19</v>
       </c>
       <c r="DO83" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -39598,7 +39598,7 @@
         <v>70</v>
       </c>
       <c r="DD84" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DE84" t="n">
         <v>0.67</v>
@@ -39631,7 +39631,7 @@
         <v>3.27</v>
       </c>
       <c r="DO84" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -40049,7 +40049,7 @@
         <v>1.33</v>
       </c>
       <c r="DE85" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DF85" t="n">
         <v>1.6</v>
@@ -40079,7 +40079,7 @@
         <v>3.26</v>
       </c>
       <c r="DO85" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -40555,7 +40555,7 @@
         <v>2.29</v>
       </c>
       <c r="DO86" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -41469,7 +41469,7 @@
         <v>2.78</v>
       </c>
       <c r="DE88" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF88" t="n">
         <v>2.6</v>
@@ -41499,7 +41499,7 @@
         <v>3.03</v>
       </c>
       <c r="DO88" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -41938,7 +41938,7 @@
         <v>65</v>
       </c>
       <c r="DD89" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE89" t="n">
         <v>0.25</v>
@@ -42091,162 +42091,170 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
         <v>45948.41666666666</v>
       </c>
       <c r="G90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
         <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K90" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L90" t="n">
+        <v>9</v>
+      </c>
+      <c r="M90" t="n">
+        <v>2</v>
+      </c>
+      <c r="N90" t="n">
+        <v>2</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
         <v>11</v>
       </c>
-      <c r="M90" t="n">
-        <v>1</v>
-      </c>
-      <c r="N90" t="n">
-        <v>2</v>
-      </c>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>3</v>
-      </c>
       <c r="R90" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T90" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="U90" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="V90" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W90" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="X90" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Y90" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="Z90" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA90" t="inlineStr"/>
-      <c r="AB90" t="inlineStr"/>
+        <v>35</v>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>Stadion Nizhny Novgorod</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>ul. Dolzhanskaya, Nizhniy Novgorod</t>
+        </is>
+      </c>
       <c r="AC90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD90" t="n">
         <v>2</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.9</v>
+        <v>2.29</v>
       </c>
       <c r="AF90" t="n">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="AG90" t="n">
-        <v>3.28</v>
+        <v>2.57</v>
       </c>
       <c r="AH90" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AI90" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AJ90" t="n">
-        <v>3.08</v>
+        <v>2.66</v>
       </c>
       <c r="AK90" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AL90" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="AM90" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AN90" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AO90" t="n">
-        <v>2.62</v>
+        <v>2.16</v>
       </c>
       <c r="AP90" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR90" t="n">
-        <v>2.74</v>
+        <v>2.51</v>
       </c>
       <c r="AS90" t="n">
-        <v>3.04</v>
+        <v>3.32</v>
       </c>
       <c r="AT90" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AU90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV90" t="n">
         <v>0</v>
       </c>
       <c r="AW90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ90" t="n">
         <v>1</v>
       </c>
       <c r="BA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB90" t="n">
-        <v>-1</v>
+        <v>668270</v>
       </c>
       <c r="BC90" t="n">
         <v>0</v>
       </c>
       <c r="BD90" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BE90" t="n">
         <v>0</v>
@@ -42279,7 +42287,7 @@
         <v>-1</v>
       </c>
       <c r="BO90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP90" t="n">
         <v>0</v>
@@ -42291,7 +42299,7 @@
         <v>2</v>
       </c>
       <c r="BS90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT90" t="n">
         <v>3</v>
@@ -42300,25 +42308,25 @@
         <v>1</v>
       </c>
       <c r="BV90" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="BW90" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="BX90" t="n">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="BY90" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BZ90" t="n">
-        <v>1.44</v>
+        <v>2.76</v>
       </c>
       <c r="CA90" t="n">
-        <v>1.34</v>
+        <v>1.09</v>
       </c>
       <c r="CB90" t="n">
-        <v>2.78</v>
+        <v>3.85</v>
       </c>
       <c r="CC90" t="n">
         <v>0</v>
@@ -42366,82 +42374,82 @@
         <v>1</v>
       </c>
       <c r="CR90" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS90" t="n">
         <v>21</v>
       </c>
-      <c r="CS90" t="n">
-        <v>23</v>
-      </c>
       <c r="CT90" t="n">
         <v>1</v>
       </c>
       <c r="CU90" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="CV90" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CW90" t="n">
         <v>1</v>
       </c>
       <c r="CX90" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="CY90" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="CZ90" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="DA90" t="n">
         <v>100</v>
       </c>
       <c r="DB90" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="DC90" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="DD90" t="n">
-        <v>1.5</v>
+        <v>0.89</v>
       </c>
       <c r="DE90" t="n">
-        <v>0.5</v>
+        <v>1.63</v>
       </c>
       <c r="DF90" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="DG90" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="DH90" t="n">
-        <v>1.09</v>
+        <v>0.55</v>
       </c>
       <c r="DI90" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="DJ90" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="DK90" t="n">
         <v>0</v>
       </c>
       <c r="DL90" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DM90" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="DN90" t="n">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="DO90" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
       </c>
       <c r="DQ90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR90" t="b">
         <v>0</v>
@@ -42456,70 +42464,82 @@
         <v>0</v>
       </c>
       <c r="DV90" t="b">
-        <v>1</v>
-      </c>
-      <c r="DW90" t="inlineStr"/>
-      <c r="DX90" t="inlineStr"/>
-      <c r="DY90" t="inlineStr"/>
-      <c r="DZ90" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="DW90" t="n">
+        <v>8</v>
+      </c>
+      <c r="DX90" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="DY90" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="DZ90" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
       <c r="EA90" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EB90" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="EC90" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="ED90" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EE90" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EF90" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="EG90" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="EH90" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="EI90" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="EJ90" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="EK90" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EL90" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="EM90" t="inlineStr"/>
@@ -42543,170 +42563,162 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F91" s="2" t="n">
         <v>45948.41666666666</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91" t="n">
         <v>1</v>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J91" t="n">
+        <v>5</v>
+      </c>
+      <c r="K91" t="n">
         <v>6</v>
       </c>
-      <c r="K91" t="n">
+      <c r="L91" t="n">
+        <v>11</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1</v>
+      </c>
+      <c r="N91" t="n">
+        <v>2</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
         <v>3</v>
       </c>
-      <c r="L91" t="n">
-        <v>9</v>
-      </c>
-      <c r="M91" t="n">
-        <v>2</v>
-      </c>
-      <c r="N91" t="n">
-        <v>2</v>
-      </c>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>11</v>
-      </c>
       <c r="R91" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S91" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T91" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="U91" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="V91" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W91" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X91" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Y91" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Z91" t="n">
-        <v>35</v>
-      </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>Stadion Nizhny Novgorod</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>ul. Dolzhanskaya, Nizhniy Novgorod</t>
-        </is>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="AA91" t="inlineStr"/>
+      <c r="AB91" t="inlineStr"/>
       <c r="AC91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD91" t="n">
         <v>2</v>
       </c>
       <c r="AE91" t="n">
-        <v>2.29</v>
+        <v>1.9</v>
       </c>
       <c r="AF91" t="n">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
       <c r="AG91" t="n">
-        <v>2.57</v>
+        <v>3.28</v>
       </c>
       <c r="AH91" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AI91" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AJ91" t="n">
-        <v>2.66</v>
+        <v>3.08</v>
       </c>
       <c r="AK91" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="AL91" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="AM91" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AN91" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AO91" t="n">
-        <v>2.16</v>
+        <v>2.62</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AR91" t="n">
-        <v>2.51</v>
+        <v>2.74</v>
       </c>
       <c r="AS91" t="n">
-        <v>3.32</v>
+        <v>3.04</v>
       </c>
       <c r="AT91" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AU91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV91" t="n">
         <v>0</v>
       </c>
       <c r="AW91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ91" t="n">
         <v>1</v>
       </c>
       <c r="BA91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB91" t="n">
-        <v>668270</v>
+        <v>-1</v>
       </c>
       <c r="BC91" t="n">
         <v>0</v>
       </c>
       <c r="BD91" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BE91" t="n">
         <v>0</v>
@@ -42739,7 +42751,7 @@
         <v>-1</v>
       </c>
       <c r="BO91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP91" t="n">
         <v>0</v>
@@ -42751,7 +42763,7 @@
         <v>2</v>
       </c>
       <c r="BS91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT91" t="n">
         <v>3</v>
@@ -42760,25 +42772,25 @@
         <v>1</v>
       </c>
       <c r="BV91" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="BW91" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="BX91" t="n">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="BY91" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="BZ91" t="n">
-        <v>2.76</v>
+        <v>1.44</v>
       </c>
       <c r="CA91" t="n">
-        <v>1.09</v>
+        <v>1.34</v>
       </c>
       <c r="CB91" t="n">
-        <v>3.85</v>
+        <v>2.78</v>
       </c>
       <c r="CC91" t="n">
         <v>0</v>
@@ -42826,73 +42838,73 @@
         <v>1</v>
       </c>
       <c r="CR91" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CS91" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CT91" t="n">
         <v>1</v>
       </c>
       <c r="CU91" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="CV91" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CW91" t="n">
         <v>1</v>
       </c>
       <c r="CX91" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="CY91" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="CZ91" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="DA91" t="n">
         <v>100</v>
       </c>
       <c r="DB91" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="DC91" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="DD91" t="n">
-        <v>0.89</v>
+        <v>1.5</v>
       </c>
       <c r="DE91" t="n">
-        <v>1.63</v>
+        <v>0.5</v>
       </c>
       <c r="DF91" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="DG91" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="DH91" t="n">
-        <v>0.55</v>
+        <v>1.09</v>
       </c>
       <c r="DI91" t="n">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="DJ91" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="DK91" t="n">
         <v>0</v>
       </c>
       <c r="DL91" t="n">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="DM91" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="DN91" t="n">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="DO91" t="n">
         <v>17</v>
@@ -42901,7 +42913,7 @@
         <v>1</v>
       </c>
       <c r="DQ91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR91" t="b">
         <v>0</v>
@@ -42916,82 +42928,70 @@
         <v>0</v>
       </c>
       <c r="DV91" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW91" t="n">
-        <v>8</v>
-      </c>
-      <c r="DX91" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="DY91" t="inlineStr">
-        <is>
-          <t>80%</t>
-        </is>
-      </c>
-      <c r="DZ91" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="DW91" t="inlineStr"/>
+      <c r="DX91" t="inlineStr"/>
+      <c r="DY91" t="inlineStr"/>
+      <c r="DZ91" t="inlineStr"/>
       <c r="EA91" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EB91" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="EC91" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="ED91" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EE91" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EF91" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="EG91" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="EH91" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="EI91" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EJ91" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="EK91" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="EL91" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EM91" t="inlineStr"/>
@@ -43367,7 +43367,7 @@
         <v>2.78</v>
       </c>
       <c r="DO92" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -44307,7 +44307,7 @@
         <v>3.2</v>
       </c>
       <c r="DO94" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -45239,7 +45239,7 @@
         <v>2.71</v>
       </c>
       <c r="DO96" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -45687,7 +45687,7 @@
         <v>3.18</v>
       </c>
       <c r="DO97" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -46159,7 +46159,7 @@
         <v>2.97</v>
       </c>
       <c r="DO98" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -46586,7 +46586,7 @@
         <v>72</v>
       </c>
       <c r="DD99" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DE99" t="n">
         <v>0.25</v>
@@ -47033,7 +47033,7 @@
         <v>2.78</v>
       </c>
       <c r="DE100" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DF100" t="n">
         <v>2.67</v>
@@ -47063,7 +47063,7 @@
         <v>2.59</v>
       </c>
       <c r="DO100" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -47489,7 +47489,7 @@
         <v>0.89</v>
       </c>
       <c r="DE101" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DF101" t="n">
         <v>0.67</v>
@@ -47519,7 +47519,7 @@
         <v>2.97</v>
       </c>
       <c r="DO101" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -47991,7 +47991,7 @@
         <v>3.06</v>
       </c>
       <c r="DO102" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP102" t="b">
         <v>0</v>
@@ -48394,10 +48394,10 @@
         <v>60</v>
       </c>
       <c r="DD103" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DE103" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF103" t="n">
         <v>2.6</v>
@@ -48427,7 +48427,7 @@
         <v>3.41</v>
       </c>
       <c r="DO103" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -48866,10 +48866,10 @@
         <v>65</v>
       </c>
       <c r="DD104" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DE104" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DF104" t="n">
         <v>2</v>
@@ -48899,7 +48899,7 @@
         <v>3.31</v>
       </c>
       <c r="DO104" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -49322,7 +49322,7 @@
         <v>57</v>
       </c>
       <c r="DD105" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DE105" t="n">
         <v>0.44</v>
@@ -50233,7 +50233,7 @@
         <v>1.5</v>
       </c>
       <c r="DE107" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DF107" t="n">
         <v>1.5</v>
@@ -50697,7 +50697,7 @@
         <v>1.89</v>
       </c>
       <c r="DE108" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF108" t="n">
         <v>1.86</v>
@@ -50727,7 +50727,7 @@
         <v>2.61</v>
       </c>
       <c r="DO108" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP108" t="b">
         <v>0</v>
@@ -51182,7 +51182,7 @@
         <v>75</v>
       </c>
       <c r="DD109" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DE109" t="n">
         <v>1.63</v>
@@ -51215,7 +51215,7 @@
         <v>2.81</v>
       </c>
       <c r="DO109" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -51646,10 +51646,10 @@
         <v>77</v>
       </c>
       <c r="DD110" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DE110" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DF110" t="n">
         <v>2.67</v>
@@ -51679,7 +51679,7 @@
         <v>3.44</v>
       </c>
       <c r="DO110" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -52558,7 +52558,7 @@
         <v>80</v>
       </c>
       <c r="DD112" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE112" t="n">
         <v>0.67</v>
@@ -52591,7 +52591,7 @@
         <v>2.57</v>
       </c>
       <c r="DO112" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -53030,10 +53030,10 @@
         <v>59</v>
       </c>
       <c r="DD113" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DE113" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF113" t="n">
         <v>2.14</v>
@@ -53063,7 +53063,7 @@
         <v>3.33</v>
       </c>
       <c r="DO113" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -53527,7 +53527,7 @@
         <v>3.16</v>
       </c>
       <c r="DO114" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP114" t="b">
         <v>1</v>
@@ -53941,7 +53941,7 @@
         <v>0.89</v>
       </c>
       <c r="DE115" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DF115" t="n">
         <v>1</v>
@@ -53971,7 +53971,7 @@
         <v>2.71</v>
       </c>
       <c r="DO115" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP115" t="b">
         <v>0</v>
@@ -55343,7 +55343,7 @@
         <v>2.53</v>
       </c>
       <c r="DO118" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -55783,7 +55783,7 @@
         <v>3.04</v>
       </c>
       <c r="DO119" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -56206,10 +56206,10 @@
         <v>75</v>
       </c>
       <c r="DD120" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DE120" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF120" t="n">
         <v>1.67</v>
@@ -56239,7 +56239,7 @@
         <v>3.17</v>
       </c>
       <c r="DO120" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -56694,7 +56694,7 @@
         <v>67</v>
       </c>
       <c r="DD121" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE121" t="n">
         <v>2</v>
@@ -56727,7 +56727,7 @@
         <v>2.71</v>
       </c>
       <c r="DO121" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -57627,7 +57627,7 @@
         <v>2.75</v>
       </c>
       <c r="DO123" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP123" t="b">
         <v>0</v>
@@ -58099,7 +58099,7 @@
         <v>3.03</v>
       </c>
       <c r="DO124" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -58571,7 +58571,7 @@
         <v>2.42</v>
       </c>
       <c r="DO125" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP125" t="b">
         <v>1</v>
@@ -59035,7 +59035,7 @@
         <v>2.45</v>
       </c>
       <c r="DO126" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP126" t="b">
         <v>1</v>
@@ -59483,7 +59483,7 @@
         <v>2.8</v>
       </c>
       <c r="DO127" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP127" t="b">
         <v>1</v>
@@ -60411,7 +60411,7 @@
         <v>3.03</v>
       </c>
       <c r="DO129" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP129" t="b">
         <v>1</v>
@@ -60564,13 +60564,13 @@
         <v>6</v>
       </c>
       <c r="R130" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S130" t="n">
         <v>7</v>
       </c>
       <c r="T130" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U130" t="n">
         <v>13</v>
@@ -60582,7 +60582,7 @@
         <v>13</v>
       </c>
       <c r="X130" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y130" t="n">
         <v>56</v>
@@ -60743,10 +60743,10 @@
         <v>1.65</v>
       </c>
       <c r="CA130" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="CB130" t="n">
-        <v>3.26</v>
+        <v>3.33</v>
       </c>
       <c r="CC130" t="n">
         <v>0</v>
@@ -60794,7 +60794,7 @@
         <v>1</v>
       </c>
       <c r="CR130" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="CS130" t="n">
         <v>20</v>
@@ -60812,7 +60812,7 @@
         <v>1</v>
       </c>
       <c r="CX130" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CY130" t="n">
         <v>9</v>
@@ -60890,22 +60890,70 @@
       <c r="DX130" t="inlineStr"/>
       <c r="DY130" t="inlineStr"/>
       <c r="DZ130" t="inlineStr"/>
-      <c r="EA130" t="inlineStr"/>
-      <c r="EB130" t="inlineStr"/>
-      <c r="EC130" t="inlineStr"/>
+      <c r="EA130" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EB130" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="EC130" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
       <c r="ED130" t="inlineStr"/>
       <c r="EE130" t="inlineStr"/>
       <c r="EF130" t="inlineStr"/>
       <c r="EG130" t="inlineStr"/>
-      <c r="EH130" t="inlineStr"/>
-      <c r="EI130" t="inlineStr"/>
-      <c r="EJ130" t="inlineStr"/>
-      <c r="EK130" t="inlineStr"/>
-      <c r="EL130" t="inlineStr"/>
-      <c r="EM130" t="inlineStr"/>
-      <c r="EN130" t="inlineStr"/>
-      <c r="EO130" t="inlineStr"/>
-      <c r="EP130" t="inlineStr"/>
+      <c r="EH130" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EI130" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="EJ130" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="EK130" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EL130" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EM130" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EN130" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EO130" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EP130" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -61137,28 +61185,28 @@
         <v>2</v>
       </c>
       <c r="BU131" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BV131" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="BW131" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="BX131" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="BY131" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="BZ131" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="CA131" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="CB131" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="CC131" t="n">
         <v>0</v>
@@ -61215,10 +61263,10 @@
         <v>1</v>
       </c>
       <c r="CU131" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CV131" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="CW131" t="n">
         <v>1</v>
@@ -61323,33 +61371,2393 @@
       <c r="EG131" t="inlineStr"/>
       <c r="EH131" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EI131" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>7.64</t>
         </is>
       </c>
       <c r="EJ131" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="EK131" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="EL131" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EM131" t="inlineStr"/>
       <c r="EN131" t="inlineStr"/>
       <c r="EO131" t="inlineStr"/>
       <c r="EP131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>17</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Baltika</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Spartak Moskva</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>45990.6875</v>
+      </c>
+      <c r="G132" t="n">
+        <v>1</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" t="n">
+        <v>1</v>
+      </c>
+      <c r="J132" t="n">
+        <v>3</v>
+      </c>
+      <c r="K132" t="n">
+        <v>13</v>
+      </c>
+      <c r="L132" t="n">
+        <v>16</v>
+      </c>
+      <c r="M132" t="n">
+        <v>2</v>
+      </c>
+      <c r="N132" t="n">
+        <v>2</v>
+      </c>
+      <c r="O132" t="n">
+        <v>1</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>3</v>
+      </c>
+      <c r="R132" t="n">
+        <v>5</v>
+      </c>
+      <c r="S132" t="n">
+        <v>6</v>
+      </c>
+      <c r="T132" t="n">
+        <v>14</v>
+      </c>
+      <c r="U132" t="n">
+        <v>9</v>
+      </c>
+      <c r="V132" t="n">
+        <v>19</v>
+      </c>
+      <c r="W132" t="n">
+        <v>12</v>
+      </c>
+      <c r="X132" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>74</v>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>Complexe Sportif Jean Bianchi 1</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>21 Avenue Marechal Leclerc, Saint-André-les-Vergers</t>
+        </is>
+      </c>
+      <c r="AC132" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>1493</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>63</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>67</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>102</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>2</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU132" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV132" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX132" t="n">
+        <v>17</v>
+      </c>
+      <c r="CY132" t="n">
+        <v>2</v>
+      </c>
+      <c r="CZ132" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA132" t="n">
+        <v>86</v>
+      </c>
+      <c r="DB132" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC132" t="n">
+        <v>71</v>
+      </c>
+      <c r="DD132" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE132" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF132" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DG132" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DH132" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="DI132" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DJ132" t="n">
+        <v>58</v>
+      </c>
+      <c r="DK132" t="n">
+        <v>15</v>
+      </c>
+      <c r="DL132" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DM132" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DN132" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="DO132" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP132" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW132" t="n">
+        <v>2</v>
+      </c>
+      <c r="DX132" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="DY132" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="DZ132" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA132" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
+      <c r="EB132" t="inlineStr">
+        <is>
+          <t>5.45</t>
+        </is>
+      </c>
+      <c r="EC132" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="ED132" t="inlineStr"/>
+      <c r="EE132" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EF132" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EG132" t="inlineStr"/>
+      <c r="EH132" t="inlineStr">
+        <is>
+          <t>3.56</t>
+        </is>
+      </c>
+      <c r="EI132" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EJ132" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="EK132" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EL132" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EM132" t="inlineStr"/>
+      <c r="EN132" t="inlineStr"/>
+      <c r="EO132" t="inlineStr"/>
+      <c r="EP132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>17</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Krasnodar</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Krylya Sovetov</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>45991.45833333334</v>
+      </c>
+      <c r="G133" t="n">
+        <v>5</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" t="n">
+        <v>5</v>
+      </c>
+      <c r="J133" t="n">
+        <v>11</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="n">
+        <v>11</v>
+      </c>
+      <c r="M133" t="n">
+        <v>2</v>
+      </c>
+      <c r="N133" t="n">
+        <v>3</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>8</v>
+      </c>
+      <c r="R133" t="n">
+        <v>1</v>
+      </c>
+      <c r="S133" t="n">
+        <v>17</v>
+      </c>
+      <c r="T133" t="n">
+        <v>4</v>
+      </c>
+      <c r="U133" t="n">
+        <v>25</v>
+      </c>
+      <c r="V133" t="n">
+        <v>5</v>
+      </c>
+      <c r="W133" t="n">
+        <v>8</v>
+      </c>
+      <c r="X133" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>69</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>31</v>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>Stadion FK Krasnodar</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>ul. Vostochno-Kruglikovskaya 126, Krasnodar</t>
+        </is>
+      </c>
+      <c r="AC133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>926</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>72</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>19</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>106</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>52</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU133" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV133" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX133" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY133" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ133" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA133" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB133" t="n">
+        <v>19</v>
+      </c>
+      <c r="DC133" t="n">
+        <v>76</v>
+      </c>
+      <c r="DD133" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DE133" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="DF133" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DG133" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DH133" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DI133" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DJ133" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK133" t="n">
+        <v>19</v>
+      </c>
+      <c r="DL133" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="DM133" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="DN133" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="DO133" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU133" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV133" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW133" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="DX133" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="DY133" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="DZ133" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA133" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EB133" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EC133" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="ED133" t="inlineStr"/>
+      <c r="EE133" t="inlineStr"/>
+      <c r="EF133" t="inlineStr"/>
+      <c r="EG133" t="inlineStr"/>
+      <c r="EH133" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EI133" t="inlineStr">
+        <is>
+          <t>10.52</t>
+        </is>
+      </c>
+      <c r="EJ133" t="inlineStr">
+        <is>
+          <t>5.65</t>
+        </is>
+      </c>
+      <c r="EK133" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EL133" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EM133" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EN133" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EO133" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EP133" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>17</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Akhmat Grozny</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Dinamo Moskva</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>45991.5625</v>
+      </c>
+      <c r="G134" t="n">
+        <v>2</v>
+      </c>
+      <c r="H134" t="n">
+        <v>1</v>
+      </c>
+      <c r="I134" t="n">
+        <v>3</v>
+      </c>
+      <c r="J134" t="n">
+        <v>7</v>
+      </c>
+      <c r="K134" t="n">
+        <v>8</v>
+      </c>
+      <c r="L134" t="n">
+        <v>15</v>
+      </c>
+      <c r="M134" t="n">
+        <v>3</v>
+      </c>
+      <c r="N134" t="n">
+        <v>2</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>6</v>
+      </c>
+      <c r="R134" t="n">
+        <v>4</v>
+      </c>
+      <c r="S134" t="n">
+        <v>12</v>
+      </c>
+      <c r="T134" t="n">
+        <v>18</v>
+      </c>
+      <c r="U134" t="n">
+        <v>18</v>
+      </c>
+      <c r="V134" t="n">
+        <v>22</v>
+      </c>
+      <c r="W134" t="n">
+        <v>8</v>
+      </c>
+      <c r="X134" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>Akhmat Arena</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
+        </is>
+      </c>
+      <c r="AC134" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>923</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>39</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>45</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>87</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>85</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU134" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV134" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX134" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY134" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ134" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA134" t="n">
+        <v>72</v>
+      </c>
+      <c r="DB134" t="n">
+        <v>22</v>
+      </c>
+      <c r="DC134" t="n">
+        <v>65</v>
+      </c>
+      <c r="DD134" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DE134" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF134" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DG134" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DH134" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI134" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DJ134" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK134" t="n">
+        <v>29</v>
+      </c>
+      <c r="DL134" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DM134" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DN134" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="DO134" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP134" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ134" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR134" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS134" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT134" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU134" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV134" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW134" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="DX134" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="DY134" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="DZ134" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA134" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EB134" t="inlineStr">
+        <is>
+          <t>2.97</t>
+        </is>
+      </c>
+      <c r="EC134" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="ED134" t="inlineStr"/>
+      <c r="EE134" t="inlineStr"/>
+      <c r="EF134" t="inlineStr"/>
+      <c r="EG134" t="inlineStr"/>
+      <c r="EH134" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="EI134" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EJ134" t="inlineStr">
+        <is>
+          <t>3.53</t>
+        </is>
+      </c>
+      <c r="EK134" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EL134" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EM134" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EN134" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EO134" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EP134" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>17</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Rostov</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Lokomotiv Moskva</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>45991.5625</v>
+      </c>
+      <c r="G135" t="n">
+        <v>1</v>
+      </c>
+      <c r="H135" t="n">
+        <v>3</v>
+      </c>
+      <c r="I135" t="n">
+        <v>4</v>
+      </c>
+      <c r="J135" t="n">
+        <v>2</v>
+      </c>
+      <c r="K135" t="n">
+        <v>4</v>
+      </c>
+      <c r="L135" t="n">
+        <v>6</v>
+      </c>
+      <c r="M135" t="n">
+        <v>2</v>
+      </c>
+      <c r="N135" t="n">
+        <v>1</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>3</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6</v>
+      </c>
+      <c r="S135" t="n">
+        <v>8</v>
+      </c>
+      <c r="T135" t="n">
+        <v>9</v>
+      </c>
+      <c r="U135" t="n">
+        <v>11</v>
+      </c>
+      <c r="V135" t="n">
+        <v>15</v>
+      </c>
+      <c r="W135" t="n">
+        <v>16</v>
+      </c>
+      <c r="X135" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>Stadion Central’nyj im. I.P. Chayka</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>ul. Suvorova, Peschanokopskoye</t>
+        </is>
+      </c>
+      <c r="AC135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>920</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>66</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>74</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>38</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>127</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>97</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>9</v>
+      </c>
+      <c r="CT135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU135" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV135" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX135" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY135" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ135" t="n">
+        <v>26</v>
+      </c>
+      <c r="DA135" t="n">
+        <v>72</v>
+      </c>
+      <c r="DB135" t="n">
+        <v>7</v>
+      </c>
+      <c r="DC135" t="n">
+        <v>66</v>
+      </c>
+      <c r="DD135" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DE135" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DF135" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DG135" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DH135" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DI135" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="DJ135" t="n">
+        <v>75</v>
+      </c>
+      <c r="DK135" t="n">
+        <v>29</v>
+      </c>
+      <c r="DL135" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DM135" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DN135" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="DO135" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP135" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ135" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR135" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS135" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV135" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW135" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="DX135" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="DY135" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="DZ135" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA135" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EB135" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="EC135" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="ED135" t="inlineStr"/>
+      <c r="EE135" t="inlineStr"/>
+      <c r="EF135" t="inlineStr"/>
+      <c r="EG135" t="inlineStr"/>
+      <c r="EH135" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="EI135" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="EJ135" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="EK135" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EL135" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EM135" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EN135" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EO135" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EP135" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>17</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Zenit</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>45991.66666666666</v>
+      </c>
+      <c r="G136" t="n">
+        <v>1</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" t="n">
+        <v>1</v>
+      </c>
+      <c r="J136" t="n">
+        <v>3</v>
+      </c>
+      <c r="K136" t="n">
+        <v>1</v>
+      </c>
+      <c r="L136" t="n">
+        <v>4</v>
+      </c>
+      <c r="M136" t="n">
+        <v>1</v>
+      </c>
+      <c r="N136" t="n">
+        <v>6</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>1</v>
+      </c>
+      <c r="R136" t="n">
+        <v>2</v>
+      </c>
+      <c r="S136" t="n">
+        <v>7</v>
+      </c>
+      <c r="T136" t="n">
+        <v>6</v>
+      </c>
+      <c r="U136" t="n">
+        <v>8</v>
+      </c>
+      <c r="V136" t="n">
+        <v>8</v>
+      </c>
+      <c r="W136" t="n">
+        <v>9</v>
+      </c>
+      <c r="X136" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>68</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA136" t="inlineStr"/>
+      <c r="AB136" t="inlineStr"/>
+      <c r="AC136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>921</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>56</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>34</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>112</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>66</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU136" t="n">
+        <v>23</v>
+      </c>
+      <c r="CV136" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX136" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY136" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ136" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA136" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB136" t="n">
+        <v>36</v>
+      </c>
+      <c r="DC136" t="n">
+        <v>79</v>
+      </c>
+      <c r="DD136" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DE136" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DF136" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DG136" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DH136" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="DI136" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DJ136" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK136" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL136" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="DM136" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DN136" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="DO136" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP136" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ136" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR136" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS136" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT136" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU136" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV136" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW136" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="DX136" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="DY136" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="DZ136" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="EA136" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EB136" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="EC136" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="ED136" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EE136" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EF136" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="EG136" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="EH136" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="EI136" t="inlineStr">
+        <is>
+          <t>12.57</t>
+        </is>
+      </c>
+      <c r="EJ136" t="inlineStr">
+        <is>
+          <t>5.58</t>
+        </is>
+      </c>
+      <c r="EK136" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EL136" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="EM136" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EN136" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EO136" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EP136" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
+++ b/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP136" headerRowCount="1">
-  <autoFilter ref="A1:EP136"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP137" headerRowCount="1">
+  <autoFilter ref="A1:EP137"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP136"/>
+  <dimension ref="A1:EP137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.8" customWidth="1" min="1" max="1"/>
@@ -2715,7 +2715,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3149,7 +3149,7 @@
         <v>2.22</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3179,7 +3179,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -7310,7 +7310,7 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="DE14" t="n">
         <v>1.63</v>
@@ -7343,7 +7343,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8245,7 +8245,7 @@
         <v>0.89</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="DF16" t="n">
         <v>1</v>
@@ -8275,7 +8275,7 @@
         <v>1.72</v>
       </c>
       <c r="DO16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -9323,70 +9323,70 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
         <v>45871.72916666666</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>5</v>
+      </c>
+      <c r="M19" t="n">
+        <v>4</v>
+      </c>
+      <c r="N19" t="n">
         <v>3</v>
       </c>
-      <c r="I19" t="n">
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>5</v>
       </c>
-      <c r="J19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K19" t="n">
-        <v>7</v>
-      </c>
-      <c r="L19" t="n">
-        <v>11</v>
-      </c>
-      <c r="M19" t="n">
-        <v>5</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>10</v>
-      </c>
       <c r="R19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
+        <v>13</v>
+      </c>
+      <c r="T19" t="n">
         <v>3</v>
       </c>
-      <c r="T19" t="n">
-        <v>8</v>
-      </c>
       <c r="U19" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="V19" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="W19" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="X19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y19" t="n">
         <v>56</v>
@@ -9396,91 +9396,91 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Akhmat Arena</t>
+          <t>Stadion FK Krasnodar</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
+          <t>ul. Vostochno-Kruglikovskaya 126, Krasnodar</t>
         </is>
       </c>
       <c r="AC19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE19" t="n">
-        <v>5.84</v>
+        <v>1.81</v>
       </c>
       <c r="AF19" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.65</v>
+        <v>3.54</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AU19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="BC19" t="n">
         <v>0</v>
@@ -9519,46 +9519,46 @@
         <v>-1</v>
       </c>
       <c r="BO19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ19" t="n">
         <v>3</v>
       </c>
       <c r="BR19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BS19" t="n">
         <v>3</v>
       </c>
       <c r="BT19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BU19" t="n">
         <v>1</v>
       </c>
       <c r="BV19" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="BW19" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="BX19" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="BY19" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.54</v>
+        <v>0.45</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.43</v>
+        <v>2.43</v>
       </c>
       <c r="CC19" t="n">
         <v>0</v>
@@ -9600,64 +9600,64 @@
         <v>0</v>
       </c>
       <c r="CP19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ19" t="n">
         <v>1</v>
       </c>
       <c r="CR19" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="CS19" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="CT19" t="n">
         <v>1</v>
       </c>
       <c r="CU19" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="CV19" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="CW19" t="n">
         <v>1</v>
       </c>
       <c r="CX19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CY19" t="n">
         <v>7</v>
       </c>
       <c r="CZ19" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DA19" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DB19" t="n">
         <v>0</v>
       </c>
       <c r="DC19" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DD19" t="n">
-        <v>0.89</v>
+        <v>2.33</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.78</v>
+        <v>1</v>
       </c>
       <c r="DF19" t="n">
         <v>0</v>
       </c>
       <c r="DG19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DH19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="DI19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DJ19" t="n">
         <v>0</v>
@@ -9666,13 +9666,13 @@
         <v>0</v>
       </c>
       <c r="DL19" t="n">
-        <v>1.17</v>
+        <v>1.82</v>
       </c>
       <c r="DM19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="DN19" t="n">
-        <v>2.42</v>
+        <v>1.82</v>
       </c>
       <c r="DO19" t="n">
         <v>17</v>
@@ -9681,63 +9681,83 @@
         <v>1</v>
       </c>
       <c r="DQ19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU19" t="b">
         <v>0</v>
       </c>
       <c r="DV19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW19" t="n">
-        <v>37.47</v>
+        <v>31.6</v>
       </c>
       <c r="DX19" t="n">
-        <v>6.85</v>
+        <v>4.87</v>
       </c>
       <c r="DY19" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="DZ19" t="inlineStr">
         <is>
-          <t>60%</t>
-        </is>
-      </c>
-      <c r="EA19" t="inlineStr"/>
-      <c r="EB19" t="inlineStr"/>
-      <c r="EC19" t="inlineStr"/>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="EA19" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EB19" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="EC19" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
       <c r="ED19" t="inlineStr"/>
       <c r="EE19" t="inlineStr"/>
       <c r="EF19" t="inlineStr"/>
       <c r="EG19" t="inlineStr"/>
       <c r="EH19" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="EI19" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="EJ19" t="inlineStr">
         <is>
-          <t>4.32</t>
-        </is>
-      </c>
-      <c r="EK19" t="inlineStr"/>
-      <c r="EL19" t="inlineStr"/>
+          <t>3.69</t>
+        </is>
+      </c>
+      <c r="EK19" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EL19" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
       <c r="EM19" t="inlineStr"/>
       <c r="EN19" t="inlineStr"/>
       <c r="EO19" t="inlineStr"/>
@@ -9759,70 +9779,70 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
         <v>45871.72916666666</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" t="n">
+        <v>7</v>
+      </c>
+      <c r="L20" t="n">
+        <v>11</v>
+      </c>
+      <c r="M20" t="n">
         <v>5</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>5</v>
-      </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>4</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>10</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6</v>
+      </c>
+      <c r="S20" t="n">
         <v>3</v>
       </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>5</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
+        <v>8</v>
+      </c>
+      <c r="U20" t="n">
         <v>13</v>
       </c>
-      <c r="T20" t="n">
-        <v>3</v>
-      </c>
-      <c r="U20" t="n">
-        <v>18</v>
-      </c>
       <c r="V20" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="W20" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="X20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y20" t="n">
         <v>56</v>
@@ -9832,91 +9852,91 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Stadion FK Krasnodar</t>
+          <t>Akhmat Arena</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>ul. Vostochno-Kruglikovskaya 126, Krasnodar</t>
+          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
         </is>
       </c>
       <c r="AC20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD20" t="n">
         <v>4</v>
       </c>
-      <c r="AD20" t="n">
-        <v>3</v>
-      </c>
       <c r="AE20" t="n">
-        <v>1.81</v>
+        <v>5.84</v>
       </c>
       <c r="AF20" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.54</v>
+        <v>1.65</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AV20" t="n">
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB20" t="n">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="BC20" t="n">
         <v>0</v>
@@ -9955,46 +9975,46 @@
         <v>-1</v>
       </c>
       <c r="BO20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ20" t="n">
         <v>3</v>
       </c>
       <c r="BR20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BS20" t="n">
         <v>3</v>
       </c>
       <c r="BT20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BU20" t="n">
         <v>1</v>
       </c>
       <c r="BV20" t="n">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="BW20" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="BX20" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="BY20" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="CA20" t="n">
-        <v>0.45</v>
+        <v>1.54</v>
       </c>
       <c r="CB20" t="n">
-        <v>2.43</v>
+        <v>3.43</v>
       </c>
       <c r="CC20" t="n">
         <v>0</v>
@@ -10036,64 +10056,64 @@
         <v>0</v>
       </c>
       <c r="CP20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ20" t="n">
         <v>1</v>
       </c>
       <c r="CR20" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="CS20" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="CT20" t="n">
         <v>1</v>
       </c>
       <c r="CU20" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="CV20" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="CW20" t="n">
         <v>1</v>
       </c>
       <c r="CX20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="CY20" t="n">
         <v>7</v>
       </c>
       <c r="CZ20" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DA20" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DB20" t="n">
         <v>0</v>
       </c>
       <c r="DC20" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DD20" t="n">
-        <v>2.33</v>
+        <v>0.89</v>
       </c>
       <c r="DE20" t="n">
-        <v>1</v>
+        <v>1.78</v>
       </c>
       <c r="DF20" t="n">
         <v>0</v>
       </c>
       <c r="DG20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DH20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="DI20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DJ20" t="n">
         <v>0</v>
@@ -10102,13 +10122,13 @@
         <v>0</v>
       </c>
       <c r="DL20" t="n">
-        <v>1.82</v>
+        <v>1.17</v>
       </c>
       <c r="DM20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="DN20" t="n">
-        <v>1.82</v>
+        <v>2.42</v>
       </c>
       <c r="DO20" t="n">
         <v>17</v>
@@ -10117,83 +10137,63 @@
         <v>1</v>
       </c>
       <c r="DQ20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU20" t="b">
         <v>0</v>
       </c>
       <c r="DV20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW20" t="n">
-        <v>31.6</v>
+        <v>37.47</v>
       </c>
       <c r="DX20" t="n">
-        <v>4.87</v>
+        <v>6.85</v>
       </c>
       <c r="DY20" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="DZ20" t="inlineStr">
         <is>
-          <t>96%</t>
-        </is>
-      </c>
-      <c r="EA20" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="EB20" t="inlineStr">
-        <is>
-          <t>2.82</t>
-        </is>
-      </c>
-      <c r="EC20" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="EA20" t="inlineStr"/>
+      <c r="EB20" t="inlineStr"/>
+      <c r="EC20" t="inlineStr"/>
       <c r="ED20" t="inlineStr"/>
       <c r="EE20" t="inlineStr"/>
       <c r="EF20" t="inlineStr"/>
       <c r="EG20" t="inlineStr"/>
       <c r="EH20" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="EI20" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EJ20" t="inlineStr">
         <is>
-          <t>3.69</t>
-        </is>
-      </c>
-      <c r="EK20" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
-      <c r="EL20" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
+          <t>4.32</t>
+        </is>
+      </c>
+      <c r="EK20" t="inlineStr"/>
+      <c r="EL20" t="inlineStr"/>
       <c r="EM20" t="inlineStr"/>
       <c r="EN20" t="inlineStr"/>
       <c r="EO20" t="inlineStr"/>
@@ -11951,7 +11951,7 @@
         <v>1.08</v>
       </c>
       <c r="DO24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12395,7 +12395,7 @@
         <v>2.16</v>
       </c>
       <c r="DO25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12883,7 +12883,7 @@
         <v>1.97</v>
       </c>
       <c r="DO26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -15634,7 +15634,7 @@
         <v>50</v>
       </c>
       <c r="DD32" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="DE32" t="n">
         <v>1</v>
@@ -15667,7 +15667,7 @@
         <v>1.95</v>
       </c>
       <c r="DO32" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -19331,7 +19331,7 @@
         <v>2.87</v>
       </c>
       <c r="DO40" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -19757,7 +19757,7 @@
         <v>0.89</v>
       </c>
       <c r="DE41" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="DF41" t="n">
         <v>0</v>
@@ -19787,7 +19787,7 @@
         <v>2.54</v>
       </c>
       <c r="DO41" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -21157,7 +21157,7 @@
         <v>2.75</v>
       </c>
       <c r="DE44" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="DF44" t="n">
         <v>2</v>
@@ -21187,7 +21187,7 @@
         <v>3.11</v>
       </c>
       <c r="DO44" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -23462,7 +23462,7 @@
         <v>84</v>
       </c>
       <c r="DD49" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="DE49" t="n">
         <v>1.78</v>
@@ -23495,7 +23495,7 @@
         <v>2.7</v>
       </c>
       <c r="DO49" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24879,7 +24879,7 @@
         <v>2</v>
       </c>
       <c r="DO52" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -27167,7 +27167,7 @@
         <v>2.24</v>
       </c>
       <c r="DO57" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -27609,7 +27609,7 @@
         <v>1.89</v>
       </c>
       <c r="DE58" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="DF58" t="n">
         <v>1.75</v>
@@ -27639,7 +27639,7 @@
         <v>2.53</v>
       </c>
       <c r="DO58" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -29931,7 +29931,7 @@
         <v>1.8</v>
       </c>
       <c r="DO63" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -32247,7 +32247,7 @@
         <v>2.38</v>
       </c>
       <c r="DO68" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -34534,7 +34534,7 @@
         <v>88</v>
       </c>
       <c r="DD73" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="DE73" t="n">
         <v>1.38</v>
@@ -34567,7 +34567,7 @@
         <v>2.46</v>
       </c>
       <c r="DO73" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -37815,7 +37815,7 @@
         <v>1.87</v>
       </c>
       <c r="DO80" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP80" t="b">
         <v>0</v>
@@ -40994,7 +40994,7 @@
         <v>70</v>
       </c>
       <c r="DD87" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="DE87" t="n">
         <v>0.38</v>
@@ -41027,7 +41027,7 @@
         <v>1.93</v>
       </c>
       <c r="DO87" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -41941,7 +41941,7 @@
         <v>2</v>
       </c>
       <c r="DE89" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="DF89" t="n">
         <v>1.5</v>
@@ -41971,7 +41971,7 @@
         <v>2.67</v>
       </c>
       <c r="DO89" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -43827,7 +43827,7 @@
         <v>2.49</v>
       </c>
       <c r="DO93" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -44746,7 +44746,7 @@
         <v>84</v>
       </c>
       <c r="DD95" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="DE95" t="n">
         <v>1.56</v>
@@ -44779,7 +44779,7 @@
         <v>2.32</v>
       </c>
       <c r="DO95" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -46589,7 +46589,7 @@
         <v>1.13</v>
       </c>
       <c r="DE99" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="DF99" t="n">
         <v>1.6</v>
@@ -46619,7 +46619,7 @@
         <v>2.84</v>
       </c>
       <c r="DO99" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -49355,7 +49355,7 @@
         <v>2.37</v>
       </c>
       <c r="DO105" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -49911,170 +49911,170 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F107" s="2" t="n">
         <v>45962.61458333334</v>
       </c>
       <c r="G107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K107" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L107" t="n">
+        <v>8</v>
+      </c>
+      <c r="M107" t="n">
+        <v>3</v>
+      </c>
+      <c r="N107" t="n">
+        <v>3</v>
+      </c>
+      <c r="O107" t="n">
+        <v>1</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>2</v>
+      </c>
+      <c r="R107" t="n">
+        <v>3</v>
+      </c>
+      <c r="S107" t="n">
+        <v>5</v>
+      </c>
+      <c r="T107" t="n">
         <v>11</v>
       </c>
-      <c r="M107" t="n">
-        <v>2</v>
-      </c>
-      <c r="N107" t="n">
-        <v>2</v>
-      </c>
-      <c r="O107" t="n">
-        <v>0</v>
-      </c>
-      <c r="P107" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>6</v>
-      </c>
-      <c r="R107" t="n">
-        <v>1</v>
-      </c>
-      <c r="S107" t="n">
+      <c r="U107" t="n">
         <v>7</v>
       </c>
-      <c r="T107" t="n">
-        <v>5</v>
-      </c>
-      <c r="U107" t="n">
-        <v>13</v>
-      </c>
       <c r="V107" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="W107" t="n">
         <v>16</v>
       </c>
       <c r="X107" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Y107" t="n">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="Z107" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>Anzhi-Arena</t>
+          <t>Kazan' Arena</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>, Kaspiysk</t>
+          <t>Prospekt Husaina Yamasheva 115a, Kazan'</t>
         </is>
       </c>
       <c r="AC107" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE107" t="n">
-        <v>2.03</v>
+        <v>3.1</v>
       </c>
       <c r="AF107" t="n">
         <v>3.2</v>
       </c>
       <c r="AG107" t="n">
-        <v>3.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH107" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AI107" t="n">
-        <v>2.48</v>
+        <v>1.91</v>
       </c>
       <c r="AJ107" t="n">
-        <v>4.65</v>
+        <v>2.9</v>
       </c>
       <c r="AK107" t="n">
-        <v>2.14</v>
+        <v>1.66</v>
       </c>
       <c r="AL107" t="n">
-        <v>1.64</v>
+        <v>2.29</v>
       </c>
       <c r="AM107" t="n">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="AN107" t="n">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="AO107" t="n">
-        <v>2.06</v>
+        <v>2.36</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="AR107" t="n">
-        <v>3.54</v>
+        <v>2.68</v>
       </c>
       <c r="AS107" t="n">
-        <v>2.4</v>
+        <v>2.89</v>
       </c>
       <c r="AT107" t="n">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AU107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW107" t="n">
         <v>0</v>
       </c>
       <c r="AX107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY107" t="n">
         <v>0</v>
       </c>
       <c r="AZ107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB107" t="n">
-        <v>668267</v>
+        <v>-1</v>
       </c>
       <c r="BC107" t="n">
         <v>0</v>
       </c>
       <c r="BD107" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="BE107" t="n">
         <v>0</v>
@@ -50107,46 +50107,46 @@
         <v>-1</v>
       </c>
       <c r="BO107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BR107" t="n">
         <v>2</v>
       </c>
       <c r="BS107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT107" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BU107" t="n">
         <v>1</v>
       </c>
       <c r="BV107" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="BW107" t="n">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="BX107" t="n">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="BY107" t="n">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="BZ107" t="n">
-        <v>1.63</v>
+        <v>0.88</v>
       </c>
       <c r="CA107" t="n">
-        <v>0.65</v>
+        <v>1.58</v>
       </c>
       <c r="CB107" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="CC107" t="n">
         <v>0</v>
@@ -50173,7 +50173,7 @@
         <v>1</v>
       </c>
       <c r="CK107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL107" t="n">
         <v>0</v>
@@ -50194,82 +50194,82 @@
         <v>1</v>
       </c>
       <c r="CR107" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="CS107" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="CT107" t="n">
         <v>1</v>
       </c>
       <c r="CU107" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="CV107" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CW107" t="n">
         <v>1</v>
       </c>
       <c r="CX107" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="CY107" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="CZ107" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="DA107" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="DB107" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="DC107" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="DD107" t="n">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="DE107" t="n">
-        <v>0.5600000000000001</v>
+        <v>1</v>
       </c>
       <c r="DF107" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="DG107" t="n">
-        <v>0.71</v>
+        <v>1.17</v>
       </c>
       <c r="DH107" t="n">
-        <v>0.85</v>
+        <v>1.38</v>
       </c>
       <c r="DI107" t="n">
-        <v>1</v>
+        <v>1.23</v>
       </c>
       <c r="DJ107" t="n">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="DK107" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="DL107" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="DM107" t="n">
-        <v>0.97</v>
+        <v>1.4</v>
       </c>
       <c r="DN107" t="n">
-        <v>2.09</v>
+        <v>2.61</v>
       </c>
       <c r="DO107" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR107" t="b">
         <v>0</v>
@@ -50287,77 +50287,101 @@
         <v>0</v>
       </c>
       <c r="DW107" t="n">
-        <v>16.76</v>
+        <v>6.32</v>
       </c>
       <c r="DX107" t="n">
-        <v>8.27</v>
+        <v>3.69</v>
       </c>
       <c r="DY107" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="DZ107" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="EA107" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EB107" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="EC107" t="inlineStr">
         <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="ED107" t="inlineStr"/>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="ED107" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
       <c r="EE107" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EF107" t="inlineStr">
         <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="EG107" t="inlineStr"/>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="EG107" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
       <c r="EH107" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="EI107" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="EJ107" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="EK107" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="EL107" t="inlineStr">
         <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="EM107" t="inlineStr"/>
-      <c r="EN107" t="inlineStr"/>
-      <c r="EO107" t="inlineStr"/>
-      <c r="EP107" t="inlineStr"/>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EM107" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EN107" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EO107" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EP107" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -50375,170 +50399,170 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F108" s="2" t="n">
         <v>45962.61458333334</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J108" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K108" t="n">
+        <v>2</v>
+      </c>
+      <c r="L108" t="n">
+        <v>11</v>
+      </c>
+      <c r="M108" t="n">
+        <v>2</v>
+      </c>
+      <c r="N108" t="n">
+        <v>2</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>6</v>
+      </c>
+      <c r="R108" t="n">
+        <v>1</v>
+      </c>
+      <c r="S108" t="n">
+        <v>7</v>
+      </c>
+      <c r="T108" t="n">
         <v>5</v>
       </c>
-      <c r="L108" t="n">
-        <v>8</v>
-      </c>
-      <c r="M108" t="n">
-        <v>3</v>
-      </c>
-      <c r="N108" t="n">
-        <v>3</v>
-      </c>
-      <c r="O108" t="n">
-        <v>1</v>
-      </c>
-      <c r="P108" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q108" t="n">
-        <v>2</v>
-      </c>
-      <c r="R108" t="n">
-        <v>3</v>
-      </c>
-      <c r="S108" t="n">
-        <v>5</v>
-      </c>
-      <c r="T108" t="n">
-        <v>11</v>
-      </c>
       <c r="U108" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="V108" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="W108" t="n">
         <v>16</v>
       </c>
       <c r="X108" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="Y108" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="Z108" t="n">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>Kazan' Arena</t>
+          <t>Anzhi-Arena</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>Prospekt Husaina Yamasheva 115a, Kazan'</t>
+          <t>, Kaspiysk</t>
         </is>
       </c>
       <c r="AC108" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AD108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE108" t="n">
-        <v>3.1</v>
+        <v>2.03</v>
       </c>
       <c r="AF108" t="n">
         <v>3.2</v>
       </c>
       <c r="AG108" t="n">
-        <v>2.2</v>
+        <v>3.95</v>
       </c>
       <c r="AH108" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AI108" t="n">
-        <v>1.91</v>
+        <v>2.48</v>
       </c>
       <c r="AJ108" t="n">
-        <v>2.9</v>
+        <v>4.65</v>
       </c>
       <c r="AK108" t="n">
-        <v>1.66</v>
+        <v>2.14</v>
       </c>
       <c r="AL108" t="n">
-        <v>2.29</v>
+        <v>1.64</v>
       </c>
       <c r="AM108" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="AN108" t="n">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="AO108" t="n">
-        <v>2.36</v>
+        <v>2.06</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="AR108" t="n">
-        <v>2.68</v>
+        <v>3.54</v>
       </c>
       <c r="AS108" t="n">
-        <v>2.89</v>
+        <v>2.4</v>
       </c>
       <c r="AT108" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AU108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW108" t="n">
         <v>0</v>
       </c>
       <c r="AX108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY108" t="n">
         <v>0</v>
       </c>
       <c r="AZ108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB108" t="n">
-        <v>-1</v>
+        <v>668267</v>
       </c>
       <c r="BC108" t="n">
         <v>0</v>
       </c>
       <c r="BD108" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="BE108" t="n">
         <v>0</v>
@@ -50571,169 +50595,169 @@
         <v>-1</v>
       </c>
       <c r="BO108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BR108" t="n">
         <v>2</v>
       </c>
       <c r="BS108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT108" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV108" t="n">
+        <v>53</v>
+      </c>
+      <c r="BW108" t="n">
+        <v>26</v>
+      </c>
+      <c r="BX108" t="n">
+        <v>126</v>
+      </c>
+      <c r="BY108" t="n">
+        <v>75</v>
+      </c>
+      <c r="BZ108" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="CA108" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="CB108" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="CC108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM108" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN108" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR108" t="n">
+        <v>29</v>
+      </c>
+      <c r="CS108" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU108" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV108" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX108" t="n">
         <v>5</v>
       </c>
-      <c r="BU108" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV108" t="n">
-        <v>39</v>
-      </c>
-      <c r="BW108" t="n">
-        <v>66</v>
-      </c>
-      <c r="BX108" t="n">
-        <v>101</v>
-      </c>
-      <c r="BY108" t="n">
-        <v>121</v>
-      </c>
-      <c r="BZ108" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="CA108" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CB108" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="CC108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM108" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CN108" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CO108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR108" t="n">
-        <v>18</v>
-      </c>
-      <c r="CS108" t="n">
-        <v>15</v>
-      </c>
-      <c r="CT108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU108" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV108" t="n">
-        <v>17</v>
-      </c>
-      <c r="CW108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX108" t="n">
-        <v>10</v>
-      </c>
       <c r="CY108" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="CZ108" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="DA108" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="DB108" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="DC108" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="DD108" t="n">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="DE108" t="n">
-        <v>1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DF108" t="n">
-        <v>1.86</v>
+        <v>1.5</v>
       </c>
       <c r="DG108" t="n">
-        <v>1.17</v>
+        <v>0.71</v>
       </c>
       <c r="DH108" t="n">
-        <v>1.38</v>
+        <v>0.85</v>
       </c>
       <c r="DI108" t="n">
-        <v>1.23</v>
+        <v>1</v>
       </c>
       <c r="DJ108" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="DK108" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="DL108" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="DM108" t="n">
-        <v>1.4</v>
+        <v>0.97</v>
       </c>
       <c r="DN108" t="n">
-        <v>2.61</v>
+        <v>2.09</v>
       </c>
       <c r="DO108" t="n">
         <v>17</v>
       </c>
       <c r="DP108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR108" t="b">
         <v>0</v>
@@ -50751,101 +50775,77 @@
         <v>0</v>
       </c>
       <c r="DW108" t="n">
-        <v>6.32</v>
+        <v>16.76</v>
       </c>
       <c r="DX108" t="n">
-        <v>3.69</v>
+        <v>8.27</v>
       </c>
       <c r="DY108" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="DZ108" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="EA108" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EB108" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="EC108" t="inlineStr">
         <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="ED108" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="ED108" t="inlineStr"/>
       <c r="EE108" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EF108" t="inlineStr">
         <is>
-          <t>3.19</t>
-        </is>
-      </c>
-      <c r="EG108" t="inlineStr">
-        <is>
-          <t>2.76</t>
-        </is>
-      </c>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EG108" t="inlineStr"/>
       <c r="EH108" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EI108" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="EJ108" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="EK108" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EL108" t="inlineStr">
         <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="EM108" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
-      </c>
-      <c r="EN108" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EO108" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="EP108" t="inlineStr">
-        <is>
-          <t>2.44</t>
-        </is>
-      </c>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EM108" t="inlineStr"/>
+      <c r="EN108" t="inlineStr"/>
+      <c r="EO108" t="inlineStr"/>
+      <c r="EP108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -52135,7 +52135,7 @@
         <v>2.03</v>
       </c>
       <c r="DO111" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -54427,7 +54427,7 @@
         <v>2.75</v>
       </c>
       <c r="DO116" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP116" t="b">
         <v>1</v>
@@ -54846,7 +54846,7 @@
         <v>72</v>
       </c>
       <c r="DD117" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="DE117" t="n">
         <v>1</v>
@@ -54879,7 +54879,7 @@
         <v>2.24</v>
       </c>
       <c r="DO117" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -57195,7 +57195,7 @@
         <v>2.2</v>
       </c>
       <c r="DO122" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -59917,7 +59917,7 @@
         <v>1.33</v>
       </c>
       <c r="DE128" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="DF128" t="n">
         <v>1.13</v>
@@ -59947,7 +59947,7 @@
         <v>3.17</v>
       </c>
       <c r="DO128" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP128" t="b">
         <v>1</v>
@@ -60579,7 +60579,7 @@
         <v>16</v>
       </c>
       <c r="W130" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X130" t="n">
         <v>13</v>
@@ -61921,19 +61921,19 @@
         <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R133" t="n">
         <v>1</v>
       </c>
       <c r="S133" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T133" t="n">
         <v>4</v>
       </c>
       <c r="U133" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="V133" t="n">
         <v>5</v>
@@ -62108,13 +62108,13 @@
         <v>52</v>
       </c>
       <c r="BZ133" t="n">
-        <v>2.65</v>
+        <v>2.84</v>
       </c>
       <c r="CA133" t="n">
         <v>0.53</v>
       </c>
       <c r="CB133" t="n">
-        <v>3.17</v>
+        <v>3.37</v>
       </c>
       <c r="CC133" t="n">
         <v>1</v>
@@ -62351,170 +62351,170 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F134" s="2" t="n">
         <v>45991.5625</v>
       </c>
       <c r="G134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I134" t="n">
+        <v>4</v>
+      </c>
+      <c r="J134" t="n">
+        <v>2</v>
+      </c>
+      <c r="K134" t="n">
+        <v>4</v>
+      </c>
+      <c r="L134" t="n">
+        <v>6</v>
+      </c>
+      <c r="M134" t="n">
+        <v>2</v>
+      </c>
+      <c r="N134" t="n">
+        <v>1</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
         <v>3</v>
       </c>
-      <c r="J134" t="n">
-        <v>7</v>
-      </c>
-      <c r="K134" t="n">
+      <c r="R134" t="n">
+        <v>6</v>
+      </c>
+      <c r="S134" t="n">
         <v>8</v>
       </c>
-      <c r="L134" t="n">
-        <v>15</v>
-      </c>
-      <c r="M134" t="n">
-        <v>3</v>
-      </c>
-      <c r="N134" t="n">
-        <v>2</v>
-      </c>
-      <c r="O134" t="n">
-        <v>0</v>
-      </c>
-      <c r="P134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q134" t="n">
-        <v>6</v>
-      </c>
-      <c r="R134" t="n">
-        <v>4</v>
-      </c>
-      <c r="S134" t="n">
-        <v>12</v>
-      </c>
       <c r="T134" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="U134" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="V134" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="W134" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X134" t="n">
         <v>13</v>
       </c>
       <c r="Y134" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="Z134" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>Akhmat Arena</t>
+          <t>Stadion Central’nyj im. I.P. Chayka</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
+          <t>ul. Suvorova, Peschanokopskoye</t>
         </is>
       </c>
       <c r="AC134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA134" t="n">
         <v>3</v>
       </c>
-      <c r="AD134" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE134" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AF134" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AG134" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AH134" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI134" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ134" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AK134" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AL134" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AM134" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AN134" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AO134" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AP134" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AQ134" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AR134" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AS134" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AT134" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AU134" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW134" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX134" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ134" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA134" t="n">
-        <v>1</v>
-      </c>
       <c r="BB134" t="n">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="BC134" t="n">
         <v>0</v>
       </c>
       <c r="BD134" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="BE134" t="n">
         <v>0</v>
@@ -62547,10 +62547,10 @@
         <v>-1</v>
       </c>
       <c r="BO134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ134" t="n">
         <v>2</v>
@@ -62559,7 +62559,7 @@
         <v>1</v>
       </c>
       <c r="BS134" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT134" t="n">
         <v>3</v>
@@ -62568,37 +62568,37 @@
         <v>1</v>
       </c>
       <c r="BV134" t="n">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="BW134" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="BX134" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="BY134" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="BZ134" t="n">
-        <v>1.84</v>
+        <v>1.45</v>
       </c>
       <c r="CA134" t="n">
-        <v>1.98</v>
+        <v>1.71</v>
       </c>
       <c r="CB134" t="n">
-        <v>3.82</v>
+        <v>3.16</v>
       </c>
       <c r="CC134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG134" t="n">
         <v>0</v>
@@ -62616,7 +62616,7 @@
         <v>0</v>
       </c>
       <c r="CL134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM134" t="n">
         <v>-1</v>
@@ -62625,7 +62625,7 @@
         <v>-1</v>
       </c>
       <c r="CO134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP134" t="n">
         <v>0</v>
@@ -62634,73 +62634,73 @@
         <v>1</v>
       </c>
       <c r="CR134" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="CS134" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="CT134" t="n">
         <v>1</v>
       </c>
       <c r="CU134" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CV134" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="CW134" t="n">
         <v>1</v>
       </c>
       <c r="CX134" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CY134" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CZ134" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="DA134" t="n">
         <v>72</v>
       </c>
       <c r="DB134" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="DC134" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="DD134" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DE134" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DF134" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DG134" t="n">
         <v>1.63</v>
       </c>
-      <c r="DE134" t="n">
-        <v>1</v>
-      </c>
-      <c r="DF134" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="DG134" t="n">
-        <v>1.14</v>
-      </c>
       <c r="DH134" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="DI134" t="n">
-        <v>1.25</v>
+        <v>1.94</v>
       </c>
       <c r="DJ134" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="DK134" t="n">
         <v>29</v>
       </c>
       <c r="DL134" t="n">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="DM134" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="DN134" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="DO134" t="n">
         <v>17</v>
@@ -62715,7 +62715,7 @@
         <v>1</v>
       </c>
       <c r="DS134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT134" t="b">
         <v>0</v>
@@ -62727,14 +62727,14 @@
         <v>1</v>
       </c>
       <c r="DW134" t="n">
-        <v>10.53</v>
+        <v>3.61</v>
       </c>
       <c r="DX134" t="n">
-        <v>1.66</v>
+        <v>3.88</v>
       </c>
       <c r="DY134" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="DZ134" t="inlineStr">
@@ -62744,17 +62744,17 @@
       </c>
       <c r="EA134" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="EB134" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="EC134" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="ED134" t="inlineStr"/>
@@ -62763,47 +62763,47 @@
       <c r="EG134" t="inlineStr"/>
       <c r="EH134" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="EI134" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="EJ134" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="EK134" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EL134" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EM134" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="EN134" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EO134" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EP134" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -62823,170 +62823,170 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F135" s="2" t="n">
         <v>45991.5625</v>
       </c>
       <c r="G135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H135" t="n">
+        <v>1</v>
+      </c>
+      <c r="I135" t="n">
         <v>3</v>
       </c>
-      <c r="I135" t="n">
+      <c r="J135" t="n">
+        <v>7</v>
+      </c>
+      <c r="K135" t="n">
+        <v>8</v>
+      </c>
+      <c r="L135" t="n">
+        <v>15</v>
+      </c>
+      <c r="M135" t="n">
+        <v>3</v>
+      </c>
+      <c r="N135" t="n">
+        <v>2</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>6</v>
+      </c>
+      <c r="R135" t="n">
         <v>4</v>
       </c>
-      <c r="J135" t="n">
-        <v>2</v>
-      </c>
-      <c r="K135" t="n">
-        <v>4</v>
-      </c>
-      <c r="L135" t="n">
-        <v>6</v>
-      </c>
-      <c r="M135" t="n">
-        <v>2</v>
-      </c>
-      <c r="N135" t="n">
-        <v>1</v>
-      </c>
-      <c r="O135" t="n">
-        <v>0</v>
-      </c>
-      <c r="P135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q135" t="n">
-        <v>3</v>
-      </c>
-      <c r="R135" t="n">
-        <v>6</v>
-      </c>
       <c r="S135" t="n">
+        <v>12</v>
+      </c>
+      <c r="T135" t="n">
+        <v>18</v>
+      </c>
+      <c r="U135" t="n">
+        <v>18</v>
+      </c>
+      <c r="V135" t="n">
+        <v>22</v>
+      </c>
+      <c r="W135" t="n">
         <v>8</v>
-      </c>
-      <c r="T135" t="n">
-        <v>9</v>
-      </c>
-      <c r="U135" t="n">
-        <v>11</v>
-      </c>
-      <c r="V135" t="n">
-        <v>15</v>
-      </c>
-      <c r="W135" t="n">
-        <v>16</v>
       </c>
       <c r="X135" t="n">
         <v>13</v>
       </c>
       <c r="Y135" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="Z135" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>Stadion Central’nyj im. I.P. Chayka</t>
+          <t>Akhmat Arena</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>ul. Suvorova, Peschanokopskoye</t>
+          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
         </is>
       </c>
       <c r="AC135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE135" t="n">
-        <v>2.49</v>
+        <v>2.89</v>
       </c>
       <c r="AF135" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="AG135" t="n">
-        <v>2.84</v>
+        <v>2.36</v>
       </c>
       <c r="AH135" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AI135" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AJ135" t="n">
-        <v>3.74</v>
+        <v>3.1</v>
       </c>
       <c r="AK135" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AL135" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="AM135" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AN135" t="n">
-        <v>2.19</v>
+        <v>1.8</v>
       </c>
       <c r="AO135" t="n">
-        <v>2.19</v>
+        <v>2.48</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AR135" t="n">
-        <v>3.09</v>
+        <v>2.62</v>
       </c>
       <c r="AS135" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="AT135" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AU135" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX135" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA135" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BB135" t="n">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="BC135" t="n">
         <v>0</v>
       </c>
       <c r="BD135" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="BE135" t="n">
         <v>0</v>
@@ -63019,10 +63019,10 @@
         <v>-1</v>
       </c>
       <c r="BO135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ135" t="n">
         <v>2</v>
@@ -63031,7 +63031,7 @@
         <v>1</v>
       </c>
       <c r="BS135" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT135" t="n">
         <v>3</v>
@@ -63040,37 +63040,37 @@
         <v>1</v>
       </c>
       <c r="BV135" t="n">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="BW135" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="BX135" t="n">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="BY135" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="BZ135" t="n">
-        <v>1.45</v>
+        <v>1.84</v>
       </c>
       <c r="CA135" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="CB135" t="n">
-        <v>3.09</v>
+        <v>3.82</v>
       </c>
       <c r="CC135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG135" t="n">
         <v>0</v>
@@ -63088,7 +63088,7 @@
         <v>0</v>
       </c>
       <c r="CL135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM135" t="n">
         <v>-1</v>
@@ -63097,7 +63097,7 @@
         <v>-1</v>
       </c>
       <c r="CO135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP135" t="n">
         <v>0</v>
@@ -63106,73 +63106,73 @@
         <v>1</v>
       </c>
       <c r="CR135" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="CS135" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="CT135" t="n">
         <v>1</v>
       </c>
       <c r="CU135" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CV135" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="CW135" t="n">
         <v>1</v>
       </c>
       <c r="CX135" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CY135" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CZ135" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="DA135" t="n">
         <v>72</v>
       </c>
       <c r="DB135" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="DC135" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="DD135" t="n">
-        <v>1.13</v>
+        <v>1.63</v>
       </c>
       <c r="DE135" t="n">
-        <v>1.78</v>
+        <v>1</v>
       </c>
       <c r="DF135" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="DG135" t="n">
-        <v>1.63</v>
+        <v>1.14</v>
       </c>
       <c r="DH135" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DI135" t="n">
-        <v>1.94</v>
+        <v>1.25</v>
       </c>
       <c r="DJ135" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DK135" t="n">
         <v>29</v>
       </c>
       <c r="DL135" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="DM135" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="DN135" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="DO135" t="n">
         <v>17</v>
@@ -63187,7 +63187,7 @@
         <v>1</v>
       </c>
       <c r="DS135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT135" t="b">
         <v>0</v>
@@ -63199,14 +63199,14 @@
         <v>1</v>
       </c>
       <c r="DW135" t="n">
-        <v>3.61</v>
+        <v>10.53</v>
       </c>
       <c r="DX135" t="n">
-        <v>3.88</v>
+        <v>1.66</v>
       </c>
       <c r="DY135" t="inlineStr">
         <is>
-          <t>96%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="DZ135" t="inlineStr">
@@ -63216,17 +63216,17 @@
       </c>
       <c r="EA135" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="EB135" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="EC135" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="ED135" t="inlineStr"/>
@@ -63235,47 +63235,47 @@
       <c r="EG135" t="inlineStr"/>
       <c r="EH135" t="inlineStr">
         <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="EI135" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EJ135" t="inlineStr">
+        <is>
+          <t>3.53</t>
+        </is>
+      </c>
+      <c r="EK135" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EL135" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EM135" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EN135" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EO135" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EP135" t="inlineStr">
+        <is>
           <t>2.54</t>
-        </is>
-      </c>
-      <c r="EI135" t="inlineStr">
-        <is>
-          <t>2.86</t>
-        </is>
-      </c>
-      <c r="EJ135" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="EK135" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="EL135" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="EM135" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="EN135" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="EO135" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EP135" t="inlineStr">
-        <is>
-          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -63758,6 +63758,470 @@
           <t>2.41</t>
         </is>
       </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>17</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>FK Sochi</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Makhachkala</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>45992.6875</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="n">
+        <v>6</v>
+      </c>
+      <c r="K137" t="n">
+        <v>6</v>
+      </c>
+      <c r="L137" t="n">
+        <v>12</v>
+      </c>
+      <c r="M137" t="n">
+        <v>1</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>3</v>
+      </c>
+      <c r="R137" t="n">
+        <v>1</v>
+      </c>
+      <c r="S137" t="n">
+        <v>8</v>
+      </c>
+      <c r="T137" t="n">
+        <v>11</v>
+      </c>
+      <c r="U137" t="n">
+        <v>11</v>
+      </c>
+      <c r="V137" t="n">
+        <v>12</v>
+      </c>
+      <c r="W137" t="n">
+        <v>9</v>
+      </c>
+      <c r="X137" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>54</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>Olimpiyskiy Stadion Fisht</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>Olimpiyskiy prospekt, Sochi</t>
+        </is>
+      </c>
+      <c r="AC137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>37</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>42</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>89</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>113</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU137" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV137" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX137" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY137" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ137" t="n">
+        <v>41</v>
+      </c>
+      <c r="DA137" t="n">
+        <v>81</v>
+      </c>
+      <c r="DB137" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC137" t="n">
+        <v>94</v>
+      </c>
+      <c r="DD137" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DE137" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DF137" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DG137" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DH137" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DI137" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DJ137" t="n">
+        <v>59</v>
+      </c>
+      <c r="DK137" t="n">
+        <v>20</v>
+      </c>
+      <c r="DL137" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="DM137" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DN137" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DO137" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP137" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ137" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR137" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS137" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT137" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU137" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV137" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW137" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="DX137" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="DY137" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="DZ137" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="EA137" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="EB137" t="inlineStr">
+        <is>
+          <t>6.41</t>
+        </is>
+      </c>
+      <c r="EC137" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="ED137" t="inlineStr"/>
+      <c r="EE137" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EF137" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EG137" t="inlineStr"/>
+      <c r="EH137" t="inlineStr">
+        <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="EI137" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EJ137" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="EK137" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EL137" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EM137" t="inlineStr"/>
+      <c r="EN137" t="inlineStr"/>
+      <c r="EO137" t="inlineStr"/>
+      <c r="EP137" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
+++ b/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP137" headerRowCount="1">
-  <autoFilter ref="A1:EP137"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP138" headerRowCount="1">
+  <autoFilter ref="A1:EP138"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP137"/>
+  <dimension ref="A1:EP138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.8" customWidth="1" min="1" max="1"/>
@@ -4550,7 +4550,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DE8" t="n">
         <v>0.75</v>
@@ -10989,7 +10989,7 @@
         <v>2</v>
       </c>
       <c r="DE22" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF22" t="n">
         <v>0</v>
@@ -14718,7 +14718,7 @@
         <v>100</v>
       </c>
       <c r="DD30" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DE30" t="n">
         <v>1.56</v>
@@ -17470,7 +17470,7 @@
         <v>100</v>
       </c>
       <c r="DD36" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DE36" t="n">
         <v>0.5600000000000001</v>
@@ -17937,7 +17937,7 @@
         <v>0.89</v>
       </c>
       <c r="DE37" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF37" t="n">
         <v>1</v>
@@ -20251,7 +20251,7 @@
         <v>2.35</v>
       </c>
       <c r="DO42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -28081,7 +28081,7 @@
         <v>0.89</v>
       </c>
       <c r="DE59" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF59" t="n">
         <v>1</v>
@@ -28534,7 +28534,7 @@
         <v>100</v>
       </c>
       <c r="DD60" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DE60" t="n">
         <v>1.78</v>
@@ -35474,7 +35474,7 @@
         <v>88</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DE75" t="n">
         <v>1.63</v>
@@ -36865,7 +36865,7 @@
         <v>2.75</v>
       </c>
       <c r="DE78" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF78" t="n">
         <v>2.5</v>
@@ -42091,170 +42091,162 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
         <v>45948.41666666666</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" t="n">
         <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J90" t="n">
+        <v>5</v>
+      </c>
+      <c r="K90" t="n">
         <v>6</v>
       </c>
-      <c r="K90" t="n">
+      <c r="L90" t="n">
+        <v>11</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1</v>
+      </c>
+      <c r="N90" t="n">
+        <v>2</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
         <v>3</v>
       </c>
-      <c r="L90" t="n">
-        <v>9</v>
-      </c>
-      <c r="M90" t="n">
-        <v>2</v>
-      </c>
-      <c r="N90" t="n">
-        <v>2</v>
-      </c>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>11</v>
-      </c>
       <c r="R90" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S90" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T90" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="U90" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="V90" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W90" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X90" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Y90" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Z90" t="n">
-        <v>35</v>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>Stadion Nizhny Novgorod</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>ul. Dolzhanskaya, Nizhniy Novgorod</t>
-        </is>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="AA90" t="inlineStr"/>
+      <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD90" t="n">
         <v>2</v>
       </c>
       <c r="AE90" t="n">
-        <v>2.29</v>
+        <v>1.9</v>
       </c>
       <c r="AF90" t="n">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
       <c r="AG90" t="n">
-        <v>2.57</v>
+        <v>3.28</v>
       </c>
       <c r="AH90" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AI90" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AJ90" t="n">
-        <v>2.66</v>
+        <v>3.08</v>
       </c>
       <c r="AK90" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="AL90" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="AM90" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AN90" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AO90" t="n">
-        <v>2.16</v>
+        <v>2.62</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AR90" t="n">
-        <v>2.51</v>
+        <v>2.74</v>
       </c>
       <c r="AS90" t="n">
-        <v>3.32</v>
+        <v>3.04</v>
       </c>
       <c r="AT90" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AU90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV90" t="n">
         <v>0</v>
       </c>
       <c r="AW90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ90" t="n">
         <v>1</v>
       </c>
       <c r="BA90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB90" t="n">
-        <v>668270</v>
+        <v>-1</v>
       </c>
       <c r="BC90" t="n">
         <v>0</v>
       </c>
       <c r="BD90" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BE90" t="n">
         <v>0</v>
@@ -42287,7 +42279,7 @@
         <v>-1</v>
       </c>
       <c r="BO90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP90" t="n">
         <v>0</v>
@@ -42299,7 +42291,7 @@
         <v>2</v>
       </c>
       <c r="BS90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT90" t="n">
         <v>3</v>
@@ -42308,25 +42300,25 @@
         <v>1</v>
       </c>
       <c r="BV90" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="BW90" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="BX90" t="n">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="BY90" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="BZ90" t="n">
-        <v>2.76</v>
+        <v>1.44</v>
       </c>
       <c r="CA90" t="n">
-        <v>1.09</v>
+        <v>1.34</v>
       </c>
       <c r="CB90" t="n">
-        <v>3.85</v>
+        <v>2.78</v>
       </c>
       <c r="CC90" t="n">
         <v>0</v>
@@ -42374,73 +42366,73 @@
         <v>1</v>
       </c>
       <c r="CR90" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CS90" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CT90" t="n">
         <v>1</v>
       </c>
       <c r="CU90" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="CV90" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CW90" t="n">
         <v>1</v>
       </c>
       <c r="CX90" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="CY90" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="CZ90" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="DA90" t="n">
         <v>100</v>
       </c>
       <c r="DB90" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="DC90" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="DD90" t="n">
-        <v>0.89</v>
+        <v>1.5</v>
       </c>
       <c r="DE90" t="n">
-        <v>1.63</v>
+        <v>0.44</v>
       </c>
       <c r="DF90" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="DG90" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="DH90" t="n">
-        <v>0.55</v>
+        <v>1.09</v>
       </c>
       <c r="DI90" t="n">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="DJ90" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="DK90" t="n">
         <v>0</v>
       </c>
       <c r="DL90" t="n">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="DM90" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="DN90" t="n">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="DO90" t="n">
         <v>17</v>
@@ -42449,7 +42441,7 @@
         <v>1</v>
       </c>
       <c r="DQ90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR90" t="b">
         <v>0</v>
@@ -42464,82 +42456,70 @@
         <v>0</v>
       </c>
       <c r="DV90" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW90" t="n">
-        <v>8</v>
-      </c>
-      <c r="DX90" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="DY90" t="inlineStr">
-        <is>
-          <t>80%</t>
-        </is>
-      </c>
-      <c r="DZ90" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="DW90" t="inlineStr"/>
+      <c r="DX90" t="inlineStr"/>
+      <c r="DY90" t="inlineStr"/>
+      <c r="DZ90" t="inlineStr"/>
       <c r="EA90" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EB90" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="EC90" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="ED90" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EE90" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EF90" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="EG90" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="EH90" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="EI90" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EJ90" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="EK90" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="EL90" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EM90" t="inlineStr"/>
@@ -42563,162 +42543,170 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F91" s="2" t="n">
         <v>45948.41666666666</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
         <v>1</v>
       </c>
       <c r="I91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K91" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L91" t="n">
+        <v>9</v>
+      </c>
+      <c r="M91" t="n">
+        <v>2</v>
+      </c>
+      <c r="N91" t="n">
+        <v>2</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
         <v>11</v>
       </c>
-      <c r="M91" t="n">
-        <v>1</v>
-      </c>
-      <c r="N91" t="n">
-        <v>2</v>
-      </c>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>3</v>
-      </c>
       <c r="R91" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T91" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="U91" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="V91" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W91" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="X91" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Y91" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="Z91" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA91" t="inlineStr"/>
-      <c r="AB91" t="inlineStr"/>
+        <v>35</v>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>Stadion Nizhny Novgorod</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>ul. Dolzhanskaya, Nizhniy Novgorod</t>
+        </is>
+      </c>
       <c r="AC91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD91" t="n">
         <v>2</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.9</v>
+        <v>2.29</v>
       </c>
       <c r="AF91" t="n">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="AG91" t="n">
-        <v>3.28</v>
+        <v>2.57</v>
       </c>
       <c r="AH91" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AI91" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AJ91" t="n">
-        <v>3.08</v>
+        <v>2.66</v>
       </c>
       <c r="AK91" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AL91" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="AM91" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AN91" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AO91" t="n">
-        <v>2.62</v>
+        <v>2.16</v>
       </c>
       <c r="AP91" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR91" t="n">
-        <v>2.74</v>
+        <v>2.51</v>
       </c>
       <c r="AS91" t="n">
-        <v>3.04</v>
+        <v>3.32</v>
       </c>
       <c r="AT91" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AU91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV91" t="n">
         <v>0</v>
       </c>
       <c r="AW91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ91" t="n">
         <v>1</v>
       </c>
       <c r="BA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB91" t="n">
-        <v>-1</v>
+        <v>668270</v>
       </c>
       <c r="BC91" t="n">
         <v>0</v>
       </c>
       <c r="BD91" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BE91" t="n">
         <v>0</v>
@@ -42751,7 +42739,7 @@
         <v>-1</v>
       </c>
       <c r="BO91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP91" t="n">
         <v>0</v>
@@ -42763,7 +42751,7 @@
         <v>2</v>
       </c>
       <c r="BS91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT91" t="n">
         <v>3</v>
@@ -42772,25 +42760,25 @@
         <v>1</v>
       </c>
       <c r="BV91" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="BW91" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="BX91" t="n">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="BY91" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BZ91" t="n">
-        <v>1.44</v>
+        <v>2.76</v>
       </c>
       <c r="CA91" t="n">
-        <v>1.34</v>
+        <v>1.09</v>
       </c>
       <c r="CB91" t="n">
-        <v>2.78</v>
+        <v>3.85</v>
       </c>
       <c r="CC91" t="n">
         <v>0</v>
@@ -42838,73 +42826,73 @@
         <v>1</v>
       </c>
       <c r="CR91" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS91" t="n">
         <v>21</v>
       </c>
-      <c r="CS91" t="n">
-        <v>23</v>
-      </c>
       <c r="CT91" t="n">
         <v>1</v>
       </c>
       <c r="CU91" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="CV91" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CW91" t="n">
         <v>1</v>
       </c>
       <c r="CX91" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="CY91" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="CZ91" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="DA91" t="n">
         <v>100</v>
       </c>
       <c r="DB91" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="DC91" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="DD91" t="n">
-        <v>1.5</v>
+        <v>0.89</v>
       </c>
       <c r="DE91" t="n">
-        <v>0.5</v>
+        <v>1.63</v>
       </c>
       <c r="DF91" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="DG91" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="DH91" t="n">
-        <v>1.09</v>
+        <v>0.55</v>
       </c>
       <c r="DI91" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="DJ91" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="DK91" t="n">
         <v>0</v>
       </c>
       <c r="DL91" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DM91" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="DN91" t="n">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="DO91" t="n">
         <v>17</v>
@@ -42913,7 +42901,7 @@
         <v>1</v>
       </c>
       <c r="DQ91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR91" t="b">
         <v>0</v>
@@ -42928,70 +42916,82 @@
         <v>0</v>
       </c>
       <c r="DV91" t="b">
-        <v>1</v>
-      </c>
-      <c r="DW91" t="inlineStr"/>
-      <c r="DX91" t="inlineStr"/>
-      <c r="DY91" t="inlineStr"/>
-      <c r="DZ91" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="DW91" t="n">
+        <v>8</v>
+      </c>
+      <c r="DX91" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="DY91" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="DZ91" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
       <c r="EA91" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EB91" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="EC91" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="ED91" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EE91" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EF91" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="EG91" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="EH91" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="EI91" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="EJ91" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="EK91" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EL91" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="EM91" t="inlineStr"/>
@@ -46129,7 +46129,7 @@
         <v>2.22</v>
       </c>
       <c r="DE98" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF98" t="n">
         <v>2</v>
@@ -49322,7 +49322,7 @@
         <v>57</v>
       </c>
       <c r="DD105" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DE105" t="n">
         <v>0.44</v>
@@ -53619,12 +53619,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F115" s="2" t="n">
@@ -53634,347 +53634,347 @@
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K115" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L115" t="n">
+        <v>13</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1</v>
+      </c>
+      <c r="N115" t="n">
+        <v>1</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>3</v>
+      </c>
+      <c r="R115" t="n">
+        <v>2</v>
+      </c>
+      <c r="S115" t="n">
         <v>12</v>
       </c>
-      <c r="M115" t="n">
-        <v>1</v>
-      </c>
-      <c r="N115" t="n">
-        <v>3</v>
-      </c>
-      <c r="O115" t="n">
-        <v>0</v>
-      </c>
-      <c r="P115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
-      <c r="R115" t="n">
-        <v>2</v>
-      </c>
-      <c r="S115" t="n">
-        <v>7</v>
-      </c>
       <c r="T115" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="U115" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="V115" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="W115" t="n">
         <v>12</v>
       </c>
       <c r="X115" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y115" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="Z115" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>Stadion Nizhny Novgorod</t>
+          <t>Anzhi-Arena</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>ul. Dolzhanskaya, Nizhniy Novgorod</t>
+          <t>, Kaspiysk</t>
         </is>
       </c>
       <c r="AC115" t="n">
         <v>1</v>
       </c>
       <c r="AD115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE115" t="n">
-        <v>2.8</v>
+        <v>3.83</v>
       </c>
       <c r="AF115" t="n">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="AG115" t="n">
-        <v>2.56</v>
+        <v>2.09</v>
       </c>
       <c r="AH115" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AI115" t="n">
         <v>2.2</v>
       </c>
       <c r="AJ115" t="n">
-        <v>3.84</v>
+        <v>4.55</v>
       </c>
       <c r="AK115" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AL115" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AM115" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AN115" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="AO115" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AR115" t="n">
-        <v>3.2</v>
+        <v>3.52</v>
       </c>
       <c r="AS115" t="n">
-        <v>2.73</v>
+        <v>2.43</v>
       </c>
       <c r="AT115" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AU115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB115" t="n">
+        <v>101</v>
+      </c>
+      <c r="BC115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD115" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT115" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV115" t="n">
+        <v>54</v>
+      </c>
+      <c r="BW115" t="n">
+        <v>45</v>
+      </c>
+      <c r="BX115" t="n">
+        <v>96</v>
+      </c>
+      <c r="BY115" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ115" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CA115" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="CB115" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="CC115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR115" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS115" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU115" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV115" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX115" t="n">
+        <v>13</v>
+      </c>
+      <c r="CY115" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ115" t="n">
+        <v>25</v>
+      </c>
+      <c r="DA115" t="n">
+        <v>62</v>
+      </c>
+      <c r="DB115" t="n">
+        <v>17</v>
+      </c>
+      <c r="DC115" t="n">
+        <v>70</v>
+      </c>
+      <c r="DD115" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE115" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DF115" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DG115" t="n">
         <v>1.33</v>
       </c>
-      <c r="AU115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ115" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA115" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB115" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BC115" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD115" t="n">
-        <v>47</v>
-      </c>
-      <c r="BE115" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF115" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BG115" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BH115" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI115" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BJ115" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BK115" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BL115" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BM115" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BN115" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BO115" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP115" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ115" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR115" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS115" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT115" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU115" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV115" t="n">
-        <v>46</v>
-      </c>
-      <c r="BW115" t="n">
-        <v>43</v>
-      </c>
-      <c r="BX115" t="n">
-        <v>80</v>
-      </c>
-      <c r="BY115" t="n">
-        <v>78</v>
-      </c>
-      <c r="BZ115" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="CA115" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="CB115" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="CC115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI115" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ115" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM115" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CN115" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CO115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ115" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR115" t="n">
-        <v>16</v>
-      </c>
-      <c r="CS115" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT115" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU115" t="n">
-        <v>14</v>
-      </c>
-      <c r="CV115" t="n">
-        <v>15</v>
-      </c>
-      <c r="CW115" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX115" t="n">
-        <v>5</v>
-      </c>
-      <c r="CY115" t="n">
-        <v>6</v>
-      </c>
-      <c r="CZ115" t="n">
-        <v>54</v>
-      </c>
-      <c r="DA115" t="n">
-        <v>69</v>
-      </c>
-      <c r="DB115" t="n">
-        <v>31</v>
-      </c>
-      <c r="DC115" t="n">
-        <v>77</v>
-      </c>
-      <c r="DD115" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="DE115" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="DF115" t="n">
-        <v>1</v>
-      </c>
-      <c r="DG115" t="n">
-        <v>0.83</v>
-      </c>
       <c r="DH115" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="DI115" t="n">
-        <v>1.36</v>
+        <v>2.14</v>
       </c>
       <c r="DJ115" t="n">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="DK115" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="DL115" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="DM115" t="n">
-        <v>1.19</v>
+        <v>1.55</v>
       </c>
       <c r="DN115" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DO115" t="n">
         <v>17</v>
       </c>
       <c r="DP115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ115" t="b">
         <v>0</v>
@@ -53995,63 +53995,59 @@
         <v>0</v>
       </c>
       <c r="DW115" t="n">
-        <v>8.43</v>
+        <v>14.21</v>
       </c>
       <c r="DX115" t="n">
-        <v>6.4</v>
+        <v>4.28</v>
       </c>
       <c r="DY115" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="DZ115" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="EA115" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="EB115" t="inlineStr">
-        <is>
-          <t>4.02</t>
-        </is>
-      </c>
-      <c r="EC115" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="EA115" t="inlineStr"/>
+      <c r="EB115" t="inlineStr"/>
+      <c r="EC115" t="inlineStr"/>
       <c r="ED115" t="inlineStr"/>
-      <c r="EE115" t="inlineStr"/>
-      <c r="EF115" t="inlineStr"/>
+      <c r="EE115" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EF115" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
       <c r="EG115" t="inlineStr"/>
       <c r="EH115" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="EI115" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EJ115" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="EK115" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EL115" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EM115" t="inlineStr"/>
@@ -54075,12 +54071,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F116" s="2" t="n">
@@ -54090,128 +54086,128 @@
         <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J116" t="n">
+        <v>2</v>
+      </c>
+      <c r="K116" t="n">
+        <v>10</v>
+      </c>
+      <c r="L116" t="n">
+        <v>12</v>
+      </c>
+      <c r="M116" t="n">
+        <v>1</v>
+      </c>
+      <c r="N116" t="n">
+        <v>3</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0</v>
+      </c>
+      <c r="R116" t="n">
+        <v>2</v>
+      </c>
+      <c r="S116" t="n">
         <v>7</v>
       </c>
-      <c r="K116" t="n">
-        <v>6</v>
-      </c>
-      <c r="L116" t="n">
+      <c r="T116" t="n">
         <v>13</v>
       </c>
-      <c r="M116" t="n">
-        <v>1</v>
-      </c>
-      <c r="N116" t="n">
-        <v>1</v>
-      </c>
-      <c r="O116" t="n">
-        <v>0</v>
-      </c>
-      <c r="P116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>3</v>
-      </c>
-      <c r="R116" t="n">
-        <v>2</v>
-      </c>
-      <c r="S116" t="n">
-        <v>12</v>
-      </c>
-      <c r="T116" t="n">
-        <v>9</v>
-      </c>
       <c r="U116" t="n">
+        <v>7</v>
+      </c>
+      <c r="V116" t="n">
         <v>15</v>
-      </c>
-      <c r="V116" t="n">
-        <v>11</v>
       </c>
       <c r="W116" t="n">
         <v>12</v>
       </c>
       <c r="X116" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y116" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="Z116" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>Anzhi-Arena</t>
+          <t>Stadion Nizhny Novgorod</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>, Kaspiysk</t>
+          <t>ul. Dolzhanskaya, Nizhniy Novgorod</t>
         </is>
       </c>
       <c r="AC116" t="n">
         <v>1</v>
       </c>
       <c r="AD116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE116" t="n">
-        <v>3.83</v>
+        <v>2.8</v>
       </c>
       <c r="AF116" t="n">
-        <v>3.03</v>
+        <v>3.1</v>
       </c>
       <c r="AG116" t="n">
-        <v>2.09</v>
+        <v>2.56</v>
       </c>
       <c r="AH116" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AI116" t="n">
         <v>2.2</v>
       </c>
       <c r="AJ116" t="n">
-        <v>4.55</v>
+        <v>3.84</v>
       </c>
       <c r="AK116" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AL116" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AM116" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AN116" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="AO116" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AR116" t="n">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="AS116" t="n">
-        <v>2.43</v>
+        <v>2.73</v>
       </c>
       <c r="AT116" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AU116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV116" t="n">
         <v>0</v>
@@ -54223,22 +54219,22 @@
         <v>0</v>
       </c>
       <c r="AY116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA116" t="n">
         <v>0</v>
       </c>
       <c r="BB116" t="n">
-        <v>101</v>
+        <v>-1</v>
       </c>
       <c r="BC116" t="n">
         <v>0</v>
       </c>
       <c r="BD116" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="BE116" t="n">
         <v>0</v>
@@ -54274,7 +54270,7 @@
         <v>0</v>
       </c>
       <c r="BP116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ116" t="n">
         <v>1</v>
@@ -54283,7 +54279,7 @@
         <v>1</v>
       </c>
       <c r="BS116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT116" t="n">
         <v>2</v>
@@ -54292,145 +54288,145 @@
         <v>1</v>
       </c>
       <c r="BV116" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW116" t="n">
+        <v>43</v>
+      </c>
+      <c r="BX116" t="n">
+        <v>80</v>
+      </c>
+      <c r="BY116" t="n">
+        <v>78</v>
+      </c>
+      <c r="BZ116" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="CA116" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CB116" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="CC116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR116" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS116" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU116" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV116" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX116" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY116" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ116" t="n">
         <v>54</v>
       </c>
-      <c r="BW116" t="n">
-        <v>45</v>
-      </c>
-      <c r="BX116" t="n">
-        <v>96</v>
-      </c>
-      <c r="BY116" t="n">
-        <v>88</v>
-      </c>
-      <c r="BZ116" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="CA116" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="CB116" t="n">
+      <c r="DA116" t="n">
+        <v>69</v>
+      </c>
+      <c r="DB116" t="n">
+        <v>31</v>
+      </c>
+      <c r="DC116" t="n">
+        <v>77</v>
+      </c>
+      <c r="DD116" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DE116" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DF116" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG116" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DH116" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DI116" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DJ116" t="n">
+        <v>47</v>
+      </c>
+      <c r="DK116" t="n">
+        <v>31</v>
+      </c>
+      <c r="DL116" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DM116" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DN116" t="n">
         <v>2.71</v>
-      </c>
-      <c r="CC116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM116" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CN116" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CO116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR116" t="n">
-        <v>26</v>
-      </c>
-      <c r="CS116" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU116" t="n">
-        <v>13</v>
-      </c>
-      <c r="CV116" t="n">
-        <v>12</v>
-      </c>
-      <c r="CW116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX116" t="n">
-        <v>13</v>
-      </c>
-      <c r="CY116" t="n">
-        <v>12</v>
-      </c>
-      <c r="CZ116" t="n">
-        <v>25</v>
-      </c>
-      <c r="DA116" t="n">
-        <v>62</v>
-      </c>
-      <c r="DB116" t="n">
-        <v>17</v>
-      </c>
-      <c r="DC116" t="n">
-        <v>70</v>
-      </c>
-      <c r="DD116" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DE116" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="DF116" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DG116" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DH116" t="n">
-        <v>1</v>
-      </c>
-      <c r="DI116" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="DJ116" t="n">
-        <v>75</v>
-      </c>
-      <c r="DK116" t="n">
-        <v>38</v>
-      </c>
-      <c r="DL116" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="DM116" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="DN116" t="n">
-        <v>2.75</v>
       </c>
       <c r="DO116" t="n">
         <v>17</v>
       </c>
       <c r="DP116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ116" t="b">
         <v>0</v>
@@ -54451,59 +54447,63 @@
         <v>0</v>
       </c>
       <c r="DW116" t="n">
-        <v>14.21</v>
+        <v>8.43</v>
       </c>
       <c r="DX116" t="n">
-        <v>4.28</v>
+        <v>6.4</v>
       </c>
       <c r="DY116" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="DZ116" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="EA116" t="inlineStr"/>
-      <c r="EB116" t="inlineStr"/>
-      <c r="EC116" t="inlineStr"/>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA116" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EB116" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="EC116" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
       <c r="ED116" t="inlineStr"/>
-      <c r="EE116" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EF116" t="inlineStr">
-        <is>
-          <t>2.62</t>
-        </is>
-      </c>
+      <c r="EE116" t="inlineStr"/>
+      <c r="EF116" t="inlineStr"/>
       <c r="EG116" t="inlineStr"/>
       <c r="EH116" t="inlineStr">
         <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="EI116" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EJ116" t="inlineStr">
+        <is>
           <t>3.30</t>
         </is>
       </c>
-      <c r="EI116" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="EJ116" t="inlineStr">
-        <is>
-          <t>3.23</t>
-        </is>
-      </c>
       <c r="EK116" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EL116" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EM116" t="inlineStr"/>
@@ -55753,7 +55753,7 @@
         <v>2.25</v>
       </c>
       <c r="DE119" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF119" t="n">
         <v>2.33</v>
@@ -56206,7 +56206,7 @@
         <v>75</v>
       </c>
       <c r="DD120" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DE120" t="n">
         <v>1</v>
@@ -61293,7 +61293,7 @@
         <v>2.78</v>
       </c>
       <c r="DE131" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF131" t="n">
         <v>2.75</v>
@@ -63142,7 +63142,7 @@
         <v>65</v>
       </c>
       <c r="DD135" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DE135" t="n">
         <v>1</v>
@@ -64222,6 +64222,470 @@
       <c r="EN137" t="inlineStr"/>
       <c r="EO137" t="inlineStr"/>
       <c r="EP137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>18</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Akhmat Grozny</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Orenburg</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>45996.66666666666</v>
+      </c>
+      <c r="G138" t="n">
+        <v>1</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>1</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
+        <v>7</v>
+      </c>
+      <c r="L138" t="n">
+        <v>7</v>
+      </c>
+      <c r="M138" t="n">
+        <v>1</v>
+      </c>
+      <c r="N138" t="n">
+        <v>2</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>3</v>
+      </c>
+      <c r="R138" t="n">
+        <v>3</v>
+      </c>
+      <c r="S138" t="n">
+        <v>5</v>
+      </c>
+      <c r="T138" t="n">
+        <v>12</v>
+      </c>
+      <c r="U138" t="n">
+        <v>8</v>
+      </c>
+      <c r="V138" t="n">
+        <v>15</v>
+      </c>
+      <c r="W138" t="n">
+        <v>12</v>
+      </c>
+      <c r="X138" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>Akhmat Arena</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
+        </is>
+      </c>
+      <c r="AC138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>923</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>27</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU138" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV138" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX138" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY138" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ138" t="n">
+        <v>57</v>
+      </c>
+      <c r="DA138" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB138" t="n">
+        <v>19</v>
+      </c>
+      <c r="DC138" t="n">
+        <v>76</v>
+      </c>
+      <c r="DD138" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DE138" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="DF138" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DG138" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH138" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="DI138" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DJ138" t="n">
+        <v>44</v>
+      </c>
+      <c r="DK138" t="n">
+        <v>19</v>
+      </c>
+      <c r="DL138" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="DM138" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DN138" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="DO138" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP138" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW138" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="DX138" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DY138" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="DZ138" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="EA138" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EB138" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="EC138" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="ED138" t="inlineStr"/>
+      <c r="EE138" t="inlineStr"/>
+      <c r="EF138" t="inlineStr"/>
+      <c r="EG138" t="inlineStr"/>
+      <c r="EH138" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EI138" t="inlineStr">
+        <is>
+          <t>3.58</t>
+        </is>
+      </c>
+      <c r="EJ138" t="inlineStr">
+        <is>
+          <t>3.59</t>
+        </is>
+      </c>
+      <c r="EK138" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EL138" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EM138" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EN138" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EO138" t="inlineStr"/>
+      <c r="EP138" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
+++ b/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP138" headerRowCount="1">
-  <autoFilter ref="A1:EP138"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP145" headerRowCount="1">
+  <autoFilter ref="A1:EP145"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP138"/>
+  <dimension ref="A1:EP145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.8" customWidth="1" min="1" max="1"/>
@@ -1827,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2245,7 +2245,7 @@
         <v>0.89</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2715,7 +2715,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3146,7 +3146,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="DE5" t="n">
         <v>0.33</v>
@@ -3179,7 +3179,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3659,7 +3659,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4106,7 +4106,7 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE7" t="n">
         <v>1</v>
@@ -4139,7 +4139,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4553,7 +4553,7 @@
         <v>1.78</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4583,7 +4583,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5025,7 +5025,7 @@
         <v>0.89</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5055,7 +5055,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP9" t="b">
         <v>0</v>
@@ -5473,7 +5473,7 @@
         <v>1.5</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5503,7 +5503,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5914,7 +5914,7 @@
         <v>100</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="DE11" t="n">
         <v>1.78</v>
@@ -5947,7 +5947,7 @@
         <v>2.56</v>
       </c>
       <c r="DO11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6411,7 +6411,7 @@
         <v>2.72</v>
       </c>
       <c r="DO12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6830,10 +6830,10 @@
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="DE13" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF13" t="n">
         <v>0</v>
@@ -6863,7 +6863,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7310,10 +7310,10 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -7343,7 +7343,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7787,7 +7787,7 @@
         <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8275,7 +8275,7 @@
         <v>1.72</v>
       </c>
       <c r="DO16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8747,7 +8747,7 @@
         <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9170,10 +9170,10 @@
         <v>50</v>
       </c>
       <c r="DD18" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DF18" t="n">
         <v>0</v>
@@ -9203,7 +9203,7 @@
         <v>1.28</v>
       </c>
       <c r="DO18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9642,7 +9642,7 @@
         <v>50</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="DE19" t="n">
         <v>1</v>
@@ -9675,7 +9675,7 @@
         <v>1.82</v>
       </c>
       <c r="DO19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10101,7 +10101,7 @@
         <v>0.89</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF20" t="n">
         <v>0</v>
@@ -10131,7 +10131,7 @@
         <v>2.42</v>
       </c>
       <c r="DO20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10559,7 +10559,7 @@
         <v>1.95</v>
       </c>
       <c r="DO21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -10986,7 +10986,7 @@
         <v>0</v>
       </c>
       <c r="DD22" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE22" t="n">
         <v>0.44</v>
@@ -11019,7 +11019,7 @@
         <v>0</v>
       </c>
       <c r="DO22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11446,10 +11446,10 @@
         <v>50</v>
       </c>
       <c r="DD23" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DF23" t="n">
         <v>3</v>
@@ -11479,7 +11479,7 @@
         <v>3.96</v>
       </c>
       <c r="DO23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -11918,7 +11918,7 @@
         <v>50</v>
       </c>
       <c r="DD24" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE24" t="n">
         <v>0.67</v>
@@ -11951,7 +11951,7 @@
         <v>1.08</v>
       </c>
       <c r="DO24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12395,7 +12395,7 @@
         <v>2.16</v>
       </c>
       <c r="DO25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12850,10 +12850,10 @@
         <v>100</v>
       </c>
       <c r="DD26" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE26" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DF26" t="n">
         <v>3</v>
@@ -12883,7 +12883,7 @@
         <v>1.97</v>
       </c>
       <c r="DO26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13363,7 +13363,7 @@
         <v>3.01</v>
       </c>
       <c r="DO27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13781,7 +13781,7 @@
         <v>2.78</v>
       </c>
       <c r="DE28" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DF28" t="n">
         <v>3</v>
@@ -13811,7 +13811,7 @@
         <v>2.04</v>
       </c>
       <c r="DO28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14279,7 +14279,7 @@
         <v>3.23</v>
       </c>
       <c r="DO29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14751,7 +14751,7 @@
         <v>3.75</v>
       </c>
       <c r="DO30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15211,7 +15211,7 @@
         <v>2.03</v>
       </c>
       <c r="DO31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15634,7 +15634,7 @@
         <v>50</v>
       </c>
       <c r="DD32" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DE32" t="n">
         <v>1</v>
@@ -15667,7 +15667,7 @@
         <v>1.95</v>
       </c>
       <c r="DO32" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16102,10 +16102,10 @@
         <v>50</v>
       </c>
       <c r="DD33" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DE33" t="n">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="DF33" t="n">
         <v>0</v>
@@ -16135,7 +16135,7 @@
         <v>3.03</v>
       </c>
       <c r="DO33" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16546,10 +16546,10 @@
         <v>100</v>
       </c>
       <c r="DD34" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE34" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF34" t="n">
         <v>3</v>
@@ -16579,7 +16579,7 @@
         <v>2.73</v>
       </c>
       <c r="DO34" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -16982,7 +16982,7 @@
         <v>75</v>
       </c>
       <c r="DD35" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="DE35" t="n">
         <v>1.56</v>
@@ -17015,7 +17015,7 @@
         <v>2.48</v>
       </c>
       <c r="DO35" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17473,7 +17473,7 @@
         <v>1.78</v>
       </c>
       <c r="DE36" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DF36" t="n">
         <v>1.5</v>
@@ -17503,7 +17503,7 @@
         <v>2.73</v>
       </c>
       <c r="DO36" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -17967,7 +17967,7 @@
         <v>2.97</v>
       </c>
       <c r="DO37" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18411,7 +18411,7 @@
         <v>2.06</v>
       </c>
       <c r="DO38" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -18845,7 +18845,7 @@
         <v>1.33</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DF39" t="n">
         <v>2</v>
@@ -18875,7 +18875,7 @@
         <v>2.78</v>
       </c>
       <c r="DO39" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19298,7 +19298,7 @@
         <v>50</v>
       </c>
       <c r="DD40" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="DE40" t="n">
         <v>0.44</v>
@@ -19331,7 +19331,7 @@
         <v>2.87</v>
       </c>
       <c r="DO40" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -19787,7 +19787,7 @@
         <v>2.54</v>
       </c>
       <c r="DO41" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20723,7 +20723,7 @@
         <v>2.55</v>
       </c>
       <c r="DO43" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21154,7 +21154,7 @@
         <v>84</v>
       </c>
       <c r="DD44" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE44" t="n">
         <v>0.33</v>
@@ -21187,7 +21187,7 @@
         <v>3.11</v>
       </c>
       <c r="DO44" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -21651,7 +21651,7 @@
         <v>2.4</v>
       </c>
       <c r="DO45" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22101,7 +22101,7 @@
         <v>1.33</v>
       </c>
       <c r="DE46" t="n">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="DF46" t="n">
         <v>1.33</v>
@@ -22131,7 +22131,7 @@
         <v>2.53</v>
       </c>
       <c r="DO46" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22579,7 +22579,7 @@
         <v>2.33</v>
       </c>
       <c r="DO47" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23009,7 +23009,7 @@
         <v>2.78</v>
       </c>
       <c r="DE48" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DF48" t="n">
         <v>3</v>
@@ -23039,7 +23039,7 @@
         <v>3.02</v>
       </c>
       <c r="DO48" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -23462,7 +23462,7 @@
         <v>84</v>
       </c>
       <c r="DD49" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DE49" t="n">
         <v>1.78</v>
@@ -23495,7 +23495,7 @@
         <v>2.7</v>
       </c>
       <c r="DO49" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -23937,7 +23937,7 @@
         <v>0.89</v>
       </c>
       <c r="DE50" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DF50" t="n">
         <v>0.75</v>
@@ -23967,7 +23967,7 @@
         <v>2.38</v>
       </c>
       <c r="DO50" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24382,10 +24382,10 @@
         <v>67</v>
       </c>
       <c r="DD51" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE51" t="n">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="DF51" t="n">
         <v>2.33</v>
@@ -24415,7 +24415,7 @@
         <v>2.54</v>
       </c>
       <c r="DO51" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -24846,7 +24846,7 @@
         <v>50</v>
       </c>
       <c r="DD52" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="DE52" t="n">
         <v>0.44</v>
@@ -24879,7 +24879,7 @@
         <v>2</v>
       </c>
       <c r="DO52" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25302,7 +25302,7 @@
         <v>75</v>
       </c>
       <c r="DD53" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DE53" t="n">
         <v>0.67</v>
@@ -25335,7 +25335,7 @@
         <v>3.04</v>
       </c>
       <c r="DO53" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -25783,7 +25783,7 @@
         <v>3.31</v>
       </c>
       <c r="DO54" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26205,7 +26205,7 @@
         <v>2.25</v>
       </c>
       <c r="DE55" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DF55" t="n">
         <v>2.33</v>
@@ -26235,7 +26235,7 @@
         <v>2.77</v>
       </c>
       <c r="DO55" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -26695,7 +26695,7 @@
         <v>3.14</v>
       </c>
       <c r="DO56" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27134,7 +27134,7 @@
         <v>75</v>
       </c>
       <c r="DD57" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE57" t="n">
         <v>1</v>
@@ -27167,7 +27167,7 @@
         <v>2.24</v>
       </c>
       <c r="DO57" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -27639,7 +27639,7 @@
         <v>2.53</v>
       </c>
       <c r="DO58" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -28111,7 +28111,7 @@
         <v>2.96</v>
       </c>
       <c r="DO59" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -28215,37 +28215,37 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
         <v>45913.57291666666</v>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K60" t="n">
         <v>5</v>
       </c>
       <c r="L60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N60" t="n">
         <v>4</v>
@@ -28257,7 +28257,7 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R60" t="n">
         <v>4</v>
@@ -28266,110 +28266,102 @@
         <v>9</v>
       </c>
       <c r="T60" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="U60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V60" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="W60" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="X60" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y60" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="Z60" t="n">
-        <v>62</v>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>Akhmat Arena</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
-        </is>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD60" t="n">
         <v>4</v>
       </c>
       <c r="AE60" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="AF60" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="AG60" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AI60" t="n">
         <v>1.77</v>
       </c>
       <c r="AJ60" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="AK60" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AL60" t="n">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="AM60" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="AN60" t="n">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AO60" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AQ60" t="n">
         <v>1.38</v>
       </c>
       <c r="AR60" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="AS60" t="n">
-        <v>2.88</v>
+        <v>3.07</v>
       </c>
       <c r="AT60" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AU60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY60" t="n">
         <v>1</v>
       </c>
       <c r="AZ60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB60" t="n">
         <v>-1</v>
@@ -28378,7 +28370,7 @@
         <v>0</v>
       </c>
       <c r="BD60" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="BE60" t="n">
         <v>0</v>
@@ -28414,43 +28406,43 @@
         <v>0</v>
       </c>
       <c r="BP60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BQ60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR60" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS60" t="n">
         <v>3</v>
       </c>
-      <c r="BS60" t="n">
-        <v>1</v>
-      </c>
       <c r="BT60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BU60" t="n">
         <v>1</v>
       </c>
       <c r="BV60" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="BW60" t="n">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="BX60" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="BY60" t="n">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="BZ60" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="CA60" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="CB60" t="n">
-        <v>3.11</v>
+        <v>2.81</v>
       </c>
       <c r="CC60" t="n">
         <v>0</v>
@@ -28498,19 +28490,19 @@
         <v>1</v>
       </c>
       <c r="CR60" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="CS60" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CT60" t="n">
         <v>1</v>
       </c>
       <c r="CU60" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="CV60" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="CW60" t="n">
         <v>1</v>
@@ -28519,55 +28511,55 @@
         <v>4</v>
       </c>
       <c r="CY60" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CZ60" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="DA60" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="DB60" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="DC60" t="n">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="DD60" t="n">
-        <v>1.78</v>
+        <v>1.33</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.78</v>
+        <v>1</v>
       </c>
       <c r="DF60" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DG60" t="n">
-        <v>2.33</v>
+        <v>1.33</v>
       </c>
       <c r="DH60" t="n">
         <v>1.14</v>
       </c>
       <c r="DI60" t="n">
-        <v>2.14</v>
+        <v>1.57</v>
       </c>
       <c r="DJ60" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="DK60" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="DL60" t="n">
-        <v>1.47</v>
+        <v>1.97</v>
       </c>
       <c r="DM60" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="DN60" t="n">
-        <v>2.92</v>
+        <v>3.31</v>
       </c>
       <c r="DO60" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -28576,10 +28568,10 @@
         <v>1</v>
       </c>
       <c r="DR60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT60" t="b">
         <v>0</v>
@@ -28591,34 +28583,34 @@
         <v>1</v>
       </c>
       <c r="DW60" t="n">
-        <v>19.43</v>
+        <v>16.47</v>
       </c>
       <c r="DX60" t="n">
-        <v>3.41</v>
+        <v>2.44</v>
       </c>
       <c r="DY60" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="DZ60" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="EA60" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EB60" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="EC60" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="ED60" t="inlineStr"/>
@@ -28627,41 +28619,49 @@
       <c r="EG60" t="inlineStr"/>
       <c r="EH60" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="EI60" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="EJ60" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EK60" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="EL60" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="EM60" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EN60" t="inlineStr">
         <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="EO60" t="inlineStr"/>
-      <c r="EP60" t="inlineStr"/>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EO60" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EP60" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -28679,37 +28679,37 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F61" s="2" t="n">
         <v>45913.57291666666</v>
       </c>
       <c r="G61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K61" t="n">
         <v>5</v>
       </c>
       <c r="L61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
         <v>4</v>
@@ -28721,7 +28721,7 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R61" t="n">
         <v>4</v>
@@ -28730,183 +28730,191 @@
         <v>9</v>
       </c>
       <c r="T61" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="U61" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V61" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W61" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="X61" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y61" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="Z61" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA61" t="inlineStr"/>
-      <c r="AB61" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>Akhmat Arena</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
+        </is>
+      </c>
       <c r="AC61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD61" t="n">
         <v>4</v>
       </c>
       <c r="AE61" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="AF61" t="n">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="AG61" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AI61" t="n">
         <v>1.77</v>
       </c>
       <c r="AJ61" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="AK61" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AL61" t="n">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="AM61" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="AN61" t="n">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AO61" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AQ61" t="n">
         <v>1.38</v>
       </c>
       <c r="AR61" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="AS61" t="n">
-        <v>3.07</v>
+        <v>2.88</v>
       </c>
       <c r="AT61" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AU61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY61" t="n">
         <v>1</v>
       </c>
       <c r="AZ61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD61" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH61" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP61" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR61" t="n">
         <v>3</v>
       </c>
-      <c r="BB61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BC61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD61" t="n">
-        <v>59</v>
-      </c>
-      <c r="BE61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BG61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BH61" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BJ61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BK61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BL61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BM61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BN61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BO61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP61" t="n">
+      <c r="BS61" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT61" t="n">
         <v>3</v>
       </c>
-      <c r="BQ61" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR61" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS61" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT61" t="n">
-        <v>2</v>
-      </c>
       <c r="BU61" t="n">
         <v>1</v>
       </c>
       <c r="BV61" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="BW61" t="n">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="BX61" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="BY61" t="n">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="BZ61" t="n">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="CA61" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="CB61" t="n">
-        <v>2.81</v>
+        <v>3.11</v>
       </c>
       <c r="CC61" t="n">
         <v>0</v>
@@ -28954,19 +28962,19 @@
         <v>1</v>
       </c>
       <c r="CR61" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="CS61" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT61" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU61" t="n">
         <v>17</v>
       </c>
-      <c r="CT61" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU61" t="n">
-        <v>21</v>
-      </c>
       <c r="CV61" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="CW61" t="n">
         <v>1</v>
@@ -28975,55 +28983,55 @@
         <v>4</v>
       </c>
       <c r="CY61" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CZ61" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="DA61" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="DB61" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="DC61" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.33</v>
+        <v>1.78</v>
       </c>
       <c r="DE61" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="DF61" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="DG61" t="n">
-        <v>1.33</v>
+        <v>2.33</v>
       </c>
       <c r="DH61" t="n">
         <v>1.14</v>
       </c>
       <c r="DI61" t="n">
-        <v>1.57</v>
+        <v>2.14</v>
       </c>
       <c r="DJ61" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="DK61" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="DL61" t="n">
-        <v>1.97</v>
+        <v>1.47</v>
       </c>
       <c r="DM61" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="DN61" t="n">
-        <v>3.31</v>
+        <v>2.92</v>
       </c>
       <c r="DO61" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -29032,10 +29040,10 @@
         <v>1</v>
       </c>
       <c r="DR61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT61" t="b">
         <v>0</v>
@@ -29047,34 +29055,34 @@
         <v>1</v>
       </c>
       <c r="DW61" t="n">
-        <v>16.47</v>
+        <v>19.43</v>
       </c>
       <c r="DX61" t="n">
-        <v>2.44</v>
+        <v>3.41</v>
       </c>
       <c r="DY61" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="DZ61" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA61" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EB61" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EC61" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="ED61" t="inlineStr"/>
@@ -29083,49 +29091,41 @@
       <c r="EG61" t="inlineStr"/>
       <c r="EH61" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="EI61" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="EJ61" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="EK61" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="EL61" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EM61" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EN61" t="inlineStr">
         <is>
-          <t>1.99</t>
-        </is>
-      </c>
-      <c r="EO61" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EP61" t="inlineStr">
-        <is>
-          <t>2.58</t>
-        </is>
-      </c>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EO61" t="inlineStr"/>
+      <c r="EP61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -29462,10 +29462,10 @@
         <v>67</v>
       </c>
       <c r="DD62" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="DE62" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DF62" t="n">
         <v>2</v>
@@ -29495,7 +29495,7 @@
         <v>3.61</v>
       </c>
       <c r="DO62" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -29931,7 +29931,7 @@
         <v>1.8</v>
       </c>
       <c r="DO63" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -30358,7 +30358,7 @@
         <v>100</v>
       </c>
       <c r="DD64" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE64" t="n">
         <v>1.56</v>
@@ -30391,7 +30391,7 @@
         <v>2.75</v>
       </c>
       <c r="DO64" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP64" t="b">
         <v>0</v>
@@ -30846,10 +30846,10 @@
         <v>67</v>
       </c>
       <c r="DD65" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DE65" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DF65" t="n">
         <v>1.33</v>
@@ -30879,7 +30879,7 @@
         <v>3.14</v>
       </c>
       <c r="DO65" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -31335,7 +31335,7 @@
         <v>2.54</v>
       </c>
       <c r="DO66" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -31757,7 +31757,7 @@
         <v>0.89</v>
       </c>
       <c r="DE67" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DF67" t="n">
         <v>0.5</v>
@@ -31787,7 +31787,7 @@
         <v>3</v>
       </c>
       <c r="DO67" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -32214,10 +32214,10 @@
         <v>71</v>
       </c>
       <c r="DD68" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE68" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF68" t="n">
         <v>2.33</v>
@@ -32247,7 +32247,7 @@
         <v>2.38</v>
       </c>
       <c r="DO68" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -32719,7 +32719,7 @@
         <v>2.57</v>
       </c>
       <c r="DO69" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -33130,10 +33130,10 @@
         <v>88</v>
       </c>
       <c r="DD70" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="DE70" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DF70" t="n">
         <v>1.75</v>
@@ -33163,7 +33163,7 @@
         <v>2.43</v>
       </c>
       <c r="DO70" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -33590,7 +33590,7 @@
         <v>71</v>
       </c>
       <c r="DD71" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE71" t="n">
         <v>1</v>
@@ -33623,7 +33623,7 @@
         <v>2.46</v>
       </c>
       <c r="DO71" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP71" t="b">
         <v>0</v>
@@ -34062,7 +34062,7 @@
         <v>63</v>
       </c>
       <c r="DD72" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="DE72" t="n">
         <v>1.56</v>
@@ -34095,7 +34095,7 @@
         <v>3.42</v>
       </c>
       <c r="DO72" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -34534,10 +34534,10 @@
         <v>88</v>
       </c>
       <c r="DD73" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DE73" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DF73" t="n">
         <v>0.33</v>
@@ -34567,7 +34567,7 @@
         <v>2.46</v>
       </c>
       <c r="DO73" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -35047,7 +35047,7 @@
         <v>2.54</v>
       </c>
       <c r="DO74" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -35477,7 +35477,7 @@
         <v>1.78</v>
       </c>
       <c r="DE75" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DF75" t="n">
         <v>1.75</v>
@@ -35507,7 +35507,7 @@
         <v>2.91</v>
       </c>
       <c r="DO75" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -35929,7 +35929,7 @@
         <v>2.25</v>
       </c>
       <c r="DE76" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DF76" t="n">
         <v>2</v>
@@ -35959,7 +35959,7 @@
         <v>3.09</v>
       </c>
       <c r="DO76" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -36414,7 +36414,7 @@
         <v>75</v>
       </c>
       <c r="DD77" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DE77" t="n">
         <v>2</v>
@@ -36447,7 +36447,7 @@
         <v>2.97</v>
       </c>
       <c r="DO77" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP77" t="b">
         <v>0</v>
@@ -36862,7 +36862,7 @@
         <v>88</v>
       </c>
       <c r="DD78" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE78" t="n">
         <v>0.44</v>
@@ -36895,7 +36895,7 @@
         <v>3.2</v>
       </c>
       <c r="DO78" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -37359,7 +37359,7 @@
         <v>3.14</v>
       </c>
       <c r="DO79" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -37782,7 +37782,7 @@
         <v>45</v>
       </c>
       <c r="DD80" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE80" t="n">
         <v>0.44</v>
@@ -37815,7 +37815,7 @@
         <v>1.87</v>
       </c>
       <c r="DO80" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP80" t="b">
         <v>0</v>
@@ -38254,10 +38254,10 @@
         <v>53</v>
       </c>
       <c r="DD81" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="DE81" t="n">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="DF81" t="n">
         <v>2</v>
@@ -38287,7 +38287,7 @@
         <v>2.45</v>
       </c>
       <c r="DO81" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -38723,7 +38723,7 @@
         <v>2.79</v>
       </c>
       <c r="DO82" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -39145,7 +39145,7 @@
         <v>1.89</v>
       </c>
       <c r="DE83" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DF83" t="n">
         <v>2</v>
@@ -39175,7 +39175,7 @@
         <v>2.19</v>
       </c>
       <c r="DO83" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -39598,7 +39598,7 @@
         <v>70</v>
       </c>
       <c r="DD84" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="DE84" t="n">
         <v>0.67</v>
@@ -39631,7 +39631,7 @@
         <v>3.27</v>
       </c>
       <c r="DO84" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -40049,7 +40049,7 @@
         <v>1.33</v>
       </c>
       <c r="DE85" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF85" t="n">
         <v>1.6</v>
@@ -40079,7 +40079,7 @@
         <v>3.26</v>
       </c>
       <c r="DO85" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -40555,7 +40555,7 @@
         <v>2.29</v>
       </c>
       <c r="DO86" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -40994,10 +40994,10 @@
         <v>70</v>
       </c>
       <c r="DD87" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DE87" t="n">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="DF87" t="n">
         <v>0.25</v>
@@ -41027,7 +41027,7 @@
         <v>1.93</v>
       </c>
       <c r="DO87" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -41499,7 +41499,7 @@
         <v>3.03</v>
       </c>
       <c r="DO88" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -41938,7 +41938,7 @@
         <v>65</v>
       </c>
       <c r="DD89" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE89" t="n">
         <v>0.33</v>
@@ -41971,7 +41971,7 @@
         <v>2.67</v>
       </c>
       <c r="DO89" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -42435,7 +42435,7 @@
         <v>2.46</v>
       </c>
       <c r="DO90" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -42865,7 +42865,7 @@
         <v>0.89</v>
       </c>
       <c r="DE91" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DF91" t="n">
         <v>1.2</v>
@@ -42895,7 +42895,7 @@
         <v>2.66</v>
       </c>
       <c r="DO91" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -43334,7 +43334,7 @@
         <v>67</v>
       </c>
       <c r="DD92" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="DE92" t="n">
         <v>1</v>
@@ -43367,7 +43367,7 @@
         <v>2.78</v>
       </c>
       <c r="DO92" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -43794,7 +43794,7 @@
         <v>50</v>
       </c>
       <c r="DD93" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE93" t="n">
         <v>2</v>
@@ -43827,7 +43827,7 @@
         <v>2.49</v>
       </c>
       <c r="DO93" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -44277,7 +44277,7 @@
         <v>2.25</v>
       </c>
       <c r="DE94" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DF94" t="n">
         <v>2.2</v>
@@ -44307,7 +44307,7 @@
         <v>3.2</v>
       </c>
       <c r="DO94" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -44746,7 +44746,7 @@
         <v>84</v>
       </c>
       <c r="DD95" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DE95" t="n">
         <v>1.56</v>
@@ -44779,7 +44779,7 @@
         <v>2.32</v>
       </c>
       <c r="DO95" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -45239,7 +45239,7 @@
         <v>2.71</v>
       </c>
       <c r="DO96" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -45687,7 +45687,7 @@
         <v>3.18</v>
       </c>
       <c r="DO97" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -46126,7 +46126,7 @@
         <v>86</v>
       </c>
       <c r="DD98" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="DE98" t="n">
         <v>0.44</v>
@@ -46159,7 +46159,7 @@
         <v>2.97</v>
       </c>
       <c r="DO98" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -46586,7 +46586,7 @@
         <v>72</v>
       </c>
       <c r="DD99" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DE99" t="n">
         <v>0.33</v>
@@ -46619,7 +46619,7 @@
         <v>2.84</v>
       </c>
       <c r="DO99" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -47033,7 +47033,7 @@
         <v>2.78</v>
       </c>
       <c r="DE100" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DF100" t="n">
         <v>2.67</v>
@@ -47063,7 +47063,7 @@
         <v>2.59</v>
       </c>
       <c r="DO100" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -47489,7 +47489,7 @@
         <v>0.89</v>
       </c>
       <c r="DE101" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF101" t="n">
         <v>0.67</v>
@@ -47519,7 +47519,7 @@
         <v>2.97</v>
       </c>
       <c r="DO101" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -47991,7 +47991,7 @@
         <v>3.06</v>
       </c>
       <c r="DO102" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP102" t="b">
         <v>0</v>
@@ -48394,7 +48394,7 @@
         <v>60</v>
       </c>
       <c r="DD103" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE103" t="n">
         <v>1</v>
@@ -48427,7 +48427,7 @@
         <v>3.41</v>
       </c>
       <c r="DO103" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -48866,10 +48866,10 @@
         <v>65</v>
       </c>
       <c r="DD104" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="DE104" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DF104" t="n">
         <v>2</v>
@@ -48899,7 +48899,7 @@
         <v>3.31</v>
       </c>
       <c r="DO104" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -49355,7 +49355,7 @@
         <v>2.37</v>
       </c>
       <c r="DO105" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -49781,7 +49781,7 @@
         <v>2.78</v>
       </c>
       <c r="DE106" t="n">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="DF106" t="n">
         <v>2.71</v>
@@ -49811,7 +49811,7 @@
         <v>2.66</v>
       </c>
       <c r="DO106" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -49911,170 +49911,170 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F107" s="2" t="n">
         <v>45962.61458333334</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J107" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K107" t="n">
+        <v>2</v>
+      </c>
+      <c r="L107" t="n">
+        <v>11</v>
+      </c>
+      <c r="M107" t="n">
+        <v>2</v>
+      </c>
+      <c r="N107" t="n">
+        <v>2</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>6</v>
+      </c>
+      <c r="R107" t="n">
+        <v>1</v>
+      </c>
+      <c r="S107" t="n">
+        <v>7</v>
+      </c>
+      <c r="T107" t="n">
         <v>5</v>
       </c>
-      <c r="L107" t="n">
-        <v>8</v>
-      </c>
-      <c r="M107" t="n">
-        <v>3</v>
-      </c>
-      <c r="N107" t="n">
-        <v>3</v>
-      </c>
-      <c r="O107" t="n">
-        <v>1</v>
-      </c>
-      <c r="P107" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>2</v>
-      </c>
-      <c r="R107" t="n">
-        <v>3</v>
-      </c>
-      <c r="S107" t="n">
-        <v>5</v>
-      </c>
-      <c r="T107" t="n">
-        <v>11</v>
-      </c>
       <c r="U107" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="V107" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="W107" t="n">
         <v>16</v>
       </c>
       <c r="X107" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="Y107" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="Z107" t="n">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>Kazan' Arena</t>
+          <t>Anzhi-Arena</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>Prospekt Husaina Yamasheva 115a, Kazan'</t>
+          <t>, Kaspiysk</t>
         </is>
       </c>
       <c r="AC107" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AD107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE107" t="n">
-        <v>3.1</v>
+        <v>2.03</v>
       </c>
       <c r="AF107" t="n">
         <v>3.2</v>
       </c>
       <c r="AG107" t="n">
-        <v>2.2</v>
+        <v>3.95</v>
       </c>
       <c r="AH107" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AI107" t="n">
-        <v>1.91</v>
+        <v>2.48</v>
       </c>
       <c r="AJ107" t="n">
-        <v>2.9</v>
+        <v>4.65</v>
       </c>
       <c r="AK107" t="n">
-        <v>1.66</v>
+        <v>2.14</v>
       </c>
       <c r="AL107" t="n">
-        <v>2.29</v>
+        <v>1.64</v>
       </c>
       <c r="AM107" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="AN107" t="n">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="AO107" t="n">
-        <v>2.36</v>
+        <v>2.06</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="AR107" t="n">
-        <v>2.68</v>
+        <v>3.54</v>
       </c>
       <c r="AS107" t="n">
-        <v>2.89</v>
+        <v>2.4</v>
       </c>
       <c r="AT107" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AU107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW107" t="n">
         <v>0</v>
       </c>
       <c r="AX107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY107" t="n">
         <v>0</v>
       </c>
       <c r="AZ107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB107" t="n">
-        <v>-1</v>
+        <v>668267</v>
       </c>
       <c r="BC107" t="n">
         <v>0</v>
       </c>
       <c r="BD107" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="BE107" t="n">
         <v>0</v>
@@ -50107,169 +50107,169 @@
         <v>-1</v>
       </c>
       <c r="BO107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BR107" t="n">
         <v>2</v>
       </c>
       <c r="BS107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT107" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV107" t="n">
+        <v>53</v>
+      </c>
+      <c r="BW107" t="n">
+        <v>26</v>
+      </c>
+      <c r="BX107" t="n">
+        <v>126</v>
+      </c>
+      <c r="BY107" t="n">
+        <v>75</v>
+      </c>
+      <c r="BZ107" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="CA107" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="CB107" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="CC107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM107" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN107" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR107" t="n">
+        <v>29</v>
+      </c>
+      <c r="CS107" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU107" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV107" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX107" t="n">
         <v>5</v>
       </c>
-      <c r="BU107" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV107" t="n">
-        <v>39</v>
-      </c>
-      <c r="BW107" t="n">
-        <v>66</v>
-      </c>
-      <c r="BX107" t="n">
-        <v>101</v>
-      </c>
-      <c r="BY107" t="n">
-        <v>121</v>
-      </c>
-      <c r="BZ107" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="CA107" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CB107" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="CC107" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD107" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE107" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF107" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG107" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH107" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI107" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ107" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK107" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL107" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM107" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CN107" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CO107" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP107" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ107" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR107" t="n">
+      <c r="CY107" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ107" t="n">
+        <v>29</v>
+      </c>
+      <c r="DA107" t="n">
+        <v>68</v>
+      </c>
+      <c r="DB107" t="n">
+        <v>7</v>
+      </c>
+      <c r="DC107" t="n">
+        <v>68</v>
+      </c>
+      <c r="DD107" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DE107" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF107" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG107" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DH107" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="DI107" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ107" t="n">
+        <v>72</v>
+      </c>
+      <c r="DK107" t="n">
+        <v>32</v>
+      </c>
+      <c r="DL107" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="DM107" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="DN107" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="DO107" t="n">
         <v>18</v>
       </c>
-      <c r="CS107" t="n">
-        <v>15</v>
-      </c>
-      <c r="CT107" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU107" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV107" t="n">
-        <v>17</v>
-      </c>
-      <c r="CW107" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX107" t="n">
-        <v>10</v>
-      </c>
-      <c r="CY107" t="n">
-        <v>9</v>
-      </c>
-      <c r="CZ107" t="n">
-        <v>47</v>
-      </c>
-      <c r="DA107" t="n">
-        <v>69</v>
-      </c>
-      <c r="DB107" t="n">
-        <v>31</v>
-      </c>
-      <c r="DC107" t="n">
-        <v>61</v>
-      </c>
-      <c r="DD107" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="DE107" t="n">
-        <v>1</v>
-      </c>
-      <c r="DF107" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="DG107" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="DH107" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="DI107" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="DJ107" t="n">
-        <v>54</v>
-      </c>
-      <c r="DK107" t="n">
-        <v>31</v>
-      </c>
-      <c r="DL107" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="DM107" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DN107" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="DO107" t="n">
-        <v>17</v>
-      </c>
       <c r="DP107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR107" t="b">
         <v>0</v>
@@ -50287,101 +50287,77 @@
         <v>0</v>
       </c>
       <c r="DW107" t="n">
-        <v>6.32</v>
+        <v>16.76</v>
       </c>
       <c r="DX107" t="n">
-        <v>3.69</v>
+        <v>8.27</v>
       </c>
       <c r="DY107" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="DZ107" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="EA107" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EB107" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="EC107" t="inlineStr">
         <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="ED107" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="ED107" t="inlineStr"/>
       <c r="EE107" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EF107" t="inlineStr">
         <is>
-          <t>3.19</t>
-        </is>
-      </c>
-      <c r="EG107" t="inlineStr">
-        <is>
-          <t>2.76</t>
-        </is>
-      </c>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EG107" t="inlineStr"/>
       <c r="EH107" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EI107" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="EJ107" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="EK107" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EL107" t="inlineStr">
         <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="EM107" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
-      </c>
-      <c r="EN107" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EO107" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="EP107" t="inlineStr">
-        <is>
-          <t>2.44</t>
-        </is>
-      </c>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EM107" t="inlineStr"/>
+      <c r="EN107" t="inlineStr"/>
+      <c r="EO107" t="inlineStr"/>
+      <c r="EP107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -50399,170 +50375,170 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F108" s="2" t="n">
         <v>45962.61458333334</v>
       </c>
       <c r="G108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K108" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L108" t="n">
+        <v>8</v>
+      </c>
+      <c r="M108" t="n">
+        <v>3</v>
+      </c>
+      <c r="N108" t="n">
+        <v>3</v>
+      </c>
+      <c r="O108" t="n">
+        <v>1</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>2</v>
+      </c>
+      <c r="R108" t="n">
+        <v>3</v>
+      </c>
+      <c r="S108" t="n">
+        <v>5</v>
+      </c>
+      <c r="T108" t="n">
         <v>11</v>
       </c>
-      <c r="M108" t="n">
-        <v>2</v>
-      </c>
-      <c r="N108" t="n">
-        <v>2</v>
-      </c>
-      <c r="O108" t="n">
-        <v>0</v>
-      </c>
-      <c r="P108" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q108" t="n">
-        <v>6</v>
-      </c>
-      <c r="R108" t="n">
-        <v>1</v>
-      </c>
-      <c r="S108" t="n">
+      <c r="U108" t="n">
         <v>7</v>
       </c>
-      <c r="T108" t="n">
-        <v>5</v>
-      </c>
-      <c r="U108" t="n">
-        <v>13</v>
-      </c>
       <c r="V108" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="W108" t="n">
         <v>16</v>
       </c>
       <c r="X108" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Y108" t="n">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="Z108" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>Anzhi-Arena</t>
+          <t>Kazan' Arena</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>, Kaspiysk</t>
+          <t>Prospekt Husaina Yamasheva 115a, Kazan'</t>
         </is>
       </c>
       <c r="AC108" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE108" t="n">
-        <v>2.03</v>
+        <v>3.1</v>
       </c>
       <c r="AF108" t="n">
         <v>3.2</v>
       </c>
       <c r="AG108" t="n">
-        <v>3.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH108" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AI108" t="n">
-        <v>2.48</v>
+        <v>1.91</v>
       </c>
       <c r="AJ108" t="n">
-        <v>4.65</v>
+        <v>2.9</v>
       </c>
       <c r="AK108" t="n">
-        <v>2.14</v>
+        <v>1.66</v>
       </c>
       <c r="AL108" t="n">
-        <v>1.64</v>
+        <v>2.29</v>
       </c>
       <c r="AM108" t="n">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="AN108" t="n">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="AO108" t="n">
-        <v>2.06</v>
+        <v>2.36</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="AR108" t="n">
-        <v>3.54</v>
+        <v>2.68</v>
       </c>
       <c r="AS108" t="n">
-        <v>2.4</v>
+        <v>2.89</v>
       </c>
       <c r="AT108" t="n">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AU108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW108" t="n">
         <v>0</v>
       </c>
       <c r="AX108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY108" t="n">
         <v>0</v>
       </c>
       <c r="AZ108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB108" t="n">
-        <v>668267</v>
+        <v>-1</v>
       </c>
       <c r="BC108" t="n">
         <v>0</v>
       </c>
       <c r="BD108" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="BE108" t="n">
         <v>0</v>
@@ -50595,46 +50571,46 @@
         <v>-1</v>
       </c>
       <c r="BO108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BR108" t="n">
         <v>2</v>
       </c>
       <c r="BS108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT108" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BU108" t="n">
         <v>1</v>
       </c>
       <c r="BV108" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="BW108" t="n">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="BX108" t="n">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="BY108" t="n">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="BZ108" t="n">
-        <v>1.63</v>
+        <v>0.88</v>
       </c>
       <c r="CA108" t="n">
-        <v>0.65</v>
+        <v>1.58</v>
       </c>
       <c r="CB108" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="CC108" t="n">
         <v>0</v>
@@ -50661,7 +50637,7 @@
         <v>1</v>
       </c>
       <c r="CK108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL108" t="n">
         <v>0</v>
@@ -50682,82 +50658,82 @@
         <v>1</v>
       </c>
       <c r="CR108" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="CS108" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="CT108" t="n">
         <v>1</v>
       </c>
       <c r="CU108" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="CV108" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX108" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY108" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ108" t="n">
+        <v>47</v>
+      </c>
+      <c r="DA108" t="n">
+        <v>69</v>
+      </c>
+      <c r="DB108" t="n">
+        <v>31</v>
+      </c>
+      <c r="DC108" t="n">
+        <v>61</v>
+      </c>
+      <c r="DD108" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DE108" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF108" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DG108" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DH108" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DI108" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DJ108" t="n">
+        <v>54</v>
+      </c>
+      <c r="DK108" t="n">
+        <v>31</v>
+      </c>
+      <c r="DL108" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DM108" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DN108" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="DO108" t="n">
         <v>18</v>
       </c>
-      <c r="CW108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX108" t="n">
-        <v>5</v>
-      </c>
-      <c r="CY108" t="n">
-        <v>4</v>
-      </c>
-      <c r="CZ108" t="n">
-        <v>29</v>
-      </c>
-      <c r="DA108" t="n">
-        <v>68</v>
-      </c>
-      <c r="DB108" t="n">
-        <v>7</v>
-      </c>
-      <c r="DC108" t="n">
-        <v>68</v>
-      </c>
-      <c r="DD108" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DE108" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="DF108" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DG108" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="DH108" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="DI108" t="n">
-        <v>1</v>
-      </c>
-      <c r="DJ108" t="n">
-        <v>72</v>
-      </c>
-      <c r="DK108" t="n">
-        <v>32</v>
-      </c>
-      <c r="DL108" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="DM108" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="DN108" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="DO108" t="n">
-        <v>17</v>
-      </c>
       <c r="DP108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR108" t="b">
         <v>0</v>
@@ -50775,77 +50751,101 @@
         <v>0</v>
       </c>
       <c r="DW108" t="n">
-        <v>16.76</v>
+        <v>6.32</v>
       </c>
       <c r="DX108" t="n">
-        <v>8.27</v>
+        <v>3.69</v>
       </c>
       <c r="DY108" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="DZ108" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="EA108" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EB108" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="EC108" t="inlineStr">
         <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="ED108" t="inlineStr"/>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="ED108" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
       <c r="EE108" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EF108" t="inlineStr">
         <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="EG108" t="inlineStr"/>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="EG108" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
       <c r="EH108" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="EI108" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="EJ108" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="EK108" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="EL108" t="inlineStr">
         <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="EM108" t="inlineStr"/>
-      <c r="EN108" t="inlineStr"/>
-      <c r="EO108" t="inlineStr"/>
-      <c r="EP108" t="inlineStr"/>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EM108" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EN108" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EO108" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EP108" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -51182,10 +51182,10 @@
         <v>75</v>
       </c>
       <c r="DD109" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DE109" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DF109" t="n">
         <v>1.5</v>
@@ -51215,7 +51215,7 @@
         <v>2.81</v>
       </c>
       <c r="DO109" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -51646,10 +51646,10 @@
         <v>77</v>
       </c>
       <c r="DD110" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE110" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF110" t="n">
         <v>2.67</v>
@@ -51679,7 +51679,7 @@
         <v>3.44</v>
       </c>
       <c r="DO110" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -52135,7 +52135,7 @@
         <v>2.03</v>
       </c>
       <c r="DO111" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -52558,7 +52558,7 @@
         <v>80</v>
       </c>
       <c r="DD112" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE112" t="n">
         <v>0.67</v>
@@ -52591,7 +52591,7 @@
         <v>2.57</v>
       </c>
       <c r="DO112" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -53030,7 +53030,7 @@
         <v>59</v>
       </c>
       <c r="DD113" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="DE113" t="n">
         <v>1</v>
@@ -53063,7 +53063,7 @@
         <v>3.33</v>
       </c>
       <c r="DO113" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -53497,7 +53497,7 @@
         <v>1.33</v>
       </c>
       <c r="DE114" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DF114" t="n">
         <v>1.29</v>
@@ -53527,7 +53527,7 @@
         <v>3.16</v>
       </c>
       <c r="DO114" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP114" t="b">
         <v>1</v>
@@ -53619,12 +53619,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F115" s="2" t="n">
@@ -53634,128 +53634,128 @@
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J115" t="n">
+        <v>2</v>
+      </c>
+      <c r="K115" t="n">
+        <v>10</v>
+      </c>
+      <c r="L115" t="n">
+        <v>12</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1</v>
+      </c>
+      <c r="N115" t="n">
+        <v>3</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" t="n">
+        <v>2</v>
+      </c>
+      <c r="S115" t="n">
         <v>7</v>
       </c>
-      <c r="K115" t="n">
-        <v>6</v>
-      </c>
-      <c r="L115" t="n">
+      <c r="T115" t="n">
         <v>13</v>
       </c>
-      <c r="M115" t="n">
-        <v>1</v>
-      </c>
-      <c r="N115" t="n">
-        <v>1</v>
-      </c>
-      <c r="O115" t="n">
-        <v>0</v>
-      </c>
-      <c r="P115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q115" t="n">
-        <v>3</v>
-      </c>
-      <c r="R115" t="n">
-        <v>2</v>
-      </c>
-      <c r="S115" t="n">
-        <v>12</v>
-      </c>
-      <c r="T115" t="n">
-        <v>9</v>
-      </c>
       <c r="U115" t="n">
+        <v>7</v>
+      </c>
+      <c r="V115" t="n">
         <v>15</v>
-      </c>
-      <c r="V115" t="n">
-        <v>11</v>
       </c>
       <c r="W115" t="n">
         <v>12</v>
       </c>
       <c r="X115" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y115" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="Z115" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>Anzhi-Arena</t>
+          <t>Stadion Nizhny Novgorod</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>, Kaspiysk</t>
+          <t>ul. Dolzhanskaya, Nizhniy Novgorod</t>
         </is>
       </c>
       <c r="AC115" t="n">
         <v>1</v>
       </c>
       <c r="AD115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE115" t="n">
-        <v>3.83</v>
+        <v>2.8</v>
       </c>
       <c r="AF115" t="n">
-        <v>3.03</v>
+        <v>3.1</v>
       </c>
       <c r="AG115" t="n">
-        <v>2.09</v>
+        <v>2.56</v>
       </c>
       <c r="AH115" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AI115" t="n">
         <v>2.2</v>
       </c>
       <c r="AJ115" t="n">
-        <v>4.55</v>
+        <v>3.84</v>
       </c>
       <c r="AK115" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AL115" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AM115" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AN115" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="AO115" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AR115" t="n">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="AS115" t="n">
-        <v>2.43</v>
+        <v>2.73</v>
       </c>
       <c r="AT115" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AU115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV115" t="n">
         <v>0</v>
@@ -53767,22 +53767,22 @@
         <v>0</v>
       </c>
       <c r="AY115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA115" t="n">
         <v>0</v>
       </c>
       <c r="BB115" t="n">
-        <v>101</v>
+        <v>-1</v>
       </c>
       <c r="BC115" t="n">
         <v>0</v>
       </c>
       <c r="BD115" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="BE115" t="n">
         <v>0</v>
@@ -53818,7 +53818,7 @@
         <v>0</v>
       </c>
       <c r="BP115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ115" t="n">
         <v>1</v>
@@ -53827,7 +53827,7 @@
         <v>1</v>
       </c>
       <c r="BS115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT115" t="n">
         <v>2</v>
@@ -53836,145 +53836,145 @@
         <v>1</v>
       </c>
       <c r="BV115" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW115" t="n">
+        <v>43</v>
+      </c>
+      <c r="BX115" t="n">
+        <v>80</v>
+      </c>
+      <c r="BY115" t="n">
+        <v>78</v>
+      </c>
+      <c r="BZ115" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="CA115" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CB115" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="CC115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR115" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS115" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU115" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV115" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX115" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY115" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ115" t="n">
         <v>54</v>
       </c>
-      <c r="BW115" t="n">
-        <v>45</v>
-      </c>
-      <c r="BX115" t="n">
-        <v>96</v>
-      </c>
-      <c r="BY115" t="n">
-        <v>88</v>
-      </c>
-      <c r="BZ115" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="CA115" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="CB115" t="n">
+      <c r="DA115" t="n">
+        <v>69</v>
+      </c>
+      <c r="DB115" t="n">
+        <v>31</v>
+      </c>
+      <c r="DC115" t="n">
+        <v>77</v>
+      </c>
+      <c r="DD115" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DE115" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DF115" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG115" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DH115" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DI115" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DJ115" t="n">
+        <v>47</v>
+      </c>
+      <c r="DK115" t="n">
+        <v>31</v>
+      </c>
+      <c r="DL115" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DM115" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DN115" t="n">
         <v>2.71</v>
       </c>
-      <c r="CC115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI115" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ115" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM115" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CN115" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CO115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ115" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR115" t="n">
-        <v>26</v>
-      </c>
-      <c r="CS115" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT115" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU115" t="n">
-        <v>13</v>
-      </c>
-      <c r="CV115" t="n">
-        <v>12</v>
-      </c>
-      <c r="CW115" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX115" t="n">
-        <v>13</v>
-      </c>
-      <c r="CY115" t="n">
-        <v>12</v>
-      </c>
-      <c r="CZ115" t="n">
-        <v>25</v>
-      </c>
-      <c r="DA115" t="n">
-        <v>62</v>
-      </c>
-      <c r="DB115" t="n">
-        <v>17</v>
-      </c>
-      <c r="DC115" t="n">
-        <v>70</v>
-      </c>
-      <c r="DD115" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DE115" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="DF115" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DG115" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DH115" t="n">
-        <v>1</v>
-      </c>
-      <c r="DI115" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="DJ115" t="n">
-        <v>75</v>
-      </c>
-      <c r="DK115" t="n">
-        <v>38</v>
-      </c>
-      <c r="DL115" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="DM115" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="DN115" t="n">
-        <v>2.75</v>
-      </c>
       <c r="DO115" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ115" t="b">
         <v>0</v>
@@ -53995,59 +53995,63 @@
         <v>0</v>
       </c>
       <c r="DW115" t="n">
-        <v>14.21</v>
+        <v>8.43</v>
       </c>
       <c r="DX115" t="n">
-        <v>4.28</v>
+        <v>6.4</v>
       </c>
       <c r="DY115" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="DZ115" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="EA115" t="inlineStr"/>
-      <c r="EB115" t="inlineStr"/>
-      <c r="EC115" t="inlineStr"/>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA115" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EB115" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="EC115" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
       <c r="ED115" t="inlineStr"/>
-      <c r="EE115" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EF115" t="inlineStr">
-        <is>
-          <t>2.62</t>
-        </is>
-      </c>
+      <c r="EE115" t="inlineStr"/>
+      <c r="EF115" t="inlineStr"/>
       <c r="EG115" t="inlineStr"/>
       <c r="EH115" t="inlineStr">
         <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="EI115" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EJ115" t="inlineStr">
+        <is>
           <t>3.30</t>
         </is>
       </c>
-      <c r="EI115" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="EJ115" t="inlineStr">
-        <is>
-          <t>3.23</t>
-        </is>
-      </c>
       <c r="EK115" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EL115" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EM115" t="inlineStr"/>
@@ -54071,12 +54075,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F116" s="2" t="n">
@@ -54086,347 +54090,347 @@
         <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J116" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K116" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L116" t="n">
+        <v>13</v>
+      </c>
+      <c r="M116" t="n">
+        <v>1</v>
+      </c>
+      <c r="N116" t="n">
+        <v>1</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>3</v>
+      </c>
+      <c r="R116" t="n">
+        <v>2</v>
+      </c>
+      <c r="S116" t="n">
         <v>12</v>
       </c>
-      <c r="M116" t="n">
-        <v>1</v>
-      </c>
-      <c r="N116" t="n">
-        <v>3</v>
-      </c>
-      <c r="O116" t="n">
-        <v>0</v>
-      </c>
-      <c r="P116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
-      <c r="R116" t="n">
-        <v>2</v>
-      </c>
-      <c r="S116" t="n">
-        <v>7</v>
-      </c>
       <c r="T116" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="U116" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="V116" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="W116" t="n">
         <v>12</v>
       </c>
       <c r="X116" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y116" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="Z116" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>Stadion Nizhny Novgorod</t>
+          <t>Anzhi-Arena</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>ul. Dolzhanskaya, Nizhniy Novgorod</t>
+          <t>, Kaspiysk</t>
         </is>
       </c>
       <c r="AC116" t="n">
         <v>1</v>
       </c>
       <c r="AD116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE116" t="n">
-        <v>2.8</v>
+        <v>3.83</v>
       </c>
       <c r="AF116" t="n">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="AG116" t="n">
-        <v>2.56</v>
+        <v>2.09</v>
       </c>
       <c r="AH116" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AI116" t="n">
         <v>2.2</v>
       </c>
       <c r="AJ116" t="n">
-        <v>3.84</v>
+        <v>4.55</v>
       </c>
       <c r="AK116" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AL116" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AM116" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AN116" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="AO116" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AR116" t="n">
-        <v>3.2</v>
+        <v>3.52</v>
       </c>
       <c r="AS116" t="n">
-        <v>2.73</v>
+        <v>2.43</v>
       </c>
       <c r="AT116" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AU116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB116" t="n">
+        <v>101</v>
+      </c>
+      <c r="BC116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD116" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT116" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV116" t="n">
+        <v>54</v>
+      </c>
+      <c r="BW116" t="n">
+        <v>45</v>
+      </c>
+      <c r="BX116" t="n">
+        <v>96</v>
+      </c>
+      <c r="BY116" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ116" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CA116" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="CB116" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="CC116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR116" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS116" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU116" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV116" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX116" t="n">
+        <v>13</v>
+      </c>
+      <c r="CY116" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ116" t="n">
+        <v>25</v>
+      </c>
+      <c r="DA116" t="n">
+        <v>62</v>
+      </c>
+      <c r="DB116" t="n">
+        <v>17</v>
+      </c>
+      <c r="DC116" t="n">
+        <v>70</v>
+      </c>
+      <c r="DD116" t="n">
         <v>1.33</v>
       </c>
-      <c r="AU116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB116" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BC116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD116" t="n">
-        <v>47</v>
-      </c>
-      <c r="BE116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF116" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BG116" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BH116" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI116" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BJ116" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BK116" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BL116" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BM116" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BN116" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BO116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP116" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ116" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR116" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS116" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT116" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU116" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV116" t="n">
-        <v>46</v>
-      </c>
-      <c r="BW116" t="n">
-        <v>43</v>
-      </c>
-      <c r="BX116" t="n">
-        <v>80</v>
-      </c>
-      <c r="BY116" t="n">
-        <v>78</v>
-      </c>
-      <c r="BZ116" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="CA116" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="CB116" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="CC116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM116" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CN116" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CO116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR116" t="n">
-        <v>16</v>
-      </c>
-      <c r="CS116" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU116" t="n">
-        <v>14</v>
-      </c>
-      <c r="CV116" t="n">
-        <v>15</v>
-      </c>
-      <c r="CW116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX116" t="n">
-        <v>5</v>
-      </c>
-      <c r="CY116" t="n">
-        <v>6</v>
-      </c>
-      <c r="CZ116" t="n">
-        <v>54</v>
-      </c>
-      <c r="DA116" t="n">
-        <v>69</v>
-      </c>
-      <c r="DB116" t="n">
-        <v>31</v>
-      </c>
-      <c r="DC116" t="n">
-        <v>77</v>
-      </c>
-      <c r="DD116" t="n">
-        <v>0.89</v>
-      </c>
       <c r="DE116" t="n">
-        <v>0.75</v>
+        <v>1.22</v>
       </c>
       <c r="DF116" t="n">
-        <v>1</v>
+        <v>1.71</v>
       </c>
       <c r="DG116" t="n">
-        <v>0.83</v>
+        <v>1.33</v>
       </c>
       <c r="DH116" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="DI116" t="n">
-        <v>1.36</v>
+        <v>2.14</v>
       </c>
       <c r="DJ116" t="n">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="DK116" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="DL116" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="DM116" t="n">
-        <v>1.19</v>
+        <v>1.55</v>
       </c>
       <c r="DN116" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DO116" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ116" t="b">
         <v>0</v>
@@ -54447,63 +54451,59 @@
         <v>0</v>
       </c>
       <c r="DW116" t="n">
-        <v>8.43</v>
+        <v>14.21</v>
       </c>
       <c r="DX116" t="n">
-        <v>6.4</v>
+        <v>4.28</v>
       </c>
       <c r="DY116" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="DZ116" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="EA116" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="EB116" t="inlineStr">
-        <is>
-          <t>4.02</t>
-        </is>
-      </c>
-      <c r="EC116" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="EA116" t="inlineStr"/>
+      <c r="EB116" t="inlineStr"/>
+      <c r="EC116" t="inlineStr"/>
       <c r="ED116" t="inlineStr"/>
-      <c r="EE116" t="inlineStr"/>
-      <c r="EF116" t="inlineStr"/>
+      <c r="EE116" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EF116" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
       <c r="EG116" t="inlineStr"/>
       <c r="EH116" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="EI116" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EJ116" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="EK116" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EL116" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EM116" t="inlineStr"/>
@@ -54846,7 +54846,7 @@
         <v>72</v>
       </c>
       <c r="DD117" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DE117" t="n">
         <v>1</v>
@@ -54879,7 +54879,7 @@
         <v>2.24</v>
       </c>
       <c r="DO117" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -55343,7 +55343,7 @@
         <v>2.53</v>
       </c>
       <c r="DO118" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -55783,7 +55783,7 @@
         <v>3.04</v>
       </c>
       <c r="DO119" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -56239,7 +56239,7 @@
         <v>3.17</v>
       </c>
       <c r="DO120" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -56694,7 +56694,7 @@
         <v>67</v>
       </c>
       <c r="DD121" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE121" t="n">
         <v>2</v>
@@ -56727,7 +56727,7 @@
         <v>2.71</v>
       </c>
       <c r="DO121" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -57195,7 +57195,7 @@
         <v>2.2</v>
       </c>
       <c r="DO122" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -57627,7 +57627,7 @@
         <v>2.75</v>
       </c>
       <c r="DO123" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP123" t="b">
         <v>0</v>
@@ -58066,10 +58066,10 @@
         <v>67</v>
       </c>
       <c r="DD124" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="DE124" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DF124" t="n">
         <v>2.13</v>
@@ -58099,7 +58099,7 @@
         <v>3.03</v>
       </c>
       <c r="DO124" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -58571,7 +58571,7 @@
         <v>2.42</v>
       </c>
       <c r="DO125" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP125" t="b">
         <v>1</v>
@@ -59035,7 +59035,7 @@
         <v>2.45</v>
       </c>
       <c r="DO126" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP126" t="b">
         <v>1</v>
@@ -59483,7 +59483,7 @@
         <v>2.8</v>
       </c>
       <c r="DO127" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP127" t="b">
         <v>1</v>
@@ -59947,7 +59947,7 @@
         <v>3.17</v>
       </c>
       <c r="DO128" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP128" t="b">
         <v>1</v>
@@ -60411,7 +60411,7 @@
         <v>3.03</v>
       </c>
       <c r="DO129" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP129" t="b">
         <v>1</v>
@@ -60833,7 +60833,7 @@
         <v>0.89</v>
       </c>
       <c r="DE130" t="n">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="DF130" t="n">
         <v>1</v>
@@ -60863,7 +60863,7 @@
         <v>2.37</v>
       </c>
       <c r="DO130" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP130" t="b">
         <v>1</v>
@@ -61323,7 +61323,7 @@
         <v>2.92</v>
       </c>
       <c r="DO131" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP131" t="b">
         <v>1</v>
@@ -61734,7 +61734,7 @@
         <v>71</v>
       </c>
       <c r="DD132" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE132" t="n">
         <v>1</v>
@@ -61767,7 +61767,7 @@
         <v>2.78</v>
       </c>
       <c r="DO132" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP132" t="b">
         <v>1</v>
@@ -62198,10 +62198,10 @@
         <v>76</v>
       </c>
       <c r="DD133" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="DE133" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DF133" t="n">
         <v>2.25</v>
@@ -62231,7 +62231,7 @@
         <v>2.77</v>
       </c>
       <c r="DO133" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP133" t="b">
         <v>1</v>
@@ -62351,170 +62351,170 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F134" s="2" t="n">
         <v>45991.5625</v>
       </c>
       <c r="G134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H134" t="n">
+        <v>1</v>
+      </c>
+      <c r="I134" t="n">
         <v>3</v>
       </c>
-      <c r="I134" t="n">
+      <c r="J134" t="n">
+        <v>7</v>
+      </c>
+      <c r="K134" t="n">
+        <v>8</v>
+      </c>
+      <c r="L134" t="n">
+        <v>15</v>
+      </c>
+      <c r="M134" t="n">
+        <v>3</v>
+      </c>
+      <c r="N134" t="n">
+        <v>2</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>6</v>
+      </c>
+      <c r="R134" t="n">
         <v>4</v>
       </c>
-      <c r="J134" t="n">
-        <v>2</v>
-      </c>
-      <c r="K134" t="n">
-        <v>4</v>
-      </c>
-      <c r="L134" t="n">
-        <v>6</v>
-      </c>
-      <c r="M134" t="n">
-        <v>2</v>
-      </c>
-      <c r="N134" t="n">
-        <v>1</v>
-      </c>
-      <c r="O134" t="n">
-        <v>0</v>
-      </c>
-      <c r="P134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q134" t="n">
-        <v>3</v>
-      </c>
-      <c r="R134" t="n">
-        <v>6</v>
-      </c>
       <c r="S134" t="n">
+        <v>12</v>
+      </c>
+      <c r="T134" t="n">
+        <v>18</v>
+      </c>
+      <c r="U134" t="n">
+        <v>18</v>
+      </c>
+      <c r="V134" t="n">
+        <v>22</v>
+      </c>
+      <c r="W134" t="n">
         <v>8</v>
-      </c>
-      <c r="T134" t="n">
-        <v>10</v>
-      </c>
-      <c r="U134" t="n">
-        <v>11</v>
-      </c>
-      <c r="V134" t="n">
-        <v>16</v>
-      </c>
-      <c r="W134" t="n">
-        <v>16</v>
       </c>
       <c r="X134" t="n">
         <v>13</v>
       </c>
       <c r="Y134" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="Z134" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>Stadion Central’nyj im. I.P. Chayka</t>
+          <t>Akhmat Arena</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>ul. Suvorova, Peschanokopskoye</t>
+          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
         </is>
       </c>
       <c r="AC134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE134" t="n">
-        <v>2.49</v>
+        <v>2.89</v>
       </c>
       <c r="AF134" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="AG134" t="n">
-        <v>2.84</v>
+        <v>2.36</v>
       </c>
       <c r="AH134" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AI134" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AJ134" t="n">
-        <v>3.74</v>
+        <v>3.1</v>
       </c>
       <c r="AK134" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AL134" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="AM134" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AN134" t="n">
-        <v>2.19</v>
+        <v>1.8</v>
       </c>
       <c r="AO134" t="n">
-        <v>2.19</v>
+        <v>2.48</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AQ134" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AR134" t="n">
-        <v>3.09</v>
+        <v>2.62</v>
       </c>
       <c r="AS134" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="AT134" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AU134" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BB134" t="n">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="BC134" t="n">
         <v>0</v>
       </c>
       <c r="BD134" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="BE134" t="n">
         <v>0</v>
@@ -62547,10 +62547,10 @@
         <v>-1</v>
       </c>
       <c r="BO134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ134" t="n">
         <v>2</v>
@@ -62559,7 +62559,7 @@
         <v>1</v>
       </c>
       <c r="BS134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT134" t="n">
         <v>3</v>
@@ -62568,37 +62568,37 @@
         <v>1</v>
       </c>
       <c r="BV134" t="n">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="BW134" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="BX134" t="n">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="BY134" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="BZ134" t="n">
-        <v>1.45</v>
+        <v>1.84</v>
       </c>
       <c r="CA134" t="n">
-        <v>1.71</v>
+        <v>1.98</v>
       </c>
       <c r="CB134" t="n">
-        <v>3.16</v>
+        <v>3.82</v>
       </c>
       <c r="CC134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG134" t="n">
         <v>0</v>
@@ -62616,7 +62616,7 @@
         <v>0</v>
       </c>
       <c r="CL134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM134" t="n">
         <v>-1</v>
@@ -62625,7 +62625,7 @@
         <v>-1</v>
       </c>
       <c r="CO134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP134" t="n">
         <v>0</v>
@@ -62634,76 +62634,76 @@
         <v>1</v>
       </c>
       <c r="CR134" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="CS134" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="CT134" t="n">
         <v>1</v>
       </c>
       <c r="CU134" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CV134" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="CW134" t="n">
         <v>1</v>
       </c>
       <c r="CX134" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CY134" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CZ134" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="DA134" t="n">
         <v>72</v>
       </c>
       <c r="DB134" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="DC134" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="DD134" t="n">
-        <v>1.13</v>
+        <v>1.78</v>
       </c>
       <c r="DE134" t="n">
-        <v>1.78</v>
+        <v>1</v>
       </c>
       <c r="DF134" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="DG134" t="n">
-        <v>1.63</v>
+        <v>1.14</v>
       </c>
       <c r="DH134" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DI134" t="n">
-        <v>1.94</v>
+        <v>1.25</v>
       </c>
       <c r="DJ134" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DK134" t="n">
         <v>29</v>
       </c>
       <c r="DL134" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="DM134" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="DN134" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="DO134" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP134" t="b">
         <v>1</v>
@@ -62715,7 +62715,7 @@
         <v>1</v>
       </c>
       <c r="DS134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT134" t="b">
         <v>0</v>
@@ -62727,14 +62727,14 @@
         <v>1</v>
       </c>
       <c r="DW134" t="n">
-        <v>3.61</v>
+        <v>10.53</v>
       </c>
       <c r="DX134" t="n">
-        <v>3.88</v>
+        <v>1.66</v>
       </c>
       <c r="DY134" t="inlineStr">
         <is>
-          <t>96%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="DZ134" t="inlineStr">
@@ -62744,17 +62744,17 @@
       </c>
       <c r="EA134" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="EB134" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="EC134" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="ED134" t="inlineStr"/>
@@ -62763,47 +62763,47 @@
       <c r="EG134" t="inlineStr"/>
       <c r="EH134" t="inlineStr">
         <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="EI134" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EJ134" t="inlineStr">
+        <is>
+          <t>3.53</t>
+        </is>
+      </c>
+      <c r="EK134" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EL134" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EM134" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EN134" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EO134" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EP134" t="inlineStr">
+        <is>
           <t>2.54</t>
-        </is>
-      </c>
-      <c r="EI134" t="inlineStr">
-        <is>
-          <t>2.86</t>
-        </is>
-      </c>
-      <c r="EJ134" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="EK134" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="EL134" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="EM134" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="EN134" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="EO134" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EP134" t="inlineStr">
-        <is>
-          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -62823,170 +62823,170 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F135" s="2" t="n">
         <v>45991.5625</v>
       </c>
       <c r="G135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I135" t="n">
+        <v>4</v>
+      </c>
+      <c r="J135" t="n">
+        <v>2</v>
+      </c>
+      <c r="K135" t="n">
+        <v>4</v>
+      </c>
+      <c r="L135" t="n">
+        <v>6</v>
+      </c>
+      <c r="M135" t="n">
+        <v>2</v>
+      </c>
+      <c r="N135" t="n">
+        <v>1</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
         <v>3</v>
       </c>
-      <c r="J135" t="n">
-        <v>7</v>
-      </c>
-      <c r="K135" t="n">
+      <c r="R135" t="n">
+        <v>6</v>
+      </c>
+      <c r="S135" t="n">
         <v>8</v>
       </c>
-      <c r="L135" t="n">
-        <v>15</v>
-      </c>
-      <c r="M135" t="n">
-        <v>3</v>
-      </c>
-      <c r="N135" t="n">
-        <v>2</v>
-      </c>
-      <c r="O135" t="n">
-        <v>0</v>
-      </c>
-      <c r="P135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q135" t="n">
-        <v>6</v>
-      </c>
-      <c r="R135" t="n">
-        <v>4</v>
-      </c>
-      <c r="S135" t="n">
-        <v>12</v>
-      </c>
       <c r="T135" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="U135" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="V135" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="W135" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X135" t="n">
         <v>13</v>
       </c>
       <c r="Y135" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="Z135" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>Akhmat Arena</t>
+          <t>Stadion Central’nyj im. I.P. Chayka</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
+          <t>ul. Suvorova, Peschanokopskoye</t>
         </is>
       </c>
       <c r="AC135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA135" t="n">
         <v>3</v>
       </c>
-      <c r="AD135" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE135" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AF135" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AG135" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AH135" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI135" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ135" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AK135" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AL135" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AM135" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AN135" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AO135" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AP135" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AQ135" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AR135" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AS135" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AT135" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AU135" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW135" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX135" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ135" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA135" t="n">
-        <v>1</v>
-      </c>
       <c r="BB135" t="n">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="BC135" t="n">
         <v>0</v>
       </c>
       <c r="BD135" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="BE135" t="n">
         <v>0</v>
@@ -63019,10 +63019,10 @@
         <v>-1</v>
       </c>
       <c r="BO135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ135" t="n">
         <v>2</v>
@@ -63031,7 +63031,7 @@
         <v>1</v>
       </c>
       <c r="BS135" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT135" t="n">
         <v>3</v>
@@ -63040,37 +63040,37 @@
         <v>1</v>
       </c>
       <c r="BV135" t="n">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="BW135" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="BX135" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="BY135" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="BZ135" t="n">
-        <v>1.84</v>
+        <v>1.45</v>
       </c>
       <c r="CA135" t="n">
-        <v>1.98</v>
+        <v>1.71</v>
       </c>
       <c r="CB135" t="n">
-        <v>3.82</v>
+        <v>3.16</v>
       </c>
       <c r="CC135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG135" t="n">
         <v>0</v>
@@ -63088,7 +63088,7 @@
         <v>0</v>
       </c>
       <c r="CL135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM135" t="n">
         <v>-1</v>
@@ -63097,7 +63097,7 @@
         <v>-1</v>
       </c>
       <c r="CO135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP135" t="n">
         <v>0</v>
@@ -63106,76 +63106,76 @@
         <v>1</v>
       </c>
       <c r="CR135" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="CS135" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="CT135" t="n">
         <v>1</v>
       </c>
       <c r="CU135" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CV135" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="CW135" t="n">
         <v>1</v>
       </c>
       <c r="CX135" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CY135" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CZ135" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="DA135" t="n">
         <v>72</v>
       </c>
       <c r="DB135" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="DC135" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="DD135" t="n">
-        <v>1.78</v>
+        <v>1.33</v>
       </c>
       <c r="DE135" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="DF135" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="DG135" t="n">
-        <v>1.14</v>
+        <v>1.63</v>
       </c>
       <c r="DH135" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="DI135" t="n">
-        <v>1.25</v>
+        <v>1.94</v>
       </c>
       <c r="DJ135" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="DK135" t="n">
         <v>29</v>
       </c>
       <c r="DL135" t="n">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="DM135" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="DN135" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="DO135" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP135" t="b">
         <v>1</v>
@@ -63187,7 +63187,7 @@
         <v>1</v>
       </c>
       <c r="DS135" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT135" t="b">
         <v>0</v>
@@ -63199,14 +63199,14 @@
         <v>1</v>
       </c>
       <c r="DW135" t="n">
-        <v>10.53</v>
+        <v>3.61</v>
       </c>
       <c r="DX135" t="n">
-        <v>1.66</v>
+        <v>3.88</v>
       </c>
       <c r="DY135" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="DZ135" t="inlineStr">
@@ -63216,17 +63216,17 @@
       </c>
       <c r="EA135" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="EB135" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="EC135" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="ED135" t="inlineStr"/>
@@ -63235,47 +63235,47 @@
       <c r="EG135" t="inlineStr"/>
       <c r="EH135" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="EI135" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="EJ135" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="EK135" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EL135" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EM135" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="EN135" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EO135" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EP135" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -63606,10 +63606,10 @@
         <v>79</v>
       </c>
       <c r="DD136" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE136" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DF136" t="n">
         <v>2.71</v>
@@ -63639,7 +63639,7 @@
         <v>3.06</v>
       </c>
       <c r="DO136" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP136" t="b">
         <v>1</v>
@@ -64094,7 +64094,7 @@
         <v>94</v>
       </c>
       <c r="DD137" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DE137" t="n">
         <v>0.33</v>
@@ -64127,7 +64127,7 @@
         <v>2.13</v>
       </c>
       <c r="DO137" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP137" t="b">
         <v>0</v>
@@ -64287,16 +64287,16 @@
         <v>3</v>
       </c>
       <c r="S138" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T138" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U138" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V138" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W138" t="n">
         <v>12</v>
@@ -64453,28 +64453,28 @@
         <v>3</v>
       </c>
       <c r="BU138" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BV138" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BW138" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BX138" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="BY138" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="BZ138" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="CA138" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="CB138" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="CC138" t="n">
         <v>0</v>
@@ -64531,10 +64531,10 @@
         <v>1</v>
       </c>
       <c r="CU138" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="CV138" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CW138" t="n">
         <v>1</v>
@@ -64686,6 +64686,3226 @@
       </c>
       <c r="EO138" t="inlineStr"/>
       <c r="EP138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>18</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Rostov</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>45997.45833333334</v>
+      </c>
+      <c r="G139" t="n">
+        <v>2</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="n">
+        <v>2</v>
+      </c>
+      <c r="J139" t="n">
+        <v>8</v>
+      </c>
+      <c r="K139" t="n">
+        <v>3</v>
+      </c>
+      <c r="L139" t="n">
+        <v>11</v>
+      </c>
+      <c r="M139" t="n">
+        <v>2</v>
+      </c>
+      <c r="N139" t="n">
+        <v>4</v>
+      </c>
+      <c r="O139" t="n">
+        <v>1</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>2</v>
+      </c>
+      <c r="R139" t="n">
+        <v>1</v>
+      </c>
+      <c r="S139" t="n">
+        <v>16</v>
+      </c>
+      <c r="T139" t="n">
+        <v>8</v>
+      </c>
+      <c r="U139" t="n">
+        <v>18</v>
+      </c>
+      <c r="V139" t="n">
+        <v>9</v>
+      </c>
+      <c r="W139" t="n">
+        <v>17</v>
+      </c>
+      <c r="X139" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>Stadion Central’nyj im. I.P. Chayka</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>ul. Suvorova, Peschanokopskoye</t>
+        </is>
+      </c>
+      <c r="AC139" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>71</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>61</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>23</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>106</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>71</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU139" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV139" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX139" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY139" t="n">
+        <v>17</v>
+      </c>
+      <c r="CZ139" t="n">
+        <v>32</v>
+      </c>
+      <c r="DA139" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB139" t="n">
+        <v>19</v>
+      </c>
+      <c r="DC139" t="n">
+        <v>63</v>
+      </c>
+      <c r="DD139" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DE139" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DF139" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DG139" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DH139" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DI139" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DJ139" t="n">
+        <v>69</v>
+      </c>
+      <c r="DK139" t="n">
+        <v>50</v>
+      </c>
+      <c r="DL139" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DM139" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DN139" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="DO139" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP139" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ139" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW139" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DX139" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="DY139" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="DZ139" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA139" t="inlineStr"/>
+      <c r="EB139" t="inlineStr"/>
+      <c r="EC139" t="inlineStr"/>
+      <c r="ED139" t="inlineStr"/>
+      <c r="EE139" t="inlineStr"/>
+      <c r="EF139" t="inlineStr"/>
+      <c r="EG139" t="inlineStr"/>
+      <c r="EH139" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EI139" t="inlineStr">
+        <is>
+          <t>3.87</t>
+        </is>
+      </c>
+      <c r="EJ139" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="EK139" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EL139" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EM139" t="inlineStr"/>
+      <c r="EN139" t="inlineStr"/>
+      <c r="EO139" t="inlineStr"/>
+      <c r="EP139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>18</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Spartak Moskva</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Dinamo Moskva</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>45997.57291666666</v>
+      </c>
+      <c r="G140" t="n">
+        <v>1</v>
+      </c>
+      <c r="H140" t="n">
+        <v>1</v>
+      </c>
+      <c r="I140" t="n">
+        <v>2</v>
+      </c>
+      <c r="J140" t="n">
+        <v>5</v>
+      </c>
+      <c r="K140" t="n">
+        <v>2</v>
+      </c>
+      <c r="L140" t="n">
+        <v>7</v>
+      </c>
+      <c r="M140" t="n">
+        <v>2</v>
+      </c>
+      <c r="N140" t="n">
+        <v>3</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>1</v>
+      </c>
+      <c r="R140" t="n">
+        <v>4</v>
+      </c>
+      <c r="S140" t="n">
+        <v>7</v>
+      </c>
+      <c r="T140" t="n">
+        <v>6</v>
+      </c>
+      <c r="U140" t="n">
+        <v>8</v>
+      </c>
+      <c r="V140" t="n">
+        <v>10</v>
+      </c>
+      <c r="W140" t="n">
+        <v>19</v>
+      </c>
+      <c r="X140" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>Otkrytiye Arena</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>Volokolamskoye shosse, Tushino, Moskva</t>
+        </is>
+      </c>
+      <c r="AC140" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>54</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>43</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>91</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>76</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>30</v>
+      </c>
+      <c r="CT140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU140" t="n">
+        <v>24</v>
+      </c>
+      <c r="CV140" t="n">
+        <v>26</v>
+      </c>
+      <c r="CW140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX140" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY140" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ140" t="n">
+        <v>53</v>
+      </c>
+      <c r="DA140" t="n">
+        <v>65</v>
+      </c>
+      <c r="DB140" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC140" t="n">
+        <v>59</v>
+      </c>
+      <c r="DD140" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="DE140" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF140" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DG140" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH140" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="DI140" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DJ140" t="n">
+        <v>47</v>
+      </c>
+      <c r="DK140" t="n">
+        <v>36</v>
+      </c>
+      <c r="DL140" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="DM140" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="DN140" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="DO140" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP140" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ140" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR140" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS140" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT140" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU140" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV140" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW140" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DX140" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="DY140" t="inlineStr">
+        <is>
+          <t>87%</t>
+        </is>
+      </c>
+      <c r="DZ140" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA140" t="inlineStr"/>
+      <c r="EB140" t="inlineStr"/>
+      <c r="EC140" t="inlineStr"/>
+      <c r="ED140" t="inlineStr"/>
+      <c r="EE140" t="inlineStr"/>
+      <c r="EF140" t="inlineStr"/>
+      <c r="EG140" t="inlineStr"/>
+      <c r="EH140" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EI140" t="inlineStr">
+        <is>
+          <t>3.53</t>
+        </is>
+      </c>
+      <c r="EJ140" t="inlineStr">
+        <is>
+          <t>3.64</t>
+        </is>
+      </c>
+      <c r="EK140" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EL140" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EM140" t="inlineStr"/>
+      <c r="EN140" t="inlineStr"/>
+      <c r="EO140" t="inlineStr"/>
+      <c r="EP140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>18</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Zenit</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Akron</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>45997.6875</v>
+      </c>
+      <c r="G141" t="n">
+        <v>2</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" t="n">
+        <v>2</v>
+      </c>
+      <c r="J141" t="n">
+        <v>4</v>
+      </c>
+      <c r="K141" t="n">
+        <v>1</v>
+      </c>
+      <c r="L141" t="n">
+        <v>5</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="n">
+        <v>3</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>6</v>
+      </c>
+      <c r="R141" t="n">
+        <v>4</v>
+      </c>
+      <c r="S141" t="n">
+        <v>9</v>
+      </c>
+      <c r="T141" t="n">
+        <v>2</v>
+      </c>
+      <c r="U141" t="n">
+        <v>15</v>
+      </c>
+      <c r="V141" t="n">
+        <v>6</v>
+      </c>
+      <c r="W141" t="n">
+        <v>6</v>
+      </c>
+      <c r="X141" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>71</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA141" t="inlineStr"/>
+      <c r="AB141" t="inlineStr"/>
+      <c r="AC141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>921</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>57</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>38</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>89</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>76</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU141" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV141" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX141" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY141" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ141" t="n">
+        <v>57</v>
+      </c>
+      <c r="DA141" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB141" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC141" t="n">
+        <v>69</v>
+      </c>
+      <c r="DD141" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="DE141" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DF141" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DG141" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DH141" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="DI141" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="DJ141" t="n">
+        <v>44</v>
+      </c>
+      <c r="DK141" t="n">
+        <v>19</v>
+      </c>
+      <c r="DL141" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DM141" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DN141" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="DO141" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP141" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ141" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR141" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS141" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT141" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU141" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV141" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW141" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="DX141" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="DY141" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="DZ141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA141" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EB141" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="EC141" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="ED141" t="inlineStr"/>
+      <c r="EE141" t="inlineStr"/>
+      <c r="EF141" t="inlineStr"/>
+      <c r="EG141" t="inlineStr"/>
+      <c r="EH141" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="EI141" t="inlineStr">
+        <is>
+          <t>12.43</t>
+        </is>
+      </c>
+      <c r="EJ141" t="inlineStr">
+        <is>
+          <t>6.35</t>
+        </is>
+      </c>
+      <c r="EK141" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EL141" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EM141" t="inlineStr"/>
+      <c r="EN141" t="inlineStr"/>
+      <c r="EO141" t="inlineStr"/>
+      <c r="EP141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>18</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Makhachkala</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Olimpiyets</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>45998.45833333334</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>1</v>
+      </c>
+      <c r="I142" t="n">
+        <v>1</v>
+      </c>
+      <c r="J142" t="n">
+        <v>6</v>
+      </c>
+      <c r="K142" t="n">
+        <v>2</v>
+      </c>
+      <c r="L142" t="n">
+        <v>8</v>
+      </c>
+      <c r="M142" t="n">
+        <v>3</v>
+      </c>
+      <c r="N142" t="n">
+        <v>5</v>
+      </c>
+      <c r="O142" t="n">
+        <v>1</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>1</v>
+      </c>
+      <c r="R142" t="n">
+        <v>3</v>
+      </c>
+      <c r="S142" t="n">
+        <v>9</v>
+      </c>
+      <c r="T142" t="n">
+        <v>6</v>
+      </c>
+      <c r="U142" t="n">
+        <v>10</v>
+      </c>
+      <c r="V142" t="n">
+        <v>9</v>
+      </c>
+      <c r="W142" t="n">
+        <v>15</v>
+      </c>
+      <c r="X142" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>Anzhi-Arena</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>, Kaspiysk</t>
+        </is>
+      </c>
+      <c r="AC142" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1482</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>58</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>39</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>104</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>78</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>33</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU142" t="n">
+        <v>27</v>
+      </c>
+      <c r="CV142" t="n">
+        <v>19</v>
+      </c>
+      <c r="CW142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX142" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY142" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ142" t="n">
+        <v>25</v>
+      </c>
+      <c r="DA142" t="n">
+        <v>69</v>
+      </c>
+      <c r="DB142" t="n">
+        <v>13</v>
+      </c>
+      <c r="DC142" t="n">
+        <v>57</v>
+      </c>
+      <c r="DD142" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DE142" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DF142" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG142" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="DH142" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DI142" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="DJ142" t="n">
+        <v>75</v>
+      </c>
+      <c r="DK142" t="n">
+        <v>32</v>
+      </c>
+      <c r="DL142" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="DM142" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DN142" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="DO142" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP142" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ142" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR142" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS142" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT142" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU142" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV142" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW142" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="DX142" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="DY142" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="DZ142" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="EA142" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="EB142" t="inlineStr">
+        <is>
+          <t>5.33</t>
+        </is>
+      </c>
+      <c r="EC142" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="ED142" t="inlineStr"/>
+      <c r="EE142" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EF142" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="EG142" t="inlineStr"/>
+      <c r="EH142" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EI142" t="inlineStr">
+        <is>
+          <t>4.65</t>
+        </is>
+      </c>
+      <c r="EJ142" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="EK142" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EL142" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EM142" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EN142" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EO142" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EP142" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>18</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>FK Sochi</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Lokomotiv Moskva</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>45998.5625</v>
+      </c>
+      <c r="G143" t="n">
+        <v>2</v>
+      </c>
+      <c r="H143" t="n">
+        <v>4</v>
+      </c>
+      <c r="I143" t="n">
+        <v>6</v>
+      </c>
+      <c r="J143" t="n">
+        <v>6</v>
+      </c>
+      <c r="K143" t="n">
+        <v>1</v>
+      </c>
+      <c r="L143" t="n">
+        <v>7</v>
+      </c>
+      <c r="M143" t="n">
+        <v>1</v>
+      </c>
+      <c r="N143" t="n">
+        <v>1</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>4</v>
+      </c>
+      <c r="R143" t="n">
+        <v>10</v>
+      </c>
+      <c r="S143" t="n">
+        <v>5</v>
+      </c>
+      <c r="T143" t="n">
+        <v>6</v>
+      </c>
+      <c r="U143" t="n">
+        <v>9</v>
+      </c>
+      <c r="V143" t="n">
+        <v>16</v>
+      </c>
+      <c r="W143" t="n">
+        <v>13</v>
+      </c>
+      <c r="X143" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>Olimpiyskiy Stadion Fisht</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>Olimpiyskiy prospekt, Sochi</t>
+        </is>
+      </c>
+      <c r="AC143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>920</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>64</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>31</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>50</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>79</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>103</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>7</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU143" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV143" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX143" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY143" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ143" t="n">
+        <v>47</v>
+      </c>
+      <c r="DA143" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB143" t="n">
+        <v>18</v>
+      </c>
+      <c r="DC143" t="n">
+        <v>83</v>
+      </c>
+      <c r="DD143" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="DE143" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DF143" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DG143" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DH143" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="DI143" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ143" t="n">
+        <v>53</v>
+      </c>
+      <c r="DK143" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL143" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="DM143" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DN143" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="DO143" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP143" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ143" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR143" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS143" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT143" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU143" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV143" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW143" t="n">
+        <v>16.88</v>
+      </c>
+      <c r="DX143" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="DY143" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="DZ143" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA143" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EB143" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="EC143" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="ED143" t="inlineStr"/>
+      <c r="EE143" t="inlineStr"/>
+      <c r="EF143" t="inlineStr"/>
+      <c r="EG143" t="inlineStr"/>
+      <c r="EH143" t="inlineStr">
+        <is>
+          <t>4.84</t>
+        </is>
+      </c>
+      <c r="EI143" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EJ143" t="inlineStr">
+        <is>
+          <t>3.93</t>
+        </is>
+      </c>
+      <c r="EK143" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EL143" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EM143" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EN143" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EO143" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EP143" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>18</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Krasnodar</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>CSKA Moskva</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>45998.66666666666</v>
+      </c>
+      <c r="G144" t="n">
+        <v>3</v>
+      </c>
+      <c r="H144" t="n">
+        <v>2</v>
+      </c>
+      <c r="I144" t="n">
+        <v>5</v>
+      </c>
+      <c r="J144" t="n">
+        <v>9</v>
+      </c>
+      <c r="K144" t="n">
+        <v>5</v>
+      </c>
+      <c r="L144" t="n">
+        <v>14</v>
+      </c>
+      <c r="M144" t="n">
+        <v>2</v>
+      </c>
+      <c r="N144" t="n">
+        <v>3</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>5</v>
+      </c>
+      <c r="R144" t="n">
+        <v>3</v>
+      </c>
+      <c r="S144" t="n">
+        <v>14</v>
+      </c>
+      <c r="T144" t="n">
+        <v>6</v>
+      </c>
+      <c r="U144" t="n">
+        <v>19</v>
+      </c>
+      <c r="V144" t="n">
+        <v>9</v>
+      </c>
+      <c r="W144" t="n">
+        <v>13</v>
+      </c>
+      <c r="X144" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>Stadion FK Krasnodar</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>ul. Vostochno-Kruglikovskaya 126, Krasnodar</t>
+        </is>
+      </c>
+      <c r="AC144" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI144" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AJ144" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AK144" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL144" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AM144" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AO144" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AP144" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ144" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR144" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AS144" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AT144" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AU144" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX144" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ144" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA144" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB144" t="n">
+        <v>926</v>
+      </c>
+      <c r="BC144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD144" t="n">
+        <v>41</v>
+      </c>
+      <c r="BE144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP144" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR144" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS144" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT144" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV144" t="n">
+        <v>52</v>
+      </c>
+      <c r="BW144" t="n">
+        <v>25</v>
+      </c>
+      <c r="BX144" t="n">
+        <v>99</v>
+      </c>
+      <c r="BY144" t="n">
+        <v>76</v>
+      </c>
+      <c r="BZ144" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CA144" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="CB144" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="CC144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR144" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS144" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU144" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV144" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX144" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY144" t="n">
+        <v>17</v>
+      </c>
+      <c r="CZ144" t="n">
+        <v>47</v>
+      </c>
+      <c r="DA144" t="n">
+        <v>64</v>
+      </c>
+      <c r="DB144" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC144" t="n">
+        <v>71</v>
+      </c>
+      <c r="DD144" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DE144" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DF144" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DG144" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DH144" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="DI144" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="DJ144" t="n">
+        <v>54</v>
+      </c>
+      <c r="DK144" t="n">
+        <v>36</v>
+      </c>
+      <c r="DL144" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="DM144" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DN144" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="DO144" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP144" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ144" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR144" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS144" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT144" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU144" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV144" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW144" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="DX144" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="DY144" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="DZ144" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA144" t="inlineStr"/>
+      <c r="EB144" t="inlineStr"/>
+      <c r="EC144" t="inlineStr"/>
+      <c r="ED144" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EE144" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EF144" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="EG144" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
+      <c r="EH144" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EI144" t="inlineStr">
+        <is>
+          <t>5.71</t>
+        </is>
+      </c>
+      <c r="EJ144" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
+      </c>
+      <c r="EK144" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EL144" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EM144" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EN144" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EO144" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EP144" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>18</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Baltika</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Krylya Sovetov</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="n">
+        <v>45998.66666666666</v>
+      </c>
+      <c r="G145" t="n">
+        <v>2</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" t="n">
+        <v>2</v>
+      </c>
+      <c r="J145" t="n">
+        <v>2</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" t="n">
+        <v>2</v>
+      </c>
+      <c r="M145" t="n">
+        <v>1</v>
+      </c>
+      <c r="N145" t="n">
+        <v>3</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>6</v>
+      </c>
+      <c r="R145" t="n">
+        <v>2</v>
+      </c>
+      <c r="S145" t="n">
+        <v>14</v>
+      </c>
+      <c r="T145" t="n">
+        <v>1</v>
+      </c>
+      <c r="U145" t="n">
+        <v>20</v>
+      </c>
+      <c r="V145" t="n">
+        <v>3</v>
+      </c>
+      <c r="W145" t="n">
+        <v>14</v>
+      </c>
+      <c r="X145" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>Complexe Sportif Jean Bianchi 1</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>21 Avenue Marechal Leclerc, Saint-André-les-Vergers</t>
+        </is>
+      </c>
+      <c r="AC145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF145" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI145" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AJ145" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AK145" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL145" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM145" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN145" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO145" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AP145" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ145" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR145" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS145" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT145" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU145" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV145" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA145" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB145" t="n">
+        <v>1493</v>
+      </c>
+      <c r="BC145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD145" t="n">
+        <v>47</v>
+      </c>
+      <c r="BE145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR145" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT145" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV145" t="n">
+        <v>68</v>
+      </c>
+      <c r="BW145" t="n">
+        <v>38</v>
+      </c>
+      <c r="BX145" t="n">
+        <v>81</v>
+      </c>
+      <c r="BY145" t="n">
+        <v>67</v>
+      </c>
+      <c r="BZ145" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="CA145" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="CB145" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="CC145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR145" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS145" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU145" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV145" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX145" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY145" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ145" t="n">
+        <v>35</v>
+      </c>
+      <c r="DA145" t="n">
+        <v>76</v>
+      </c>
+      <c r="DB145" t="n">
+        <v>18</v>
+      </c>
+      <c r="DC145" t="n">
+        <v>76</v>
+      </c>
+      <c r="DD145" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DE145" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF145" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG145" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="DH145" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DI145" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ145" t="n">
+        <v>66</v>
+      </c>
+      <c r="DK145" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL145" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DM145" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DN145" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DO145" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP145" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ145" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR145" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS145" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT145" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU145" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV145" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW145" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="DX145" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="DY145" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="DZ145" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA145" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EB145" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
+      </c>
+      <c r="EC145" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="ED145" t="inlineStr"/>
+      <c r="EE145" t="inlineStr"/>
+      <c r="EF145" t="inlineStr"/>
+      <c r="EG145" t="inlineStr"/>
+      <c r="EH145" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EI145" t="inlineStr">
+        <is>
+          <t>7.60</t>
+        </is>
+      </c>
+      <c r="EJ145" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="EK145" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EL145" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="EM145" t="inlineStr"/>
+      <c r="EN145" t="inlineStr"/>
+      <c r="EO145" t="inlineStr"/>
+      <c r="EP145" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
+++ b/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
@@ -65430,7 +65430,7 @@
         <v>1</v>
       </c>
       <c r="CR140" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CS140" t="n">
         <v>30</v>
@@ -65639,13 +65639,13 @@
         <v>4</v>
       </c>
       <c r="S141" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T141" t="n">
         <v>2</v>
       </c>
       <c r="U141" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V141" t="n">
         <v>6</v>
@@ -65812,13 +65812,13 @@
         <v>76</v>
       </c>
       <c r="BZ141" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="CA141" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="CB141" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="CC141" t="n">
         <v>0</v>
@@ -65866,10 +65866,10 @@
         <v>1</v>
       </c>
       <c r="CR141" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CS141" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CT141" t="n">
         <v>1</v>
@@ -65887,7 +65887,7 @@
         <v>6</v>
       </c>
       <c r="CY141" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CZ141" t="n">
         <v>57</v>
@@ -67033,7 +67033,7 @@
         <v>1</v>
       </c>
       <c r="Q144" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R144" t="n">
         <v>3</v>
@@ -67045,22 +67045,22 @@
         <v>6</v>
       </c>
       <c r="U144" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V144" t="n">
         <v>9</v>
       </c>
       <c r="W144" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X144" t="n">
         <v>14</v>
       </c>
       <c r="Y144" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Z144" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
@@ -67220,13 +67220,13 @@
         <v>76</v>
       </c>
       <c r="BZ144" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="CA144" t="n">
         <v>0.97</v>
       </c>
       <c r="CB144" t="n">
-        <v>2.89</v>
+        <v>2.76</v>
       </c>
       <c r="CC144" t="n">
         <v>0</v>
@@ -67295,7 +67295,7 @@
         <v>5</v>
       </c>
       <c r="CY144" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CZ144" t="n">
         <v>47</v>

--- a/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
+++ b/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
@@ -34864,7 +34864,7 @@
         <v>0</v>
       </c>
       <c r="BF74" t="n">
-        <v>-1</v>
+        <v>6220</v>
       </c>
       <c r="BG74" t="n">
         <v>-1</v>
@@ -35324,7 +35324,7 @@
         <v>0</v>
       </c>
       <c r="BF75" t="n">
-        <v>-1</v>
+        <v>4491</v>
       </c>
       <c r="BG75" t="n">
         <v>-1</v>
@@ -36264,7 +36264,7 @@
         <v>0</v>
       </c>
       <c r="BF77" t="n">
-        <v>-1</v>
+        <v>26881</v>
       </c>
       <c r="BG77" t="n">
         <v>-1</v>
@@ -36712,7 +36712,7 @@
         <v>0</v>
       </c>
       <c r="BF78" t="n">
-        <v>-1</v>
+        <v>28887</v>
       </c>
       <c r="BG78" t="n">
         <v>-1</v>
@@ -37176,7 +37176,7 @@
         <v>0</v>
       </c>
       <c r="BF79" t="n">
-        <v>-1</v>
+        <v>14458</v>
       </c>
       <c r="BG79" t="n">
         <v>-1</v>
@@ -37632,7 +37632,7 @@
         <v>0</v>
       </c>
       <c r="BF80" t="n">
-        <v>-1</v>
+        <v>4469</v>
       </c>
       <c r="BG80" t="n">
         <v>-1</v>
@@ -38104,7 +38104,7 @@
         <v>0</v>
       </c>
       <c r="BF81" t="n">
-        <v>-1</v>
+        <v>14336</v>
       </c>
       <c r="BG81" t="n">
         <v>-1</v>
@@ -38540,7 +38540,7 @@
         <v>0</v>
       </c>
       <c r="BF82" t="n">
-        <v>-1</v>
+        <v>4792</v>
       </c>
       <c r="BG82" t="n">
         <v>-1</v>
@@ -38992,7 +38992,7 @@
         <v>0</v>
       </c>
       <c r="BF83" t="n">
-        <v>-1</v>
+        <v>10495</v>
       </c>
       <c r="BG83" t="n">
         <v>-1</v>
@@ -39896,7 +39896,7 @@
         <v>0</v>
       </c>
       <c r="BF85" t="n">
-        <v>-1</v>
+        <v>18820</v>
       </c>
       <c r="BG85" t="n">
         <v>-1</v>
@@ -40372,7 +40372,7 @@
         <v>0</v>
       </c>
       <c r="BF86" t="n">
-        <v>-1</v>
+        <v>4131</v>
       </c>
       <c r="BG86" t="n">
         <v>-1</v>
@@ -40726,13 +40726,13 @@
         <v>6</v>
       </c>
       <c r="T87" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U87" t="n">
         <v>9</v>
       </c>
       <c r="V87" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W87" t="n">
         <v>12</v>
@@ -40844,7 +40844,7 @@
         <v>0</v>
       </c>
       <c r="BF87" t="n">
-        <v>-1</v>
+        <v>3648</v>
       </c>
       <c r="BG87" t="n">
         <v>-1</v>
@@ -40907,10 +40907,10 @@
         <v>1.08</v>
       </c>
       <c r="CA87" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="CB87" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="CC87" t="n">
         <v>0</v>
@@ -41316,7 +41316,7 @@
         <v>0</v>
       </c>
       <c r="BF88" t="n">
-        <v>-1</v>
+        <v>29216</v>
       </c>
       <c r="BG88" t="n">
         <v>-1</v>
@@ -41788,7 +41788,7 @@
         <v>0</v>
       </c>
       <c r="BF89" t="n">
-        <v>-1</v>
+        <v>12187</v>
       </c>
       <c r="BG89" t="n">
         <v>-1</v>
@@ -42252,7 +42252,7 @@
         <v>0</v>
       </c>
       <c r="BF90" t="n">
-        <v>-1</v>
+        <v>6069</v>
       </c>
       <c r="BG90" t="n">
         <v>-1</v>
@@ -42591,28 +42591,28 @@
         <v>1</v>
       </c>
       <c r="S91" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T91" t="n">
         <v>11</v>
       </c>
       <c r="U91" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="V91" t="n">
         <v>12</v>
       </c>
       <c r="W91" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="X91" t="n">
         <v>15</v>
       </c>
       <c r="Y91" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Z91" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
@@ -42712,7 +42712,7 @@
         <v>0</v>
       </c>
       <c r="BF91" t="n">
-        <v>-1</v>
+        <v>4088</v>
       </c>
       <c r="BG91" t="n">
         <v>-1</v>
@@ -42772,13 +42772,13 @@
         <v>94</v>
       </c>
       <c r="BZ91" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="CA91" t="n">
         <v>1.09</v>
       </c>
       <c r="CB91" t="n">
-        <v>3.85</v>
+        <v>3.91</v>
       </c>
       <c r="CC91" t="n">
         <v>0</v>
@@ -43505,10 +43505,10 @@
         <v>9</v>
       </c>
       <c r="M93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -43526,13 +43526,13 @@
         <v>6</v>
       </c>
       <c r="T93" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U93" t="n">
         <v>7</v>
       </c>
       <c r="V93" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="W93" t="n">
         <v>19</v>
@@ -43557,10 +43557,10 @@
         </is>
       </c>
       <c r="AC93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE93" t="n">
         <v>5</v>
@@ -43677,16 +43677,16 @@
         <v>1</v>
       </c>
       <c r="BQ93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS93" t="n">
         <v>2</v>
       </c>
       <c r="BT93" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BU93" t="n">
         <v>1</v>
@@ -43707,10 +43707,10 @@
         <v>0.86</v>
       </c>
       <c r="CA93" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="CB93" t="n">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="CC93" t="n">
         <v>0</v>
@@ -44014,13 +44014,13 @@
         <v>18</v>
       </c>
       <c r="T94" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U94" t="n">
         <v>25</v>
       </c>
       <c r="V94" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="W94" t="n">
         <v>7</v>
@@ -44124,7 +44124,7 @@
         <v>0</v>
       </c>
       <c r="BF94" t="n">
-        <v>-1</v>
+        <v>21230</v>
       </c>
       <c r="BG94" t="n">
         <v>-1</v>
@@ -44187,10 +44187,10 @@
         <v>2.44</v>
       </c>
       <c r="CA94" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="CB94" t="n">
-        <v>4.03</v>
+        <v>3.96</v>
       </c>
       <c r="CC94" t="n">
         <v>0</v>
@@ -44596,7 +44596,7 @@
         <v>0</v>
       </c>
       <c r="BF95" t="n">
-        <v>-1</v>
+        <v>8273</v>
       </c>
       <c r="BG95" t="n">
         <v>-1</v>
@@ -45504,7 +45504,7 @@
         <v>0</v>
       </c>
       <c r="BF97" t="n">
-        <v>-1</v>
+        <v>10693</v>
       </c>
       <c r="BG97" t="n">
         <v>-1</v>
@@ -45870,7 +45870,7 @@
         <v>16</v>
       </c>
       <c r="X98" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y98" t="n">
         <v>66</v>
@@ -46090,7 +46090,7 @@
         <v>1</v>
       </c>
       <c r="CR98" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="CS98" t="n">
         <v>25</v>
@@ -46759,13 +46759,13 @@
         <v>2</v>
       </c>
       <c r="S100" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T100" t="n">
         <v>5</v>
       </c>
       <c r="U100" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V100" t="n">
         <v>7</v>
@@ -46940,13 +46940,13 @@
         <v>67</v>
       </c>
       <c r="BZ100" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="CA100" t="n">
         <v>0.76</v>
       </c>
       <c r="CB100" t="n">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="CC100" t="n">
         <v>0</v>
@@ -46997,7 +46997,7 @@
         <v>20</v>
       </c>
       <c r="CS100" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CT100" t="n">
         <v>1</v>
@@ -47212,13 +47212,13 @@
         <v>2</v>
       </c>
       <c r="R101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S101" t="n">
         <v>1</v>
       </c>
       <c r="T101" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U101" t="n">
         <v>3</v>
@@ -47230,7 +47230,7 @@
         <v>17</v>
       </c>
       <c r="X101" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y101" t="n">
         <v>35</v>
@@ -47399,10 +47399,10 @@
         <v>0.6</v>
       </c>
       <c r="CA101" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="CB101" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="CC101" t="n">
         <v>0</v>
@@ -47808,7 +47808,7 @@
         <v>0</v>
       </c>
       <c r="BF102" t="n">
-        <v>-1</v>
+        <v>3997</v>
       </c>
       <c r="BG102" t="n">
         <v>-1</v>
@@ -47982,13 +47982,13 @@
         <v>16</v>
       </c>
       <c r="DL102" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="DM102" t="n">
         <v>1.54</v>
       </c>
       <c r="DN102" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="DO102" t="n">
         <v>18</v>
@@ -48125,7 +48125,7 @@
         <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R103" t="n">
         <v>1</v>
@@ -48137,7 +48137,7 @@
         <v>4</v>
       </c>
       <c r="U103" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V103" t="n">
         <v>5</v>
@@ -48244,7 +48244,7 @@
         <v>0</v>
       </c>
       <c r="BF103" t="n">
-        <v>-1</v>
+        <v>43427</v>
       </c>
       <c r="BG103" t="n">
         <v>-1</v>
@@ -48304,13 +48304,13 @@
         <v>73</v>
       </c>
       <c r="BZ103" t="n">
-        <v>2.13</v>
+        <v>2.26</v>
       </c>
       <c r="CA103" t="n">
         <v>0.59</v>
       </c>
       <c r="CB103" t="n">
-        <v>2.72</v>
+        <v>2.85</v>
       </c>
       <c r="CC103" t="n">
         <v>0</v>
@@ -48376,7 +48376,7 @@
         <v>1</v>
       </c>
       <c r="CX103" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CY103" t="n">
         <v>3</v>
@@ -48716,7 +48716,7 @@
         <v>0</v>
       </c>
       <c r="BF104" t="n">
-        <v>-1</v>
+        <v>24784</v>
       </c>
       <c r="BG104" t="n">
         <v>-1</v>
@@ -49036,7 +49036,7 @@
         <v>3</v>
       </c>
       <c r="N105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -49069,10 +49069,10 @@
         <v>12</v>
       </c>
       <c r="Y105" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Z105" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
@@ -49088,7 +49088,7 @@
         <v>3</v>
       </c>
       <c r="AD105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE105" t="n">
         <v>1.57</v>
@@ -49172,7 +49172,7 @@
         <v>0</v>
       </c>
       <c r="BF105" t="n">
-        <v>-1</v>
+        <v>4568</v>
       </c>
       <c r="BG105" t="n">
         <v>-1</v>
@@ -49208,13 +49208,13 @@
         <v>3</v>
       </c>
       <c r="BR105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS105" t="n">
         <v>1</v>
       </c>
       <c r="BT105" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BU105" t="n">
         <v>1</v>
@@ -49286,7 +49286,7 @@
         <v>1</v>
       </c>
       <c r="CR105" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CS105" t="n">
         <v>20</v>
@@ -49802,10 +49802,10 @@
         <v>23</v>
       </c>
       <c r="DL106" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="DM106" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="DN106" t="n">
         <v>2.66</v>
@@ -49962,19 +49962,19 @@
         <v>7</v>
       </c>
       <c r="T107" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U107" t="n">
         <v>13</v>
       </c>
       <c r="V107" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W107" t="n">
         <v>16</v>
       </c>
       <c r="X107" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y107" t="n">
         <v>58</v>
@@ -50080,7 +50080,7 @@
         <v>0</v>
       </c>
       <c r="BF107" t="n">
-        <v>-1</v>
+        <v>3519</v>
       </c>
       <c r="BG107" t="n">
         <v>-1</v>
@@ -50143,10 +50143,10 @@
         <v>1.63</v>
       </c>
       <c r="CA107" t="n">
-        <v>0.65</v>
+        <v>0.52</v>
       </c>
       <c r="CB107" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="CC107" t="n">
         <v>0</v>
@@ -50194,7 +50194,7 @@
         <v>1</v>
       </c>
       <c r="CR107" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CS107" t="n">
         <v>22</v>
@@ -50420,7 +50420,7 @@
         <v>2</v>
       </c>
       <c r="R108" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -50432,7 +50432,7 @@
         <v>7</v>
       </c>
       <c r="V108" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W108" t="n">
         <v>16</v>
@@ -50544,7 +50544,7 @@
         <v>0</v>
       </c>
       <c r="BF108" t="n">
-        <v>-1</v>
+        <v>13245</v>
       </c>
       <c r="BG108" t="n">
         <v>-1</v>
@@ -50607,10 +50607,10 @@
         <v>0.88</v>
       </c>
       <c r="CA108" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="CB108" t="n">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="CC108" t="n">
         <v>0</v>
@@ -50896,7 +50896,7 @@
         <v>2</v>
       </c>
       <c r="N109" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O109" t="n">
         <v>1</v>
@@ -50948,7 +50948,7 @@
         <v>3</v>
       </c>
       <c r="AD109" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE109" t="n">
         <v>1.8</v>
@@ -51032,7 +51032,7 @@
         <v>0</v>
       </c>
       <c r="BF109" t="n">
-        <v>-1</v>
+        <v>7890</v>
       </c>
       <c r="BG109" t="n">
         <v>-1</v>
@@ -51068,13 +51068,13 @@
         <v>1</v>
       </c>
       <c r="BR109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS109" t="n">
         <v>4</v>
       </c>
       <c r="BT109" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BU109" t="n">
         <v>1</v>
@@ -51496,7 +51496,7 @@
         <v>0</v>
       </c>
       <c r="BF110" t="n">
-        <v>-1</v>
+        <v>45133</v>
       </c>
       <c r="BG110" t="n">
         <v>-1</v>
@@ -51670,13 +51670,13 @@
         <v>0</v>
       </c>
       <c r="DL110" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="DM110" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="DN110" t="n">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="DO110" t="n">
         <v>18</v>
@@ -51952,7 +51952,7 @@
         <v>0</v>
       </c>
       <c r="BF111" t="n">
-        <v>-1</v>
+        <v>3135</v>
       </c>
       <c r="BG111" t="n">
         <v>-1</v>
@@ -52284,7 +52284,7 @@
         <v>6</v>
       </c>
       <c r="R112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S112" t="n">
         <v>9</v>
@@ -52296,7 +52296,7 @@
         <v>15</v>
       </c>
       <c r="V112" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W112" t="n">
         <v>19</v>
@@ -52408,7 +52408,7 @@
         <v>0</v>
       </c>
       <c r="BF112" t="n">
-        <v>-1</v>
+        <v>12510</v>
       </c>
       <c r="BG112" t="n">
         <v>-1</v>
@@ -52471,10 +52471,10 @@
         <v>1.75</v>
       </c>
       <c r="CA112" t="n">
-        <v>1.1</v>
+        <v>0.97</v>
       </c>
       <c r="CB112" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="CC112" t="n">
         <v>0</v>
@@ -53231,13 +53231,13 @@
         <v>3</v>
       </c>
       <c r="S114" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T114" t="n">
         <v>2</v>
       </c>
       <c r="U114" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V114" t="n">
         <v>5</v>
@@ -53344,7 +53344,7 @@
         <v>0</v>
       </c>
       <c r="BF114" t="n">
-        <v>-1</v>
+        <v>11017</v>
       </c>
       <c r="BG114" t="n">
         <v>-1</v>
@@ -53404,13 +53404,13 @@
         <v>74</v>
       </c>
       <c r="BZ114" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="CA114" t="n">
         <v>0.75</v>
       </c>
       <c r="CB114" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="CC114" t="n">
         <v>0</v>
@@ -53685,10 +53685,10 @@
         <v>13</v>
       </c>
       <c r="Y115" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Z115" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
@@ -53788,7 +53788,7 @@
         <v>0</v>
       </c>
       <c r="BF115" t="n">
-        <v>-1</v>
+        <v>4922</v>
       </c>
       <c r="BG115" t="n">
         <v>-1</v>
@@ -54421,10 +54421,10 @@
         <v>1.2</v>
       </c>
       <c r="DM116" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="DN116" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="DO116" t="n">
         <v>18</v>
@@ -54590,7 +54590,7 @@
         <v>13</v>
       </c>
       <c r="X117" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y117" t="n">
         <v>46</v>
@@ -55600,7 +55600,7 @@
         <v>0</v>
       </c>
       <c r="BF119" t="n">
-        <v>-1</v>
+        <v>8054</v>
       </c>
       <c r="BG119" t="n">
         <v>-1</v>
@@ -56056,7 +56056,7 @@
         <v>0</v>
       </c>
       <c r="BF120" t="n">
-        <v>-1</v>
+        <v>5087</v>
       </c>
       <c r="BG120" t="n">
         <v>-1</v>
@@ -56544,7 +56544,7 @@
         <v>0</v>
       </c>
       <c r="BF121" t="n">
-        <v>-1</v>
+        <v>19650</v>
       </c>
       <c r="BG121" t="n">
         <v>-1</v>
@@ -56721,10 +56721,10 @@
         <v>1.37</v>
       </c>
       <c r="DM121" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DN121" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="DO121" t="n">
         <v>18</v>
@@ -57323,16 +57323,16 @@
         <v>2</v>
       </c>
       <c r="S123" t="n">
+        <v>8</v>
+      </c>
+      <c r="T123" t="n">
         <v>7</v>
       </c>
-      <c r="T123" t="n">
-        <v>6</v>
-      </c>
       <c r="U123" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V123" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W123" t="n">
         <v>13</v>
@@ -57444,7 +57444,7 @@
         <v>0</v>
       </c>
       <c r="BF123" t="n">
-        <v>-1</v>
+        <v>3345</v>
       </c>
       <c r="BG123" t="n">
         <v>-1</v>
@@ -57504,13 +57504,13 @@
         <v>92</v>
       </c>
       <c r="BZ123" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="CA123" t="n">
-        <v>0.99</v>
+        <v>1.05</v>
       </c>
       <c r="CB123" t="n">
-        <v>2.27</v>
+        <v>2.39</v>
       </c>
       <c r="CC123" t="n">
         <v>0</v>
@@ -57813,10 +57813,10 @@
         <v>14</v>
       </c>
       <c r="Y124" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Z124" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
@@ -57916,7 +57916,7 @@
         <v>0</v>
       </c>
       <c r="BF124" t="n">
-        <v>-1</v>
+        <v>40178</v>
       </c>
       <c r="BG124" t="n">
         <v>-1</v>
@@ -58093,10 +58093,10 @@
         <v>1.54</v>
       </c>
       <c r="DM124" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="DN124" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="DO124" t="n">
         <v>18</v>
@@ -58270,13 +58270,13 @@
         <v>7</v>
       </c>
       <c r="T125" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U125" t="n">
         <v>10</v>
       </c>
       <c r="V125" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W125" t="n">
         <v>14</v>
@@ -58285,10 +58285,10 @@
         <v>13</v>
       </c>
       <c r="Y125" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Z125" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
@@ -58388,7 +58388,7 @@
         <v>0</v>
       </c>
       <c r="BF125" t="n">
-        <v>-1</v>
+        <v>7532</v>
       </c>
       <c r="BG125" t="n">
         <v>-1</v>
@@ -58451,10 +58451,10 @@
         <v>1.18</v>
       </c>
       <c r="CA125" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="CB125" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="CC125" t="n">
         <v>0</v>
@@ -58502,7 +58502,7 @@
         <v>1</v>
       </c>
       <c r="CR125" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CS125" t="n">
         <v>16</v>
@@ -58565,10 +58565,10 @@
         <v>1.17</v>
       </c>
       <c r="DM125" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DN125" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="DO125" t="n">
         <v>18</v>
@@ -58742,13 +58742,13 @@
         <v>0</v>
       </c>
       <c r="T126" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U126" t="n">
         <v>3</v>
       </c>
       <c r="V126" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W126" t="n">
         <v>18</v>
@@ -58852,7 +58852,7 @@
         <v>0</v>
       </c>
       <c r="BF126" t="n">
-        <v>-1</v>
+        <v>6095</v>
       </c>
       <c r="BG126" t="n">
         <v>-1</v>
@@ -58915,10 +58915,10 @@
         <v>0.57</v>
       </c>
       <c r="CA126" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="CB126" t="n">
-        <v>2.49</v>
+        <v>2.42</v>
       </c>
       <c r="CC126" t="n">
         <v>0</v>
@@ -59300,7 +59300,7 @@
         <v>0</v>
       </c>
       <c r="BF127" t="n">
-        <v>-1</v>
+        <v>7876</v>
       </c>
       <c r="BG127" t="n">
         <v>-1</v>
@@ -59474,13 +59474,13 @@
         <v>32</v>
       </c>
       <c r="DL127" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="DM127" t="n">
         <v>1.38</v>
       </c>
       <c r="DN127" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="DO127" t="n">
         <v>18</v>
@@ -59624,13 +59624,13 @@
         <v>3</v>
       </c>
       <c r="J128" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K128" t="n">
         <v>3</v>
       </c>
       <c r="L128" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M128" t="n">
         <v>0</v>
@@ -59645,34 +59645,34 @@
         <v>1</v>
       </c>
       <c r="Q128" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R128" t="n">
         <v>1</v>
       </c>
       <c r="S128" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T128" t="n">
         <v>3</v>
       </c>
       <c r="U128" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="V128" t="n">
         <v>4</v>
       </c>
       <c r="W128" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="X128" t="n">
         <v>10</v>
       </c>
       <c r="Y128" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Z128" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AA128" t="inlineStr"/>
       <c r="AB128" t="inlineStr"/>
@@ -59764,7 +59764,7 @@
         <v>0</v>
       </c>
       <c r="BF128" t="n">
-        <v>-1</v>
+        <v>10563</v>
       </c>
       <c r="BG128" t="n">
         <v>-1</v>
@@ -59824,13 +59824,13 @@
         <v>99</v>
       </c>
       <c r="BZ128" t="n">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="CA128" t="n">
         <v>0.7</v>
       </c>
       <c r="CB128" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="CC128" t="n">
         <v>0</v>
@@ -59878,7 +59878,7 @@
         <v>1</v>
       </c>
       <c r="CR128" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="CS128" t="n">
         <v>14</v>
@@ -59899,7 +59899,7 @@
         <v>6</v>
       </c>
       <c r="CY128" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CZ128" t="n">
         <v>45</v>
@@ -59938,13 +59938,13 @@
         <v>21</v>
       </c>
       <c r="DL128" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DM128" t="n">
         <v>1.27</v>
       </c>
       <c r="DN128" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="DO128" t="n">
         <v>18</v>
@@ -60228,7 +60228,7 @@
         <v>0</v>
       </c>
       <c r="BF129" t="n">
-        <v>-1</v>
+        <v>15389</v>
       </c>
       <c r="BG129" t="n">
         <v>-1</v>
@@ -60405,10 +60405,10 @@
         <v>1.76</v>
       </c>
       <c r="DM129" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="DN129" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="DO129" t="n">
         <v>18</v>
@@ -60680,7 +60680,7 @@
         <v>0</v>
       </c>
       <c r="BF130" t="n">
-        <v>-1</v>
+        <v>2583</v>
       </c>
       <c r="BG130" t="n">
         <v>-1</v>
@@ -60857,10 +60857,10 @@
         <v>1.35</v>
       </c>
       <c r="DM130" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="DN130" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="DO130" t="n">
         <v>18</v>
@@ -61140,7 +61140,7 @@
         <v>0</v>
       </c>
       <c r="BF131" t="n">
-        <v>-1</v>
+        <v>9092</v>
       </c>
       <c r="BG131" t="n">
         <v>-1</v>
@@ -61314,13 +61314,13 @@
         <v>27</v>
       </c>
       <c r="DL131" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="DM131" t="n">
         <v>1.22</v>
       </c>
       <c r="DN131" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="DO131" t="n">
         <v>18</v>
@@ -61481,10 +61481,10 @@
         <v>14</v>
       </c>
       <c r="Y132" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z132" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
@@ -62048,7 +62048,7 @@
         <v>0</v>
       </c>
       <c r="BF133" t="n">
-        <v>-1</v>
+        <v>25925</v>
       </c>
       <c r="BG133" t="n">
         <v>-1</v>
@@ -62225,10 +62225,10 @@
         <v>1.84</v>
       </c>
       <c r="DM133" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="DN133" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="DO133" t="n">
         <v>18</v>
@@ -62396,19 +62396,19 @@
         <v>6</v>
       </c>
       <c r="R134" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S134" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T134" t="n">
         <v>18</v>
       </c>
       <c r="U134" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V134" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W134" t="n">
         <v>8</v>
@@ -62520,7 +62520,7 @@
         <v>0</v>
       </c>
       <c r="BF134" t="n">
-        <v>-1</v>
+        <v>4236</v>
       </c>
       <c r="BG134" t="n">
         <v>-1</v>
@@ -62580,13 +62580,13 @@
         <v>85</v>
       </c>
       <c r="BZ134" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="CA134" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="CB134" t="n">
-        <v>3.82</v>
+        <v>3.89</v>
       </c>
       <c r="CC134" t="n">
         <v>1</v>
@@ -62697,10 +62697,10 @@
         <v>1.63</v>
       </c>
       <c r="DM134" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="DN134" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="DO134" t="n">
         <v>18</v>
@@ -62992,7 +62992,7 @@
         <v>0</v>
       </c>
       <c r="BF135" t="n">
-        <v>-1</v>
+        <v>12383</v>
       </c>
       <c r="BG135" t="n">
         <v>-1</v>
@@ -63169,10 +63169,10 @@
         <v>1.45</v>
       </c>
       <c r="DM135" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="DN135" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="DO135" t="n">
         <v>18</v>
@@ -63630,13 +63630,13 @@
         <v>22</v>
       </c>
       <c r="DL136" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="DM136" t="n">
         <v>1.22</v>
       </c>
       <c r="DN136" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="DO136" t="n">
         <v>18</v>
@@ -63944,7 +63944,7 @@
         <v>0</v>
       </c>
       <c r="BF137" t="n">
-        <v>-1</v>
+        <v>2146</v>
       </c>
       <c r="BG137" t="n">
         <v>-1</v>
@@ -64058,7 +64058,7 @@
         <v>1</v>
       </c>
       <c r="CR137" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CS137" t="n">
         <v>21</v>
@@ -64287,16 +64287,16 @@
         <v>3</v>
       </c>
       <c r="S138" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T138" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="U138" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V138" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="W138" t="n">
         <v>12</v>
@@ -64408,7 +64408,7 @@
         <v>0</v>
       </c>
       <c r="BF138" t="n">
-        <v>-1</v>
+        <v>3900</v>
       </c>
       <c r="BG138" t="n">
         <v>-1</v>
@@ -64468,13 +64468,13 @@
         <v>69</v>
       </c>
       <c r="BZ138" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="CA138" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="CB138" t="n">
-        <v>2.52</v>
+        <v>2.65</v>
       </c>
       <c r="CC138" t="n">
         <v>0</v>
@@ -64525,7 +64525,7 @@
         <v>27</v>
       </c>
       <c r="CS138" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CT138" t="n">
         <v>1</v>
@@ -64582,13 +64582,13 @@
         <v>19</v>
       </c>
       <c r="DL138" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DM138" t="n">
         <v>1.3</v>
       </c>
       <c r="DN138" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="DO138" t="n">
         <v>18</v>
@@ -64751,13 +64751,13 @@
         <v>1</v>
       </c>
       <c r="S139" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T139" t="n">
         <v>8</v>
       </c>
       <c r="U139" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V139" t="n">
         <v>9</v>
@@ -64872,7 +64872,7 @@
         <v>0</v>
       </c>
       <c r="BF139" t="n">
-        <v>-1</v>
+        <v>6312</v>
       </c>
       <c r="BG139" t="n">
         <v>-1</v>
@@ -64932,13 +64932,13 @@
         <v>71</v>
       </c>
       <c r="BZ139" t="n">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="CA139" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="CB139" t="n">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="CC139" t="n">
         <v>1</v>
@@ -65198,13 +65198,13 @@
         <v>7</v>
       </c>
       <c r="T140" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U140" t="n">
         <v>8</v>
       </c>
       <c r="V140" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W140" t="n">
         <v>19</v>
@@ -65379,10 +65379,10 @@
         <v>0.92</v>
       </c>
       <c r="CA140" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="CB140" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="CC140" t="n">
         <v>0</v>
@@ -65493,10 +65493,10 @@
         <v>1.48</v>
       </c>
       <c r="DM140" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="DN140" t="n">
-        <v>2.97</v>
+        <v>3.01</v>
       </c>
       <c r="DO140" t="n">
         <v>18</v>
@@ -65926,13 +65926,13 @@
         <v>19</v>
       </c>
       <c r="DL141" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="DM141" t="n">
         <v>1.21</v>
       </c>
       <c r="DN141" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="DO141" t="n">
         <v>18</v>
@@ -66208,7 +66208,7 @@
         <v>0</v>
       </c>
       <c r="BF142" t="n">
-        <v>-1</v>
+        <v>3844</v>
       </c>
       <c r="BG142" t="n">
         <v>-1</v>
@@ -66385,10 +66385,10 @@
         <v>1.24</v>
       </c>
       <c r="DM142" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="DN142" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="DO142" t="n">
         <v>18</v>
@@ -66570,13 +66570,13 @@
         <v>5</v>
       </c>
       <c r="T143" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U143" t="n">
         <v>9</v>
       </c>
       <c r="V143" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W143" t="n">
         <v>13</v>
@@ -66688,7 +66688,7 @@
         <v>0</v>
       </c>
       <c r="BF143" t="n">
-        <v>-1</v>
+        <v>4515</v>
       </c>
       <c r="BG143" t="n">
         <v>-1</v>
@@ -66751,10 +66751,10 @@
         <v>1.08</v>
       </c>
       <c r="CA143" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="CB143" t="n">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="CC143" t="n">
         <v>0</v>
@@ -66865,10 +66865,10 @@
         <v>0.96</v>
       </c>
       <c r="DM143" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="DN143" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="DO143" t="n">
         <v>18</v>
@@ -67337,10 +67337,10 @@
         <v>1.95</v>
       </c>
       <c r="DM144" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="DN144" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="DO144" t="n">
         <v>18</v>
@@ -67813,10 +67813,10 @@
         <v>1.33</v>
       </c>
       <c r="DM145" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="DN145" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="DO145" t="n">
         <v>18</v>

--- a/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
+++ b/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL145" headerRowCount="1">
-  <autoFilter ref="A1:EL145"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL150" headerRowCount="1">
+  <autoFilter ref="A1:EL150"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL145"/>
+  <dimension ref="A1:EL150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.8" customWidth="1" min="1" max="1"/>
@@ -1769,7 +1769,7 @@
         <v>1.33</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -2634,7 +2634,7 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DE4" t="n">
         <v>0.44</v>
@@ -3579,7 +3579,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4010,10 +4010,10 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DE7" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4043,7 +4043,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4441,7 +4441,7 @@
         <v>1.78</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4894,7 +4894,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE9" t="n">
         <v>1.22</v>
@@ -5329,7 +5329,7 @@
         <v>1.5</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5769,7 +5769,7 @@
         <v>2.1</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DF11" t="n">
         <v>3</v>
@@ -6217,7 +6217,7 @@
         <v>1.33</v>
       </c>
       <c r="DE12" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF12" t="n">
         <v>1</v>
@@ -6650,7 +6650,7 @@
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="DE13" t="n">
         <v>1.9</v>
@@ -6683,7 +6683,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7117,7 +7117,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -8014,7 +8014,7 @@
         <v>50</v>
       </c>
       <c r="DD16" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE16" t="n">
         <v>0.33</v>
@@ -8047,7 +8047,7 @@
         <v>1.72</v>
       </c>
       <c r="DO16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8503,7 +8503,7 @@
         <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9366,7 +9366,7 @@
         <v>50</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="DE19" t="n">
         <v>1</v>
@@ -9839,7 +9839,7 @@
         <v>2.42</v>
       </c>
       <c r="DO20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10707,7 +10707,7 @@
         <v>0</v>
       </c>
       <c r="DO22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11118,7 +11118,7 @@
         <v>50</v>
       </c>
       <c r="DD23" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DE23" t="n">
         <v>1.22</v>
@@ -11574,7 +11574,7 @@
         <v>50</v>
       </c>
       <c r="DD24" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE24" t="n">
         <v>0.67</v>
@@ -12474,10 +12474,10 @@
         <v>100</v>
       </c>
       <c r="DD26" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE26" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DF26" t="n">
         <v>3</v>
@@ -12507,7 +12507,7 @@
         <v>1.97</v>
       </c>
       <c r="DO26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -12941,7 +12941,7 @@
         <v>1.5</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DF27" t="n">
         <v>3</v>
@@ -13385,7 +13385,7 @@
         <v>2.78</v>
       </c>
       <c r="DE28" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DF28" t="n">
         <v>3</v>
@@ -13834,7 +13834,7 @@
         <v>0</v>
       </c>
       <c r="DD29" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DE29" t="n">
         <v>1</v>
@@ -14734,7 +14734,7 @@
         <v>50</v>
       </c>
       <c r="DD31" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE31" t="n">
         <v>2</v>
@@ -14767,7 +14767,7 @@
         <v>2.03</v>
       </c>
       <c r="DO31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15629,7 +15629,7 @@
         <v>1.33</v>
       </c>
       <c r="DE33" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DF33" t="n">
         <v>0</v>
@@ -15659,7 +15659,7 @@
         <v>3.03</v>
       </c>
       <c r="DO33" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16087,7 +16087,7 @@
         <v>2.73</v>
       </c>
       <c r="DO34" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17427,7 +17427,7 @@
         <v>2.97</v>
       </c>
       <c r="DO37" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -17837,7 +17837,7 @@
         <v>1.89</v>
       </c>
       <c r="DE38" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF38" t="n">
         <v>2</v>
@@ -17867,7 +17867,7 @@
         <v>2.06</v>
       </c>
       <c r="DO38" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -18722,7 +18722,7 @@
         <v>50</v>
       </c>
       <c r="DD40" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="DE40" t="n">
         <v>0.44</v>
@@ -19195,7 +19195,7 @@
         <v>2.54</v>
       </c>
       <c r="DO41" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -19610,7 +19610,7 @@
         <v>50</v>
       </c>
       <c r="DD42" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE42" t="n">
         <v>0.67</v>
@@ -20514,7 +20514,7 @@
         <v>84</v>
       </c>
       <c r="DD44" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DE44" t="n">
         <v>0.33</v>
@@ -20547,7 +20547,7 @@
         <v>3.11</v>
       </c>
       <c r="DO44" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -20962,10 +20962,10 @@
         <v>59</v>
       </c>
       <c r="DD45" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DE45" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF45" t="n">
         <v>3</v>
@@ -20995,7 +20995,7 @@
         <v>2.4</v>
       </c>
       <c r="DO45" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -21429,7 +21429,7 @@
         <v>1.33</v>
       </c>
       <c r="DE46" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DF46" t="n">
         <v>1.33</v>
@@ -22317,7 +22317,7 @@
         <v>2.78</v>
       </c>
       <c r="DE48" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DF48" t="n">
         <v>3</v>
@@ -22757,7 +22757,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="DE49" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DF49" t="n">
         <v>0.5</v>
@@ -23210,10 +23210,10 @@
         <v>63</v>
       </c>
       <c r="DD50" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE50" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DF50" t="n">
         <v>0.75</v>
@@ -23243,7 +23243,7 @@
         <v>2.38</v>
       </c>
       <c r="DO50" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -23642,10 +23642,10 @@
         <v>67</v>
       </c>
       <c r="DD51" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DE51" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DF51" t="n">
         <v>2.33</v>
@@ -23675,7 +23675,7 @@
         <v>2.54</v>
       </c>
       <c r="DO51" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -24965,7 +24965,7 @@
         <v>0.89</v>
       </c>
       <c r="DE54" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DF54" t="n">
         <v>0.67</v>
@@ -24995,7 +24995,7 @@
         <v>3.31</v>
       </c>
       <c r="DO54" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -25410,7 +25410,7 @@
         <v>84</v>
       </c>
       <c r="DD55" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DE55" t="n">
         <v>0.5</v>
@@ -26310,7 +26310,7 @@
         <v>75</v>
       </c>
       <c r="DD57" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE57" t="n">
         <v>1</v>
@@ -26799,7 +26799,7 @@
         <v>2.53</v>
       </c>
       <c r="DO58" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -27255,7 +27255,7 @@
         <v>2.96</v>
       </c>
       <c r="DO59" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -27343,37 +27343,37 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
         <v>45913.57291666666</v>
       </c>
       <c r="G60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I60" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K60" t="n">
         <v>5</v>
       </c>
       <c r="L60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
         <v>4</v>
@@ -27385,7 +27385,7 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R60" t="n">
         <v>4</v>
@@ -27394,183 +27394,191 @@
         <v>9</v>
       </c>
       <c r="T60" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="U60" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V60" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W60" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="X60" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y60" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="Z60" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA60" t="inlineStr"/>
-      <c r="AB60" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>Akhmat Arena</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
+        </is>
+      </c>
       <c r="AC60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
         <v>4</v>
       </c>
       <c r="AE60" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="AF60" t="n">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="AG60" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AI60" t="n">
         <v>1.77</v>
       </c>
       <c r="AJ60" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="AK60" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AL60" t="n">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="AM60" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="AN60" t="n">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AO60" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AQ60" t="n">
         <v>1.38</v>
       </c>
       <c r="AR60" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="AS60" t="n">
-        <v>3.07</v>
+        <v>2.88</v>
       </c>
       <c r="AT60" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AU60" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY60" t="n">
         <v>1</v>
       </c>
       <c r="AZ60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD60" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH60" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP60" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR60" t="n">
         <v>3</v>
       </c>
-      <c r="BB60" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BC60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD60" t="n">
-        <v>59</v>
-      </c>
-      <c r="BE60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF60" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BG60" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BH60" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI60" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BJ60" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BK60" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BL60" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BM60" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BN60" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BO60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP60" t="n">
+      <c r="BS60" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT60" t="n">
         <v>3</v>
       </c>
-      <c r="BQ60" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR60" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS60" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT60" t="n">
-        <v>2</v>
-      </c>
       <c r="BU60" t="n">
         <v>1</v>
       </c>
       <c r="BV60" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="BW60" t="n">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="BX60" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="BY60" t="n">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="BZ60" t="n">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="CA60" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="CB60" t="n">
-        <v>2.81</v>
+        <v>3.11</v>
       </c>
       <c r="CC60" t="n">
         <v>0</v>
@@ -27618,19 +27626,19 @@
         <v>1</v>
       </c>
       <c r="CR60" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="CS60" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT60" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU60" t="n">
         <v>17</v>
       </c>
-      <c r="CT60" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU60" t="n">
-        <v>21</v>
-      </c>
       <c r="CV60" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="CW60" t="n">
         <v>1</v>
@@ -27639,52 +27647,52 @@
         <v>4</v>
       </c>
       <c r="CY60" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CZ60" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="DA60" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="DB60" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="DC60" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="DD60" t="n">
-        <v>1.33</v>
+        <v>1.78</v>
       </c>
       <c r="DE60" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="DF60" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="DG60" t="n">
-        <v>1.33</v>
+        <v>2.33</v>
       </c>
       <c r="DH60" t="n">
         <v>1.14</v>
       </c>
       <c r="DI60" t="n">
-        <v>1.57</v>
+        <v>2.14</v>
       </c>
       <c r="DJ60" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="DK60" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="DL60" t="n">
-        <v>1.97</v>
+        <v>1.47</v>
       </c>
       <c r="DM60" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="DN60" t="n">
-        <v>3.31</v>
+        <v>2.92</v>
       </c>
       <c r="DO60" t="n">
         <v>18</v>
@@ -27696,10 +27704,10 @@
         <v>1</v>
       </c>
       <c r="DR60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT60" t="b">
         <v>0</v>
@@ -27712,17 +27720,17 @@
       </c>
       <c r="DW60" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="DX60" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="DY60" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="DZ60" t="inlineStr"/>
@@ -27731,49 +27739,41 @@
       <c r="EC60" t="inlineStr"/>
       <c r="ED60" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="EE60" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="EF60" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="EG60" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="EH60" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EI60" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EJ60" t="inlineStr">
         <is>
-          <t>1.99</t>
-        </is>
-      </c>
-      <c r="EK60" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EL60" t="inlineStr">
-        <is>
-          <t>2.58</t>
-        </is>
-      </c>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EK60" t="inlineStr"/>
+      <c r="EL60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -27791,37 +27791,37 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F61" s="2" t="n">
         <v>45913.57291666666</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K61" t="n">
         <v>5</v>
       </c>
       <c r="L61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N61" t="n">
         <v>4</v>
@@ -27833,7 +27833,7 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R61" t="n">
         <v>4</v>
@@ -27842,110 +27842,102 @@
         <v>9</v>
       </c>
       <c r="T61" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="U61" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V61" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="W61" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="X61" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y61" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="Z61" t="n">
-        <v>62</v>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>Akhmat Arena</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
-        </is>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD61" t="n">
         <v>4</v>
       </c>
       <c r="AE61" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="AF61" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="AG61" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AI61" t="n">
         <v>1.77</v>
       </c>
       <c r="AJ61" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="AK61" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AL61" t="n">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="AM61" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="AN61" t="n">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AO61" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AQ61" t="n">
         <v>1.38</v>
       </c>
       <c r="AR61" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="AS61" t="n">
-        <v>2.88</v>
+        <v>3.07</v>
       </c>
       <c r="AT61" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AU61" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY61" t="n">
         <v>1</v>
       </c>
       <c r="AZ61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB61" t="n">
         <v>-1</v>
@@ -27954,7 +27946,7 @@
         <v>0</v>
       </c>
       <c r="BD61" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="BE61" t="n">
         <v>0</v>
@@ -27990,43 +27982,43 @@
         <v>0</v>
       </c>
       <c r="BP61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BQ61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR61" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS61" t="n">
         <v>3</v>
       </c>
-      <c r="BS61" t="n">
-        <v>1</v>
-      </c>
       <c r="BT61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BU61" t="n">
         <v>1</v>
       </c>
       <c r="BV61" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="BW61" t="n">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="BX61" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="BY61" t="n">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="BZ61" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="CA61" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="CB61" t="n">
-        <v>3.11</v>
+        <v>2.81</v>
       </c>
       <c r="CC61" t="n">
         <v>0</v>
@@ -28074,19 +28066,19 @@
         <v>1</v>
       </c>
       <c r="CR61" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="CS61" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CT61" t="n">
         <v>1</v>
       </c>
       <c r="CU61" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="CV61" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="CW61" t="n">
         <v>1</v>
@@ -28095,52 +28087,52 @@
         <v>4</v>
       </c>
       <c r="CY61" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CZ61" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="DA61" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="DB61" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="DC61" t="n">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.78</v>
+        <v>1.33</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="DF61" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DG61" t="n">
-        <v>2.33</v>
+        <v>1.33</v>
       </c>
       <c r="DH61" t="n">
         <v>1.14</v>
       </c>
       <c r="DI61" t="n">
-        <v>2.14</v>
+        <v>1.57</v>
       </c>
       <c r="DJ61" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="DK61" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="DL61" t="n">
-        <v>1.47</v>
+        <v>1.97</v>
       </c>
       <c r="DM61" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="DN61" t="n">
-        <v>2.92</v>
+        <v>3.31</v>
       </c>
       <c r="DO61" t="n">
         <v>18</v>
@@ -28152,10 +28144,10 @@
         <v>1</v>
       </c>
       <c r="DR61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT61" t="b">
         <v>0</v>
@@ -28168,17 +28160,17 @@
       </c>
       <c r="DW61" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="DX61" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="DY61" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="DZ61" t="inlineStr"/>
@@ -28187,41 +28179,49 @@
       <c r="EC61" t="inlineStr"/>
       <c r="ED61" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="EE61" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="EF61" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EG61" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="EH61" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="EI61" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EJ61" t="inlineStr">
         <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="EK61" t="inlineStr"/>
-      <c r="EL61" t="inlineStr"/>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EK61" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EL61" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -28558,10 +28558,10 @@
         <v>67</v>
       </c>
       <c r="DD62" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="DE62" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DF62" t="n">
         <v>2</v>
@@ -28591,7 +28591,7 @@
         <v>3.61</v>
       </c>
       <c r="DO62" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -29467,7 +29467,7 @@
         <v>2.75</v>
       </c>
       <c r="DO64" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP64" t="b">
         <v>0</v>
@@ -30785,7 +30785,7 @@
         <v>0.89</v>
       </c>
       <c r="DE67" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DF67" t="n">
         <v>0.5</v>
@@ -30815,7 +30815,7 @@
         <v>3</v>
       </c>
       <c r="DO67" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -31238,7 +31238,7 @@
         <v>71</v>
       </c>
       <c r="DD68" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE68" t="n">
         <v>1.9</v>
@@ -31271,7 +31271,7 @@
         <v>2.38</v>
       </c>
       <c r="DO68" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -31694,7 +31694,7 @@
         <v>37</v>
       </c>
       <c r="DD69" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE69" t="n">
         <v>1</v>
@@ -32569,7 +32569,7 @@
         <v>2.11</v>
       </c>
       <c r="DE71" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF71" t="n">
         <v>1.67</v>
@@ -32599,7 +32599,7 @@
         <v>2.46</v>
       </c>
       <c r="DO71" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP71" t="b">
         <v>0</v>
@@ -33022,7 +33022,7 @@
         <v>63</v>
       </c>
       <c r="DD72" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="DE72" t="n">
         <v>1.56</v>
@@ -33055,7 +33055,7 @@
         <v>3.42</v>
       </c>
       <c r="DO72" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -34401,7 +34401,7 @@
         <v>1.78</v>
       </c>
       <c r="DE75" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DF75" t="n">
         <v>1.75</v>
@@ -34834,10 +34834,10 @@
         <v>88</v>
       </c>
       <c r="DD76" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DE76" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DF76" t="n">
         <v>2</v>
@@ -34867,7 +34867,7 @@
         <v>3.09</v>
       </c>
       <c r="DO76" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -35339,7 +35339,7 @@
         <v>2.97</v>
       </c>
       <c r="DO77" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP77" t="b">
         <v>0</v>
@@ -35738,7 +35738,7 @@
         <v>88</v>
       </c>
       <c r="DD78" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DE78" t="n">
         <v>0.44</v>
@@ -35771,7 +35771,7 @@
         <v>3.2</v>
       </c>
       <c r="DO78" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -36189,7 +36189,7 @@
         <v>2.78</v>
       </c>
       <c r="DE79" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DF79" t="n">
         <v>2.5</v>
@@ -36626,7 +36626,7 @@
         <v>45</v>
       </c>
       <c r="DD80" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE80" t="n">
         <v>0.44</v>
@@ -37085,7 +37085,7 @@
         <v>2.1</v>
       </c>
       <c r="DE81" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DF81" t="n">
         <v>2</v>
@@ -37535,7 +37535,7 @@
         <v>2.79</v>
       </c>
       <c r="DO82" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -38390,7 +38390,7 @@
         <v>70</v>
       </c>
       <c r="DD84" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="DE84" t="n">
         <v>0.67</v>
@@ -39282,10 +39282,10 @@
         <v>47</v>
       </c>
       <c r="DD86" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE86" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF86" t="n">
         <v>0.67</v>
@@ -39315,7 +39315,7 @@
         <v>2.29</v>
       </c>
       <c r="DO86" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -39741,7 +39741,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="DE87" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DF87" t="n">
         <v>0.25</v>
@@ -40683,7 +40683,7 @@
         <v>2.67</v>
       </c>
       <c r="DO89" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -40787,168 +40787,176 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
         <v>45948.41666666666</v>
       </c>
       <c r="G90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
         <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K90" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L90" t="n">
+        <v>9</v>
+      </c>
+      <c r="M90" t="n">
+        <v>2</v>
+      </c>
+      <c r="N90" t="n">
+        <v>2</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
         <v>11</v>
       </c>
-      <c r="M90" t="n">
-        <v>1</v>
-      </c>
-      <c r="N90" t="n">
-        <v>2</v>
-      </c>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>3</v>
-      </c>
       <c r="R90" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T90" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="U90" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="V90" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W90" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="X90" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Y90" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="Z90" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA90" t="inlineStr"/>
-      <c r="AB90" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>Stadion Nizhny Novgorod</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>ul. Dolzhanskaya, Nizhniy Novgorod</t>
+        </is>
+      </c>
       <c r="AC90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD90" t="n">
         <v>2</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.9</v>
+        <v>2.29</v>
       </c>
       <c r="AF90" t="n">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="AG90" t="n">
-        <v>3.28</v>
+        <v>2.57</v>
       </c>
       <c r="AH90" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AI90" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AJ90" t="n">
-        <v>3.08</v>
+        <v>2.66</v>
       </c>
       <c r="AK90" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AL90" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="AM90" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AN90" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AO90" t="n">
-        <v>2.62</v>
+        <v>2.16</v>
       </c>
       <c r="AP90" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR90" t="n">
-        <v>2.74</v>
+        <v>2.51</v>
       </c>
       <c r="AS90" t="n">
-        <v>3.04</v>
+        <v>3.32</v>
       </c>
       <c r="AT90" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AU90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV90" t="n">
         <v>0</v>
       </c>
       <c r="AW90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ90" t="n">
         <v>1</v>
       </c>
       <c r="BA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB90" t="n">
-        <v>-1</v>
+        <v>668270</v>
       </c>
       <c r="BC90" t="n">
         <v>0</v>
       </c>
       <c r="BD90" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BE90" t="n">
         <v>0</v>
       </c>
       <c r="BF90" t="n">
-        <v>6069</v>
+        <v>4088</v>
       </c>
       <c r="BG90" t="n">
         <v>-1</v>
@@ -40975,7 +40983,7 @@
         <v>-1</v>
       </c>
       <c r="BO90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP90" t="n">
         <v>0</v>
@@ -40987,7 +40995,7 @@
         <v>2</v>
       </c>
       <c r="BS90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT90" t="n">
         <v>3</v>
@@ -40996,25 +41004,25 @@
         <v>1</v>
       </c>
       <c r="BV90" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="BW90" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="BX90" t="n">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="BY90" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BZ90" t="n">
-        <v>1.44</v>
+        <v>2.82</v>
       </c>
       <c r="CA90" t="n">
-        <v>1.34</v>
+        <v>1.09</v>
       </c>
       <c r="CB90" t="n">
-        <v>2.78</v>
+        <v>3.91</v>
       </c>
       <c r="CC90" t="n">
         <v>0</v>
@@ -41062,82 +41070,82 @@
         <v>1</v>
       </c>
       <c r="CR90" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS90" t="n">
         <v>21</v>
       </c>
-      <c r="CS90" t="n">
-        <v>23</v>
-      </c>
       <c r="CT90" t="n">
         <v>1</v>
       </c>
       <c r="CU90" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="CV90" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CW90" t="n">
         <v>1</v>
       </c>
       <c r="CX90" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="CY90" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="CZ90" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="DA90" t="n">
         <v>100</v>
       </c>
       <c r="DB90" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="DC90" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="DD90" t="n">
-        <v>1.5</v>
+        <v>0.89</v>
       </c>
       <c r="DE90" t="n">
-        <v>0.44</v>
+        <v>1.3</v>
       </c>
       <c r="DF90" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="DG90" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="DH90" t="n">
-        <v>1.09</v>
+        <v>0.55</v>
       </c>
       <c r="DI90" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="DJ90" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="DK90" t="n">
         <v>0</v>
       </c>
       <c r="DL90" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DM90" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="DN90" t="n">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="DO90" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
       </c>
       <c r="DQ90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR90" t="b">
         <v>0</v>
@@ -41152,66 +41160,66 @@
         <v>0</v>
       </c>
       <c r="DV90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW90" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="DX90" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="DY90" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="DZ90" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EA90" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EB90" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="EC90" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="ED90" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="EE90" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="EF90" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="EG90" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EH90" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="EI90" t="inlineStr"/>
@@ -41235,176 +41243,168 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F91" s="2" t="n">
         <v>45948.41666666666</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91" t="n">
         <v>1</v>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J91" t="n">
+        <v>5</v>
+      </c>
+      <c r="K91" t="n">
         <v>6</v>
       </c>
-      <c r="K91" t="n">
+      <c r="L91" t="n">
+        <v>11</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1</v>
+      </c>
+      <c r="N91" t="n">
+        <v>2</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
         <v>3</v>
       </c>
-      <c r="L91" t="n">
-        <v>9</v>
-      </c>
-      <c r="M91" t="n">
-        <v>2</v>
-      </c>
-      <c r="N91" t="n">
-        <v>2</v>
-      </c>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>11</v>
-      </c>
       <c r="R91" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T91" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="U91" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="V91" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W91" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="X91" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Y91" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="Z91" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>Stadion Nizhny Novgorod</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>ul. Dolzhanskaya, Nizhniy Novgorod</t>
-        </is>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="AA91" t="inlineStr"/>
+      <c r="AB91" t="inlineStr"/>
       <c r="AC91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD91" t="n">
         <v>2</v>
       </c>
       <c r="AE91" t="n">
-        <v>2.29</v>
+        <v>1.9</v>
       </c>
       <c r="AF91" t="n">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
       <c r="AG91" t="n">
-        <v>2.57</v>
+        <v>3.28</v>
       </c>
       <c r="AH91" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AI91" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AJ91" t="n">
-        <v>2.66</v>
+        <v>3.08</v>
       </c>
       <c r="AK91" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="AL91" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="AM91" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AN91" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AO91" t="n">
-        <v>2.16</v>
+        <v>2.62</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AR91" t="n">
-        <v>2.51</v>
+        <v>2.74</v>
       </c>
       <c r="AS91" t="n">
-        <v>3.32</v>
+        <v>3.04</v>
       </c>
       <c r="AT91" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AU91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV91" t="n">
         <v>0</v>
       </c>
       <c r="AW91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ91" t="n">
         <v>1</v>
       </c>
       <c r="BA91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB91" t="n">
-        <v>668270</v>
+        <v>-1</v>
       </c>
       <c r="BC91" t="n">
         <v>0</v>
       </c>
       <c r="BD91" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BE91" t="n">
         <v>0</v>
       </c>
       <c r="BF91" t="n">
-        <v>4088</v>
+        <v>6069</v>
       </c>
       <c r="BG91" t="n">
         <v>-1</v>
@@ -41431,7 +41431,7 @@
         <v>-1</v>
       </c>
       <c r="BO91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP91" t="n">
         <v>0</v>
@@ -41443,7 +41443,7 @@
         <v>2</v>
       </c>
       <c r="BS91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT91" t="n">
         <v>3</v>
@@ -41452,25 +41452,25 @@
         <v>1</v>
       </c>
       <c r="BV91" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="BW91" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="BX91" t="n">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="BY91" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="BZ91" t="n">
-        <v>2.82</v>
+        <v>1.44</v>
       </c>
       <c r="CA91" t="n">
-        <v>1.09</v>
+        <v>1.34</v>
       </c>
       <c r="CB91" t="n">
-        <v>3.91</v>
+        <v>2.78</v>
       </c>
       <c r="CC91" t="n">
         <v>0</v>
@@ -41518,73 +41518,73 @@
         <v>1</v>
       </c>
       <c r="CR91" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CS91" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CT91" t="n">
         <v>1</v>
       </c>
       <c r="CU91" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="CV91" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CW91" t="n">
         <v>1</v>
       </c>
       <c r="CX91" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="CY91" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="CZ91" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="DA91" t="n">
         <v>100</v>
       </c>
       <c r="DB91" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="DC91" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="DD91" t="n">
-        <v>0.89</v>
+        <v>1.5</v>
       </c>
       <c r="DE91" t="n">
-        <v>1.44</v>
+        <v>0.44</v>
       </c>
       <c r="DF91" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="DG91" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="DH91" t="n">
-        <v>0.55</v>
+        <v>1.09</v>
       </c>
       <c r="DI91" t="n">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="DJ91" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="DK91" t="n">
         <v>0</v>
       </c>
       <c r="DL91" t="n">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="DM91" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="DN91" t="n">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="DO91" t="n">
         <v>18</v>
@@ -41593,7 +41593,7 @@
         <v>1</v>
       </c>
       <c r="DQ91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR91" t="b">
         <v>0</v>
@@ -41608,66 +41608,66 @@
         <v>0</v>
       </c>
       <c r="DV91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW91" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="DX91" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="DY91" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="DZ91" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EA91" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EB91" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="EC91" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="ED91" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="EE91" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EF91" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="EG91" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="EH91" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EI91" t="inlineStr"/>
@@ -42013,7 +42013,7 @@
         <v>2.1</v>
       </c>
       <c r="DE92" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF92" t="n">
         <v>2.17</v>
@@ -42454,7 +42454,7 @@
         <v>50</v>
       </c>
       <c r="DD93" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE93" t="n">
         <v>2</v>
@@ -42487,7 +42487,7 @@
         <v>2.49</v>
       </c>
       <c r="DO93" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -42918,7 +42918,7 @@
         <v>70</v>
       </c>
       <c r="DD94" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DE94" t="n">
         <v>1.22</v>
@@ -43821,7 +43821,7 @@
         <v>1.89</v>
       </c>
       <c r="DE96" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DF96" t="n">
         <v>2.17</v>
@@ -43851,7 +43851,7 @@
         <v>2.71</v>
       </c>
       <c r="DO96" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -45183,7 +45183,7 @@
         <v>2.84</v>
       </c>
       <c r="DO99" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -46051,7 +46051,7 @@
         <v>2.97</v>
       </c>
       <c r="DO101" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -46477,7 +46477,7 @@
         <v>0.89</v>
       </c>
       <c r="DE102" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DF102" t="n">
         <v>1</v>
@@ -46507,7 +46507,7 @@
         <v>3.07</v>
       </c>
       <c r="DO102" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP102" t="b">
         <v>0</v>
@@ -46894,7 +46894,7 @@
         <v>60</v>
       </c>
       <c r="DD103" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DE103" t="n">
         <v>1</v>
@@ -47350,10 +47350,10 @@
         <v>65</v>
       </c>
       <c r="DD104" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="DE104" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DF104" t="n">
         <v>2</v>
@@ -47383,7 +47383,7 @@
         <v>3.31</v>
       </c>
       <c r="DO104" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -48233,7 +48233,7 @@
         <v>2.78</v>
       </c>
       <c r="DE106" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DF106" t="n">
         <v>2.71</v>
@@ -48666,7 +48666,7 @@
         <v>68</v>
       </c>
       <c r="DD107" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE107" t="n">
         <v>0.5</v>
@@ -49589,7 +49589,7 @@
         <v>1.33</v>
       </c>
       <c r="DE109" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DF109" t="n">
         <v>1.5</v>
@@ -49619,7 +49619,7 @@
         <v>2.81</v>
       </c>
       <c r="DO109" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -50034,7 +50034,7 @@
         <v>77</v>
       </c>
       <c r="DD110" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DE110" t="n">
         <v>1.9</v>
@@ -50067,7 +50067,7 @@
         <v>3.47</v>
       </c>
       <c r="DO110" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -50474,7 +50474,7 @@
         <v>36</v>
       </c>
       <c r="DD111" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE111" t="n">
         <v>0.44</v>
@@ -51370,7 +51370,7 @@
         <v>59</v>
       </c>
       <c r="DD113" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="DE113" t="n">
         <v>1</v>
@@ -51821,7 +51821,7 @@
         <v>1.33</v>
       </c>
       <c r="DE114" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DF114" t="n">
         <v>1.29</v>
@@ -52249,7 +52249,7 @@
         <v>0.89</v>
       </c>
       <c r="DE115" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DF115" t="n">
         <v>1</v>
@@ -52279,7 +52279,7 @@
         <v>2.71</v>
       </c>
       <c r="DO115" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP115" t="b">
         <v>0</v>
@@ -52686,7 +52686,7 @@
         <v>70</v>
       </c>
       <c r="DD116" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE116" t="n">
         <v>1.22</v>
@@ -53125,7 +53125,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="DE117" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF117" t="n">
         <v>0.67</v>
@@ -54006,7 +54006,7 @@
         <v>75</v>
       </c>
       <c r="DD119" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DE119" t="n">
         <v>0.44</v>
@@ -54039,7 +54039,7 @@
         <v>3.04</v>
       </c>
       <c r="DO119" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -54951,7 +54951,7 @@
         <v>2.7</v>
       </c>
       <c r="DO121" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -55798,10 +55798,10 @@
         <v>51</v>
       </c>
       <c r="DD123" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE123" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DF123" t="n">
         <v>0.88</v>
@@ -55831,7 +55831,7 @@
         <v>2.75</v>
       </c>
       <c r="DO123" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP123" t="b">
         <v>0</v>
@@ -57161,7 +57161,7 @@
         <v>1.5</v>
       </c>
       <c r="DE126" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF126" t="n">
         <v>1.29</v>
@@ -57635,7 +57635,7 @@
         <v>2.81</v>
       </c>
       <c r="DO127" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP127" t="b">
         <v>1</v>
@@ -58498,7 +58498,7 @@
         <v>64</v>
       </c>
       <c r="DD129" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DE129" t="n">
         <v>2</v>
@@ -58531,7 +58531,7 @@
         <v>3.02</v>
       </c>
       <c r="DO129" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP129" t="b">
         <v>1</v>
@@ -58937,7 +58937,7 @@
         <v>0.89</v>
       </c>
       <c r="DE130" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DF130" t="n">
         <v>1</v>
@@ -58967,7 +58967,7 @@
         <v>2.38</v>
       </c>
       <c r="DO130" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP130" t="b">
         <v>1</v>
@@ -60266,7 +60266,7 @@
         <v>76</v>
       </c>
       <c r="DD133" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="DE133" t="n">
         <v>0.5</v>
@@ -61211,7 +61211,7 @@
         <v>2.93</v>
       </c>
       <c r="DO135" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP135" t="b">
         <v>1</v>
@@ -61626,10 +61626,10 @@
         <v>79</v>
       </c>
       <c r="DD136" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DE136" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DF136" t="n">
         <v>2.71</v>
@@ -61659,7 +61659,7 @@
         <v>3.08</v>
       </c>
       <c r="DO136" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP136" t="b">
         <v>1</v>
@@ -62997,7 +62997,7 @@
         <v>1.33</v>
       </c>
       <c r="DE139" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DF139" t="n">
         <v>1.13</v>
@@ -63027,7 +63027,7 @@
         <v>2.63</v>
       </c>
       <c r="DO139" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP139" t="b">
         <v>1</v>
@@ -63842,10 +63842,10 @@
         <v>69</v>
       </c>
       <c r="DD141" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DE141" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DF141" t="n">
         <v>2.75</v>
@@ -63875,7 +63875,7 @@
         <v>2.96</v>
       </c>
       <c r="DO141" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP141" t="b">
         <v>1</v>
@@ -64282,10 +64282,10 @@
         <v>57</v>
       </c>
       <c r="DD142" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE142" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DF142" t="n">
         <v>1.5</v>
@@ -64315,7 +64315,7 @@
         <v>2.35</v>
       </c>
       <c r="DO142" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP142" t="b">
         <v>1</v>
@@ -64883,37 +64883,37 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F144" s="2" t="n">
         <v>45998.66666666666</v>
       </c>
       <c r="G144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H144" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J144" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K144" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L144" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="M144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N144" t="n">
         <v>3</v>
@@ -64922,25 +64922,25 @@
         <v>0</v>
       </c>
       <c r="P144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S144" t="n">
         <v>14</v>
       </c>
       <c r="T144" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U144" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V144" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="W144" t="n">
         <v>14</v>
@@ -64949,185 +64949,185 @@
         <v>14</v>
       </c>
       <c r="Y144" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Z144" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>Stadion FK Krasnodar</t>
+          <t>Complexe Sportif Jean Bianchi 1</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>ul. Vostochno-Kruglikovskaya 126, Krasnodar</t>
+          <t>21 Avenue Marechal Leclerc, Saint-André-les-Vergers</t>
         </is>
       </c>
       <c r="AC144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD144" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI144" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AJ144" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AK144" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL144" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM144" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO144" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AP144" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ144" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR144" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS144" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT144" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU144" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV144" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA144" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB144" t="n">
+        <v>1493</v>
+      </c>
+      <c r="BC144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD144" t="n">
+        <v>47</v>
+      </c>
+      <c r="BE144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR144" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT144" t="n">
         <v>4</v>
       </c>
-      <c r="AE144" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AF144" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AG144" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH144" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AI144" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AJ144" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AK144" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AL144" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AM144" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AN144" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AO144" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AP144" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AQ144" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR144" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AS144" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AT144" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AU144" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV144" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW144" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX144" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY144" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ144" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA144" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB144" t="n">
-        <v>926</v>
-      </c>
-      <c r="BC144" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD144" t="n">
-        <v>41</v>
-      </c>
-      <c r="BE144" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF144" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BG144" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BH144" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI144" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BJ144" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BK144" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BL144" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BM144" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BN144" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BO144" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP144" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ144" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR144" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS144" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT144" t="n">
-        <v>3</v>
-      </c>
       <c r="BU144" t="n">
         <v>1</v>
       </c>
       <c r="BV144" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="BW144" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="BX144" t="n">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="BY144" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="BZ144" t="n">
-        <v>1.79</v>
+        <v>2.16</v>
       </c>
       <c r="CA144" t="n">
-        <v>0.97</v>
+        <v>0.61</v>
       </c>
       <c r="CB144" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CC144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD144" t="n">
         <v>0</v>
       </c>
       <c r="CE144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF144" t="n">
         <v>0</v>
@@ -65166,19 +65166,19 @@
         <v>1</v>
       </c>
       <c r="CR144" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="CS144" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="CT144" t="n">
         <v>1</v>
       </c>
       <c r="CU144" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="CV144" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="CW144" t="n">
         <v>1</v>
@@ -65187,52 +65187,52 @@
         <v>5</v>
       </c>
       <c r="CY144" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="CZ144" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="DA144" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="DB144" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="DC144" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="DD144" t="n">
-        <v>2.4</v>
+        <v>2.11</v>
       </c>
       <c r="DE144" t="n">
-        <v>1.22</v>
+        <v>0.5</v>
       </c>
       <c r="DF144" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="DG144" t="n">
-        <v>1.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DH144" t="n">
-        <v>2.18</v>
+        <v>1.88</v>
       </c>
       <c r="DI144" t="n">
-        <v>2.12</v>
+        <v>1</v>
       </c>
       <c r="DJ144" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="DK144" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="DL144" t="n">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="DM144" t="n">
-        <v>1.42</v>
+        <v>0.87</v>
       </c>
       <c r="DN144" t="n">
-        <v>3.37</v>
+        <v>2.2</v>
       </c>
       <c r="DO144" t="n">
         <v>18</v>
@@ -65244,88 +65244,68 @@
         <v>1</v>
       </c>
       <c r="DR144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU144" t="b">
         <v>0</v>
       </c>
       <c r="DV144" t="b">
-        <v>1</v>
-      </c>
-      <c r="DW144" t="inlineStr"/>
-      <c r="DX144" t="inlineStr"/>
-      <c r="DY144" t="inlineStr"/>
-      <c r="DZ144" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="EA144" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="EB144" t="inlineStr">
-        <is>
-          <t>3.19</t>
-        </is>
-      </c>
-      <c r="EC144" t="inlineStr">
-        <is>
-          <t>2.74</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="DW144" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="DX144" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
+      </c>
+      <c r="DY144" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="DZ144" t="inlineStr"/>
+      <c r="EA144" t="inlineStr"/>
+      <c r="EB144" t="inlineStr"/>
+      <c r="EC144" t="inlineStr"/>
       <c r="ED144" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EE144" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>7.60</t>
         </is>
       </c>
       <c r="EF144" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="EG144" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EH144" t="inlineStr">
         <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="EI144" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EJ144" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
-      </c>
-      <c r="EK144" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="EL144" t="inlineStr">
-        <is>
-          <t>2.44</t>
-        </is>
-      </c>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="EI144" t="inlineStr"/>
+      <c r="EJ144" t="inlineStr"/>
+      <c r="EK144" t="inlineStr"/>
+      <c r="EL144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -65343,37 +65323,37 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F145" s="2" t="n">
         <v>45998.66666666666</v>
       </c>
       <c r="G145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I145" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J145" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K145" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L145" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="M145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N145" t="n">
         <v>3</v>
@@ -65382,25 +65362,25 @@
         <v>0</v>
       </c>
       <c r="P145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q145" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S145" t="n">
         <v>14</v>
       </c>
       <c r="T145" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U145" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="V145" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W145" t="n">
         <v>14</v>
@@ -65409,104 +65389,104 @@
         <v>14</v>
       </c>
       <c r="Y145" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Z145" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>Complexe Sportif Jean Bianchi 1</t>
+          <t>Stadion FK Krasnodar</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>21 Avenue Marechal Leclerc, Saint-André-les-Vergers</t>
+          <t>ul. Vostochno-Kruglikovskaya 126, Krasnodar</t>
         </is>
       </c>
       <c r="AC145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD145" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AF145" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI145" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AJ145" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AK145" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL145" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AM145" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN145" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AO145" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AP145" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ145" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR145" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AS145" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AT145" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AU145" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX145" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ145" t="n">
         <v>3</v>
       </c>
-      <c r="AE145" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AF145" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AG145" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AH145" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI145" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AJ145" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AK145" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL145" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AM145" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AN145" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AO145" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AP145" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AQ145" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AR145" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AS145" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT145" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AU145" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV145" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ145" t="n">
-        <v>0</v>
-      </c>
       <c r="BA145" t="n">
         <v>2</v>
       </c>
       <c r="BB145" t="n">
-        <v>1493</v>
+        <v>926</v>
       </c>
       <c r="BC145" t="n">
         <v>0</v>
       </c>
       <c r="BD145" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="BE145" t="n">
         <v>0</v>
@@ -65539,55 +65519,55 @@
         <v>-1</v>
       </c>
       <c r="BO145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ145" t="n">
         <v>1</v>
       </c>
       <c r="BR145" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS145" t="n">
         <v>3</v>
       </c>
-      <c r="BS145" t="n">
-        <v>0</v>
-      </c>
       <c r="BT145" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BU145" t="n">
         <v>1</v>
       </c>
       <c r="BV145" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="BW145" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="BX145" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="BY145" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="BZ145" t="n">
-        <v>2.16</v>
+        <v>1.79</v>
       </c>
       <c r="CA145" t="n">
-        <v>0.61</v>
+        <v>0.97</v>
       </c>
       <c r="CB145" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CC145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD145" t="n">
         <v>0</v>
       </c>
       <c r="CE145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF145" t="n">
         <v>0</v>
@@ -65626,19 +65606,19 @@
         <v>1</v>
       </c>
       <c r="CR145" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="CS145" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="CT145" t="n">
         <v>1</v>
       </c>
       <c r="CU145" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="CV145" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="CW145" t="n">
         <v>1</v>
@@ -65647,52 +65627,52 @@
         <v>5</v>
       </c>
       <c r="CY145" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="CZ145" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="DA145" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="DB145" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="DC145" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="DD145" t="n">
-        <v>2.11</v>
+        <v>2.45</v>
       </c>
       <c r="DE145" t="n">
-        <v>0.5</v>
+        <v>1.22</v>
       </c>
       <c r="DF145" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="DG145" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.38</v>
       </c>
       <c r="DH145" t="n">
-        <v>1.88</v>
+        <v>2.18</v>
       </c>
       <c r="DI145" t="n">
-        <v>1</v>
+        <v>2.12</v>
       </c>
       <c r="DJ145" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="DK145" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="DL145" t="n">
-        <v>1.33</v>
+        <v>1.95</v>
       </c>
       <c r="DM145" t="n">
-        <v>0.87</v>
+        <v>1.42</v>
       </c>
       <c r="DN145" t="n">
-        <v>2.2</v>
+        <v>3.37</v>
       </c>
       <c r="DO145" t="n">
         <v>18</v>
@@ -65704,68 +65684,2356 @@
         <v>1</v>
       </c>
       <c r="DR145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU145" t="b">
         <v>0</v>
       </c>
       <c r="DV145" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW145" t="inlineStr">
-        <is>
-          <t>2.23</t>
-        </is>
-      </c>
-      <c r="DX145" t="inlineStr">
-        <is>
-          <t>4.08</t>
-        </is>
-      </c>
-      <c r="DY145" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="DZ145" t="inlineStr"/>
-      <c r="EA145" t="inlineStr"/>
-      <c r="EB145" t="inlineStr"/>
-      <c r="EC145" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="DW145" t="inlineStr"/>
+      <c r="DX145" t="inlineStr"/>
+      <c r="DY145" t="inlineStr"/>
+      <c r="DZ145" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EA145" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EB145" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="EC145" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
       <c r="ED145" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="EE145" t="inlineStr">
         <is>
-          <t>7.60</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="EF145" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="EG145" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EH145" t="inlineStr">
         <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="EI145" t="inlineStr"/>
-      <c r="EJ145" t="inlineStr"/>
-      <c r="EK145" t="inlineStr"/>
-      <c r="EL145" t="inlineStr"/>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EI145" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EJ145" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EK145" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EL145" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>19</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Zenit</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Baltika</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="n">
+        <v>46080.6875</v>
+      </c>
+      <c r="G146" t="n">
+        <v>1</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" t="n">
+        <v>1</v>
+      </c>
+      <c r="J146" t="n">
+        <v>7</v>
+      </c>
+      <c r="K146" t="n">
+        <v>5</v>
+      </c>
+      <c r="L146" t="n">
+        <v>12</v>
+      </c>
+      <c r="M146" t="n">
+        <v>1</v>
+      </c>
+      <c r="N146" t="n">
+        <v>3</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0</v>
+      </c>
+      <c r="P146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>3</v>
+      </c>
+      <c r="R146" t="n">
+        <v>1</v>
+      </c>
+      <c r="S146" t="n">
+        <v>14</v>
+      </c>
+      <c r="T146" t="n">
+        <v>7</v>
+      </c>
+      <c r="U146" t="n">
+        <v>17</v>
+      </c>
+      <c r="V146" t="n">
+        <v>8</v>
+      </c>
+      <c r="W146" t="n">
+        <v>8</v>
+      </c>
+      <c r="X146" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>63</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>37</v>
+      </c>
+      <c r="AA146" t="inlineStr"/>
+      <c r="AB146" t="inlineStr"/>
+      <c r="AC146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD146" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE146" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF146" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AG146" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AH146" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI146" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AJ146" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AK146" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AL146" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM146" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN146" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AO146" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AP146" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ146" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AR146" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AS146" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AT146" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AU146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ146" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB146" t="n">
+        <v>921</v>
+      </c>
+      <c r="BC146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD146" t="n">
+        <v>33</v>
+      </c>
+      <c r="BE146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF146" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG146" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH146" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI146" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ146" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK146" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL146" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM146" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN146" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP146" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ146" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR146" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS146" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT146" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU146" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV146" t="n">
+        <v>47</v>
+      </c>
+      <c r="BW146" t="n">
+        <v>46</v>
+      </c>
+      <c r="BX146" t="n">
+        <v>100</v>
+      </c>
+      <c r="BY146" t="n">
+        <v>97</v>
+      </c>
+      <c r="BZ146" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CA146" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="CB146" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="CC146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI146" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ146" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM146" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN146" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP146" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ146" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR146" t="n">
+        <v>27</v>
+      </c>
+      <c r="CS146" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT146" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU146" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV146" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW146" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX146" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY146" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ146" t="n">
+        <v>33</v>
+      </c>
+      <c r="DA146" t="n">
+        <v>78</v>
+      </c>
+      <c r="DB146" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC146" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD146" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="DE146" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DF146" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="DG146" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DH146" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DI146" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="DJ146" t="n">
+        <v>67</v>
+      </c>
+      <c r="DK146" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL146" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="DM146" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DN146" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="DO146" t="n">
+        <v>19</v>
+      </c>
+      <c r="DP146" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ146" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR146" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS146" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT146" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU146" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV146" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW146" t="inlineStr"/>
+      <c r="DX146" t="inlineStr"/>
+      <c r="DY146" t="inlineStr"/>
+      <c r="DZ146" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EA146" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EB146" t="inlineStr">
+        <is>
+          <t>2.84</t>
+        </is>
+      </c>
+      <c r="EC146" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="ED146" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EE146" t="inlineStr">
+        <is>
+          <t>6.94</t>
+        </is>
+      </c>
+      <c r="EF146" t="inlineStr">
+        <is>
+          <t>3.93</t>
+        </is>
+      </c>
+      <c r="EG146" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EH146" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EI146" t="inlineStr"/>
+      <c r="EJ146" t="inlineStr"/>
+      <c r="EK146" t="inlineStr"/>
+      <c r="EL146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>19</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Orenburg</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Akron</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="n">
+        <v>46081.375</v>
+      </c>
+      <c r="G147" t="n">
+        <v>2</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" t="n">
+        <v>2</v>
+      </c>
+      <c r="J147" t="n">
+        <v>4</v>
+      </c>
+      <c r="K147" t="n">
+        <v>5</v>
+      </c>
+      <c r="L147" t="n">
+        <v>9</v>
+      </c>
+      <c r="M147" t="n">
+        <v>2</v>
+      </c>
+      <c r="N147" t="n">
+        <v>2</v>
+      </c>
+      <c r="O147" t="n">
+        <v>0</v>
+      </c>
+      <c r="P147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>7</v>
+      </c>
+      <c r="R147" t="n">
+        <v>5</v>
+      </c>
+      <c r="S147" t="n">
+        <v>14</v>
+      </c>
+      <c r="T147" t="n">
+        <v>6</v>
+      </c>
+      <c r="U147" t="n">
+        <v>21</v>
+      </c>
+      <c r="V147" t="n">
+        <v>11</v>
+      </c>
+      <c r="W147" t="n">
+        <v>14</v>
+      </c>
+      <c r="X147" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>Stadion Gazovik</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>Tsvetnoy bulvar' 31, Rostoshi</t>
+        </is>
+      </c>
+      <c r="AC147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI147" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AJ147" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK147" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL147" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AM147" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN147" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AO147" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AP147" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AQ147" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR147" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AS147" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AT147" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ147" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA147" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB147" t="n">
+        <v>922</v>
+      </c>
+      <c r="BC147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD147" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF147" t="n">
+        <v>2888</v>
+      </c>
+      <c r="BG147" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH147" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI147" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ147" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK147" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL147" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM147" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN147" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO147" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP147" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ147" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR147" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS147" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT147" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU147" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV147" t="n">
+        <v>39</v>
+      </c>
+      <c r="BW147" t="n">
+        <v>21</v>
+      </c>
+      <c r="BX147" t="n">
+        <v>90</v>
+      </c>
+      <c r="BY147" t="n">
+        <v>73</v>
+      </c>
+      <c r="BZ147" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CA147" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="CB147" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="CC147" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD147" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE147" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF147" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG147" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH147" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI147" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ147" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK147" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL147" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM147" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN147" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO147" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP147" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ147" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR147" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS147" t="n">
+        <v>12</v>
+      </c>
+      <c r="CT147" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU147" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV147" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW147" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX147" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY147" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ147" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA147" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB147" t="n">
+        <v>39</v>
+      </c>
+      <c r="DC147" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD147" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DE147" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DF147" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DG147" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DH147" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DI147" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DJ147" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK147" t="n">
+        <v>33</v>
+      </c>
+      <c r="DL147" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DM147" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DN147" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="DO147" t="n">
+        <v>19</v>
+      </c>
+      <c r="DP147" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ147" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR147" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS147" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT147" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU147" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV147" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW147" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="DX147" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="DY147" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="DZ147" t="inlineStr"/>
+      <c r="EA147" t="inlineStr"/>
+      <c r="EB147" t="inlineStr"/>
+      <c r="EC147" t="inlineStr"/>
+      <c r="ED147" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EE147" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="EF147" t="inlineStr">
+        <is>
+          <t>3.69</t>
+        </is>
+      </c>
+      <c r="EG147" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="EH147" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EI147" t="inlineStr"/>
+      <c r="EJ147" t="inlineStr"/>
+      <c r="EK147" t="inlineStr"/>
+      <c r="EL147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>19</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Krasnodar</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Rostov</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v>46081.47916666666</v>
+      </c>
+      <c r="G148" t="n">
+        <v>2</v>
+      </c>
+      <c r="H148" t="n">
+        <v>1</v>
+      </c>
+      <c r="I148" t="n">
+        <v>3</v>
+      </c>
+      <c r="J148" t="n">
+        <v>4</v>
+      </c>
+      <c r="K148" t="n">
+        <v>5</v>
+      </c>
+      <c r="L148" t="n">
+        <v>9</v>
+      </c>
+      <c r="M148" t="n">
+        <v>2</v>
+      </c>
+      <c r="N148" t="n">
+        <v>3</v>
+      </c>
+      <c r="O148" t="n">
+        <v>0</v>
+      </c>
+      <c r="P148" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>6</v>
+      </c>
+      <c r="R148" t="n">
+        <v>4</v>
+      </c>
+      <c r="S148" t="n">
+        <v>13</v>
+      </c>
+      <c r="T148" t="n">
+        <v>9</v>
+      </c>
+      <c r="U148" t="n">
+        <v>19</v>
+      </c>
+      <c r="V148" t="n">
+        <v>13</v>
+      </c>
+      <c r="W148" t="n">
+        <v>16</v>
+      </c>
+      <c r="X148" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>Stadion FK Krasnodar</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>ul. Vostochno-Kruglikovskaya 126, Krasnodar</t>
+        </is>
+      </c>
+      <c r="AC148" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD148" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF148" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AG148" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="AH148" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI148" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ148" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AK148" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AL148" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM148" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN148" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AO148" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AP148" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ148" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR148" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AS148" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AT148" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AU148" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ148" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA148" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB148" t="n">
+        <v>926</v>
+      </c>
+      <c r="BC148" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD148" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE148" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF148" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG148" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH148" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI148" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ148" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK148" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL148" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM148" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN148" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO148" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP148" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ148" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR148" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS148" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT148" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU148" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV148" t="n">
+        <v>49</v>
+      </c>
+      <c r="BW148" t="n">
+        <v>38</v>
+      </c>
+      <c r="BX148" t="n">
+        <v>95</v>
+      </c>
+      <c r="BY148" t="n">
+        <v>82</v>
+      </c>
+      <c r="BZ148" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CA148" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CB148" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="CC148" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD148" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE148" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF148" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG148" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH148" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI148" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ148" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK148" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL148" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM148" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN148" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO148" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP148" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ148" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR148" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS148" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT148" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU148" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV148" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW148" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX148" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY148" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ148" t="n">
+        <v>41</v>
+      </c>
+      <c r="DA148" t="n">
+        <v>62</v>
+      </c>
+      <c r="DB148" t="n">
+        <v>26</v>
+      </c>
+      <c r="DC148" t="n">
+        <v>63</v>
+      </c>
+      <c r="DD148" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="DE148" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DF148" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DG148" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH148" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DI148" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DJ148" t="n">
+        <v>59</v>
+      </c>
+      <c r="DK148" t="n">
+        <v>38</v>
+      </c>
+      <c r="DL148" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="DM148" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="DN148" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="DO148" t="n">
+        <v>19</v>
+      </c>
+      <c r="DP148" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ148" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR148" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS148" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT148" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU148" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV148" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW148" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="DX148" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="DY148" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="DZ148" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EA148" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EB148" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="EC148" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="ED148" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EE148" t="inlineStr">
+        <is>
+          <t>5.48</t>
+        </is>
+      </c>
+      <c r="EF148" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="EG148" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EH148" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EI148" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EJ148" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EK148" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EL148" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>19</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Lokomotiv Moskva</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Olimpiyets</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="n">
+        <v>46081.58333333334</v>
+      </c>
+      <c r="G149" t="n">
+        <v>2</v>
+      </c>
+      <c r="H149" t="n">
+        <v>1</v>
+      </c>
+      <c r="I149" t="n">
+        <v>3</v>
+      </c>
+      <c r="J149" t="n">
+        <v>3</v>
+      </c>
+      <c r="K149" t="n">
+        <v>4</v>
+      </c>
+      <c r="L149" t="n">
+        <v>7</v>
+      </c>
+      <c r="M149" t="n">
+        <v>1</v>
+      </c>
+      <c r="N149" t="n">
+        <v>2</v>
+      </c>
+      <c r="O149" t="n">
+        <v>1</v>
+      </c>
+      <c r="P149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>6</v>
+      </c>
+      <c r="R149" t="n">
+        <v>5</v>
+      </c>
+      <c r="S149" t="n">
+        <v>5</v>
+      </c>
+      <c r="T149" t="n">
+        <v>9</v>
+      </c>
+      <c r="U149" t="n">
+        <v>11</v>
+      </c>
+      <c r="V149" t="n">
+        <v>14</v>
+      </c>
+      <c r="W149" t="n">
+        <v>14</v>
+      </c>
+      <c r="X149" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA149" t="inlineStr"/>
+      <c r="AB149" t="inlineStr"/>
+      <c r="AC149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI149" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ149" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AK149" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AL149" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM149" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN149" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO149" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AP149" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ149" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR149" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AS149" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AT149" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AU149" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ149" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA149" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB149" t="n">
+        <v>920</v>
+      </c>
+      <c r="BC149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD149" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF149" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG149" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH149" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI149" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ149" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK149" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL149" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM149" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN149" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO149" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR149" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS149" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT149" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU149" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV149" t="n">
+        <v>48</v>
+      </c>
+      <c r="BW149" t="n">
+        <v>41</v>
+      </c>
+      <c r="BX149" t="n">
+        <v>99</v>
+      </c>
+      <c r="BY149" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ149" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CA149" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CB149" t="n">
+        <v>3</v>
+      </c>
+      <c r="CC149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD149" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF149" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI149" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ149" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM149" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN149" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ149" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR149" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS149" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT149" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU149" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV149" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW149" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX149" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY149" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ149" t="n">
+        <v>54</v>
+      </c>
+      <c r="DA149" t="n">
+        <v>77</v>
+      </c>
+      <c r="DB149" t="n">
+        <v>43</v>
+      </c>
+      <c r="DC149" t="n">
+        <v>65</v>
+      </c>
+      <c r="DD149" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DE149" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DF149" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DG149" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DH149" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="DI149" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DJ149" t="n">
+        <v>47</v>
+      </c>
+      <c r="DK149" t="n">
+        <v>24</v>
+      </c>
+      <c r="DL149" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="DM149" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DN149" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="DO149" t="n">
+        <v>19</v>
+      </c>
+      <c r="DP149" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ149" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR149" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS149" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT149" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU149" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV149" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW149" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="DX149" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="DY149" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="DZ149" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EA149" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EB149" t="inlineStr">
+        <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="EC149" t="inlineStr">
+        <is>
+          <t>2.78</t>
+        </is>
+      </c>
+      <c r="ED149" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EE149" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="EF149" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="EG149" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EH149" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EI149" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EJ149" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EK149" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EL149" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>19</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Makhachkala</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="n">
+        <v>46081.70833333334</v>
+      </c>
+      <c r="G150" t="n">
+        <v>2</v>
+      </c>
+      <c r="H150" t="n">
+        <v>1</v>
+      </c>
+      <c r="I150" t="n">
+        <v>3</v>
+      </c>
+      <c r="J150" t="n">
+        <v>6</v>
+      </c>
+      <c r="K150" t="n">
+        <v>1</v>
+      </c>
+      <c r="L150" t="n">
+        <v>7</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0</v>
+      </c>
+      <c r="N150" t="n">
+        <v>4</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>3</v>
+      </c>
+      <c r="R150" t="n">
+        <v>1</v>
+      </c>
+      <c r="S150" t="n">
+        <v>7</v>
+      </c>
+      <c r="T150" t="n">
+        <v>6</v>
+      </c>
+      <c r="U150" t="n">
+        <v>10</v>
+      </c>
+      <c r="V150" t="n">
+        <v>7</v>
+      </c>
+      <c r="W150" t="n">
+        <v>12</v>
+      </c>
+      <c r="X150" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>Anzhi-Arena</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>, Kaspiysk</t>
+        </is>
+      </c>
+      <c r="AC150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AF150" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AI150" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AJ150" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AK150" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AL150" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AM150" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AN150" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AO150" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AP150" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AQ150" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AR150" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS150" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AT150" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AU150" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ150" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA150" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB150" t="n">
+        <v>668267</v>
+      </c>
+      <c r="BC150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD150" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF150" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG150" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH150" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI150" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ150" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK150" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL150" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM150" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN150" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP150" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR150" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS150" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT150" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU150" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV150" t="n">
+        <v>60</v>
+      </c>
+      <c r="BW150" t="n">
+        <v>26</v>
+      </c>
+      <c r="BX150" t="n">
+        <v>111</v>
+      </c>
+      <c r="BY150" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ150" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="CA150" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="CB150" t="n">
+        <v>2</v>
+      </c>
+      <c r="CC150" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD150" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE150" t="n">
+        <v>2</v>
+      </c>
+      <c r="CF150" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG150" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH150" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI150" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ150" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK150" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL150" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM150" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN150" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO150" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP150" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ150" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR150" t="n">
+        <v>35</v>
+      </c>
+      <c r="CS150" t="n">
+        <v>30</v>
+      </c>
+      <c r="CT150" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU150" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV150" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW150" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX150" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY150" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ150" t="n">
+        <v>17</v>
+      </c>
+      <c r="DA150" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB150" t="n">
+        <v>11</v>
+      </c>
+      <c r="DC150" t="n">
+        <v>56</v>
+      </c>
+      <c r="DD150" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE150" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DF150" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG150" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DH150" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DI150" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DJ150" t="n">
+        <v>84</v>
+      </c>
+      <c r="DK150" t="n">
+        <v>50</v>
+      </c>
+      <c r="DL150" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DM150" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DN150" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="DO150" t="n">
+        <v>19</v>
+      </c>
+      <c r="DP150" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ150" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR150" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS150" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT150" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU150" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV150" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW150" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="DX150" t="inlineStr">
+        <is>
+          <t>7.43</t>
+        </is>
+      </c>
+      <c r="DY150" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="DZ150" t="inlineStr"/>
+      <c r="EA150" t="inlineStr"/>
+      <c r="EB150" t="inlineStr"/>
+      <c r="EC150" t="inlineStr"/>
+      <c r="ED150" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="EE150" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="EF150" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="EG150" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EH150" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="EI150" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="EJ150" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EK150" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EL150" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
+++ b/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL150" headerRowCount="1">
-  <autoFilter ref="A1:EL150"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL153" headerRowCount="1">
+  <autoFilter ref="A1:EL153"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL150"/>
+  <dimension ref="A1:EL153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.8" customWidth="1" min="1" max="1"/>
@@ -1766,7 +1766,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE2" t="n">
         <v>1.6</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2201,7 +2201,7 @@
         <v>0.89</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2667,7 +2667,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -4438,7 +4438,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DE8" t="n">
         <v>0.6</v>
@@ -4471,7 +4471,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -4897,7 +4897,7 @@
         <v>1.1</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -4927,7 +4927,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP9" t="b">
         <v>0</v>
@@ -5359,7 +5359,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5799,7 +5799,7 @@
         <v>2.56</v>
       </c>
       <c r="DO11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6214,7 +6214,7 @@
         <v>100</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE12" t="n">
         <v>0.9</v>
@@ -6247,7 +6247,7 @@
         <v>2.72</v>
       </c>
       <c r="DO12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7114,7 +7114,7 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DE14" t="n">
         <v>1.3</v>
@@ -7147,7 +7147,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7575,7 +7575,7 @@
         <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8913,7 +8913,7 @@
         <v>1.33</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DF18" t="n">
         <v>0</v>
@@ -8943,7 +8943,7 @@
         <v>1.28</v>
       </c>
       <c r="DO18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9047,70 +9047,70 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
         <v>45871.72916666666</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>7</v>
+      </c>
+      <c r="L19" t="n">
+        <v>11</v>
+      </c>
+      <c r="M19" t="n">
         <v>5</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>5</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>4</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>10</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6</v>
+      </c>
+      <c r="S19" t="n">
         <v>3</v>
       </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>5</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
+        <v>8</v>
+      </c>
+      <c r="U19" t="n">
         <v>13</v>
       </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>18</v>
-      </c>
       <c r="V19" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="W19" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="X19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y19" t="n">
         <v>56</v>
@@ -9120,91 +9120,91 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Stadion FK Krasnodar</t>
+          <t>Akhmat Arena</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>ul. Vostochno-Kruglikovskaya 126, Krasnodar</t>
+          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
         </is>
       </c>
       <c r="AC19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD19" t="n">
         <v>4</v>
       </c>
-      <c r="AD19" t="n">
-        <v>3</v>
-      </c>
       <c r="AE19" t="n">
-        <v>1.81</v>
+        <v>5.84</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.54</v>
+        <v>1.65</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB19" t="n">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="BC19" t="n">
         <v>0</v>
@@ -9243,46 +9243,46 @@
         <v>-1</v>
       </c>
       <c r="BO19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ19" t="n">
         <v>3</v>
       </c>
       <c r="BR19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BS19" t="n">
         <v>3</v>
       </c>
       <c r="BT19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BU19" t="n">
         <v>1</v>
       </c>
       <c r="BV19" t="n">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="BW19" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="BX19" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="BY19" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="CA19" t="n">
-        <v>0.45</v>
+        <v>1.54</v>
       </c>
       <c r="CB19" t="n">
-        <v>2.43</v>
+        <v>3.43</v>
       </c>
       <c r="CC19" t="n">
         <v>0</v>
@@ -9324,64 +9324,64 @@
         <v>0</v>
       </c>
       <c r="CP19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ19" t="n">
         <v>1</v>
       </c>
       <c r="CR19" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="CS19" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="CT19" t="n">
         <v>1</v>
       </c>
       <c r="CU19" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="CV19" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="CW19" t="n">
         <v>1</v>
       </c>
       <c r="CX19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="CY19" t="n">
         <v>7</v>
       </c>
       <c r="CZ19" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DA19" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DB19" t="n">
         <v>0</v>
       </c>
       <c r="DC19" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.45</v>
+        <v>0.89</v>
       </c>
       <c r="DE19" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="DF19" t="n">
         <v>0</v>
       </c>
       <c r="DG19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DH19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="DI19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DJ19" t="n">
         <v>0</v>
@@ -9390,82 +9390,62 @@
         <v>0</v>
       </c>
       <c r="DL19" t="n">
-        <v>1.82</v>
+        <v>1.17</v>
       </c>
       <c r="DM19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.82</v>
+        <v>2.42</v>
       </c>
       <c r="DO19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
       </c>
       <c r="DQ19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU19" t="b">
         <v>0</v>
       </c>
       <c r="DV19" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW19" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="DX19" t="inlineStr">
-        <is>
-          <t>2.82</t>
-        </is>
-      </c>
-      <c r="DY19" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="DW19" t="inlineStr"/>
+      <c r="DX19" t="inlineStr"/>
+      <c r="DY19" t="inlineStr"/>
       <c r="DZ19" t="inlineStr"/>
       <c r="EA19" t="inlineStr"/>
       <c r="EB19" t="inlineStr"/>
       <c r="EC19" t="inlineStr"/>
       <c r="ED19" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="EE19" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EF19" t="inlineStr">
         <is>
-          <t>3.69</t>
-        </is>
-      </c>
-      <c r="EG19" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
-      <c r="EH19" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
+          <t>4.32</t>
+        </is>
+      </c>
+      <c r="EG19" t="inlineStr"/>
+      <c r="EH19" t="inlineStr"/>
       <c r="EI19" t="inlineStr"/>
       <c r="EJ19" t="inlineStr"/>
       <c r="EK19" t="inlineStr"/>
@@ -9487,70 +9467,70 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
         <v>45871.72916666666</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>5</v>
+      </c>
+      <c r="M20" t="n">
+        <v>4</v>
+      </c>
+      <c r="N20" t="n">
         <v>3</v>
       </c>
-      <c r="I20" t="n">
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>5</v>
       </c>
-      <c r="J20" t="n">
-        <v>4</v>
-      </c>
-      <c r="K20" t="n">
-        <v>7</v>
-      </c>
-      <c r="L20" t="n">
-        <v>11</v>
-      </c>
-      <c r="M20" t="n">
-        <v>5</v>
-      </c>
-      <c r="N20" t="n">
-        <v>4</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>10</v>
-      </c>
       <c r="R20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
+        <v>13</v>
+      </c>
+      <c r="T20" t="n">
         <v>3</v>
       </c>
-      <c r="T20" t="n">
-        <v>8</v>
-      </c>
       <c r="U20" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="V20" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="W20" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="X20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y20" t="n">
         <v>56</v>
@@ -9560,91 +9540,91 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Akhmat Arena</t>
+          <t>Stadion FK Krasnodar</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
+          <t>ul. Vostochno-Kruglikovskaya 126, Krasnodar</t>
         </is>
       </c>
       <c r="AC20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE20" t="n">
-        <v>5.84</v>
+        <v>1.81</v>
       </c>
       <c r="AF20" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.65</v>
+        <v>3.54</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AU20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AV20" t="n">
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="BC20" t="n">
         <v>0</v>
@@ -9683,46 +9663,46 @@
         <v>-1</v>
       </c>
       <c r="BO20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ20" t="n">
         <v>3</v>
       </c>
       <c r="BR20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BS20" t="n">
         <v>3</v>
       </c>
       <c r="BT20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BU20" t="n">
         <v>1</v>
       </c>
       <c r="BV20" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="BW20" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="BX20" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="BY20" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.54</v>
+        <v>0.45</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.43</v>
+        <v>2.43</v>
       </c>
       <c r="CC20" t="n">
         <v>0</v>
@@ -9764,64 +9744,64 @@
         <v>0</v>
       </c>
       <c r="CP20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ20" t="n">
         <v>1</v>
       </c>
       <c r="CR20" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="CS20" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="CT20" t="n">
         <v>1</v>
       </c>
       <c r="CU20" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="CV20" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="CW20" t="n">
         <v>1</v>
       </c>
       <c r="CX20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CY20" t="n">
         <v>7</v>
       </c>
       <c r="CZ20" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DA20" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DB20" t="n">
         <v>0</v>
       </c>
       <c r="DC20" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DD20" t="n">
-        <v>0.89</v>
+        <v>2.45</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="DF20" t="n">
         <v>0</v>
       </c>
       <c r="DG20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DH20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="DI20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DJ20" t="n">
         <v>0</v>
@@ -9830,13 +9810,13 @@
         <v>0</v>
       </c>
       <c r="DL20" t="n">
-        <v>1.17</v>
+        <v>1.82</v>
       </c>
       <c r="DM20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="DN20" t="n">
-        <v>2.42</v>
+        <v>1.82</v>
       </c>
       <c r="DO20" t="n">
         <v>19</v>
@@ -9845,47 +9825,67 @@
         <v>1</v>
       </c>
       <c r="DQ20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU20" t="b">
         <v>0</v>
       </c>
       <c r="DV20" t="b">
-        <v>1</v>
-      </c>
-      <c r="DW20" t="inlineStr"/>
-      <c r="DX20" t="inlineStr"/>
-      <c r="DY20" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="DW20" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="DX20" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="DY20" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
       <c r="DZ20" t="inlineStr"/>
       <c r="EA20" t="inlineStr"/>
       <c r="EB20" t="inlineStr"/>
       <c r="EC20" t="inlineStr"/>
       <c r="ED20" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="EE20" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="EF20" t="inlineStr">
         <is>
-          <t>4.32</t>
-        </is>
-      </c>
-      <c r="EG20" t="inlineStr"/>
-      <c r="EH20" t="inlineStr"/>
+          <t>3.69</t>
+        </is>
+      </c>
+      <c r="EG20" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EH20" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
       <c r="EI20" t="inlineStr"/>
       <c r="EJ20" t="inlineStr"/>
       <c r="EK20" t="inlineStr"/>
@@ -10221,7 +10221,7 @@
         <v>0.89</v>
       </c>
       <c r="DE21" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DF21" t="n">
         <v>1</v>
@@ -10251,7 +10251,7 @@
         <v>1.95</v>
       </c>
       <c r="DO21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11121,7 +11121,7 @@
         <v>2.8</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DF23" t="n">
         <v>3</v>
@@ -11151,7 +11151,7 @@
         <v>3.96</v>
       </c>
       <c r="DO23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -11607,7 +11607,7 @@
         <v>1.08</v>
       </c>
       <c r="DO24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12035,7 +12035,7 @@
         <v>2.16</v>
       </c>
       <c r="DO25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12971,7 +12971,7 @@
         <v>3.01</v>
       </c>
       <c r="DO27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13415,7 +13415,7 @@
         <v>2.04</v>
       </c>
       <c r="DO28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -13837,7 +13837,7 @@
         <v>2.33</v>
       </c>
       <c r="DE29" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DF29" t="n">
         <v>3</v>
@@ -13867,7 +13867,7 @@
         <v>3.23</v>
       </c>
       <c r="DO29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14290,7 +14290,7 @@
         <v>100</v>
       </c>
       <c r="DD30" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DE30" t="n">
         <v>1.56</v>
@@ -14323,7 +14323,7 @@
         <v>3.75</v>
       </c>
       <c r="DO30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15174,7 +15174,7 @@
         <v>50</v>
       </c>
       <c r="DD32" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DE32" t="n">
         <v>1</v>
@@ -15207,7 +15207,7 @@
         <v>1.95</v>
       </c>
       <c r="DO32" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16507,7 +16507,7 @@
         <v>2.48</v>
       </c>
       <c r="DO35" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -16946,10 +16946,10 @@
         <v>100</v>
       </c>
       <c r="DD36" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DE36" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DF36" t="n">
         <v>1.5</v>
@@ -16979,7 +16979,7 @@
         <v>2.73</v>
       </c>
       <c r="DO36" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18282,10 +18282,10 @@
         <v>75</v>
       </c>
       <c r="DD39" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DF39" t="n">
         <v>2</v>
@@ -18315,7 +18315,7 @@
         <v>2.78</v>
       </c>
       <c r="DO39" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -18755,7 +18755,7 @@
         <v>2.87</v>
       </c>
       <c r="DO40" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -19643,7 +19643,7 @@
         <v>2.35</v>
       </c>
       <c r="DO42" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -20069,7 +20069,7 @@
         <v>1.89</v>
       </c>
       <c r="DE43" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DF43" t="n">
         <v>2.33</v>
@@ -20099,7 +20099,7 @@
         <v>2.55</v>
       </c>
       <c r="DO43" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21426,7 +21426,7 @@
         <v>50</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE46" t="n">
         <v>0.6</v>
@@ -21459,7 +21459,7 @@
         <v>2.53</v>
       </c>
       <c r="DO46" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -21891,7 +21891,7 @@
         <v>2.33</v>
       </c>
       <c r="DO47" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -22347,7 +22347,7 @@
         <v>3.02</v>
       </c>
       <c r="DO48" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -22754,7 +22754,7 @@
         <v>84</v>
       </c>
       <c r="DD49" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DE49" t="n">
         <v>1.6</v>
@@ -22787,7 +22787,7 @@
         <v>2.7</v>
       </c>
       <c r="DO49" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24123,7 +24123,7 @@
         <v>2</v>
       </c>
       <c r="DO52" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -24563,7 +24563,7 @@
         <v>3.04</v>
       </c>
       <c r="DO53" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -25413,7 +25413,7 @@
         <v>2.33</v>
       </c>
       <c r="DE55" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DF55" t="n">
         <v>2.33</v>
@@ -25443,7 +25443,7 @@
         <v>2.77</v>
       </c>
       <c r="DO55" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -25887,7 +25887,7 @@
         <v>3.14</v>
       </c>
       <c r="DO56" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -26343,7 +26343,7 @@
         <v>2.24</v>
       </c>
       <c r="DO57" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -27343,37 +27343,37 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
         <v>45913.57291666666</v>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K60" t="n">
         <v>5</v>
       </c>
       <c r="L60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N60" t="n">
         <v>4</v>
@@ -27385,7 +27385,7 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R60" t="n">
         <v>4</v>
@@ -27394,110 +27394,102 @@
         <v>9</v>
       </c>
       <c r="T60" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="U60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V60" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="W60" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="X60" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y60" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="Z60" t="n">
-        <v>62</v>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>Akhmat Arena</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
-        </is>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD60" t="n">
         <v>4</v>
       </c>
       <c r="AE60" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="AF60" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="AG60" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AI60" t="n">
         <v>1.77</v>
       </c>
       <c r="AJ60" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="AK60" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AL60" t="n">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="AM60" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="AN60" t="n">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AO60" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AQ60" t="n">
         <v>1.38</v>
       </c>
       <c r="AR60" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="AS60" t="n">
-        <v>2.88</v>
+        <v>3.07</v>
       </c>
       <c r="AT60" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AU60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY60" t="n">
         <v>1</v>
       </c>
       <c r="AZ60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB60" t="n">
         <v>-1</v>
@@ -27506,7 +27498,7 @@
         <v>0</v>
       </c>
       <c r="BD60" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="BE60" t="n">
         <v>0</v>
@@ -27542,43 +27534,43 @@
         <v>0</v>
       </c>
       <c r="BP60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BQ60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR60" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS60" t="n">
         <v>3</v>
       </c>
-      <c r="BS60" t="n">
-        <v>1</v>
-      </c>
       <c r="BT60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BU60" t="n">
         <v>1</v>
       </c>
       <c r="BV60" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="BW60" t="n">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="BX60" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="BY60" t="n">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="BZ60" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="CA60" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="CB60" t="n">
-        <v>3.11</v>
+        <v>2.81</v>
       </c>
       <c r="CC60" t="n">
         <v>0</v>
@@ -27626,19 +27618,19 @@
         <v>1</v>
       </c>
       <c r="CR60" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="CS60" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CT60" t="n">
         <v>1</v>
       </c>
       <c r="CU60" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="CV60" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="CW60" t="n">
         <v>1</v>
@@ -27647,55 +27639,55 @@
         <v>4</v>
       </c>
       <c r="CY60" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CZ60" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="DA60" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="DB60" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="DC60" t="n">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="DD60" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.9</v>
+        <v>1.22</v>
       </c>
       <c r="DF60" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DG60" t="n">
-        <v>2.33</v>
+        <v>1.33</v>
       </c>
       <c r="DH60" t="n">
         <v>1.14</v>
       </c>
       <c r="DI60" t="n">
-        <v>2.14</v>
+        <v>1.57</v>
       </c>
       <c r="DJ60" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="DK60" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="DL60" t="n">
-        <v>1.47</v>
+        <v>1.97</v>
       </c>
       <c r="DM60" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="DN60" t="n">
-        <v>2.92</v>
+        <v>3.31</v>
       </c>
       <c r="DO60" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -27704,10 +27696,10 @@
         <v>1</v>
       </c>
       <c r="DR60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT60" t="b">
         <v>0</v>
@@ -27720,17 +27712,17 @@
       </c>
       <c r="DW60" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="DX60" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="DY60" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="DZ60" t="inlineStr"/>
@@ -27739,41 +27731,49 @@
       <c r="EC60" t="inlineStr"/>
       <c r="ED60" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="EE60" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="EF60" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EG60" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="EH60" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="EI60" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EJ60" t="inlineStr">
         <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="EK60" t="inlineStr"/>
-      <c r="EL60" t="inlineStr"/>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EK60" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EL60" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -27791,37 +27791,37 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F61" s="2" t="n">
         <v>45913.57291666666</v>
       </c>
       <c r="G61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K61" t="n">
         <v>5</v>
       </c>
       <c r="L61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
         <v>4</v>
@@ -27833,7 +27833,7 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R61" t="n">
         <v>4</v>
@@ -27842,183 +27842,191 @@
         <v>9</v>
       </c>
       <c r="T61" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="U61" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V61" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W61" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="X61" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y61" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="Z61" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA61" t="inlineStr"/>
-      <c r="AB61" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>Akhmat Arena</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
+        </is>
+      </c>
       <c r="AC61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD61" t="n">
         <v>4</v>
       </c>
       <c r="AE61" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="AF61" t="n">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="AG61" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AI61" t="n">
         <v>1.77</v>
       </c>
       <c r="AJ61" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="AK61" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AL61" t="n">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="AM61" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="AN61" t="n">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AO61" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AQ61" t="n">
         <v>1.38</v>
       </c>
       <c r="AR61" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="AS61" t="n">
-        <v>3.07</v>
+        <v>2.88</v>
       </c>
       <c r="AT61" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AU61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY61" t="n">
         <v>1</v>
       </c>
       <c r="AZ61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD61" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH61" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP61" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR61" t="n">
         <v>3</v>
       </c>
-      <c r="BB61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BC61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD61" t="n">
-        <v>59</v>
-      </c>
-      <c r="BE61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BG61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BH61" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BJ61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BK61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BL61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BM61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BN61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BO61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP61" t="n">
+      <c r="BS61" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT61" t="n">
         <v>3</v>
       </c>
-      <c r="BQ61" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR61" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS61" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT61" t="n">
-        <v>2</v>
-      </c>
       <c r="BU61" t="n">
         <v>1</v>
       </c>
       <c r="BV61" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="BW61" t="n">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="BX61" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="BY61" t="n">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="BZ61" t="n">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="CA61" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="CB61" t="n">
-        <v>2.81</v>
+        <v>3.11</v>
       </c>
       <c r="CC61" t="n">
         <v>0</v>
@@ -28066,19 +28074,19 @@
         <v>1</v>
       </c>
       <c r="CR61" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="CS61" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT61" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU61" t="n">
         <v>17</v>
       </c>
-      <c r="CT61" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU61" t="n">
-        <v>21</v>
-      </c>
       <c r="CV61" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="CW61" t="n">
         <v>1</v>
@@ -28087,55 +28095,55 @@
         <v>4</v>
       </c>
       <c r="CY61" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CZ61" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="DA61" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="DB61" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="DC61" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.33</v>
+        <v>1.9</v>
       </c>
       <c r="DE61" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="DF61" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="DG61" t="n">
-        <v>1.33</v>
+        <v>2.33</v>
       </c>
       <c r="DH61" t="n">
         <v>1.14</v>
       </c>
       <c r="DI61" t="n">
-        <v>1.57</v>
+        <v>2.14</v>
       </c>
       <c r="DJ61" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="DK61" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="DL61" t="n">
-        <v>1.97</v>
+        <v>1.47</v>
       </c>
       <c r="DM61" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="DN61" t="n">
-        <v>3.31</v>
+        <v>2.92</v>
       </c>
       <c r="DO61" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -28144,10 +28152,10 @@
         <v>1</v>
       </c>
       <c r="DR61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT61" t="b">
         <v>0</v>
@@ -28160,17 +28168,17 @@
       </c>
       <c r="DW61" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="DX61" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="DY61" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="DZ61" t="inlineStr"/>
@@ -28179,49 +28187,41 @@
       <c r="EC61" t="inlineStr"/>
       <c r="ED61" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="EE61" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="EF61" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="EG61" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="EH61" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EI61" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EJ61" t="inlineStr">
         <is>
-          <t>1.99</t>
-        </is>
-      </c>
-      <c r="EK61" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EL61" t="inlineStr">
-        <is>
-          <t>2.58</t>
-        </is>
-      </c>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EK61" t="inlineStr"/>
+      <c r="EL61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -29011,7 +29011,7 @@
         <v>1.8</v>
       </c>
       <c r="DO63" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -29909,7 +29909,7 @@
         <v>1.33</v>
       </c>
       <c r="DE65" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DF65" t="n">
         <v>1.33</v>
@@ -29939,7 +29939,7 @@
         <v>3.14</v>
       </c>
       <c r="DO65" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -30379,7 +30379,7 @@
         <v>2.54</v>
       </c>
       <c r="DO66" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -31727,7 +31727,7 @@
         <v>2.57</v>
       </c>
       <c r="DO69" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -32125,7 +32125,7 @@
         <v>2.1</v>
       </c>
       <c r="DE70" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DF70" t="n">
         <v>1.75</v>
@@ -32155,7 +32155,7 @@
         <v>2.43</v>
       </c>
       <c r="DO70" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -33478,10 +33478,10 @@
         <v>88</v>
       </c>
       <c r="DD73" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DE73" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DF73" t="n">
         <v>0.33</v>
@@ -33511,7 +33511,7 @@
         <v>2.46</v>
       </c>
       <c r="DO73" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -33975,7 +33975,7 @@
         <v>2.54</v>
       </c>
       <c r="DO74" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -34398,7 +34398,7 @@
         <v>88</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DE75" t="n">
         <v>1.3</v>
@@ -34431,7 +34431,7 @@
         <v>2.91</v>
       </c>
       <c r="DO75" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -36219,7 +36219,7 @@
         <v>3.14</v>
       </c>
       <c r="DO79" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -36659,7 +36659,7 @@
         <v>1.87</v>
       </c>
       <c r="DO80" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP80" t="b">
         <v>0</v>
@@ -37115,7 +37115,7 @@
         <v>2.45</v>
       </c>
       <c r="DO81" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -37953,7 +37953,7 @@
         <v>1.89</v>
       </c>
       <c r="DE83" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DF83" t="n">
         <v>2</v>
@@ -37983,7 +37983,7 @@
         <v>2.19</v>
       </c>
       <c r="DO83" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -38423,7 +38423,7 @@
         <v>3.27</v>
       </c>
       <c r="DO84" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -38822,7 +38822,7 @@
         <v>80</v>
       </c>
       <c r="DD85" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE85" t="n">
         <v>1.9</v>
@@ -38855,7 +38855,7 @@
         <v>3.26</v>
       </c>
       <c r="DO85" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -39738,7 +39738,7 @@
         <v>70</v>
       </c>
       <c r="DD87" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DE87" t="n">
         <v>0.6</v>
@@ -39771,7 +39771,7 @@
         <v>1.93</v>
       </c>
       <c r="DO87" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -40197,7 +40197,7 @@
         <v>2.78</v>
       </c>
       <c r="DE88" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DF88" t="n">
         <v>2.6</v>
@@ -40227,7 +40227,7 @@
         <v>3.03</v>
       </c>
       <c r="DO88" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -40787,176 +40787,168 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
         <v>45948.41666666666</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" t="n">
         <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J90" t="n">
+        <v>5</v>
+      </c>
+      <c r="K90" t="n">
         <v>6</v>
       </c>
-      <c r="K90" t="n">
+      <c r="L90" t="n">
+        <v>11</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1</v>
+      </c>
+      <c r="N90" t="n">
+        <v>2</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
         <v>3</v>
       </c>
-      <c r="L90" t="n">
-        <v>9</v>
-      </c>
-      <c r="M90" t="n">
-        <v>2</v>
-      </c>
-      <c r="N90" t="n">
-        <v>2</v>
-      </c>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>11</v>
-      </c>
       <c r="R90" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="U90" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="V90" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W90" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="X90" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Y90" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="Z90" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>Stadion Nizhny Novgorod</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>ul. Dolzhanskaya, Nizhniy Novgorod</t>
-        </is>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="AA90" t="inlineStr"/>
+      <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD90" t="n">
         <v>2</v>
       </c>
       <c r="AE90" t="n">
-        <v>2.29</v>
+        <v>1.9</v>
       </c>
       <c r="AF90" t="n">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
       <c r="AG90" t="n">
-        <v>2.57</v>
+        <v>3.28</v>
       </c>
       <c r="AH90" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AI90" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AJ90" t="n">
-        <v>2.66</v>
+        <v>3.08</v>
       </c>
       <c r="AK90" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="AL90" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="AM90" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AN90" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AO90" t="n">
-        <v>2.16</v>
+        <v>2.62</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AR90" t="n">
-        <v>2.51</v>
+        <v>2.74</v>
       </c>
       <c r="AS90" t="n">
-        <v>3.32</v>
+        <v>3.04</v>
       </c>
       <c r="AT90" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AU90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV90" t="n">
         <v>0</v>
       </c>
       <c r="AW90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ90" t="n">
         <v>1</v>
       </c>
       <c r="BA90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB90" t="n">
-        <v>668270</v>
+        <v>-1</v>
       </c>
       <c r="BC90" t="n">
         <v>0</v>
       </c>
       <c r="BD90" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BE90" t="n">
         <v>0</v>
       </c>
       <c r="BF90" t="n">
-        <v>4088</v>
+        <v>6069</v>
       </c>
       <c r="BG90" t="n">
         <v>-1</v>
@@ -40983,7 +40975,7 @@
         <v>-1</v>
       </c>
       <c r="BO90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP90" t="n">
         <v>0</v>
@@ -40995,7 +40987,7 @@
         <v>2</v>
       </c>
       <c r="BS90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT90" t="n">
         <v>3</v>
@@ -41004,25 +40996,25 @@
         <v>1</v>
       </c>
       <c r="BV90" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="BW90" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="BX90" t="n">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="BY90" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="BZ90" t="n">
-        <v>2.82</v>
+        <v>1.44</v>
       </c>
       <c r="CA90" t="n">
-        <v>1.09</v>
+        <v>1.34</v>
       </c>
       <c r="CB90" t="n">
-        <v>3.91</v>
+        <v>2.78</v>
       </c>
       <c r="CC90" t="n">
         <v>0</v>
@@ -41070,73 +41062,73 @@
         <v>1</v>
       </c>
       <c r="CR90" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CS90" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CT90" t="n">
         <v>1</v>
       </c>
       <c r="CU90" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="CV90" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CW90" t="n">
         <v>1</v>
       </c>
       <c r="CX90" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="CY90" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="CZ90" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="DA90" t="n">
         <v>100</v>
       </c>
       <c r="DB90" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="DC90" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="DD90" t="n">
-        <v>0.89</v>
+        <v>1.5</v>
       </c>
       <c r="DE90" t="n">
-        <v>1.3</v>
+        <v>0.44</v>
       </c>
       <c r="DF90" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="DG90" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="DH90" t="n">
-        <v>0.55</v>
+        <v>1.09</v>
       </c>
       <c r="DI90" t="n">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="DJ90" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="DK90" t="n">
         <v>0</v>
       </c>
       <c r="DL90" t="n">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="DM90" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="DN90" t="n">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="DO90" t="n">
         <v>19</v>
@@ -41145,7 +41137,7 @@
         <v>1</v>
       </c>
       <c r="DQ90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR90" t="b">
         <v>0</v>
@@ -41160,66 +41152,66 @@
         <v>0</v>
       </c>
       <c r="DV90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW90" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="DX90" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="DY90" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="DZ90" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EA90" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EB90" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="EC90" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="ED90" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="EE90" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EF90" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="EG90" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="EH90" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EI90" t="inlineStr"/>
@@ -41243,168 +41235,176 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F91" s="2" t="n">
         <v>45948.41666666666</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
         <v>1</v>
       </c>
       <c r="I91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K91" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L91" t="n">
+        <v>9</v>
+      </c>
+      <c r="M91" t="n">
+        <v>2</v>
+      </c>
+      <c r="N91" t="n">
+        <v>2</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
         <v>11</v>
       </c>
-      <c r="M91" t="n">
-        <v>1</v>
-      </c>
-      <c r="N91" t="n">
-        <v>2</v>
-      </c>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>3</v>
-      </c>
       <c r="R91" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T91" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="U91" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="V91" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W91" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="X91" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Y91" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="Z91" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA91" t="inlineStr"/>
-      <c r="AB91" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>Stadion Nizhny Novgorod</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>ul. Dolzhanskaya, Nizhniy Novgorod</t>
+        </is>
+      </c>
       <c r="AC91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD91" t="n">
         <v>2</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.9</v>
+        <v>2.29</v>
       </c>
       <c r="AF91" t="n">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="AG91" t="n">
-        <v>3.28</v>
+        <v>2.57</v>
       </c>
       <c r="AH91" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AI91" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AJ91" t="n">
-        <v>3.08</v>
+        <v>2.66</v>
       </c>
       <c r="AK91" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AL91" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="AM91" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AN91" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AO91" t="n">
-        <v>2.62</v>
+        <v>2.16</v>
       </c>
       <c r="AP91" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR91" t="n">
-        <v>2.74</v>
+        <v>2.51</v>
       </c>
       <c r="AS91" t="n">
-        <v>3.04</v>
+        <v>3.32</v>
       </c>
       <c r="AT91" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AU91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV91" t="n">
         <v>0</v>
       </c>
       <c r="AW91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ91" t="n">
         <v>1</v>
       </c>
       <c r="BA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB91" t="n">
-        <v>-1</v>
+        <v>668270</v>
       </c>
       <c r="BC91" t="n">
         <v>0</v>
       </c>
       <c r="BD91" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BE91" t="n">
         <v>0</v>
       </c>
       <c r="BF91" t="n">
-        <v>6069</v>
+        <v>4088</v>
       </c>
       <c r="BG91" t="n">
         <v>-1</v>
@@ -41431,7 +41431,7 @@
         <v>-1</v>
       </c>
       <c r="BO91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP91" t="n">
         <v>0</v>
@@ -41443,7 +41443,7 @@
         <v>2</v>
       </c>
       <c r="BS91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT91" t="n">
         <v>3</v>
@@ -41452,25 +41452,25 @@
         <v>1</v>
       </c>
       <c r="BV91" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="BW91" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="BX91" t="n">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="BY91" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BZ91" t="n">
-        <v>1.44</v>
+        <v>2.82</v>
       </c>
       <c r="CA91" t="n">
-        <v>1.34</v>
+        <v>1.09</v>
       </c>
       <c r="CB91" t="n">
-        <v>2.78</v>
+        <v>3.91</v>
       </c>
       <c r="CC91" t="n">
         <v>0</v>
@@ -41518,82 +41518,82 @@
         <v>1</v>
       </c>
       <c r="CR91" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS91" t="n">
         <v>21</v>
       </c>
-      <c r="CS91" t="n">
-        <v>23</v>
-      </c>
       <c r="CT91" t="n">
         <v>1</v>
       </c>
       <c r="CU91" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="CV91" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CW91" t="n">
         <v>1</v>
       </c>
       <c r="CX91" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="CY91" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="CZ91" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="DA91" t="n">
         <v>100</v>
       </c>
       <c r="DB91" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="DC91" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="DD91" t="n">
-        <v>1.5</v>
+        <v>0.89</v>
       </c>
       <c r="DE91" t="n">
-        <v>0.44</v>
+        <v>1.3</v>
       </c>
       <c r="DF91" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="DG91" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="DH91" t="n">
-        <v>1.09</v>
+        <v>0.55</v>
       </c>
       <c r="DI91" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="DJ91" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="DK91" t="n">
         <v>0</v>
       </c>
       <c r="DL91" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DM91" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="DN91" t="n">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="DO91" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
       </c>
       <c r="DQ91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR91" t="b">
         <v>0</v>
@@ -41608,66 +41608,66 @@
         <v>0</v>
       </c>
       <c r="DV91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW91" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="DX91" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="DY91" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="DZ91" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EA91" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EB91" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="EC91" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="ED91" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="EE91" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="EF91" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="EG91" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EH91" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="EI91" t="inlineStr"/>
@@ -42043,7 +42043,7 @@
         <v>2.78</v>
       </c>
       <c r="DO92" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -42921,7 +42921,7 @@
         <v>2.33</v>
       </c>
       <c r="DE94" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DF94" t="n">
         <v>2.2</v>
@@ -42951,7 +42951,7 @@
         <v>3.2</v>
       </c>
       <c r="DO94" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -43374,7 +43374,7 @@
         <v>84</v>
       </c>
       <c r="DD95" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DE95" t="n">
         <v>1.56</v>
@@ -43407,7 +43407,7 @@
         <v>2.32</v>
       </c>
       <c r="DO95" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -44250,7 +44250,7 @@
         <v>100</v>
       </c>
       <c r="DD97" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE97" t="n">
         <v>0.67</v>
@@ -44283,7 +44283,7 @@
         <v>3.18</v>
       </c>
       <c r="DO97" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -44739,7 +44739,7 @@
         <v>2.97</v>
       </c>
       <c r="DO98" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -45581,7 +45581,7 @@
         <v>2.78</v>
       </c>
       <c r="DE100" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DF100" t="n">
         <v>2.67</v>
@@ -45611,7 +45611,7 @@
         <v>2.59</v>
       </c>
       <c r="DO100" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -46927,7 +46927,7 @@
         <v>3.41</v>
       </c>
       <c r="DO103" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -47790,7 +47790,7 @@
         <v>57</v>
       </c>
       <c r="DD105" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DE105" t="n">
         <v>0.44</v>
@@ -47823,7 +47823,7 @@
         <v>2.37</v>
       </c>
       <c r="DO105" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -48263,7 +48263,7 @@
         <v>2.66</v>
       </c>
       <c r="DO106" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -48669,7 +48669,7 @@
         <v>1.5</v>
       </c>
       <c r="DE107" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DF107" t="n">
         <v>1.5</v>
@@ -48699,7 +48699,7 @@
         <v>2.09</v>
       </c>
       <c r="DO107" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -49147,7 +49147,7 @@
         <v>2.61</v>
       </c>
       <c r="DO108" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP108" t="b">
         <v>0</v>
@@ -49267,25 +49267,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F109" s="2" t="n">
         <v>45962.71875</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J109" t="n">
         <v>6</v>
@@ -49300,323 +49300,315 @@
         <v>2</v>
       </c>
       <c r="N109" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P109" t="n">
         <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R109" t="n">
         <v>2</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T109" t="n">
         <v>6</v>
       </c>
       <c r="U109" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V109" t="n">
         <v>8</v>
       </c>
       <c r="W109" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X109" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Y109" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Z109" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA109" t="inlineStr">
-        <is>
-          <t>Stadion Central’nyj im. I.P. Chayka</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>ul. Suvorova, Peschanokopskoye</t>
-        </is>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="AA109" t="inlineStr"/>
+      <c r="AB109" t="inlineStr"/>
       <c r="AC109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD109" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE109" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AF109" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG109" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AH109" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI109" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ109" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AK109" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL109" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM109" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO109" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AP109" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ109" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR109" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AS109" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT109" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AU109" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB109" t="n">
+        <v>921</v>
+      </c>
+      <c r="BC109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD109" t="n">
+        <v>84</v>
+      </c>
+      <c r="BE109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF109" t="n">
+        <v>45133</v>
+      </c>
+      <c r="BG109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV109" t="n">
+        <v>51</v>
+      </c>
+      <c r="BW109" t="n">
+        <v>46</v>
+      </c>
+      <c r="BX109" t="n">
+        <v>89</v>
+      </c>
+      <c r="BY109" t="n">
+        <v>85</v>
+      </c>
+      <c r="BZ109" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CA109" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="CB109" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="CC109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR109" t="n">
+        <v>28</v>
+      </c>
+      <c r="CS109" t="n">
+        <v>8</v>
+      </c>
+      <c r="CT109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU109" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV109" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX109" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY109" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ109" t="n">
+        <v>55</v>
+      </c>
+      <c r="DA109" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB109" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC109" t="n">
+        <v>77</v>
+      </c>
+      <c r="DD109" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="DE109" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DF109" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DG109" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DH109" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI109" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="DJ109" t="n">
+        <v>45</v>
+      </c>
+      <c r="DK109" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL109" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DM109" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DN109" t="n">
         <v>3.47</v>
-      </c>
-      <c r="AG109" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AH109" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI109" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ109" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AK109" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AL109" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM109" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AN109" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AO109" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AP109" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AQ109" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AR109" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AS109" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AT109" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AU109" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY109" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ109" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA109" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB109" t="n">
-        <v>668270</v>
-      </c>
-      <c r="BC109" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD109" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE109" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF109" t="n">
-        <v>7890</v>
-      </c>
-      <c r="BG109" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BH109" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI109" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BJ109" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BK109" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BL109" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BM109" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BN109" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BO109" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP109" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ109" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR109" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS109" t="n">
-        <v>4</v>
-      </c>
-      <c r="BT109" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU109" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV109" t="n">
-        <v>44</v>
-      </c>
-      <c r="BW109" t="n">
-        <v>35</v>
-      </c>
-      <c r="BX109" t="n">
-        <v>78</v>
-      </c>
-      <c r="BY109" t="n">
-        <v>87</v>
-      </c>
-      <c r="BZ109" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="CA109" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="CB109" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="CC109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM109" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CN109" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CO109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR109" t="n">
-        <v>20</v>
-      </c>
-      <c r="CS109" t="n">
-        <v>15</v>
-      </c>
-      <c r="CT109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU109" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV109" t="n">
-        <v>15</v>
-      </c>
-      <c r="CW109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX109" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY109" t="n">
-        <v>15</v>
-      </c>
-      <c r="CZ109" t="n">
-        <v>42</v>
-      </c>
-      <c r="DA109" t="n">
-        <v>67</v>
-      </c>
-      <c r="DB109" t="n">
-        <v>25</v>
-      </c>
-      <c r="DC109" t="n">
-        <v>75</v>
-      </c>
-      <c r="DD109" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DE109" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="DF109" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DG109" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="DH109" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="DI109" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="DJ109" t="n">
-        <v>58</v>
-      </c>
-      <c r="DK109" t="n">
-        <v>34</v>
-      </c>
-      <c r="DL109" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="DM109" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="DN109" t="n">
-        <v>2.81</v>
       </c>
       <c r="DO109" t="n">
         <v>19</v>
@@ -49625,7 +49617,7 @@
         <v>1</v>
       </c>
       <c r="DQ109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR109" t="b">
         <v>0</v>
@@ -49644,62 +49636,46 @@
       </c>
       <c r="DW109" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="DX109" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="DY109" t="inlineStr">
         <is>
-          <t>1.28</t>
-        </is>
-      </c>
-      <c r="DZ109" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EA109" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="EB109" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="EC109" t="inlineStr">
-        <is>
-          <t>2.79</t>
-        </is>
-      </c>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="DZ109" t="inlineStr"/>
+      <c r="EA109" t="inlineStr"/>
+      <c r="EB109" t="inlineStr"/>
+      <c r="EC109" t="inlineStr"/>
       <c r="ED109" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="EE109" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="EF109" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="EG109" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="EH109" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EI109" t="inlineStr"/>
@@ -49723,25 +49699,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F110" s="2" t="n">
         <v>45962.71875</v>
       </c>
       <c r="G110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J110" t="n">
         <v>6</v>
@@ -49756,315 +49732,323 @@
         <v>2</v>
       </c>
       <c r="N110" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P110" t="n">
         <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R110" t="n">
         <v>2</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T110" t="n">
         <v>6</v>
       </c>
       <c r="U110" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V110" t="n">
         <v>8</v>
       </c>
       <c r="W110" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="X110" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Y110" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Z110" t="n">
-        <v>51</v>
-      </c>
-      <c r="AA110" t="inlineStr"/>
-      <c r="AB110" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>Stadion Central’nyj im. I.P. Chayka</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>ul. Suvorova, Peschanokopskoye</t>
+        </is>
+      </c>
       <c r="AC110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD110" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE110" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AF110" t="n">
-        <v>3.9</v>
+        <v>3.47</v>
       </c>
       <c r="AG110" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AH110" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AI110" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AJ110" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="AK110" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AL110" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AM110" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="AN110" t="n">
-        <v>1.92</v>
+        <v>2.23</v>
       </c>
       <c r="AO110" t="n">
-        <v>2.65</v>
+        <v>2.32</v>
       </c>
       <c r="AP110" t="n">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="AQ110" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR110" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AS110" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AT110" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB110" t="n">
+        <v>668270</v>
+      </c>
+      <c r="BC110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD110" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF110" t="n">
+        <v>7890</v>
+      </c>
+      <c r="BG110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO110" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP110" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR110" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS110" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT110" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV110" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW110" t="n">
+        <v>35</v>
+      </c>
+      <c r="BX110" t="n">
+        <v>78</v>
+      </c>
+      <c r="BY110" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ110" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CA110" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="CB110" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="CC110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR110" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS110" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU110" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV110" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX110" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY110" t="n">
+        <v>15</v>
+      </c>
+      <c r="CZ110" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA110" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB110" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC110" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD110" t="n">
         <v>1.33</v>
       </c>
-      <c r="AR110" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AS110" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AT110" t="n">
+      <c r="DE110" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DF110" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG110" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DH110" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DI110" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DJ110" t="n">
+        <v>58</v>
+      </c>
+      <c r="DK110" t="n">
+        <v>34</v>
+      </c>
+      <c r="DL110" t="n">
         <v>1.47</v>
       </c>
-      <c r="AU110" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV110" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX110" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ110" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA110" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB110" t="n">
-        <v>921</v>
-      </c>
-      <c r="BC110" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD110" t="n">
-        <v>84</v>
-      </c>
-      <c r="BE110" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF110" t="n">
-        <v>45133</v>
-      </c>
-      <c r="BG110" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BH110" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI110" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BJ110" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BK110" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BL110" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BM110" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BN110" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BO110" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP110" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ110" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR110" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS110" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT110" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU110" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV110" t="n">
-        <v>51</v>
-      </c>
-      <c r="BW110" t="n">
-        <v>46</v>
-      </c>
-      <c r="BX110" t="n">
-        <v>89</v>
-      </c>
-      <c r="BY110" t="n">
-        <v>85</v>
-      </c>
-      <c r="BZ110" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CA110" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="CB110" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="CC110" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD110" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE110" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF110" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG110" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH110" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI110" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ110" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK110" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL110" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM110" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CN110" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CO110" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP110" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ110" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR110" t="n">
-        <v>28</v>
-      </c>
-      <c r="CS110" t="n">
-        <v>8</v>
-      </c>
-      <c r="CT110" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU110" t="n">
-        <v>20</v>
-      </c>
-      <c r="CV110" t="n">
-        <v>13</v>
-      </c>
-      <c r="CW110" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX110" t="n">
-        <v>7</v>
-      </c>
-      <c r="CY110" t="n">
-        <v>6</v>
-      </c>
-      <c r="CZ110" t="n">
-        <v>55</v>
-      </c>
-      <c r="DA110" t="n">
-        <v>100</v>
-      </c>
-      <c r="DB110" t="n">
-        <v>32</v>
-      </c>
-      <c r="DC110" t="n">
-        <v>77</v>
-      </c>
-      <c r="DD110" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="DE110" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="DF110" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="DG110" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="DH110" t="n">
-        <v>2</v>
-      </c>
-      <c r="DI110" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="DJ110" t="n">
-        <v>45</v>
-      </c>
-      <c r="DK110" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL110" t="n">
-        <v>1.92</v>
-      </c>
       <c r="DM110" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="DN110" t="n">
-        <v>3.47</v>
+        <v>2.81</v>
       </c>
       <c r="DO110" t="n">
         <v>19</v>
@@ -50073,7 +50057,7 @@
         <v>1</v>
       </c>
       <c r="DQ110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR110" t="b">
         <v>0</v>
@@ -50092,46 +50076,62 @@
       </c>
       <c r="DW110" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="DX110" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="DY110" t="inlineStr">
         <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="DZ110" t="inlineStr"/>
-      <c r="EA110" t="inlineStr"/>
-      <c r="EB110" t="inlineStr"/>
-      <c r="EC110" t="inlineStr"/>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="DZ110" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EA110" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EB110" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="EC110" t="inlineStr">
+        <is>
+          <t>2.79</t>
+        </is>
+      </c>
       <c r="ED110" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EE110" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="EF110" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="EG110" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="EH110" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EI110" t="inlineStr"/>
@@ -50507,7 +50507,7 @@
         <v>2.03</v>
       </c>
       <c r="DO111" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -50947,7 +50947,7 @@
         <v>2.57</v>
       </c>
       <c r="DO112" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -51373,7 +51373,7 @@
         <v>2.45</v>
       </c>
       <c r="DE113" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DF113" t="n">
         <v>2.14</v>
@@ -51403,7 +51403,7 @@
         <v>3.33</v>
       </c>
       <c r="DO113" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -51818,7 +51818,7 @@
         <v>86</v>
       </c>
       <c r="DD114" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE114" t="n">
         <v>1.3</v>
@@ -51851,7 +51851,7 @@
         <v>3.16</v>
       </c>
       <c r="DO114" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP114" t="b">
         <v>1</v>
@@ -52689,7 +52689,7 @@
         <v>1.5</v>
       </c>
       <c r="DE116" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DF116" t="n">
         <v>1.71</v>
@@ -52719,7 +52719,7 @@
         <v>2.74</v>
       </c>
       <c r="DO116" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP116" t="b">
         <v>1</v>
@@ -53122,7 +53122,7 @@
         <v>72</v>
       </c>
       <c r="DD117" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DE117" t="n">
         <v>0.9</v>
@@ -53155,7 +53155,7 @@
         <v>2.24</v>
       </c>
       <c r="DO117" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -53603,7 +53603,7 @@
         <v>2.53</v>
       </c>
       <c r="DO118" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -54446,10 +54446,10 @@
         <v>75</v>
       </c>
       <c r="DD120" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DE120" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DF120" t="n">
         <v>1.67</v>
@@ -54479,7 +54479,7 @@
         <v>3.17</v>
       </c>
       <c r="DO120" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -55403,7 +55403,7 @@
         <v>2.2</v>
       </c>
       <c r="DO122" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -56257,7 +56257,7 @@
         <v>2.1</v>
       </c>
       <c r="DE124" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DF124" t="n">
         <v>2.13</v>
@@ -56287,7 +56287,7 @@
         <v>3.02</v>
       </c>
       <c r="DO124" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -56743,7 +56743,7 @@
         <v>2.41</v>
       </c>
       <c r="DO125" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP125" t="b">
         <v>1</v>
@@ -57191,7 +57191,7 @@
         <v>2.45</v>
       </c>
       <c r="DO126" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP126" t="b">
         <v>1</v>
@@ -58050,7 +58050,7 @@
         <v>87</v>
       </c>
       <c r="DD128" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE128" t="n">
         <v>0.33</v>
@@ -58083,7 +58083,7 @@
         <v>3.18</v>
       </c>
       <c r="DO128" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP128" t="b">
         <v>1</v>
@@ -59423,7 +59423,7 @@
         <v>2.91</v>
       </c>
       <c r="DO131" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP131" t="b">
         <v>1</v>
@@ -59821,7 +59821,7 @@
         <v>2.11</v>
       </c>
       <c r="DE132" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DF132" t="n">
         <v>1.86</v>
@@ -59851,7 +59851,7 @@
         <v>2.78</v>
       </c>
       <c r="DO132" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP132" t="b">
         <v>1</v>
@@ -60269,7 +60269,7 @@
         <v>2.45</v>
       </c>
       <c r="DE133" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DF133" t="n">
         <v>2.25</v>
@@ -60299,7 +60299,7 @@
         <v>2.76</v>
       </c>
       <c r="DO133" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP133" t="b">
         <v>1</v>
@@ -60403,176 +60403,176 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F134" s="2" t="n">
         <v>45991.5625</v>
       </c>
       <c r="G134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I134" t="n">
+        <v>4</v>
+      </c>
+      <c r="J134" t="n">
+        <v>2</v>
+      </c>
+      <c r="K134" t="n">
+        <v>4</v>
+      </c>
+      <c r="L134" t="n">
+        <v>6</v>
+      </c>
+      <c r="M134" t="n">
+        <v>2</v>
+      </c>
+      <c r="N134" t="n">
+        <v>1</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
         <v>3</v>
       </c>
-      <c r="J134" t="n">
-        <v>7</v>
-      </c>
-      <c r="K134" t="n">
+      <c r="R134" t="n">
+        <v>6</v>
+      </c>
+      <c r="S134" t="n">
         <v>8</v>
       </c>
-      <c r="L134" t="n">
-        <v>15</v>
-      </c>
-      <c r="M134" t="n">
-        <v>3</v>
-      </c>
-      <c r="N134" t="n">
-        <v>2</v>
-      </c>
-      <c r="O134" t="n">
-        <v>0</v>
-      </c>
-      <c r="P134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q134" t="n">
-        <v>6</v>
-      </c>
-      <c r="R134" t="n">
-        <v>5</v>
-      </c>
-      <c r="S134" t="n">
+      <c r="T134" t="n">
+        <v>10</v>
+      </c>
+      <c r="U134" t="n">
         <v>11</v>
       </c>
-      <c r="T134" t="n">
-        <v>18</v>
-      </c>
-      <c r="U134" t="n">
-        <v>17</v>
-      </c>
       <c r="V134" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="W134" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X134" t="n">
         <v>13</v>
       </c>
       <c r="Y134" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="Z134" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>Akhmat Arena</t>
+          <t>Stadion Central’nyj im. I.P. Chayka</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
+          <t>ul. Suvorova, Peschanokopskoye</t>
         </is>
       </c>
       <c r="AC134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA134" t="n">
         <v>3</v>
       </c>
-      <c r="AD134" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE134" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AF134" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AG134" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AH134" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI134" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ134" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AK134" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AL134" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AM134" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AN134" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AO134" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AP134" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AQ134" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AR134" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AS134" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AT134" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AU134" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW134" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX134" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ134" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA134" t="n">
-        <v>1</v>
-      </c>
       <c r="BB134" t="n">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="BC134" t="n">
         <v>0</v>
       </c>
       <c r="BD134" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="BE134" t="n">
         <v>0</v>
       </c>
       <c r="BF134" t="n">
-        <v>4236</v>
+        <v>12383</v>
       </c>
       <c r="BG134" t="n">
         <v>-1</v>
@@ -60599,10 +60599,10 @@
         <v>-1</v>
       </c>
       <c r="BO134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ134" t="n">
         <v>2</v>
@@ -60611,7 +60611,7 @@
         <v>1</v>
       </c>
       <c r="BS134" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT134" t="n">
         <v>3</v>
@@ -60620,37 +60620,37 @@
         <v>1</v>
       </c>
       <c r="BV134" t="n">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="BW134" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="BX134" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="BY134" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="BZ134" t="n">
-        <v>1.77</v>
+        <v>1.45</v>
       </c>
       <c r="CA134" t="n">
-        <v>2.12</v>
+        <v>1.71</v>
       </c>
       <c r="CB134" t="n">
-        <v>3.89</v>
+        <v>3.16</v>
       </c>
       <c r="CC134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG134" t="n">
         <v>0</v>
@@ -60668,7 +60668,7 @@
         <v>0</v>
       </c>
       <c r="CL134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM134" t="n">
         <v>-1</v>
@@ -60677,7 +60677,7 @@
         <v>-1</v>
       </c>
       <c r="CO134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP134" t="n">
         <v>0</v>
@@ -60686,76 +60686,76 @@
         <v>1</v>
       </c>
       <c r="CR134" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="CS134" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="CT134" t="n">
         <v>1</v>
       </c>
       <c r="CU134" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CV134" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="CW134" t="n">
         <v>1</v>
       </c>
       <c r="CX134" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CY134" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CZ134" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="DA134" t="n">
         <v>72</v>
       </c>
       <c r="DB134" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="DC134" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="DD134" t="n">
-        <v>1.78</v>
+        <v>1.33</v>
       </c>
       <c r="DE134" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="DF134" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="DG134" t="n">
-        <v>1.14</v>
+        <v>1.63</v>
       </c>
       <c r="DH134" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="DI134" t="n">
-        <v>1.25</v>
+        <v>1.94</v>
       </c>
       <c r="DJ134" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="DK134" t="n">
         <v>29</v>
       </c>
       <c r="DL134" t="n">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="DM134" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="DN134" t="n">
-        <v>3.07</v>
+        <v>2.93</v>
       </c>
       <c r="DO134" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP134" t="b">
         <v>1</v>
@@ -60767,7 +60767,7 @@
         <v>1</v>
       </c>
       <c r="DS134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT134" t="b">
         <v>0</v>
@@ -60780,17 +60780,17 @@
       </c>
       <c r="DW134" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="DX134" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="DY134" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="DZ134" t="inlineStr"/>
@@ -60799,47 +60799,47 @@
       <c r="EC134" t="inlineStr"/>
       <c r="ED134" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="EE134" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="EF134" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="EG134" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EH134" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EI134" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="EJ134" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EK134" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EL134" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -60859,176 +60859,176 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F135" s="2" t="n">
         <v>45991.5625</v>
       </c>
       <c r="G135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H135" t="n">
+        <v>1</v>
+      </c>
+      <c r="I135" t="n">
         <v>3</v>
       </c>
-      <c r="I135" t="n">
-        <v>4</v>
-      </c>
       <c r="J135" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K135" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L135" t="n">
+        <v>15</v>
+      </c>
+      <c r="M135" t="n">
+        <v>3</v>
+      </c>
+      <c r="N135" t="n">
+        <v>2</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
         <v>6</v>
       </c>
-      <c r="M135" t="n">
-        <v>2</v>
-      </c>
-      <c r="N135" t="n">
-        <v>1</v>
-      </c>
-      <c r="O135" t="n">
-        <v>0</v>
-      </c>
-      <c r="P135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q135" t="n">
-        <v>3</v>
-      </c>
       <c r="R135" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S135" t="n">
+        <v>11</v>
+      </c>
+      <c r="T135" t="n">
+        <v>18</v>
+      </c>
+      <c r="U135" t="n">
+        <v>17</v>
+      </c>
+      <c r="V135" t="n">
+        <v>23</v>
+      </c>
+      <c r="W135" t="n">
         <v>8</v>
-      </c>
-      <c r="T135" t="n">
-        <v>10</v>
-      </c>
-      <c r="U135" t="n">
-        <v>11</v>
-      </c>
-      <c r="V135" t="n">
-        <v>16</v>
-      </c>
-      <c r="W135" t="n">
-        <v>16</v>
       </c>
       <c r="X135" t="n">
         <v>13</v>
       </c>
       <c r="Y135" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="Z135" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>Stadion Central’nyj im. I.P. Chayka</t>
+          <t>Akhmat Arena</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>ul. Suvorova, Peschanokopskoye</t>
+          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
         </is>
       </c>
       <c r="AC135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE135" t="n">
-        <v>2.49</v>
+        <v>2.89</v>
       </c>
       <c r="AF135" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="AG135" t="n">
-        <v>2.84</v>
+        <v>2.36</v>
       </c>
       <c r="AH135" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AI135" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AJ135" t="n">
-        <v>3.74</v>
+        <v>3.1</v>
       </c>
       <c r="AK135" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AL135" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="AM135" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AN135" t="n">
-        <v>2.19</v>
+        <v>1.8</v>
       </c>
       <c r="AO135" t="n">
-        <v>2.19</v>
+        <v>2.48</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AR135" t="n">
-        <v>3.09</v>
+        <v>2.62</v>
       </c>
       <c r="AS135" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="AT135" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AU135" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX135" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA135" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BB135" t="n">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="BC135" t="n">
         <v>0</v>
       </c>
       <c r="BD135" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="BE135" t="n">
         <v>0</v>
       </c>
       <c r="BF135" t="n">
-        <v>12383</v>
+        <v>4236</v>
       </c>
       <c r="BG135" t="n">
         <v>-1</v>
@@ -61055,10 +61055,10 @@
         <v>-1</v>
       </c>
       <c r="BO135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ135" t="n">
         <v>2</v>
@@ -61067,7 +61067,7 @@
         <v>1</v>
       </c>
       <c r="BS135" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT135" t="n">
         <v>3</v>
@@ -61076,37 +61076,37 @@
         <v>1</v>
       </c>
       <c r="BV135" t="n">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="BW135" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="BX135" t="n">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="BY135" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="BZ135" t="n">
-        <v>1.45</v>
+        <v>1.77</v>
       </c>
       <c r="CA135" t="n">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="CB135" t="n">
-        <v>3.16</v>
+        <v>3.89</v>
       </c>
       <c r="CC135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG135" t="n">
         <v>0</v>
@@ -61124,7 +61124,7 @@
         <v>0</v>
       </c>
       <c r="CL135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM135" t="n">
         <v>-1</v>
@@ -61133,7 +61133,7 @@
         <v>-1</v>
       </c>
       <c r="CO135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP135" t="n">
         <v>0</v>
@@ -61142,73 +61142,73 @@
         <v>1</v>
       </c>
       <c r="CR135" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="CS135" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="CT135" t="n">
         <v>1</v>
       </c>
       <c r="CU135" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CV135" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="CW135" t="n">
         <v>1</v>
       </c>
       <c r="CX135" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CY135" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CZ135" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="DA135" t="n">
         <v>72</v>
       </c>
       <c r="DB135" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="DC135" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="DD135" t="n">
-        <v>1.33</v>
+        <v>1.9</v>
       </c>
       <c r="DE135" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="DF135" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="DG135" t="n">
-        <v>1.63</v>
+        <v>1.14</v>
       </c>
       <c r="DH135" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DI135" t="n">
-        <v>1.94</v>
+        <v>1.25</v>
       </c>
       <c r="DJ135" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DK135" t="n">
         <v>29</v>
       </c>
       <c r="DL135" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="DM135" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="DN135" t="n">
-        <v>2.93</v>
+        <v>3.07</v>
       </c>
       <c r="DO135" t="n">
         <v>19</v>
@@ -61223,7 +61223,7 @@
         <v>1</v>
       </c>
       <c r="DS135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT135" t="b">
         <v>0</v>
@@ -61236,17 +61236,17 @@
       </c>
       <c r="DW135" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="DX135" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="DY135" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="DZ135" t="inlineStr"/>
@@ -61255,47 +61255,47 @@
       <c r="EC135" t="inlineStr"/>
       <c r="ED135" t="inlineStr">
         <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="EE135" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EF135" t="inlineStr">
+        <is>
+          <t>3.53</t>
+        </is>
+      </c>
+      <c r="EG135" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EH135" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EI135" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EJ135" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EK135" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EL135" t="inlineStr">
+        <is>
           <t>2.54</t>
-        </is>
-      </c>
-      <c r="EE135" t="inlineStr">
-        <is>
-          <t>2.86</t>
-        </is>
-      </c>
-      <c r="EF135" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="EG135" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="EH135" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="EI135" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="EJ135" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="EK135" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EL135" t="inlineStr">
-        <is>
-          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -62098,7 +62098,7 @@
         <v>94</v>
       </c>
       <c r="DD137" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DE137" t="n">
         <v>0.33</v>
@@ -62131,7 +62131,7 @@
         <v>2.13</v>
       </c>
       <c r="DO137" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP137" t="b">
         <v>0</v>
@@ -62546,7 +62546,7 @@
         <v>76</v>
       </c>
       <c r="DD138" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DE138" t="n">
         <v>0.44</v>
@@ -62579,7 +62579,7 @@
         <v>2.95</v>
       </c>
       <c r="DO138" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP138" t="b">
         <v>1</v>
@@ -63455,7 +63455,7 @@
         <v>3.01</v>
       </c>
       <c r="DO140" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP140" t="b">
         <v>1</v>
@@ -64746,7 +64746,7 @@
         <v>83</v>
       </c>
       <c r="DD143" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DE143" t="n">
         <v>1.9</v>
@@ -64779,7 +64779,7 @@
         <v>2.47</v>
       </c>
       <c r="DO143" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP143" t="b">
         <v>1</v>
@@ -65205,7 +65205,7 @@
         <v>2.11</v>
       </c>
       <c r="DE144" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DF144" t="n">
         <v>2</v>
@@ -65235,7 +65235,7 @@
         <v>2.2</v>
       </c>
       <c r="DO144" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP144" t="b">
         <v>1</v>
@@ -65645,7 +65645,7 @@
         <v>2.45</v>
       </c>
       <c r="DE145" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DF145" t="n">
         <v>2.33</v>
@@ -65675,7 +65675,7 @@
         <v>3.37</v>
       </c>
       <c r="DO145" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP145" t="b">
         <v>1</v>
@@ -66698,7 +66698,7 @@
         <v>0</v>
       </c>
       <c r="P148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q148" t="n">
         <v>6</v>
@@ -66707,16 +66707,16 @@
         <v>4</v>
       </c>
       <c r="S148" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T148" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U148" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V148" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W148" t="n">
         <v>16</v>
@@ -66725,10 +66725,10 @@
         <v>15</v>
       </c>
       <c r="Y148" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Z148" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
@@ -66744,7 +66744,7 @@
         <v>2</v>
       </c>
       <c r="AD148" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE148" t="n">
         <v>1.61</v>
@@ -66864,13 +66864,13 @@
         <v>1</v>
       </c>
       <c r="BR148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS148" t="n">
         <v>4</v>
       </c>
       <c r="BT148" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BU148" t="n">
         <v>1</v>
@@ -66882,19 +66882,19 @@
         <v>38</v>
       </c>
       <c r="BX148" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="BY148" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="BZ148" t="n">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="CA148" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="CB148" t="n">
-        <v>3.35</v>
+        <v>3.47</v>
       </c>
       <c r="CC148" t="n">
         <v>1</v>
@@ -66951,10 +66951,10 @@
         <v>1</v>
       </c>
       <c r="CU148" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="CV148" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="CW148" t="n">
         <v>1</v>
@@ -67155,10 +67155,10 @@
         <v>3</v>
       </c>
       <c r="K149" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L149" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M149" t="n">
         <v>1</v>
@@ -68032,6 +68032,1358 @@
       <c r="EL150" t="inlineStr">
         <is>
           <t>1.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>19</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Dinamo Moskva</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Krylya Sovetov</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="n">
+        <v>46082.41666666666</v>
+      </c>
+      <c r="G151" t="n">
+        <v>4</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" t="n">
+        <v>4</v>
+      </c>
+      <c r="J151" t="n">
+        <v>3</v>
+      </c>
+      <c r="K151" t="n">
+        <v>5</v>
+      </c>
+      <c r="L151" t="n">
+        <v>8</v>
+      </c>
+      <c r="M151" t="n">
+        <v>1</v>
+      </c>
+      <c r="N151" t="n">
+        <v>2</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>5</v>
+      </c>
+      <c r="R151" t="n">
+        <v>1</v>
+      </c>
+      <c r="S151" t="n">
+        <v>8</v>
+      </c>
+      <c r="T151" t="n">
+        <v>6</v>
+      </c>
+      <c r="U151" t="n">
+        <v>13</v>
+      </c>
+      <c r="V151" t="n">
+        <v>7</v>
+      </c>
+      <c r="W151" t="n">
+        <v>8</v>
+      </c>
+      <c r="X151" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA151" t="inlineStr"/>
+      <c r="AB151" t="inlineStr"/>
+      <c r="AC151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD151" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF151" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AG151" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="AH151" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI151" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ151" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AK151" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL151" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM151" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN151" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AO151" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AP151" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ151" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR151" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AS151" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AT151" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AU151" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV151" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA151" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB151" t="n">
+        <v>935</v>
+      </c>
+      <c r="BC151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD151" t="n">
+        <v>59</v>
+      </c>
+      <c r="BE151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF151" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG151" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI151" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ151" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK151" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL151" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM151" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN151" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP151" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS151" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV151" t="n">
+        <v>49</v>
+      </c>
+      <c r="BW151" t="n">
+        <v>29</v>
+      </c>
+      <c r="BX151" t="n">
+        <v>94</v>
+      </c>
+      <c r="BY151" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ151" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CA151" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="CB151" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="CC151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM151" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN151" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR151" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS151" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU151" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV151" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX151" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY151" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ151" t="n">
+        <v>64</v>
+      </c>
+      <c r="DA151" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB151" t="n">
+        <v>37</v>
+      </c>
+      <c r="DC151" t="n">
+        <v>90</v>
+      </c>
+      <c r="DD151" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE151" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="DF151" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG151" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH151" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DI151" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DJ151" t="n">
+        <v>36</v>
+      </c>
+      <c r="DK151" t="n">
+        <v>11</v>
+      </c>
+      <c r="DL151" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DM151" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="DN151" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="DO151" t="n">
+        <v>19</v>
+      </c>
+      <c r="DP151" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ151" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR151" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS151" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT151" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU151" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV151" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW151" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="DX151" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="DY151" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="DZ151" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EA151" t="inlineStr"/>
+      <c r="EB151" t="inlineStr"/>
+      <c r="EC151" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="ED151" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EE151" t="inlineStr">
+        <is>
+          <t>7.02</t>
+        </is>
+      </c>
+      <c r="EF151" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="EG151" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EH151" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EI151" t="inlineStr"/>
+      <c r="EJ151" t="inlineStr"/>
+      <c r="EK151" t="inlineStr"/>
+      <c r="EL151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>19</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Akhmat Grozny</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>CSKA Moskva</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="n">
+        <v>46082.66666666666</v>
+      </c>
+      <c r="G152" t="n">
+        <v>1</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" t="n">
+        <v>1</v>
+      </c>
+      <c r="J152" t="n">
+        <v>5</v>
+      </c>
+      <c r="K152" t="n">
+        <v>7</v>
+      </c>
+      <c r="L152" t="n">
+        <v>12</v>
+      </c>
+      <c r="M152" t="n">
+        <v>3</v>
+      </c>
+      <c r="N152" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>6</v>
+      </c>
+      <c r="R152" t="n">
+        <v>5</v>
+      </c>
+      <c r="S152" t="n">
+        <v>11</v>
+      </c>
+      <c r="T152" t="n">
+        <v>16</v>
+      </c>
+      <c r="U152" t="n">
+        <v>17</v>
+      </c>
+      <c r="V152" t="n">
+        <v>21</v>
+      </c>
+      <c r="W152" t="n">
+        <v>14</v>
+      </c>
+      <c r="X152" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>35</v>
+      </c>
+      <c r="Z152" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>Akhmat Arena</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
+        </is>
+      </c>
+      <c r="AC152" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AF152" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AG152" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH152" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI152" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AJ152" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AK152" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AL152" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM152" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN152" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO152" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AP152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ152" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR152" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AS152" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AT152" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU152" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV152" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA152" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB152" t="n">
+        <v>923</v>
+      </c>
+      <c r="BC152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD152" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF152" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG152" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH152" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI152" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ152" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK152" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL152" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM152" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN152" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ152" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT152" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU152" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV152" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW152" t="n">
+        <v>60</v>
+      </c>
+      <c r="BX152" t="n">
+        <v>69</v>
+      </c>
+      <c r="BY152" t="n">
+        <v>110</v>
+      </c>
+      <c r="BZ152" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CA152" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="CB152" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="CC152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI152" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ152" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK152" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM152" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN152" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ152" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR152" t="n">
+        <v>3</v>
+      </c>
+      <c r="CS152" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT152" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU152" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV152" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW152" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX152" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY152" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ152" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA152" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB152" t="n">
+        <v>22</v>
+      </c>
+      <c r="DC152" t="n">
+        <v>78</v>
+      </c>
+      <c r="DD152" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DE152" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DF152" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DG152" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DH152" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DI152" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ152" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK152" t="n">
+        <v>33</v>
+      </c>
+      <c r="DL152" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DM152" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="DN152" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="DO152" t="n">
+        <v>19</v>
+      </c>
+      <c r="DP152" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ152" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR152" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS152" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT152" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU152" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV152" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW152" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="DX152" t="inlineStr">
+        <is>
+          <t>3.57</t>
+        </is>
+      </c>
+      <c r="DY152" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="DZ152" t="inlineStr"/>
+      <c r="EA152" t="inlineStr"/>
+      <c r="EB152" t="inlineStr"/>
+      <c r="EC152" t="inlineStr"/>
+      <c r="ED152" t="inlineStr">
+        <is>
+          <t>2.96</t>
+        </is>
+      </c>
+      <c r="EE152" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="EF152" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
+      <c r="EG152" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EH152" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EI152" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EJ152" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EK152" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EL152" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>19</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>FK Sochi</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Spartak Moskva</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="n">
+        <v>46083.5</v>
+      </c>
+      <c r="G153" t="n">
+        <v>2</v>
+      </c>
+      <c r="H153" t="n">
+        <v>3</v>
+      </c>
+      <c r="I153" t="n">
+        <v>5</v>
+      </c>
+      <c r="J153" t="n">
+        <v>4</v>
+      </c>
+      <c r="K153" t="n">
+        <v>6</v>
+      </c>
+      <c r="L153" t="n">
+        <v>10</v>
+      </c>
+      <c r="M153" t="n">
+        <v>5</v>
+      </c>
+      <c r="N153" t="n">
+        <v>3</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>4</v>
+      </c>
+      <c r="R153" t="n">
+        <v>5</v>
+      </c>
+      <c r="S153" t="n">
+        <v>5</v>
+      </c>
+      <c r="T153" t="n">
+        <v>11</v>
+      </c>
+      <c r="U153" t="n">
+        <v>9</v>
+      </c>
+      <c r="V153" t="n">
+        <v>16</v>
+      </c>
+      <c r="W153" t="n">
+        <v>15</v>
+      </c>
+      <c r="X153" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>39</v>
+      </c>
+      <c r="Z153" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>Olimpiyskiy Stadion Fisht</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>Olimpiyskiy prospekt, Sochi</t>
+        </is>
+      </c>
+      <c r="AC153" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD153" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE153" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AF153" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG153" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AH153" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI153" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AJ153" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AK153" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AL153" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM153" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN153" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AO153" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AP153" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AQ153" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR153" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AS153" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AT153" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AU153" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX153" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY153" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ153" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA153" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB153" t="n">
+        <v>924</v>
+      </c>
+      <c r="BC153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD153" t="n">
+        <v>60</v>
+      </c>
+      <c r="BE153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF153" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG153" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH153" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI153" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ153" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK153" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL153" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM153" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN153" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO153" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ153" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR153" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS153" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT153" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU153" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV153" t="n">
+        <v>31</v>
+      </c>
+      <c r="BW153" t="n">
+        <v>63</v>
+      </c>
+      <c r="BX153" t="n">
+        <v>68</v>
+      </c>
+      <c r="BY153" t="n">
+        <v>107</v>
+      </c>
+      <c r="BZ153" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="CA153" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CB153" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="CC153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM153" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN153" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR153" t="n">
+        <v>11</v>
+      </c>
+      <c r="CS153" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU153" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV153" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX153" t="n">
+        <v>18</v>
+      </c>
+      <c r="CY153" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ153" t="n">
+        <v>60</v>
+      </c>
+      <c r="DA153" t="n">
+        <v>83</v>
+      </c>
+      <c r="DB153" t="n">
+        <v>30</v>
+      </c>
+      <c r="DC153" t="n">
+        <v>76</v>
+      </c>
+      <c r="DD153" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DE153" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DF153" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="DG153" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH153" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DI153" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="DJ153" t="n">
+        <v>41</v>
+      </c>
+      <c r="DK153" t="n">
+        <v>18</v>
+      </c>
+      <c r="DL153" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="DM153" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DN153" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="DO153" t="n">
+        <v>19</v>
+      </c>
+      <c r="DP153" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ153" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR153" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS153" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT153" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU153" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV153" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW153" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="DX153" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="DY153" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="DZ153" t="inlineStr"/>
+      <c r="EA153" t="inlineStr"/>
+      <c r="EB153" t="inlineStr"/>
+      <c r="EC153" t="inlineStr"/>
+      <c r="ED153" t="inlineStr">
+        <is>
+          <t>6.65</t>
+        </is>
+      </c>
+      <c r="EE153" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EF153" t="inlineStr">
+        <is>
+          <t>4.41</t>
+        </is>
+      </c>
+      <c r="EG153" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EH153" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EI153" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EJ153" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EK153" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EL153" t="inlineStr">
+        <is>
+          <t>2.35</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
+++ b/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
@@ -66701,7 +66701,7 @@
         <v>2</v>
       </c>
       <c r="Q148" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R148" t="n">
         <v>4</v>
@@ -66710,13 +66710,13 @@
         <v>14</v>
       </c>
       <c r="T148" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U148" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V148" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="W148" t="n">
         <v>16</v>
@@ -66888,10 +66888,10 @@
         <v>76</v>
       </c>
       <c r="BZ148" t="n">
-        <v>2.03</v>
+        <v>2.16</v>
       </c>
       <c r="CA148" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="CB148" t="n">
         <v>3.47</v>

--- a/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
+++ b/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL153" headerRowCount="1">
-  <autoFilter ref="A1:EL153"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL155" headerRowCount="1">
+  <autoFilter ref="A1:EL155"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL153"/>
+  <dimension ref="A1:EL155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.8" customWidth="1" min="1" max="1"/>
@@ -1769,7 +1769,7 @@
         <v>1.5</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -2637,7 +2637,7 @@
         <v>2.33</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE6" t="n">
         <v>2</v>
@@ -5769,7 +5769,7 @@
         <v>2.1</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DF11" t="n">
         <v>3</v>
@@ -8910,7 +8910,7 @@
         <v>50</v>
       </c>
       <c r="DD18" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE18" t="n">
         <v>0.45</v>
@@ -9366,7 +9366,7 @@
         <v>100</v>
       </c>
       <c r="DD19" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE19" t="n">
         <v>1.9</v>
@@ -12005,7 +12005,7 @@
         <v>1.89</v>
       </c>
       <c r="DE25" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DF25" t="n">
         <v>1</v>
@@ -12941,7 +12941,7 @@
         <v>1.5</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DF27" t="n">
         <v>3</v>
@@ -15626,7 +15626,7 @@
         <v>50</v>
       </c>
       <c r="DD33" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE33" t="n">
         <v>0.6</v>
@@ -15659,7 +15659,7 @@
         <v>3.03</v>
       </c>
       <c r="DO33" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -18725,7 +18725,7 @@
         <v>2.45</v>
       </c>
       <c r="DE40" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DF40" t="n">
         <v>1.5</v>
@@ -19162,7 +19162,7 @@
         <v>75</v>
       </c>
       <c r="DD41" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE41" t="n">
         <v>0.33</v>
@@ -22757,7 +22757,7 @@
         <v>0.5</v>
       </c>
       <c r="DE49" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DF49" t="n">
         <v>0.5</v>
@@ -22787,7 +22787,7 @@
         <v>2.7</v>
       </c>
       <c r="DO49" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24093,7 +24093,7 @@
         <v>2.1</v>
       </c>
       <c r="DE52" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DF52" t="n">
         <v>1.33</v>
@@ -24530,7 +24530,7 @@
         <v>75</v>
       </c>
       <c r="DD53" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE53" t="n">
         <v>0.67</v>
@@ -24965,7 +24965,7 @@
         <v>0.89</v>
       </c>
       <c r="DE54" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DF54" t="n">
         <v>0.67</v>
@@ -27222,7 +27222,7 @@
         <v>100</v>
       </c>
       <c r="DD59" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE59" t="n">
         <v>0.44</v>
@@ -28981,7 +28981,7 @@
         <v>1.5</v>
       </c>
       <c r="DE63" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DF63" t="n">
         <v>1.33</v>
@@ -29906,7 +29906,7 @@
         <v>67</v>
       </c>
       <c r="DD65" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE65" t="n">
         <v>1.1</v>
@@ -30346,7 +30346,7 @@
         <v>100</v>
       </c>
       <c r="DD66" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE66" t="n">
         <v>0.67</v>
@@ -32599,7 +32599,7 @@
         <v>2.46</v>
       </c>
       <c r="DO71" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP71" t="b">
         <v>0</v>
@@ -35306,7 +35306,7 @@
         <v>75</v>
       </c>
       <c r="DD77" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE77" t="n">
         <v>2</v>
@@ -36189,7 +36189,7 @@
         <v>2.78</v>
       </c>
       <c r="DE79" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DF79" t="n">
         <v>2.5</v>
@@ -36629,7 +36629,7 @@
         <v>1.5</v>
       </c>
       <c r="DE80" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DF80" t="n">
         <v>2</v>
@@ -39771,7 +39771,7 @@
         <v>1.93</v>
       </c>
       <c r="DO87" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -41554,7 +41554,7 @@
         <v>100</v>
       </c>
       <c r="DD91" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE91" t="n">
         <v>1.3</v>
@@ -43821,7 +43821,7 @@
         <v>1.89</v>
       </c>
       <c r="DE96" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DF96" t="n">
         <v>2.17</v>
@@ -45150,7 +45150,7 @@
         <v>72</v>
       </c>
       <c r="DD99" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE99" t="n">
         <v>0.33</v>
@@ -46474,10 +46474,10 @@
         <v>77</v>
       </c>
       <c r="DD102" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE102" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DF102" t="n">
         <v>1</v>
@@ -46507,7 +46507,7 @@
         <v>3.07</v>
       </c>
       <c r="DO102" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP102" t="b">
         <v>0</v>
@@ -47793,7 +47793,7 @@
         <v>1.9</v>
       </c>
       <c r="DE105" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DF105" t="n">
         <v>2</v>
@@ -50018,7 +50018,7 @@
         <v>75</v>
       </c>
       <c r="DD110" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE110" t="n">
         <v>1.3</v>
@@ -50477,7 +50477,7 @@
         <v>1.1</v>
       </c>
       <c r="DE111" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DF111" t="n">
         <v>0.57</v>
@@ -52246,7 +52246,7 @@
         <v>77</v>
       </c>
       <c r="DD115" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE115" t="n">
         <v>0.6</v>
@@ -53155,7 +53155,7 @@
         <v>2.24</v>
       </c>
       <c r="DO117" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -55373,7 +55373,7 @@
         <v>0.89</v>
       </c>
       <c r="DE122" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DF122" t="n">
         <v>0.71</v>
@@ -55801,7 +55801,7 @@
         <v>1.1</v>
       </c>
       <c r="DE123" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DF123" t="n">
         <v>0.88</v>
@@ -57602,7 +57602,7 @@
         <v>63</v>
       </c>
       <c r="DD127" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE127" t="n">
         <v>1.56</v>
@@ -60403,176 +60403,176 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F134" s="2" t="n">
         <v>45991.5625</v>
       </c>
       <c r="G134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H134" t="n">
+        <v>1</v>
+      </c>
+      <c r="I134" t="n">
         <v>3</v>
       </c>
-      <c r="I134" t="n">
-        <v>4</v>
-      </c>
       <c r="J134" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K134" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L134" t="n">
+        <v>15</v>
+      </c>
+      <c r="M134" t="n">
+        <v>3</v>
+      </c>
+      <c r="N134" t="n">
+        <v>2</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
         <v>6</v>
       </c>
-      <c r="M134" t="n">
-        <v>2</v>
-      </c>
-      <c r="N134" t="n">
-        <v>1</v>
-      </c>
-      <c r="O134" t="n">
-        <v>0</v>
-      </c>
-      <c r="P134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q134" t="n">
-        <v>3</v>
-      </c>
       <c r="R134" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S134" t="n">
+        <v>11</v>
+      </c>
+      <c r="T134" t="n">
+        <v>18</v>
+      </c>
+      <c r="U134" t="n">
+        <v>17</v>
+      </c>
+      <c r="V134" t="n">
+        <v>23</v>
+      </c>
+      <c r="W134" t="n">
         <v>8</v>
-      </c>
-      <c r="T134" t="n">
-        <v>10</v>
-      </c>
-      <c r="U134" t="n">
-        <v>11</v>
-      </c>
-      <c r="V134" t="n">
-        <v>16</v>
-      </c>
-      <c r="W134" t="n">
-        <v>16</v>
       </c>
       <c r="X134" t="n">
         <v>13</v>
       </c>
       <c r="Y134" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="Z134" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>Stadion Central’nyj im. I.P. Chayka</t>
+          <t>Akhmat Arena</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>ul. Suvorova, Peschanokopskoye</t>
+          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
         </is>
       </c>
       <c r="AC134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE134" t="n">
-        <v>2.49</v>
+        <v>2.89</v>
       </c>
       <c r="AF134" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="AG134" t="n">
-        <v>2.84</v>
+        <v>2.36</v>
       </c>
       <c r="AH134" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AI134" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AJ134" t="n">
-        <v>3.74</v>
+        <v>3.1</v>
       </c>
       <c r="AK134" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AL134" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="AM134" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AN134" t="n">
-        <v>2.19</v>
+        <v>1.8</v>
       </c>
       <c r="AO134" t="n">
-        <v>2.19</v>
+        <v>2.48</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AQ134" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AR134" t="n">
-        <v>3.09</v>
+        <v>2.62</v>
       </c>
       <c r="AS134" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="AT134" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AU134" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BB134" t="n">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="BC134" t="n">
         <v>0</v>
       </c>
       <c r="BD134" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="BE134" t="n">
         <v>0</v>
       </c>
       <c r="BF134" t="n">
-        <v>12383</v>
+        <v>4236</v>
       </c>
       <c r="BG134" t="n">
         <v>-1</v>
@@ -60599,10 +60599,10 @@
         <v>-1</v>
       </c>
       <c r="BO134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ134" t="n">
         <v>2</v>
@@ -60611,7 +60611,7 @@
         <v>1</v>
       </c>
       <c r="BS134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT134" t="n">
         <v>3</v>
@@ -60620,37 +60620,37 @@
         <v>1</v>
       </c>
       <c r="BV134" t="n">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="BW134" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="BX134" t="n">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="BY134" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="BZ134" t="n">
-        <v>1.45</v>
+        <v>1.77</v>
       </c>
       <c r="CA134" t="n">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="CB134" t="n">
-        <v>3.16</v>
+        <v>3.89</v>
       </c>
       <c r="CC134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG134" t="n">
         <v>0</v>
@@ -60668,7 +60668,7 @@
         <v>0</v>
       </c>
       <c r="CL134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM134" t="n">
         <v>-1</v>
@@ -60677,7 +60677,7 @@
         <v>-1</v>
       </c>
       <c r="CO134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP134" t="n">
         <v>0</v>
@@ -60686,73 +60686,73 @@
         <v>1</v>
       </c>
       <c r="CR134" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="CS134" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="CT134" t="n">
         <v>1</v>
       </c>
       <c r="CU134" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CV134" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="CW134" t="n">
         <v>1</v>
       </c>
       <c r="CX134" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CY134" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CZ134" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="DA134" t="n">
         <v>72</v>
       </c>
       <c r="DB134" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="DC134" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="DD134" t="n">
-        <v>1.33</v>
+        <v>1.9</v>
       </c>
       <c r="DE134" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="DF134" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="DG134" t="n">
-        <v>1.63</v>
+        <v>1.14</v>
       </c>
       <c r="DH134" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DI134" t="n">
-        <v>1.94</v>
+        <v>1.25</v>
       </c>
       <c r="DJ134" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DK134" t="n">
         <v>29</v>
       </c>
       <c r="DL134" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="DM134" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="DN134" t="n">
-        <v>2.93</v>
+        <v>3.07</v>
       </c>
       <c r="DO134" t="n">
         <v>19</v>
@@ -60767,7 +60767,7 @@
         <v>1</v>
       </c>
       <c r="DS134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT134" t="b">
         <v>0</v>
@@ -60780,17 +60780,17 @@
       </c>
       <c r="DW134" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="DX134" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="DY134" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="DZ134" t="inlineStr"/>
@@ -60799,47 +60799,47 @@
       <c r="EC134" t="inlineStr"/>
       <c r="ED134" t="inlineStr">
         <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="EE134" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EF134" t="inlineStr">
+        <is>
+          <t>3.53</t>
+        </is>
+      </c>
+      <c r="EG134" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EH134" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EI134" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EJ134" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EK134" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EL134" t="inlineStr">
+        <is>
           <t>2.54</t>
-        </is>
-      </c>
-      <c r="EE134" t="inlineStr">
-        <is>
-          <t>2.86</t>
-        </is>
-      </c>
-      <c r="EF134" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="EG134" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="EH134" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="EI134" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="EJ134" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="EK134" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EL134" t="inlineStr">
-        <is>
-          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -60859,176 +60859,176 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F135" s="2" t="n">
         <v>45991.5625</v>
       </c>
       <c r="G135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I135" t="n">
+        <v>4</v>
+      </c>
+      <c r="J135" t="n">
+        <v>2</v>
+      </c>
+      <c r="K135" t="n">
+        <v>4</v>
+      </c>
+      <c r="L135" t="n">
+        <v>6</v>
+      </c>
+      <c r="M135" t="n">
+        <v>2</v>
+      </c>
+      <c r="N135" t="n">
+        <v>1</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
         <v>3</v>
       </c>
-      <c r="J135" t="n">
-        <v>7</v>
-      </c>
-      <c r="K135" t="n">
+      <c r="R135" t="n">
+        <v>6</v>
+      </c>
+      <c r="S135" t="n">
         <v>8</v>
       </c>
-      <c r="L135" t="n">
-        <v>15</v>
-      </c>
-      <c r="M135" t="n">
-        <v>3</v>
-      </c>
-      <c r="N135" t="n">
-        <v>2</v>
-      </c>
-      <c r="O135" t="n">
-        <v>0</v>
-      </c>
-      <c r="P135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q135" t="n">
-        <v>6</v>
-      </c>
-      <c r="R135" t="n">
-        <v>5</v>
-      </c>
-      <c r="S135" t="n">
+      <c r="T135" t="n">
+        <v>10</v>
+      </c>
+      <c r="U135" t="n">
         <v>11</v>
       </c>
-      <c r="T135" t="n">
-        <v>18</v>
-      </c>
-      <c r="U135" t="n">
-        <v>17</v>
-      </c>
       <c r="V135" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="W135" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X135" t="n">
         <v>13</v>
       </c>
       <c r="Y135" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="Z135" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>Akhmat Arena</t>
+          <t>Stadion Central’nyj im. I.P. Chayka</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
+          <t>ul. Suvorova, Peschanokopskoye</t>
         </is>
       </c>
       <c r="AC135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA135" t="n">
         <v>3</v>
       </c>
-      <c r="AD135" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE135" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AF135" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AG135" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AH135" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI135" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ135" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AK135" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AL135" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AM135" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AN135" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AO135" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AP135" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AQ135" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AR135" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AS135" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AT135" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AU135" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW135" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX135" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ135" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA135" t="n">
-        <v>1</v>
-      </c>
       <c r="BB135" t="n">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="BC135" t="n">
         <v>0</v>
       </c>
       <c r="BD135" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="BE135" t="n">
         <v>0</v>
       </c>
       <c r="BF135" t="n">
-        <v>4236</v>
+        <v>12383</v>
       </c>
       <c r="BG135" t="n">
         <v>-1</v>
@@ -61055,10 +61055,10 @@
         <v>-1</v>
       </c>
       <c r="BO135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ135" t="n">
         <v>2</v>
@@ -61067,7 +61067,7 @@
         <v>1</v>
       </c>
       <c r="BS135" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT135" t="n">
         <v>3</v>
@@ -61076,37 +61076,37 @@
         <v>1</v>
       </c>
       <c r="BV135" t="n">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="BW135" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="BX135" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="BY135" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="BZ135" t="n">
-        <v>1.77</v>
+        <v>1.45</v>
       </c>
       <c r="CA135" t="n">
-        <v>2.12</v>
+        <v>1.71</v>
       </c>
       <c r="CB135" t="n">
-        <v>3.89</v>
+        <v>3.16</v>
       </c>
       <c r="CC135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG135" t="n">
         <v>0</v>
@@ -61124,7 +61124,7 @@
         <v>0</v>
       </c>
       <c r="CL135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM135" t="n">
         <v>-1</v>
@@ -61133,7 +61133,7 @@
         <v>-1</v>
       </c>
       <c r="CO135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP135" t="n">
         <v>0</v>
@@ -61142,73 +61142,73 @@
         <v>1</v>
       </c>
       <c r="CR135" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="CS135" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="CT135" t="n">
         <v>1</v>
       </c>
       <c r="CU135" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CV135" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="CW135" t="n">
         <v>1</v>
       </c>
       <c r="CX135" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CY135" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CZ135" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="DA135" t="n">
         <v>72</v>
       </c>
       <c r="DB135" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="DC135" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="DD135" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DE135" t="n">
         <v>1.9</v>
       </c>
-      <c r="DE135" t="n">
-        <v>1</v>
-      </c>
       <c r="DF135" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="DG135" t="n">
-        <v>1.14</v>
+        <v>1.63</v>
       </c>
       <c r="DH135" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="DI135" t="n">
-        <v>1.25</v>
+        <v>1.94</v>
       </c>
       <c r="DJ135" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="DK135" t="n">
         <v>29</v>
       </c>
       <c r="DL135" t="n">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="DM135" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="DN135" t="n">
-        <v>3.07</v>
+        <v>2.93</v>
       </c>
       <c r="DO135" t="n">
         <v>19</v>
@@ -61223,7 +61223,7 @@
         <v>1</v>
       </c>
       <c r="DS135" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT135" t="b">
         <v>0</v>
@@ -61236,17 +61236,17 @@
       </c>
       <c r="DW135" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="DX135" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="DY135" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="DZ135" t="inlineStr"/>
@@ -61255,47 +61255,47 @@
       <c r="EC135" t="inlineStr"/>
       <c r="ED135" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="EE135" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="EF135" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="EG135" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EH135" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EI135" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="EJ135" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EK135" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EL135" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -62994,7 +62994,7 @@
         <v>63</v>
       </c>
       <c r="DD139" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE139" t="n">
         <v>0.6</v>
@@ -66097,7 +66097,7 @@
         <v>2.8</v>
       </c>
       <c r="DE146" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DF146" t="n">
         <v>2.78</v>
@@ -69384,6 +69384,918 @@
       <c r="EL153" t="inlineStr">
         <is>
           <t>2.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>20</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Rostov</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Baltika</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="n">
+        <v>46088.57291666666</v>
+      </c>
+      <c r="G154" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" t="n">
+        <v>1</v>
+      </c>
+      <c r="I154" t="n">
+        <v>2</v>
+      </c>
+      <c r="J154" t="n">
+        <v>4</v>
+      </c>
+      <c r="K154" t="n">
+        <v>2</v>
+      </c>
+      <c r="L154" t="n">
+        <v>6</v>
+      </c>
+      <c r="M154" t="n">
+        <v>0</v>
+      </c>
+      <c r="N154" t="n">
+        <v>4</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>3</v>
+      </c>
+      <c r="R154" t="n">
+        <v>4</v>
+      </c>
+      <c r="S154" t="n">
+        <v>12</v>
+      </c>
+      <c r="T154" t="n">
+        <v>3</v>
+      </c>
+      <c r="U154" t="n">
+        <v>15</v>
+      </c>
+      <c r="V154" t="n">
+        <v>7</v>
+      </c>
+      <c r="W154" t="n">
+        <v>9</v>
+      </c>
+      <c r="X154" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>Stadion Central’nyj im. I.P. Chayka</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>ul. Suvorova, Peschanokopskoye</t>
+        </is>
+      </c>
+      <c r="AC154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI154" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ154" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AK154" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AL154" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AM154" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AN154" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AO154" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AP154" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AQ154" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AR154" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AS154" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AT154" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AU154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB154" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD154" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF154" t="n">
+        <v>6950</v>
+      </c>
+      <c r="BG154" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI154" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ154" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK154" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL154" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM154" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN154" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR154" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT154" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV154" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW154" t="n">
+        <v>37</v>
+      </c>
+      <c r="BX154" t="n">
+        <v>103</v>
+      </c>
+      <c r="BY154" t="n">
+        <v>101</v>
+      </c>
+      <c r="BZ154" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CA154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB154" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="CC154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM154" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN154" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR154" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS154" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU154" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV154" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX154" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY154" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ154" t="n">
+        <v>21</v>
+      </c>
+      <c r="DA154" t="n">
+        <v>58</v>
+      </c>
+      <c r="DB154" t="n">
+        <v>16</v>
+      </c>
+      <c r="DC154" t="n">
+        <v>53</v>
+      </c>
+      <c r="DD154" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DE154" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DF154" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG154" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DH154" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DI154" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="DJ154" t="n">
+        <v>79</v>
+      </c>
+      <c r="DK154" t="n">
+        <v>42</v>
+      </c>
+      <c r="DL154" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="DM154" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DN154" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="DO154" t="n">
+        <v>20</v>
+      </c>
+      <c r="DP154" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ154" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR154" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS154" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT154" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU154" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV154" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW154" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="DX154" t="inlineStr">
+        <is>
+          <t>5.39</t>
+        </is>
+      </c>
+      <c r="DY154" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="DZ154" t="inlineStr"/>
+      <c r="EA154" t="inlineStr"/>
+      <c r="EB154" t="inlineStr"/>
+      <c r="EC154" t="inlineStr"/>
+      <c r="ED154" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="EE154" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="EF154" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="EG154" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="EH154" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EI154" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="EJ154" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EK154" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EL154" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>20</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Olimpiyets</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>FK Sochi</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="n">
+        <v>46088.66666666666</v>
+      </c>
+      <c r="G155" t="n">
+        <v>2</v>
+      </c>
+      <c r="H155" t="n">
+        <v>1</v>
+      </c>
+      <c r="I155" t="n">
+        <v>3</v>
+      </c>
+      <c r="J155" t="n">
+        <v>8</v>
+      </c>
+      <c r="K155" t="n">
+        <v>1</v>
+      </c>
+      <c r="L155" t="n">
+        <v>9</v>
+      </c>
+      <c r="M155" t="n">
+        <v>2</v>
+      </c>
+      <c r="N155" t="n">
+        <v>1</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>6</v>
+      </c>
+      <c r="R155" t="n">
+        <v>3</v>
+      </c>
+      <c r="S155" t="n">
+        <v>13</v>
+      </c>
+      <c r="T155" t="n">
+        <v>2</v>
+      </c>
+      <c r="U155" t="n">
+        <v>19</v>
+      </c>
+      <c r="V155" t="n">
+        <v>5</v>
+      </c>
+      <c r="W155" t="n">
+        <v>11</v>
+      </c>
+      <c r="X155" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>Stadion Nizhny Novgorod</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>ul. Dolzhanskaya, Nizhniy Novgorod</t>
+        </is>
+      </c>
+      <c r="AC155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI155" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AK155" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL155" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM155" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN155" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ155" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR155" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AS155" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AT155" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU155" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ155" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB155" t="n">
+        <v>1482</v>
+      </c>
+      <c r="BC155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD155" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF155" t="n">
+        <v>4246</v>
+      </c>
+      <c r="BG155" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI155" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ155" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK155" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL155" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM155" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN155" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT155" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV155" t="n">
+        <v>62</v>
+      </c>
+      <c r="BW155" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX155" t="n">
+        <v>127</v>
+      </c>
+      <c r="BY155" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ155" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CA155" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="CB155" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="CC155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM155" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN155" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR155" t="n">
+        <v>34</v>
+      </c>
+      <c r="CS155" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU155" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV155" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX155" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY155" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ155" t="n">
+        <v>61</v>
+      </c>
+      <c r="DA155" t="n">
+        <v>78</v>
+      </c>
+      <c r="DB155" t="n">
+        <v>28</v>
+      </c>
+      <c r="DC155" t="n">
+        <v>56</v>
+      </c>
+      <c r="DD155" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DE155" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DF155" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DG155" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="DH155" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="DI155" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="DJ155" t="n">
+        <v>39</v>
+      </c>
+      <c r="DK155" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL155" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DM155" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DN155" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="DO155" t="n">
+        <v>20</v>
+      </c>
+      <c r="DP155" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ155" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR155" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS155" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT155" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU155" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV155" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW155" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="DX155" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="DY155" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="DZ155" t="inlineStr"/>
+      <c r="EA155" t="inlineStr"/>
+      <c r="EB155" t="inlineStr"/>
+      <c r="EC155" t="inlineStr"/>
+      <c r="ED155" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EE155" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="EF155" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="EG155" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EH155" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EI155" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EJ155" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EK155" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EL155" t="inlineStr">
+        <is>
+          <t>2.29</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
+++ b/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL155" headerRowCount="1">
-  <autoFilter ref="A1:EL155"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL161" headerRowCount="1">
+  <autoFilter ref="A1:EL161"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL155"/>
+  <dimension ref="A1:EL161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.8" customWidth="1" min="1" max="1"/>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2634,7 +2634,7 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="DE4" t="n">
         <v>0.4</v>
@@ -2667,7 +2667,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3082,10 +3082,10 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3549,7 +3549,7 @@
         <v>1.1</v>
       </c>
       <c r="DE6" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3579,7 +3579,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4043,7 +4043,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4471,7 +4471,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -4894,7 +4894,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DE9" t="n">
         <v>1.1</v>
@@ -4927,7 +4927,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP9" t="b">
         <v>0</v>
@@ -5326,7 +5326,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE10" t="n">
         <v>0.6</v>
@@ -5359,7 +5359,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5766,7 +5766,7 @@
         <v>100</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="DE11" t="n">
         <v>1.55</v>
@@ -5799,7 +5799,7 @@
         <v>2.56</v>
       </c>
       <c r="DO11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6247,7 +6247,7 @@
         <v>2.72</v>
       </c>
       <c r="DO12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6683,7 +6683,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7117,7 +7117,7 @@
         <v>0.5</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -7147,7 +7147,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7542,10 +7542,10 @@
         <v>0</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="DF15" t="n">
         <v>0</v>
@@ -7575,7 +7575,7 @@
         <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8014,10 +8014,10 @@
         <v>50</v>
       </c>
       <c r="DD16" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DF16" t="n">
         <v>1</v>
@@ -8047,7 +8047,7 @@
         <v>1.72</v>
       </c>
       <c r="DO16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8470,10 +8470,10 @@
         <v>0</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -8503,7 +8503,7 @@
         <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -8943,7 +8943,7 @@
         <v>1.28</v>
       </c>
       <c r="DO18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9047,70 +9047,70 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
         <v>45871.72916666666</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>5</v>
+      </c>
+      <c r="M19" t="n">
+        <v>4</v>
+      </c>
+      <c r="N19" t="n">
         <v>3</v>
       </c>
-      <c r="I19" t="n">
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>5</v>
       </c>
-      <c r="J19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K19" t="n">
-        <v>7</v>
-      </c>
-      <c r="L19" t="n">
-        <v>11</v>
-      </c>
-      <c r="M19" t="n">
-        <v>5</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>10</v>
-      </c>
       <c r="R19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
+        <v>13</v>
+      </c>
+      <c r="T19" t="n">
         <v>3</v>
       </c>
-      <c r="T19" t="n">
-        <v>8</v>
-      </c>
       <c r="U19" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="V19" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="W19" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="X19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y19" t="n">
         <v>56</v>
@@ -9120,91 +9120,91 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Akhmat Arena</t>
+          <t>Stadion FK Krasnodar</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
+          <t>ul. Vostochno-Kruglikovskaya 126, Krasnodar</t>
         </is>
       </c>
       <c r="AC19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE19" t="n">
-        <v>5.84</v>
+        <v>1.81</v>
       </c>
       <c r="AF19" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.65</v>
+        <v>3.54</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AU19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="BC19" t="n">
         <v>0</v>
@@ -9243,46 +9243,46 @@
         <v>-1</v>
       </c>
       <c r="BO19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ19" t="n">
         <v>3</v>
       </c>
       <c r="BR19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BS19" t="n">
         <v>3</v>
       </c>
       <c r="BT19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BU19" t="n">
         <v>1</v>
       </c>
       <c r="BV19" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="BW19" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="BX19" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="BY19" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.54</v>
+        <v>0.45</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.43</v>
+        <v>2.43</v>
       </c>
       <c r="CC19" t="n">
         <v>0</v>
@@ -9324,64 +9324,64 @@
         <v>0</v>
       </c>
       <c r="CP19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ19" t="n">
         <v>1</v>
       </c>
       <c r="CR19" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="CS19" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="CT19" t="n">
         <v>1</v>
       </c>
       <c r="CU19" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="CV19" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="CW19" t="n">
         <v>1</v>
       </c>
       <c r="CX19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CY19" t="n">
         <v>7</v>
       </c>
       <c r="CZ19" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DA19" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DB19" t="n">
         <v>0</v>
       </c>
       <c r="DC19" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DD19" t="n">
-        <v>1.1</v>
+        <v>2.45</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="DF19" t="n">
         <v>0</v>
       </c>
       <c r="DG19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DH19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="DI19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DJ19" t="n">
         <v>0</v>
@@ -9390,62 +9390,82 @@
         <v>0</v>
       </c>
       <c r="DL19" t="n">
-        <v>1.17</v>
+        <v>1.82</v>
       </c>
       <c r="DM19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="DN19" t="n">
-        <v>2.42</v>
+        <v>1.82</v>
       </c>
       <c r="DO19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
       </c>
       <c r="DQ19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU19" t="b">
         <v>0</v>
       </c>
       <c r="DV19" t="b">
-        <v>1</v>
-      </c>
-      <c r="DW19" t="inlineStr"/>
-      <c r="DX19" t="inlineStr"/>
-      <c r="DY19" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="DW19" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="DX19" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="DY19" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
       <c r="DZ19" t="inlineStr"/>
       <c r="EA19" t="inlineStr"/>
       <c r="EB19" t="inlineStr"/>
       <c r="EC19" t="inlineStr"/>
       <c r="ED19" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="EE19" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="EF19" t="inlineStr">
         <is>
-          <t>4.32</t>
-        </is>
-      </c>
-      <c r="EG19" t="inlineStr"/>
-      <c r="EH19" t="inlineStr"/>
+          <t>3.69</t>
+        </is>
+      </c>
+      <c r="EG19" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EH19" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
       <c r="EI19" t="inlineStr"/>
       <c r="EJ19" t="inlineStr"/>
       <c r="EK19" t="inlineStr"/>
@@ -9467,70 +9487,70 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
         <v>45871.72916666666</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" t="n">
+        <v>7</v>
+      </c>
+      <c r="L20" t="n">
+        <v>11</v>
+      </c>
+      <c r="M20" t="n">
         <v>5</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>5</v>
-      </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>4</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>10</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6</v>
+      </c>
+      <c r="S20" t="n">
         <v>3</v>
       </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>5</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
+        <v>8</v>
+      </c>
+      <c r="U20" t="n">
         <v>13</v>
       </c>
-      <c r="T20" t="n">
-        <v>3</v>
-      </c>
-      <c r="U20" t="n">
-        <v>18</v>
-      </c>
       <c r="V20" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="W20" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="X20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y20" t="n">
         <v>56</v>
@@ -9540,91 +9560,91 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Stadion FK Krasnodar</t>
+          <t>Akhmat Arena</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>ul. Vostochno-Kruglikovskaya 126, Krasnodar</t>
+          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
         </is>
       </c>
       <c r="AC20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD20" t="n">
         <v>4</v>
       </c>
-      <c r="AD20" t="n">
-        <v>3</v>
-      </c>
       <c r="AE20" t="n">
-        <v>1.81</v>
+        <v>5.84</v>
       </c>
       <c r="AF20" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.54</v>
+        <v>1.65</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AV20" t="n">
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB20" t="n">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="BC20" t="n">
         <v>0</v>
@@ -9663,46 +9683,46 @@
         <v>-1</v>
       </c>
       <c r="BO20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ20" t="n">
         <v>3</v>
       </c>
       <c r="BR20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BS20" t="n">
         <v>3</v>
       </c>
       <c r="BT20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BU20" t="n">
         <v>1</v>
       </c>
       <c r="BV20" t="n">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="BW20" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="BX20" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="BY20" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="CA20" t="n">
-        <v>0.45</v>
+        <v>1.54</v>
       </c>
       <c r="CB20" t="n">
-        <v>2.43</v>
+        <v>3.43</v>
       </c>
       <c r="CC20" t="n">
         <v>0</v>
@@ -9744,64 +9764,64 @@
         <v>0</v>
       </c>
       <c r="CP20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ20" t="n">
         <v>1</v>
       </c>
       <c r="CR20" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="CS20" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="CT20" t="n">
         <v>1</v>
       </c>
       <c r="CU20" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="CV20" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="CW20" t="n">
         <v>1</v>
       </c>
       <c r="CX20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="CY20" t="n">
         <v>7</v>
       </c>
       <c r="CZ20" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DA20" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DB20" t="n">
         <v>0</v>
       </c>
       <c r="DC20" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DD20" t="n">
-        <v>2.45</v>
+        <v>1.1</v>
       </c>
       <c r="DE20" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="DF20" t="n">
         <v>0</v>
       </c>
       <c r="DG20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DH20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="DI20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DJ20" t="n">
         <v>0</v>
@@ -9810,82 +9830,62 @@
         <v>0</v>
       </c>
       <c r="DL20" t="n">
-        <v>1.82</v>
+        <v>1.17</v>
       </c>
       <c r="DM20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="DN20" t="n">
-        <v>1.82</v>
+        <v>2.42</v>
       </c>
       <c r="DO20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
       </c>
       <c r="DQ20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU20" t="b">
         <v>0</v>
       </c>
       <c r="DV20" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW20" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="DX20" t="inlineStr">
-        <is>
-          <t>2.82</t>
-        </is>
-      </c>
-      <c r="DY20" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="DW20" t="inlineStr"/>
+      <c r="DX20" t="inlineStr"/>
+      <c r="DY20" t="inlineStr"/>
       <c r="DZ20" t="inlineStr"/>
       <c r="EA20" t="inlineStr"/>
       <c r="EB20" t="inlineStr"/>
       <c r="EC20" t="inlineStr"/>
       <c r="ED20" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="EE20" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EF20" t="inlineStr">
         <is>
-          <t>3.69</t>
-        </is>
-      </c>
-      <c r="EG20" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
-      <c r="EH20" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
+          <t>4.32</t>
+        </is>
+      </c>
+      <c r="EG20" t="inlineStr"/>
+      <c r="EH20" t="inlineStr"/>
       <c r="EI20" t="inlineStr"/>
       <c r="EJ20" t="inlineStr"/>
       <c r="EK20" t="inlineStr"/>
@@ -10251,7 +10251,7 @@
         <v>1.95</v>
       </c>
       <c r="DO21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -10707,7 +10707,7 @@
         <v>0</v>
       </c>
       <c r="DO22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11151,7 +11151,7 @@
         <v>3.96</v>
       </c>
       <c r="DO23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -11577,7 +11577,7 @@
         <v>1.5</v>
       </c>
       <c r="DE24" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="DF24" t="n">
         <v>0</v>
@@ -11607,7 +11607,7 @@
         <v>1.08</v>
       </c>
       <c r="DO24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12002,7 +12002,7 @@
         <v>50</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="DE25" t="n">
         <v>0.4</v>
@@ -12035,7 +12035,7 @@
         <v>2.16</v>
       </c>
       <c r="DO25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12477,7 +12477,7 @@
         <v>1.5</v>
       </c>
       <c r="DE26" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DF26" t="n">
         <v>3</v>
@@ -12507,7 +12507,7 @@
         <v>1.97</v>
       </c>
       <c r="DO26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -12938,7 +12938,7 @@
         <v>25</v>
       </c>
       <c r="DD27" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE27" t="n">
         <v>1.55</v>
@@ -12971,7 +12971,7 @@
         <v>3.01</v>
       </c>
       <c r="DO27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13382,7 +13382,7 @@
         <v>100</v>
       </c>
       <c r="DD28" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="DE28" t="n">
         <v>0.6</v>
@@ -13415,7 +13415,7 @@
         <v>2.04</v>
       </c>
       <c r="DO28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -13834,7 +13834,7 @@
         <v>0</v>
       </c>
       <c r="DD29" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="DE29" t="n">
         <v>1.22</v>
@@ -13867,7 +13867,7 @@
         <v>3.23</v>
       </c>
       <c r="DO29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14293,7 +14293,7 @@
         <v>1.9</v>
       </c>
       <c r="DE30" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DF30" t="n">
         <v>0</v>
@@ -14323,7 +14323,7 @@
         <v>3.75</v>
       </c>
       <c r="DO30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -14734,10 +14734,10 @@
         <v>50</v>
       </c>
       <c r="DD31" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DE31" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DF31" t="n">
         <v>1</v>
@@ -14767,7 +14767,7 @@
         <v>2.03</v>
       </c>
       <c r="DO31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15177,7 +15177,7 @@
         <v>0.5</v>
       </c>
       <c r="DE32" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF32" t="n">
         <v>0</v>
@@ -15207,7 +15207,7 @@
         <v>1.95</v>
       </c>
       <c r="DO32" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16087,7 +16087,7 @@
         <v>2.73</v>
       </c>
       <c r="DO34" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -16474,10 +16474,10 @@
         <v>75</v>
       </c>
       <c r="DD35" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="DE35" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DF35" t="n">
         <v>1.5</v>
@@ -16507,7 +16507,7 @@
         <v>2.48</v>
       </c>
       <c r="DO35" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -16979,7 +16979,7 @@
         <v>2.73</v>
       </c>
       <c r="DO36" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -17427,7 +17427,7 @@
         <v>2.97</v>
       </c>
       <c r="DO37" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -17834,7 +17834,7 @@
         <v>100</v>
       </c>
       <c r="DD38" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="DE38" t="n">
         <v>0.9</v>
@@ -17867,7 +17867,7 @@
         <v>2.06</v>
       </c>
       <c r="DO38" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -18315,7 +18315,7 @@
         <v>2.78</v>
       </c>
       <c r="DO39" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -18755,7 +18755,7 @@
         <v>2.87</v>
       </c>
       <c r="DO40" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -19165,7 +19165,7 @@
         <v>1.1</v>
       </c>
       <c r="DE41" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DF41" t="n">
         <v>0</v>
@@ -19195,7 +19195,7 @@
         <v>2.54</v>
       </c>
       <c r="DO41" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -19610,10 +19610,10 @@
         <v>50</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DE42" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="DF42" t="n">
         <v>0.67</v>
@@ -19643,7 +19643,7 @@
         <v>2.35</v>
       </c>
       <c r="DO42" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -20066,7 +20066,7 @@
         <v>59</v>
       </c>
       <c r="DD43" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="DE43" t="n">
         <v>1.22</v>
@@ -20099,7 +20099,7 @@
         <v>2.55</v>
       </c>
       <c r="DO43" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -20517,7 +20517,7 @@
         <v>2.8</v>
       </c>
       <c r="DE44" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DF44" t="n">
         <v>2</v>
@@ -20547,7 +20547,7 @@
         <v>3.11</v>
       </c>
       <c r="DO44" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -20962,7 +20962,7 @@
         <v>59</v>
       </c>
       <c r="DD45" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="DE45" t="n">
         <v>0.9</v>
@@ -20995,7 +20995,7 @@
         <v>2.4</v>
       </c>
       <c r="DO45" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -21459,7 +21459,7 @@
         <v>2.53</v>
       </c>
       <c r="DO46" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -21858,10 +21858,10 @@
         <v>50</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE47" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DF47" t="n">
         <v>2</v>
@@ -21891,7 +21891,7 @@
         <v>2.33</v>
       </c>
       <c r="DO47" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -22314,10 +22314,10 @@
         <v>100</v>
       </c>
       <c r="DD48" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="DE48" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DF48" t="n">
         <v>3</v>
@@ -22347,7 +22347,7 @@
         <v>3.02</v>
       </c>
       <c r="DO48" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -23210,7 +23210,7 @@
         <v>63</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DE50" t="n">
         <v>0.6</v>
@@ -23243,7 +23243,7 @@
         <v>2.38</v>
       </c>
       <c r="DO50" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -23675,7 +23675,7 @@
         <v>2.54</v>
       </c>
       <c r="DO51" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -24090,7 +24090,7 @@
         <v>50</v>
       </c>
       <c r="DD52" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="DE52" t="n">
         <v>0.4</v>
@@ -24123,7 +24123,7 @@
         <v>2</v>
       </c>
       <c r="DO52" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -24533,7 +24533,7 @@
         <v>1.3</v>
       </c>
       <c r="DE53" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="DF53" t="n">
         <v>1.5</v>
@@ -24563,7 +24563,7 @@
         <v>3.04</v>
       </c>
       <c r="DO53" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -24995,7 +24995,7 @@
         <v>3.31</v>
       </c>
       <c r="DO54" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -25410,7 +25410,7 @@
         <v>84</v>
       </c>
       <c r="DD55" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="DE55" t="n">
         <v>0.45</v>
@@ -25443,7 +25443,7 @@
         <v>2.77</v>
       </c>
       <c r="DO55" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -25854,10 +25854,10 @@
         <v>84</v>
       </c>
       <c r="DD56" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="DE56" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DF56" t="n">
         <v>3</v>
@@ -25887,7 +25887,7 @@
         <v>3.14</v>
       </c>
       <c r="DO56" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -26313,7 +26313,7 @@
         <v>1.5</v>
       </c>
       <c r="DE57" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF57" t="n">
         <v>2</v>
@@ -26343,7 +26343,7 @@
         <v>2.24</v>
       </c>
       <c r="DO57" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -26766,10 +26766,10 @@
         <v>63</v>
       </c>
       <c r="DD58" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="DE58" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DF58" t="n">
         <v>1.75</v>
@@ -26799,7 +26799,7 @@
         <v>2.53</v>
       </c>
       <c r="DO58" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -27255,7 +27255,7 @@
         <v>2.96</v>
       </c>
       <c r="DO59" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -27687,7 +27687,7 @@
         <v>3.31</v>
       </c>
       <c r="DO60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -28143,7 +28143,7 @@
         <v>2.92</v>
       </c>
       <c r="DO61" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -28561,7 +28561,7 @@
         <v>2.45</v>
       </c>
       <c r="DE62" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DF62" t="n">
         <v>2</v>
@@ -28591,7 +28591,7 @@
         <v>3.61</v>
       </c>
       <c r="DO62" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -28978,7 +28978,7 @@
         <v>59</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE63" t="n">
         <v>0.4</v>
@@ -29011,7 +29011,7 @@
         <v>1.8</v>
       </c>
       <c r="DO63" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -29437,7 +29437,7 @@
         <v>2.11</v>
       </c>
       <c r="DE64" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DF64" t="n">
         <v>2</v>
@@ -29467,7 +29467,7 @@
         <v>2.75</v>
       </c>
       <c r="DO64" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP64" t="b">
         <v>0</v>
@@ -29939,7 +29939,7 @@
         <v>3.14</v>
       </c>
       <c r="DO65" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -30349,7 +30349,7 @@
         <v>1.1</v>
       </c>
       <c r="DE66" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="DF66" t="n">
         <v>1.5</v>
@@ -30379,7 +30379,7 @@
         <v>2.54</v>
       </c>
       <c r="DO66" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -30815,7 +30815,7 @@
         <v>3</v>
       </c>
       <c r="DO67" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -31271,7 +31271,7 @@
         <v>2.38</v>
       </c>
       <c r="DO68" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -31694,10 +31694,10 @@
         <v>37</v>
       </c>
       <c r="DD69" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DE69" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF69" t="n">
         <v>0.8</v>
@@ -31727,7 +31727,7 @@
         <v>2.57</v>
       </c>
       <c r="DO69" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -32122,7 +32122,7 @@
         <v>88</v>
       </c>
       <c r="DD70" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="DE70" t="n">
         <v>0.45</v>
@@ -32155,7 +32155,7 @@
         <v>2.43</v>
       </c>
       <c r="DO70" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -33025,7 +33025,7 @@
         <v>2.45</v>
       </c>
       <c r="DE72" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DF72" t="n">
         <v>2.25</v>
@@ -33055,7 +33055,7 @@
         <v>3.42</v>
       </c>
       <c r="DO72" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -33511,7 +33511,7 @@
         <v>2.46</v>
       </c>
       <c r="DO73" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -33942,10 +33942,10 @@
         <v>38</v>
       </c>
       <c r="DD74" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE74" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF74" t="n">
         <v>1.75</v>
@@ -33975,7 +33975,7 @@
         <v>2.54</v>
       </c>
       <c r="DO74" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -34401,7 +34401,7 @@
         <v>1.9</v>
       </c>
       <c r="DE75" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DF75" t="n">
         <v>1.75</v>
@@ -34431,7 +34431,7 @@
         <v>2.91</v>
       </c>
       <c r="DO75" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -34834,7 +34834,7 @@
         <v>88</v>
       </c>
       <c r="DD76" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="DE76" t="n">
         <v>0.6</v>
@@ -34867,7 +34867,7 @@
         <v>3.09</v>
       </c>
       <c r="DO76" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -35309,7 +35309,7 @@
         <v>1.3</v>
       </c>
       <c r="DE77" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DF77" t="n">
         <v>1.75</v>
@@ -35339,7 +35339,7 @@
         <v>2.97</v>
       </c>
       <c r="DO77" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP77" t="b">
         <v>0</v>
@@ -35771,7 +35771,7 @@
         <v>3.2</v>
       </c>
       <c r="DO78" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -36186,7 +36186,7 @@
         <v>90</v>
       </c>
       <c r="DD79" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="DE79" t="n">
         <v>1.55</v>
@@ -36219,7 +36219,7 @@
         <v>3.14</v>
       </c>
       <c r="DO79" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -36659,7 +36659,7 @@
         <v>1.87</v>
       </c>
       <c r="DO80" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP80" t="b">
         <v>0</v>
@@ -37082,7 +37082,7 @@
         <v>53</v>
       </c>
       <c r="DD81" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="DE81" t="n">
         <v>0.6</v>
@@ -37115,7 +37115,7 @@
         <v>2.45</v>
       </c>
       <c r="DO81" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -37505,7 +37505,7 @@
         <v>0.89</v>
       </c>
       <c r="DE82" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DF82" t="n">
         <v>0.6</v>
@@ -37535,7 +37535,7 @@
         <v>2.79</v>
       </c>
       <c r="DO82" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -37950,7 +37950,7 @@
         <v>80</v>
       </c>
       <c r="DD83" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="DE83" t="n">
         <v>0.45</v>
@@ -37983,7 +37983,7 @@
         <v>2.19</v>
       </c>
       <c r="DO83" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -38393,7 +38393,7 @@
         <v>2.45</v>
       </c>
       <c r="DE84" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="DF84" t="n">
         <v>1.8</v>
@@ -38423,7 +38423,7 @@
         <v>3.27</v>
       </c>
       <c r="DO84" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -38855,7 +38855,7 @@
         <v>3.26</v>
       </c>
       <c r="DO85" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -39282,7 +39282,7 @@
         <v>47</v>
       </c>
       <c r="DD86" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DE86" t="n">
         <v>0.9</v>
@@ -39315,7 +39315,7 @@
         <v>2.29</v>
       </c>
       <c r="DO86" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -40194,7 +40194,7 @@
         <v>65</v>
       </c>
       <c r="DD88" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="DE88" t="n">
         <v>1.22</v>
@@ -40227,7 +40227,7 @@
         <v>3.03</v>
       </c>
       <c r="DO88" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -40653,7 +40653,7 @@
         <v>2.11</v>
       </c>
       <c r="DE89" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DF89" t="n">
         <v>1.5</v>
@@ -40683,7 +40683,7 @@
         <v>2.67</v>
       </c>
       <c r="DO89" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -41098,7 +41098,7 @@
         <v>80</v>
       </c>
       <c r="DD90" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE90" t="n">
         <v>0.44</v>
@@ -41131,7 +41131,7 @@
         <v>2.46</v>
       </c>
       <c r="DO90" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -41557,7 +41557,7 @@
         <v>1.1</v>
       </c>
       <c r="DE91" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DF91" t="n">
         <v>1.2</v>
@@ -41587,7 +41587,7 @@
         <v>2.66</v>
       </c>
       <c r="DO91" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -42010,7 +42010,7 @@
         <v>67</v>
       </c>
       <c r="DD92" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="DE92" t="n">
         <v>0.9</v>
@@ -42043,7 +42043,7 @@
         <v>2.78</v>
       </c>
       <c r="DO92" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -42457,7 +42457,7 @@
         <v>1.5</v>
       </c>
       <c r="DE93" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DF93" t="n">
         <v>1.8</v>
@@ -42487,7 +42487,7 @@
         <v>2.49</v>
       </c>
       <c r="DO93" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -42918,7 +42918,7 @@
         <v>70</v>
       </c>
       <c r="DD94" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="DE94" t="n">
         <v>1.1</v>
@@ -42951,7 +42951,7 @@
         <v>3.2</v>
       </c>
       <c r="DO94" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -43377,7 +43377,7 @@
         <v>0.5</v>
       </c>
       <c r="DE95" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DF95" t="n">
         <v>0.8</v>
@@ -43407,7 +43407,7 @@
         <v>2.32</v>
       </c>
       <c r="DO95" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -43818,7 +43818,7 @@
         <v>67</v>
       </c>
       <c r="DD96" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="DE96" t="n">
         <v>1.55</v>
@@ -43851,7 +43851,7 @@
         <v>2.71</v>
       </c>
       <c r="DO96" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -44253,7 +44253,7 @@
         <v>1.5</v>
       </c>
       <c r="DE97" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="DF97" t="n">
         <v>1.33</v>
@@ -44283,7 +44283,7 @@
         <v>3.18</v>
       </c>
       <c r="DO97" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -44706,7 +44706,7 @@
         <v>86</v>
       </c>
       <c r="DD98" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="DE98" t="n">
         <v>0.44</v>
@@ -44739,7 +44739,7 @@
         <v>2.97</v>
       </c>
       <c r="DO98" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -45153,7 +45153,7 @@
         <v>1.3</v>
       </c>
       <c r="DE99" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DF99" t="n">
         <v>1.6</v>
@@ -45183,7 +45183,7 @@
         <v>2.84</v>
       </c>
       <c r="DO99" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -45578,7 +45578,7 @@
         <v>92</v>
       </c>
       <c r="DD100" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="DE100" t="n">
         <v>0.45</v>
@@ -45611,7 +45611,7 @@
         <v>2.59</v>
       </c>
       <c r="DO100" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -46051,7 +46051,7 @@
         <v>2.97</v>
       </c>
       <c r="DO101" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -46897,7 +46897,7 @@
         <v>2.8</v>
       </c>
       <c r="DE103" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF103" t="n">
         <v>2.6</v>
@@ -46927,7 +46927,7 @@
         <v>3.41</v>
       </c>
       <c r="DO103" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -47383,7 +47383,7 @@
         <v>3.31</v>
       </c>
       <c r="DO104" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -47823,7 +47823,7 @@
         <v>2.37</v>
       </c>
       <c r="DO105" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -48230,7 +48230,7 @@
         <v>61</v>
       </c>
       <c r="DD106" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="DE106" t="n">
         <v>0.6</v>
@@ -48263,7 +48263,7 @@
         <v>2.66</v>
       </c>
       <c r="DO106" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -48699,7 +48699,7 @@
         <v>2.09</v>
       </c>
       <c r="DO107" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -49114,10 +49114,10 @@
         <v>61</v>
       </c>
       <c r="DD108" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="DE108" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF108" t="n">
         <v>1.86</v>
@@ -49147,7 +49147,7 @@
         <v>2.61</v>
       </c>
       <c r="DO108" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP108" t="b">
         <v>0</v>
@@ -49611,7 +49611,7 @@
         <v>3.47</v>
       </c>
       <c r="DO109" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -50021,7 +50021,7 @@
         <v>1.3</v>
       </c>
       <c r="DE110" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DF110" t="n">
         <v>1.5</v>
@@ -50051,7 +50051,7 @@
         <v>2.81</v>
       </c>
       <c r="DO110" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -50474,7 +50474,7 @@
         <v>36</v>
       </c>
       <c r="DD111" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DE111" t="n">
         <v>0.4</v>
@@ -50507,7 +50507,7 @@
         <v>2.03</v>
       </c>
       <c r="DO111" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -50917,7 +50917,7 @@
         <v>2.11</v>
       </c>
       <c r="DE112" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="DF112" t="n">
         <v>1.8</v>
@@ -50947,7 +50947,7 @@
         <v>2.57</v>
       </c>
       <c r="DO112" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -51403,7 +51403,7 @@
         <v>3.33</v>
       </c>
       <c r="DO113" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -51821,7 +51821,7 @@
         <v>1.5</v>
       </c>
       <c r="DE114" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DF114" t="n">
         <v>1.29</v>
@@ -51851,7 +51851,7 @@
         <v>3.16</v>
       </c>
       <c r="DO114" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP114" t="b">
         <v>1</v>
@@ -52279,7 +52279,7 @@
         <v>2.71</v>
       </c>
       <c r="DO115" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP115" t="b">
         <v>0</v>
@@ -52719,7 +52719,7 @@
         <v>2.74</v>
       </c>
       <c r="DO116" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP116" t="b">
         <v>1</v>
@@ -53570,10 +53570,10 @@
         <v>69</v>
       </c>
       <c r="DD118" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE118" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DF118" t="n">
         <v>1.33</v>
@@ -53603,7 +53603,7 @@
         <v>2.53</v>
       </c>
       <c r="DO118" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -54006,7 +54006,7 @@
         <v>75</v>
       </c>
       <c r="DD119" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="DE119" t="n">
         <v>0.44</v>
@@ -54039,7 +54039,7 @@
         <v>3.04</v>
       </c>
       <c r="DO119" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -54479,7 +54479,7 @@
         <v>3.17</v>
       </c>
       <c r="DO120" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -54921,7 +54921,7 @@
         <v>2.11</v>
       </c>
       <c r="DE121" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DF121" t="n">
         <v>2</v>
@@ -54951,7 +54951,7 @@
         <v>2.7</v>
       </c>
       <c r="DO121" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -55403,7 +55403,7 @@
         <v>2.2</v>
       </c>
       <c r="DO122" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -55798,7 +55798,7 @@
         <v>51</v>
       </c>
       <c r="DD123" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DE123" t="n">
         <v>1.55</v>
@@ -55831,7 +55831,7 @@
         <v>2.75</v>
       </c>
       <c r="DO123" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP123" t="b">
         <v>0</v>
@@ -56254,7 +56254,7 @@
         <v>67</v>
       </c>
       <c r="DD124" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="DE124" t="n">
         <v>1.1</v>
@@ -56287,7 +56287,7 @@
         <v>3.02</v>
       </c>
       <c r="DO124" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -56710,10 +56710,10 @@
         <v>82</v>
       </c>
       <c r="DD125" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="DE125" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="DF125" t="n">
         <v>1.75</v>
@@ -56743,7 +56743,7 @@
         <v>2.41</v>
       </c>
       <c r="DO125" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP125" t="b">
         <v>1</v>
@@ -57158,7 +57158,7 @@
         <v>54</v>
       </c>
       <c r="DD126" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE126" t="n">
         <v>0.9</v>
@@ -57191,7 +57191,7 @@
         <v>2.45</v>
       </c>
       <c r="DO126" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP126" t="b">
         <v>1</v>
@@ -57605,7 +57605,7 @@
         <v>1.1</v>
       </c>
       <c r="DE127" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DF127" t="n">
         <v>1</v>
@@ -57635,7 +57635,7 @@
         <v>2.81</v>
       </c>
       <c r="DO127" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP127" t="b">
         <v>1</v>
@@ -58053,7 +58053,7 @@
         <v>1.5</v>
       </c>
       <c r="DE128" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DF128" t="n">
         <v>1.13</v>
@@ -58083,7 +58083,7 @@
         <v>3.18</v>
       </c>
       <c r="DO128" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP128" t="b">
         <v>1</v>
@@ -58498,10 +58498,10 @@
         <v>64</v>
       </c>
       <c r="DD129" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="DE129" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DF129" t="n">
         <v>2.43</v>
@@ -58531,7 +58531,7 @@
         <v>3.02</v>
       </c>
       <c r="DO129" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP129" t="b">
         <v>1</v>
@@ -58967,7 +58967,7 @@
         <v>2.38</v>
       </c>
       <c r="DO130" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP130" t="b">
         <v>1</v>
@@ -59390,7 +59390,7 @@
         <v>73</v>
       </c>
       <c r="DD131" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="DE131" t="n">
         <v>0.44</v>
@@ -59423,7 +59423,7 @@
         <v>2.91</v>
       </c>
       <c r="DO131" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP131" t="b">
         <v>1</v>
@@ -59851,7 +59851,7 @@
         <v>2.78</v>
       </c>
       <c r="DO132" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP132" t="b">
         <v>1</v>
@@ -60299,7 +60299,7 @@
         <v>2.76</v>
       </c>
       <c r="DO133" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP133" t="b">
         <v>1</v>
@@ -60725,7 +60725,7 @@
         <v>1.9</v>
       </c>
       <c r="DE134" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF134" t="n">
         <v>1.43</v>
@@ -60755,7 +60755,7 @@
         <v>3.07</v>
       </c>
       <c r="DO134" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP134" t="b">
         <v>1</v>
@@ -61211,7 +61211,7 @@
         <v>2.93</v>
       </c>
       <c r="DO135" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP135" t="b">
         <v>1</v>
@@ -61659,7 +61659,7 @@
         <v>3.08</v>
       </c>
       <c r="DO136" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP136" t="b">
         <v>1</v>
@@ -62101,7 +62101,7 @@
         <v>0.5</v>
       </c>
       <c r="DE137" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DF137" t="n">
         <v>0.57</v>
@@ -62131,7 +62131,7 @@
         <v>2.13</v>
       </c>
       <c r="DO137" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP137" t="b">
         <v>0</v>
@@ -62579,7 +62579,7 @@
         <v>2.95</v>
       </c>
       <c r="DO138" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP138" t="b">
         <v>1</v>
@@ -63027,7 +63027,7 @@
         <v>2.63</v>
       </c>
       <c r="DO139" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP139" t="b">
         <v>1</v>
@@ -63422,10 +63422,10 @@
         <v>59</v>
       </c>
       <c r="DD140" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="DE140" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF140" t="n">
         <v>2.22</v>
@@ -63455,7 +63455,7 @@
         <v>3.01</v>
       </c>
       <c r="DO140" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP140" t="b">
         <v>1</v>
@@ -63845,7 +63845,7 @@
         <v>2.8</v>
       </c>
       <c r="DE141" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DF141" t="n">
         <v>2.75</v>
@@ -63875,7 +63875,7 @@
         <v>2.96</v>
       </c>
       <c r="DO141" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP141" t="b">
         <v>1</v>
@@ -64315,7 +64315,7 @@
         <v>2.35</v>
       </c>
       <c r="DO142" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP142" t="b">
         <v>1</v>
@@ -64779,7 +64779,7 @@
         <v>2.47</v>
       </c>
       <c r="DO143" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP143" t="b">
         <v>1</v>
@@ -64883,37 +64883,37 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F144" s="2" t="n">
         <v>45998.66666666666</v>
       </c>
       <c r="G144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H144" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I144" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J144" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K144" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L144" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="M144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N144" t="n">
         <v>3</v>
@@ -64922,25 +64922,25 @@
         <v>0</v>
       </c>
       <c r="P144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q144" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S144" t="n">
         <v>14</v>
       </c>
       <c r="T144" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U144" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="V144" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W144" t="n">
         <v>14</v>
@@ -64949,104 +64949,104 @@
         <v>14</v>
       </c>
       <c r="Y144" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Z144" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>Complexe Sportif Jean Bianchi 1</t>
+          <t>Stadion FK Krasnodar</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>21 Avenue Marechal Leclerc, Saint-André-les-Vergers</t>
+          <t>ul. Vostochno-Kruglikovskaya 126, Krasnodar</t>
         </is>
       </c>
       <c r="AC144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD144" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI144" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AJ144" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AK144" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL144" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AM144" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AO144" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AP144" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ144" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR144" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AS144" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AT144" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AU144" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX144" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ144" t="n">
         <v>3</v>
       </c>
-      <c r="AE144" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AF144" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AG144" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AH144" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI144" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AJ144" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AK144" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL144" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AM144" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AN144" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AO144" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AP144" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AQ144" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AR144" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AS144" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT144" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AU144" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV144" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ144" t="n">
-        <v>0</v>
-      </c>
       <c r="BA144" t="n">
         <v>2</v>
       </c>
       <c r="BB144" t="n">
-        <v>1493</v>
+        <v>926</v>
       </c>
       <c r="BC144" t="n">
         <v>0</v>
       </c>
       <c r="BD144" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="BE144" t="n">
         <v>0</v>
@@ -65079,55 +65079,55 @@
         <v>-1</v>
       </c>
       <c r="BO144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP144" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ144" t="n">
         <v>1</v>
       </c>
       <c r="BR144" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS144" t="n">
         <v>3</v>
       </c>
-      <c r="BS144" t="n">
-        <v>0</v>
-      </c>
       <c r="BT144" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BU144" t="n">
         <v>1</v>
       </c>
       <c r="BV144" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="BW144" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="BX144" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="BY144" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="BZ144" t="n">
-        <v>2.16</v>
+        <v>1.79</v>
       </c>
       <c r="CA144" t="n">
-        <v>0.61</v>
+        <v>0.97</v>
       </c>
       <c r="CB144" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CC144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD144" t="n">
         <v>0</v>
       </c>
       <c r="CE144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF144" t="n">
         <v>0</v>
@@ -65166,19 +65166,19 @@
         <v>1</v>
       </c>
       <c r="CR144" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="CS144" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="CT144" t="n">
         <v>1</v>
       </c>
       <c r="CU144" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="CV144" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="CW144" t="n">
         <v>1</v>
@@ -65187,55 +65187,55 @@
         <v>5</v>
       </c>
       <c r="CY144" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="CZ144" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="DA144" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="DB144" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="DC144" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="DD144" t="n">
-        <v>2.11</v>
+        <v>2.45</v>
       </c>
       <c r="DE144" t="n">
-        <v>0.45</v>
+        <v>1.1</v>
       </c>
       <c r="DF144" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="DG144" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.38</v>
       </c>
       <c r="DH144" t="n">
-        <v>1.88</v>
+        <v>2.18</v>
       </c>
       <c r="DI144" t="n">
-        <v>1</v>
+        <v>2.12</v>
       </c>
       <c r="DJ144" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="DK144" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="DL144" t="n">
-        <v>1.33</v>
+        <v>1.95</v>
       </c>
       <c r="DM144" t="n">
-        <v>0.87</v>
+        <v>1.42</v>
       </c>
       <c r="DN144" t="n">
-        <v>2.2</v>
+        <v>3.37</v>
       </c>
       <c r="DO144" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP144" t="b">
         <v>1</v>
@@ -65244,68 +65244,88 @@
         <v>1</v>
       </c>
       <c r="DR144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU144" t="b">
         <v>0</v>
       </c>
       <c r="DV144" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW144" t="inlineStr">
-        <is>
-          <t>2.23</t>
-        </is>
-      </c>
-      <c r="DX144" t="inlineStr">
-        <is>
-          <t>4.08</t>
-        </is>
-      </c>
-      <c r="DY144" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="DZ144" t="inlineStr"/>
-      <c r="EA144" t="inlineStr"/>
-      <c r="EB144" t="inlineStr"/>
-      <c r="EC144" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="DW144" t="inlineStr"/>
+      <c r="DX144" t="inlineStr"/>
+      <c r="DY144" t="inlineStr"/>
+      <c r="DZ144" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EA144" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EB144" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="EC144" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
       <c r="ED144" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="EE144" t="inlineStr">
         <is>
-          <t>7.60</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="EF144" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="EG144" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EH144" t="inlineStr">
         <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="EI144" t="inlineStr"/>
-      <c r="EJ144" t="inlineStr"/>
-      <c r="EK144" t="inlineStr"/>
-      <c r="EL144" t="inlineStr"/>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EI144" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EJ144" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EK144" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EL144" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -65323,37 +65343,37 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F145" s="2" t="n">
         <v>45998.66666666666</v>
       </c>
       <c r="G145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H145" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J145" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K145" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L145" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="M145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N145" t="n">
         <v>3</v>
@@ -65362,25 +65382,25 @@
         <v>0</v>
       </c>
       <c r="P145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S145" t="n">
         <v>14</v>
       </c>
       <c r="T145" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U145" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V145" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="W145" t="n">
         <v>14</v>
@@ -65389,185 +65409,185 @@
         <v>14</v>
       </c>
       <c r="Y145" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Z145" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>Stadion FK Krasnodar</t>
+          <t>Complexe Sportif Jean Bianchi 1</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>ul. Vostochno-Kruglikovskaya 126, Krasnodar</t>
+          <t>21 Avenue Marechal Leclerc, Saint-André-les-Vergers</t>
         </is>
       </c>
       <c r="AC145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD145" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF145" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI145" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AJ145" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AK145" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL145" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM145" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN145" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO145" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AP145" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ145" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR145" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS145" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT145" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU145" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV145" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA145" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB145" t="n">
+        <v>1493</v>
+      </c>
+      <c r="BC145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD145" t="n">
+        <v>47</v>
+      </c>
+      <c r="BE145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR145" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT145" t="n">
         <v>4</v>
       </c>
-      <c r="AE145" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AF145" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AG145" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH145" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AI145" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AJ145" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AK145" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AL145" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AM145" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AN145" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AO145" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AP145" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AQ145" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR145" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AS145" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AT145" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AU145" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV145" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW145" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX145" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY145" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ145" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA145" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB145" t="n">
-        <v>926</v>
-      </c>
-      <c r="BC145" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD145" t="n">
-        <v>41</v>
-      </c>
-      <c r="BE145" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF145" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BG145" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BH145" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI145" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BJ145" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BK145" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BL145" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BM145" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BN145" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BO145" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP145" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ145" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR145" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS145" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT145" t="n">
-        <v>3</v>
-      </c>
       <c r="BU145" t="n">
         <v>1</v>
       </c>
       <c r="BV145" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="BW145" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="BX145" t="n">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="BY145" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="BZ145" t="n">
-        <v>1.79</v>
+        <v>2.16</v>
       </c>
       <c r="CA145" t="n">
-        <v>0.97</v>
+        <v>0.61</v>
       </c>
       <c r="CB145" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CC145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD145" t="n">
         <v>0</v>
       </c>
       <c r="CE145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF145" t="n">
         <v>0</v>
@@ -65606,19 +65626,19 @@
         <v>1</v>
       </c>
       <c r="CR145" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="CS145" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="CT145" t="n">
         <v>1</v>
       </c>
       <c r="CU145" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="CV145" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="CW145" t="n">
         <v>1</v>
@@ -65627,55 +65647,55 @@
         <v>5</v>
       </c>
       <c r="CY145" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="CZ145" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="DA145" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="DB145" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="DC145" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="DD145" t="n">
-        <v>2.45</v>
+        <v>2.11</v>
       </c>
       <c r="DE145" t="n">
-        <v>1.1</v>
+        <v>0.45</v>
       </c>
       <c r="DF145" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="DG145" t="n">
-        <v>1.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DH145" t="n">
-        <v>2.18</v>
+        <v>1.88</v>
       </c>
       <c r="DI145" t="n">
-        <v>2.12</v>
+        <v>1</v>
       </c>
       <c r="DJ145" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="DK145" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="DL145" t="n">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="DM145" t="n">
-        <v>1.42</v>
+        <v>0.87</v>
       </c>
       <c r="DN145" t="n">
-        <v>3.37</v>
+        <v>2.2</v>
       </c>
       <c r="DO145" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP145" t="b">
         <v>1</v>
@@ -65684,88 +65704,68 @@
         <v>1</v>
       </c>
       <c r="DR145" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS145" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT145" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU145" t="b">
         <v>0</v>
       </c>
       <c r="DV145" t="b">
-        <v>1</v>
-      </c>
-      <c r="DW145" t="inlineStr"/>
-      <c r="DX145" t="inlineStr"/>
-      <c r="DY145" t="inlineStr"/>
-      <c r="DZ145" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="EA145" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="EB145" t="inlineStr">
-        <is>
-          <t>3.19</t>
-        </is>
-      </c>
-      <c r="EC145" t="inlineStr">
-        <is>
-          <t>2.74</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="DW145" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="DX145" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
+      </c>
+      <c r="DY145" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="DZ145" t="inlineStr"/>
+      <c r="EA145" t="inlineStr"/>
+      <c r="EB145" t="inlineStr"/>
+      <c r="EC145" t="inlineStr"/>
       <c r="ED145" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EE145" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>7.60</t>
         </is>
       </c>
       <c r="EF145" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="EG145" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EH145" t="inlineStr">
         <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="EI145" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EJ145" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
-      </c>
-      <c r="EK145" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="EL145" t="inlineStr">
-        <is>
-          <t>2.44</t>
-        </is>
-      </c>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="EI145" t="inlineStr"/>
+      <c r="EJ145" t="inlineStr"/>
+      <c r="EK145" t="inlineStr"/>
+      <c r="EL145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -66127,7 +66127,7 @@
         <v>3.19</v>
       </c>
       <c r="DO146" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP146" t="b">
         <v>1</v>
@@ -66538,10 +66538,10 @@
         <v>50</v>
       </c>
       <c r="DD147" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DE147" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DF147" t="n">
         <v>0.89</v>
@@ -66571,7 +66571,7 @@
         <v>2.46</v>
       </c>
       <c r="DO147" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP147" t="b">
         <v>1</v>
@@ -67011,7 +67011,7 @@
         <v>3.3</v>
       </c>
       <c r="DO148" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP148" t="b">
         <v>1</v>
@@ -67442,7 +67442,7 @@
         <v>65</v>
       </c>
       <c r="DD149" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="DE149" t="n">
         <v>0.6</v>
@@ -67475,7 +67475,7 @@
         <v>2.83</v>
       </c>
       <c r="DO149" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP149" t="b">
         <v>1</v>
@@ -67947,7 +67947,7 @@
         <v>2.37</v>
       </c>
       <c r="DO150" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP150" t="b">
         <v>1</v>
@@ -68395,7 +68395,7 @@
         <v>2.73</v>
       </c>
       <c r="DO151" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP151" t="b">
         <v>1</v>
@@ -68843,7 +68843,7 @@
         <v>2.95</v>
       </c>
       <c r="DO152" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP152" t="b">
         <v>1</v>
@@ -69299,7 +69299,7 @@
         <v>2.44</v>
       </c>
       <c r="DO153" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP153" t="b">
         <v>1</v>
@@ -69445,22 +69445,22 @@
         <v>0</v>
       </c>
       <c r="Q154" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R154" t="n">
         <v>4</v>
       </c>
       <c r="S154" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T154" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U154" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="V154" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W154" t="n">
         <v>9</v>
@@ -69469,10 +69469,10 @@
         <v>18</v>
       </c>
       <c r="Y154" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Z154" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
@@ -69620,25 +69620,25 @@
         <v>1</v>
       </c>
       <c r="BV154" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="BW154" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="BX154" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="BY154" t="n">
         <v>101</v>
       </c>
       <c r="BZ154" t="n">
-        <v>1.56</v>
+        <v>1.77</v>
       </c>
       <c r="CA154" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="CB154" t="n">
-        <v>2.56</v>
+        <v>2.91</v>
       </c>
       <c r="CC154" t="n">
         <v>0</v>
@@ -69686,7 +69686,7 @@
         <v>1</v>
       </c>
       <c r="CR154" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="CS154" t="n">
         <v>21</v>
@@ -69695,10 +69695,10 @@
         <v>1</v>
       </c>
       <c r="CU154" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="CV154" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CW154" t="n">
         <v>1</v>
@@ -69780,17 +69780,17 @@
       </c>
       <c r="DW154" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="DX154" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="DY154" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="DZ154" t="inlineStr"/>
@@ -69799,27 +69799,27 @@
       <c r="EC154" t="inlineStr"/>
       <c r="ED154" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="EE154" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="EF154" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="EG154" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EH154" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="EI154" t="inlineStr">
@@ -69834,12 +69834,12 @@
       </c>
       <c r="EK154" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EL154" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.93</t>
         </is>
       </c>
     </row>
@@ -69901,7 +69901,7 @@
         <v>0</v>
       </c>
       <c r="Q155" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R155" t="n">
         <v>3</v>
@@ -69913,7 +69913,7 @@
         <v>2</v>
       </c>
       <c r="U155" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V155" t="n">
         <v>5</v>
@@ -70082,19 +70082,19 @@
         <v>28</v>
       </c>
       <c r="BX155" t="n">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="BY155" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="BZ155" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="CA155" t="n">
         <v>0.74</v>
       </c>
       <c r="CB155" t="n">
-        <v>2.81</v>
+        <v>2.67</v>
       </c>
       <c r="CC155" t="n">
         <v>0</v>
@@ -70151,10 +70151,10 @@
         <v>1</v>
       </c>
       <c r="CU155" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CV155" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="CW155" t="n">
         <v>1</v>
@@ -70163,7 +70163,7 @@
         <v>6</v>
       </c>
       <c r="CY155" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CZ155" t="n">
         <v>61</v>
@@ -70236,17 +70236,17 @@
       </c>
       <c r="DW155" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="DX155" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="DY155" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="DZ155" t="inlineStr"/>
@@ -70255,49 +70255,2749 @@
       <c r="EC155" t="inlineStr"/>
       <c r="ED155" t="inlineStr">
         <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EE155" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="EF155" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="EG155" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EH155" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EI155" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EJ155" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EK155" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EL155" t="inlineStr">
+        <is>
           <t>2.28</t>
         </is>
       </c>
-      <c r="EE155" t="inlineStr">
-        <is>
-          <t>3.62</t>
-        </is>
-      </c>
-      <c r="EF155" t="inlineStr">
-        <is>
-          <t>3.14</t>
-        </is>
-      </c>
-      <c r="EG155" t="inlineStr">
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>20</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Orenburg</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Zenit</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="n">
+        <v>46089.375</v>
+      </c>
+      <c r="G156" t="n">
+        <v>2</v>
+      </c>
+      <c r="H156" t="n">
+        <v>1</v>
+      </c>
+      <c r="I156" t="n">
+        <v>3</v>
+      </c>
+      <c r="J156" t="n">
+        <v>8</v>
+      </c>
+      <c r="K156" t="n">
+        <v>5</v>
+      </c>
+      <c r="L156" t="n">
+        <v>13</v>
+      </c>
+      <c r="M156" t="n">
+        <v>2</v>
+      </c>
+      <c r="N156" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" t="n">
+        <v>0</v>
+      </c>
+      <c r="P156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>5</v>
+      </c>
+      <c r="R156" t="n">
+        <v>5</v>
+      </c>
+      <c r="S156" t="n">
+        <v>10</v>
+      </c>
+      <c r="T156" t="n">
+        <v>13</v>
+      </c>
+      <c r="U156" t="n">
+        <v>15</v>
+      </c>
+      <c r="V156" t="n">
+        <v>18</v>
+      </c>
+      <c r="W156" t="n">
+        <v>18</v>
+      </c>
+      <c r="X156" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z156" t="n">
+        <v>62</v>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>Stadion Gazovik</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>Tsvetnoy bulvar' 31, Rostoshi</t>
+        </is>
+      </c>
+      <c r="AC156" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="AF156" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AG156" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH156" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI156" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AJ156" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AK156" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AL156" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AM156" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN156" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO156" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AP156" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AQ156" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR156" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AS156" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AT156" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AU156" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX156" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ156" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA156" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB156" t="n">
+        <v>922</v>
+      </c>
+      <c r="BC156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD156" t="n">
+        <v>47</v>
+      </c>
+      <c r="BE156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF156" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG156" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH156" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI156" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ156" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK156" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL156" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM156" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN156" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ156" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT156" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU156" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV156" t="n">
+        <v>41</v>
+      </c>
+      <c r="BW156" t="n">
+        <v>41</v>
+      </c>
+      <c r="BX156" t="n">
+        <v>71</v>
+      </c>
+      <c r="BY156" t="n">
+        <v>69</v>
+      </c>
+      <c r="BZ156" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CA156" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CB156" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="CC156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI156" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ156" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM156" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN156" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ156" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR156" t="n">
+        <v>11</v>
+      </c>
+      <c r="CS156" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT156" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU156" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV156" t="n">
+        <v>19</v>
+      </c>
+      <c r="CW156" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX156" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY156" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ156" t="n">
+        <v>37</v>
+      </c>
+      <c r="DA156" t="n">
+        <v>69</v>
+      </c>
+      <c r="DB156" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC156" t="n">
+        <v>48</v>
+      </c>
+      <c r="DD156" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DE156" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DF156" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DG156" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DH156" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DI156" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="DJ156" t="n">
+        <v>64</v>
+      </c>
+      <c r="DK156" t="n">
+        <v>31</v>
+      </c>
+      <c r="DL156" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DM156" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DN156" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DO156" t="n">
+        <v>20</v>
+      </c>
+      <c r="DP156" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ156" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR156" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS156" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT156" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU156" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV156" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW156" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="DX156" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="DY156" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="DZ156" t="inlineStr"/>
+      <c r="EA156" t="inlineStr"/>
+      <c r="EB156" t="inlineStr"/>
+      <c r="EC156" t="inlineStr"/>
+      <c r="ED156" t="inlineStr">
+        <is>
+          <t>7.40</t>
+        </is>
+      </c>
+      <c r="EE156" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EF156" t="inlineStr">
+        <is>
+          <t>4.70</t>
+        </is>
+      </c>
+      <c r="EG156" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EH156" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EI156" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EJ156" t="inlineStr">
         <is>
           <t>1.92</t>
         </is>
       </c>
-      <c r="EH155" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="EI155" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
-      </c>
-      <c r="EJ155" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="EK155" t="inlineStr">
+      <c r="EK156" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EL156" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>20</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Krylya Sovetov</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Makhachkala</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="n">
+        <v>46089.47916666666</v>
+      </c>
+      <c r="G157" t="n">
+        <v>2</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
+      <c r="I157" t="n">
+        <v>2</v>
+      </c>
+      <c r="J157" t="n">
+        <v>6</v>
+      </c>
+      <c r="K157" t="n">
+        <v>7</v>
+      </c>
+      <c r="L157" t="n">
+        <v>13</v>
+      </c>
+      <c r="M157" t="n">
+        <v>1</v>
+      </c>
+      <c r="N157" t="n">
+        <v>1</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>4</v>
+      </c>
+      <c r="R157" t="n">
+        <v>3</v>
+      </c>
+      <c r="S157" t="n">
+        <v>4</v>
+      </c>
+      <c r="T157" t="n">
+        <v>6</v>
+      </c>
+      <c r="U157" t="n">
+        <v>8</v>
+      </c>
+      <c r="V157" t="n">
+        <v>9</v>
+      </c>
+      <c r="W157" t="n">
+        <v>16</v>
+      </c>
+      <c r="X157" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA157" t="inlineStr"/>
+      <c r="AB157" t="inlineStr"/>
+      <c r="AC157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AI157" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AJ157" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AK157" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AL157" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM157" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN157" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AO157" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AP157" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ157" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AR157" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS157" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT157" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AU157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA157" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB157" t="n">
+        <v>928</v>
+      </c>
+      <c r="BC157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD157" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF157" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG157" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH157" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI157" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ157" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK157" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL157" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM157" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN157" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP157" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ157" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS157" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT157" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU157" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV157" t="n">
+        <v>35</v>
+      </c>
+      <c r="BW157" t="n">
+        <v>35</v>
+      </c>
+      <c r="BX157" t="n">
+        <v>95</v>
+      </c>
+      <c r="BY157" t="n">
+        <v>106</v>
+      </c>
+      <c r="BZ157" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="CA157" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB157" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CC157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM157" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN157" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR157" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS157" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU157" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV157" t="n">
+        <v>20</v>
+      </c>
+      <c r="CW157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX157" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY157" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ157" t="n">
+        <v>24</v>
+      </c>
+      <c r="DA157" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB157" t="n">
+        <v>24</v>
+      </c>
+      <c r="DC157" t="n">
+        <v>71</v>
+      </c>
+      <c r="DD157" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DE157" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="DF157" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG157" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DH157" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DI157" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="DJ157" t="n">
+        <v>77</v>
+      </c>
+      <c r="DK157" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL157" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="DM157" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DN157" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="DO157" t="n">
+        <v>20</v>
+      </c>
+      <c r="DP157" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ157" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR157" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS157" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT157" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU157" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV157" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW157" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="DX157" t="inlineStr">
+        <is>
+          <t>6.63</t>
+        </is>
+      </c>
+      <c r="DY157" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="DZ157" t="inlineStr"/>
+      <c r="EA157" t="inlineStr"/>
+      <c r="EB157" t="inlineStr"/>
+      <c r="EC157" t="inlineStr"/>
+      <c r="ED157" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="EE157" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
+      <c r="EF157" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="EG157" t="inlineStr">
         <is>
           <t>1.61</t>
         </is>
       </c>
-      <c r="EL155" t="inlineStr">
-        <is>
-          <t>2.29</t>
-        </is>
-      </c>
+      <c r="EH157" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EI157" t="inlineStr"/>
+      <c r="EJ157" t="inlineStr"/>
+      <c r="EK157" t="inlineStr"/>
+      <c r="EL157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>20</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Krasnodar</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="n">
+        <v>46089.58333333334</v>
+      </c>
+      <c r="G158" t="n">
+        <v>2</v>
+      </c>
+      <c r="H158" t="n">
+        <v>1</v>
+      </c>
+      <c r="I158" t="n">
+        <v>3</v>
+      </c>
+      <c r="J158" t="n">
+        <v>1</v>
+      </c>
+      <c r="K158" t="n">
+        <v>2</v>
+      </c>
+      <c r="L158" t="n">
+        <v>3</v>
+      </c>
+      <c r="M158" t="n">
+        <v>3</v>
+      </c>
+      <c r="N158" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>4</v>
+      </c>
+      <c r="R158" t="n">
+        <v>3</v>
+      </c>
+      <c r="S158" t="n">
+        <v>3</v>
+      </c>
+      <c r="T158" t="n">
+        <v>4</v>
+      </c>
+      <c r="U158" t="n">
+        <v>7</v>
+      </c>
+      <c r="V158" t="n">
+        <v>7</v>
+      </c>
+      <c r="W158" t="n">
+        <v>17</v>
+      </c>
+      <c r="X158" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z158" t="n">
+        <v>62</v>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>Kazan' Arena</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>Prospekt Husaina Yamasheva 115a, Kazan'</t>
+        </is>
+      </c>
+      <c r="AC158" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG158" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH158" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI158" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ158" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AK158" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AL158" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AM158" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN158" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AO158" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AP158" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AQ158" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AR158" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AS158" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AT158" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU158" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ158" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA158" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB158" t="n">
+        <v>932</v>
+      </c>
+      <c r="BC158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD158" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF158" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG158" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH158" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI158" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ158" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK158" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL158" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM158" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN158" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO158" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ158" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS158" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT158" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU158" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV158" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW158" t="n">
+        <v>30</v>
+      </c>
+      <c r="BX158" t="n">
+        <v>96</v>
+      </c>
+      <c r="BY158" t="n">
+        <v>95</v>
+      </c>
+      <c r="BZ158" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CA158" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="CB158" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CC158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI158" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ158" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM158" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN158" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ158" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR158" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS158" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT158" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU158" t="n">
+        <v>26</v>
+      </c>
+      <c r="CV158" t="n">
+        <v>19</v>
+      </c>
+      <c r="CW158" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX158" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY158" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ158" t="n">
+        <v>29</v>
+      </c>
+      <c r="DA158" t="n">
+        <v>66</v>
+      </c>
+      <c r="DB158" t="n">
+        <v>36</v>
+      </c>
+      <c r="DC158" t="n">
+        <v>66</v>
+      </c>
+      <c r="DD158" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE158" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DF158" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DG158" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH158" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DI158" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="DJ158" t="n">
+        <v>71</v>
+      </c>
+      <c r="DK158" t="n">
+        <v>35</v>
+      </c>
+      <c r="DL158" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DM158" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DN158" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="DO158" t="n">
+        <v>20</v>
+      </c>
+      <c r="DP158" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ158" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR158" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS158" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT158" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU158" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV158" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW158" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="DX158" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="DY158" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="DZ158" t="inlineStr"/>
+      <c r="EA158" t="inlineStr"/>
+      <c r="EB158" t="inlineStr"/>
+      <c r="EC158" t="inlineStr"/>
+      <c r="ED158" t="inlineStr">
+        <is>
+          <t>5.89</t>
+        </is>
+      </c>
+      <c r="EE158" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EF158" t="inlineStr">
+        <is>
+          <t>3.64</t>
+        </is>
+      </c>
+      <c r="EG158" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EH158" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EI158" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EJ158" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EK158" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EL158" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>20</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>CSKA Moskva</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Dinamo Moskva</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="n">
+        <v>46089.6875</v>
+      </c>
+      <c r="G159" t="n">
+        <v>1</v>
+      </c>
+      <c r="H159" t="n">
+        <v>4</v>
+      </c>
+      <c r="I159" t="n">
+        <v>5</v>
+      </c>
+      <c r="J159" t="n">
+        <v>8</v>
+      </c>
+      <c r="K159" t="n">
+        <v>9</v>
+      </c>
+      <c r="L159" t="n">
+        <v>17</v>
+      </c>
+      <c r="M159" t="n">
+        <v>0</v>
+      </c>
+      <c r="N159" t="n">
+        <v>2</v>
+      </c>
+      <c r="O159" t="n">
+        <v>1</v>
+      </c>
+      <c r="P159" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>3</v>
+      </c>
+      <c r="R159" t="n">
+        <v>7</v>
+      </c>
+      <c r="S159" t="n">
+        <v>10</v>
+      </c>
+      <c r="T159" t="n">
+        <v>17</v>
+      </c>
+      <c r="U159" t="n">
+        <v>13</v>
+      </c>
+      <c r="V159" t="n">
+        <v>24</v>
+      </c>
+      <c r="W159" t="n">
+        <v>8</v>
+      </c>
+      <c r="X159" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>56</v>
+      </c>
+      <c r="Z159" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>VEB Arena</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>3-ya Peschanaya ul., Moskva</t>
+        </is>
+      </c>
+      <c r="AC159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE159" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AF159" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG159" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AH159" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI159" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AJ159" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AK159" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL159" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AM159" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN159" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AO159" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AP159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ159" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR159" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AS159" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT159" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AU159" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX159" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ159" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA159" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB159" t="n">
+        <v>935</v>
+      </c>
+      <c r="BC159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD159" t="n">
+        <v>62</v>
+      </c>
+      <c r="BE159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF159" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG159" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH159" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI159" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ159" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK159" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL159" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM159" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN159" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO159" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP159" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR159" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS159" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT159" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU159" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV159" t="n">
+        <v>49</v>
+      </c>
+      <c r="BW159" t="n">
+        <v>49</v>
+      </c>
+      <c r="BX159" t="n">
+        <v>106</v>
+      </c>
+      <c r="BY159" t="n">
+        <v>82</v>
+      </c>
+      <c r="BZ159" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CA159" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="CB159" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="CC159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI159" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ159" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM159" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN159" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ159" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR159" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS159" t="n">
+        <v>12</v>
+      </c>
+      <c r="CT159" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU159" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV159" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW159" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX159" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY159" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ159" t="n">
+        <v>44</v>
+      </c>
+      <c r="DA159" t="n">
+        <v>73</v>
+      </c>
+      <c r="DB159" t="n">
+        <v>39</v>
+      </c>
+      <c r="DC159" t="n">
+        <v>62</v>
+      </c>
+      <c r="DD159" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DE159" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DF159" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="DG159" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH159" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DI159" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="DJ159" t="n">
+        <v>56</v>
+      </c>
+      <c r="DK159" t="n">
+        <v>28</v>
+      </c>
+      <c r="DL159" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="DM159" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DN159" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="DO159" t="n">
+        <v>20</v>
+      </c>
+      <c r="DP159" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ159" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR159" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS159" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT159" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU159" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV159" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW159" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="DX159" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="DY159" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="DZ159" t="inlineStr"/>
+      <c r="EA159" t="inlineStr"/>
+      <c r="EB159" t="inlineStr"/>
+      <c r="EC159" t="inlineStr"/>
+      <c r="ED159" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EE159" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="EF159" t="inlineStr">
+        <is>
+          <t>3.68</t>
+        </is>
+      </c>
+      <c r="EG159" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="EH159" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EI159" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EJ159" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EK159" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EL159" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>20</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Lokomotiv Moskva</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Akhmat Grozny</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="n">
+        <v>46090.5625</v>
+      </c>
+      <c r="G160" t="n">
+        <v>2</v>
+      </c>
+      <c r="H160" t="n">
+        <v>2</v>
+      </c>
+      <c r="I160" t="n">
+        <v>4</v>
+      </c>
+      <c r="J160" t="n">
+        <v>7</v>
+      </c>
+      <c r="K160" t="n">
+        <v>4</v>
+      </c>
+      <c r="L160" t="n">
+        <v>11</v>
+      </c>
+      <c r="M160" t="n">
+        <v>2</v>
+      </c>
+      <c r="N160" t="n">
+        <v>1</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
+      <c r="P160" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>4</v>
+      </c>
+      <c r="R160" t="n">
+        <v>3</v>
+      </c>
+      <c r="S160" t="n">
+        <v>7</v>
+      </c>
+      <c r="T160" t="n">
+        <v>3</v>
+      </c>
+      <c r="U160" t="n">
+        <v>11</v>
+      </c>
+      <c r="V160" t="n">
+        <v>6</v>
+      </c>
+      <c r="W160" t="n">
+        <v>24</v>
+      </c>
+      <c r="X160" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA160" t="inlineStr"/>
+      <c r="AB160" t="inlineStr"/>
+      <c r="AC160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AF160" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG160" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AH160" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI160" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AJ160" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AK160" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL160" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM160" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN160" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO160" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AP160" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ160" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR160" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AS160" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT160" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU160" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ160" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA160" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB160" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC160" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD160" t="n">
+        <v>56</v>
+      </c>
+      <c r="BE160" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF160" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG160" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH160" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI160" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ160" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK160" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL160" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM160" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN160" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO160" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP160" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ160" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR160" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS160" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT160" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU160" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV160" t="n">
+        <v>59</v>
+      </c>
+      <c r="BW160" t="n">
+        <v>35</v>
+      </c>
+      <c r="BX160" t="n">
+        <v>90</v>
+      </c>
+      <c r="BY160" t="n">
+        <v>81</v>
+      </c>
+      <c r="BZ160" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CA160" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="CB160" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="CC160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI160" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ160" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM160" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN160" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ160" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR160" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS160" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT160" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU160" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV160" t="n">
+        <v>25</v>
+      </c>
+      <c r="CW160" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX160" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY160" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ160" t="n">
+        <v>56</v>
+      </c>
+      <c r="DA160" t="n">
+        <v>78</v>
+      </c>
+      <c r="DB160" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC160" t="n">
+        <v>78</v>
+      </c>
+      <c r="DD160" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DE160" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DF160" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DG160" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DH160" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DI160" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DJ160" t="n">
+        <v>45</v>
+      </c>
+      <c r="DK160" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL160" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="DM160" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DN160" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="DO160" t="n">
+        <v>20</v>
+      </c>
+      <c r="DP160" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ160" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR160" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS160" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT160" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU160" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV160" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW160" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="DX160" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="DY160" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="DZ160" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EA160" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EB160" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="EC160" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="ED160" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EE160" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="EF160" t="inlineStr">
+        <is>
+          <t>4.13</t>
+        </is>
+      </c>
+      <c r="EG160" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="EH160" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EI160" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EJ160" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EK160" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EL160" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>20</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Spartak Moskva</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Akron</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="n">
+        <v>46090.66666666666</v>
+      </c>
+      <c r="G161" t="n">
+        <v>4</v>
+      </c>
+      <c r="H161" t="n">
+        <v>3</v>
+      </c>
+      <c r="I161" t="n">
+        <v>7</v>
+      </c>
+      <c r="J161" t="n">
+        <v>9</v>
+      </c>
+      <c r="K161" t="n">
+        <v>1</v>
+      </c>
+      <c r="L161" t="n">
+        <v>10</v>
+      </c>
+      <c r="M161" t="n">
+        <v>2</v>
+      </c>
+      <c r="N161" t="n">
+        <v>2</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>9</v>
+      </c>
+      <c r="R161" t="n">
+        <v>4</v>
+      </c>
+      <c r="S161" t="n">
+        <v>6</v>
+      </c>
+      <c r="T161" t="n">
+        <v>6</v>
+      </c>
+      <c r="U161" t="n">
+        <v>15</v>
+      </c>
+      <c r="V161" t="n">
+        <v>10</v>
+      </c>
+      <c r="W161" t="n">
+        <v>13</v>
+      </c>
+      <c r="X161" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>35</v>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>Otkrytiye Arena</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>Volokolamskoye shosse, Tushino, Moskva</t>
+        </is>
+      </c>
+      <c r="AC161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF161" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AG161" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AH161" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI161" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AJ161" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AK161" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AL161" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM161" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN161" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AO161" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AP161" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AQ161" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AR161" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AS161" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AT161" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AU161" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV161" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ161" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA161" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB161" t="n">
+        <v>924</v>
+      </c>
+      <c r="BC161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD161" t="n">
+        <v>45</v>
+      </c>
+      <c r="BE161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF161" t="n">
+        <v>17797</v>
+      </c>
+      <c r="BG161" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH161" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI161" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ161" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK161" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL161" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM161" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN161" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP161" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ161" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR161" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS161" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT161" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU161" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV161" t="n">
+        <v>54</v>
+      </c>
+      <c r="BW161" t="n">
+        <v>42</v>
+      </c>
+      <c r="BX161" t="n">
+        <v>103</v>
+      </c>
+      <c r="BY161" t="n">
+        <v>78</v>
+      </c>
+      <c r="BZ161" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CA161" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CB161" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="CC161" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD161" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE161" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF161" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG161" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH161" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI161" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ161" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK161" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL161" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM161" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN161" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO161" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP161" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ161" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR161" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS161" t="n">
+        <v>12</v>
+      </c>
+      <c r="CT161" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU161" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV161" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW161" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX161" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY161" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ161" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA161" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB161" t="n">
+        <v>35</v>
+      </c>
+      <c r="DC161" t="n">
+        <v>70</v>
+      </c>
+      <c r="DD161" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="DE161" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DF161" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="DG161" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DH161" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="DI161" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DJ161" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK161" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL161" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DM161" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DN161" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="DO161" t="n">
+        <v>20</v>
+      </c>
+      <c r="DP161" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ161" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR161" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS161" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT161" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU161" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV161" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW161" t="inlineStr"/>
+      <c r="DX161" t="inlineStr"/>
+      <c r="DY161" t="inlineStr"/>
+      <c r="DZ161" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EA161" t="inlineStr"/>
+      <c r="EB161" t="inlineStr"/>
+      <c r="EC161" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="ED161" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EE161" t="inlineStr">
+        <is>
+          <t>8.12</t>
+        </is>
+      </c>
+      <c r="EF161" t="inlineStr">
+        <is>
+          <t>5.36</t>
+        </is>
+      </c>
+      <c r="EG161" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EH161" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EI161" t="inlineStr"/>
+      <c r="EJ161" t="inlineStr"/>
+      <c r="EK161" t="inlineStr"/>
+      <c r="EL161" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
+++ b/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
@@ -70366,13 +70366,13 @@
         <v>10</v>
       </c>
       <c r="T156" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U156" t="n">
         <v>15</v>
       </c>
       <c r="V156" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W156" t="n">
         <v>18</v>
@@ -70547,10 +70547,10 @@
         <v>1.59</v>
       </c>
       <c r="CA156" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="CB156" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="CC156" t="n">
         <v>0</v>
@@ -70837,10 +70837,10 @@
         <v>13</v>
       </c>
       <c r="Y157" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Z157" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AA157" t="inlineStr"/>
       <c r="AB157" t="inlineStr"/>
@@ -72627,13 +72627,13 @@
         <v>4</v>
       </c>
       <c r="S161" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T161" t="n">
         <v>6</v>
       </c>
       <c r="U161" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V161" t="n">
         <v>10</v>
@@ -72802,19 +72802,19 @@
         <v>42</v>
       </c>
       <c r="BX161" t="n">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="BY161" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="BZ161" t="n">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="CA161" t="n">
         <v>1.22</v>
       </c>
       <c r="CB161" t="n">
-        <v>3.19</v>
+        <v>3.24</v>
       </c>
       <c r="CC161" t="n">
         <v>0</v>
@@ -72874,7 +72874,7 @@
         <v>16</v>
       </c>
       <c r="CV161" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="CW161" t="n">
         <v>1</v>

--- a/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
+++ b/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL161" headerRowCount="1">
-  <autoFilter ref="A1:EL161"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL162" headerRowCount="1">
+  <autoFilter ref="A1:EL162"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL161"/>
+  <dimension ref="A1:EL162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.8" customWidth="1" min="1" max="1"/>
@@ -8047,7 +8047,7 @@
         <v>1.72</v>
       </c>
       <c r="DO16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -10677,7 +10677,7 @@
         <v>2.11</v>
       </c>
       <c r="DE22" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DF22" t="n">
         <v>0</v>
@@ -11574,7 +11574,7 @@
         <v>50</v>
       </c>
       <c r="DD24" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="DE24" t="n">
         <v>0.7</v>
@@ -12474,7 +12474,7 @@
         <v>100</v>
       </c>
       <c r="DD26" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="DE26" t="n">
         <v>1.18</v>
@@ -17397,7 +17397,7 @@
         <v>0.89</v>
       </c>
       <c r="DE37" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DF37" t="n">
         <v>1</v>
@@ -26310,7 +26310,7 @@
         <v>75</v>
       </c>
       <c r="DD57" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="DE57" t="n">
         <v>1.2</v>
@@ -27225,7 +27225,7 @@
         <v>1.1</v>
       </c>
       <c r="DE59" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DF59" t="n">
         <v>1</v>
@@ -31238,7 +31238,7 @@
         <v>71</v>
       </c>
       <c r="DD68" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="DE68" t="n">
         <v>1.9</v>
@@ -35741,7 +35741,7 @@
         <v>2.8</v>
       </c>
       <c r="DE78" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DF78" t="n">
         <v>2.5</v>
@@ -36626,7 +36626,7 @@
         <v>45</v>
       </c>
       <c r="DD80" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="DE80" t="n">
         <v>0.4</v>
@@ -40787,168 +40787,176 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
         <v>45948.41666666666</v>
       </c>
       <c r="G90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
         <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K90" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L90" t="n">
+        <v>9</v>
+      </c>
+      <c r="M90" t="n">
+        <v>2</v>
+      </c>
+      <c r="N90" t="n">
+        <v>2</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
         <v>11</v>
       </c>
-      <c r="M90" t="n">
-        <v>1</v>
-      </c>
-      <c r="N90" t="n">
-        <v>2</v>
-      </c>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>3</v>
-      </c>
       <c r="R90" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T90" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="U90" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="V90" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W90" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="X90" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Y90" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="Z90" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA90" t="inlineStr"/>
-      <c r="AB90" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>Stadion Nizhny Novgorod</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>ul. Dolzhanskaya, Nizhniy Novgorod</t>
+        </is>
+      </c>
       <c r="AC90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD90" t="n">
         <v>2</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.9</v>
+        <v>2.29</v>
       </c>
       <c r="AF90" t="n">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="AG90" t="n">
-        <v>3.28</v>
+        <v>2.57</v>
       </c>
       <c r="AH90" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AI90" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AJ90" t="n">
-        <v>3.08</v>
+        <v>2.66</v>
       </c>
       <c r="AK90" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AL90" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="AM90" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AN90" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AO90" t="n">
-        <v>2.62</v>
+        <v>2.16</v>
       </c>
       <c r="AP90" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR90" t="n">
-        <v>2.74</v>
+        <v>2.51</v>
       </c>
       <c r="AS90" t="n">
-        <v>3.04</v>
+        <v>3.32</v>
       </c>
       <c r="AT90" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AU90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV90" t="n">
         <v>0</v>
       </c>
       <c r="AW90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ90" t="n">
         <v>1</v>
       </c>
       <c r="BA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB90" t="n">
-        <v>-1</v>
+        <v>668270</v>
       </c>
       <c r="BC90" t="n">
         <v>0</v>
       </c>
       <c r="BD90" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BE90" t="n">
         <v>0</v>
       </c>
       <c r="BF90" t="n">
-        <v>6069</v>
+        <v>4088</v>
       </c>
       <c r="BG90" t="n">
         <v>-1</v>
@@ -40975,7 +40983,7 @@
         <v>-1</v>
       </c>
       <c r="BO90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP90" t="n">
         <v>0</v>
@@ -40987,7 +40995,7 @@
         <v>2</v>
       </c>
       <c r="BS90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT90" t="n">
         <v>3</v>
@@ -40996,25 +41004,25 @@
         <v>1</v>
       </c>
       <c r="BV90" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="BW90" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="BX90" t="n">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="BY90" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BZ90" t="n">
-        <v>1.44</v>
+        <v>2.82</v>
       </c>
       <c r="CA90" t="n">
-        <v>1.34</v>
+        <v>1.09</v>
       </c>
       <c r="CB90" t="n">
-        <v>2.78</v>
+        <v>3.91</v>
       </c>
       <c r="CC90" t="n">
         <v>0</v>
@@ -41062,73 +41070,73 @@
         <v>1</v>
       </c>
       <c r="CR90" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS90" t="n">
         <v>21</v>
       </c>
-      <c r="CS90" t="n">
-        <v>23</v>
-      </c>
       <c r="CT90" t="n">
         <v>1</v>
       </c>
       <c r="CU90" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="CV90" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CW90" t="n">
         <v>1</v>
       </c>
       <c r="CX90" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="CY90" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="CZ90" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="DA90" t="n">
         <v>100</v>
       </c>
       <c r="DB90" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="DC90" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="DD90" t="n">
-        <v>1.67</v>
+        <v>1.1</v>
       </c>
       <c r="DE90" t="n">
-        <v>0.44</v>
+        <v>1.18</v>
       </c>
       <c r="DF90" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="DG90" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="DH90" t="n">
-        <v>1.09</v>
+        <v>0.55</v>
       </c>
       <c r="DI90" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="DJ90" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="DK90" t="n">
         <v>0</v>
       </c>
       <c r="DL90" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DM90" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="DN90" t="n">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="DO90" t="n">
         <v>20</v>
@@ -41137,7 +41145,7 @@
         <v>1</v>
       </c>
       <c r="DQ90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR90" t="b">
         <v>0</v>
@@ -41152,66 +41160,66 @@
         <v>0</v>
       </c>
       <c r="DV90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW90" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="DX90" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="DY90" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="DZ90" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EA90" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EB90" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="EC90" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="ED90" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="EE90" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="EF90" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="EG90" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EH90" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="EI90" t="inlineStr"/>
@@ -41235,176 +41243,168 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F91" s="2" t="n">
         <v>45948.41666666666</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91" t="n">
         <v>1</v>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J91" t="n">
+        <v>5</v>
+      </c>
+      <c r="K91" t="n">
         <v>6</v>
       </c>
-      <c r="K91" t="n">
+      <c r="L91" t="n">
+        <v>11</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1</v>
+      </c>
+      <c r="N91" t="n">
+        <v>2</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
         <v>3</v>
       </c>
-      <c r="L91" t="n">
-        <v>9</v>
-      </c>
-      <c r="M91" t="n">
-        <v>2</v>
-      </c>
-      <c r="N91" t="n">
-        <v>2</v>
-      </c>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>11</v>
-      </c>
       <c r="R91" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T91" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="U91" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="V91" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W91" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="X91" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Y91" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="Z91" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>Stadion Nizhny Novgorod</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>ul. Dolzhanskaya, Nizhniy Novgorod</t>
-        </is>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="AA91" t="inlineStr"/>
+      <c r="AB91" t="inlineStr"/>
       <c r="AC91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD91" t="n">
         <v>2</v>
       </c>
       <c r="AE91" t="n">
-        <v>2.29</v>
+        <v>1.9</v>
       </c>
       <c r="AF91" t="n">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
       <c r="AG91" t="n">
-        <v>2.57</v>
+        <v>3.28</v>
       </c>
       <c r="AH91" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AI91" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AJ91" t="n">
-        <v>2.66</v>
+        <v>3.08</v>
       </c>
       <c r="AK91" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="AL91" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="AM91" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AN91" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AO91" t="n">
-        <v>2.16</v>
+        <v>2.62</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AR91" t="n">
-        <v>2.51</v>
+        <v>2.74</v>
       </c>
       <c r="AS91" t="n">
-        <v>3.32</v>
+        <v>3.04</v>
       </c>
       <c r="AT91" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AU91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV91" t="n">
         <v>0</v>
       </c>
       <c r="AW91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ91" t="n">
         <v>1</v>
       </c>
       <c r="BA91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB91" t="n">
-        <v>668270</v>
+        <v>-1</v>
       </c>
       <c r="BC91" t="n">
         <v>0</v>
       </c>
       <c r="BD91" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BE91" t="n">
         <v>0</v>
       </c>
       <c r="BF91" t="n">
-        <v>4088</v>
+        <v>6069</v>
       </c>
       <c r="BG91" t="n">
         <v>-1</v>
@@ -41431,7 +41431,7 @@
         <v>-1</v>
       </c>
       <c r="BO91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP91" t="n">
         <v>0</v>
@@ -41443,7 +41443,7 @@
         <v>2</v>
       </c>
       <c r="BS91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT91" t="n">
         <v>3</v>
@@ -41452,25 +41452,25 @@
         <v>1</v>
       </c>
       <c r="BV91" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="BW91" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="BX91" t="n">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="BY91" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="BZ91" t="n">
-        <v>2.82</v>
+        <v>1.44</v>
       </c>
       <c r="CA91" t="n">
-        <v>1.09</v>
+        <v>1.34</v>
       </c>
       <c r="CB91" t="n">
-        <v>3.91</v>
+        <v>2.78</v>
       </c>
       <c r="CC91" t="n">
         <v>0</v>
@@ -41518,73 +41518,73 @@
         <v>1</v>
       </c>
       <c r="CR91" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CS91" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CT91" t="n">
         <v>1</v>
       </c>
       <c r="CU91" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="CV91" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CW91" t="n">
         <v>1</v>
       </c>
       <c r="CX91" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="CY91" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="CZ91" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="DA91" t="n">
         <v>100</v>
       </c>
       <c r="DB91" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="DC91" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="DD91" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DE91" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DF91" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DG91" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DH91" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DI91" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DJ91" t="n">
+        <v>30</v>
+      </c>
+      <c r="DK91" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL91" t="n">
         <v>1.1</v>
       </c>
-      <c r="DE91" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="DF91" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="DG91" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="DH91" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="DI91" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="DJ91" t="n">
-        <v>20</v>
-      </c>
-      <c r="DK91" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL91" t="n">
-        <v>1.27</v>
-      </c>
       <c r="DM91" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="DN91" t="n">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="DO91" t="n">
         <v>20</v>
@@ -41593,7 +41593,7 @@
         <v>1</v>
       </c>
       <c r="DQ91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR91" t="b">
         <v>0</v>
@@ -41608,66 +41608,66 @@
         <v>0</v>
       </c>
       <c r="DV91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW91" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="DX91" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="DY91" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="DZ91" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EA91" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EB91" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="EC91" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="ED91" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="EE91" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EF91" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="EG91" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="EH91" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EI91" t="inlineStr"/>
@@ -42454,7 +42454,7 @@
         <v>50</v>
       </c>
       <c r="DD93" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="DE93" t="n">
         <v>1.78</v>
@@ -44709,7 +44709,7 @@
         <v>2.18</v>
       </c>
       <c r="DE98" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DF98" t="n">
         <v>2</v>
@@ -48666,7 +48666,7 @@
         <v>68</v>
       </c>
       <c r="DD107" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="DE107" t="n">
         <v>0.45</v>
@@ -49267,25 +49267,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F109" s="2" t="n">
         <v>45962.71875</v>
       </c>
       <c r="G109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J109" t="n">
         <v>6</v>
@@ -49300,315 +49300,323 @@
         <v>2</v>
       </c>
       <c r="N109" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P109" t="n">
         <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R109" t="n">
         <v>2</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T109" t="n">
         <v>6</v>
       </c>
       <c r="U109" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V109" t="n">
         <v>8</v>
       </c>
       <c r="W109" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="X109" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Y109" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Z109" t="n">
-        <v>51</v>
-      </c>
-      <c r="AA109" t="inlineStr"/>
-      <c r="AB109" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>Stadion Central’nyj im. I.P. Chayka</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>ul. Suvorova, Peschanokopskoye</t>
+        </is>
+      </c>
       <c r="AC109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD109" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE109" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AF109" t="n">
-        <v>3.9</v>
+        <v>3.47</v>
       </c>
       <c r="AG109" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AH109" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AI109" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AJ109" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="AK109" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AL109" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AM109" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="AN109" t="n">
-        <v>1.92</v>
+        <v>2.23</v>
       </c>
       <c r="AO109" t="n">
-        <v>2.65</v>
+        <v>2.32</v>
       </c>
       <c r="AP109" t="n">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AR109" t="n">
-        <v>2.6</v>
+        <v>2.77</v>
       </c>
       <c r="AS109" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="AT109" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB109" t="n">
+        <v>668270</v>
+      </c>
+      <c r="BC109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD109" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF109" t="n">
+        <v>7890</v>
+      </c>
+      <c r="BG109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS109" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT109" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV109" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW109" t="n">
+        <v>35</v>
+      </c>
+      <c r="BX109" t="n">
+        <v>78</v>
+      </c>
+      <c r="BY109" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ109" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CA109" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="CB109" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="CC109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR109" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS109" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU109" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV109" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX109" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY109" t="n">
+        <v>15</v>
+      </c>
+      <c r="CZ109" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA109" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB109" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC109" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD109" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DE109" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DF109" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG109" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DH109" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DI109" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DJ109" t="n">
+        <v>58</v>
+      </c>
+      <c r="DK109" t="n">
+        <v>34</v>
+      </c>
+      <c r="DL109" t="n">
         <v>1.47</v>
       </c>
-      <c r="AU109" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV109" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX109" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ109" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA109" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB109" t="n">
-        <v>921</v>
-      </c>
-      <c r="BC109" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD109" t="n">
-        <v>84</v>
-      </c>
-      <c r="BE109" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF109" t="n">
-        <v>45133</v>
-      </c>
-      <c r="BG109" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BH109" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI109" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BJ109" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BK109" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BL109" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BM109" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BN109" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BO109" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP109" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ109" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR109" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS109" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT109" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU109" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV109" t="n">
-        <v>51</v>
-      </c>
-      <c r="BW109" t="n">
-        <v>46</v>
-      </c>
-      <c r="BX109" t="n">
-        <v>89</v>
-      </c>
-      <c r="BY109" t="n">
-        <v>85</v>
-      </c>
-      <c r="BZ109" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CA109" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="CB109" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="CC109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM109" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CN109" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CO109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR109" t="n">
-        <v>28</v>
-      </c>
-      <c r="CS109" t="n">
-        <v>8</v>
-      </c>
-      <c r="CT109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU109" t="n">
-        <v>20</v>
-      </c>
-      <c r="CV109" t="n">
-        <v>13</v>
-      </c>
-      <c r="CW109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX109" t="n">
-        <v>7</v>
-      </c>
-      <c r="CY109" t="n">
-        <v>6</v>
-      </c>
-      <c r="CZ109" t="n">
-        <v>55</v>
-      </c>
-      <c r="DA109" t="n">
-        <v>100</v>
-      </c>
-      <c r="DB109" t="n">
-        <v>32</v>
-      </c>
-      <c r="DC109" t="n">
-        <v>77</v>
-      </c>
-      <c r="DD109" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="DE109" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="DF109" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="DG109" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="DH109" t="n">
-        <v>2</v>
-      </c>
-      <c r="DI109" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="DJ109" t="n">
-        <v>45</v>
-      </c>
-      <c r="DK109" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL109" t="n">
-        <v>1.92</v>
-      </c>
       <c r="DM109" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="DN109" t="n">
-        <v>3.47</v>
+        <v>2.81</v>
       </c>
       <c r="DO109" t="n">
         <v>20</v>
@@ -49617,7 +49625,7 @@
         <v>1</v>
       </c>
       <c r="DQ109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR109" t="b">
         <v>0</v>
@@ -49636,46 +49644,62 @@
       </c>
       <c r="DW109" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="DX109" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="DY109" t="inlineStr">
         <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="DZ109" t="inlineStr"/>
-      <c r="EA109" t="inlineStr"/>
-      <c r="EB109" t="inlineStr"/>
-      <c r="EC109" t="inlineStr"/>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="DZ109" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EA109" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EB109" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="EC109" t="inlineStr">
+        <is>
+          <t>2.79</t>
+        </is>
+      </c>
       <c r="ED109" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EE109" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="EF109" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="EG109" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="EH109" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EI109" t="inlineStr"/>
@@ -49699,25 +49723,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F110" s="2" t="n">
         <v>45962.71875</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J110" t="n">
         <v>6</v>
@@ -49732,323 +49756,315 @@
         <v>2</v>
       </c>
       <c r="N110" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P110" t="n">
         <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R110" t="n">
         <v>2</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T110" t="n">
         <v>6</v>
       </c>
       <c r="U110" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V110" t="n">
         <v>8</v>
       </c>
       <c r="W110" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X110" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Y110" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Z110" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA110" t="inlineStr">
-        <is>
-          <t>Stadion Central’nyj im. I.P. Chayka</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>ul. Suvorova, Peschanokopskoye</t>
-        </is>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="AA110" t="inlineStr"/>
+      <c r="AB110" t="inlineStr"/>
       <c r="AC110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD110" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE110" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AF110" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG110" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AH110" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI110" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ110" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AK110" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL110" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM110" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO110" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AP110" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ110" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR110" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AS110" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT110" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AU110" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB110" t="n">
+        <v>921</v>
+      </c>
+      <c r="BC110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD110" t="n">
+        <v>84</v>
+      </c>
+      <c r="BE110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF110" t="n">
+        <v>45133</v>
+      </c>
+      <c r="BG110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS110" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV110" t="n">
+        <v>51</v>
+      </c>
+      <c r="BW110" t="n">
+        <v>46</v>
+      </c>
+      <c r="BX110" t="n">
+        <v>89</v>
+      </c>
+      <c r="BY110" t="n">
+        <v>85</v>
+      </c>
+      <c r="BZ110" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CA110" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="CB110" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="CC110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR110" t="n">
+        <v>28</v>
+      </c>
+      <c r="CS110" t="n">
+        <v>8</v>
+      </c>
+      <c r="CT110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU110" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV110" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX110" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY110" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ110" t="n">
+        <v>55</v>
+      </c>
+      <c r="DA110" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB110" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC110" t="n">
+        <v>77</v>
+      </c>
+      <c r="DD110" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="DE110" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DF110" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DG110" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DH110" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI110" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="DJ110" t="n">
+        <v>45</v>
+      </c>
+      <c r="DK110" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL110" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DM110" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DN110" t="n">
         <v>3.47</v>
-      </c>
-      <c r="AG110" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AH110" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI110" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ110" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AK110" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AL110" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM110" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AN110" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AO110" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AP110" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AQ110" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AR110" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AS110" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AT110" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AU110" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY110" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ110" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA110" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB110" t="n">
-        <v>668270</v>
-      </c>
-      <c r="BC110" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD110" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE110" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF110" t="n">
-        <v>7890</v>
-      </c>
-      <c r="BG110" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BH110" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI110" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BJ110" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BK110" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BL110" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BM110" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BN110" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BO110" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP110" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ110" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR110" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS110" t="n">
-        <v>4</v>
-      </c>
-      <c r="BT110" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU110" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV110" t="n">
-        <v>44</v>
-      </c>
-      <c r="BW110" t="n">
-        <v>35</v>
-      </c>
-      <c r="BX110" t="n">
-        <v>78</v>
-      </c>
-      <c r="BY110" t="n">
-        <v>87</v>
-      </c>
-      <c r="BZ110" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="CA110" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="CB110" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="CC110" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD110" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE110" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF110" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG110" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH110" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI110" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ110" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK110" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL110" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM110" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CN110" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CO110" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP110" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ110" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR110" t="n">
-        <v>20</v>
-      </c>
-      <c r="CS110" t="n">
-        <v>15</v>
-      </c>
-      <c r="CT110" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU110" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV110" t="n">
-        <v>15</v>
-      </c>
-      <c r="CW110" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX110" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY110" t="n">
-        <v>15</v>
-      </c>
-      <c r="CZ110" t="n">
-        <v>42</v>
-      </c>
-      <c r="DA110" t="n">
-        <v>67</v>
-      </c>
-      <c r="DB110" t="n">
-        <v>25</v>
-      </c>
-      <c r="DC110" t="n">
-        <v>75</v>
-      </c>
-      <c r="DD110" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="DE110" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="DF110" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DG110" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="DH110" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="DI110" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="DJ110" t="n">
-        <v>58</v>
-      </c>
-      <c r="DK110" t="n">
-        <v>34</v>
-      </c>
-      <c r="DL110" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="DM110" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="DN110" t="n">
-        <v>2.81</v>
       </c>
       <c r="DO110" t="n">
         <v>20</v>
@@ -50057,7 +50073,7 @@
         <v>1</v>
       </c>
       <c r="DQ110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR110" t="b">
         <v>0</v>
@@ -50076,62 +50092,46 @@
       </c>
       <c r="DW110" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="DX110" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="DY110" t="inlineStr">
         <is>
-          <t>1.28</t>
-        </is>
-      </c>
-      <c r="DZ110" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EA110" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="EB110" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="EC110" t="inlineStr">
-        <is>
-          <t>2.79</t>
-        </is>
-      </c>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="DZ110" t="inlineStr"/>
+      <c r="EA110" t="inlineStr"/>
+      <c r="EB110" t="inlineStr"/>
+      <c r="EC110" t="inlineStr"/>
       <c r="ED110" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="EE110" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="EF110" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="EG110" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="EH110" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EI110" t="inlineStr"/>
@@ -52686,7 +52686,7 @@
         <v>70</v>
       </c>
       <c r="DD116" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="DE116" t="n">
         <v>1.1</v>
@@ -54009,7 +54009,7 @@
         <v>2.2</v>
       </c>
       <c r="DE119" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DF119" t="n">
         <v>2.33</v>
@@ -59393,7 +59393,7 @@
         <v>2.5</v>
       </c>
       <c r="DE131" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DF131" t="n">
         <v>2.75</v>
@@ -60403,176 +60403,176 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F134" s="2" t="n">
         <v>45991.5625</v>
       </c>
       <c r="G134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I134" t="n">
+        <v>4</v>
+      </c>
+      <c r="J134" t="n">
+        <v>2</v>
+      </c>
+      <c r="K134" t="n">
+        <v>4</v>
+      </c>
+      <c r="L134" t="n">
+        <v>6</v>
+      </c>
+      <c r="M134" t="n">
+        <v>2</v>
+      </c>
+      <c r="N134" t="n">
+        <v>1</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
         <v>3</v>
       </c>
-      <c r="J134" t="n">
-        <v>7</v>
-      </c>
-      <c r="K134" t="n">
+      <c r="R134" t="n">
+        <v>6</v>
+      </c>
+      <c r="S134" t="n">
         <v>8</v>
       </c>
-      <c r="L134" t="n">
-        <v>15</v>
-      </c>
-      <c r="M134" t="n">
-        <v>3</v>
-      </c>
-      <c r="N134" t="n">
-        <v>2</v>
-      </c>
-      <c r="O134" t="n">
-        <v>0</v>
-      </c>
-      <c r="P134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q134" t="n">
-        <v>6</v>
-      </c>
-      <c r="R134" t="n">
-        <v>5</v>
-      </c>
-      <c r="S134" t="n">
+      <c r="T134" t="n">
+        <v>10</v>
+      </c>
+      <c r="U134" t="n">
         <v>11</v>
       </c>
-      <c r="T134" t="n">
-        <v>18</v>
-      </c>
-      <c r="U134" t="n">
-        <v>17</v>
-      </c>
       <c r="V134" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="W134" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X134" t="n">
         <v>13</v>
       </c>
       <c r="Y134" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="Z134" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>Akhmat Arena</t>
+          <t>Stadion Central’nyj im. I.P. Chayka</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
+          <t>ul. Suvorova, Peschanokopskoye</t>
         </is>
       </c>
       <c r="AC134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA134" t="n">
         <v>3</v>
       </c>
-      <c r="AD134" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE134" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AF134" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AG134" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AH134" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI134" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ134" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AK134" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AL134" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AM134" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AN134" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AO134" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AP134" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AQ134" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AR134" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AS134" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AT134" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AU134" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW134" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX134" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ134" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA134" t="n">
-        <v>1</v>
-      </c>
       <c r="BB134" t="n">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="BC134" t="n">
         <v>0</v>
       </c>
       <c r="BD134" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="BE134" t="n">
         <v>0</v>
       </c>
       <c r="BF134" t="n">
-        <v>4236</v>
+        <v>12383</v>
       </c>
       <c r="BG134" t="n">
         <v>-1</v>
@@ -60599,10 +60599,10 @@
         <v>-1</v>
       </c>
       <c r="BO134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ134" t="n">
         <v>2</v>
@@ -60611,7 +60611,7 @@
         <v>1</v>
       </c>
       <c r="BS134" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT134" t="n">
         <v>3</v>
@@ -60620,37 +60620,37 @@
         <v>1</v>
       </c>
       <c r="BV134" t="n">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="BW134" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="BX134" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="BY134" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="BZ134" t="n">
-        <v>1.77</v>
+        <v>1.45</v>
       </c>
       <c r="CA134" t="n">
-        <v>2.12</v>
+        <v>1.71</v>
       </c>
       <c r="CB134" t="n">
-        <v>3.89</v>
+        <v>3.16</v>
       </c>
       <c r="CC134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG134" t="n">
         <v>0</v>
@@ -60668,7 +60668,7 @@
         <v>0</v>
       </c>
       <c r="CL134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM134" t="n">
         <v>-1</v>
@@ -60677,7 +60677,7 @@
         <v>-1</v>
       </c>
       <c r="CO134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP134" t="n">
         <v>0</v>
@@ -60686,73 +60686,73 @@
         <v>1</v>
       </c>
       <c r="CR134" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="CS134" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="CT134" t="n">
         <v>1</v>
       </c>
       <c r="CU134" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CV134" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="CW134" t="n">
         <v>1</v>
       </c>
       <c r="CX134" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CY134" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CZ134" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="DA134" t="n">
         <v>72</v>
       </c>
       <c r="DB134" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="DC134" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="DD134" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DE134" t="n">
         <v>1.9</v>
       </c>
-      <c r="DE134" t="n">
-        <v>1.2</v>
-      </c>
       <c r="DF134" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="DG134" t="n">
-        <v>1.14</v>
+        <v>1.63</v>
       </c>
       <c r="DH134" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="DI134" t="n">
-        <v>1.25</v>
+        <v>1.94</v>
       </c>
       <c r="DJ134" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="DK134" t="n">
         <v>29</v>
       </c>
       <c r="DL134" t="n">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="DM134" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="DN134" t="n">
-        <v>3.07</v>
+        <v>2.93</v>
       </c>
       <c r="DO134" t="n">
         <v>20</v>
@@ -60767,7 +60767,7 @@
         <v>1</v>
       </c>
       <c r="DS134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT134" t="b">
         <v>0</v>
@@ -60780,17 +60780,17 @@
       </c>
       <c r="DW134" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="DX134" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="DY134" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="DZ134" t="inlineStr"/>
@@ -60799,47 +60799,47 @@
       <c r="EC134" t="inlineStr"/>
       <c r="ED134" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="EE134" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="EF134" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="EG134" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EH134" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EI134" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="EJ134" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EK134" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EL134" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -60859,176 +60859,176 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F135" s="2" t="n">
         <v>45991.5625</v>
       </c>
       <c r="G135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H135" t="n">
+        <v>1</v>
+      </c>
+      <c r="I135" t="n">
         <v>3</v>
       </c>
-      <c r="I135" t="n">
-        <v>4</v>
-      </c>
       <c r="J135" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K135" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L135" t="n">
+        <v>15</v>
+      </c>
+      <c r="M135" t="n">
+        <v>3</v>
+      </c>
+      <c r="N135" t="n">
+        <v>2</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
         <v>6</v>
       </c>
-      <c r="M135" t="n">
-        <v>2</v>
-      </c>
-      <c r="N135" t="n">
-        <v>1</v>
-      </c>
-      <c r="O135" t="n">
-        <v>0</v>
-      </c>
-      <c r="P135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q135" t="n">
-        <v>3</v>
-      </c>
       <c r="R135" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S135" t="n">
+        <v>11</v>
+      </c>
+      <c r="T135" t="n">
+        <v>18</v>
+      </c>
+      <c r="U135" t="n">
+        <v>17</v>
+      </c>
+      <c r="V135" t="n">
+        <v>23</v>
+      </c>
+      <c r="W135" t="n">
         <v>8</v>
-      </c>
-      <c r="T135" t="n">
-        <v>10</v>
-      </c>
-      <c r="U135" t="n">
-        <v>11</v>
-      </c>
-      <c r="V135" t="n">
-        <v>16</v>
-      </c>
-      <c r="W135" t="n">
-        <v>16</v>
       </c>
       <c r="X135" t="n">
         <v>13</v>
       </c>
       <c r="Y135" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="Z135" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>Stadion Central’nyj im. I.P. Chayka</t>
+          <t>Akhmat Arena</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>ul. Suvorova, Peschanokopskoye</t>
+          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
         </is>
       </c>
       <c r="AC135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE135" t="n">
-        <v>2.49</v>
+        <v>2.89</v>
       </c>
       <c r="AF135" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="AG135" t="n">
-        <v>2.84</v>
+        <v>2.36</v>
       </c>
       <c r="AH135" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AI135" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AJ135" t="n">
-        <v>3.74</v>
+        <v>3.1</v>
       </c>
       <c r="AK135" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AL135" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="AM135" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AN135" t="n">
-        <v>2.19</v>
+        <v>1.8</v>
       </c>
       <c r="AO135" t="n">
-        <v>2.19</v>
+        <v>2.48</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AR135" t="n">
-        <v>3.09</v>
+        <v>2.62</v>
       </c>
       <c r="AS135" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="AT135" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AU135" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX135" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA135" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BB135" t="n">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="BC135" t="n">
         <v>0</v>
       </c>
       <c r="BD135" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="BE135" t="n">
         <v>0</v>
       </c>
       <c r="BF135" t="n">
-        <v>12383</v>
+        <v>4236</v>
       </c>
       <c r="BG135" t="n">
         <v>-1</v>
@@ -61055,10 +61055,10 @@
         <v>-1</v>
       </c>
       <c r="BO135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ135" t="n">
         <v>2</v>
@@ -61067,7 +61067,7 @@
         <v>1</v>
       </c>
       <c r="BS135" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT135" t="n">
         <v>3</v>
@@ -61076,37 +61076,37 @@
         <v>1</v>
       </c>
       <c r="BV135" t="n">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="BW135" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="BX135" t="n">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="BY135" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="BZ135" t="n">
-        <v>1.45</v>
+        <v>1.77</v>
       </c>
       <c r="CA135" t="n">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="CB135" t="n">
-        <v>3.16</v>
+        <v>3.89</v>
       </c>
       <c r="CC135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG135" t="n">
         <v>0</v>
@@ -61124,7 +61124,7 @@
         <v>0</v>
       </c>
       <c r="CL135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM135" t="n">
         <v>-1</v>
@@ -61133,7 +61133,7 @@
         <v>-1</v>
       </c>
       <c r="CO135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP135" t="n">
         <v>0</v>
@@ -61142,73 +61142,73 @@
         <v>1</v>
       </c>
       <c r="CR135" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="CS135" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="CT135" t="n">
         <v>1</v>
       </c>
       <c r="CU135" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CV135" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="CW135" t="n">
         <v>1</v>
       </c>
       <c r="CX135" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CY135" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CZ135" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="DA135" t="n">
         <v>72</v>
       </c>
       <c r="DB135" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="DC135" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="DD135" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="DE135" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="DF135" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="DG135" t="n">
-        <v>1.63</v>
+        <v>1.14</v>
       </c>
       <c r="DH135" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DI135" t="n">
-        <v>1.94</v>
+        <v>1.25</v>
       </c>
       <c r="DJ135" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DK135" t="n">
         <v>29</v>
       </c>
       <c r="DL135" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="DM135" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="DN135" t="n">
-        <v>2.93</v>
+        <v>3.07</v>
       </c>
       <c r="DO135" t="n">
         <v>20</v>
@@ -61223,7 +61223,7 @@
         <v>1</v>
       </c>
       <c r="DS135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT135" t="b">
         <v>0</v>
@@ -61236,17 +61236,17 @@
       </c>
       <c r="DW135" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="DX135" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="DY135" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="DZ135" t="inlineStr"/>
@@ -61255,47 +61255,47 @@
       <c r="EC135" t="inlineStr"/>
       <c r="ED135" t="inlineStr">
         <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="EE135" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EF135" t="inlineStr">
+        <is>
+          <t>3.53</t>
+        </is>
+      </c>
+      <c r="EG135" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EH135" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EI135" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EJ135" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EK135" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EL135" t="inlineStr">
+        <is>
           <t>2.54</t>
-        </is>
-      </c>
-      <c r="EE135" t="inlineStr">
-        <is>
-          <t>2.86</t>
-        </is>
-      </c>
-      <c r="EF135" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="EG135" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="EH135" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="EI135" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="EJ135" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="EK135" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EL135" t="inlineStr">
-        <is>
-          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -62549,7 +62549,7 @@
         <v>1.9</v>
       </c>
       <c r="DE138" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DF138" t="n">
         <v>1.63</v>
@@ -64282,7 +64282,7 @@
         <v>57</v>
       </c>
       <c r="DD142" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="DE142" t="n">
         <v>0.6</v>
@@ -67914,7 +67914,7 @@
         <v>56</v>
       </c>
       <c r="DD150" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="DE150" t="n">
         <v>0.6</v>
@@ -72998,6 +72998,446 @@
       <c r="EJ161" t="inlineStr"/>
       <c r="EK161" t="inlineStr"/>
       <c r="EL161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>21</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Makhachkala</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Orenburg</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="n">
+        <v>46094.6875</v>
+      </c>
+      <c r="G162" t="n">
+        <v>1</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" t="n">
+        <v>1</v>
+      </c>
+      <c r="J162" t="n">
+        <v>6</v>
+      </c>
+      <c r="K162" t="n">
+        <v>5</v>
+      </c>
+      <c r="L162" t="n">
+        <v>11</v>
+      </c>
+      <c r="M162" t="n">
+        <v>2</v>
+      </c>
+      <c r="N162" t="n">
+        <v>2</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>4</v>
+      </c>
+      <c r="R162" t="n">
+        <v>3</v>
+      </c>
+      <c r="S162" t="n">
+        <v>8</v>
+      </c>
+      <c r="T162" t="n">
+        <v>5</v>
+      </c>
+      <c r="U162" t="n">
+        <v>12</v>
+      </c>
+      <c r="V162" t="n">
+        <v>8</v>
+      </c>
+      <c r="W162" t="n">
+        <v>13</v>
+      </c>
+      <c r="X162" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z162" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>Anzhi-Arena</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>, Kaspiysk</t>
+        </is>
+      </c>
+      <c r="AC162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG162" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH162" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI162" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AJ162" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="AK162" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL162" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AM162" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN162" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AO162" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AP162" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AQ162" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AR162" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AS162" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AT162" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AU162" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV162" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA162" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB162" t="n">
+        <v>668267</v>
+      </c>
+      <c r="BC162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD162" t="n">
+        <v>43</v>
+      </c>
+      <c r="BE162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF162" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG162" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH162" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI162" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ162" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK162" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL162" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM162" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN162" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO162" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP162" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ162" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR162" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS162" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT162" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU162" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV162" t="n">
+        <v>49</v>
+      </c>
+      <c r="BW162" t="n">
+        <v>47</v>
+      </c>
+      <c r="BX162" t="n">
+        <v>78</v>
+      </c>
+      <c r="BY162" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ162" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CA162" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="CB162" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="CC162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI162" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ162" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM162" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN162" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ162" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR162" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS162" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT162" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU162" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV162" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW162" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX162" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY162" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ162" t="n">
+        <v>27</v>
+      </c>
+      <c r="DA162" t="n">
+        <v>59</v>
+      </c>
+      <c r="DB162" t="n">
+        <v>16</v>
+      </c>
+      <c r="DC162" t="n">
+        <v>58</v>
+      </c>
+      <c r="DD162" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DE162" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DF162" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG162" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="DH162" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DI162" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DJ162" t="n">
+        <v>73</v>
+      </c>
+      <c r="DK162" t="n">
+        <v>42</v>
+      </c>
+      <c r="DL162" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DM162" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DN162" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="DO162" t="n">
+        <v>21</v>
+      </c>
+      <c r="DP162" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ162" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR162" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS162" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT162" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU162" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV162" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW162" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="DX162" t="inlineStr">
+        <is>
+          <t>5.07</t>
+        </is>
+      </c>
+      <c r="DY162" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="DZ162" t="inlineStr"/>
+      <c r="EA162" t="inlineStr"/>
+      <c r="EB162" t="inlineStr"/>
+      <c r="EC162" t="inlineStr"/>
+      <c r="ED162" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EE162" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="EF162" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="EG162" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EH162" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EI162" t="inlineStr"/>
+      <c r="EJ162" t="inlineStr"/>
+      <c r="EK162" t="inlineStr"/>
+      <c r="EL162" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
+++ b/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL162" headerRowCount="1">
-  <autoFilter ref="A1:EL162"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL169" headerRowCount="1">
+  <autoFilter ref="A1:EL169"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL162"/>
+  <dimension ref="A1:EL169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.8" customWidth="1" min="1" max="1"/>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2198,10 +2198,10 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2667,7 +2667,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DE6" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3579,7 +3579,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4010,7 +4010,7 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="DE7" t="n">
         <v>0.9</v>
@@ -4043,7 +4043,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4471,7 +4471,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -4897,7 +4897,7 @@
         <v>1.27</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -4927,7 +4927,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP9" t="b">
         <v>0</v>
@@ -5359,7 +5359,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5799,7 +5799,7 @@
         <v>2.56</v>
       </c>
       <c r="DO11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6247,7 +6247,7 @@
         <v>2.72</v>
       </c>
       <c r="DO12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6653,7 +6653,7 @@
         <v>2.45</v>
       </c>
       <c r="DE13" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="DF13" t="n">
         <v>0</v>
@@ -6683,7 +6683,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7114,7 +7114,7 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DE14" t="n">
         <v>1.18</v>
@@ -7147,7 +7147,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7545,7 +7545,7 @@
         <v>2.5</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="DF15" t="n">
         <v>0</v>
@@ -7575,7 +7575,7 @@
         <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8470,7 +8470,7 @@
         <v>0</v>
       </c>
       <c r="DD17" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="DE17" t="n">
         <v>1.4</v>
@@ -8503,7 +8503,7 @@
         <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -8910,10 +8910,10 @@
         <v>50</v>
       </c>
       <c r="DD18" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DF18" t="n">
         <v>0</v>
@@ -8943,7 +8943,7 @@
         <v>1.28</v>
       </c>
       <c r="DO18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9047,70 +9047,70 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
         <v>45871.72916666666</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>7</v>
+      </c>
+      <c r="L19" t="n">
+        <v>11</v>
+      </c>
+      <c r="M19" t="n">
         <v>5</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>5</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>4</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>10</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6</v>
+      </c>
+      <c r="S19" t="n">
         <v>3</v>
       </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>5</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
+        <v>8</v>
+      </c>
+      <c r="U19" t="n">
         <v>13</v>
       </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>18</v>
-      </c>
       <c r="V19" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="W19" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="X19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y19" t="n">
         <v>56</v>
@@ -9120,91 +9120,91 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Stadion FK Krasnodar</t>
+          <t>Akhmat Arena</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>ul. Vostochno-Kruglikovskaya 126, Krasnodar</t>
+          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
         </is>
       </c>
       <c r="AC19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD19" t="n">
         <v>4</v>
       </c>
-      <c r="AD19" t="n">
-        <v>3</v>
-      </c>
       <c r="AE19" t="n">
-        <v>1.81</v>
+        <v>5.84</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.54</v>
+        <v>1.65</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB19" t="n">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="BC19" t="n">
         <v>0</v>
@@ -9243,46 +9243,46 @@
         <v>-1</v>
       </c>
       <c r="BO19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ19" t="n">
         <v>3</v>
       </c>
       <c r="BR19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BS19" t="n">
         <v>3</v>
       </c>
       <c r="BT19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BU19" t="n">
         <v>1</v>
       </c>
       <c r="BV19" t="n">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="BW19" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="BX19" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="BY19" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="CA19" t="n">
-        <v>0.45</v>
+        <v>1.54</v>
       </c>
       <c r="CB19" t="n">
-        <v>2.43</v>
+        <v>3.43</v>
       </c>
       <c r="CC19" t="n">
         <v>0</v>
@@ -9324,64 +9324,64 @@
         <v>0</v>
       </c>
       <c r="CP19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ19" t="n">
         <v>1</v>
       </c>
       <c r="CR19" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="CS19" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="CT19" t="n">
         <v>1</v>
       </c>
       <c r="CU19" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="CV19" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="CW19" t="n">
         <v>1</v>
       </c>
       <c r="CX19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="CY19" t="n">
         <v>7</v>
       </c>
       <c r="CZ19" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DA19" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DB19" t="n">
         <v>0</v>
       </c>
       <c r="DC19" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.45</v>
+        <v>1.27</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.2</v>
+        <v>1.73</v>
       </c>
       <c r="DF19" t="n">
         <v>0</v>
       </c>
       <c r="DG19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DH19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="DI19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DJ19" t="n">
         <v>0</v>
@@ -9390,82 +9390,62 @@
         <v>0</v>
       </c>
       <c r="DL19" t="n">
-        <v>1.82</v>
+        <v>1.17</v>
       </c>
       <c r="DM19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.82</v>
+        <v>2.42</v>
       </c>
       <c r="DO19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
       </c>
       <c r="DQ19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU19" t="b">
         <v>0</v>
       </c>
       <c r="DV19" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW19" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="DX19" t="inlineStr">
-        <is>
-          <t>2.82</t>
-        </is>
-      </c>
-      <c r="DY19" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="DW19" t="inlineStr"/>
+      <c r="DX19" t="inlineStr"/>
+      <c r="DY19" t="inlineStr"/>
       <c r="DZ19" t="inlineStr"/>
       <c r="EA19" t="inlineStr"/>
       <c r="EB19" t="inlineStr"/>
       <c r="EC19" t="inlineStr"/>
       <c r="ED19" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="EE19" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EF19" t="inlineStr">
         <is>
-          <t>3.69</t>
-        </is>
-      </c>
-      <c r="EG19" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
-      <c r="EH19" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
+          <t>4.32</t>
+        </is>
+      </c>
+      <c r="EG19" t="inlineStr"/>
+      <c r="EH19" t="inlineStr"/>
       <c r="EI19" t="inlineStr"/>
       <c r="EJ19" t="inlineStr"/>
       <c r="EK19" t="inlineStr"/>
@@ -9487,70 +9467,70 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
         <v>45871.72916666666</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>5</v>
+      </c>
+      <c r="M20" t="n">
+        <v>4</v>
+      </c>
+      <c r="N20" t="n">
         <v>3</v>
       </c>
-      <c r="I20" t="n">
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>5</v>
       </c>
-      <c r="J20" t="n">
-        <v>4</v>
-      </c>
-      <c r="K20" t="n">
-        <v>7</v>
-      </c>
-      <c r="L20" t="n">
-        <v>11</v>
-      </c>
-      <c r="M20" t="n">
-        <v>5</v>
-      </c>
-      <c r="N20" t="n">
-        <v>4</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>10</v>
-      </c>
       <c r="R20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
+        <v>13</v>
+      </c>
+      <c r="T20" t="n">
         <v>3</v>
       </c>
-      <c r="T20" t="n">
-        <v>8</v>
-      </c>
       <c r="U20" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="V20" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="W20" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="X20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y20" t="n">
         <v>56</v>
@@ -9560,91 +9540,91 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Akhmat Arena</t>
+          <t>Stadion FK Krasnodar</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
+          <t>ul. Vostochno-Kruglikovskaya 126, Krasnodar</t>
         </is>
       </c>
       <c r="AC20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE20" t="n">
-        <v>5.84</v>
+        <v>1.81</v>
       </c>
       <c r="AF20" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.65</v>
+        <v>3.54</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AU20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AV20" t="n">
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="BC20" t="n">
         <v>0</v>
@@ -9683,46 +9663,46 @@
         <v>-1</v>
       </c>
       <c r="BO20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ20" t="n">
         <v>3</v>
       </c>
       <c r="BR20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BS20" t="n">
         <v>3</v>
       </c>
       <c r="BT20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BU20" t="n">
         <v>1</v>
       </c>
       <c r="BV20" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="BW20" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="BX20" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="BY20" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.54</v>
+        <v>0.45</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.43</v>
+        <v>2.43</v>
       </c>
       <c r="CC20" t="n">
         <v>0</v>
@@ -9764,64 +9744,64 @@
         <v>0</v>
       </c>
       <c r="CP20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ20" t="n">
         <v>1</v>
       </c>
       <c r="CR20" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="CS20" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="CT20" t="n">
         <v>1</v>
       </c>
       <c r="CU20" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="CV20" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="CW20" t="n">
         <v>1</v>
       </c>
       <c r="CX20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CY20" t="n">
         <v>7</v>
       </c>
       <c r="CZ20" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DA20" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DB20" t="n">
         <v>0</v>
       </c>
       <c r="DC20" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DD20" t="n">
-        <v>1.1</v>
+        <v>2.45</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.9</v>
+        <v>1.36</v>
       </c>
       <c r="DF20" t="n">
         <v>0</v>
       </c>
       <c r="DG20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DH20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="DI20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DJ20" t="n">
         <v>0</v>
@@ -9830,62 +9810,82 @@
         <v>0</v>
       </c>
       <c r="DL20" t="n">
-        <v>1.17</v>
+        <v>1.82</v>
       </c>
       <c r="DM20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="DN20" t="n">
-        <v>2.42</v>
+        <v>1.82</v>
       </c>
       <c r="DO20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
       </c>
       <c r="DQ20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU20" t="b">
         <v>0</v>
       </c>
       <c r="DV20" t="b">
-        <v>1</v>
-      </c>
-      <c r="DW20" t="inlineStr"/>
-      <c r="DX20" t="inlineStr"/>
-      <c r="DY20" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="DW20" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="DX20" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="DY20" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
       <c r="DZ20" t="inlineStr"/>
       <c r="EA20" t="inlineStr"/>
       <c r="EB20" t="inlineStr"/>
       <c r="EC20" t="inlineStr"/>
       <c r="ED20" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="EE20" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="EF20" t="inlineStr">
         <is>
-          <t>4.32</t>
-        </is>
-      </c>
-      <c r="EG20" t="inlineStr"/>
-      <c r="EH20" t="inlineStr"/>
+          <t>3.69</t>
+        </is>
+      </c>
+      <c r="EG20" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EH20" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
       <c r="EI20" t="inlineStr"/>
       <c r="EJ20" t="inlineStr"/>
       <c r="EK20" t="inlineStr"/>
@@ -10218,10 +10218,10 @@
         <v>50</v>
       </c>
       <c r="DD21" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DF21" t="n">
         <v>1</v>
@@ -10251,7 +10251,7 @@
         <v>1.95</v>
       </c>
       <c r="DO21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -10674,7 +10674,7 @@
         <v>0</v>
       </c>
       <c r="DD22" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE22" t="n">
         <v>0.4</v>
@@ -10707,7 +10707,7 @@
         <v>0</v>
       </c>
       <c r="DO22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11118,10 +11118,10 @@
         <v>50</v>
       </c>
       <c r="DD23" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF23" t="n">
         <v>3</v>
@@ -11151,7 +11151,7 @@
         <v>3.96</v>
       </c>
       <c r="DO23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -11577,7 +11577,7 @@
         <v>1.64</v>
       </c>
       <c r="DE24" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="DF24" t="n">
         <v>0</v>
@@ -11607,7 +11607,7 @@
         <v>1.08</v>
       </c>
       <c r="DO24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12002,7 +12002,7 @@
         <v>50</v>
       </c>
       <c r="DD25" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="DE25" t="n">
         <v>0.4</v>
@@ -12035,7 +12035,7 @@
         <v>2.16</v>
       </c>
       <c r="DO25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12507,7 +12507,7 @@
         <v>1.97</v>
       </c>
       <c r="DO26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -12971,7 +12971,7 @@
         <v>3.01</v>
       </c>
       <c r="DO27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13415,7 +13415,7 @@
         <v>2.04</v>
       </c>
       <c r="DO28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -13837,7 +13837,7 @@
         <v>2.2</v>
       </c>
       <c r="DE29" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DF29" t="n">
         <v>3</v>
@@ -13867,7 +13867,7 @@
         <v>3.23</v>
       </c>
       <c r="DO29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14323,7 +14323,7 @@
         <v>3.75</v>
       </c>
       <c r="DO30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -14737,7 +14737,7 @@
         <v>1.27</v>
       </c>
       <c r="DE31" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF31" t="n">
         <v>1</v>
@@ -14767,7 +14767,7 @@
         <v>2.03</v>
       </c>
       <c r="DO31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15174,10 +15174,10 @@
         <v>50</v>
       </c>
       <c r="DD32" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DE32" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="DF32" t="n">
         <v>0</v>
@@ -15207,7 +15207,7 @@
         <v>1.95</v>
       </c>
       <c r="DO32" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -15626,7 +15626,7 @@
         <v>50</v>
       </c>
       <c r="DD33" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DE33" t="n">
         <v>0.6</v>
@@ -15659,7 +15659,7 @@
         <v>3.03</v>
       </c>
       <c r="DO33" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16054,10 +16054,10 @@
         <v>100</v>
       </c>
       <c r="DD34" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE34" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="DF34" t="n">
         <v>3</v>
@@ -16087,7 +16087,7 @@
         <v>2.73</v>
       </c>
       <c r="DO34" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -16507,7 +16507,7 @@
         <v>2.48</v>
       </c>
       <c r="DO35" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -16949,7 +16949,7 @@
         <v>1.9</v>
       </c>
       <c r="DE36" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DF36" t="n">
         <v>1.5</v>
@@ -16979,7 +16979,7 @@
         <v>2.73</v>
       </c>
       <c r="DO36" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -17394,7 +17394,7 @@
         <v>75</v>
       </c>
       <c r="DD37" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DE37" t="n">
         <v>0.4</v>
@@ -17427,7 +17427,7 @@
         <v>2.97</v>
       </c>
       <c r="DO37" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -17834,7 +17834,7 @@
         <v>100</v>
       </c>
       <c r="DD38" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="DE38" t="n">
         <v>0.9</v>
@@ -17867,7 +17867,7 @@
         <v>2.06</v>
       </c>
       <c r="DO38" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -18285,7 +18285,7 @@
         <v>1.5</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF39" t="n">
         <v>2</v>
@@ -18315,7 +18315,7 @@
         <v>2.78</v>
       </c>
       <c r="DO39" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -18755,7 +18755,7 @@
         <v>2.87</v>
       </c>
       <c r="DO40" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -19162,7 +19162,7 @@
         <v>75</v>
       </c>
       <c r="DD41" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DE41" t="n">
         <v>0.3</v>
@@ -19195,7 +19195,7 @@
         <v>2.54</v>
       </c>
       <c r="DO41" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -19613,7 +19613,7 @@
         <v>1.27</v>
       </c>
       <c r="DE42" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="DF42" t="n">
         <v>0.67</v>
@@ -19643,7 +19643,7 @@
         <v>2.35</v>
       </c>
       <c r="DO42" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -20066,10 +20066,10 @@
         <v>59</v>
       </c>
       <c r="DD43" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="DE43" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DF43" t="n">
         <v>2.33</v>
@@ -20099,7 +20099,7 @@
         <v>2.55</v>
       </c>
       <c r="DO43" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -20514,7 +20514,7 @@
         <v>84</v>
       </c>
       <c r="DD44" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="DE44" t="n">
         <v>0.3</v>
@@ -20547,7 +20547,7 @@
         <v>3.11</v>
       </c>
       <c r="DO44" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -20995,7 +20995,7 @@
         <v>2.4</v>
       </c>
       <c r="DO45" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -21459,7 +21459,7 @@
         <v>2.53</v>
       </c>
       <c r="DO46" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -21861,7 +21861,7 @@
         <v>1.67</v>
       </c>
       <c r="DE47" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF47" t="n">
         <v>2</v>
@@ -21891,7 +21891,7 @@
         <v>2.33</v>
       </c>
       <c r="DO47" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -22347,7 +22347,7 @@
         <v>3.02</v>
       </c>
       <c r="DO48" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -22754,7 +22754,7 @@
         <v>84</v>
       </c>
       <c r="DD49" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DE49" t="n">
         <v>1.55</v>
@@ -22787,7 +22787,7 @@
         <v>2.7</v>
       </c>
       <c r="DO49" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -23243,7 +23243,7 @@
         <v>2.38</v>
       </c>
       <c r="DO50" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -23642,7 +23642,7 @@
         <v>67</v>
       </c>
       <c r="DD51" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="DE51" t="n">
         <v>0.6</v>
@@ -23675,7 +23675,7 @@
         <v>2.54</v>
       </c>
       <c r="DO51" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -24123,7 +24123,7 @@
         <v>2</v>
       </c>
       <c r="DO52" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -24530,10 +24530,10 @@
         <v>75</v>
       </c>
       <c r="DD53" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DE53" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="DF53" t="n">
         <v>1.5</v>
@@ -24563,7 +24563,7 @@
         <v>3.04</v>
       </c>
       <c r="DO53" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -24962,7 +24962,7 @@
         <v>71</v>
       </c>
       <c r="DD54" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DE54" t="n">
         <v>1.55</v>
@@ -24995,7 +24995,7 @@
         <v>3.31</v>
       </c>
       <c r="DO54" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -25413,7 +25413,7 @@
         <v>2.2</v>
       </c>
       <c r="DE55" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DF55" t="n">
         <v>2.33</v>
@@ -25443,7 +25443,7 @@
         <v>2.77</v>
       </c>
       <c r="DO55" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -25857,7 +25857,7 @@
         <v>2.5</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF56" t="n">
         <v>3</v>
@@ -25887,7 +25887,7 @@
         <v>3.14</v>
       </c>
       <c r="DO56" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -26313,7 +26313,7 @@
         <v>1.64</v>
       </c>
       <c r="DE57" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="DF57" t="n">
         <v>2</v>
@@ -26343,7 +26343,7 @@
         <v>2.24</v>
       </c>
       <c r="DO57" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -26766,7 +26766,7 @@
         <v>63</v>
       </c>
       <c r="DD58" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="DE58" t="n">
         <v>0.3</v>
@@ -26799,7 +26799,7 @@
         <v>2.53</v>
       </c>
       <c r="DO58" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -27222,7 +27222,7 @@
         <v>100</v>
       </c>
       <c r="DD59" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DE59" t="n">
         <v>0.4</v>
@@ -27255,7 +27255,7 @@
         <v>2.96</v>
       </c>
       <c r="DO59" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -27657,7 +27657,7 @@
         <v>1.5</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DF60" t="n">
         <v>1.75</v>
@@ -27687,7 +27687,7 @@
         <v>3.31</v>
       </c>
       <c r="DO60" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -28113,7 +28113,7 @@
         <v>1.9</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="DF61" t="n">
         <v>2</v>
@@ -28143,7 +28143,7 @@
         <v>2.92</v>
       </c>
       <c r="DO61" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -28591,7 +28591,7 @@
         <v>3.61</v>
       </c>
       <c r="DO62" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -29011,7 +29011,7 @@
         <v>1.8</v>
       </c>
       <c r="DO63" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -29434,7 +29434,7 @@
         <v>100</v>
       </c>
       <c r="DD64" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE64" t="n">
         <v>1.4</v>
@@ -29467,7 +29467,7 @@
         <v>2.75</v>
       </c>
       <c r="DO64" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP64" t="b">
         <v>0</v>
@@ -29906,10 +29906,10 @@
         <v>67</v>
       </c>
       <c r="DD65" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DE65" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF65" t="n">
         <v>1.33</v>
@@ -29939,7 +29939,7 @@
         <v>3.14</v>
       </c>
       <c r="DO65" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -30346,10 +30346,10 @@
         <v>100</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DE66" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="DF66" t="n">
         <v>1.5</v>
@@ -30379,7 +30379,7 @@
         <v>2.54</v>
       </c>
       <c r="DO66" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -30782,7 +30782,7 @@
         <v>88</v>
       </c>
       <c r="DD67" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DE67" t="n">
         <v>0.6</v>
@@ -30815,7 +30815,7 @@
         <v>3</v>
       </c>
       <c r="DO67" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -31241,7 +31241,7 @@
         <v>1.64</v>
       </c>
       <c r="DE68" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="DF68" t="n">
         <v>2.33</v>
@@ -31271,7 +31271,7 @@
         <v>2.38</v>
       </c>
       <c r="DO68" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -31697,7 +31697,7 @@
         <v>1.27</v>
       </c>
       <c r="DE69" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="DF69" t="n">
         <v>0.8</v>
@@ -31727,7 +31727,7 @@
         <v>2.57</v>
       </c>
       <c r="DO69" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -32125,7 +32125,7 @@
         <v>2.18</v>
       </c>
       <c r="DE70" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DF70" t="n">
         <v>1.75</v>
@@ -32155,7 +32155,7 @@
         <v>2.43</v>
       </c>
       <c r="DO70" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -32566,7 +32566,7 @@
         <v>71</v>
       </c>
       <c r="DD71" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE71" t="n">
         <v>0.9</v>
@@ -32599,7 +32599,7 @@
         <v>2.46</v>
       </c>
       <c r="DO71" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP71" t="b">
         <v>0</v>
@@ -33055,7 +33055,7 @@
         <v>3.42</v>
       </c>
       <c r="DO72" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -33478,10 +33478,10 @@
         <v>88</v>
       </c>
       <c r="DD73" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DE73" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF73" t="n">
         <v>0.33</v>
@@ -33511,7 +33511,7 @@
         <v>2.46</v>
       </c>
       <c r="DO73" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -33945,7 +33945,7 @@
         <v>1.67</v>
       </c>
       <c r="DE74" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="DF74" t="n">
         <v>1.75</v>
@@ -33975,7 +33975,7 @@
         <v>2.54</v>
       </c>
       <c r="DO74" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -34431,7 +34431,7 @@
         <v>2.91</v>
       </c>
       <c r="DO75" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -34867,7 +34867,7 @@
         <v>3.09</v>
       </c>
       <c r="DO76" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -35306,10 +35306,10 @@
         <v>75</v>
       </c>
       <c r="DD77" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DE77" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF77" t="n">
         <v>1.75</v>
@@ -35339,7 +35339,7 @@
         <v>2.97</v>
       </c>
       <c r="DO77" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP77" t="b">
         <v>0</v>
@@ -35738,7 +35738,7 @@
         <v>88</v>
       </c>
       <c r="DD78" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="DE78" t="n">
         <v>0.4</v>
@@ -35771,7 +35771,7 @@
         <v>3.2</v>
       </c>
       <c r="DO78" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -36219,7 +36219,7 @@
         <v>3.14</v>
       </c>
       <c r="DO79" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -36659,7 +36659,7 @@
         <v>1.87</v>
       </c>
       <c r="DO80" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP80" t="b">
         <v>0</v>
@@ -37115,7 +37115,7 @@
         <v>2.45</v>
       </c>
       <c r="DO81" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -37502,7 +37502,7 @@
         <v>70</v>
       </c>
       <c r="DD82" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DE82" t="n">
         <v>1.4</v>
@@ -37535,7 +37535,7 @@
         <v>2.79</v>
       </c>
       <c r="DO82" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -37950,10 +37950,10 @@
         <v>80</v>
       </c>
       <c r="DD83" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="DE83" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DF83" t="n">
         <v>2</v>
@@ -37983,7 +37983,7 @@
         <v>2.19</v>
       </c>
       <c r="DO83" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -38393,7 +38393,7 @@
         <v>2.45</v>
       </c>
       <c r="DE84" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="DF84" t="n">
         <v>1.8</v>
@@ -38423,7 +38423,7 @@
         <v>3.27</v>
       </c>
       <c r="DO84" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -38825,7 +38825,7 @@
         <v>1.5</v>
       </c>
       <c r="DE85" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="DF85" t="n">
         <v>1.6</v>
@@ -38855,7 +38855,7 @@
         <v>3.26</v>
       </c>
       <c r="DO85" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -39315,7 +39315,7 @@
         <v>2.29</v>
       </c>
       <c r="DO86" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -39738,7 +39738,7 @@
         <v>70</v>
       </c>
       <c r="DD87" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DE87" t="n">
         <v>0.6</v>
@@ -39771,7 +39771,7 @@
         <v>1.93</v>
       </c>
       <c r="DO87" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -40197,7 +40197,7 @@
         <v>2.5</v>
       </c>
       <c r="DE88" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DF88" t="n">
         <v>2.6</v>
@@ -40227,7 +40227,7 @@
         <v>3.03</v>
       </c>
       <c r="DO88" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -40650,7 +40650,7 @@
         <v>65</v>
       </c>
       <c r="DD89" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE89" t="n">
         <v>0.3</v>
@@ -40683,7 +40683,7 @@
         <v>2.67</v>
       </c>
       <c r="DO89" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -40787,176 +40787,168 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
         <v>45948.41666666666</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" t="n">
         <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J90" t="n">
+        <v>5</v>
+      </c>
+      <c r="K90" t="n">
         <v>6</v>
       </c>
-      <c r="K90" t="n">
+      <c r="L90" t="n">
+        <v>11</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1</v>
+      </c>
+      <c r="N90" t="n">
+        <v>2</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
         <v>3</v>
       </c>
-      <c r="L90" t="n">
-        <v>9</v>
-      </c>
-      <c r="M90" t="n">
-        <v>2</v>
-      </c>
-      <c r="N90" t="n">
-        <v>2</v>
-      </c>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>11</v>
-      </c>
       <c r="R90" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="U90" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="V90" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W90" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="X90" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Y90" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="Z90" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>Stadion Nizhny Novgorod</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>ul. Dolzhanskaya, Nizhniy Novgorod</t>
-        </is>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="AA90" t="inlineStr"/>
+      <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD90" t="n">
         <v>2</v>
       </c>
       <c r="AE90" t="n">
-        <v>2.29</v>
+        <v>1.9</v>
       </c>
       <c r="AF90" t="n">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
       <c r="AG90" t="n">
-        <v>2.57</v>
+        <v>3.28</v>
       </c>
       <c r="AH90" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AI90" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AJ90" t="n">
-        <v>2.66</v>
+        <v>3.08</v>
       </c>
       <c r="AK90" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="AL90" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="AM90" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AN90" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AO90" t="n">
-        <v>2.16</v>
+        <v>2.62</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AR90" t="n">
-        <v>2.51</v>
+        <v>2.74</v>
       </c>
       <c r="AS90" t="n">
-        <v>3.32</v>
+        <v>3.04</v>
       </c>
       <c r="AT90" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AU90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV90" t="n">
         <v>0</v>
       </c>
       <c r="AW90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ90" t="n">
         <v>1</v>
       </c>
       <c r="BA90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB90" t="n">
-        <v>668270</v>
+        <v>-1</v>
       </c>
       <c r="BC90" t="n">
         <v>0</v>
       </c>
       <c r="BD90" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BE90" t="n">
         <v>0</v>
       </c>
       <c r="BF90" t="n">
-        <v>4088</v>
+        <v>6069</v>
       </c>
       <c r="BG90" t="n">
         <v>-1</v>
@@ -40983,7 +40975,7 @@
         <v>-1</v>
       </c>
       <c r="BO90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP90" t="n">
         <v>0</v>
@@ -40995,7 +40987,7 @@
         <v>2</v>
       </c>
       <c r="BS90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT90" t="n">
         <v>3</v>
@@ -41004,25 +40996,25 @@
         <v>1</v>
       </c>
       <c r="BV90" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="BW90" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="BX90" t="n">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="BY90" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="BZ90" t="n">
-        <v>2.82</v>
+        <v>1.44</v>
       </c>
       <c r="CA90" t="n">
-        <v>1.09</v>
+        <v>1.34</v>
       </c>
       <c r="CB90" t="n">
-        <v>3.91</v>
+        <v>2.78</v>
       </c>
       <c r="CC90" t="n">
         <v>0</v>
@@ -41070,82 +41062,82 @@
         <v>1</v>
       </c>
       <c r="CR90" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CS90" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CT90" t="n">
         <v>1</v>
       </c>
       <c r="CU90" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="CV90" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CW90" t="n">
         <v>1</v>
       </c>
       <c r="CX90" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="CY90" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="CZ90" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="DA90" t="n">
         <v>100</v>
       </c>
       <c r="DB90" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="DC90" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="DD90" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DE90" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DF90" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DG90" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DH90" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DI90" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DJ90" t="n">
+        <v>30</v>
+      </c>
+      <c r="DK90" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL90" t="n">
         <v>1.1</v>
       </c>
-      <c r="DE90" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="DF90" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="DG90" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="DH90" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="DI90" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="DJ90" t="n">
-        <v>20</v>
-      </c>
-      <c r="DK90" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL90" t="n">
-        <v>1.27</v>
-      </c>
       <c r="DM90" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="DN90" t="n">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="DO90" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
       </c>
       <c r="DQ90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR90" t="b">
         <v>0</v>
@@ -41160,66 +41152,66 @@
         <v>0</v>
       </c>
       <c r="DV90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW90" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="DX90" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="DY90" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="DZ90" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EA90" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EB90" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="EC90" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="ED90" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="EE90" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EF90" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="EG90" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="EH90" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EI90" t="inlineStr"/>
@@ -41243,168 +41235,176 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F91" s="2" t="n">
         <v>45948.41666666666</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
         <v>1</v>
       </c>
       <c r="I91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K91" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L91" t="n">
+        <v>9</v>
+      </c>
+      <c r="M91" t="n">
+        <v>2</v>
+      </c>
+      <c r="N91" t="n">
+        <v>2</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
         <v>11</v>
       </c>
-      <c r="M91" t="n">
-        <v>1</v>
-      </c>
-      <c r="N91" t="n">
-        <v>2</v>
-      </c>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>3</v>
-      </c>
       <c r="R91" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T91" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="U91" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="V91" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W91" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="X91" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Y91" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="Z91" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA91" t="inlineStr"/>
-      <c r="AB91" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>Stadion Nizhny Novgorod</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>ul. Dolzhanskaya, Nizhniy Novgorod</t>
+        </is>
+      </c>
       <c r="AC91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD91" t="n">
         <v>2</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.9</v>
+        <v>2.29</v>
       </c>
       <c r="AF91" t="n">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="AG91" t="n">
-        <v>3.28</v>
+        <v>2.57</v>
       </c>
       <c r="AH91" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AI91" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AJ91" t="n">
-        <v>3.08</v>
+        <v>2.66</v>
       </c>
       <c r="AK91" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AL91" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="AM91" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AN91" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AO91" t="n">
-        <v>2.62</v>
+        <v>2.16</v>
       </c>
       <c r="AP91" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR91" t="n">
-        <v>2.74</v>
+        <v>2.51</v>
       </c>
       <c r="AS91" t="n">
-        <v>3.04</v>
+        <v>3.32</v>
       </c>
       <c r="AT91" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AU91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV91" t="n">
         <v>0</v>
       </c>
       <c r="AW91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ91" t="n">
         <v>1</v>
       </c>
       <c r="BA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB91" t="n">
-        <v>-1</v>
+        <v>668270</v>
       </c>
       <c r="BC91" t="n">
         <v>0</v>
       </c>
       <c r="BD91" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BE91" t="n">
         <v>0</v>
       </c>
       <c r="BF91" t="n">
-        <v>6069</v>
+        <v>4088</v>
       </c>
       <c r="BG91" t="n">
         <v>-1</v>
@@ -41431,7 +41431,7 @@
         <v>-1</v>
       </c>
       <c r="BO91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP91" t="n">
         <v>0</v>
@@ -41443,7 +41443,7 @@
         <v>2</v>
       </c>
       <c r="BS91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT91" t="n">
         <v>3</v>
@@ -41452,25 +41452,25 @@
         <v>1</v>
       </c>
       <c r="BV91" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="BW91" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="BX91" t="n">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="BY91" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BZ91" t="n">
-        <v>1.44</v>
+        <v>2.82</v>
       </c>
       <c r="CA91" t="n">
-        <v>1.34</v>
+        <v>1.09</v>
       </c>
       <c r="CB91" t="n">
-        <v>2.78</v>
+        <v>3.91</v>
       </c>
       <c r="CC91" t="n">
         <v>0</v>
@@ -41518,82 +41518,82 @@
         <v>1</v>
       </c>
       <c r="CR91" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS91" t="n">
         <v>21</v>
       </c>
-      <c r="CS91" t="n">
-        <v>23</v>
-      </c>
       <c r="CT91" t="n">
         <v>1</v>
       </c>
       <c r="CU91" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="CV91" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CW91" t="n">
         <v>1</v>
       </c>
       <c r="CX91" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="CY91" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="CZ91" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="DA91" t="n">
         <v>100</v>
       </c>
       <c r="DB91" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="DC91" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="DD91" t="n">
-        <v>1.67</v>
+        <v>1.27</v>
       </c>
       <c r="DE91" t="n">
-        <v>0.4</v>
+        <v>1.18</v>
       </c>
       <c r="DF91" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="DG91" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="DH91" t="n">
-        <v>1.09</v>
+        <v>0.55</v>
       </c>
       <c r="DI91" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="DJ91" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="DK91" t="n">
         <v>0</v>
       </c>
       <c r="DL91" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DM91" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="DN91" t="n">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="DO91" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
       </c>
       <c r="DQ91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR91" t="b">
         <v>0</v>
@@ -41608,66 +41608,66 @@
         <v>0</v>
       </c>
       <c r="DV91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW91" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="DX91" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="DY91" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="DZ91" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EA91" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EB91" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="EC91" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="ED91" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="EE91" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="EF91" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="EG91" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EH91" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="EI91" t="inlineStr"/>
@@ -42043,7 +42043,7 @@
         <v>2.78</v>
       </c>
       <c r="DO92" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -42457,7 +42457,7 @@
         <v>1.64</v>
       </c>
       <c r="DE93" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF93" t="n">
         <v>1.8</v>
@@ -42487,7 +42487,7 @@
         <v>2.49</v>
       </c>
       <c r="DO93" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -42921,7 +42921,7 @@
         <v>2.2</v>
       </c>
       <c r="DE94" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF94" t="n">
         <v>2.2</v>
@@ -42951,7 +42951,7 @@
         <v>3.2</v>
       </c>
       <c r="DO94" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -43374,7 +43374,7 @@
         <v>84</v>
       </c>
       <c r="DD95" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DE95" t="n">
         <v>1.4</v>
@@ -43407,7 +43407,7 @@
         <v>2.32</v>
       </c>
       <c r="DO95" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -43818,7 +43818,7 @@
         <v>67</v>
       </c>
       <c r="DD96" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="DE96" t="n">
         <v>1.55</v>
@@ -43851,7 +43851,7 @@
         <v>2.71</v>
       </c>
       <c r="DO96" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -44253,7 +44253,7 @@
         <v>1.5</v>
       </c>
       <c r="DE97" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="DF97" t="n">
         <v>1.33</v>
@@ -44283,7 +44283,7 @@
         <v>3.18</v>
       </c>
       <c r="DO97" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -44739,7 +44739,7 @@
         <v>2.97</v>
       </c>
       <c r="DO98" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -45150,7 +45150,7 @@
         <v>72</v>
       </c>
       <c r="DD99" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DE99" t="n">
         <v>0.3</v>
@@ -45183,7 +45183,7 @@
         <v>2.84</v>
       </c>
       <c r="DO99" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -45581,7 +45581,7 @@
         <v>2.5</v>
       </c>
       <c r="DE100" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DF100" t="n">
         <v>2.67</v>
@@ -45611,7 +45611,7 @@
         <v>2.59</v>
       </c>
       <c r="DO100" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -46018,10 +46018,10 @@
         <v>75</v>
       </c>
       <c r="DD101" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DE101" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="DF101" t="n">
         <v>0.67</v>
@@ -46051,7 +46051,7 @@
         <v>2.97</v>
       </c>
       <c r="DO101" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -46474,7 +46474,7 @@
         <v>77</v>
       </c>
       <c r="DD102" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DE102" t="n">
         <v>1.55</v>
@@ -46507,7 +46507,7 @@
         <v>3.07</v>
       </c>
       <c r="DO102" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP102" t="b">
         <v>0</v>
@@ -46894,10 +46894,10 @@
         <v>60</v>
       </c>
       <c r="DD103" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="DE103" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="DF103" t="n">
         <v>2.6</v>
@@ -46927,7 +46927,7 @@
         <v>3.41</v>
       </c>
       <c r="DO103" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -47383,7 +47383,7 @@
         <v>3.31</v>
       </c>
       <c r="DO104" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -47823,7 +47823,7 @@
         <v>2.37</v>
       </c>
       <c r="DO105" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -48263,7 +48263,7 @@
         <v>2.66</v>
       </c>
       <c r="DO106" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -48669,7 +48669,7 @@
         <v>1.64</v>
       </c>
       <c r="DE107" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DF107" t="n">
         <v>1.5</v>
@@ -48699,7 +48699,7 @@
         <v>2.09</v>
       </c>
       <c r="DO107" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -49114,10 +49114,10 @@
         <v>61</v>
       </c>
       <c r="DD108" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="DE108" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="DF108" t="n">
         <v>1.86</v>
@@ -49147,7 +49147,7 @@
         <v>2.61</v>
       </c>
       <c r="DO108" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP108" t="b">
         <v>0</v>
@@ -49586,7 +49586,7 @@
         <v>75</v>
       </c>
       <c r="DD109" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DE109" t="n">
         <v>1.18</v>
@@ -49619,7 +49619,7 @@
         <v>2.81</v>
       </c>
       <c r="DO109" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -50034,10 +50034,10 @@
         <v>77</v>
       </c>
       <c r="DD110" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="DE110" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="DF110" t="n">
         <v>2.67</v>
@@ -50067,7 +50067,7 @@
         <v>3.47</v>
       </c>
       <c r="DO110" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -50507,7 +50507,7 @@
         <v>2.03</v>
       </c>
       <c r="DO111" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -50914,10 +50914,10 @@
         <v>80</v>
       </c>
       <c r="DD112" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE112" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="DF112" t="n">
         <v>1.8</v>
@@ -50947,7 +50947,7 @@
         <v>2.57</v>
       </c>
       <c r="DO112" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -51373,7 +51373,7 @@
         <v>2.45</v>
       </c>
       <c r="DE113" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DF113" t="n">
         <v>2.14</v>
@@ -51403,7 +51403,7 @@
         <v>3.33</v>
       </c>
       <c r="DO113" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -51851,7 +51851,7 @@
         <v>3.16</v>
       </c>
       <c r="DO114" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP114" t="b">
         <v>1</v>
@@ -52246,7 +52246,7 @@
         <v>77</v>
       </c>
       <c r="DD115" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DE115" t="n">
         <v>0.6</v>
@@ -52279,7 +52279,7 @@
         <v>2.71</v>
       </c>
       <c r="DO115" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP115" t="b">
         <v>0</v>
@@ -52689,7 +52689,7 @@
         <v>1.64</v>
       </c>
       <c r="DE116" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF116" t="n">
         <v>1.71</v>
@@ -52719,7 +52719,7 @@
         <v>2.74</v>
       </c>
       <c r="DO116" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP116" t="b">
         <v>1</v>
@@ -53122,7 +53122,7 @@
         <v>72</v>
       </c>
       <c r="DD117" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DE117" t="n">
         <v>0.9</v>
@@ -53155,7 +53155,7 @@
         <v>2.24</v>
       </c>
       <c r="DO117" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -53603,7 +53603,7 @@
         <v>2.53</v>
       </c>
       <c r="DO118" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -54039,7 +54039,7 @@
         <v>3.04</v>
       </c>
       <c r="DO119" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -54449,7 +54449,7 @@
         <v>1.9</v>
       </c>
       <c r="DE120" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DF120" t="n">
         <v>1.67</v>
@@ -54479,7 +54479,7 @@
         <v>3.17</v>
       </c>
       <c r="DO120" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -54918,10 +54918,10 @@
         <v>67</v>
       </c>
       <c r="DD121" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE121" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF121" t="n">
         <v>2</v>
@@ -54951,7 +54951,7 @@
         <v>2.7</v>
       </c>
       <c r="DO121" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -55370,7 +55370,7 @@
         <v>68</v>
       </c>
       <c r="DD122" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DE122" t="n">
         <v>0.4</v>
@@ -55403,7 +55403,7 @@
         <v>2.2</v>
       </c>
       <c r="DO122" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -55831,7 +55831,7 @@
         <v>2.75</v>
       </c>
       <c r="DO123" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP123" t="b">
         <v>0</v>
@@ -56257,7 +56257,7 @@
         <v>2.18</v>
       </c>
       <c r="DE124" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF124" t="n">
         <v>2.13</v>
@@ -56287,7 +56287,7 @@
         <v>3.02</v>
       </c>
       <c r="DO124" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -56710,10 +56710,10 @@
         <v>82</v>
       </c>
       <c r="DD125" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="DE125" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="DF125" t="n">
         <v>1.75</v>
@@ -56743,7 +56743,7 @@
         <v>2.41</v>
       </c>
       <c r="DO125" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP125" t="b">
         <v>1</v>
@@ -57191,7 +57191,7 @@
         <v>2.45</v>
       </c>
       <c r="DO126" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP126" t="b">
         <v>1</v>
@@ -57602,7 +57602,7 @@
         <v>63</v>
       </c>
       <c r="DD127" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DE127" t="n">
         <v>1.4</v>
@@ -57635,7 +57635,7 @@
         <v>2.81</v>
       </c>
       <c r="DO127" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP127" t="b">
         <v>1</v>
@@ -58083,7 +58083,7 @@
         <v>3.18</v>
       </c>
       <c r="DO128" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP128" t="b">
         <v>1</v>
@@ -58501,7 +58501,7 @@
         <v>2.2</v>
       </c>
       <c r="DE129" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF129" t="n">
         <v>2.43</v>
@@ -58531,7 +58531,7 @@
         <v>3.02</v>
       </c>
       <c r="DO129" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP129" t="b">
         <v>1</v>
@@ -58934,7 +58934,7 @@
         <v>73</v>
       </c>
       <c r="DD130" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DE130" t="n">
         <v>0.6</v>
@@ -58967,7 +58967,7 @@
         <v>2.38</v>
       </c>
       <c r="DO130" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP130" t="b">
         <v>1</v>
@@ -59423,7 +59423,7 @@
         <v>2.91</v>
       </c>
       <c r="DO131" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP131" t="b">
         <v>1</v>
@@ -59818,10 +59818,10 @@
         <v>71</v>
       </c>
       <c r="DD132" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE132" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DF132" t="n">
         <v>1.86</v>
@@ -59851,7 +59851,7 @@
         <v>2.78</v>
       </c>
       <c r="DO132" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP132" t="b">
         <v>1</v>
@@ -60269,7 +60269,7 @@
         <v>2.45</v>
       </c>
       <c r="DE133" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DF133" t="n">
         <v>2.25</v>
@@ -60299,7 +60299,7 @@
         <v>2.76</v>
       </c>
       <c r="DO133" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP133" t="b">
         <v>1</v>
@@ -60722,10 +60722,10 @@
         <v>66</v>
       </c>
       <c r="DD134" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DE134" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="DF134" t="n">
         <v>1.29</v>
@@ -60755,7 +60755,7 @@
         <v>2.93</v>
       </c>
       <c r="DO134" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP134" t="b">
         <v>1</v>
@@ -61181,7 +61181,7 @@
         <v>1.9</v>
       </c>
       <c r="DE135" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="DF135" t="n">
         <v>1.43</v>
@@ -61211,7 +61211,7 @@
         <v>3.07</v>
       </c>
       <c r="DO135" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP135" t="b">
         <v>1</v>
@@ -61626,7 +61626,7 @@
         <v>79</v>
       </c>
       <c r="DD136" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="DE136" t="n">
         <v>0.6</v>
@@ -61659,7 +61659,7 @@
         <v>3.08</v>
       </c>
       <c r="DO136" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP136" t="b">
         <v>1</v>
@@ -62098,7 +62098,7 @@
         <v>94</v>
       </c>
       <c r="DD137" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DE137" t="n">
         <v>0.3</v>
@@ -62131,7 +62131,7 @@
         <v>2.13</v>
       </c>
       <c r="DO137" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP137" t="b">
         <v>0</v>
@@ -62579,7 +62579,7 @@
         <v>2.95</v>
       </c>
       <c r="DO138" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP138" t="b">
         <v>1</v>
@@ -62994,7 +62994,7 @@
         <v>63</v>
       </c>
       <c r="DD139" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DE139" t="n">
         <v>0.6</v>
@@ -63027,7 +63027,7 @@
         <v>2.63</v>
       </c>
       <c r="DO139" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP139" t="b">
         <v>1</v>
@@ -63425,7 +63425,7 @@
         <v>2.18</v>
       </c>
       <c r="DE140" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="DF140" t="n">
         <v>2.22</v>
@@ -63455,7 +63455,7 @@
         <v>3.01</v>
       </c>
       <c r="DO140" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP140" t="b">
         <v>1</v>
@@ -63842,7 +63842,7 @@
         <v>69</v>
       </c>
       <c r="DD141" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="DE141" t="n">
         <v>1.18</v>
@@ -63875,7 +63875,7 @@
         <v>2.96</v>
       </c>
       <c r="DO141" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP141" t="b">
         <v>1</v>
@@ -64315,7 +64315,7 @@
         <v>2.35</v>
       </c>
       <c r="DO142" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP142" t="b">
         <v>1</v>
@@ -64746,10 +64746,10 @@
         <v>83</v>
       </c>
       <c r="DD143" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DE143" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="DF143" t="n">
         <v>0.63</v>
@@ -64779,7 +64779,7 @@
         <v>2.47</v>
       </c>
       <c r="DO143" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP143" t="b">
         <v>1</v>
@@ -65205,7 +65205,7 @@
         <v>2.45</v>
       </c>
       <c r="DE144" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF144" t="n">
         <v>2.33</v>
@@ -65235,7 +65235,7 @@
         <v>3.37</v>
       </c>
       <c r="DO144" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP144" t="b">
         <v>1</v>
@@ -65662,10 +65662,10 @@
         <v>76</v>
       </c>
       <c r="DD145" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE145" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DF145" t="n">
         <v>2</v>
@@ -65695,7 +65695,7 @@
         <v>2.2</v>
       </c>
       <c r="DO145" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP145" t="b">
         <v>1</v>
@@ -66094,7 +66094,7 @@
         <v>67</v>
       </c>
       <c r="DD146" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="DE146" t="n">
         <v>1.55</v>
@@ -66127,7 +66127,7 @@
         <v>3.19</v>
       </c>
       <c r="DO146" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP146" t="b">
         <v>1</v>
@@ -66571,7 +66571,7 @@
         <v>2.46</v>
       </c>
       <c r="DO147" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP147" t="b">
         <v>1</v>
@@ -67011,7 +67011,7 @@
         <v>3.3</v>
       </c>
       <c r="DO148" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP148" t="b">
         <v>1</v>
@@ -67475,7 +67475,7 @@
         <v>2.83</v>
       </c>
       <c r="DO149" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP149" t="b">
         <v>1</v>
@@ -67947,7 +67947,7 @@
         <v>2.37</v>
       </c>
       <c r="DO150" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP150" t="b">
         <v>1</v>
@@ -68365,7 +68365,7 @@
         <v>1.5</v>
       </c>
       <c r="DE151" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DF151" t="n">
         <v>1.33</v>
@@ -68395,7 +68395,7 @@
         <v>2.73</v>
       </c>
       <c r="DO151" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP151" t="b">
         <v>1</v>
@@ -68813,7 +68813,7 @@
         <v>1.9</v>
       </c>
       <c r="DE152" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF152" t="n">
         <v>1.78</v>
@@ -68843,7 +68843,7 @@
         <v>2.95</v>
       </c>
       <c r="DO152" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP152" t="b">
         <v>1</v>
@@ -69266,10 +69266,10 @@
         <v>76</v>
       </c>
       <c r="DD153" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DE153" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DF153" t="n">
         <v>0.5600000000000001</v>
@@ -69299,7 +69299,7 @@
         <v>2.44</v>
       </c>
       <c r="DO153" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP153" t="b">
         <v>1</v>
@@ -69722,7 +69722,7 @@
         <v>53</v>
       </c>
       <c r="DD154" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DE154" t="n">
         <v>1.55</v>
@@ -69755,7 +69755,7 @@
         <v>2.87</v>
       </c>
       <c r="DO154" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP154" t="b">
         <v>1</v>
@@ -70178,7 +70178,7 @@
         <v>56</v>
       </c>
       <c r="DD155" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DE155" t="n">
         <v>0.4</v>
@@ -70211,7 +70211,7 @@
         <v>2.37</v>
       </c>
       <c r="DO155" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP155" t="b">
         <v>1</v>
@@ -70667,7 +70667,7 @@
         <v>2.71</v>
       </c>
       <c r="DO156" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP156" t="b">
         <v>1</v>
@@ -71115,7 +71115,7 @@
         <v>2.26</v>
       </c>
       <c r="DO157" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP157" t="b">
         <v>1</v>
@@ -71522,10 +71522,10 @@
         <v>66</v>
       </c>
       <c r="DD158" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="DE158" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF158" t="n">
         <v>1.89</v>
@@ -71555,7 +71555,7 @@
         <v>2.57</v>
       </c>
       <c r="DO158" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP158" t="b">
         <v>1</v>
@@ -71981,7 +71981,7 @@
         <v>2.5</v>
       </c>
       <c r="DE159" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="DF159" t="n">
         <v>2.78</v>
@@ -72011,7 +72011,7 @@
         <v>3.18</v>
       </c>
       <c r="DO159" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP159" t="b">
         <v>1</v>
@@ -72429,7 +72429,7 @@
         <v>2.2</v>
       </c>
       <c r="DE160" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="DF160" t="n">
         <v>2.33</v>
@@ -72459,7 +72459,7 @@
         <v>2.88</v>
       </c>
       <c r="DO160" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP160" t="b">
         <v>1</v>
@@ -72931,7 +72931,7 @@
         <v>2.6</v>
       </c>
       <c r="DO161" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP161" t="b">
         <v>1</v>
@@ -73039,10 +73039,10 @@
         <v>6</v>
       </c>
       <c r="K162" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L162" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M162" t="n">
         <v>2</v>
@@ -73063,16 +73063,16 @@
         <v>3</v>
       </c>
       <c r="S162" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T162" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U162" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V162" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W162" t="n">
         <v>13</v>
@@ -73081,10 +73081,10 @@
         <v>13</v>
       </c>
       <c r="Y162" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Z162" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
@@ -73244,13 +73244,13 @@
         <v>87</v>
       </c>
       <c r="BZ162" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="CA162" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="CB162" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="CC162" t="n">
         <v>0</v>
@@ -73298,10 +73298,10 @@
         <v>1</v>
       </c>
       <c r="CR162" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS162" t="n">
         <v>22</v>
-      </c>
-      <c r="CS162" t="n">
-        <v>21</v>
       </c>
       <c r="CT162" t="n">
         <v>1</v>
@@ -73316,10 +73316,10 @@
         <v>1</v>
       </c>
       <c r="CX162" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CY162" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CZ162" t="n">
         <v>27</v>
@@ -73438,6 +73438,3202 @@
       <c r="EJ162" t="inlineStr"/>
       <c r="EK162" t="inlineStr"/>
       <c r="EL162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>21</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>FK Sochi</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Krasnodar</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="n">
+        <v>46095.44791666666</v>
+      </c>
+      <c r="G163" t="n">
+        <v>1</v>
+      </c>
+      <c r="H163" t="n">
+        <v>2</v>
+      </c>
+      <c r="I163" t="n">
+        <v>3</v>
+      </c>
+      <c r="J163" t="n">
+        <v>4</v>
+      </c>
+      <c r="K163" t="n">
+        <v>10</v>
+      </c>
+      <c r="L163" t="n">
+        <v>14</v>
+      </c>
+      <c r="M163" t="n">
+        <v>3</v>
+      </c>
+      <c r="N163" t="n">
+        <v>3</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>2</v>
+      </c>
+      <c r="R163" t="n">
+        <v>10</v>
+      </c>
+      <c r="S163" t="n">
+        <v>3</v>
+      </c>
+      <c r="T163" t="n">
+        <v>15</v>
+      </c>
+      <c r="U163" t="n">
+        <v>5</v>
+      </c>
+      <c r="V163" t="n">
+        <v>25</v>
+      </c>
+      <c r="W163" t="n">
+        <v>18</v>
+      </c>
+      <c r="X163" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>66</v>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>Olimpiyskiy Stadion Fisht</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>Olimpiyskiy prospekt, Sochi</t>
+        </is>
+      </c>
+      <c r="AC163" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD163" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="AF163" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG163" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH163" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI163" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ163" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AK163" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AL163" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM163" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AN163" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO163" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AP163" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AQ163" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR163" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AS163" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AT163" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AU163" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ163" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA163" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB163" t="n">
+        <v>926</v>
+      </c>
+      <c r="BC163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD163" t="n">
+        <v>47</v>
+      </c>
+      <c r="BE163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF163" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG163" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH163" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI163" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ163" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK163" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL163" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM163" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN163" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO163" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP163" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ163" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR163" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS163" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT163" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU163" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV163" t="n">
+        <v>43</v>
+      </c>
+      <c r="BW163" t="n">
+        <v>53</v>
+      </c>
+      <c r="BX163" t="n">
+        <v>79</v>
+      </c>
+      <c r="BY163" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ163" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="CA163" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="CB163" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="CC163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD163" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF163" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI163" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ163" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL163" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM163" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN163" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO163" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP163" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ163" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR163" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS163" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT163" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU163" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV163" t="n">
+        <v>20</v>
+      </c>
+      <c r="CW163" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX163" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY163" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ163" t="n">
+        <v>47</v>
+      </c>
+      <c r="DA163" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB163" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC163" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD163" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="DE163" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DF163" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DG163" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DH163" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="DI163" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="DJ163" t="n">
+        <v>54</v>
+      </c>
+      <c r="DK163" t="n">
+        <v>21</v>
+      </c>
+      <c r="DL163" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="DM163" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DN163" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="DO163" t="n">
+        <v>21</v>
+      </c>
+      <c r="DP163" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ163" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR163" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS163" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT163" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU163" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV163" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW163" t="inlineStr"/>
+      <c r="DX163" t="inlineStr"/>
+      <c r="DY163" t="inlineStr"/>
+      <c r="DZ163" t="inlineStr"/>
+      <c r="EA163" t="inlineStr"/>
+      <c r="EB163" t="inlineStr"/>
+      <c r="EC163" t="inlineStr"/>
+      <c r="ED163" t="inlineStr">
+        <is>
+          <t>9.89</t>
+        </is>
+      </c>
+      <c r="EE163" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EF163" t="inlineStr">
+        <is>
+          <t>5.53</t>
+        </is>
+      </c>
+      <c r="EG163" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EH163" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EI163" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EJ163" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EK163" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EL163" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>21</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Zenit</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Spartak Moskva</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="n">
+        <v>46095.54166666666</v>
+      </c>
+      <c r="G164" t="n">
+        <v>2</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0</v>
+      </c>
+      <c r="I164" t="n">
+        <v>2</v>
+      </c>
+      <c r="J164" t="n">
+        <v>2</v>
+      </c>
+      <c r="K164" t="n">
+        <v>5</v>
+      </c>
+      <c r="L164" t="n">
+        <v>7</v>
+      </c>
+      <c r="M164" t="n">
+        <v>2</v>
+      </c>
+      <c r="N164" t="n">
+        <v>4</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>4</v>
+      </c>
+      <c r="R164" t="n">
+        <v>0</v>
+      </c>
+      <c r="S164" t="n">
+        <v>7</v>
+      </c>
+      <c r="T164" t="n">
+        <v>9</v>
+      </c>
+      <c r="U164" t="n">
+        <v>11</v>
+      </c>
+      <c r="V164" t="n">
+        <v>9</v>
+      </c>
+      <c r="W164" t="n">
+        <v>7</v>
+      </c>
+      <c r="X164" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>45</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA164" t="inlineStr"/>
+      <c r="AB164" t="inlineStr"/>
+      <c r="AC164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD164" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF164" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG164" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AH164" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI164" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AJ164" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AK164" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AL164" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM164" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AN164" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AO164" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AP164" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AQ164" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR164" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AS164" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AT164" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV164" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX164" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ164" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA164" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB164" t="n">
+        <v>921</v>
+      </c>
+      <c r="BC164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD164" t="n">
+        <v>59</v>
+      </c>
+      <c r="BE164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF164" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG164" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH164" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI164" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ164" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK164" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL164" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM164" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN164" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO164" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP164" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR164" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS164" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT164" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU164" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV164" t="n">
+        <v>35</v>
+      </c>
+      <c r="BW164" t="n">
+        <v>57</v>
+      </c>
+      <c r="BX164" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY164" t="n">
+        <v>95</v>
+      </c>
+      <c r="BZ164" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CA164" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="CB164" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="CC164" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE164" t="n">
+        <v>2</v>
+      </c>
+      <c r="CF164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI164" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ164" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM164" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN164" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ164" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR164" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS164" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT164" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU164" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV164" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW164" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX164" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY164" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ164" t="n">
+        <v>54</v>
+      </c>
+      <c r="DA164" t="n">
+        <v>85</v>
+      </c>
+      <c r="DB164" t="n">
+        <v>37</v>
+      </c>
+      <c r="DC164" t="n">
+        <v>69</v>
+      </c>
+      <c r="DD164" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="DE164" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DF164" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="DG164" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DH164" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="DI164" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DJ164" t="n">
+        <v>47</v>
+      </c>
+      <c r="DK164" t="n">
+        <v>16</v>
+      </c>
+      <c r="DL164" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DM164" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="DN164" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="DO164" t="n">
+        <v>21</v>
+      </c>
+      <c r="DP164" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ164" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR164" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS164" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT164" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU164" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV164" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW164" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="DX164" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="DY164" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="DZ164" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EA164" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EB164" t="inlineStr">
+        <is>
+          <t>2.96</t>
+        </is>
+      </c>
+      <c r="EC164" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="ED164" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EE164" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="EF164" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="EG164" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EH164" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EI164" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EJ164" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="EK164" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EL164" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>21</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Rostov</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Dinamo Moskva</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="n">
+        <v>46095.63541666666</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="n">
+        <v>1</v>
+      </c>
+      <c r="I165" t="n">
+        <v>1</v>
+      </c>
+      <c r="J165" t="n">
+        <v>7</v>
+      </c>
+      <c r="K165" t="n">
+        <v>7</v>
+      </c>
+      <c r="L165" t="n">
+        <v>14</v>
+      </c>
+      <c r="M165" t="n">
+        <v>2</v>
+      </c>
+      <c r="N165" t="n">
+        <v>4</v>
+      </c>
+      <c r="O165" t="n">
+        <v>1</v>
+      </c>
+      <c r="P165" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>6</v>
+      </c>
+      <c r="R165" t="n">
+        <v>3</v>
+      </c>
+      <c r="S165" t="n">
+        <v>9</v>
+      </c>
+      <c r="T165" t="n">
+        <v>14</v>
+      </c>
+      <c r="U165" t="n">
+        <v>15</v>
+      </c>
+      <c r="V165" t="n">
+        <v>17</v>
+      </c>
+      <c r="W165" t="n">
+        <v>14</v>
+      </c>
+      <c r="X165" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>41</v>
+      </c>
+      <c r="Z165" t="n">
+        <v>59</v>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>Stadion Central’nyj im. I.P. Chayka</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>ul. Suvorova, Peschanokopskoye</t>
+        </is>
+      </c>
+      <c r="AC165" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD165" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE165" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AF165" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG165" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AH165" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI165" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AJ165" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AK165" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AL165" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AM165" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN165" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AO165" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AP165" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AQ165" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR165" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AS165" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AT165" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AU165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA165" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB165" t="n">
+        <v>935</v>
+      </c>
+      <c r="BC165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD165" t="n">
+        <v>60</v>
+      </c>
+      <c r="BE165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF165" t="n">
+        <v>10996</v>
+      </c>
+      <c r="BG165" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH165" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI165" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ165" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK165" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL165" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM165" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN165" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO165" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP165" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR165" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS165" t="n">
+        <v>5</v>
+      </c>
+      <c r="BT165" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU165" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV165" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW165" t="n">
+        <v>61</v>
+      </c>
+      <c r="BX165" t="n">
+        <v>68</v>
+      </c>
+      <c r="BY165" t="n">
+        <v>97</v>
+      </c>
+      <c r="BZ165" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CA165" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CB165" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="CC165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI165" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ165" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM165" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN165" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ165" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR165" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS165" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT165" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU165" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV165" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW165" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX165" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY165" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ165" t="n">
+        <v>35</v>
+      </c>
+      <c r="DA165" t="n">
+        <v>65</v>
+      </c>
+      <c r="DB165" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC165" t="n">
+        <v>60</v>
+      </c>
+      <c r="DD165" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DE165" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DF165" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DG165" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DH165" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DI165" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DJ165" t="n">
+        <v>65</v>
+      </c>
+      <c r="DK165" t="n">
+        <v>35</v>
+      </c>
+      <c r="DL165" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DM165" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DN165" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="DO165" t="n">
+        <v>21</v>
+      </c>
+      <c r="DP165" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ165" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR165" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS165" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT165" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU165" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV165" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW165" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="DX165" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="DY165" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="DZ165" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EA165" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EB165" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="EC165" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="ED165" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="EE165" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="EF165" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
+      <c r="EG165" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EH165" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EI165" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EJ165" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EK165" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EL165" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>21</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Baltika</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>CSKA Moskva</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="n">
+        <v>46095.72916666666</v>
+      </c>
+      <c r="G166" t="n">
+        <v>1</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0</v>
+      </c>
+      <c r="I166" t="n">
+        <v>1</v>
+      </c>
+      <c r="J166" t="n">
+        <v>5</v>
+      </c>
+      <c r="K166" t="n">
+        <v>6</v>
+      </c>
+      <c r="L166" t="n">
+        <v>11</v>
+      </c>
+      <c r="M166" t="n">
+        <v>3</v>
+      </c>
+      <c r="N166" t="n">
+        <v>2</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
+      <c r="P166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>5</v>
+      </c>
+      <c r="R166" t="n">
+        <v>4</v>
+      </c>
+      <c r="S166" t="n">
+        <v>5</v>
+      </c>
+      <c r="T166" t="n">
+        <v>8</v>
+      </c>
+      <c r="U166" t="n">
+        <v>10</v>
+      </c>
+      <c r="V166" t="n">
+        <v>12</v>
+      </c>
+      <c r="W166" t="n">
+        <v>23</v>
+      </c>
+      <c r="X166" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z166" t="n">
+        <v>62</v>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>Complexe Sportif Jean Bianchi 1</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>21 Avenue Marechal Leclerc, Saint-André-les-Vergers</t>
+        </is>
+      </c>
+      <c r="AC166" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD166" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AF166" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG166" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AH166" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI166" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AJ166" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AK166" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL166" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM166" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN166" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AO166" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AP166" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ166" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR166" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AS166" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AT166" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AU166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ166" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB166" t="n">
+        <v>1493</v>
+      </c>
+      <c r="BC166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD166" t="n">
+        <v>37</v>
+      </c>
+      <c r="BE166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF166" t="n">
+        <v>19860</v>
+      </c>
+      <c r="BG166" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH166" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI166" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ166" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK166" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL166" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM166" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN166" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO166" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ166" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR166" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS166" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT166" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU166" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV166" t="n">
+        <v>45</v>
+      </c>
+      <c r="BW166" t="n">
+        <v>56</v>
+      </c>
+      <c r="BX166" t="n">
+        <v>87</v>
+      </c>
+      <c r="BY166" t="n">
+        <v>110</v>
+      </c>
+      <c r="BZ166" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="CA166" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CB166" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="CC166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI166" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ166" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM166" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN166" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ166" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR166" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS166" t="n">
+        <v>32</v>
+      </c>
+      <c r="CT166" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU166" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV166" t="n">
+        <v>24</v>
+      </c>
+      <c r="CW166" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX166" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY166" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ166" t="n">
+        <v>26</v>
+      </c>
+      <c r="DA166" t="n">
+        <v>59</v>
+      </c>
+      <c r="DB166" t="n">
+        <v>26</v>
+      </c>
+      <c r="DC166" t="n">
+        <v>74</v>
+      </c>
+      <c r="DD166" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DE166" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF166" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DG166" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DH166" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DI166" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DJ166" t="n">
+        <v>75</v>
+      </c>
+      <c r="DK166" t="n">
+        <v>42</v>
+      </c>
+      <c r="DL166" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DM166" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DN166" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="DO166" t="n">
+        <v>21</v>
+      </c>
+      <c r="DP166" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ166" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR166" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS166" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT166" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU166" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV166" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW166" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="DX166" t="inlineStr">
+        <is>
+          <t>4.51</t>
+        </is>
+      </c>
+      <c r="DY166" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="DZ166" t="inlineStr"/>
+      <c r="EA166" t="inlineStr"/>
+      <c r="EB166" t="inlineStr"/>
+      <c r="EC166" t="inlineStr"/>
+      <c r="ED166" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="EE166" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="EF166" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="EG166" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EH166" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EI166" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EJ166" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EK166" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EL166" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>21</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Akron</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Akhmat Grozny</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="n">
+        <v>46096.45833333334</v>
+      </c>
+      <c r="G167" t="n">
+        <v>1</v>
+      </c>
+      <c r="H167" t="n">
+        <v>1</v>
+      </c>
+      <c r="I167" t="n">
+        <v>2</v>
+      </c>
+      <c r="J167" t="n">
+        <v>4</v>
+      </c>
+      <c r="K167" t="n">
+        <v>3</v>
+      </c>
+      <c r="L167" t="n">
+        <v>7</v>
+      </c>
+      <c r="M167" t="n">
+        <v>1</v>
+      </c>
+      <c r="N167" t="n">
+        <v>3</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>4</v>
+      </c>
+      <c r="R167" t="n">
+        <v>3</v>
+      </c>
+      <c r="S167" t="n">
+        <v>13</v>
+      </c>
+      <c r="T167" t="n">
+        <v>9</v>
+      </c>
+      <c r="U167" t="n">
+        <v>17</v>
+      </c>
+      <c r="V167" t="n">
+        <v>12</v>
+      </c>
+      <c r="W167" t="n">
+        <v>16</v>
+      </c>
+      <c r="X167" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z167" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA167" t="inlineStr"/>
+      <c r="AB167" t="inlineStr"/>
+      <c r="AC167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD167" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AF167" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AG167" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AH167" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI167" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AJ167" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AK167" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL167" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM167" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AN167" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO167" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AP167" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ167" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR167" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS167" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT167" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AU167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ167" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA167" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB167" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD167" t="n">
+        <v>75</v>
+      </c>
+      <c r="BE167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF167" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG167" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH167" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI167" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ167" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK167" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL167" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM167" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN167" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO167" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP167" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR167" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS167" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT167" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU167" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV167" t="n">
+        <v>71</v>
+      </c>
+      <c r="BW167" t="n">
+        <v>33</v>
+      </c>
+      <c r="BX167" t="n">
+        <v>113</v>
+      </c>
+      <c r="BY167" t="n">
+        <v>74</v>
+      </c>
+      <c r="BZ167" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CA167" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CB167" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="CC167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI167" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ167" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM167" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN167" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP167" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ167" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR167" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS167" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT167" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU167" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV167" t="n">
+        <v>20</v>
+      </c>
+      <c r="CW167" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX167" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY167" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ167" t="n">
+        <v>47</v>
+      </c>
+      <c r="DA167" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB167" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC167" t="n">
+        <v>90</v>
+      </c>
+      <c r="DD167" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DE167" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="DF167" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DG167" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DH167" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="DI167" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DJ167" t="n">
+        <v>53</v>
+      </c>
+      <c r="DK167" t="n">
+        <v>10</v>
+      </c>
+      <c r="DL167" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DM167" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="DN167" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="DO167" t="n">
+        <v>21</v>
+      </c>
+      <c r="DP167" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ167" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR167" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS167" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT167" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU167" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV167" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW167" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="DX167" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="DY167" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="DZ167" t="inlineStr"/>
+      <c r="EA167" t="inlineStr"/>
+      <c r="EB167" t="inlineStr"/>
+      <c r="EC167" t="inlineStr"/>
+      <c r="ED167" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="EE167" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EF167" t="inlineStr">
+        <is>
+          <t>3.51</t>
+        </is>
+      </c>
+      <c r="EG167" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EH167" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EI167" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EJ167" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EK167" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EL167" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>21</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Olimpiyets</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Krylya Sovetov</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="n">
+        <v>46096.5625</v>
+      </c>
+      <c r="G168" t="n">
+        <v>3</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0</v>
+      </c>
+      <c r="I168" t="n">
+        <v>3</v>
+      </c>
+      <c r="J168" t="n">
+        <v>7</v>
+      </c>
+      <c r="K168" t="n">
+        <v>2</v>
+      </c>
+      <c r="L168" t="n">
+        <v>9</v>
+      </c>
+      <c r="M168" t="n">
+        <v>1</v>
+      </c>
+      <c r="N168" t="n">
+        <v>2</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>9</v>
+      </c>
+      <c r="R168" t="n">
+        <v>3</v>
+      </c>
+      <c r="S168" t="n">
+        <v>7</v>
+      </c>
+      <c r="T168" t="n">
+        <v>7</v>
+      </c>
+      <c r="U168" t="n">
+        <v>16</v>
+      </c>
+      <c r="V168" t="n">
+        <v>10</v>
+      </c>
+      <c r="W168" t="n">
+        <v>7</v>
+      </c>
+      <c r="X168" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>45</v>
+      </c>
+      <c r="Z168" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>Stadion Nizhny Novgorod</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>ul. Dolzhanskaya, Nizhniy Novgorod</t>
+        </is>
+      </c>
+      <c r="AC168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE168" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AF168" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AG168" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH168" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI168" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ168" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AK168" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AL168" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM168" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AN168" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AO168" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AP168" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ168" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR168" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AS168" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AT168" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AU168" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ168" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA168" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB168" t="n">
+        <v>1482</v>
+      </c>
+      <c r="BC168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD168" t="n">
+        <v>43</v>
+      </c>
+      <c r="BE168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF168" t="n">
+        <v>6367</v>
+      </c>
+      <c r="BG168" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH168" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI168" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ168" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK168" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL168" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM168" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN168" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP168" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ168" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR168" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS168" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT168" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU168" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV168" t="n">
+        <v>37</v>
+      </c>
+      <c r="BW168" t="n">
+        <v>47</v>
+      </c>
+      <c r="BX168" t="n">
+        <v>78</v>
+      </c>
+      <c r="BY168" t="n">
+        <v>107</v>
+      </c>
+      <c r="BZ168" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CA168" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="CB168" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="CC168" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE168" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI168" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ168" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM168" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN168" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ168" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR168" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS168" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT168" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU168" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV168" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW168" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX168" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY168" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ168" t="n">
+        <v>53</v>
+      </c>
+      <c r="DA168" t="n">
+        <v>81</v>
+      </c>
+      <c r="DB168" t="n">
+        <v>28</v>
+      </c>
+      <c r="DC168" t="n">
+        <v>76</v>
+      </c>
+      <c r="DD168" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DE168" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="DF168" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DG168" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="DH168" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="DI168" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ168" t="n">
+        <v>48</v>
+      </c>
+      <c r="DK168" t="n">
+        <v>20</v>
+      </c>
+      <c r="DL168" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="DM168" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="DN168" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="DO168" t="n">
+        <v>21</v>
+      </c>
+      <c r="DP168" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ168" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR168" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS168" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT168" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU168" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV168" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW168" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="DX168" t="inlineStr">
+        <is>
+          <t>4.51</t>
+        </is>
+      </c>
+      <c r="DY168" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="DZ168" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EA168" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EB168" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="EC168" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="ED168" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EE168" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="EF168" t="inlineStr">
+        <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="EG168" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EH168" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EI168" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EJ168" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EK168" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EL168" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>21</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Lokomotiv Moskva</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="n">
+        <v>46096.66666666666</v>
+      </c>
+      <c r="G169" t="n">
+        <v>3</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0</v>
+      </c>
+      <c r="I169" t="n">
+        <v>3</v>
+      </c>
+      <c r="J169" t="n">
+        <v>4</v>
+      </c>
+      <c r="K169" t="n">
+        <v>4</v>
+      </c>
+      <c r="L169" t="n">
+        <v>8</v>
+      </c>
+      <c r="M169" t="n">
+        <v>1</v>
+      </c>
+      <c r="N169" t="n">
+        <v>5</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>4</v>
+      </c>
+      <c r="R169" t="n">
+        <v>2</v>
+      </c>
+      <c r="S169" t="n">
+        <v>9</v>
+      </c>
+      <c r="T169" t="n">
+        <v>5</v>
+      </c>
+      <c r="U169" t="n">
+        <v>13</v>
+      </c>
+      <c r="V169" t="n">
+        <v>7</v>
+      </c>
+      <c r="W169" t="n">
+        <v>14</v>
+      </c>
+      <c r="X169" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z169" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>Kazan' Arena</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>Prospekt Husaina Yamasheva 115a, Kazan'</t>
+        </is>
+      </c>
+      <c r="AC169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD169" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE169" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AF169" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG169" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AH169" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI169" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AJ169" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="AK169" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL169" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM169" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AN169" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AO169" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AP169" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AQ169" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR169" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AS169" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AT169" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU169" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX169" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ169" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB169" t="n">
+        <v>932</v>
+      </c>
+      <c r="BC169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD169" t="n">
+        <v>60</v>
+      </c>
+      <c r="BE169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF169" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG169" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI169" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ169" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK169" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL169" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM169" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN169" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP169" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR169" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS169" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT169" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV169" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW169" t="n">
+        <v>40</v>
+      </c>
+      <c r="BX169" t="n">
+        <v>91</v>
+      </c>
+      <c r="BY169" t="n">
+        <v>98</v>
+      </c>
+      <c r="BZ169" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CA169" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="CB169" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="CC169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM169" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN169" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR169" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS169" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU169" t="n">
+        <v>24</v>
+      </c>
+      <c r="CV169" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX169" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY169" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ169" t="n">
+        <v>45</v>
+      </c>
+      <c r="DA169" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB169" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC169" t="n">
+        <v>70</v>
+      </c>
+      <c r="DD169" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="DE169" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DF169" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG169" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DH169" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DI169" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="DJ169" t="n">
+        <v>55</v>
+      </c>
+      <c r="DK169" t="n">
+        <v>20</v>
+      </c>
+      <c r="DL169" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DM169" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DN169" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="DO169" t="n">
+        <v>21</v>
+      </c>
+      <c r="DP169" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ169" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR169" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS169" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT169" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU169" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV169" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW169" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="DX169" t="inlineStr">
+        <is>
+          <t>4.23</t>
+        </is>
+      </c>
+      <c r="DY169" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="DZ169" t="inlineStr"/>
+      <c r="EA169" t="inlineStr"/>
+      <c r="EB169" t="inlineStr"/>
+      <c r="EC169" t="inlineStr"/>
+      <c r="ED169" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="EE169" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EF169" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="EG169" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EH169" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EI169" t="inlineStr"/>
+      <c r="EJ169" t="inlineStr"/>
+      <c r="EK169" t="inlineStr"/>
+      <c r="EL169" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
+++ b/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
@@ -65825,13 +65825,13 @@
         <v>0</v>
       </c>
       <c r="Q146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R146" t="n">
         <v>1</v>
       </c>
       <c r="S146" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T146" t="n">
         <v>7</v>
@@ -66004,13 +66004,13 @@
         <v>97</v>
       </c>
       <c r="BZ146" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="CA146" t="n">
         <v>0.92</v>
       </c>
       <c r="CB146" t="n">
-        <v>2.54</v>
+        <v>2.47</v>
       </c>
       <c r="CC146" t="n">
         <v>0</v>
@@ -66079,7 +66079,7 @@
         <v>6</v>
       </c>
       <c r="CY146" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CZ146" t="n">
         <v>33</v>
@@ -67427,7 +67427,7 @@
         <v>6</v>
       </c>
       <c r="CY149" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CZ149" t="n">
         <v>54</v>
@@ -68557,10 +68557,10 @@
         <v>13</v>
       </c>
       <c r="Y152" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Z152" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
@@ -72630,13 +72630,13 @@
         <v>7</v>
       </c>
       <c r="T161" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U161" t="n">
         <v>16</v>
       </c>
       <c r="V161" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W161" t="n">
         <v>13</v>
@@ -72645,21 +72645,13 @@
         <v>16</v>
       </c>
       <c r="Y161" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Z161" t="n">
-        <v>35</v>
-      </c>
-      <c r="AA161" t="inlineStr">
-        <is>
-          <t>Otkrytiye Arena</t>
-        </is>
-      </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>Volokolamskoye shosse, Tushino, Moskva</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="AA161" t="inlineStr"/>
+      <c r="AB161" t="inlineStr"/>
       <c r="AC161" t="n">
         <v>2</v>
       </c>
@@ -72811,10 +72803,10 @@
         <v>2.03</v>
       </c>
       <c r="CA161" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="CB161" t="n">
-        <v>3.24</v>
+        <v>3.31</v>
       </c>
       <c r="CC161" t="n">
         <v>0</v>
@@ -73060,13 +73052,13 @@
         <v>4</v>
       </c>
       <c r="R162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S162" t="n">
         <v>9</v>
       </c>
       <c r="T162" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U162" t="n">
         <v>13</v>
@@ -73081,10 +73073,10 @@
         <v>13</v>
       </c>
       <c r="Y162" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Z162" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
@@ -73247,10 +73239,10 @@
         <v>1.45</v>
       </c>
       <c r="CA162" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="CB162" t="n">
-        <v>2.58</v>
+        <v>2.51</v>
       </c>
       <c r="CC162" t="n">
         <v>0</v>
@@ -73500,7 +73492,7 @@
         <v>2</v>
       </c>
       <c r="R163" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S163" t="n">
         <v>3</v>
@@ -73512,7 +73504,7 @@
         <v>5</v>
       </c>
       <c r="V163" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="W163" t="n">
         <v>18</v>
@@ -73687,10 +73679,10 @@
         <v>0.77</v>
       </c>
       <c r="CA163" t="n">
-        <v>2.65</v>
+        <v>2.91</v>
       </c>
       <c r="CB163" t="n">
-        <v>3.42</v>
+        <v>3.69</v>
       </c>
       <c r="CC163" t="n">
         <v>0</v>
@@ -73759,7 +73751,7 @@
         <v>9</v>
       </c>
       <c r="CY163" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CZ163" t="n">
         <v>47</v>
@@ -73947,13 +73939,13 @@
         <v>0</v>
       </c>
       <c r="S164" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T164" t="n">
         <v>9</v>
       </c>
       <c r="U164" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V164" t="n">
         <v>9</v>
@@ -74120,13 +74112,13 @@
         <v>95</v>
       </c>
       <c r="BZ164" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="CA164" t="n">
         <v>0.99</v>
       </c>
       <c r="CB164" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="CC164" t="n">
         <v>2</v>
@@ -74234,13 +74226,13 @@
         <v>16</v>
       </c>
       <c r="DL164" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DM164" t="n">
         <v>1.51</v>
       </c>
       <c r="DN164" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="DO164" t="n">
         <v>22</v>
@@ -74649,7 +74641,7 @@
         <v>16</v>
       </c>
       <c r="CS165" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CT165" t="n">
         <v>1</v>
@@ -74883,13 +74875,13 @@
         <v>4</v>
       </c>
       <c r="S166" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T166" t="n">
         <v>8</v>
       </c>
       <c r="U166" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V166" t="n">
         <v>12</v>
@@ -75064,13 +75056,13 @@
         <v>110</v>
       </c>
       <c r="BZ166" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="CA166" t="n">
         <v>1.45</v>
       </c>
       <c r="CB166" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="CC166" t="n">
         <v>0</v>
@@ -75339,13 +75331,13 @@
         <v>3</v>
       </c>
       <c r="S167" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T167" t="n">
         <v>9</v>
       </c>
       <c r="U167" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V167" t="n">
         <v>12</v>
@@ -75512,13 +75504,13 @@
         <v>74</v>
       </c>
       <c r="BZ167" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="CA167" t="n">
         <v>1.21</v>
       </c>
       <c r="CB167" t="n">
-        <v>3.07</v>
+        <v>3.13</v>
       </c>
       <c r="CC167" t="n">
         <v>0</v>
@@ -75566,7 +75558,7 @@
         <v>1</v>
       </c>
       <c r="CR167" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CS167" t="n">
         <v>15</v>
@@ -75787,16 +75779,16 @@
         <v>3</v>
       </c>
       <c r="S168" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T168" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U168" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="V168" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W168" t="n">
         <v>7</v>
@@ -75968,13 +75960,13 @@
         <v>107</v>
       </c>
       <c r="BZ168" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="CA168" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="CB168" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="CC168" t="n">
         <v>1</v>
@@ -76025,7 +76017,7 @@
         <v>17</v>
       </c>
       <c r="CS168" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CT168" t="n">
         <v>1</v>
@@ -76262,13 +76254,13 @@
         <v>9</v>
       </c>
       <c r="T169" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U169" t="n">
         <v>13</v>
       </c>
       <c r="V169" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W169" t="n">
         <v>14</v>
@@ -76443,10 +76435,10 @@
         <v>1.37</v>
       </c>
       <c r="CA169" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="CB169" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="CC169" t="n">
         <v>0</v>
@@ -78318,13 +78310,13 @@
         <v>25</v>
       </c>
       <c r="DL173" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="DM173" t="n">
         <v>0.92</v>
       </c>
       <c r="DN173" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="DO173" t="n">
         <v>22</v>
@@ -79373,10 +79365,10 @@
         <v>10</v>
       </c>
       <c r="Y176" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Z176" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AA176" t="inlineStr"/>
       <c r="AB176" t="inlineStr"/>
@@ -79781,22 +79773,22 @@
         <v>1</v>
       </c>
       <c r="Q177" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R177" t="n">
         <v>4</v>
       </c>
       <c r="S177" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T177" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U177" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="V177" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W177" t="n">
         <v>17</v>
@@ -79960,13 +79952,13 @@
         <v>68</v>
       </c>
       <c r="BZ177" t="n">
-        <v>2.27</v>
+        <v>2.46</v>
       </c>
       <c r="CA177" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="CB177" t="n">
-        <v>3.45</v>
+        <v>3.71</v>
       </c>
       <c r="CC177" t="n">
         <v>0</v>

--- a/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
+++ b/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
@@ -1616,7 +1616,7 @@
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>-1</v>
+        <v>15189</v>
       </c>
       <c r="BG2" t="n">
         <v>-1</v>
@@ -2048,7 +2048,7 @@
         <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>-1</v>
+        <v>10015</v>
       </c>
       <c r="BG3" t="n">
         <v>-1</v>
@@ -2484,7 +2484,7 @@
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-1</v>
+        <v>8102</v>
       </c>
       <c r="BG4" t="n">
         <v>-1</v>
@@ -2834,16 +2834,8 @@
       <c r="Z5" t="n">
         <v>37</v>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Otkrytiye Arena</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Volokolamskoye shosse, Tushino, Moskva</t>
-        </is>
-      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
         <v>3</v>
       </c>
@@ -2932,7 +2924,7 @@
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-1</v>
+        <v>17045</v>
       </c>
       <c r="BG5" t="n">
         <v>-1</v>
@@ -3396,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-1</v>
+        <v>2120</v>
       </c>
       <c r="BG6" t="n">
         <v>-1</v>
@@ -3860,7 +3852,7 @@
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-1</v>
+        <v>35338</v>
       </c>
       <c r="BG7" t="n">
         <v>-1</v>
@@ -4288,7 +4280,7 @@
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-1</v>
+        <v>4426</v>
       </c>
       <c r="BG8" t="n">
         <v>-1</v>
@@ -4744,7 +4736,7 @@
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-1</v>
+        <v>6792</v>
       </c>
       <c r="BG9" t="n">
         <v>-1</v>
@@ -5176,7 +5168,7 @@
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-1</v>
+        <v>9235</v>
       </c>
       <c r="BG10" t="n">
         <v>-1</v>
@@ -5518,16 +5510,8 @@
       <c r="Z11" t="n">
         <v>66</v>
       </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Otkrytiye Arena</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Volokolamskoye shosse, Tushino, Moskva</t>
-        </is>
-      </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
         <v>6</v>
       </c>
@@ -5616,7 +5600,7 @@
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>-1</v>
+        <v>20072</v>
       </c>
       <c r="BG11" t="n">
         <v>-1</v>
@@ -6064,7 +6048,7 @@
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-1</v>
+        <v>15603</v>
       </c>
       <c r="BG12" t="n">
         <v>-1</v>
@@ -6500,7 +6484,7 @@
         <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>-1</v>
+        <v>28257</v>
       </c>
       <c r="BG13" t="n">
         <v>-1</v>
@@ -6964,7 +6948,7 @@
         <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>-1</v>
+        <v>6029</v>
       </c>
       <c r="BG14" t="n">
         <v>-1</v>
@@ -7271,28 +7255,28 @@
         <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="U15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="V15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="W15" t="n">
+        <v>19</v>
+      </c>
+      <c r="X15" t="n">
         <v>18</v>
       </c>
-      <c r="X15" t="n">
-        <v>17</v>
-      </c>
       <c r="Y15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Z15" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -7392,7 +7376,7 @@
         <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>-1</v>
+        <v>10751</v>
       </c>
       <c r="BG15" t="n">
         <v>-1</v>
@@ -7452,13 +7436,13 @@
         <v>93</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="CB15" t="n">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="CC15" t="n">
         <v>0</v>
@@ -7527,7 +7511,7 @@
         <v>8</v>
       </c>
       <c r="CY15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CZ15" t="n">
         <v>0</v>
@@ -7864,7 +7848,7 @@
         <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>-1</v>
+        <v>5437</v>
       </c>
       <c r="BG16" t="n">
         <v>-1</v>
@@ -8320,7 +8304,7 @@
         <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>-1</v>
+        <v>23456</v>
       </c>
       <c r="BG17" t="n">
         <v>-1</v>
@@ -8760,7 +8744,7 @@
         <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>-1</v>
+        <v>9577</v>
       </c>
       <c r="BG18" t="n">
         <v>-1</v>
@@ -9216,7 +9200,7 @@
         <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>-1</v>
+        <v>25445</v>
       </c>
       <c r="BG19" t="n">
         <v>-1</v>
@@ -9656,7 +9640,7 @@
         <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>-1</v>
+        <v>232</v>
       </c>
       <c r="BG20" t="n">
         <v>-1</v>
@@ -10068,7 +10052,7 @@
         <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>-1</v>
+        <v>9338</v>
       </c>
       <c r="BG21" t="n">
         <v>-1</v>
@@ -10426,16 +10410,8 @@
       <c r="Z22" t="n">
         <v>61</v>
       </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>Complexe Sportif Jean Bianchi 1</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>21 Avenue Marechal Leclerc, Saint-André-les-Vergers</t>
-        </is>
-      </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
         <v>5</v>
       </c>
@@ -10524,7 +10500,7 @@
         <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>-1</v>
+        <v>16731</v>
       </c>
       <c r="BG22" t="n">
         <v>-1</v>
@@ -10968,7 +10944,7 @@
         <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>-1</v>
+        <v>45371</v>
       </c>
       <c r="BG23" t="n">
         <v>-1</v>
@@ -11424,7 +11400,7 @@
         <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>-1</v>
+        <v>6788</v>
       </c>
       <c r="BG24" t="n">
         <v>-1</v>
@@ -11601,10 +11577,10 @@
         <v>0</v>
       </c>
       <c r="DM24" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="DN24" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="DO24" t="n">
         <v>22</v>
@@ -11852,7 +11828,7 @@
         <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>-1</v>
+        <v>8952</v>
       </c>
       <c r="BG25" t="n">
         <v>-1</v>
@@ -12324,7 +12300,7 @@
         <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>-1</v>
+        <v>6277</v>
       </c>
       <c r="BG26" t="n">
         <v>-1</v>
@@ -12788,7 +12764,7 @@
         <v>0</v>
       </c>
       <c r="BF27" t="n">
-        <v>-1</v>
+        <v>11664</v>
       </c>
       <c r="BG27" t="n">
         <v>-1</v>
@@ -13232,7 +13208,7 @@
         <v>0</v>
       </c>
       <c r="BF28" t="n">
-        <v>-1</v>
+        <v>11815</v>
       </c>
       <c r="BG28" t="n">
         <v>-1</v>
@@ -13406,13 +13382,13 @@
         <v>0</v>
       </c>
       <c r="DL28" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="DM28" t="n">
         <v>0.62</v>
       </c>
       <c r="DN28" t="n">
-        <v>2.04</v>
+        <v>2.17</v>
       </c>
       <c r="DO28" t="n">
         <v>22</v>
@@ -13684,7 +13660,7 @@
         <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>-1</v>
+        <v>21808</v>
       </c>
       <c r="BG29" t="n">
         <v>-1</v>
@@ -14140,7 +14116,7 @@
         <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>-1</v>
+        <v>4769</v>
       </c>
       <c r="BG30" t="n">
         <v>-1</v>
@@ -14584,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>-1</v>
+        <v>6527</v>
       </c>
       <c r="BG31" t="n">
         <v>-1</v>
@@ -15024,7 +15000,7 @@
         <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>-1</v>
+        <v>7782</v>
       </c>
       <c r="BG32" t="n">
         <v>-1</v>
@@ -15476,7 +15452,7 @@
         <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>-1</v>
+        <v>8824</v>
       </c>
       <c r="BG33" t="n">
         <v>-1</v>
@@ -15904,7 +15880,7 @@
         <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>-1</v>
+        <v>16731</v>
       </c>
       <c r="BG34" t="n">
         <v>-1</v>
@@ -16226,16 +16202,8 @@
       <c r="Z35" t="n">
         <v>41</v>
       </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>Otkrytiye Arena</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>Volokolamskoye shosse, Tushino, Moskva</t>
-        </is>
-      </c>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="n">
         <v>1</v>
       </c>
@@ -16324,7 +16292,7 @@
         <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>-1</v>
+        <v>17045</v>
       </c>
       <c r="BG35" t="n">
         <v>-1</v>
@@ -16796,7 +16764,7 @@
         <v>0</v>
       </c>
       <c r="BF36" t="n">
-        <v>-1</v>
+        <v>4769</v>
       </c>
       <c r="BG36" t="n">
         <v>-1</v>
@@ -17244,7 +17212,7 @@
         <v>0</v>
       </c>
       <c r="BF37" t="n">
-        <v>-1</v>
+        <v>3522</v>
       </c>
       <c r="BG37" t="n">
         <v>-1</v>
@@ -17684,7 +17652,7 @@
         <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>-1</v>
+        <v>13438</v>
       </c>
       <c r="BG38" t="n">
         <v>-1</v>
@@ -18132,7 +18100,7 @@
         <v>0</v>
       </c>
       <c r="BF39" t="n">
-        <v>-1</v>
+        <v>22626</v>
       </c>
       <c r="BG39" t="n">
         <v>-1</v>
@@ -18572,7 +18540,7 @@
         <v>0</v>
       </c>
       <c r="BF40" t="n">
-        <v>-1</v>
+        <v>27173</v>
       </c>
       <c r="BG40" t="n">
         <v>-1</v>
@@ -19012,7 +18980,7 @@
         <v>0</v>
       </c>
       <c r="BF41" t="n">
-        <v>-1</v>
+        <v>4243</v>
       </c>
       <c r="BG41" t="n">
         <v>-1</v>
@@ -19460,7 +19428,7 @@
         <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>-1</v>
+        <v>4966</v>
       </c>
       <c r="BG42" t="n">
         <v>-1</v>
@@ -19637,10 +19605,10 @@
         <v>0.98</v>
       </c>
       <c r="DM42" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="DN42" t="n">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="DO42" t="n">
         <v>22</v>
@@ -19916,7 +19884,7 @@
         <v>0</v>
       </c>
       <c r="BF43" t="n">
-        <v>-1</v>
+        <v>34128</v>
       </c>
       <c r="BG43" t="n">
         <v>-1</v>
@@ -20364,7 +20332,7 @@
         <v>0</v>
       </c>
       <c r="BF44" t="n">
-        <v>-1</v>
+        <v>31466</v>
       </c>
       <c r="BG44" t="n">
         <v>-1</v>
@@ -20812,7 +20780,7 @@
         <v>0</v>
       </c>
       <c r="BF45" t="n">
-        <v>-1</v>
+        <v>11055</v>
       </c>
       <c r="BG45" t="n">
         <v>-1</v>
@@ -21276,7 +21244,7 @@
         <v>0</v>
       </c>
       <c r="BF46" t="n">
-        <v>-1</v>
+        <v>10070</v>
       </c>
       <c r="BG46" t="n">
         <v>-1</v>
@@ -21708,7 +21676,7 @@
         <v>0</v>
       </c>
       <c r="BF47" t="n">
-        <v>-1</v>
+        <v>14900</v>
       </c>
       <c r="BG47" t="n">
         <v>-1</v>
@@ -22164,7 +22132,7 @@
         <v>0</v>
       </c>
       <c r="BF48" t="n">
-        <v>-1</v>
+        <v>13758</v>
       </c>
       <c r="BG48" t="n">
         <v>-1</v>
@@ -22338,13 +22306,13 @@
         <v>0</v>
       </c>
       <c r="DL48" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="DM48" t="n">
         <v>1.44</v>
       </c>
       <c r="DN48" t="n">
-        <v>3.02</v>
+        <v>3.09</v>
       </c>
       <c r="DO48" t="n">
         <v>22</v>
@@ -22604,7 +22572,7 @@
         <v>0</v>
       </c>
       <c r="BF49" t="n">
-        <v>-1</v>
+        <v>4264</v>
       </c>
       <c r="BG49" t="n">
         <v>-1</v>
@@ -23060,7 +23028,7 @@
         <v>0</v>
       </c>
       <c r="BF50" t="n">
-        <v>-1</v>
+        <v>4903</v>
       </c>
       <c r="BG50" t="n">
         <v>-1</v>
@@ -23492,7 +23460,7 @@
         <v>0</v>
       </c>
       <c r="BF51" t="n">
-        <v>-1</v>
+        <v>36106</v>
       </c>
       <c r="BG51" t="n">
         <v>-1</v>
@@ -23842,16 +23810,8 @@
       <c r="Z52" t="n">
         <v>31</v>
       </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>Otkrytiye Arena</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>Volokolamskoye shosse, Tushino, Moskva</t>
-        </is>
-      </c>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="n">
         <v>1</v>
       </c>
@@ -23940,7 +23900,7 @@
         <v>0</v>
       </c>
       <c r="BF52" t="n">
-        <v>-1</v>
+        <v>19265</v>
       </c>
       <c r="BG52" t="n">
         <v>-1</v>
@@ -24380,7 +24340,7 @@
         <v>0</v>
       </c>
       <c r="BF53" t="n">
-        <v>-1</v>
+        <v>8386</v>
       </c>
       <c r="BG53" t="n">
         <v>-1</v>
@@ -24557,10 +24517,10 @@
         <v>1.76</v>
       </c>
       <c r="DM53" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="DN53" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="DO53" t="n">
         <v>22</v>
@@ -24812,7 +24772,7 @@
         <v>0</v>
       </c>
       <c r="BF54" t="n">
-        <v>-1</v>
+        <v>3240</v>
       </c>
       <c r="BG54" t="n">
         <v>-1</v>
@@ -25260,7 +25220,7 @@
         <v>0</v>
       </c>
       <c r="BF55" t="n">
-        <v>-1</v>
+        <v>9733</v>
       </c>
       <c r="BG55" t="n">
         <v>-1</v>
@@ -25704,7 +25664,7 @@
         <v>0</v>
       </c>
       <c r="BF56" t="n">
-        <v>-1</v>
+        <v>24675</v>
       </c>
       <c r="BG56" t="n">
         <v>-1</v>
@@ -25878,13 +25838,13 @@
         <v>17</v>
       </c>
       <c r="DL56" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="DM56" t="n">
         <v>1.55</v>
       </c>
       <c r="DN56" t="n">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="DO56" t="n">
         <v>22</v>
@@ -26160,7 +26120,7 @@
         <v>0</v>
       </c>
       <c r="BF57" t="n">
-        <v>-1</v>
+        <v>8304</v>
       </c>
       <c r="BG57" t="n">
         <v>-1</v>
@@ -26616,7 +26576,7 @@
         <v>0</v>
       </c>
       <c r="BF58" t="n">
-        <v>-1</v>
+        <v>11051</v>
       </c>
       <c r="BG58" t="n">
         <v>-1</v>
@@ -27072,7 +27032,7 @@
         <v>0</v>
       </c>
       <c r="BF59" t="n">
-        <v>-1</v>
+        <v>2667</v>
       </c>
       <c r="BG59" t="n">
         <v>-1</v>
@@ -27512,7 +27472,7 @@
         <v>0</v>
       </c>
       <c r="BF60" t="n">
-        <v>-1</v>
+        <v>4320</v>
       </c>
       <c r="BG60" t="n">
         <v>-1</v>
@@ -27952,7 +27912,7 @@
         <v>0</v>
       </c>
       <c r="BF61" t="n">
-        <v>-1</v>
+        <v>22917</v>
       </c>
       <c r="BG61" t="n">
         <v>-1</v>
@@ -28408,7 +28368,7 @@
         <v>0</v>
       </c>
       <c r="BF62" t="n">
-        <v>-1</v>
+        <v>27503</v>
       </c>
       <c r="BG62" t="n">
         <v>-1</v>
@@ -28828,7 +28788,7 @@
         <v>0</v>
       </c>
       <c r="BF63" t="n">
-        <v>-1</v>
+        <v>10156</v>
       </c>
       <c r="BG63" t="n">
         <v>-1</v>
@@ -29284,7 +29244,7 @@
         <v>0</v>
       </c>
       <c r="BF64" t="n">
-        <v>-1</v>
+        <v>27447</v>
       </c>
       <c r="BG64" t="n">
         <v>-1</v>
@@ -29756,7 +29716,7 @@
         <v>0</v>
       </c>
       <c r="BF65" t="n">
-        <v>-1</v>
+        <v>16444</v>
       </c>
       <c r="BG65" t="n">
         <v>-1</v>
@@ -30196,7 +30156,7 @@
         <v>0</v>
       </c>
       <c r="BF66" t="n">
-        <v>-1</v>
+        <v>3053</v>
       </c>
       <c r="BG66" t="n">
         <v>-1</v>
@@ -30373,10 +30333,10 @@
         <v>1.33</v>
       </c>
       <c r="DM66" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="DN66" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="DO66" t="n">
         <v>22</v>
@@ -30632,7 +30592,7 @@
         <v>0</v>
       </c>
       <c r="BF67" t="n">
-        <v>-1</v>
+        <v>2838</v>
       </c>
       <c r="BG67" t="n">
         <v>-1</v>
@@ -31088,7 +31048,7 @@
         <v>0</v>
       </c>
       <c r="BF68" t="n">
-        <v>-1</v>
+        <v>4599</v>
       </c>
       <c r="BG68" t="n">
         <v>-1</v>
@@ -31544,7 +31504,7 @@
         <v>0</v>
       </c>
       <c r="BF69" t="n">
-        <v>-1</v>
+        <v>5438</v>
       </c>
       <c r="BG69" t="n">
         <v>-1</v>
@@ -31874,16 +31834,8 @@
       <c r="Z70" t="n">
         <v>29</v>
       </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>Otkrytiye Arena</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>Volokolamskoye shosse, Tushino, Moskva</t>
-        </is>
-      </c>
+      <c r="AA70" t="inlineStr"/>
+      <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="n">
         <v>1</v>
       </c>
@@ -31972,7 +31924,7 @@
         <v>0</v>
       </c>
       <c r="BF70" t="n">
-        <v>-1</v>
+        <v>20180</v>
       </c>
       <c r="BG70" t="n">
         <v>-1</v>
@@ -32416,7 +32368,7 @@
         <v>0</v>
       </c>
       <c r="BF71" t="n">
-        <v>-1</v>
+        <v>17248</v>
       </c>
       <c r="BG71" t="n">
         <v>-1</v>
@@ -32872,7 +32824,7 @@
         <v>0</v>
       </c>
       <c r="BF72" t="n">
-        <v>-1</v>
+        <v>33000</v>
       </c>
       <c r="BG72" t="n">
         <v>-1</v>
@@ -33328,7 +33280,7 @@
         <v>0</v>
       </c>
       <c r="BF73" t="n">
-        <v>-1</v>
+        <v>6348</v>
       </c>
       <c r="BG73" t="n">
         <v>-1</v>
@@ -36210,13 +36162,13 @@
         <v>0</v>
       </c>
       <c r="DL79" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="DM79" t="n">
         <v>1.6</v>
       </c>
       <c r="DN79" t="n">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="DO79" t="n">
         <v>22</v>
@@ -36834,16 +36786,8 @@
       <c r="Z81" t="n">
         <v>31</v>
       </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>Otkrytiye Arena</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>Volokolamskoye shosse, Tushino, Moskva</t>
-        </is>
-      </c>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="n">
         <v>2</v>
       </c>
@@ -38240,7 +38184,7 @@
         <v>0</v>
       </c>
       <c r="BF84" t="n">
-        <v>-1</v>
+        <v>25617</v>
       </c>
       <c r="BG84" t="n">
         <v>-1</v>
@@ -38417,10 +38361,10 @@
         <v>2.04</v>
       </c>
       <c r="DM84" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="DN84" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="DO84" t="n">
         <v>22</v>
@@ -40218,13 +40162,13 @@
         <v>10</v>
       </c>
       <c r="DL88" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="DM88" t="n">
         <v>1.37</v>
       </c>
       <c r="DN88" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="DO88" t="n">
         <v>22</v>
@@ -41762,16 +41706,8 @@
       <c r="Z92" t="n">
         <v>39</v>
       </c>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>Otkrytiye Arena</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>Volokolamskoye shosse, Tushino, Moskva</t>
-        </is>
-      </c>
+      <c r="AA92" t="inlineStr"/>
+      <c r="AB92" t="inlineStr"/>
       <c r="AC92" t="n">
         <v>4</v>
       </c>
@@ -41860,7 +41796,7 @@
         <v>0</v>
       </c>
       <c r="BF92" t="n">
-        <v>-1</v>
+        <v>21338</v>
       </c>
       <c r="BG92" t="n">
         <v>-1</v>
@@ -42304,7 +42240,7 @@
         <v>0</v>
       </c>
       <c r="BF93" t="n">
-        <v>-1</v>
+        <v>6026</v>
       </c>
       <c r="BG93" t="n">
         <v>-1</v>
@@ -43668,7 +43604,7 @@
         <v>0</v>
       </c>
       <c r="BF96" t="n">
-        <v>-1</v>
+        <v>9031</v>
       </c>
       <c r="BG96" t="n">
         <v>-1</v>
@@ -44277,10 +44213,10 @@
         <v>1.94</v>
       </c>
       <c r="DM97" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="DN97" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="DO97" t="n">
         <v>22</v>
@@ -44458,16 +44394,8 @@
       <c r="Z98" t="n">
         <v>34</v>
       </c>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>Otkrytiye Arena</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>Volokolamskoye shosse, Tushino, Moskva</t>
-        </is>
-      </c>
+      <c r="AA98" t="inlineStr"/>
+      <c r="AB98" t="inlineStr"/>
       <c r="AC98" t="n">
         <v>1</v>
       </c>
@@ -45602,13 +45530,13 @@
         <v>9</v>
       </c>
       <c r="DL100" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="DM100" t="n">
         <v>1.01</v>
       </c>
       <c r="DN100" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="DO100" t="n">
         <v>22</v>
@@ -45868,7 +45796,7 @@
         <v>0</v>
       </c>
       <c r="BF101" t="n">
-        <v>-1</v>
+        <v>8531</v>
       </c>
       <c r="BG101" t="n">
         <v>-1</v>
@@ -48254,13 +48182,13 @@
         <v>23</v>
       </c>
       <c r="DL106" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="DM106" t="n">
         <v>0.99</v>
       </c>
       <c r="DN106" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="DO106" t="n">
         <v>22</v>
@@ -50941,10 +50869,10 @@
         <v>1.29</v>
       </c>
       <c r="DM112" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="DN112" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="DO112" t="n">
         <v>22</v>
@@ -51220,7 +51148,7 @@
         <v>0</v>
       </c>
       <c r="BF113" t="n">
-        <v>-1</v>
+        <v>33000</v>
       </c>
       <c r="BG113" t="n">
         <v>-1</v>
@@ -53420,7 +53348,7 @@
         <v>0</v>
       </c>
       <c r="BF118" t="n">
-        <v>-1</v>
+        <v>7865</v>
       </c>
       <c r="BG118" t="n">
         <v>-1</v>
@@ -56006,16 +55934,8 @@
       <c r="Z124" t="n">
         <v>51</v>
       </c>
-      <c r="AA124" t="inlineStr">
-        <is>
-          <t>Otkrytiye Arena</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>Volokolamskoye shosse, Tushino, Moskva</t>
-        </is>
-      </c>
+      <c r="AA124" t="inlineStr"/>
+      <c r="AB124" t="inlineStr"/>
       <c r="AC124" t="n">
         <v>2</v>
       </c>
@@ -56737,10 +56657,10 @@
         <v>1.17</v>
       </c>
       <c r="DM125" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="DN125" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="DO125" t="n">
         <v>22</v>
@@ -59414,13 +59334,13 @@
         <v>27</v>
       </c>
       <c r="DL131" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="DM131" t="n">
         <v>1.22</v>
       </c>
       <c r="DN131" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="DO131" t="n">
         <v>22</v>
@@ -59668,7 +59588,7 @@
         <v>0</v>
       </c>
       <c r="BF132" t="n">
-        <v>-1</v>
+        <v>19629</v>
       </c>
       <c r="BG132" t="n">
         <v>-1</v>
@@ -63174,16 +63094,8 @@
       <c r="Z140" t="n">
         <v>42</v>
       </c>
-      <c r="AA140" t="inlineStr">
-        <is>
-          <t>Otkrytiye Arena</t>
-        </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>Volokolamskoye shosse, Tushino, Moskva</t>
-        </is>
-      </c>
+      <c r="AA140" t="inlineStr"/>
+      <c r="AB140" t="inlineStr"/>
       <c r="AC140" t="n">
         <v>2</v>
       </c>
@@ -63272,7 +63184,7 @@
         <v>0</v>
       </c>
       <c r="BF140" t="n">
-        <v>-1</v>
+        <v>27727</v>
       </c>
       <c r="BG140" t="n">
         <v>-1</v>
@@ -72002,13 +71914,13 @@
         <v>28</v>
       </c>
       <c r="DL159" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="DM159" t="n">
         <v>1.5</v>
       </c>
       <c r="DN159" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="DO159" t="n">
         <v>22</v>
@@ -72453,10 +72365,10 @@
         <v>1.69</v>
       </c>
       <c r="DM160" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="DN160" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="DO160" t="n">
         <v>22</v>
@@ -75621,10 +75533,10 @@
         <v>1.38</v>
       </c>
       <c r="DM167" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="DN167" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="DO167" t="n">
         <v>22</v>
@@ -77426,13 +77338,13 @@
         <v>25</v>
       </c>
       <c r="DL171" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="DM171" t="n">
         <v>1.18</v>
       </c>
       <c r="DN171" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="DO171" t="n">
         <v>22</v>

--- a/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
+++ b/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL177" headerRowCount="1">
-  <autoFilter ref="A1:EL177"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL183" headerRowCount="1">
+  <autoFilter ref="A1:EL183"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL177"/>
+  <dimension ref="A1:EL183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.8" customWidth="1" min="1" max="1"/>
@@ -1766,10 +1766,10 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2198,10 +2198,10 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -3538,10 +3538,10 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DE6" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3571,7 +3571,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4002,10 +4002,10 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4035,7 +4035,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4430,7 +4430,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="DE8" t="n">
         <v>0.64</v>
@@ -4889,7 +4889,7 @@
         <v>1.17</v>
       </c>
       <c r="DE9" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP9" t="b">
         <v>0</v>
@@ -5351,7 +5351,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5753,7 +5753,7 @@
         <v>2.18</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DF11" t="n">
         <v>3</v>
@@ -6198,10 +6198,10 @@
         <v>100</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="DF12" t="n">
         <v>1</v>
@@ -6231,7 +6231,7 @@
         <v>2.72</v>
       </c>
       <c r="DO12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7559,7 +7559,7 @@
         <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8031,7 +8031,7 @@
         <v>1.72</v>
       </c>
       <c r="DO16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8897,7 +8897,7 @@
         <v>1.18</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="DF18" t="n">
         <v>0</v>
@@ -8927,7 +8927,7 @@
         <v>1.28</v>
       </c>
       <c r="DO18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9383,7 +9383,7 @@
         <v>1.82</v>
       </c>
       <c r="DO19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -9790,7 +9790,7 @@
         <v>100</v>
       </c>
       <c r="DD20" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DE20" t="n">
         <v>1.73</v>
@@ -10202,7 +10202,7 @@
         <v>50</v>
       </c>
       <c r="DD21" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="DE21" t="n">
         <v>1.27</v>
@@ -10653,7 +10653,7 @@
         <v>2.27</v>
       </c>
       <c r="DE22" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="DF22" t="n">
         <v>0</v>
@@ -10683,7 +10683,7 @@
         <v>0</v>
       </c>
       <c r="DO22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11094,10 +11094,10 @@
         <v>50</v>
       </c>
       <c r="DD23" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DE23" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="DF23" t="n">
         <v>3</v>
@@ -11127,7 +11127,7 @@
         <v>3.96</v>
       </c>
       <c r="DO23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -11550,7 +11550,7 @@
         <v>50</v>
       </c>
       <c r="DD24" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="DE24" t="n">
         <v>0.73</v>
@@ -11583,7 +11583,7 @@
         <v>1.2</v>
       </c>
       <c r="DO24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12450,7 +12450,7 @@
         <v>100</v>
       </c>
       <c r="DD26" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="DE26" t="n">
         <v>1.08</v>
@@ -12483,7 +12483,7 @@
         <v>1.97</v>
       </c>
       <c r="DO26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -12917,7 +12917,7 @@
         <v>1.6</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DF27" t="n">
         <v>3</v>
@@ -12947,7 +12947,7 @@
         <v>3.01</v>
       </c>
       <c r="DO27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14266,7 +14266,7 @@
         <v>100</v>
       </c>
       <c r="DD30" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="DE30" t="n">
         <v>1.55</v>
@@ -14299,7 +14299,7 @@
         <v>3.75</v>
       </c>
       <c r="DO30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -14713,7 +14713,7 @@
         <v>1.17</v>
       </c>
       <c r="DE31" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DF31" t="n">
         <v>1</v>
@@ -14743,7 +14743,7 @@
         <v>2.03</v>
       </c>
       <c r="DO31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15635,7 +15635,7 @@
         <v>3.03</v>
       </c>
       <c r="DO33" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16914,10 +16914,10 @@
         <v>100</v>
       </c>
       <c r="DD36" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="DE36" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="DF36" t="n">
         <v>1.5</v>
@@ -16947,7 +16947,7 @@
         <v>2.73</v>
       </c>
       <c r="DO36" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -17362,10 +17362,10 @@
         <v>75</v>
       </c>
       <c r="DD37" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="DE37" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="DF37" t="n">
         <v>1</v>
@@ -17395,7 +17395,7 @@
         <v>2.97</v>
       </c>
       <c r="DO37" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -17805,7 +17805,7 @@
         <v>2.09</v>
       </c>
       <c r="DE38" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="DF38" t="n">
         <v>2</v>
@@ -18250,10 +18250,10 @@
         <v>75</v>
       </c>
       <c r="DD39" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DE39" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="DF39" t="n">
         <v>2</v>
@@ -18283,7 +18283,7 @@
         <v>2.78</v>
       </c>
       <c r="DO39" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19130,7 +19130,7 @@
         <v>75</v>
       </c>
       <c r="DD41" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DE41" t="n">
         <v>0.27</v>
@@ -19163,7 +19163,7 @@
         <v>2.54</v>
       </c>
       <c r="DO41" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -19611,7 +19611,7 @@
         <v>2.42</v>
       </c>
       <c r="DO42" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -20482,7 +20482,7 @@
         <v>84</v>
       </c>
       <c r="DD44" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DE44" t="n">
         <v>0.27</v>
@@ -20515,7 +20515,7 @@
         <v>3.11</v>
       </c>
       <c r="DO44" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -20933,7 +20933,7 @@
         <v>2.27</v>
       </c>
       <c r="DE45" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="DF45" t="n">
         <v>3</v>
@@ -21394,7 +21394,7 @@
         <v>50</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DE46" t="n">
         <v>0.55</v>
@@ -21427,7 +21427,7 @@
         <v>2.53</v>
       </c>
       <c r="DO46" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -21829,7 +21829,7 @@
         <v>1.6</v>
       </c>
       <c r="DE47" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DF47" t="n">
         <v>2</v>
@@ -21859,7 +21859,7 @@
         <v>2.33</v>
       </c>
       <c r="DO47" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -22315,7 +22315,7 @@
         <v>3.09</v>
       </c>
       <c r="DO48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -22725,7 +22725,7 @@
         <v>0.45</v>
       </c>
       <c r="DE49" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DF49" t="n">
         <v>0.5</v>
@@ -23610,7 +23610,7 @@
         <v>67</v>
       </c>
       <c r="DD51" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DE51" t="n">
         <v>0.55</v>
@@ -23643,7 +23643,7 @@
         <v>2.54</v>
       </c>
       <c r="DO51" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -24523,7 +24523,7 @@
         <v>3.08</v>
       </c>
       <c r="DO53" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -24922,10 +24922,10 @@
         <v>71</v>
       </c>
       <c r="DD54" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="DE54" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DF54" t="n">
         <v>0.67</v>
@@ -24955,7 +24955,7 @@
         <v>3.31</v>
       </c>
       <c r="DO54" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -25373,7 +25373,7 @@
         <v>2.27</v>
       </c>
       <c r="DE55" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="DF55" t="n">
         <v>2.33</v>
@@ -25817,7 +25817,7 @@
         <v>2.55</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DF56" t="n">
         <v>3</v>
@@ -25847,7 +25847,7 @@
         <v>3.18</v>
       </c>
       <c r="DO56" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -26270,7 +26270,7 @@
         <v>75</v>
       </c>
       <c r="DD57" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="DE57" t="n">
         <v>1.36</v>
@@ -26303,7 +26303,7 @@
         <v>2.24</v>
       </c>
       <c r="DO57" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -27182,10 +27182,10 @@
         <v>100</v>
       </c>
       <c r="DD59" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DE59" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="DF59" t="n">
         <v>1</v>
@@ -27215,7 +27215,7 @@
         <v>2.96</v>
       </c>
       <c r="DO59" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -27303,37 +27303,37 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
         <v>45913.57291666666</v>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K60" t="n">
         <v>5</v>
       </c>
       <c r="L60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N60" t="n">
         <v>4</v>
@@ -27345,7 +27345,7 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R60" t="n">
         <v>4</v>
@@ -27354,110 +27354,102 @@
         <v>9</v>
       </c>
       <c r="T60" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="U60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V60" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="W60" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="X60" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y60" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="Z60" t="n">
-        <v>62</v>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>Akhmat Arena</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
-        </is>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD60" t="n">
         <v>4</v>
       </c>
       <c r="AE60" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="AF60" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="AG60" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AI60" t="n">
         <v>1.77</v>
       </c>
       <c r="AJ60" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="AK60" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AL60" t="n">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="AM60" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="AN60" t="n">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AO60" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AQ60" t="n">
         <v>1.38</v>
       </c>
       <c r="AR60" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="AS60" t="n">
-        <v>2.88</v>
+        <v>3.07</v>
       </c>
       <c r="AT60" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AU60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY60" t="n">
         <v>1</v>
       </c>
       <c r="AZ60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB60" t="n">
         <v>-1</v>
@@ -27466,13 +27458,13 @@
         <v>0</v>
       </c>
       <c r="BD60" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="BE60" t="n">
         <v>0</v>
       </c>
       <c r="BF60" t="n">
-        <v>4320</v>
+        <v>22917</v>
       </c>
       <c r="BG60" t="n">
         <v>-1</v>
@@ -27502,43 +27494,43 @@
         <v>0</v>
       </c>
       <c r="BP60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BQ60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR60" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS60" t="n">
         <v>3</v>
       </c>
-      <c r="BS60" t="n">
-        <v>1</v>
-      </c>
       <c r="BT60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BU60" t="n">
         <v>1</v>
       </c>
       <c r="BV60" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="BW60" t="n">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="BX60" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="BY60" t="n">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="BZ60" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="CA60" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="CB60" t="n">
-        <v>3.11</v>
+        <v>2.81</v>
       </c>
       <c r="CC60" t="n">
         <v>0</v>
@@ -27586,19 +27578,19 @@
         <v>1</v>
       </c>
       <c r="CR60" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="CS60" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CT60" t="n">
         <v>1</v>
       </c>
       <c r="CU60" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="CV60" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="CW60" t="n">
         <v>1</v>
@@ -27607,52 +27599,52 @@
         <v>4</v>
       </c>
       <c r="CY60" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CZ60" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="DA60" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="DB60" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="DC60" t="n">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="DD60" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.73</v>
+        <v>1.27</v>
       </c>
       <c r="DF60" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DG60" t="n">
-        <v>2.33</v>
+        <v>1.33</v>
       </c>
       <c r="DH60" t="n">
         <v>1.14</v>
       </c>
       <c r="DI60" t="n">
-        <v>2.14</v>
+        <v>1.57</v>
       </c>
       <c r="DJ60" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="DK60" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="DL60" t="n">
-        <v>1.47</v>
+        <v>1.97</v>
       </c>
       <c r="DM60" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="DN60" t="n">
-        <v>2.92</v>
+        <v>3.31</v>
       </c>
       <c r="DO60" t="n">
         <v>22</v>
@@ -27664,10 +27656,10 @@
         <v>1</v>
       </c>
       <c r="DR60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT60" t="b">
         <v>0</v>
@@ -27680,17 +27672,17 @@
       </c>
       <c r="DW60" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="DX60" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="DY60" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="DZ60" t="inlineStr"/>
@@ -27699,41 +27691,49 @@
       <c r="EC60" t="inlineStr"/>
       <c r="ED60" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="EE60" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="EF60" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EG60" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="EH60" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="EI60" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EJ60" t="inlineStr">
         <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="EK60" t="inlineStr"/>
-      <c r="EL60" t="inlineStr"/>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EK60" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EL60" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -27751,37 +27751,37 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F61" s="2" t="n">
         <v>45913.57291666666</v>
       </c>
       <c r="G61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K61" t="n">
         <v>5</v>
       </c>
       <c r="L61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
         <v>4</v>
@@ -27793,7 +27793,7 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R61" t="n">
         <v>4</v>
@@ -27802,183 +27802,191 @@
         <v>9</v>
       </c>
       <c r="T61" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="U61" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V61" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W61" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="X61" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y61" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="Z61" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA61" t="inlineStr"/>
-      <c r="AB61" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>Akhmat Arena</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
+        </is>
+      </c>
       <c r="AC61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD61" t="n">
         <v>4</v>
       </c>
       <c r="AE61" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="AF61" t="n">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="AG61" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AI61" t="n">
         <v>1.77</v>
       </c>
       <c r="AJ61" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="AK61" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AL61" t="n">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="AM61" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="AN61" t="n">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AO61" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AQ61" t="n">
         <v>1.38</v>
       </c>
       <c r="AR61" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="AS61" t="n">
-        <v>3.07</v>
+        <v>2.88</v>
       </c>
       <c r="AT61" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AU61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY61" t="n">
         <v>1</v>
       </c>
       <c r="AZ61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD61" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF61" t="n">
+        <v>4320</v>
+      </c>
+      <c r="BG61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH61" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP61" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR61" t="n">
         <v>3</v>
       </c>
-      <c r="BB61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BC61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD61" t="n">
-        <v>59</v>
-      </c>
-      <c r="BE61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF61" t="n">
-        <v>22917</v>
-      </c>
-      <c r="BG61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BH61" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BJ61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BK61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BL61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BM61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BN61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BO61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP61" t="n">
+      <c r="BS61" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT61" t="n">
         <v>3</v>
       </c>
-      <c r="BQ61" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR61" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS61" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT61" t="n">
-        <v>2</v>
-      </c>
       <c r="BU61" t="n">
         <v>1</v>
       </c>
       <c r="BV61" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="BW61" t="n">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="BX61" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="BY61" t="n">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="BZ61" t="n">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="CA61" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="CB61" t="n">
-        <v>2.81</v>
+        <v>3.11</v>
       </c>
       <c r="CC61" t="n">
         <v>0</v>
@@ -28026,19 +28034,19 @@
         <v>1</v>
       </c>
       <c r="CR61" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="CS61" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT61" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU61" t="n">
         <v>17</v>
       </c>
-      <c r="CT61" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU61" t="n">
-        <v>21</v>
-      </c>
       <c r="CV61" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="CW61" t="n">
         <v>1</v>
@@ -28047,52 +28055,52 @@
         <v>4</v>
       </c>
       <c r="CY61" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CZ61" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="DA61" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="DB61" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="DC61" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.27</v>
+        <v>1.73</v>
       </c>
       <c r="DF61" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="DG61" t="n">
-        <v>1.33</v>
+        <v>2.33</v>
       </c>
       <c r="DH61" t="n">
         <v>1.14</v>
       </c>
       <c r="DI61" t="n">
-        <v>1.57</v>
+        <v>2.14</v>
       </c>
       <c r="DJ61" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="DK61" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="DL61" t="n">
-        <v>1.97</v>
+        <v>1.47</v>
       </c>
       <c r="DM61" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="DN61" t="n">
-        <v>3.31</v>
+        <v>2.92</v>
       </c>
       <c r="DO61" t="n">
         <v>22</v>
@@ -28104,10 +28112,10 @@
         <v>1</v>
       </c>
       <c r="DR61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT61" t="b">
         <v>0</v>
@@ -28120,17 +28128,17 @@
       </c>
       <c r="DW61" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="DX61" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="DY61" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="DZ61" t="inlineStr"/>
@@ -28139,49 +28147,41 @@
       <c r="EC61" t="inlineStr"/>
       <c r="ED61" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="EE61" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="EF61" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="EG61" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="EH61" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EI61" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EJ61" t="inlineStr">
         <is>
-          <t>1.99</t>
-        </is>
-      </c>
-      <c r="EK61" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EL61" t="inlineStr">
-        <is>
-          <t>2.58</t>
-        </is>
-      </c>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EK61" t="inlineStr"/>
+      <c r="EL61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -28551,7 +28551,7 @@
         <v>3.61</v>
       </c>
       <c r="DO62" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -29427,7 +29427,7 @@
         <v>2.75</v>
       </c>
       <c r="DO64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP64" t="b">
         <v>0</v>
@@ -29869,7 +29869,7 @@
         <v>1.18</v>
       </c>
       <c r="DE65" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="DF65" t="n">
         <v>1.33</v>
@@ -29899,7 +29899,7 @@
         <v>3.14</v>
       </c>
       <c r="DO65" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -30306,7 +30306,7 @@
         <v>100</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DE66" t="n">
         <v>0.73</v>
@@ -30339,7 +30339,7 @@
         <v>2.57</v>
       </c>
       <c r="DO66" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -30742,7 +30742,7 @@
         <v>88</v>
       </c>
       <c r="DD67" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="DE67" t="n">
         <v>0.64</v>
@@ -31198,7 +31198,7 @@
         <v>71</v>
       </c>
       <c r="DD68" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="DE68" t="n">
         <v>1.73</v>
@@ -31687,7 +31687,7 @@
         <v>2.57</v>
       </c>
       <c r="DO69" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -32077,7 +32077,7 @@
         <v>2.18</v>
       </c>
       <c r="DE70" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="DF70" t="n">
         <v>1.75</v>
@@ -32521,7 +32521,7 @@
         <v>2.27</v>
       </c>
       <c r="DE71" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="DF71" t="n">
         <v>1.67</v>
@@ -32551,7 +32551,7 @@
         <v>2.46</v>
       </c>
       <c r="DO71" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP71" t="b">
         <v>0</v>
@@ -33007,7 +33007,7 @@
         <v>3.42</v>
       </c>
       <c r="DO72" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -33433,7 +33433,7 @@
         <v>0.45</v>
       </c>
       <c r="DE73" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="DF73" t="n">
         <v>0.33</v>
@@ -33927,7 +33927,7 @@
         <v>2.54</v>
       </c>
       <c r="DO74" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -34350,7 +34350,7 @@
         <v>88</v>
       </c>
       <c r="DD75" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="DE75" t="n">
         <v>1.08</v>
@@ -34383,7 +34383,7 @@
         <v>2.91</v>
       </c>
       <c r="DO75" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -35261,7 +35261,7 @@
         <v>1.18</v>
       </c>
       <c r="DE77" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DF77" t="n">
         <v>1.75</v>
@@ -35291,7 +35291,7 @@
         <v>2.97</v>
       </c>
       <c r="DO77" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP77" t="b">
         <v>0</v>
@@ -35690,10 +35690,10 @@
         <v>88</v>
       </c>
       <c r="DD78" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DE78" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="DF78" t="n">
         <v>2.5</v>
@@ -35723,7 +35723,7 @@
         <v>3.2</v>
       </c>
       <c r="DO78" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -36141,7 +36141,7 @@
         <v>2.55</v>
       </c>
       <c r="DE79" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DF79" t="n">
         <v>2.5</v>
@@ -36171,7 +36171,7 @@
         <v>3.17</v>
       </c>
       <c r="DO79" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -36578,7 +36578,7 @@
         <v>45</v>
       </c>
       <c r="DD80" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="DE80" t="n">
         <v>0.36</v>
@@ -37446,7 +37446,7 @@
         <v>70</v>
       </c>
       <c r="DD82" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="DE82" t="n">
         <v>1.55</v>
@@ -37479,7 +37479,7 @@
         <v>2.79</v>
       </c>
       <c r="DO82" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -37897,7 +37897,7 @@
         <v>2.09</v>
       </c>
       <c r="DE83" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="DF83" t="n">
         <v>2</v>
@@ -38367,7 +38367,7 @@
         <v>3.3</v>
       </c>
       <c r="DO84" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -38766,7 +38766,7 @@
         <v>80</v>
       </c>
       <c r="DD85" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DE85" t="n">
         <v>1.73</v>
@@ -39229,7 +39229,7 @@
         <v>1.17</v>
       </c>
       <c r="DE86" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="DF86" t="n">
         <v>0.67</v>
@@ -39259,7 +39259,7 @@
         <v>2.29</v>
       </c>
       <c r="DO86" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -40627,7 +40627,7 @@
         <v>2.67</v>
       </c>
       <c r="DO89" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -40731,176 +40731,168 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
         <v>45948.41666666666</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" t="n">
         <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J90" t="n">
+        <v>5</v>
+      </c>
+      <c r="K90" t="n">
         <v>6</v>
       </c>
-      <c r="K90" t="n">
+      <c r="L90" t="n">
+        <v>11</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1</v>
+      </c>
+      <c r="N90" t="n">
+        <v>2</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
         <v>3</v>
       </c>
-      <c r="L90" t="n">
-        <v>9</v>
-      </c>
-      <c r="M90" t="n">
-        <v>2</v>
-      </c>
-      <c r="N90" t="n">
-        <v>2</v>
-      </c>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>11</v>
-      </c>
       <c r="R90" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="U90" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="V90" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W90" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="X90" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Y90" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="Z90" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>Stadion Nizhny Novgorod</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>ul. Dolzhanskaya, Nizhniy Novgorod</t>
-        </is>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="AA90" t="inlineStr"/>
+      <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD90" t="n">
         <v>2</v>
       </c>
       <c r="AE90" t="n">
-        <v>2.29</v>
+        <v>1.9</v>
       </c>
       <c r="AF90" t="n">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
       <c r="AG90" t="n">
-        <v>2.57</v>
+        <v>3.28</v>
       </c>
       <c r="AH90" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AI90" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AJ90" t="n">
-        <v>2.66</v>
+        <v>3.08</v>
       </c>
       <c r="AK90" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="AL90" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="AM90" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AN90" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AO90" t="n">
-        <v>2.16</v>
+        <v>2.62</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AR90" t="n">
-        <v>2.51</v>
+        <v>2.74</v>
       </c>
       <c r="AS90" t="n">
-        <v>3.32</v>
+        <v>3.04</v>
       </c>
       <c r="AT90" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AU90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV90" t="n">
         <v>0</v>
       </c>
       <c r="AW90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ90" t="n">
         <v>1</v>
       </c>
       <c r="BA90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB90" t="n">
-        <v>668270</v>
+        <v>-1</v>
       </c>
       <c r="BC90" t="n">
         <v>0</v>
       </c>
       <c r="BD90" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BE90" t="n">
         <v>0</v>
       </c>
       <c r="BF90" t="n">
-        <v>4088</v>
+        <v>6069</v>
       </c>
       <c r="BG90" t="n">
         <v>-1</v>
@@ -40927,7 +40919,7 @@
         <v>-1</v>
       </c>
       <c r="BO90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP90" t="n">
         <v>0</v>
@@ -40939,7 +40931,7 @@
         <v>2</v>
       </c>
       <c r="BS90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT90" t="n">
         <v>3</v>
@@ -40948,25 +40940,25 @@
         <v>1</v>
       </c>
       <c r="BV90" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="BW90" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="BX90" t="n">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="BY90" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="BZ90" t="n">
-        <v>2.82</v>
+        <v>1.44</v>
       </c>
       <c r="CA90" t="n">
-        <v>1.09</v>
+        <v>1.34</v>
       </c>
       <c r="CB90" t="n">
-        <v>3.91</v>
+        <v>2.78</v>
       </c>
       <c r="CC90" t="n">
         <v>0</v>
@@ -41014,82 +41006,82 @@
         <v>1</v>
       </c>
       <c r="CR90" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CS90" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CT90" t="n">
         <v>1</v>
       </c>
       <c r="CU90" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="CV90" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CW90" t="n">
         <v>1</v>
       </c>
       <c r="CX90" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="CY90" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="CZ90" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="DA90" t="n">
         <v>100</v>
       </c>
       <c r="DB90" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="DC90" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="DD90" t="n">
-        <v>1.27</v>
+        <v>1.6</v>
       </c>
       <c r="DE90" t="n">
-        <v>1.08</v>
+        <v>0.45</v>
       </c>
       <c r="DF90" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="DG90" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="DH90" t="n">
-        <v>0.55</v>
+        <v>1.09</v>
       </c>
       <c r="DI90" t="n">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="DJ90" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="DK90" t="n">
         <v>0</v>
       </c>
       <c r="DL90" t="n">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="DM90" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="DN90" t="n">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="DO90" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
       </c>
       <c r="DQ90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR90" t="b">
         <v>0</v>
@@ -41104,66 +41096,66 @@
         <v>0</v>
       </c>
       <c r="DV90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW90" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="DX90" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="DY90" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="DZ90" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EA90" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EB90" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="EC90" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="ED90" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="EE90" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EF90" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="EG90" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="EH90" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EI90" t="inlineStr"/>
@@ -41187,168 +41179,176 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F91" s="2" t="n">
         <v>45948.41666666666</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
         <v>1</v>
       </c>
       <c r="I91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K91" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L91" t="n">
+        <v>9</v>
+      </c>
+      <c r="M91" t="n">
+        <v>2</v>
+      </c>
+      <c r="N91" t="n">
+        <v>2</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
         <v>11</v>
       </c>
-      <c r="M91" t="n">
-        <v>1</v>
-      </c>
-      <c r="N91" t="n">
-        <v>2</v>
-      </c>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>3</v>
-      </c>
       <c r="R91" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T91" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="U91" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="V91" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W91" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="X91" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Y91" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="Z91" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA91" t="inlineStr"/>
-      <c r="AB91" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>Stadion Nizhny Novgorod</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>ul. Dolzhanskaya, Nizhniy Novgorod</t>
+        </is>
+      </c>
       <c r="AC91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD91" t="n">
         <v>2</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.9</v>
+        <v>2.29</v>
       </c>
       <c r="AF91" t="n">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="AG91" t="n">
-        <v>3.28</v>
+        <v>2.57</v>
       </c>
       <c r="AH91" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AI91" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AJ91" t="n">
-        <v>3.08</v>
+        <v>2.66</v>
       </c>
       <c r="AK91" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AL91" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="AM91" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AN91" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AO91" t="n">
-        <v>2.62</v>
+        <v>2.16</v>
       </c>
       <c r="AP91" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR91" t="n">
-        <v>2.74</v>
+        <v>2.51</v>
       </c>
       <c r="AS91" t="n">
-        <v>3.04</v>
+        <v>3.32</v>
       </c>
       <c r="AT91" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AU91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV91" t="n">
         <v>0</v>
       </c>
       <c r="AW91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ91" t="n">
         <v>1</v>
       </c>
       <c r="BA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB91" t="n">
-        <v>-1</v>
+        <v>668270</v>
       </c>
       <c r="BC91" t="n">
         <v>0</v>
       </c>
       <c r="BD91" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BE91" t="n">
         <v>0</v>
       </c>
       <c r="BF91" t="n">
-        <v>6069</v>
+        <v>4088</v>
       </c>
       <c r="BG91" t="n">
         <v>-1</v>
@@ -41375,7 +41375,7 @@
         <v>-1</v>
       </c>
       <c r="BO91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP91" t="n">
         <v>0</v>
@@ -41387,7 +41387,7 @@
         <v>2</v>
       </c>
       <c r="BS91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT91" t="n">
         <v>3</v>
@@ -41396,25 +41396,25 @@
         <v>1</v>
       </c>
       <c r="BV91" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="BW91" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="BX91" t="n">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="BY91" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BZ91" t="n">
-        <v>1.44</v>
+        <v>2.82</v>
       </c>
       <c r="CA91" t="n">
-        <v>1.34</v>
+        <v>1.09</v>
       </c>
       <c r="CB91" t="n">
-        <v>2.78</v>
+        <v>3.91</v>
       </c>
       <c r="CC91" t="n">
         <v>0</v>
@@ -41462,82 +41462,82 @@
         <v>1</v>
       </c>
       <c r="CR91" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS91" t="n">
         <v>21</v>
       </c>
-      <c r="CS91" t="n">
-        <v>23</v>
-      </c>
       <c r="CT91" t="n">
         <v>1</v>
       </c>
       <c r="CU91" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="CV91" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CW91" t="n">
         <v>1</v>
       </c>
       <c r="CX91" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="CY91" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="CZ91" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="DA91" t="n">
         <v>100</v>
       </c>
       <c r="DB91" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="DC91" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="DD91" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="DE91" t="n">
-        <v>0.4</v>
+        <v>1.08</v>
       </c>
       <c r="DF91" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="DG91" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="DH91" t="n">
-        <v>1.09</v>
+        <v>0.55</v>
       </c>
       <c r="DI91" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="DJ91" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="DK91" t="n">
         <v>0</v>
       </c>
       <c r="DL91" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DM91" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="DN91" t="n">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="DO91" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
       </c>
       <c r="DQ91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR91" t="b">
         <v>0</v>
@@ -41552,66 +41552,66 @@
         <v>0</v>
       </c>
       <c r="DV91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW91" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="DX91" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="DY91" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="DZ91" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EA91" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EB91" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="EC91" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="ED91" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="EE91" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="EF91" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="EG91" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EH91" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="EI91" t="inlineStr"/>
@@ -41949,7 +41949,7 @@
         <v>2.18</v>
       </c>
       <c r="DE92" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="DF92" t="n">
         <v>2.17</v>
@@ -42390,10 +42390,10 @@
         <v>50</v>
       </c>
       <c r="DD93" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="DE93" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DF93" t="n">
         <v>1.8</v>
@@ -42423,7 +42423,7 @@
         <v>2.49</v>
       </c>
       <c r="DO93" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -42857,7 +42857,7 @@
         <v>2.27</v>
       </c>
       <c r="DE94" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="DF94" t="n">
         <v>2.2</v>
@@ -43757,7 +43757,7 @@
         <v>2.09</v>
       </c>
       <c r="DE96" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DF96" t="n">
         <v>2.17</v>
@@ -44186,7 +44186,7 @@
         <v>100</v>
       </c>
       <c r="DD97" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DE97" t="n">
         <v>0.73</v>
@@ -44219,7 +44219,7 @@
         <v>3.2</v>
       </c>
       <c r="DO97" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -44637,7 +44637,7 @@
         <v>2.18</v>
       </c>
       <c r="DE98" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="DF98" t="n">
         <v>2</v>
@@ -45111,7 +45111,7 @@
         <v>2.84</v>
       </c>
       <c r="DO99" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -45509,7 +45509,7 @@
         <v>2.55</v>
       </c>
       <c r="DE100" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="DF100" t="n">
         <v>2.67</v>
@@ -45539,7 +45539,7 @@
         <v>2.61</v>
       </c>
       <c r="DO100" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -45946,7 +45946,7 @@
         <v>75</v>
       </c>
       <c r="DD101" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="DE101" t="n">
         <v>1.73</v>
@@ -46402,10 +46402,10 @@
         <v>77</v>
       </c>
       <c r="DD102" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DE102" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DF102" t="n">
         <v>1</v>
@@ -46435,7 +46435,7 @@
         <v>3.07</v>
       </c>
       <c r="DO102" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP102" t="b">
         <v>0</v>
@@ -46822,7 +46822,7 @@
         <v>60</v>
       </c>
       <c r="DD103" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DE103" t="n">
         <v>1.36</v>
@@ -46855,7 +46855,7 @@
         <v>3.41</v>
       </c>
       <c r="DO103" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -47718,7 +47718,7 @@
         <v>57</v>
       </c>
       <c r="DD105" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="DE105" t="n">
         <v>0.36</v>
@@ -48191,7 +48191,7 @@
         <v>2.68</v>
       </c>
       <c r="DO106" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -48275,176 +48275,176 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F107" s="2" t="n">
         <v>45962.61458333334</v>
       </c>
       <c r="G107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K107" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L107" t="n">
+        <v>8</v>
+      </c>
+      <c r="M107" t="n">
+        <v>3</v>
+      </c>
+      <c r="N107" t="n">
+        <v>3</v>
+      </c>
+      <c r="O107" t="n">
+        <v>1</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>2</v>
+      </c>
+      <c r="R107" t="n">
+        <v>4</v>
+      </c>
+      <c r="S107" t="n">
+        <v>5</v>
+      </c>
+      <c r="T107" t="n">
         <v>11</v>
       </c>
-      <c r="M107" t="n">
-        <v>2</v>
-      </c>
-      <c r="N107" t="n">
-        <v>2</v>
-      </c>
-      <c r="O107" t="n">
-        <v>0</v>
-      </c>
-      <c r="P107" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>6</v>
-      </c>
-      <c r="R107" t="n">
-        <v>1</v>
-      </c>
-      <c r="S107" t="n">
+      <c r="U107" t="n">
         <v>7</v>
       </c>
-      <c r="T107" t="n">
-        <v>3</v>
-      </c>
-      <c r="U107" t="n">
-        <v>13</v>
-      </c>
       <c r="V107" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="W107" t="n">
         <v>16</v>
       </c>
       <c r="X107" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Y107" t="n">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="Z107" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>Anzhi-Arena</t>
+          <t>Kazan' Arena</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>, Kaspiysk</t>
+          <t>Prospekt Husaina Yamasheva 115a, Kazan'</t>
         </is>
       </c>
       <c r="AC107" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE107" t="n">
-        <v>2.03</v>
+        <v>3.1</v>
       </c>
       <c r="AF107" t="n">
         <v>3.2</v>
       </c>
       <c r="AG107" t="n">
-        <v>3.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH107" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AI107" t="n">
-        <v>2.48</v>
+        <v>1.91</v>
       </c>
       <c r="AJ107" t="n">
-        <v>4.65</v>
+        <v>2.9</v>
       </c>
       <c r="AK107" t="n">
-        <v>2.14</v>
+        <v>1.66</v>
       </c>
       <c r="AL107" t="n">
-        <v>1.64</v>
+        <v>2.29</v>
       </c>
       <c r="AM107" t="n">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="AN107" t="n">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="AO107" t="n">
-        <v>2.06</v>
+        <v>2.36</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="AR107" t="n">
-        <v>3.54</v>
+        <v>2.68</v>
       </c>
       <c r="AS107" t="n">
-        <v>2.4</v>
+        <v>2.89</v>
       </c>
       <c r="AT107" t="n">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AU107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW107" t="n">
         <v>0</v>
       </c>
       <c r="AX107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY107" t="n">
         <v>0</v>
       </c>
       <c r="AZ107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB107" t="n">
-        <v>668267</v>
+        <v>-1</v>
       </c>
       <c r="BC107" t="n">
         <v>0</v>
       </c>
       <c r="BD107" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="BE107" t="n">
         <v>0</v>
       </c>
       <c r="BF107" t="n">
-        <v>3519</v>
+        <v>13245</v>
       </c>
       <c r="BG107" t="n">
         <v>-1</v>
@@ -48471,46 +48471,46 @@
         <v>-1</v>
       </c>
       <c r="BO107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BR107" t="n">
         <v>2</v>
       </c>
       <c r="BS107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT107" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BU107" t="n">
         <v>1</v>
       </c>
       <c r="BV107" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="BW107" t="n">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="BX107" t="n">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="BY107" t="n">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="BZ107" t="n">
-        <v>1.63</v>
+        <v>0.88</v>
       </c>
       <c r="CA107" t="n">
-        <v>0.52</v>
+        <v>1.71</v>
       </c>
       <c r="CB107" t="n">
-        <v>2.16</v>
+        <v>2.59</v>
       </c>
       <c r="CC107" t="n">
         <v>0</v>
@@ -48537,7 +48537,7 @@
         <v>1</v>
       </c>
       <c r="CK107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL107" t="n">
         <v>0</v>
@@ -48558,82 +48558,82 @@
         <v>1</v>
       </c>
       <c r="CR107" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="CS107" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="CT107" t="n">
         <v>1</v>
       </c>
       <c r="CU107" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="CV107" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CW107" t="n">
         <v>1</v>
       </c>
       <c r="CX107" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="CY107" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="CZ107" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="DA107" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="DB107" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="DC107" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="DD107" t="n">
-        <v>1.64</v>
+        <v>2.09</v>
       </c>
       <c r="DE107" t="n">
-        <v>0.42</v>
+        <v>1.36</v>
       </c>
       <c r="DF107" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="DG107" t="n">
-        <v>0.71</v>
+        <v>1.17</v>
       </c>
       <c r="DH107" t="n">
-        <v>0.85</v>
+        <v>1.38</v>
       </c>
       <c r="DI107" t="n">
-        <v>1</v>
+        <v>1.23</v>
       </c>
       <c r="DJ107" t="n">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="DK107" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="DL107" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="DM107" t="n">
-        <v>0.97</v>
+        <v>1.4</v>
       </c>
       <c r="DN107" t="n">
-        <v>2.09</v>
+        <v>2.61</v>
       </c>
       <c r="DO107" t="n">
         <v>22</v>
       </c>
       <c r="DP107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR107" t="b">
         <v>0</v>
@@ -48652,60 +48652,84 @@
       </c>
       <c r="DW107" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="DX107" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="DY107" t="inlineStr">
         <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="DZ107" t="inlineStr"/>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="DZ107" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
       <c r="EA107" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EB107" t="inlineStr">
         <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="EC107" t="inlineStr"/>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="EC107" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
       <c r="ED107" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="EE107" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="EF107" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="EG107" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="EH107" t="inlineStr">
         <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="EI107" t="inlineStr"/>
-      <c r="EJ107" t="inlineStr"/>
-      <c r="EK107" t="inlineStr"/>
-      <c r="EL107" t="inlineStr"/>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EI107" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EJ107" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EK107" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EL107" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -48723,176 +48747,176 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F108" s="2" t="n">
         <v>45962.61458333334</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J108" t="n">
+        <v>9</v>
+      </c>
+      <c r="K108" t="n">
+        <v>2</v>
+      </c>
+      <c r="L108" t="n">
+        <v>11</v>
+      </c>
+      <c r="M108" t="n">
+        <v>2</v>
+      </c>
+      <c r="N108" t="n">
+        <v>2</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>6</v>
+      </c>
+      <c r="R108" t="n">
+        <v>1</v>
+      </c>
+      <c r="S108" t="n">
+        <v>7</v>
+      </c>
+      <c r="T108" t="n">
         <v>3</v>
       </c>
-      <c r="K108" t="n">
-        <v>5</v>
-      </c>
-      <c r="L108" t="n">
-        <v>8</v>
-      </c>
-      <c r="M108" t="n">
-        <v>3</v>
-      </c>
-      <c r="N108" t="n">
-        <v>3</v>
-      </c>
-      <c r="O108" t="n">
-        <v>1</v>
-      </c>
-      <c r="P108" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q108" t="n">
-        <v>2</v>
-      </c>
-      <c r="R108" t="n">
+      <c r="U108" t="n">
+        <v>13</v>
+      </c>
+      <c r="V108" t="n">
         <v>4</v>
-      </c>
-      <c r="S108" t="n">
-        <v>5</v>
-      </c>
-      <c r="T108" t="n">
-        <v>11</v>
-      </c>
-      <c r="U108" t="n">
-        <v>7</v>
-      </c>
-      <c r="V108" t="n">
-        <v>15</v>
       </c>
       <c r="W108" t="n">
         <v>16</v>
       </c>
       <c r="X108" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Y108" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="Z108" t="n">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>Kazan' Arena</t>
+          <t>Anzhi-Arena</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>Prospekt Husaina Yamasheva 115a, Kazan'</t>
+          <t>, Kaspiysk</t>
         </is>
       </c>
       <c r="AC108" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AD108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE108" t="n">
-        <v>3.1</v>
+        <v>2.03</v>
       </c>
       <c r="AF108" t="n">
         <v>3.2</v>
       </c>
       <c r="AG108" t="n">
-        <v>2.2</v>
+        <v>3.95</v>
       </c>
       <c r="AH108" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AI108" t="n">
-        <v>1.91</v>
+        <v>2.48</v>
       </c>
       <c r="AJ108" t="n">
-        <v>2.9</v>
+        <v>4.65</v>
       </c>
       <c r="AK108" t="n">
-        <v>1.66</v>
+        <v>2.14</v>
       </c>
       <c r="AL108" t="n">
-        <v>2.29</v>
+        <v>1.64</v>
       </c>
       <c r="AM108" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="AN108" t="n">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="AO108" t="n">
-        <v>2.36</v>
+        <v>2.06</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="AR108" t="n">
-        <v>2.68</v>
+        <v>3.54</v>
       </c>
       <c r="AS108" t="n">
-        <v>2.89</v>
+        <v>2.4</v>
       </c>
       <c r="AT108" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AU108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW108" t="n">
         <v>0</v>
       </c>
       <c r="AX108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY108" t="n">
         <v>0</v>
       </c>
       <c r="AZ108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB108" t="n">
-        <v>-1</v>
+        <v>668267</v>
       </c>
       <c r="BC108" t="n">
         <v>0</v>
       </c>
       <c r="BD108" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="BE108" t="n">
         <v>0</v>
       </c>
       <c r="BF108" t="n">
-        <v>13245</v>
+        <v>3519</v>
       </c>
       <c r="BG108" t="n">
         <v>-1</v>
@@ -48919,169 +48943,169 @@
         <v>-1</v>
       </c>
       <c r="BO108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BR108" t="n">
         <v>2</v>
       </c>
       <c r="BS108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT108" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV108" t="n">
+        <v>53</v>
+      </c>
+      <c r="BW108" t="n">
+        <v>26</v>
+      </c>
+      <c r="BX108" t="n">
+        <v>126</v>
+      </c>
+      <c r="BY108" t="n">
+        <v>75</v>
+      </c>
+      <c r="BZ108" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="CA108" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="CB108" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="CC108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM108" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN108" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR108" t="n">
+        <v>28</v>
+      </c>
+      <c r="CS108" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU108" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV108" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX108" t="n">
         <v>5</v>
       </c>
-      <c r="BU108" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV108" t="n">
-        <v>39</v>
-      </c>
-      <c r="BW108" t="n">
-        <v>66</v>
-      </c>
-      <c r="BX108" t="n">
-        <v>101</v>
-      </c>
-      <c r="BY108" t="n">
-        <v>121</v>
-      </c>
-      <c r="BZ108" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="CA108" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="CB108" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="CC108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM108" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CN108" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CO108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR108" t="n">
-        <v>18</v>
-      </c>
-      <c r="CS108" t="n">
-        <v>15</v>
-      </c>
-      <c r="CT108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU108" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV108" t="n">
-        <v>17</v>
-      </c>
-      <c r="CW108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX108" t="n">
-        <v>10</v>
-      </c>
       <c r="CY108" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="CZ108" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="DA108" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="DB108" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="DC108" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="DD108" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DE108" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="DF108" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG108" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DH108" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="DI108" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ108" t="n">
+        <v>72</v>
+      </c>
+      <c r="DK108" t="n">
+        <v>32</v>
+      </c>
+      <c r="DL108" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="DM108" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="DN108" t="n">
         <v>2.09</v>
       </c>
-      <c r="DE108" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="DF108" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="DG108" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="DH108" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="DI108" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="DJ108" t="n">
-        <v>54</v>
-      </c>
-      <c r="DK108" t="n">
-        <v>31</v>
-      </c>
-      <c r="DL108" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="DM108" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DN108" t="n">
-        <v>2.61</v>
-      </c>
       <c r="DO108" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR108" t="b">
         <v>0</v>
@@ -49100,84 +49124,60 @@
       </c>
       <c r="DW108" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="DX108" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="DY108" t="inlineStr">
         <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="DZ108" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="DZ108" t="inlineStr"/>
       <c r="EA108" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EB108" t="inlineStr">
         <is>
-          <t>3.19</t>
-        </is>
-      </c>
-      <c r="EC108" t="inlineStr">
-        <is>
-          <t>2.76</t>
-        </is>
-      </c>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EC108" t="inlineStr"/>
       <c r="ED108" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EE108" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="EF108" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="EG108" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EH108" t="inlineStr">
         <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="EI108" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
-      </c>
-      <c r="EJ108" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EK108" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="EL108" t="inlineStr">
-        <is>
-          <t>2.44</t>
-        </is>
-      </c>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EI108" t="inlineStr"/>
+      <c r="EJ108" t="inlineStr"/>
+      <c r="EK108" t="inlineStr"/>
+      <c r="EL108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -49506,7 +49506,7 @@
         <v>77</v>
       </c>
       <c r="DD109" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DE109" t="n">
         <v>1.73</v>
@@ -49979,7 +49979,7 @@
         <v>2.81</v>
       </c>
       <c r="DO110" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -50875,7 +50875,7 @@
         <v>2.58</v>
       </c>
       <c r="DO112" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -51746,7 +51746,7 @@
         <v>86</v>
       </c>
       <c r="DD114" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DE114" t="n">
         <v>1.08</v>
@@ -51779,7 +51779,7 @@
         <v>3.16</v>
       </c>
       <c r="DO114" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP114" t="b">
         <v>1</v>
@@ -52174,7 +52174,7 @@
         <v>77</v>
       </c>
       <c r="DD115" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DE115" t="n">
         <v>0.64</v>
@@ -52614,10 +52614,10 @@
         <v>70</v>
       </c>
       <c r="DD116" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="DE116" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="DF116" t="n">
         <v>1.71</v>
@@ -52647,7 +52647,7 @@
         <v>2.74</v>
       </c>
       <c r="DO116" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP116" t="b">
         <v>1</v>
@@ -53053,7 +53053,7 @@
         <v>0.45</v>
       </c>
       <c r="DE117" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="DF117" t="n">
         <v>0.67</v>
@@ -53531,7 +53531,7 @@
         <v>2.53</v>
       </c>
       <c r="DO118" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -53937,7 +53937,7 @@
         <v>2.27</v>
       </c>
       <c r="DE119" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="DF119" t="n">
         <v>2.33</v>
@@ -54374,7 +54374,7 @@
         <v>75</v>
       </c>
       <c r="DD120" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="DE120" t="n">
         <v>1.27</v>
@@ -54849,7 +54849,7 @@
         <v>2.27</v>
       </c>
       <c r="DE121" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DF121" t="n">
         <v>2</v>
@@ -54879,7 +54879,7 @@
         <v>2.7</v>
       </c>
       <c r="DO121" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -55298,7 +55298,7 @@
         <v>68</v>
       </c>
       <c r="DD122" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="DE122" t="n">
         <v>0.36</v>
@@ -55729,7 +55729,7 @@
         <v>1.17</v>
       </c>
       <c r="DE123" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DF123" t="n">
         <v>0.88</v>
@@ -55759,7 +55759,7 @@
         <v>2.75</v>
       </c>
       <c r="DO123" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP123" t="b">
         <v>0</v>
@@ -56177,7 +56177,7 @@
         <v>2.18</v>
       </c>
       <c r="DE124" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="DF124" t="n">
         <v>2.13</v>
@@ -57081,7 +57081,7 @@
         <v>1.6</v>
       </c>
       <c r="DE126" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="DF126" t="n">
         <v>1.29</v>
@@ -57111,7 +57111,7 @@
         <v>2.45</v>
       </c>
       <c r="DO126" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP126" t="b">
         <v>1</v>
@@ -57522,7 +57522,7 @@
         <v>63</v>
       </c>
       <c r="DD127" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DE127" t="n">
         <v>1.55</v>
@@ -57555,7 +57555,7 @@
         <v>2.81</v>
       </c>
       <c r="DO127" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP127" t="b">
         <v>1</v>
@@ -57970,7 +57970,7 @@
         <v>87</v>
       </c>
       <c r="DD128" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DE128" t="n">
         <v>0.27</v>
@@ -58003,7 +58003,7 @@
         <v>3.18</v>
       </c>
       <c r="DO128" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP128" t="b">
         <v>1</v>
@@ -58421,7 +58421,7 @@
         <v>2.27</v>
       </c>
       <c r="DE129" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DF129" t="n">
         <v>2.43</v>
@@ -58854,7 +58854,7 @@
         <v>73</v>
       </c>
       <c r="DD130" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="DE130" t="n">
         <v>0.55</v>
@@ -58887,7 +58887,7 @@
         <v>2.38</v>
       </c>
       <c r="DO130" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP130" t="b">
         <v>1</v>
@@ -59313,7 +59313,7 @@
         <v>2.55</v>
       </c>
       <c r="DE131" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="DF131" t="n">
         <v>2.75</v>
@@ -59343,7 +59343,7 @@
         <v>2.93</v>
       </c>
       <c r="DO131" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP131" t="b">
         <v>1</v>
@@ -60189,7 +60189,7 @@
         <v>2.5</v>
       </c>
       <c r="DE133" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="DF133" t="n">
         <v>2.25</v>
@@ -60219,7 +60219,7 @@
         <v>2.76</v>
       </c>
       <c r="DO133" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP133" t="b">
         <v>1</v>
@@ -60323,176 +60323,176 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F134" s="2" t="n">
         <v>45991.5625</v>
       </c>
       <c r="G134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H134" t="n">
+        <v>1</v>
+      </c>
+      <c r="I134" t="n">
         <v>3</v>
       </c>
-      <c r="I134" t="n">
-        <v>4</v>
-      </c>
       <c r="J134" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K134" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L134" t="n">
+        <v>15</v>
+      </c>
+      <c r="M134" t="n">
+        <v>3</v>
+      </c>
+      <c r="N134" t="n">
+        <v>2</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
         <v>6</v>
       </c>
-      <c r="M134" t="n">
-        <v>2</v>
-      </c>
-      <c r="N134" t="n">
-        <v>1</v>
-      </c>
-      <c r="O134" t="n">
-        <v>0</v>
-      </c>
-      <c r="P134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q134" t="n">
-        <v>3</v>
-      </c>
       <c r="R134" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S134" t="n">
+        <v>11</v>
+      </c>
+      <c r="T134" t="n">
+        <v>18</v>
+      </c>
+      <c r="U134" t="n">
+        <v>17</v>
+      </c>
+      <c r="V134" t="n">
+        <v>23</v>
+      </c>
+      <c r="W134" t="n">
         <v>8</v>
-      </c>
-      <c r="T134" t="n">
-        <v>10</v>
-      </c>
-      <c r="U134" t="n">
-        <v>11</v>
-      </c>
-      <c r="V134" t="n">
-        <v>16</v>
-      </c>
-      <c r="W134" t="n">
-        <v>16</v>
       </c>
       <c r="X134" t="n">
         <v>13</v>
       </c>
       <c r="Y134" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="Z134" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>Stadion Central’nyj im. I.P. Chayka</t>
+          <t>Akhmat Arena</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>ul. Suvorova, Peschanokopskoye</t>
+          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
         </is>
       </c>
       <c r="AC134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE134" t="n">
-        <v>2.49</v>
+        <v>2.89</v>
       </c>
       <c r="AF134" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="AG134" t="n">
-        <v>2.84</v>
+        <v>2.36</v>
       </c>
       <c r="AH134" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AI134" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AJ134" t="n">
-        <v>3.74</v>
+        <v>3.1</v>
       </c>
       <c r="AK134" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AL134" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="AM134" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AN134" t="n">
-        <v>2.19</v>
+        <v>1.8</v>
       </c>
       <c r="AO134" t="n">
-        <v>2.19</v>
+        <v>2.48</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AQ134" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AR134" t="n">
-        <v>3.09</v>
+        <v>2.62</v>
       </c>
       <c r="AS134" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="AT134" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AU134" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BB134" t="n">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="BC134" t="n">
         <v>0</v>
       </c>
       <c r="BD134" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="BE134" t="n">
         <v>0</v>
       </c>
       <c r="BF134" t="n">
-        <v>12383</v>
+        <v>4236</v>
       </c>
       <c r="BG134" t="n">
         <v>-1</v>
@@ -60519,10 +60519,10 @@
         <v>-1</v>
       </c>
       <c r="BO134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ134" t="n">
         <v>2</v>
@@ -60531,7 +60531,7 @@
         <v>1</v>
       </c>
       <c r="BS134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT134" t="n">
         <v>3</v>
@@ -60540,37 +60540,37 @@
         <v>1</v>
       </c>
       <c r="BV134" t="n">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="BW134" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="BX134" t="n">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="BY134" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="BZ134" t="n">
-        <v>1.45</v>
+        <v>1.77</v>
       </c>
       <c r="CA134" t="n">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="CB134" t="n">
-        <v>3.16</v>
+        <v>3.89</v>
       </c>
       <c r="CC134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG134" t="n">
         <v>0</v>
@@ -60588,7 +60588,7 @@
         <v>0</v>
       </c>
       <c r="CL134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM134" t="n">
         <v>-1</v>
@@ -60597,7 +60597,7 @@
         <v>-1</v>
       </c>
       <c r="CO134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP134" t="n">
         <v>0</v>
@@ -60606,76 +60606,76 @@
         <v>1</v>
       </c>
       <c r="CR134" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="CS134" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="CT134" t="n">
         <v>1</v>
       </c>
       <c r="CU134" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CV134" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="CW134" t="n">
         <v>1</v>
       </c>
       <c r="CX134" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CY134" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CZ134" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="DA134" t="n">
         <v>72</v>
       </c>
       <c r="DB134" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="DC134" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="DD134" t="n">
-        <v>1.18</v>
+        <v>1.83</v>
       </c>
       <c r="DE134" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="DF134" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="DG134" t="n">
-        <v>1.63</v>
+        <v>1.14</v>
       </c>
       <c r="DH134" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DI134" t="n">
-        <v>1.94</v>
+        <v>1.25</v>
       </c>
       <c r="DJ134" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DK134" t="n">
         <v>29</v>
       </c>
       <c r="DL134" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="DM134" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="DN134" t="n">
-        <v>2.93</v>
+        <v>3.07</v>
       </c>
       <c r="DO134" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP134" t="b">
         <v>1</v>
@@ -60687,7 +60687,7 @@
         <v>1</v>
       </c>
       <c r="DS134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT134" t="b">
         <v>0</v>
@@ -60700,17 +60700,17 @@
       </c>
       <c r="DW134" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="DX134" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="DY134" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="DZ134" t="inlineStr"/>
@@ -60719,47 +60719,47 @@
       <c r="EC134" t="inlineStr"/>
       <c r="ED134" t="inlineStr">
         <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="EE134" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EF134" t="inlineStr">
+        <is>
+          <t>3.53</t>
+        </is>
+      </c>
+      <c r="EG134" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EH134" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EI134" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EJ134" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EK134" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EL134" t="inlineStr">
+        <is>
           <t>2.54</t>
-        </is>
-      </c>
-      <c r="EE134" t="inlineStr">
-        <is>
-          <t>2.86</t>
-        </is>
-      </c>
-      <c r="EF134" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="EG134" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="EH134" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="EI134" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="EJ134" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="EK134" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EL134" t="inlineStr">
-        <is>
-          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -60779,176 +60779,176 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F135" s="2" t="n">
         <v>45991.5625</v>
       </c>
       <c r="G135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I135" t="n">
+        <v>4</v>
+      </c>
+      <c r="J135" t="n">
+        <v>2</v>
+      </c>
+      <c r="K135" t="n">
+        <v>4</v>
+      </c>
+      <c r="L135" t="n">
+        <v>6</v>
+      </c>
+      <c r="M135" t="n">
+        <v>2</v>
+      </c>
+      <c r="N135" t="n">
+        <v>1</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
         <v>3</v>
       </c>
-      <c r="J135" t="n">
-        <v>7</v>
-      </c>
-      <c r="K135" t="n">
+      <c r="R135" t="n">
+        <v>6</v>
+      </c>
+      <c r="S135" t="n">
         <v>8</v>
       </c>
-      <c r="L135" t="n">
-        <v>15</v>
-      </c>
-      <c r="M135" t="n">
-        <v>3</v>
-      </c>
-      <c r="N135" t="n">
-        <v>2</v>
-      </c>
-      <c r="O135" t="n">
-        <v>0</v>
-      </c>
-      <c r="P135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q135" t="n">
-        <v>6</v>
-      </c>
-      <c r="R135" t="n">
-        <v>5</v>
-      </c>
-      <c r="S135" t="n">
+      <c r="T135" t="n">
+        <v>10</v>
+      </c>
+      <c r="U135" t="n">
         <v>11</v>
       </c>
-      <c r="T135" t="n">
-        <v>18</v>
-      </c>
-      <c r="U135" t="n">
-        <v>17</v>
-      </c>
       <c r="V135" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="W135" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X135" t="n">
         <v>13</v>
       </c>
       <c r="Y135" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="Z135" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>Akhmat Arena</t>
+          <t>Stadion Central’nyj im. I.P. Chayka</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
+          <t>ul. Suvorova, Peschanokopskoye</t>
         </is>
       </c>
       <c r="AC135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA135" t="n">
         <v>3</v>
       </c>
-      <c r="AD135" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE135" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AF135" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AG135" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AH135" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI135" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ135" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AK135" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AL135" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AM135" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AN135" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AO135" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AP135" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AQ135" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AR135" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AS135" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AT135" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AU135" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW135" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX135" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ135" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA135" t="n">
-        <v>1</v>
-      </c>
       <c r="BB135" t="n">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="BC135" t="n">
         <v>0</v>
       </c>
       <c r="BD135" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="BE135" t="n">
         <v>0</v>
       </c>
       <c r="BF135" t="n">
-        <v>4236</v>
+        <v>12383</v>
       </c>
       <c r="BG135" t="n">
         <v>-1</v>
@@ -60975,10 +60975,10 @@
         <v>-1</v>
       </c>
       <c r="BO135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ135" t="n">
         <v>2</v>
@@ -60987,7 +60987,7 @@
         <v>1</v>
       </c>
       <c r="BS135" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT135" t="n">
         <v>3</v>
@@ -60996,37 +60996,37 @@
         <v>1</v>
       </c>
       <c r="BV135" t="n">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="BW135" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="BX135" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="BY135" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="BZ135" t="n">
-        <v>1.77</v>
+        <v>1.45</v>
       </c>
       <c r="CA135" t="n">
-        <v>2.12</v>
+        <v>1.71</v>
       </c>
       <c r="CB135" t="n">
-        <v>3.89</v>
+        <v>3.16</v>
       </c>
       <c r="CC135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG135" t="n">
         <v>0</v>
@@ -61044,7 +61044,7 @@
         <v>0</v>
       </c>
       <c r="CL135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM135" t="n">
         <v>-1</v>
@@ -61053,7 +61053,7 @@
         <v>-1</v>
       </c>
       <c r="CO135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP135" t="n">
         <v>0</v>
@@ -61062,73 +61062,73 @@
         <v>1</v>
       </c>
       <c r="CR135" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="CS135" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="CT135" t="n">
         <v>1</v>
       </c>
       <c r="CU135" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CV135" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="CW135" t="n">
         <v>1</v>
       </c>
       <c r="CX135" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CY135" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CZ135" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="DA135" t="n">
         <v>72</v>
       </c>
       <c r="DB135" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="DC135" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="DD135" t="n">
-        <v>2</v>
+        <v>1.18</v>
       </c>
       <c r="DE135" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="DF135" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="DG135" t="n">
-        <v>1.14</v>
+        <v>1.63</v>
       </c>
       <c r="DH135" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="DI135" t="n">
-        <v>1.25</v>
+        <v>1.94</v>
       </c>
       <c r="DJ135" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="DK135" t="n">
         <v>29</v>
       </c>
       <c r="DL135" t="n">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="DM135" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="DN135" t="n">
-        <v>3.07</v>
+        <v>2.93</v>
       </c>
       <c r="DO135" t="n">
         <v>22</v>
@@ -61143,7 +61143,7 @@
         <v>1</v>
       </c>
       <c r="DS135" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT135" t="b">
         <v>0</v>
@@ -61156,17 +61156,17 @@
       </c>
       <c r="DW135" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="DX135" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="DY135" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="DZ135" t="inlineStr"/>
@@ -61175,47 +61175,47 @@
       <c r="EC135" t="inlineStr"/>
       <c r="ED135" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="EE135" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="EF135" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="EG135" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EH135" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EI135" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="EJ135" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EK135" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EL135" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -61546,7 +61546,7 @@
         <v>79</v>
       </c>
       <c r="DD136" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DE136" t="n">
         <v>0.64</v>
@@ -62466,10 +62466,10 @@
         <v>76</v>
       </c>
       <c r="DD138" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="DE138" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="DF138" t="n">
         <v>1.63</v>
@@ -62499,7 +62499,7 @@
         <v>2.95</v>
       </c>
       <c r="DO138" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP138" t="b">
         <v>1</v>
@@ -63754,7 +63754,7 @@
         <v>69</v>
       </c>
       <c r="DD141" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DE141" t="n">
         <v>1.08</v>
@@ -63787,7 +63787,7 @@
         <v>2.96</v>
       </c>
       <c r="DO141" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP141" t="b">
         <v>1</v>
@@ -64194,7 +64194,7 @@
         <v>57</v>
       </c>
       <c r="DD142" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="DE142" t="n">
         <v>0.55</v>
@@ -64227,7 +64227,7 @@
         <v>2.35</v>
       </c>
       <c r="DO142" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP142" t="b">
         <v>1</v>
@@ -65117,7 +65117,7 @@
         <v>2.27</v>
       </c>
       <c r="DE144" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="DF144" t="n">
         <v>2</v>
@@ -65147,7 +65147,7 @@
         <v>2.2</v>
       </c>
       <c r="DO144" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP144" t="b">
         <v>1</v>
@@ -65557,7 +65557,7 @@
         <v>2.5</v>
       </c>
       <c r="DE145" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="DF145" t="n">
         <v>2.33</v>
@@ -65587,7 +65587,7 @@
         <v>3.37</v>
       </c>
       <c r="DO145" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP145" t="b">
         <v>1</v>
@@ -66006,10 +66006,10 @@
         <v>67</v>
       </c>
       <c r="DD146" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DE146" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DF146" t="n">
         <v>2.78</v>
@@ -66039,7 +66039,7 @@
         <v>3.19</v>
       </c>
       <c r="DO146" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP146" t="b">
         <v>1</v>
@@ -66483,7 +66483,7 @@
         <v>2.46</v>
       </c>
       <c r="DO147" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP147" t="b">
         <v>1</v>
@@ -66893,7 +66893,7 @@
         <v>2.5</v>
       </c>
       <c r="DE148" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="DF148" t="n">
         <v>2.4</v>
@@ -66923,7 +66923,7 @@
         <v>3.3</v>
       </c>
       <c r="DO148" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP148" t="b">
         <v>1</v>
@@ -67826,7 +67826,7 @@
         <v>56</v>
       </c>
       <c r="DD150" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="DE150" t="n">
         <v>0.64</v>
@@ -68274,10 +68274,10 @@
         <v>90</v>
       </c>
       <c r="DD151" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DE151" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="DF151" t="n">
         <v>1.33</v>
@@ -68307,7 +68307,7 @@
         <v>2.73</v>
       </c>
       <c r="DO151" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP151" t="b">
         <v>1</v>
@@ -68722,10 +68722,10 @@
         <v>78</v>
       </c>
       <c r="DD152" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="DE152" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="DF152" t="n">
         <v>1.78</v>
@@ -68755,7 +68755,7 @@
         <v>2.95</v>
       </c>
       <c r="DO152" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP152" t="b">
         <v>1</v>
@@ -69637,7 +69637,7 @@
         <v>1.18</v>
       </c>
       <c r="DE154" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DF154" t="n">
         <v>1.33</v>
@@ -69667,7 +69667,7 @@
         <v>2.87</v>
       </c>
       <c r="DO154" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP154" t="b">
         <v>1</v>
@@ -70090,7 +70090,7 @@
         <v>56</v>
       </c>
       <c r="DD155" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DE155" t="n">
         <v>0.36</v>
@@ -70579,7 +70579,7 @@
         <v>2.71</v>
       </c>
       <c r="DO156" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP156" t="b">
         <v>1</v>
@@ -71027,7 +71027,7 @@
         <v>2.26</v>
       </c>
       <c r="DO157" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP157" t="b">
         <v>1</v>
@@ -71437,7 +71437,7 @@
         <v>2.09</v>
       </c>
       <c r="DE158" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DF158" t="n">
         <v>1.89</v>
@@ -71923,7 +71923,7 @@
         <v>3.2</v>
       </c>
       <c r="DO159" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP159" t="b">
         <v>1</v>
@@ -73238,10 +73238,10 @@
         <v>58</v>
       </c>
       <c r="DD162" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="DE162" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="DF162" t="n">
         <v>1.5</v>
@@ -73271,7 +73271,7 @@
         <v>2.57</v>
       </c>
       <c r="DO162" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP162" t="b">
         <v>1</v>
@@ -73681,7 +73681,7 @@
         <v>0.45</v>
       </c>
       <c r="DE163" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DF163" t="n">
         <v>0.5</v>
@@ -74114,7 +74114,7 @@
         <v>69</v>
       </c>
       <c r="DD164" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DE164" t="n">
         <v>1.27</v>
@@ -74619,7 +74619,7 @@
         <v>3.1</v>
       </c>
       <c r="DO165" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP165" t="b">
         <v>1</v>
@@ -75061,7 +75061,7 @@
         <v>2.27</v>
       </c>
       <c r="DE166" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="DF166" t="n">
         <v>2.11</v>
@@ -75091,7 +75091,7 @@
         <v>2.87</v>
       </c>
       <c r="DO166" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP166" t="b">
         <v>1</v>
@@ -75506,7 +75506,7 @@
         <v>90</v>
       </c>
       <c r="DD167" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="DE167" t="n">
         <v>0.73</v>
@@ -75539,7 +75539,7 @@
         <v>2.55</v>
       </c>
       <c r="DO167" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP167" t="b">
         <v>1</v>
@@ -75962,10 +75962,10 @@
         <v>76</v>
       </c>
       <c r="DD168" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DE168" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="DF168" t="n">
         <v>1.1</v>
@@ -75995,7 +75995,7 @@
         <v>2.32</v>
       </c>
       <c r="DO168" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP168" t="b">
         <v>1</v>
@@ -76874,10 +76874,10 @@
         <v>70</v>
       </c>
       <c r="DD170" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="DE170" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="DF170" t="n">
         <v>1.9</v>
@@ -76907,7 +76907,7 @@
         <v>2.96</v>
       </c>
       <c r="DO170" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP170" t="b">
         <v>1</v>
@@ -77347,7 +77347,7 @@
         <v>2.85</v>
       </c>
       <c r="DO171" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP171" t="b">
         <v>1</v>
@@ -77803,7 +77803,7 @@
         <v>3.1</v>
       </c>
       <c r="DO172" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP172" t="b">
         <v>1</v>
@@ -79058,7 +79058,7 @@
         <v>75</v>
       </c>
       <c r="DD175" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DE175" t="n">
         <v>1.55</v>
@@ -79091,7 +79091,7 @@
         <v>3.25</v>
       </c>
       <c r="DO175" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP175" t="b">
         <v>1</v>
@@ -80063,6 +80063,2642 @@
         </is>
       </c>
     </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>23</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Akron</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>CSKA Moskva</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="n">
+        <v>46116.41666666666</v>
+      </c>
+      <c r="G178" t="n">
+        <v>1</v>
+      </c>
+      <c r="H178" t="n">
+        <v>2</v>
+      </c>
+      <c r="I178" t="n">
+        <v>3</v>
+      </c>
+      <c r="J178" t="n">
+        <v>1</v>
+      </c>
+      <c r="K178" t="n">
+        <v>5</v>
+      </c>
+      <c r="L178" t="n">
+        <v>6</v>
+      </c>
+      <c r="M178" t="n">
+        <v>1</v>
+      </c>
+      <c r="N178" t="n">
+        <v>2</v>
+      </c>
+      <c r="O178" t="n">
+        <v>0</v>
+      </c>
+      <c r="P178" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>3</v>
+      </c>
+      <c r="R178" t="n">
+        <v>3</v>
+      </c>
+      <c r="S178" t="n">
+        <v>4</v>
+      </c>
+      <c r="T178" t="n">
+        <v>13</v>
+      </c>
+      <c r="U178" t="n">
+        <v>7</v>
+      </c>
+      <c r="V178" t="n">
+        <v>16</v>
+      </c>
+      <c r="W178" t="n">
+        <v>13</v>
+      </c>
+      <c r="X178" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>45</v>
+      </c>
+      <c r="Z178" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA178" t="inlineStr"/>
+      <c r="AB178" t="inlineStr"/>
+      <c r="AC178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD178" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE178" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AF178" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AG178" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH178" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI178" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AJ178" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK178" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL178" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AM178" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN178" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO178" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AP178" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ178" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR178" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AS178" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AT178" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AU178" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ178" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA178" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB178" t="n">
+        <v>101</v>
+      </c>
+      <c r="BC178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD178" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF178" t="n">
+        <v>5399</v>
+      </c>
+      <c r="BG178" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH178" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI178" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ178" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK178" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL178" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM178" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN178" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO178" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR178" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS178" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT178" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU178" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV178" t="n">
+        <v>41</v>
+      </c>
+      <c r="BW178" t="n">
+        <v>54</v>
+      </c>
+      <c r="BX178" t="n">
+        <v>84</v>
+      </c>
+      <c r="BY178" t="n">
+        <v>83</v>
+      </c>
+      <c r="BZ178" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="CA178" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CB178" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="CC178" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE178" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI178" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ178" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL178" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM178" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN178" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ178" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR178" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS178" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT178" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU178" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV178" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW178" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX178" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY178" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ178" t="n">
+        <v>38</v>
+      </c>
+      <c r="DA178" t="n">
+        <v>73</v>
+      </c>
+      <c r="DB178" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC178" t="n">
+        <v>82</v>
+      </c>
+      <c r="DD178" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="DE178" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DF178" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DG178" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH178" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI178" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="DJ178" t="n">
+        <v>62</v>
+      </c>
+      <c r="DK178" t="n">
+        <v>28</v>
+      </c>
+      <c r="DL178" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DM178" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DN178" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="DO178" t="n">
+        <v>23</v>
+      </c>
+      <c r="DP178" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ178" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR178" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS178" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT178" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU178" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV178" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW178" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="DX178" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="DY178" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="DZ178" t="inlineStr"/>
+      <c r="EA178" t="inlineStr"/>
+      <c r="EB178" t="inlineStr"/>
+      <c r="EC178" t="inlineStr"/>
+      <c r="ED178" t="inlineStr">
+        <is>
+          <t>4.49</t>
+        </is>
+      </c>
+      <c r="EE178" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EF178" t="inlineStr">
+        <is>
+          <t>4.27</t>
+        </is>
+      </c>
+      <c r="EG178" t="inlineStr"/>
+      <c r="EH178" t="inlineStr"/>
+      <c r="EI178" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EJ178" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EK178" t="inlineStr"/>
+      <c r="EL178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>23</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Zenit</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Krylya Sovetov</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="n">
+        <v>46116.51041666666</v>
+      </c>
+      <c r="G179" t="n">
+        <v>2</v>
+      </c>
+      <c r="H179" t="n">
+        <v>1</v>
+      </c>
+      <c r="I179" t="n">
+        <v>3</v>
+      </c>
+      <c r="J179" t="n">
+        <v>6</v>
+      </c>
+      <c r="K179" t="n">
+        <v>3</v>
+      </c>
+      <c r="L179" t="n">
+        <v>9</v>
+      </c>
+      <c r="M179" t="n">
+        <v>2</v>
+      </c>
+      <c r="N179" t="n">
+        <v>1</v>
+      </c>
+      <c r="O179" t="n">
+        <v>0</v>
+      </c>
+      <c r="P179" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>5</v>
+      </c>
+      <c r="R179" t="n">
+        <v>5</v>
+      </c>
+      <c r="S179" t="n">
+        <v>11</v>
+      </c>
+      <c r="T179" t="n">
+        <v>6</v>
+      </c>
+      <c r="U179" t="n">
+        <v>16</v>
+      </c>
+      <c r="V179" t="n">
+        <v>11</v>
+      </c>
+      <c r="W179" t="n">
+        <v>14</v>
+      </c>
+      <c r="X179" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y179" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z179" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA179" t="inlineStr"/>
+      <c r="AB179" t="inlineStr"/>
+      <c r="AC179" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD179" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE179" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF179" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AG179" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH179" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI179" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ179" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AK179" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AL179" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AM179" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN179" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO179" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AP179" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AQ179" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AR179" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS179" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AT179" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AU179" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX179" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY179" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ179" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB179" t="n">
+        <v>921</v>
+      </c>
+      <c r="BC179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD179" t="n">
+        <v>39</v>
+      </c>
+      <c r="BE179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF179" t="n">
+        <v>30315</v>
+      </c>
+      <c r="BG179" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH179" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI179" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ179" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK179" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL179" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM179" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN179" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP179" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ179" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS179" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT179" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU179" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV179" t="n">
+        <v>53</v>
+      </c>
+      <c r="BW179" t="n">
+        <v>45</v>
+      </c>
+      <c r="BX179" t="n">
+        <v>90</v>
+      </c>
+      <c r="BY179" t="n">
+        <v>86</v>
+      </c>
+      <c r="BZ179" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CA179" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CB179" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="CC179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI179" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ179" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM179" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN179" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ179" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR179" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS179" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT179" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU179" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV179" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW179" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX179" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY179" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ179" t="n">
+        <v>47</v>
+      </c>
+      <c r="DA179" t="n">
+        <v>87</v>
+      </c>
+      <c r="DB179" t="n">
+        <v>39</v>
+      </c>
+      <c r="DC179" t="n">
+        <v>83</v>
+      </c>
+      <c r="DD179" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="DE179" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="DF179" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="DG179" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="DH179" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="DI179" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="DJ179" t="n">
+        <v>53</v>
+      </c>
+      <c r="DK179" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL179" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DM179" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DN179" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="DO179" t="n">
+        <v>23</v>
+      </c>
+      <c r="DP179" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ179" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR179" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS179" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT179" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU179" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV179" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW179" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="DX179" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="DY179" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="DZ179" t="inlineStr"/>
+      <c r="EA179" t="inlineStr"/>
+      <c r="EB179" t="inlineStr"/>
+      <c r="EC179" t="inlineStr"/>
+      <c r="ED179" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="EE179" t="inlineStr">
+        <is>
+          <t>13.75</t>
+        </is>
+      </c>
+      <c r="EF179" t="inlineStr">
+        <is>
+          <t>6.67</t>
+        </is>
+      </c>
+      <c r="EG179" t="inlineStr"/>
+      <c r="EH179" t="inlineStr"/>
+      <c r="EI179" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EJ179" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EK179" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EL179" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>23</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Dinamo Moskva</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Orenburg</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="n">
+        <v>46116.60416666666</v>
+      </c>
+      <c r="G180" t="n">
+        <v>3</v>
+      </c>
+      <c r="H180" t="n">
+        <v>3</v>
+      </c>
+      <c r="I180" t="n">
+        <v>6</v>
+      </c>
+      <c r="J180" t="n">
+        <v>3</v>
+      </c>
+      <c r="K180" t="n">
+        <v>1</v>
+      </c>
+      <c r="L180" t="n">
+        <v>4</v>
+      </c>
+      <c r="M180" t="n">
+        <v>2</v>
+      </c>
+      <c r="N180" t="n">
+        <v>4</v>
+      </c>
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>5</v>
+      </c>
+      <c r="R180" t="n">
+        <v>3</v>
+      </c>
+      <c r="S180" t="n">
+        <v>13</v>
+      </c>
+      <c r="T180" t="n">
+        <v>7</v>
+      </c>
+      <c r="U180" t="n">
+        <v>18</v>
+      </c>
+      <c r="V180" t="n">
+        <v>10</v>
+      </c>
+      <c r="W180" t="n">
+        <v>7</v>
+      </c>
+      <c r="X180" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y180" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z180" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA180" t="inlineStr"/>
+      <c r="AB180" t="inlineStr"/>
+      <c r="AC180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD180" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF180" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG180" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="AH180" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI180" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ180" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AK180" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AL180" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AM180" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN180" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AO180" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AP180" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AQ180" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR180" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AS180" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AT180" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AU180" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW180" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX180" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ180" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA180" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB180" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC180" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD180" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE180" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF180" t="n">
+        <v>13856</v>
+      </c>
+      <c r="BG180" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH180" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI180" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ180" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK180" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL180" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM180" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN180" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO180" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP180" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ180" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR180" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS180" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT180" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU180" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV180" t="n">
+        <v>47</v>
+      </c>
+      <c r="BW180" t="n">
+        <v>45</v>
+      </c>
+      <c r="BX180" t="n">
+        <v>102</v>
+      </c>
+      <c r="BY180" t="n">
+        <v>82</v>
+      </c>
+      <c r="BZ180" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="CA180" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="CB180" t="n">
+        <v>3</v>
+      </c>
+      <c r="CC180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI180" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ180" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM180" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN180" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ180" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR180" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS180" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT180" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU180" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV180" t="n">
+        <v>6</v>
+      </c>
+      <c r="CW180" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX180" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY180" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ180" t="n">
+        <v>61</v>
+      </c>
+      <c r="DA180" t="n">
+        <v>76</v>
+      </c>
+      <c r="DB180" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC180" t="n">
+        <v>76</v>
+      </c>
+      <c r="DD180" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DE180" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="DF180" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DG180" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DH180" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DI180" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="DJ180" t="n">
+        <v>39</v>
+      </c>
+      <c r="DK180" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL180" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DM180" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DN180" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="DO180" t="n">
+        <v>23</v>
+      </c>
+      <c r="DP180" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ180" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR180" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS180" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT180" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU180" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV180" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW180" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="DX180" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="DY180" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="DZ180" t="inlineStr"/>
+      <c r="EA180" t="inlineStr"/>
+      <c r="EB180" t="inlineStr"/>
+      <c r="EC180" t="inlineStr"/>
+      <c r="ED180" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EE180" t="inlineStr">
+        <is>
+          <t>6.28</t>
+        </is>
+      </c>
+      <c r="EF180" t="inlineStr">
+        <is>
+          <t>4.96</t>
+        </is>
+      </c>
+      <c r="EG180" t="inlineStr"/>
+      <c r="EH180" t="inlineStr"/>
+      <c r="EI180" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EJ180" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EK180" t="inlineStr"/>
+      <c r="EL180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>23</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Akhmat Grozny</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Krasnodar</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="n">
+        <v>46116.69791666666</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" t="n">
+        <v>1</v>
+      </c>
+      <c r="I181" t="n">
+        <v>1</v>
+      </c>
+      <c r="J181" t="n">
+        <v>5</v>
+      </c>
+      <c r="K181" t="n">
+        <v>4</v>
+      </c>
+      <c r="L181" t="n">
+        <v>9</v>
+      </c>
+      <c r="M181" t="n">
+        <v>0</v>
+      </c>
+      <c r="N181" t="n">
+        <v>2</v>
+      </c>
+      <c r="O181" t="n">
+        <v>1</v>
+      </c>
+      <c r="P181" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>1</v>
+      </c>
+      <c r="R181" t="n">
+        <v>2</v>
+      </c>
+      <c r="S181" t="n">
+        <v>11</v>
+      </c>
+      <c r="T181" t="n">
+        <v>9</v>
+      </c>
+      <c r="U181" t="n">
+        <v>12</v>
+      </c>
+      <c r="V181" t="n">
+        <v>11</v>
+      </c>
+      <c r="W181" t="n">
+        <v>9</v>
+      </c>
+      <c r="X181" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z181" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>Akhmat Arena</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
+        </is>
+      </c>
+      <c r="AC181" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD181" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AF181" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG181" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH181" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI181" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AJ181" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AK181" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AL181" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM181" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN181" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO181" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AP181" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AQ181" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR181" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AS181" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AT181" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AU181" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY181" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ181" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB181" t="n">
+        <v>926</v>
+      </c>
+      <c r="BC181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD181" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF181" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG181" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH181" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI181" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ181" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK181" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL181" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM181" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN181" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ181" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR181" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT181" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU181" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV181" t="n">
+        <v>56</v>
+      </c>
+      <c r="BW181" t="n">
+        <v>39</v>
+      </c>
+      <c r="BX181" t="n">
+        <v>91</v>
+      </c>
+      <c r="BY181" t="n">
+        <v>98</v>
+      </c>
+      <c r="BZ181" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CA181" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="CB181" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="CC181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI181" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ181" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM181" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN181" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ181" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR181" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS181" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT181" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU181" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV181" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW181" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX181" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY181" t="n">
+        <v>14</v>
+      </c>
+      <c r="CZ181" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA181" t="n">
+        <v>72</v>
+      </c>
+      <c r="DB181" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC181" t="n">
+        <v>81</v>
+      </c>
+      <c r="DD181" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DE181" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF181" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG181" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DH181" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DI181" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="DJ181" t="n">
+        <v>58</v>
+      </c>
+      <c r="DK181" t="n">
+        <v>28</v>
+      </c>
+      <c r="DL181" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DM181" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DN181" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="DO181" t="n">
+        <v>23</v>
+      </c>
+      <c r="DP181" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ181" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR181" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS181" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT181" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU181" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV181" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW181" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="DX181" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="DY181" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="DZ181" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EA181" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EB181" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="EC181" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="ED181" t="inlineStr">
+        <is>
+          <t>4.55</t>
+        </is>
+      </c>
+      <c r="EE181" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EF181" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="EG181" t="inlineStr"/>
+      <c r="EH181" t="inlineStr"/>
+      <c r="EI181" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EJ181" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EK181" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EL181" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>23</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Olimpiyets</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Rostov</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="n">
+        <v>46117.45833333334</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" t="n">
+        <v>1</v>
+      </c>
+      <c r="I182" t="n">
+        <v>1</v>
+      </c>
+      <c r="J182" t="n">
+        <v>8</v>
+      </c>
+      <c r="K182" t="n">
+        <v>7</v>
+      </c>
+      <c r="L182" t="n">
+        <v>15</v>
+      </c>
+      <c r="M182" t="n">
+        <v>2</v>
+      </c>
+      <c r="N182" t="n">
+        <v>3</v>
+      </c>
+      <c r="O182" t="n">
+        <v>0</v>
+      </c>
+      <c r="P182" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>0</v>
+      </c>
+      <c r="R182" t="n">
+        <v>3</v>
+      </c>
+      <c r="S182" t="n">
+        <v>7</v>
+      </c>
+      <c r="T182" t="n">
+        <v>7</v>
+      </c>
+      <c r="U182" t="n">
+        <v>7</v>
+      </c>
+      <c r="V182" t="n">
+        <v>10</v>
+      </c>
+      <c r="W182" t="n">
+        <v>17</v>
+      </c>
+      <c r="X182" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y182" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z182" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>Stadion Nizhny Novgorod</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>ul. Dolzhanskaya, Nizhniy Novgorod</t>
+        </is>
+      </c>
+      <c r="AC182" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD182" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE182" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AF182" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AG182" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AH182" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI182" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AJ182" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AK182" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL182" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM182" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AN182" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AO182" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AP182" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AQ182" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR182" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AS182" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AT182" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AU182" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW182" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA182" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB182" t="n">
+        <v>71</v>
+      </c>
+      <c r="BC182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD182" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF182" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG182" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH182" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI182" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ182" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK182" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL182" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM182" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN182" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ182" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR182" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT182" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU182" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV182" t="n">
+        <v>25</v>
+      </c>
+      <c r="BW182" t="n">
+        <v>59</v>
+      </c>
+      <c r="BX182" t="n">
+        <v>71</v>
+      </c>
+      <c r="BY182" t="n">
+        <v>104</v>
+      </c>
+      <c r="BZ182" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="CA182" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="CB182" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CC182" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD182" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE182" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF182" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG182" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH182" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI182" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ182" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK182" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL182" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM182" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN182" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO182" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP182" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ182" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR182" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS182" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT182" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU182" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV182" t="n">
+        <v>20</v>
+      </c>
+      <c r="CW182" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX182" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY182" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ182" t="n">
+        <v>41</v>
+      </c>
+      <c r="DA182" t="n">
+        <v>59</v>
+      </c>
+      <c r="DB182" t="n">
+        <v>23</v>
+      </c>
+      <c r="DC182" t="n">
+        <v>64</v>
+      </c>
+      <c r="DD182" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DE182" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF182" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DG182" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="DH182" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="DI182" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ182" t="n">
+        <v>59</v>
+      </c>
+      <c r="DK182" t="n">
+        <v>41</v>
+      </c>
+      <c r="DL182" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="DM182" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DN182" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="DO182" t="n">
+        <v>23</v>
+      </c>
+      <c r="DP182" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ182" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR182" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS182" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT182" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU182" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV182" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW182" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="DX182" t="inlineStr">
+        <is>
+          <t>4.60</t>
+        </is>
+      </c>
+      <c r="DY182" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="DZ182" t="inlineStr"/>
+      <c r="EA182" t="inlineStr"/>
+      <c r="EB182" t="inlineStr"/>
+      <c r="EC182" t="inlineStr"/>
+      <c r="ED182" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="EE182" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="EF182" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="EG182" t="inlineStr"/>
+      <c r="EH182" t="inlineStr"/>
+      <c r="EI182" t="inlineStr"/>
+      <c r="EJ182" t="inlineStr"/>
+      <c r="EK182" t="inlineStr"/>
+      <c r="EL182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>23</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Makhachkala</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Baltika</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="n">
+        <v>46117.5625</v>
+      </c>
+      <c r="G183" t="n">
+        <v>2</v>
+      </c>
+      <c r="H183" t="n">
+        <v>2</v>
+      </c>
+      <c r="I183" t="n">
+        <v>4</v>
+      </c>
+      <c r="J183" t="n">
+        <v>4</v>
+      </c>
+      <c r="K183" t="n">
+        <v>5</v>
+      </c>
+      <c r="L183" t="n">
+        <v>9</v>
+      </c>
+      <c r="M183" t="n">
+        <v>0</v>
+      </c>
+      <c r="N183" t="n">
+        <v>1</v>
+      </c>
+      <c r="O183" t="n">
+        <v>0</v>
+      </c>
+      <c r="P183" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>4</v>
+      </c>
+      <c r="R183" t="n">
+        <v>4</v>
+      </c>
+      <c r="S183" t="n">
+        <v>9</v>
+      </c>
+      <c r="T183" t="n">
+        <v>9</v>
+      </c>
+      <c r="U183" t="n">
+        <v>13</v>
+      </c>
+      <c r="V183" t="n">
+        <v>13</v>
+      </c>
+      <c r="W183" t="n">
+        <v>14</v>
+      </c>
+      <c r="X183" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y183" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z183" t="n">
+        <v>56</v>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>Anzhi-Arena</t>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>, Kaspiysk</t>
+        </is>
+      </c>
+      <c r="AC183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD183" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE183" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AF183" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AG183" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AH183" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI183" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AJ183" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AK183" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AL183" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AM183" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AN183" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AO183" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AP183" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AQ183" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AR183" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS183" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AT183" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AU183" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW183" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX183" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY183" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ183" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA183" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB183" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD183" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF183" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG183" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH183" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI183" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ183" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK183" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL183" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM183" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN183" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR183" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT183" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU183" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV183" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW183" t="n">
+        <v>44</v>
+      </c>
+      <c r="BX183" t="n">
+        <v>96</v>
+      </c>
+      <c r="BY183" t="n">
+        <v>92</v>
+      </c>
+      <c r="BZ183" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CA183" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CB183" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="CC183" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE183" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI183" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ183" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM183" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN183" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ183" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR183" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS183" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT183" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU183" t="n">
+        <v>22</v>
+      </c>
+      <c r="CV183" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW183" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX183" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY183" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ183" t="n">
+        <v>14</v>
+      </c>
+      <c r="DA183" t="n">
+        <v>55</v>
+      </c>
+      <c r="DB183" t="n">
+        <v>14</v>
+      </c>
+      <c r="DC183" t="n">
+        <v>60</v>
+      </c>
+      <c r="DD183" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DE183" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF183" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DG183" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DH183" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="DI183" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="DJ183" t="n">
+        <v>87</v>
+      </c>
+      <c r="DK183" t="n">
+        <v>46</v>
+      </c>
+      <c r="DL183" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DM183" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DN183" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="DO183" t="n">
+        <v>23</v>
+      </c>
+      <c r="DP183" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ183" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR183" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS183" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT183" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU183" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV183" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW183" t="inlineStr"/>
+      <c r="DX183" t="inlineStr"/>
+      <c r="DY183" t="inlineStr"/>
+      <c r="DZ183" t="inlineStr"/>
+      <c r="EA183" t="inlineStr"/>
+      <c r="EB183" t="inlineStr"/>
+      <c r="EC183" t="inlineStr"/>
+      <c r="ED183" t="inlineStr">
+        <is>
+          <t>3.71</t>
+        </is>
+      </c>
+      <c r="EE183" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EF183" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="EG183" t="inlineStr"/>
+      <c r="EH183" t="inlineStr"/>
+      <c r="EI183" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EJ183" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EK183" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EL183" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
+++ b/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL183" headerRowCount="1">
-  <autoFilter ref="A1:EL183"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL185" headerRowCount="1">
+  <autoFilter ref="A1:EL185"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL183"/>
+  <dimension ref="A1:EL185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.8" customWidth="1" min="1" max="1"/>
@@ -2667,7 +2667,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3074,7 +3074,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="DE5" t="n">
         <v>0.27</v>
@@ -3107,7 +3107,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -4433,7 +4433,7 @@
         <v>1.83</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4463,7 +4463,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5750,7 +5750,7 @@
         <v>100</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="DE11" t="n">
         <v>1.5</v>
@@ -5783,7 +5783,7 @@
         <v>2.56</v>
       </c>
       <c r="DO11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6637,7 +6637,7 @@
         <v>2.5</v>
       </c>
       <c r="DE13" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DF13" t="n">
         <v>0</v>
@@ -6667,7 +6667,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7098,7 +7098,7 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DE14" t="n">
         <v>1.08</v>
@@ -7131,7 +7131,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8487,7 +8487,7 @@
         <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9793,7 +9793,7 @@
         <v>1.17</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DF20" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>2.42</v>
       </c>
       <c r="DO20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10235,7 +10235,7 @@
         <v>1.95</v>
       </c>
       <c r="DO21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -12011,7 +12011,7 @@
         <v>2.16</v>
       </c>
       <c r="DO25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13361,7 +13361,7 @@
         <v>2.55</v>
       </c>
       <c r="DE28" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="DF28" t="n">
         <v>3</v>
@@ -13391,7 +13391,7 @@
         <v>2.17</v>
       </c>
       <c r="DO28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -13843,7 +13843,7 @@
         <v>3.23</v>
       </c>
       <c r="DO29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -15150,7 +15150,7 @@
         <v>50</v>
       </c>
       <c r="DD32" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DE32" t="n">
         <v>1.36</v>
@@ -15183,7 +15183,7 @@
         <v>1.95</v>
       </c>
       <c r="DO32" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16033,7 +16033,7 @@
         <v>2.27</v>
       </c>
       <c r="DE34" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DF34" t="n">
         <v>3</v>
@@ -16063,7 +16063,7 @@
         <v>2.73</v>
       </c>
       <c r="DO34" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -16442,7 +16442,7 @@
         <v>75</v>
       </c>
       <c r="DD35" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="DE35" t="n">
         <v>1.55</v>
@@ -16475,7 +16475,7 @@
         <v>2.48</v>
       </c>
       <c r="DO35" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17835,7 +17835,7 @@
         <v>2.06</v>
       </c>
       <c r="DO38" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -18723,7 +18723,7 @@
         <v>2.87</v>
       </c>
       <c r="DO40" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20067,7 +20067,7 @@
         <v>2.55</v>
       </c>
       <c r="DO43" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -20963,7 +20963,7 @@
         <v>2.4</v>
       </c>
       <c r="DO45" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22722,7 +22722,7 @@
         <v>84</v>
       </c>
       <c r="DD49" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DE49" t="n">
         <v>1.5</v>
@@ -22755,7 +22755,7 @@
         <v>2.7</v>
       </c>
       <c r="DO49" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -23181,7 +23181,7 @@
         <v>1.17</v>
       </c>
       <c r="DE50" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="DF50" t="n">
         <v>0.75</v>
@@ -23211,7 +23211,7 @@
         <v>2.38</v>
       </c>
       <c r="DO50" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24050,7 +24050,7 @@
         <v>50</v>
       </c>
       <c r="DD52" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="DE52" t="n">
         <v>0.36</v>
@@ -24083,7 +24083,7 @@
         <v>2</v>
       </c>
       <c r="DO52" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25403,7 +25403,7 @@
         <v>2.77</v>
       </c>
       <c r="DO55" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -26759,7 +26759,7 @@
         <v>2.53</v>
       </c>
       <c r="DO58" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -27647,7 +27647,7 @@
         <v>3.31</v>
       </c>
       <c r="DO60" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -28073,7 +28073,7 @@
         <v>1.83</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DF61" t="n">
         <v>2</v>
@@ -28103,7 +28103,7 @@
         <v>2.92</v>
       </c>
       <c r="DO61" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -28971,7 +28971,7 @@
         <v>1.8</v>
       </c>
       <c r="DO63" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -30745,7 +30745,7 @@
         <v>0.82</v>
       </c>
       <c r="DE67" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="DF67" t="n">
         <v>0.5</v>
@@ -30775,7 +30775,7 @@
         <v>3</v>
       </c>
       <c r="DO67" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -31201,7 +31201,7 @@
         <v>1.58</v>
       </c>
       <c r="DE68" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DF68" t="n">
         <v>2.33</v>
@@ -31231,7 +31231,7 @@
         <v>2.38</v>
       </c>
       <c r="DO68" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -32074,7 +32074,7 @@
         <v>88</v>
       </c>
       <c r="DD70" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="DE70" t="n">
         <v>0.38</v>
@@ -32107,7 +32107,7 @@
         <v>2.43</v>
       </c>
       <c r="DO70" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -33430,7 +33430,7 @@
         <v>88</v>
       </c>
       <c r="DD73" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DE73" t="n">
         <v>1.17</v>
@@ -33463,7 +33463,7 @@
         <v>2.46</v>
       </c>
       <c r="DO73" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -34789,7 +34789,7 @@
         <v>2.27</v>
       </c>
       <c r="DE76" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="DF76" t="n">
         <v>2</v>
@@ -34819,7 +34819,7 @@
         <v>3.09</v>
       </c>
       <c r="DO76" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -36611,7 +36611,7 @@
         <v>1.87</v>
       </c>
       <c r="DO80" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP80" t="b">
         <v>0</v>
@@ -37026,7 +37026,7 @@
         <v>53</v>
       </c>
       <c r="DD81" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="DE81" t="n">
         <v>0.55</v>
@@ -37059,7 +37059,7 @@
         <v>2.45</v>
       </c>
       <c r="DO81" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -37927,7 +37927,7 @@
         <v>2.19</v>
       </c>
       <c r="DO83" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -38769,7 +38769,7 @@
         <v>1.33</v>
       </c>
       <c r="DE85" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DF85" t="n">
         <v>1.6</v>
@@ -38799,7 +38799,7 @@
         <v>3.26</v>
       </c>
       <c r="DO85" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -39682,7 +39682,7 @@
         <v>70</v>
       </c>
       <c r="DD87" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DE87" t="n">
         <v>0.55</v>
@@ -39715,7 +39715,7 @@
         <v>1.93</v>
       </c>
       <c r="DO87" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -40171,7 +40171,7 @@
         <v>3.05</v>
       </c>
       <c r="DO88" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -40731,168 +40731,176 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
         <v>45948.41666666666</v>
       </c>
       <c r="G90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
         <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K90" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L90" t="n">
+        <v>9</v>
+      </c>
+      <c r="M90" t="n">
+        <v>2</v>
+      </c>
+      <c r="N90" t="n">
+        <v>2</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
         <v>11</v>
       </c>
-      <c r="M90" t="n">
-        <v>1</v>
-      </c>
-      <c r="N90" t="n">
-        <v>2</v>
-      </c>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>3</v>
-      </c>
       <c r="R90" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T90" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="U90" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="V90" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W90" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="X90" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Y90" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="Z90" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA90" t="inlineStr"/>
-      <c r="AB90" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>Stadion Nizhny Novgorod</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>ul. Dolzhanskaya, Nizhniy Novgorod</t>
+        </is>
+      </c>
       <c r="AC90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD90" t="n">
         <v>2</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.9</v>
+        <v>2.29</v>
       </c>
       <c r="AF90" t="n">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="AG90" t="n">
-        <v>3.28</v>
+        <v>2.57</v>
       </c>
       <c r="AH90" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AI90" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AJ90" t="n">
-        <v>3.08</v>
+        <v>2.66</v>
       </c>
       <c r="AK90" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AL90" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="AM90" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AN90" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AO90" t="n">
-        <v>2.62</v>
+        <v>2.16</v>
       </c>
       <c r="AP90" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR90" t="n">
-        <v>2.74</v>
+        <v>2.51</v>
       </c>
       <c r="AS90" t="n">
-        <v>3.04</v>
+        <v>3.32</v>
       </c>
       <c r="AT90" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AU90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV90" t="n">
         <v>0</v>
       </c>
       <c r="AW90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ90" t="n">
         <v>1</v>
       </c>
       <c r="BA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB90" t="n">
-        <v>-1</v>
+        <v>668270</v>
       </c>
       <c r="BC90" t="n">
         <v>0</v>
       </c>
       <c r="BD90" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BE90" t="n">
         <v>0</v>
       </c>
       <c r="BF90" t="n">
-        <v>6069</v>
+        <v>4088</v>
       </c>
       <c r="BG90" t="n">
         <v>-1</v>
@@ -40919,7 +40927,7 @@
         <v>-1</v>
       </c>
       <c r="BO90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP90" t="n">
         <v>0</v>
@@ -40931,7 +40939,7 @@
         <v>2</v>
       </c>
       <c r="BS90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT90" t="n">
         <v>3</v>
@@ -40940,25 +40948,25 @@
         <v>1</v>
       </c>
       <c r="BV90" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="BW90" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="BX90" t="n">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="BY90" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BZ90" t="n">
-        <v>1.44</v>
+        <v>2.82</v>
       </c>
       <c r="CA90" t="n">
-        <v>1.34</v>
+        <v>1.09</v>
       </c>
       <c r="CB90" t="n">
-        <v>2.78</v>
+        <v>3.91</v>
       </c>
       <c r="CC90" t="n">
         <v>0</v>
@@ -41006,73 +41014,73 @@
         <v>1</v>
       </c>
       <c r="CR90" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS90" t="n">
         <v>21</v>
       </c>
-      <c r="CS90" t="n">
-        <v>23</v>
-      </c>
       <c r="CT90" t="n">
         <v>1</v>
       </c>
       <c r="CU90" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="CV90" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CW90" t="n">
         <v>1</v>
       </c>
       <c r="CX90" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="CY90" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="CZ90" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="DA90" t="n">
         <v>100</v>
       </c>
       <c r="DB90" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="DC90" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="DD90" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="DE90" t="n">
-        <v>0.45</v>
+        <v>1.08</v>
       </c>
       <c r="DF90" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="DG90" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="DH90" t="n">
-        <v>1.09</v>
+        <v>0.55</v>
       </c>
       <c r="DI90" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="DJ90" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="DK90" t="n">
         <v>0</v>
       </c>
       <c r="DL90" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DM90" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="DN90" t="n">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="DO90" t="n">
         <v>23</v>
@@ -41081,7 +41089,7 @@
         <v>1</v>
       </c>
       <c r="DQ90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR90" t="b">
         <v>0</v>
@@ -41096,66 +41104,66 @@
         <v>0</v>
       </c>
       <c r="DV90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW90" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="DX90" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="DY90" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="DZ90" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EA90" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EB90" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="EC90" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="ED90" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="EE90" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="EF90" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="EG90" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EH90" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="EI90" t="inlineStr"/>
@@ -41179,176 +41187,168 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F91" s="2" t="n">
         <v>45948.41666666666</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91" t="n">
         <v>1</v>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J91" t="n">
+        <v>5</v>
+      </c>
+      <c r="K91" t="n">
         <v>6</v>
       </c>
-      <c r="K91" t="n">
+      <c r="L91" t="n">
+        <v>11</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1</v>
+      </c>
+      <c r="N91" t="n">
+        <v>2</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
         <v>3</v>
       </c>
-      <c r="L91" t="n">
-        <v>9</v>
-      </c>
-      <c r="M91" t="n">
-        <v>2</v>
-      </c>
-      <c r="N91" t="n">
-        <v>2</v>
-      </c>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>11</v>
-      </c>
       <c r="R91" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T91" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="U91" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="V91" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W91" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="X91" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Y91" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="Z91" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>Stadion Nizhny Novgorod</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>ul. Dolzhanskaya, Nizhniy Novgorod</t>
-        </is>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="AA91" t="inlineStr"/>
+      <c r="AB91" t="inlineStr"/>
       <c r="AC91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD91" t="n">
         <v>2</v>
       </c>
       <c r="AE91" t="n">
-        <v>2.29</v>
+        <v>1.9</v>
       </c>
       <c r="AF91" t="n">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
       <c r="AG91" t="n">
-        <v>2.57</v>
+        <v>3.28</v>
       </c>
       <c r="AH91" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AI91" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AJ91" t="n">
-        <v>2.66</v>
+        <v>3.08</v>
       </c>
       <c r="AK91" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="AL91" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="AM91" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AN91" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AO91" t="n">
-        <v>2.16</v>
+        <v>2.62</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AR91" t="n">
-        <v>2.51</v>
+        <v>2.74</v>
       </c>
       <c r="AS91" t="n">
-        <v>3.32</v>
+        <v>3.04</v>
       </c>
       <c r="AT91" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AU91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV91" t="n">
         <v>0</v>
       </c>
       <c r="AW91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ91" t="n">
         <v>1</v>
       </c>
       <c r="BA91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB91" t="n">
-        <v>668270</v>
+        <v>-1</v>
       </c>
       <c r="BC91" t="n">
         <v>0</v>
       </c>
       <c r="BD91" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BE91" t="n">
         <v>0</v>
       </c>
       <c r="BF91" t="n">
-        <v>4088</v>
+        <v>6069</v>
       </c>
       <c r="BG91" t="n">
         <v>-1</v>
@@ -41375,7 +41375,7 @@
         <v>-1</v>
       </c>
       <c r="BO91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP91" t="n">
         <v>0</v>
@@ -41387,7 +41387,7 @@
         <v>2</v>
       </c>
       <c r="BS91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT91" t="n">
         <v>3</v>
@@ -41396,25 +41396,25 @@
         <v>1</v>
       </c>
       <c r="BV91" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="BW91" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="BX91" t="n">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="BY91" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="BZ91" t="n">
-        <v>2.82</v>
+        <v>1.44</v>
       </c>
       <c r="CA91" t="n">
-        <v>1.09</v>
+        <v>1.34</v>
       </c>
       <c r="CB91" t="n">
-        <v>3.91</v>
+        <v>2.78</v>
       </c>
       <c r="CC91" t="n">
         <v>0</v>
@@ -41462,73 +41462,73 @@
         <v>1</v>
       </c>
       <c r="CR91" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CS91" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CT91" t="n">
         <v>1</v>
       </c>
       <c r="CU91" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="CV91" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CW91" t="n">
         <v>1</v>
       </c>
       <c r="CX91" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="CY91" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="CZ91" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="DA91" t="n">
         <v>100</v>
       </c>
       <c r="DB91" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="DC91" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="DD91" t="n">
-        <v>1.17</v>
+        <v>1.6</v>
       </c>
       <c r="DE91" t="n">
-        <v>1.08</v>
+        <v>0.45</v>
       </c>
       <c r="DF91" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="DG91" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="DH91" t="n">
-        <v>0.55</v>
+        <v>1.09</v>
       </c>
       <c r="DI91" t="n">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="DJ91" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="DK91" t="n">
         <v>0</v>
       </c>
       <c r="DL91" t="n">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="DM91" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="DN91" t="n">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="DO91" t="n">
         <v>23</v>
@@ -41537,7 +41537,7 @@
         <v>1</v>
       </c>
       <c r="DQ91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR91" t="b">
         <v>0</v>
@@ -41552,66 +41552,66 @@
         <v>0</v>
       </c>
       <c r="DV91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW91" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="DX91" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="DY91" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="DZ91" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EA91" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EB91" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="EC91" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="ED91" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="EE91" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EF91" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="EG91" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="EH91" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EI91" t="inlineStr"/>
@@ -41946,7 +41946,7 @@
         <v>67</v>
       </c>
       <c r="DD92" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="DE92" t="n">
         <v>1</v>
@@ -41979,7 +41979,7 @@
         <v>2.78</v>
       </c>
       <c r="DO92" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -42887,7 +42887,7 @@
         <v>3.2</v>
       </c>
       <c r="DO94" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -43310,7 +43310,7 @@
         <v>84</v>
       </c>
       <c r="DD95" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DE95" t="n">
         <v>1.55</v>
@@ -43343,7 +43343,7 @@
         <v>2.32</v>
       </c>
       <c r="DO95" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -43787,7 +43787,7 @@
         <v>2.71</v>
       </c>
       <c r="DO96" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -44634,7 +44634,7 @@
         <v>86</v>
       </c>
       <c r="DD98" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="DE98" t="n">
         <v>0.45</v>
@@ -44667,7 +44667,7 @@
         <v>2.97</v>
       </c>
       <c r="DO98" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -45949,7 +45949,7 @@
         <v>0.82</v>
       </c>
       <c r="DE101" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DF101" t="n">
         <v>0.67</v>
@@ -45979,7 +45979,7 @@
         <v>2.97</v>
       </c>
       <c r="DO101" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -47281,7 +47281,7 @@
         <v>2.5</v>
       </c>
       <c r="DE104" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="DF104" t="n">
         <v>2</v>
@@ -47311,7 +47311,7 @@
         <v>3.31</v>
       </c>
       <c r="DO104" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -47751,7 +47751,7 @@
         <v>2.37</v>
       </c>
       <c r="DO105" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -48627,7 +48627,7 @@
         <v>2.61</v>
       </c>
       <c r="DO107" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP107" t="b">
         <v>0</v>
@@ -49195,25 +49195,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F109" s="2" t="n">
         <v>45962.71875</v>
       </c>
       <c r="G109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J109" t="n">
         <v>6</v>
@@ -49228,324 +49228,332 @@
         <v>2</v>
       </c>
       <c r="N109" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P109" t="n">
         <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R109" t="n">
         <v>2</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T109" t="n">
         <v>6</v>
       </c>
       <c r="U109" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V109" t="n">
         <v>8</v>
       </c>
       <c r="W109" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="X109" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Y109" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Z109" t="n">
-        <v>51</v>
-      </c>
-      <c r="AA109" t="inlineStr"/>
-      <c r="AB109" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>Stadion Central’nyj im. I.P. Chayka</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>ul. Suvorova, Peschanokopskoye</t>
+        </is>
+      </c>
       <c r="AC109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD109" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE109" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AF109" t="n">
-        <v>3.9</v>
+        <v>3.47</v>
       </c>
       <c r="AG109" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AH109" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AI109" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AJ109" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="AK109" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AL109" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AM109" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="AN109" t="n">
-        <v>1.92</v>
+        <v>2.23</v>
       </c>
       <c r="AO109" t="n">
-        <v>2.65</v>
+        <v>2.32</v>
       </c>
       <c r="AP109" t="n">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AR109" t="n">
-        <v>2.6</v>
+        <v>2.77</v>
       </c>
       <c r="AS109" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="AT109" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB109" t="n">
+        <v>668270</v>
+      </c>
+      <c r="BC109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD109" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF109" t="n">
+        <v>7890</v>
+      </c>
+      <c r="BG109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS109" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT109" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV109" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW109" t="n">
+        <v>35</v>
+      </c>
+      <c r="BX109" t="n">
+        <v>78</v>
+      </c>
+      <c r="BY109" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ109" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CA109" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="CB109" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="CC109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR109" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS109" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU109" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV109" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX109" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY109" t="n">
+        <v>15</v>
+      </c>
+      <c r="CZ109" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA109" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB109" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC109" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD109" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DE109" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DF109" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG109" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DH109" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DI109" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DJ109" t="n">
+        <v>58</v>
+      </c>
+      <c r="DK109" t="n">
+        <v>34</v>
+      </c>
+      <c r="DL109" t="n">
         <v>1.47</v>
       </c>
-      <c r="AU109" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV109" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX109" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ109" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA109" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB109" t="n">
-        <v>921</v>
-      </c>
-      <c r="BC109" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD109" t="n">
-        <v>84</v>
-      </c>
-      <c r="BE109" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF109" t="n">
-        <v>45133</v>
-      </c>
-      <c r="BG109" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BH109" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI109" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BJ109" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BK109" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BL109" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BM109" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BN109" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BO109" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP109" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ109" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR109" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS109" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT109" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU109" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV109" t="n">
-        <v>51</v>
-      </c>
-      <c r="BW109" t="n">
-        <v>46</v>
-      </c>
-      <c r="BX109" t="n">
-        <v>89</v>
-      </c>
-      <c r="BY109" t="n">
-        <v>85</v>
-      </c>
-      <c r="BZ109" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CA109" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="CB109" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="CC109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM109" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CN109" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CO109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR109" t="n">
-        <v>28</v>
-      </c>
-      <c r="CS109" t="n">
-        <v>8</v>
-      </c>
-      <c r="CT109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU109" t="n">
-        <v>20</v>
-      </c>
-      <c r="CV109" t="n">
-        <v>13</v>
-      </c>
-      <c r="CW109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX109" t="n">
-        <v>7</v>
-      </c>
-      <c r="CY109" t="n">
-        <v>6</v>
-      </c>
-      <c r="CZ109" t="n">
-        <v>55</v>
-      </c>
-      <c r="DA109" t="n">
-        <v>100</v>
-      </c>
-      <c r="DB109" t="n">
-        <v>32</v>
-      </c>
-      <c r="DC109" t="n">
-        <v>77</v>
-      </c>
-      <c r="DD109" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="DE109" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="DF109" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="DG109" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="DH109" t="n">
-        <v>2</v>
-      </c>
-      <c r="DI109" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="DJ109" t="n">
-        <v>45</v>
-      </c>
-      <c r="DK109" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL109" t="n">
-        <v>1.92</v>
-      </c>
       <c r="DM109" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="DN109" t="n">
-        <v>3.47</v>
+        <v>2.81</v>
       </c>
       <c r="DO109" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
       </c>
       <c r="DQ109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR109" t="b">
         <v>0</v>
@@ -49564,46 +49572,62 @@
       </c>
       <c r="DW109" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="DX109" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="DY109" t="inlineStr">
         <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="DZ109" t="inlineStr"/>
-      <c r="EA109" t="inlineStr"/>
-      <c r="EB109" t="inlineStr"/>
-      <c r="EC109" t="inlineStr"/>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="DZ109" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EA109" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EB109" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="EC109" t="inlineStr">
+        <is>
+          <t>2.79</t>
+        </is>
+      </c>
       <c r="ED109" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EE109" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="EF109" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="EG109" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="EH109" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EI109" t="inlineStr"/>
@@ -49627,25 +49651,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F110" s="2" t="n">
         <v>45962.71875</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J110" t="n">
         <v>6</v>
@@ -49660,323 +49684,315 @@
         <v>2</v>
       </c>
       <c r="N110" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P110" t="n">
         <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R110" t="n">
         <v>2</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T110" t="n">
         <v>6</v>
       </c>
       <c r="U110" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V110" t="n">
         <v>8</v>
       </c>
       <c r="W110" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X110" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Y110" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Z110" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA110" t="inlineStr">
-        <is>
-          <t>Stadion Central’nyj im. I.P. Chayka</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>ul. Suvorova, Peschanokopskoye</t>
-        </is>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="AA110" t="inlineStr"/>
+      <c r="AB110" t="inlineStr"/>
       <c r="AC110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD110" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE110" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AF110" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG110" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AH110" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI110" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ110" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AK110" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL110" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM110" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO110" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AP110" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ110" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR110" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AS110" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT110" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AU110" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB110" t="n">
+        <v>921</v>
+      </c>
+      <c r="BC110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD110" t="n">
+        <v>84</v>
+      </c>
+      <c r="BE110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF110" t="n">
+        <v>45133</v>
+      </c>
+      <c r="BG110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS110" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV110" t="n">
+        <v>51</v>
+      </c>
+      <c r="BW110" t="n">
+        <v>46</v>
+      </c>
+      <c r="BX110" t="n">
+        <v>89</v>
+      </c>
+      <c r="BY110" t="n">
+        <v>85</v>
+      </c>
+      <c r="BZ110" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CA110" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="CB110" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="CC110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR110" t="n">
+        <v>28</v>
+      </c>
+      <c r="CS110" t="n">
+        <v>8</v>
+      </c>
+      <c r="CT110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU110" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV110" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX110" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY110" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ110" t="n">
+        <v>55</v>
+      </c>
+      <c r="DA110" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB110" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC110" t="n">
+        <v>77</v>
+      </c>
+      <c r="DD110" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="DE110" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DF110" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DG110" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DH110" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI110" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="DJ110" t="n">
+        <v>45</v>
+      </c>
+      <c r="DK110" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL110" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DM110" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DN110" t="n">
         <v>3.47</v>
-      </c>
-      <c r="AG110" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AH110" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI110" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ110" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AK110" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AL110" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM110" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AN110" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AO110" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AP110" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AQ110" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AR110" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AS110" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AT110" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AU110" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY110" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ110" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA110" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB110" t="n">
-        <v>668270</v>
-      </c>
-      <c r="BC110" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD110" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE110" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF110" t="n">
-        <v>7890</v>
-      </c>
-      <c r="BG110" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BH110" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI110" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BJ110" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BK110" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BL110" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BM110" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BN110" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BO110" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP110" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ110" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR110" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS110" t="n">
-        <v>4</v>
-      </c>
-      <c r="BT110" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU110" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV110" t="n">
-        <v>44</v>
-      </c>
-      <c r="BW110" t="n">
-        <v>35</v>
-      </c>
-      <c r="BX110" t="n">
-        <v>78</v>
-      </c>
-      <c r="BY110" t="n">
-        <v>87</v>
-      </c>
-      <c r="BZ110" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="CA110" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="CB110" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="CC110" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD110" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE110" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF110" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG110" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH110" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI110" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ110" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK110" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL110" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM110" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CN110" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CO110" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP110" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ110" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR110" t="n">
-        <v>20</v>
-      </c>
-      <c r="CS110" t="n">
-        <v>15</v>
-      </c>
-      <c r="CT110" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU110" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV110" t="n">
-        <v>15</v>
-      </c>
-      <c r="CW110" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX110" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY110" t="n">
-        <v>15</v>
-      </c>
-      <c r="CZ110" t="n">
-        <v>42</v>
-      </c>
-      <c r="DA110" t="n">
-        <v>67</v>
-      </c>
-      <c r="DB110" t="n">
-        <v>25</v>
-      </c>
-      <c r="DC110" t="n">
-        <v>75</v>
-      </c>
-      <c r="DD110" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="DE110" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="DF110" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DG110" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="DH110" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="DI110" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="DJ110" t="n">
-        <v>58</v>
-      </c>
-      <c r="DK110" t="n">
-        <v>34</v>
-      </c>
-      <c r="DL110" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="DM110" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="DN110" t="n">
-        <v>2.81</v>
       </c>
       <c r="DO110" t="n">
         <v>23</v>
@@ -49985,7 +50001,7 @@
         <v>1</v>
       </c>
       <c r="DQ110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR110" t="b">
         <v>0</v>
@@ -50004,62 +50020,46 @@
       </c>
       <c r="DW110" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="DX110" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="DY110" t="inlineStr">
         <is>
-          <t>1.28</t>
-        </is>
-      </c>
-      <c r="DZ110" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EA110" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="EB110" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="EC110" t="inlineStr">
-        <is>
-          <t>2.79</t>
-        </is>
-      </c>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="DZ110" t="inlineStr"/>
+      <c r="EA110" t="inlineStr"/>
+      <c r="EB110" t="inlineStr"/>
+      <c r="EC110" t="inlineStr"/>
       <c r="ED110" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="EE110" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="EF110" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="EG110" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="EH110" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EI110" t="inlineStr"/>
@@ -50435,7 +50435,7 @@
         <v>2.03</v>
       </c>
       <c r="DO111" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -51331,7 +51331,7 @@
         <v>3.33</v>
       </c>
       <c r="DO113" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -52177,7 +52177,7 @@
         <v>1.17</v>
       </c>
       <c r="DE115" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="DF115" t="n">
         <v>1</v>
@@ -52207,7 +52207,7 @@
         <v>2.71</v>
       </c>
       <c r="DO115" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP115" t="b">
         <v>0</v>
@@ -53050,7 +53050,7 @@
         <v>72</v>
       </c>
       <c r="DD117" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DE117" t="n">
         <v>1</v>
@@ -53083,7 +53083,7 @@
         <v>2.24</v>
       </c>
       <c r="DO117" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -53967,7 +53967,7 @@
         <v>3.04</v>
       </c>
       <c r="DO119" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -54407,7 +54407,7 @@
         <v>3.17</v>
       </c>
       <c r="DO120" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -55331,7 +55331,7 @@
         <v>2.2</v>
       </c>
       <c r="DO122" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -56174,7 +56174,7 @@
         <v>67</v>
       </c>
       <c r="DD124" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="DE124" t="n">
         <v>1.17</v>
@@ -56207,7 +56207,7 @@
         <v>3.02</v>
       </c>
       <c r="DO124" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -56663,7 +56663,7 @@
         <v>2.42</v>
       </c>
       <c r="DO125" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP125" t="b">
         <v>1</v>
@@ -58451,7 +58451,7 @@
         <v>3.02</v>
       </c>
       <c r="DO129" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP129" t="b">
         <v>1</v>
@@ -59771,7 +59771,7 @@
         <v>2.78</v>
       </c>
       <c r="DO132" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP132" t="b">
         <v>1</v>
@@ -61101,7 +61101,7 @@
         <v>1.18</v>
       </c>
       <c r="DE135" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DF135" t="n">
         <v>1.29</v>
@@ -61131,7 +61131,7 @@
         <v>2.93</v>
       </c>
       <c r="DO135" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP135" t="b">
         <v>1</v>
@@ -61549,7 +61549,7 @@
         <v>2.83</v>
       </c>
       <c r="DE136" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="DF136" t="n">
         <v>2.71</v>
@@ -61579,7 +61579,7 @@
         <v>3.08</v>
       </c>
       <c r="DO136" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP136" t="b">
         <v>1</v>
@@ -62018,7 +62018,7 @@
         <v>94</v>
       </c>
       <c r="DD137" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DE137" t="n">
         <v>0.27</v>
@@ -62051,7 +62051,7 @@
         <v>2.13</v>
       </c>
       <c r="DO137" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP137" t="b">
         <v>0</v>
@@ -62917,7 +62917,7 @@
         <v>1.18</v>
       </c>
       <c r="DE139" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="DF139" t="n">
         <v>1.13</v>
@@ -62947,7 +62947,7 @@
         <v>2.63</v>
       </c>
       <c r="DO139" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP139" t="b">
         <v>1</v>
@@ -63334,7 +63334,7 @@
         <v>59</v>
       </c>
       <c r="DD140" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="DE140" t="n">
         <v>1.36</v>
@@ -63367,7 +63367,7 @@
         <v>3.01</v>
       </c>
       <c r="DO140" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP140" t="b">
         <v>1</v>
@@ -64658,10 +64658,10 @@
         <v>83</v>
       </c>
       <c r="DD143" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DE143" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DF143" t="n">
         <v>0.63</v>
@@ -64691,7 +64691,7 @@
         <v>2.47</v>
       </c>
       <c r="DO143" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP143" t="b">
         <v>1</v>
@@ -67387,7 +67387,7 @@
         <v>2.83</v>
       </c>
       <c r="DO149" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP149" t="b">
         <v>1</v>
@@ -67829,7 +67829,7 @@
         <v>1.58</v>
       </c>
       <c r="DE150" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="DF150" t="n">
         <v>1.33</v>
@@ -67859,7 +67859,7 @@
         <v>2.37</v>
       </c>
       <c r="DO150" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP150" t="b">
         <v>1</v>
@@ -69178,7 +69178,7 @@
         <v>76</v>
       </c>
       <c r="DD153" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DE153" t="n">
         <v>1.27</v>
@@ -69211,7 +69211,7 @@
         <v>2.44</v>
       </c>
       <c r="DO153" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP153" t="b">
         <v>1</v>
@@ -70123,7 +70123,7 @@
         <v>2.37</v>
       </c>
       <c r="DO155" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP155" t="b">
         <v>1</v>
@@ -71467,7 +71467,7 @@
         <v>2.57</v>
       </c>
       <c r="DO158" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP158" t="b">
         <v>1</v>
@@ -72371,7 +72371,7 @@
         <v>2.9</v>
       </c>
       <c r="DO160" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP160" t="b">
         <v>1</v>
@@ -72802,7 +72802,7 @@
         <v>70</v>
       </c>
       <c r="DD161" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="DE161" t="n">
         <v>1.08</v>
@@ -72835,7 +72835,7 @@
         <v>2.6</v>
       </c>
       <c r="DO161" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP161" t="b">
         <v>1</v>
@@ -73678,7 +73678,7 @@
         <v>84</v>
       </c>
       <c r="DD163" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DE163" t="n">
         <v>2</v>
@@ -73711,7 +73711,7 @@
         <v>2.32</v>
       </c>
       <c r="DO163" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP163" t="b">
         <v>1</v>
@@ -74147,7 +74147,7 @@
         <v>3.25</v>
       </c>
       <c r="DO164" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP164" t="b">
         <v>1</v>
@@ -76437,7 +76437,7 @@
         <v>2.09</v>
       </c>
       <c r="DE169" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DF169" t="n">
         <v>2</v>
@@ -76467,7 +76467,7 @@
         <v>2.72</v>
       </c>
       <c r="DO169" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP169" t="b">
         <v>1</v>
@@ -78231,7 +78231,7 @@
         <v>2.34</v>
       </c>
       <c r="DO173" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP173" t="b">
         <v>1</v>
@@ -78671,7 +78671,7 @@
         <v>2.84</v>
       </c>
       <c r="DO174" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP174" t="b">
         <v>1</v>
@@ -79525,7 +79525,7 @@
         <v>1.6</v>
       </c>
       <c r="DE176" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="DF176" t="n">
         <v>1.67</v>
@@ -79555,7 +79555,7 @@
         <v>2.16</v>
       </c>
       <c r="DO176" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP176" t="b">
         <v>0</v>
@@ -79987,7 +79987,7 @@
         <v>2.85</v>
       </c>
       <c r="DO177" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP177" t="b">
         <v>1</v>
@@ -80145,10 +80145,10 @@
         <v>18</v>
       </c>
       <c r="Y178" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Z178" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AA178" t="inlineStr"/>
       <c r="AB178" t="inlineStr"/>
@@ -80375,7 +80375,7 @@
         <v>9</v>
       </c>
       <c r="CY178" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CZ178" t="n">
         <v>38</v>
@@ -81017,10 +81017,10 @@
         <v>17</v>
       </c>
       <c r="Y180" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Z180" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AA180" t="inlineStr"/>
       <c r="AB180" t="inlineStr"/>
@@ -81889,7 +81889,7 @@
         <v>0</v>
       </c>
       <c r="Q182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R182" t="n">
         <v>3</v>
@@ -81898,25 +81898,25 @@
         <v>7</v>
       </c>
       <c r="T182" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U182" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V182" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W182" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X182" t="n">
         <v>14</v>
       </c>
       <c r="Y182" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Z182" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
@@ -82076,13 +82076,13 @@
         <v>104</v>
       </c>
       <c r="BZ182" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="CA182" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="CB182" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="CC182" t="n">
         <v>0</v>
@@ -82133,7 +82133,7 @@
         <v>23</v>
       </c>
       <c r="CS182" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CT182" t="n">
         <v>1</v>
@@ -82237,10 +82237,26 @@
           <t>1.45</t>
         </is>
       </c>
-      <c r="DZ182" t="inlineStr"/>
-      <c r="EA182" t="inlineStr"/>
-      <c r="EB182" t="inlineStr"/>
-      <c r="EC182" t="inlineStr"/>
+      <c r="DZ182" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EA182" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EB182" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="EC182" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
       <c r="ED182" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -82448,7 +82464,7 @@
         <v>0</v>
       </c>
       <c r="BF183" t="n">
-        <v>-1</v>
+        <v>2559</v>
       </c>
       <c r="BG183" t="n">
         <v>-1</v>
@@ -82583,7 +82599,7 @@
         <v>6</v>
       </c>
       <c r="CY183" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CZ183" t="n">
         <v>14</v>
@@ -82654,9 +82670,21 @@
       <c r="DV183" t="b">
         <v>1</v>
       </c>
-      <c r="DW183" t="inlineStr"/>
-      <c r="DX183" t="inlineStr"/>
-      <c r="DY183" t="inlineStr"/>
+      <c r="DW183" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="DX183" t="inlineStr">
+        <is>
+          <t>6.51</t>
+        </is>
+      </c>
+      <c r="DY183" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
       <c r="DZ183" t="inlineStr"/>
       <c r="EA183" t="inlineStr"/>
       <c r="EB183" t="inlineStr"/>
@@ -82678,26 +82706,874 @@
       </c>
       <c r="EG183" t="inlineStr"/>
       <c r="EH183" t="inlineStr"/>
-      <c r="EI183" t="inlineStr">
-        <is>
-          <t>2.13</t>
-        </is>
-      </c>
-      <c r="EJ183" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="EK183" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="EL183" t="inlineStr">
-        <is>
-          <t>2.13</t>
-        </is>
-      </c>
+      <c r="EI183" t="inlineStr"/>
+      <c r="EJ183" t="inlineStr"/>
+      <c r="EK183" t="inlineStr"/>
+      <c r="EL183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>23</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Spartak Moskva</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Lokomotiv Moskva</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="n">
+        <v>46117.6875</v>
+      </c>
+      <c r="G184" t="n">
+        <v>2</v>
+      </c>
+      <c r="H184" t="n">
+        <v>1</v>
+      </c>
+      <c r="I184" t="n">
+        <v>3</v>
+      </c>
+      <c r="J184" t="n">
+        <v>3</v>
+      </c>
+      <c r="K184" t="n">
+        <v>3</v>
+      </c>
+      <c r="L184" t="n">
+        <v>6</v>
+      </c>
+      <c r="M184" t="n">
+        <v>1</v>
+      </c>
+      <c r="N184" t="n">
+        <v>4</v>
+      </c>
+      <c r="O184" t="n">
+        <v>0</v>
+      </c>
+      <c r="P184" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>6</v>
+      </c>
+      <c r="R184" t="n">
+        <v>4</v>
+      </c>
+      <c r="S184" t="n">
+        <v>10</v>
+      </c>
+      <c r="T184" t="n">
+        <v>6</v>
+      </c>
+      <c r="U184" t="n">
+        <v>16</v>
+      </c>
+      <c r="V184" t="n">
+        <v>10</v>
+      </c>
+      <c r="W184" t="n">
+        <v>15</v>
+      </c>
+      <c r="X184" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y184" t="n">
+        <v>62</v>
+      </c>
+      <c r="Z184" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA184" t="inlineStr"/>
+      <c r="AB184" t="inlineStr"/>
+      <c r="AC184" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD184" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE184" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF184" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG184" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH184" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI184" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ184" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK184" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL184" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AM184" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN184" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO184" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AP184" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AQ184" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR184" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AS184" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT184" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AU184" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW184" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX184" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ184" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA184" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB184" t="n">
+        <v>924</v>
+      </c>
+      <c r="BC184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD184" t="n">
+        <v>69</v>
+      </c>
+      <c r="BE184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF184" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG184" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH184" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI184" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ184" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK184" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL184" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM184" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN184" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ184" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR184" t="n">
+        <v>5</v>
+      </c>
+      <c r="BS184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT184" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU184" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV184" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW184" t="n">
+        <v>30</v>
+      </c>
+      <c r="BX184" t="n">
+        <v>98</v>
+      </c>
+      <c r="BY184" t="n">
+        <v>76</v>
+      </c>
+      <c r="BZ184" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="CA184" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="CB184" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="CC184" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE184" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI184" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ184" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM184" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN184" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP184" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ184" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR184" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS184" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT184" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU184" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV184" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW184" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX184" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY184" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ184" t="n">
+        <v>55</v>
+      </c>
+      <c r="DA184" t="n">
+        <v>87</v>
+      </c>
+      <c r="DB184" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC184" t="n">
+        <v>78</v>
+      </c>
+      <c r="DD184" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DE184" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DF184" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="DG184" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DH184" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DI184" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ184" t="n">
+        <v>45</v>
+      </c>
+      <c r="DK184" t="n">
+        <v>14</v>
+      </c>
+      <c r="DL184" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="DM184" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DN184" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="DO184" t="n">
+        <v>23</v>
+      </c>
+      <c r="DP184" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ184" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR184" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS184" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT184" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU184" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV184" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW184" t="inlineStr"/>
+      <c r="DX184" t="inlineStr"/>
+      <c r="DY184" t="inlineStr"/>
+      <c r="DZ184" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EA184" t="inlineStr"/>
+      <c r="EB184" t="inlineStr"/>
+      <c r="EC184" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="ED184" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EE184" t="inlineStr">
+        <is>
+          <t>3.99</t>
+        </is>
+      </c>
+      <c r="EF184" t="inlineStr">
+        <is>
+          <t>3.83</t>
+        </is>
+      </c>
+      <c r="EG184" t="inlineStr"/>
+      <c r="EH184" t="inlineStr"/>
+      <c r="EI184" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EJ184" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EK184" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EL184" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>23</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>FK Sochi</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="n">
+        <v>46118.6875</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" t="n">
+        <v>1</v>
+      </c>
+      <c r="I185" t="n">
+        <v>1</v>
+      </c>
+      <c r="J185" t="n">
+        <v>6</v>
+      </c>
+      <c r="K185" t="n">
+        <v>1</v>
+      </c>
+      <c r="L185" t="n">
+        <v>7</v>
+      </c>
+      <c r="M185" t="n">
+        <v>2</v>
+      </c>
+      <c r="N185" t="n">
+        <v>2</v>
+      </c>
+      <c r="O185" t="n">
+        <v>0</v>
+      </c>
+      <c r="P185" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>4</v>
+      </c>
+      <c r="R185" t="n">
+        <v>1</v>
+      </c>
+      <c r="S185" t="n">
+        <v>11</v>
+      </c>
+      <c r="T185" t="n">
+        <v>5</v>
+      </c>
+      <c r="U185" t="n">
+        <v>15</v>
+      </c>
+      <c r="V185" t="n">
+        <v>6</v>
+      </c>
+      <c r="W185" t="n">
+        <v>15</v>
+      </c>
+      <c r="X185" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y185" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z185" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>Olimpiyskiy Stadion Fisht</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>Olimpiyskiy prospekt, Sochi</t>
+        </is>
+      </c>
+      <c r="AC185" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD185" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE185" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AF185" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG185" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH185" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI185" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AJ185" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AK185" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AL185" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AM185" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN185" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AO185" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AP185" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AQ185" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR185" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AS185" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT185" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AU185" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW185" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ185" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA185" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB185" t="n">
+        <v>932</v>
+      </c>
+      <c r="BC185" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD185" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE185" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF185" t="n">
+        <v>3662</v>
+      </c>
+      <c r="BG185" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH185" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI185" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ185" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK185" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL185" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM185" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN185" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO185" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP185" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ185" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR185" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS185" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT185" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU185" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV185" t="n">
+        <v>53</v>
+      </c>
+      <c r="BW185" t="n">
+        <v>33</v>
+      </c>
+      <c r="BX185" t="n">
+        <v>107</v>
+      </c>
+      <c r="BY185" t="n">
+        <v>83</v>
+      </c>
+      <c r="BZ185" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CA185" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CB185" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="CC185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI185" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ185" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM185" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN185" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ185" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR185" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS185" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT185" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU185" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV185" t="n">
+        <v>22</v>
+      </c>
+      <c r="CW185" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX185" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY185" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ185" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA185" t="n">
+        <v>69</v>
+      </c>
+      <c r="DB185" t="n">
+        <v>23</v>
+      </c>
+      <c r="DC185" t="n">
+        <v>73</v>
+      </c>
+      <c r="DD185" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="DE185" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DF185" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="DG185" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DH185" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="DI185" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DJ185" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK185" t="n">
+        <v>32</v>
+      </c>
+      <c r="DL185" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="DM185" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="DN185" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="DO185" t="n">
+        <v>23</v>
+      </c>
+      <c r="DP185" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ185" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR185" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS185" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT185" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU185" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV185" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW185" t="inlineStr"/>
+      <c r="DX185" t="inlineStr"/>
+      <c r="DY185" t="inlineStr"/>
+      <c r="DZ185" t="inlineStr"/>
+      <c r="EA185" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EB185" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="EC185" t="inlineStr"/>
+      <c r="ED185" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
+      </c>
+      <c r="EE185" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EF185" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="EG185" t="inlineStr"/>
+      <c r="EH185" t="inlineStr"/>
+      <c r="EI185" t="inlineStr"/>
+      <c r="EJ185" t="inlineStr"/>
+      <c r="EK185" t="inlineStr"/>
+      <c r="EL185" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
+++ b/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
@@ -83205,25 +83205,25 @@
         <v>0</v>
       </c>
       <c r="Q185" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R185" t="n">
         <v>1</v>
       </c>
       <c r="S185" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T185" t="n">
         <v>5</v>
       </c>
       <c r="U185" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="V185" t="n">
         <v>6</v>
       </c>
       <c r="W185" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="X185" t="n">
         <v>18</v>
@@ -83392,13 +83392,13 @@
         <v>83</v>
       </c>
       <c r="BZ185" t="n">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="CA185" t="n">
         <v>0.7</v>
       </c>
       <c r="CB185" t="n">
-        <v>2.31</v>
+        <v>2.51</v>
       </c>
       <c r="CC185" t="n">
         <v>0</v>
@@ -83446,10 +83446,10 @@
         <v>1</v>
       </c>
       <c r="CR185" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="CS185" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CT185" t="n">
         <v>1</v>
@@ -83467,7 +83467,7 @@
         <v>5</v>
       </c>
       <c r="CY185" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CZ185" t="n">
         <v>50</v>

--- a/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
+++ b/data/matches/leagues/Russian_Premier_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL185" headerRowCount="1">
-  <autoFilter ref="A1:EL185"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL188" headerRowCount="1">
+  <autoFilter ref="A1:EL188"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL185"/>
+  <dimension ref="A1:EL188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.8" customWidth="1" min="1" max="1"/>
@@ -4463,7 +4463,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5318,10 +5318,10 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5351,7 +5351,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -7529,7 +7529,7 @@
         <v>2.55</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DF15" t="n">
         <v>0</v>
@@ -8454,7 +8454,7 @@
         <v>0</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DE17" t="n">
         <v>1.55</v>
@@ -10650,10 +10650,10 @@
         <v>0</v>
       </c>
       <c r="DD22" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="DE22" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="DF22" t="n">
         <v>0</v>
@@ -10683,7 +10683,7 @@
         <v>0</v>
       </c>
       <c r="DO22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11553,7 +11553,7 @@
         <v>1.58</v>
       </c>
       <c r="DE24" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DF24" t="n">
         <v>0</v>
@@ -11978,7 +11978,7 @@
         <v>50</v>
       </c>
       <c r="DD25" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DE25" t="n">
         <v>0.36</v>
@@ -12914,7 +12914,7 @@
         <v>25</v>
       </c>
       <c r="DD27" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DE27" t="n">
         <v>1.5</v>
@@ -12947,7 +12947,7 @@
         <v>3.01</v>
       </c>
       <c r="DO27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -15605,7 +15605,7 @@
         <v>1.18</v>
       </c>
       <c r="DE33" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="DF33" t="n">
         <v>0</v>
@@ -16030,7 +16030,7 @@
         <v>100</v>
       </c>
       <c r="DD34" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="DE34" t="n">
         <v>1.58</v>
@@ -16947,7 +16947,7 @@
         <v>2.73</v>
       </c>
       <c r="DO36" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -17365,7 +17365,7 @@
         <v>0.82</v>
       </c>
       <c r="DE37" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="DF37" t="n">
         <v>1</v>
@@ -17802,7 +17802,7 @@
         <v>100</v>
       </c>
       <c r="DD38" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DE38" t="n">
         <v>1</v>
@@ -19581,7 +19581,7 @@
         <v>1.17</v>
       </c>
       <c r="DE42" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DF42" t="n">
         <v>0.67</v>
@@ -19611,7 +19611,7 @@
         <v>2.42</v>
       </c>
       <c r="DO42" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -20034,7 +20034,7 @@
         <v>59</v>
       </c>
       <c r="DD43" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DE43" t="n">
         <v>1.27</v>
@@ -21397,7 +21397,7 @@
         <v>1.33</v>
       </c>
       <c r="DE46" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="DF46" t="n">
         <v>1.33</v>
@@ -21826,7 +21826,7 @@
         <v>50</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DE47" t="n">
         <v>2</v>
@@ -23211,7 +23211,7 @@
         <v>2.38</v>
       </c>
       <c r="DO50" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -23613,7 +23613,7 @@
         <v>2.83</v>
       </c>
       <c r="DE51" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="DF51" t="n">
         <v>2.33</v>
@@ -24493,7 +24493,7 @@
         <v>1.18</v>
       </c>
       <c r="DE53" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DF53" t="n">
         <v>1.5</v>
@@ -26726,7 +26726,7 @@
         <v>63</v>
       </c>
       <c r="DD58" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DE58" t="n">
         <v>0.27</v>
@@ -27185,7 +27185,7 @@
         <v>1.17</v>
       </c>
       <c r="DE59" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="DF59" t="n">
         <v>1</v>
@@ -27215,7 +27215,7 @@
         <v>2.96</v>
       </c>
       <c r="DO59" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -28938,7 +28938,7 @@
         <v>59</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DE63" t="n">
         <v>0.36</v>
@@ -29394,7 +29394,7 @@
         <v>100</v>
       </c>
       <c r="DD64" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="DE64" t="n">
         <v>1.55</v>
@@ -30309,7 +30309,7 @@
         <v>1.17</v>
       </c>
       <c r="DE66" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DF66" t="n">
         <v>1.5</v>
@@ -30339,7 +30339,7 @@
         <v>2.57</v>
       </c>
       <c r="DO66" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -32518,7 +32518,7 @@
         <v>71</v>
       </c>
       <c r="DD71" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="DE71" t="n">
         <v>1</v>
@@ -33894,7 +33894,7 @@
         <v>38</v>
       </c>
       <c r="DD74" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DE74" t="n">
         <v>1.36</v>
@@ -35693,7 +35693,7 @@
         <v>2.83</v>
       </c>
       <c r="DE78" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="DF78" t="n">
         <v>2.5</v>
@@ -37029,7 +37029,7 @@
         <v>2.25</v>
       </c>
       <c r="DE81" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="DF81" t="n">
         <v>2</v>
@@ -37894,7 +37894,7 @@
         <v>80</v>
       </c>
       <c r="DD83" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DE83" t="n">
         <v>0.38</v>
@@ -37927,7 +37927,7 @@
         <v>2.19</v>
       </c>
       <c r="DO83" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -38337,7 +38337,7 @@
         <v>2.5</v>
       </c>
       <c r="DE84" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DF84" t="n">
         <v>1.8</v>
@@ -39685,7 +39685,7 @@
         <v>0.42</v>
       </c>
       <c r="DE87" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="DF87" t="n">
         <v>0.25</v>
@@ -40594,7 +40594,7 @@
         <v>65</v>
       </c>
       <c r="DD89" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="DE89" t="n">
         <v>0.27</v>
@@ -41498,10 +41498,10 @@
         <v>80</v>
       </c>
       <c r="DD91" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DE91" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="DF91" t="n">
         <v>1.4</v>
@@ -41531,7 +41531,7 @@
         <v>2.46</v>
       </c>
       <c r="DO91" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -43754,7 +43754,7 @@
         <v>67</v>
       </c>
       <c r="DD96" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DE96" t="n">
         <v>1.5</v>
@@ -43787,7 +43787,7 @@
         <v>2.71</v>
       </c>
       <c r="DO96" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -44189,7 +44189,7 @@
         <v>1.33</v>
       </c>
       <c r="DE97" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DF97" t="n">
         <v>1.33</v>
@@ -44637,7 +44637,7 @@
         <v>2.25</v>
       </c>
       <c r="DE98" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="DF98" t="n">
         <v>2</v>
@@ -46435,7 +46435,7 @@
         <v>3.07</v>
       </c>
       <c r="DO102" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP102" t="b">
         <v>0</v>
@@ -48161,7 +48161,7 @@
         <v>2.55</v>
       </c>
       <c r="DE106" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="DF106" t="n">
         <v>2.71</v>
@@ -48594,7 +48594,7 @@
         <v>61</v>
       </c>
       <c r="DD107" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DE107" t="n">
         <v>1.36</v>
@@ -50842,10 +50842,10 @@
         <v>80</v>
       </c>
       <c r="DD112" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="DE112" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DF112" t="n">
         <v>1.8</v>
@@ -50875,7 +50875,7 @@
         <v>2.58</v>
       </c>
       <c r="DO112" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -51855,12 +51855,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F115" s="2" t="n">
@@ -51870,347 +51870,347 @@
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K115" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L115" t="n">
+        <v>13</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1</v>
+      </c>
+      <c r="N115" t="n">
+        <v>1</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>3</v>
+      </c>
+      <c r="R115" t="n">
+        <v>2</v>
+      </c>
+      <c r="S115" t="n">
         <v>12</v>
       </c>
-      <c r="M115" t="n">
-        <v>1</v>
-      </c>
-      <c r="N115" t="n">
-        <v>3</v>
-      </c>
-      <c r="O115" t="n">
-        <v>0</v>
-      </c>
-      <c r="P115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
-      <c r="R115" t="n">
-        <v>2</v>
-      </c>
-      <c r="S115" t="n">
-        <v>7</v>
-      </c>
       <c r="T115" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="U115" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="V115" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="W115" t="n">
         <v>12</v>
       </c>
       <c r="X115" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y115" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="Z115" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>Stadion Nizhny Novgorod</t>
+          <t>Anzhi-Arena</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>ul. Dolzhanskaya, Nizhniy Novgorod</t>
+          <t>, Kaspiysk</t>
         </is>
       </c>
       <c r="AC115" t="n">
         <v>1</v>
       </c>
       <c r="AD115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE115" t="n">
-        <v>2.8</v>
+        <v>3.83</v>
       </c>
       <c r="AF115" t="n">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="AG115" t="n">
-        <v>2.56</v>
+        <v>2.09</v>
       </c>
       <c r="AH115" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AI115" t="n">
         <v>2.2</v>
       </c>
       <c r="AJ115" t="n">
-        <v>3.84</v>
+        <v>4.55</v>
       </c>
       <c r="AK115" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AL115" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AM115" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AN115" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="AO115" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AR115" t="n">
-        <v>3.2</v>
+        <v>3.52</v>
       </c>
       <c r="AS115" t="n">
-        <v>2.73</v>
+        <v>2.43</v>
       </c>
       <c r="AT115" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AU115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB115" t="n">
+        <v>101</v>
+      </c>
+      <c r="BC115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD115" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT115" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV115" t="n">
+        <v>54</v>
+      </c>
+      <c r="BW115" t="n">
+        <v>45</v>
+      </c>
+      <c r="BX115" t="n">
+        <v>96</v>
+      </c>
+      <c r="BY115" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ115" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CA115" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="CB115" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="CC115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR115" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS115" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU115" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV115" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX115" t="n">
+        <v>13</v>
+      </c>
+      <c r="CY115" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ115" t="n">
+        <v>25</v>
+      </c>
+      <c r="DA115" t="n">
+        <v>62</v>
+      </c>
+      <c r="DB115" t="n">
+        <v>17</v>
+      </c>
+      <c r="DC115" t="n">
+        <v>70</v>
+      </c>
+      <c r="DD115" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DE115" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DF115" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DG115" t="n">
         <v>1.33</v>
       </c>
-      <c r="AU115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ115" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA115" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB115" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BC115" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD115" t="n">
-        <v>47</v>
-      </c>
-      <c r="BE115" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF115" t="n">
-        <v>4922</v>
-      </c>
-      <c r="BG115" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BH115" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI115" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BJ115" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BK115" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BL115" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BM115" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BN115" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BO115" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP115" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ115" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR115" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS115" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT115" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU115" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV115" t="n">
-        <v>46</v>
-      </c>
-      <c r="BW115" t="n">
-        <v>43</v>
-      </c>
-      <c r="BX115" t="n">
-        <v>80</v>
-      </c>
-      <c r="BY115" t="n">
-        <v>78</v>
-      </c>
-      <c r="BZ115" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="CA115" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="CB115" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="CC115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI115" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ115" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM115" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CN115" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CO115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ115" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR115" t="n">
-        <v>16</v>
-      </c>
-      <c r="CS115" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT115" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU115" t="n">
-        <v>14</v>
-      </c>
-      <c r="CV115" t="n">
-        <v>15</v>
-      </c>
-      <c r="CW115" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX115" t="n">
-        <v>5</v>
-      </c>
-      <c r="CY115" t="n">
-        <v>6</v>
-      </c>
-      <c r="CZ115" t="n">
-        <v>54</v>
-      </c>
-      <c r="DA115" t="n">
-        <v>69</v>
-      </c>
-      <c r="DB115" t="n">
-        <v>31</v>
-      </c>
-      <c r="DC115" t="n">
-        <v>77</v>
-      </c>
-      <c r="DD115" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="DE115" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="DF115" t="n">
-        <v>1</v>
-      </c>
-      <c r="DG115" t="n">
-        <v>0.83</v>
-      </c>
       <c r="DH115" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="DI115" t="n">
-        <v>1.36</v>
+        <v>2.14</v>
       </c>
       <c r="DJ115" t="n">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="DK115" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="DL115" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="DM115" t="n">
-        <v>1.19</v>
+        <v>1.54</v>
       </c>
       <c r="DN115" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="DO115" t="n">
         <v>23</v>
       </c>
       <c r="DP115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ115" t="b">
         <v>0</v>
@@ -52230,48 +52230,44 @@
       <c r="DV115" t="b">
         <v>0</v>
       </c>
-      <c r="DW115" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="DX115" t="inlineStr">
-        <is>
-          <t>4.02</t>
-        </is>
-      </c>
-      <c r="DY115" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
+      <c r="DW115" t="inlineStr"/>
+      <c r="DX115" t="inlineStr"/>
+      <c r="DY115" t="inlineStr"/>
       <c r="DZ115" t="inlineStr"/>
-      <c r="EA115" t="inlineStr"/>
-      <c r="EB115" t="inlineStr"/>
+      <c r="EA115" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EB115" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
       <c r="EC115" t="inlineStr"/>
       <c r="ED115" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="EE115" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EF115" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="EG115" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EH115" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EI115" t="inlineStr"/>
@@ -52295,12 +52291,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F116" s="2" t="n">
@@ -52310,128 +52306,128 @@
         <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J116" t="n">
+        <v>2</v>
+      </c>
+      <c r="K116" t="n">
+        <v>10</v>
+      </c>
+      <c r="L116" t="n">
+        <v>12</v>
+      </c>
+      <c r="M116" t="n">
+        <v>1</v>
+      </c>
+      <c r="N116" t="n">
+        <v>3</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0</v>
+      </c>
+      <c r="R116" t="n">
+        <v>2</v>
+      </c>
+      <c r="S116" t="n">
         <v>7</v>
       </c>
-      <c r="K116" t="n">
-        <v>6</v>
-      </c>
-      <c r="L116" t="n">
+      <c r="T116" t="n">
         <v>13</v>
       </c>
-      <c r="M116" t="n">
-        <v>1</v>
-      </c>
-      <c r="N116" t="n">
-        <v>1</v>
-      </c>
-      <c r="O116" t="n">
-        <v>0</v>
-      </c>
-      <c r="P116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>3</v>
-      </c>
-      <c r="R116" t="n">
-        <v>2</v>
-      </c>
-      <c r="S116" t="n">
-        <v>12</v>
-      </c>
-      <c r="T116" t="n">
-        <v>9</v>
-      </c>
       <c r="U116" t="n">
+        <v>7</v>
+      </c>
+      <c r="V116" t="n">
         <v>15</v>
-      </c>
-      <c r="V116" t="n">
-        <v>11</v>
       </c>
       <c r="W116" t="n">
         <v>12</v>
       </c>
       <c r="X116" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y116" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="Z116" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>Anzhi-Arena</t>
+          <t>Stadion Nizhny Novgorod</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>, Kaspiysk</t>
+          <t>ul. Dolzhanskaya, Nizhniy Novgorod</t>
         </is>
       </c>
       <c r="AC116" t="n">
         <v>1</v>
       </c>
       <c r="AD116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE116" t="n">
-        <v>3.83</v>
+        <v>2.8</v>
       </c>
       <c r="AF116" t="n">
-        <v>3.03</v>
+        <v>3.1</v>
       </c>
       <c r="AG116" t="n">
-        <v>2.09</v>
+        <v>2.56</v>
       </c>
       <c r="AH116" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AI116" t="n">
         <v>2.2</v>
       </c>
       <c r="AJ116" t="n">
-        <v>4.55</v>
+        <v>3.84</v>
       </c>
       <c r="AK116" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AL116" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AM116" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AN116" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="AO116" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AR116" t="n">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="AS116" t="n">
-        <v>2.43</v>
+        <v>2.73</v>
       </c>
       <c r="AT116" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AU116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV116" t="n">
         <v>0</v>
@@ -52443,28 +52439,28 @@
         <v>0</v>
       </c>
       <c r="AY116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA116" t="n">
         <v>0</v>
       </c>
       <c r="BB116" t="n">
-        <v>101</v>
+        <v>-1</v>
       </c>
       <c r="BC116" t="n">
         <v>0</v>
       </c>
       <c r="BD116" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="BE116" t="n">
         <v>0</v>
       </c>
       <c r="BF116" t="n">
-        <v>-1</v>
+        <v>4922</v>
       </c>
       <c r="BG116" t="n">
         <v>-1</v>
@@ -52494,7 +52490,7 @@
         <v>0</v>
       </c>
       <c r="BP116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ116" t="n">
         <v>1</v>
@@ -52503,7 +52499,7 @@
         <v>1</v>
       </c>
       <c r="BS116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT116" t="n">
         <v>2</v>
@@ -52512,145 +52508,145 @@
         <v>1</v>
       </c>
       <c r="BV116" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW116" t="n">
+        <v>43</v>
+      </c>
+      <c r="BX116" t="n">
+        <v>80</v>
+      </c>
+      <c r="BY116" t="n">
+        <v>78</v>
+      </c>
+      <c r="BZ116" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="CA116" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CB116" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="CC116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR116" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS116" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU116" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV116" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX116" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY116" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ116" t="n">
         <v>54</v>
       </c>
-      <c r="BW116" t="n">
-        <v>45</v>
-      </c>
-      <c r="BX116" t="n">
-        <v>96</v>
-      </c>
-      <c r="BY116" t="n">
-        <v>88</v>
-      </c>
-      <c r="BZ116" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="CA116" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="CB116" t="n">
+      <c r="DA116" t="n">
+        <v>69</v>
+      </c>
+      <c r="DB116" t="n">
+        <v>31</v>
+      </c>
+      <c r="DC116" t="n">
+        <v>77</v>
+      </c>
+      <c r="DD116" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DE116" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DF116" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG116" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DH116" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DI116" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DJ116" t="n">
+        <v>47</v>
+      </c>
+      <c r="DK116" t="n">
+        <v>31</v>
+      </c>
+      <c r="DL116" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DM116" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DN116" t="n">
         <v>2.71</v>
       </c>
-      <c r="CC116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM116" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CN116" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CO116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR116" t="n">
-        <v>26</v>
-      </c>
-      <c r="CS116" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU116" t="n">
-        <v>13</v>
-      </c>
-      <c r="CV116" t="n">
-        <v>12</v>
-      </c>
-      <c r="CW116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX116" t="n">
-        <v>13</v>
-      </c>
-      <c r="CY116" t="n">
-        <v>12</v>
-      </c>
-      <c r="CZ116" t="n">
-        <v>25</v>
-      </c>
-      <c r="DA116" t="n">
-        <v>62</v>
-      </c>
-      <c r="DB116" t="n">
-        <v>17</v>
-      </c>
-      <c r="DC116" t="n">
-        <v>70</v>
-      </c>
-      <c r="DD116" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="DE116" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="DF116" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DG116" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DH116" t="n">
-        <v>1</v>
-      </c>
-      <c r="DI116" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="DJ116" t="n">
-        <v>75</v>
-      </c>
-      <c r="DK116" t="n">
-        <v>38</v>
-      </c>
-      <c r="DL116" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="DM116" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="DN116" t="n">
-        <v>2.74</v>
-      </c>
       <c r="DO116" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ116" t="b">
         <v>0</v>
@@ -52670,44 +52666,48 @@
       <c r="DV116" t="b">
         <v>0</v>
       </c>
-      <c r="DW116" t="inlineStr"/>
-      <c r="DX116" t="inlineStr"/>
-      <c r="DY116" t="inlineStr"/>
+      <c r="DW116" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="DX116" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="DY116" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
       <c r="DZ116" t="inlineStr"/>
-      <c r="EA116" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EB116" t="inlineStr">
-        <is>
-          <t>2.62</t>
-        </is>
-      </c>
+      <c r="EA116" t="inlineStr"/>
+      <c r="EB116" t="inlineStr"/>
       <c r="EC116" t="inlineStr"/>
       <c r="ED116" t="inlineStr">
         <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="EE116" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EF116" t="inlineStr">
+        <is>
           <t>3.30</t>
         </is>
       </c>
-      <c r="EE116" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="EF116" t="inlineStr">
-        <is>
-          <t>3.23</t>
-        </is>
-      </c>
       <c r="EG116" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EH116" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EI116" t="inlineStr"/>
@@ -53498,7 +53498,7 @@
         <v>69</v>
       </c>
       <c r="DD118" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DE118" t="n">
         <v>1.55</v>
@@ -53937,7 +53937,7 @@
         <v>2.27</v>
       </c>
       <c r="DE119" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="DF119" t="n">
         <v>2.33</v>
@@ -54846,7 +54846,7 @@
         <v>67</v>
       </c>
       <c r="DD121" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="DE121" t="n">
         <v>2</v>
@@ -55759,7 +55759,7 @@
         <v>2.75</v>
       </c>
       <c r="DO123" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP123" t="b">
         <v>0</v>
@@ -56630,10 +56630,10 @@
         <v>82</v>
       </c>
       <c r="DD125" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DE125" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DF125" t="n">
         <v>1.75</v>
@@ -56663,7 +56663,7 @@
         <v>2.42</v>
       </c>
       <c r="DO125" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP125" t="b">
         <v>1</v>
@@ -57078,7 +57078,7 @@
         <v>54</v>
       </c>
       <c r="DD126" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DE126" t="n">
         <v>1</v>
@@ -58857,7 +58857,7 @@
         <v>0.82</v>
       </c>
       <c r="DE130" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="DF130" t="n">
         <v>1</v>
@@ -59313,7 +59313,7 @@
         <v>2.55</v>
       </c>
       <c r="DE131" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="DF131" t="n">
         <v>2.75</v>
@@ -59738,7 +59738,7 @@
         <v>71</v>
       </c>
       <c r="DD132" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="DE132" t="n">
         <v>1.27</v>
@@ -60323,176 +60323,176 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F134" s="2" t="n">
         <v>45991.5625</v>
       </c>
       <c r="G134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I134" t="n">
+        <v>4</v>
+      </c>
+      <c r="J134" t="n">
+        <v>2</v>
+      </c>
+      <c r="K134" t="n">
+        <v>4</v>
+      </c>
+      <c r="L134" t="n">
+        <v>6</v>
+      </c>
+      <c r="M134" t="n">
+        <v>2</v>
+      </c>
+      <c r="N134" t="n">
+        <v>1</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
         <v>3</v>
       </c>
-      <c r="J134" t="n">
-        <v>7</v>
-      </c>
-      <c r="K134" t="n">
+      <c r="R134" t="n">
+        <v>6</v>
+      </c>
+      <c r="S134" t="n">
         <v>8</v>
       </c>
-      <c r="L134" t="n">
-        <v>15</v>
-      </c>
-      <c r="M134" t="n">
-        <v>3</v>
-      </c>
-      <c r="N134" t="n">
-        <v>2</v>
-      </c>
-      <c r="O134" t="n">
-        <v>0</v>
-      </c>
-      <c r="P134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q134" t="n">
-        <v>6</v>
-      </c>
-      <c r="R134" t="n">
-        <v>5</v>
-      </c>
-      <c r="S134" t="n">
+      <c r="T134" t="n">
+        <v>10</v>
+      </c>
+      <c r="U134" t="n">
         <v>11</v>
       </c>
-      <c r="T134" t="n">
-        <v>18</v>
-      </c>
-      <c r="U134" t="n">
-        <v>17</v>
-      </c>
       <c r="V134" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="W134" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X134" t="n">
         <v>13</v>
       </c>
       <c r="Y134" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="Z134" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>Akhmat Arena</t>
+          <t>Stadion Central’nyj im. I.P. Chayka</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
+          <t>ul. Suvorova, Peschanokopskoye</t>
         </is>
       </c>
       <c r="AC134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA134" t="n">
         <v>3</v>
       </c>
-      <c r="AD134" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE134" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AF134" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AG134" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AH134" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI134" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ134" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AK134" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AL134" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AM134" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AN134" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AO134" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AP134" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AQ134" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AR134" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AS134" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AT134" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AU134" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW134" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX134" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ134" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA134" t="n">
-        <v>1</v>
-      </c>
       <c r="BB134" t="n">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="BC134" t="n">
         <v>0</v>
       </c>
       <c r="BD134" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="BE134" t="n">
         <v>0</v>
       </c>
       <c r="BF134" t="n">
-        <v>4236</v>
+        <v>12383</v>
       </c>
       <c r="BG134" t="n">
         <v>-1</v>
@@ -60519,10 +60519,10 @@
         <v>-1</v>
       </c>
       <c r="BO134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ134" t="n">
         <v>2</v>
@@ -60531,7 +60531,7 @@
         <v>1</v>
       </c>
       <c r="BS134" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT134" t="n">
         <v>3</v>
@@ -60540,37 +60540,37 @@
         <v>1</v>
       </c>
       <c r="BV134" t="n">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="BW134" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="BX134" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="BY134" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="BZ134" t="n">
-        <v>1.77</v>
+        <v>1.45</v>
       </c>
       <c r="CA134" t="n">
-        <v>2.12</v>
+        <v>1.71</v>
       </c>
       <c r="CB134" t="n">
-        <v>3.89</v>
+        <v>3.16</v>
       </c>
       <c r="CC134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG134" t="n">
         <v>0</v>
@@ -60588,7 +60588,7 @@
         <v>0</v>
       </c>
       <c r="CL134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM134" t="n">
         <v>-1</v>
@@ -60597,7 +60597,7 @@
         <v>-1</v>
       </c>
       <c r="CO134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP134" t="n">
         <v>0</v>
@@ -60606,73 +60606,73 @@
         <v>1</v>
       </c>
       <c r="CR134" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="CS134" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="CT134" t="n">
         <v>1</v>
       </c>
       <c r="CU134" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CV134" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="CW134" t="n">
         <v>1</v>
       </c>
       <c r="CX134" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CY134" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CZ134" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="DA134" t="n">
         <v>72</v>
       </c>
       <c r="DB134" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="DC134" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="DD134" t="n">
-        <v>1.83</v>
+        <v>1.18</v>
       </c>
       <c r="DE134" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="DF134" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="DG134" t="n">
-        <v>1.14</v>
+        <v>1.63</v>
       </c>
       <c r="DH134" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="DI134" t="n">
-        <v>1.25</v>
+        <v>1.94</v>
       </c>
       <c r="DJ134" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="DK134" t="n">
         <v>29</v>
       </c>
       <c r="DL134" t="n">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="DM134" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="DN134" t="n">
-        <v>3.07</v>
+        <v>2.93</v>
       </c>
       <c r="DO134" t="n">
         <v>23</v>
@@ -60687,7 +60687,7 @@
         <v>1</v>
       </c>
       <c r="DS134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT134" t="b">
         <v>0</v>
@@ -60700,17 +60700,17 @@
       </c>
       <c r="DW134" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="DX134" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="DY134" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="DZ134" t="inlineStr"/>
@@ -60719,47 +60719,47 @@
       <c r="EC134" t="inlineStr"/>
       <c r="ED134" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="EE134" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="EF134" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="EG134" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EH134" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EI134" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="EJ134" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EK134" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EL134" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -60779,176 +60779,176 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F135" s="2" t="n">
         <v>45991.5625</v>
       </c>
       <c r="G135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H135" t="n">
+        <v>1</v>
+      </c>
+      <c r="I135" t="n">
         <v>3</v>
       </c>
-      <c r="I135" t="n">
-        <v>4</v>
-      </c>
       <c r="J135" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K135" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L135" t="n">
+        <v>15</v>
+      </c>
+      <c r="M135" t="n">
+        <v>3</v>
+      </c>
+      <c r="N135" t="n">
+        <v>2</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
         <v>6</v>
       </c>
-      <c r="M135" t="n">
-        <v>2</v>
-      </c>
-      <c r="N135" t="n">
-        <v>1</v>
-      </c>
-      <c r="O135" t="n">
-        <v>0</v>
-      </c>
-      <c r="P135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q135" t="n">
-        <v>3</v>
-      </c>
       <c r="R135" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S135" t="n">
+        <v>11</v>
+      </c>
+      <c r="T135" t="n">
+        <v>18</v>
+      </c>
+      <c r="U135" t="n">
+        <v>17</v>
+      </c>
+      <c r="V135" t="n">
+        <v>23</v>
+      </c>
+      <c r="W135" t="n">
         <v>8</v>
-      </c>
-      <c r="T135" t="n">
-        <v>10</v>
-      </c>
-      <c r="U135" t="n">
-        <v>11</v>
-      </c>
-      <c r="V135" t="n">
-        <v>16</v>
-      </c>
-      <c r="W135" t="n">
-        <v>16</v>
       </c>
       <c r="X135" t="n">
         <v>13</v>
       </c>
       <c r="Y135" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="Z135" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>Stadion Central’nyj im. I.P. Chayka</t>
+          <t>Akhmat Arena</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>ul. Suvorova, Peschanokopskoye</t>
+          <t>Zhukavskogo per. 9, Staraya Sunzha, Groznyi</t>
         </is>
       </c>
       <c r="AC135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE135" t="n">
-        <v>2.49</v>
+        <v>2.89</v>
       </c>
       <c r="AF135" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="AG135" t="n">
-        <v>2.84</v>
+        <v>2.36</v>
       </c>
       <c r="AH135" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AI135" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AJ135" t="n">
-        <v>3.74</v>
+        <v>3.1</v>
       </c>
       <c r="AK135" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AL135" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="AM135" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AN135" t="n">
-        <v>2.19</v>
+        <v>1.8</v>
       </c>
       <c r="AO135" t="n">
-        <v>2.19</v>
+        <v>2.48</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AR135" t="n">
-        <v>3.09</v>
+        <v>2.62</v>
       </c>
       <c r="AS135" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="AT135" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AU135" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX135" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA135" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BB135" t="n">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="BC135" t="n">
         <v>0</v>
       </c>
       <c r="BD135" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="BE135" t="n">
         <v>0</v>
       </c>
       <c r="BF135" t="n">
-        <v>12383</v>
+        <v>4236</v>
       </c>
       <c r="BG135" t="n">
         <v>-1</v>
@@ -60975,10 +60975,10 @@
         <v>-1</v>
       </c>
       <c r="BO135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ135" t="n">
         <v>2</v>
@@ -60987,7 +60987,7 @@
         <v>1</v>
       </c>
       <c r="BS135" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT135" t="n">
         <v>3</v>
@@ -60996,37 +60996,37 @@
         <v>1</v>
       </c>
       <c r="BV135" t="n">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="BW135" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="BX135" t="n">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="BY135" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="BZ135" t="n">
-        <v>1.45</v>
+        <v>1.77</v>
       </c>
       <c r="CA135" t="n">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="CB135" t="n">
-        <v>3.16</v>
+        <v>3.89</v>
       </c>
       <c r="CC135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG135" t="n">
         <v>0</v>
@@ -61044,7 +61044,7 @@
         <v>0</v>
       </c>
       <c r="CL135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM135" t="n">
         <v>-1</v>
@@ -61053,7 +61053,7 @@
         <v>-1</v>
       </c>
       <c r="CO135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP135" t="n">
         <v>0</v>
@@ -61062,73 +61062,73 @@
         <v>1</v>
       </c>
       <c r="CR135" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="CS135" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="CT135" t="n">
         <v>1</v>
       </c>
       <c r="CU135" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CV135" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="CW135" t="n">
         <v>1</v>
       </c>
       <c r="CX135" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CY135" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CZ135" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="DA135" t="n">
         <v>72</v>
       </c>
       <c r="DB135" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="DC135" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="DD135" t="n">
-        <v>1.18</v>
+        <v>1.83</v>
       </c>
       <c r="DE135" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="DF135" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="DG135" t="n">
-        <v>1.63</v>
+        <v>1.14</v>
       </c>
       <c r="DH135" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DI135" t="n">
-        <v>1.94</v>
+        <v>1.25</v>
       </c>
       <c r="DJ135" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DK135" t="n">
         <v>29</v>
       </c>
       <c r="DL135" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="DM135" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="DN135" t="n">
-        <v>2.93</v>
+        <v>3.07</v>
       </c>
       <c r="DO135" t="n">
         <v>23</v>
@@ -61143,7 +61143,7 @@
         <v>1</v>
       </c>
       <c r="DS135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT135" t="b">
         <v>0</v>
@@ -61156,17 +61156,17 @@
       </c>
       <c r="DW135" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="DX135" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="DY135" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="DZ135" t="inlineStr"/>
@@ -61175,47 +61175,47 @@
       <c r="EC135" t="inlineStr"/>
       <c r="ED135" t="inlineStr">
         <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="EE135" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EF135" t="inlineStr">
+        <is>
+          <t>3.53</t>
+        </is>
+      </c>
+      <c r="EG135" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EH135" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EI135" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EJ135" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EK135" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EL135" t="inlineStr">
+        <is>
           <t>2.54</t>
-        </is>
-      </c>
-      <c r="EE135" t="inlineStr">
-        <is>
-          <t>2.86</t>
-        </is>
-      </c>
-      <c r="EF135" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="EG135" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="EH135" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="EI135" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="EJ135" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="EK135" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EL135" t="inlineStr">
-        <is>
-          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -62469,7 +62469,7 @@
         <v>1.83</v>
       </c>
       <c r="DE138" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="DF138" t="n">
         <v>1.63</v>
@@ -62499,7 +62499,7 @@
         <v>2.95</v>
       </c>
       <c r="DO138" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP138" t="b">
         <v>1</v>
@@ -64197,7 +64197,7 @@
         <v>1.58</v>
       </c>
       <c r="DE142" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="DF142" t="n">
         <v>1.5</v>
@@ -64795,37 +64795,37 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F144" s="2" t="n">
         <v>45998.66666666666</v>
       </c>
       <c r="G144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H144" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I144" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J144" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K144" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L144" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="M144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N144" t="n">
         <v>3</v>
@@ -64834,25 +64834,25 @@
         <v>0</v>
       </c>
       <c r="P144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q144" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S144" t="n">
         <v>14</v>
       </c>
       <c r="T144" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U144" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="V144" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W144" t="n">
         <v>14</v>
@@ -64861,104 +64861,104 @@
         <v>14</v>
       </c>
       <c r="Y144" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Z144" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>Complexe Sportif Jean Bianchi 1</t>
+          <t>Stadion FK Krasnodar</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>21 Avenue Marechal Leclerc, Saint-André-les-Vergers</t>
+          <t>ul. Vostochno-Kruglikovskaya 126, Krasnodar</t>
         </is>
       </c>
       <c r="AC144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD144" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI144" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AJ144" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AK144" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL144" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AM144" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AO144" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AP144" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ144" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR144" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AS144" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AT144" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AU144" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX144" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ144" t="n">
         <v>3</v>
       </c>
-      <c r="AE144" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AF144" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AG144" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AH144" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI144" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AJ144" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AK144" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL144" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AM144" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AN144" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AO144" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AP144" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AQ144" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AR144" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AS144" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT144" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AU144" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV144" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ144" t="n">
-        <v>0</v>
-      </c>
       <c r="BA144" t="n">
         <v>2</v>
       </c>
       <c r="BB144" t="n">
-        <v>1493</v>
+        <v>926</v>
       </c>
       <c r="BC144" t="n">
         <v>0</v>
       </c>
       <c r="BD144" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="BE144" t="n">
         <v>0</v>
@@ -64991,55 +64991,55 @@
         <v>-1</v>
       </c>
       <c r="BO144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP144" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ144" t="n">
         <v>1</v>
       </c>
       <c r="BR144" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS144" t="n">
         <v>3</v>
       </c>
-      <c r="BS144" t="n">
-        <v>0</v>
-      </c>
       <c r="BT144" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BU144" t="n">
         <v>1</v>
       </c>
       <c r="BV144" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="BW144" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="BX144" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="BY144" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="BZ144" t="n">
-        <v>2.16</v>
+        <v>1.79</v>
       </c>
       <c r="CA144" t="n">
-        <v>0.61</v>
+        <v>0.97</v>
       </c>
       <c r="CB144" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CC144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD144" t="n">
         <v>0</v>
       </c>
       <c r="CE144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF144" t="n">
         <v>0</v>
@@ -65078,19 +65078,19 @@
         <v>1</v>
       </c>
       <c r="CR144" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="CS144" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="CT144" t="n">
         <v>1</v>
       </c>
       <c r="CU144" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="CV144" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="CW144" t="n">
         <v>1</v>
@@ -65099,52 +65099,52 @@
         <v>5</v>
       </c>
       <c r="CY144" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="CZ144" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="DA144" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="DB144" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="DC144" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="DD144" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="DE144" t="n">
-        <v>0.38</v>
+        <v>1.17</v>
       </c>
       <c r="DF144" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="DG144" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.38</v>
       </c>
       <c r="DH144" t="n">
-        <v>1.88</v>
+        <v>2.18</v>
       </c>
       <c r="DI144" t="n">
-        <v>1</v>
+        <v>2.12</v>
       </c>
       <c r="DJ144" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="DK144" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="DL144" t="n">
-        <v>1.33</v>
+        <v>1.95</v>
       </c>
       <c r="DM144" t="n">
-        <v>0.87</v>
+        <v>1.42</v>
       </c>
       <c r="DN144" t="n">
-        <v>2.2</v>
+        <v>3.37</v>
       </c>
       <c r="DO144" t="n">
         <v>23</v>
@@ -65156,68 +65156,88 @@
         <v>1</v>
       </c>
       <c r="DR144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU144" t="b">
         <v>0</v>
       </c>
       <c r="DV144" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW144" t="inlineStr">
-        <is>
-          <t>2.23</t>
-        </is>
-      </c>
-      <c r="DX144" t="inlineStr">
-        <is>
-          <t>4.08</t>
-        </is>
-      </c>
-      <c r="DY144" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="DZ144" t="inlineStr"/>
-      <c r="EA144" t="inlineStr"/>
-      <c r="EB144" t="inlineStr"/>
-      <c r="EC144" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="DW144" t="inlineStr"/>
+      <c r="DX144" t="inlineStr"/>
+      <c r="DY144" t="inlineStr"/>
+      <c r="DZ144" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EA144" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EB144" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="EC144" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
       <c r="ED144" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="EE144" t="inlineStr">
         <is>
-          <t>7.60</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="EF144" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="EG144" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EH144" t="inlineStr">
         <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="EI144" t="inlineStr"/>
-      <c r="EJ144" t="inlineStr"/>
-      <c r="EK144" t="inlineStr"/>
-      <c r="EL144" t="inlineStr"/>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EI144" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EJ144" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EK144" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EL144" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -65235,37 +65255,37 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F145" s="2" t="n">
         <v>45998.66666666666</v>
       </c>
       <c r="G145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H145" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J145" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K145" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L145" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="M145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N145" t="n">
         <v>3</v>
@@ -65274,25 +65294,25 @@
         <v>0</v>
       </c>
       <c r="P145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S145" t="n">
         <v>14</v>
       </c>
       <c r="T145" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U145" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V145" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="W145" t="n">
         <v>14</v>
@@ -65301,185 +65321,185 @@
         <v>14</v>
       </c>
       <c r="Y145" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Z145" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>Stadion FK Krasnodar</t>
+          <t>Complexe Sportif Jean Bianchi 1</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>ul. Vostochno-Kruglikovskaya 126, Krasnodar</t>
+          <t>21 Avenue Marechal Leclerc, Saint-André-les-Vergers</t>
         </is>
       </c>
       <c r="AC145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD145" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF145" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI145" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AJ145" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AK145" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL145" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM145" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN145" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO145" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AP145" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ145" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR145" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS145" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT145" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU145" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV145" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA145" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB145" t="n">
+        <v>1493</v>
+      </c>
+      <c r="BC145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD145" t="n">
+        <v>47</v>
+      </c>
+      <c r="BE145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR145" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT145" t="n">
         <v>4</v>
       </c>
-      <c r="AE145" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AF145" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AG145" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH145" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AI145" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AJ145" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AK145" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AL145" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AM145" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AN145" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AO145" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AP145" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AQ145" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR145" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AS145" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AT145" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AU145" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV145" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW145" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX145" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY145" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ145" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA145" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB145" t="n">
-        <v>926</v>
-      </c>
-      <c r="BC145" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD145" t="n">
-        <v>41</v>
-      </c>
-      <c r="BE145" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF145" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BG145" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BH145" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI145" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BJ145" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BK145" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BL145" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BM145" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BN145" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BO145" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP145" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ145" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR145" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS145" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT145" t="n">
-        <v>3</v>
-      </c>
       <c r="BU145" t="n">
         <v>1</v>
       </c>
       <c r="BV145" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="BW145" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="BX145" t="n">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="BY145" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="BZ145" t="n">
-        <v>1.79</v>
+        <v>2.16</v>
       </c>
       <c r="CA145" t="n">
-        <v>0.97</v>
+        <v>0.61</v>
       </c>
       <c r="CB145" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CC145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD145" t="n">
         <v>0</v>
       </c>
       <c r="CE145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF145" t="n">
         <v>0</v>
@@ -65518,19 +65538,19 @@
         <v>1</v>
       </c>
       <c r="CR145" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="CS145" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="CT145" t="n">
         <v>1</v>
       </c>
       <c r="CU145" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="CV145" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="CW145" t="n">
         <v>1</v>
@@ -65539,55 +65559,55 @@
         <v>5</v>
       </c>
       <c r="CY145" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="CZ145" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="DA145" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="DB145" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="DC145" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="DD145" t="n">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="DE145" t="n">
-        <v>1.17</v>
+        <v>0.38</v>
       </c>
       <c r="DF145" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="DG145" t="n">
-        <v>1.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DH145" t="n">
-        <v>2.18</v>
+        <v>1.88</v>
       </c>
       <c r="DI145" t="n">
-        <v>2.12</v>
+        <v>1</v>
       </c>
       <c r="DJ145" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="DK145" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="DL145" t="n">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="DM145" t="n">
-        <v>1.42</v>
+        <v>0.87</v>
       </c>
       <c r="DN145" t="n">
-        <v>3.37</v>
+        <v>2.2</v>
       </c>
       <c r="DO145" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP145" t="b">
         <v>1</v>
@@ -65596,88 +65616,68 @@
         <v>1</v>
       </c>
       <c r="DR145" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS145" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT145" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU145" t="b">
         <v>0</v>
       </c>
       <c r="DV145" t="b">
-        <v>1</v>
-      </c>
-      <c r="DW145" t="inlineStr"/>
-      <c r="DX145" t="inlineStr"/>
-      <c r="DY145" t="inlineStr"/>
-      <c r="DZ145" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="EA145" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="EB145" t="inlineStr">
-        <is>
-          <t>3.19</t>
-        </is>
-      </c>
-      <c r="EC145" t="inlineStr">
-        <is>
-          <t>2.74</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="DW145" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="DX145" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
+      </c>
+      <c r="DY145" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="DZ145" t="inlineStr"/>
+      <c r="EA145" t="inlineStr"/>
+      <c r="EB145" t="inlineStr"/>
+      <c r="EC145" t="inlineStr"/>
       <c r="ED145" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EE145" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>7.60</t>
         </is>
       </c>
       <c r="EF145" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="EG145" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EH145" t="inlineStr">
         <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="EI145" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EJ145" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
-      </c>
-      <c r="EK145" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="EL145" t="inlineStr">
-        <is>
-          <t>2.44</t>
-        </is>
-      </c>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="EI145" t="inlineStr"/>
+      <c r="EJ145" t="inlineStr"/>
+      <c r="EK145" t="inlineStr"/>
+      <c r="EL145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -67357,7 +67357,7 @@
         <v>2.27</v>
       </c>
       <c r="DE149" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="DF149" t="n">
         <v>2.25</v>
@@ -70994,7 +70994,7 @@
         <v>71</v>
       </c>
       <c r="DD157" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DE157" t="n">
         <v>0.27</v>
@@ -71434,7 +71434,7 @@
         <v>66</v>
       </c>
       <c r="DD158" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DE158" t="n">
         <v>2</v>
@@ -72341,7 +72341,7 @@
         <v>2.27</v>
       </c>
       <c r="DE160" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DF160" t="n">
         <v>2.33</v>
@@ -73241,7 +73241,7 @@
         <v>1.58</v>
       </c>
       <c r="DE162" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="DF162" t="n">
         <v>1.5</v>
@@ -75058,7 +75058,7 @@
         <v>74</v>
       </c>
       <c r="DD166" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="DE166" t="n">
         <v>1.17</v>
@@ -75509,7 +75509,7 @@
         <v>0.82</v>
       </c>
       <c r="DE167" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DF167" t="n">
         <v>0.89</v>
@@ -75995,7 +75995,7 @@
         <v>2.32</v>
       </c>
       <c r="DO168" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP168" t="b">
         <v>1</v>
@@ -76434,7 +76434,7 @@
         <v>70</v>
       </c>
       <c r="DD169" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DE169" t="n">
         <v>1.58</v>
@@ -77773,7 +77773,7 @@
         <v>2.5</v>
       </c>
       <c r="DE172" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="DF172" t="n">
         <v>2.45</v>
@@ -78198,7 +78198,7 @@
         <v>60</v>
       </c>
       <c r="DD173" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="DE173" t="n">
         <v>0.36</v>
@@ -79522,7 +79522,7 @@
         <v>64</v>
       </c>
       <c r="DD176" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DE176" t="n">
         <v>0.83</v>
@@ -79555,7 +79555,7 @@
         <v>2.16</v>
       </c>
       <c r="DO176" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP176" t="b">
         <v>0</v>
@@ -81265,7 +81265,7 @@
         <v>1.33</v>
       </c>
       <c r="DE180" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="DF180" t="n">
         <v>1.36</v>
@@ -83575,6 +83575,1298 @@
       <c r="EK185" t="inlineStr"/>
       <c r="EL185" t="inlineStr"/>
     </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>24</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Krylya Sovetov</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Akhmat Grozny</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="n">
+        <v>46123.45833333334</v>
+      </c>
+      <c r="G186" t="n">
+        <v>2</v>
+      </c>
+      <c r="H186" t="n">
+        <v>2</v>
+      </c>
+      <c r="I186" t="n">
+        <v>4</v>
+      </c>
+      <c r="J186" t="n">
+        <v>11</v>
+      </c>
+      <c r="K186" t="n">
+        <v>4</v>
+      </c>
+      <c r="L186" t="n">
+        <v>15</v>
+      </c>
+      <c r="M186" t="n">
+        <v>3</v>
+      </c>
+      <c r="N186" t="n">
+        <v>3</v>
+      </c>
+      <c r="O186" t="n">
+        <v>0</v>
+      </c>
+      <c r="P186" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>6</v>
+      </c>
+      <c r="R186" t="n">
+        <v>3</v>
+      </c>
+      <c r="S186" t="n">
+        <v>3</v>
+      </c>
+      <c r="T186" t="n">
+        <v>8</v>
+      </c>
+      <c r="U186" t="n">
+        <v>9</v>
+      </c>
+      <c r="V186" t="n">
+        <v>11</v>
+      </c>
+      <c r="W186" t="n">
+        <v>12</v>
+      </c>
+      <c r="X186" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y186" t="n">
+        <v>61</v>
+      </c>
+      <c r="Z186" t="n">
+        <v>39</v>
+      </c>
+      <c r="AA186" t="inlineStr"/>
+      <c r="AB186" t="inlineStr"/>
+      <c r="AC186" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD186" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE186" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AF186" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG186" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH186" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI186" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AJ186" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AK186" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AL186" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM186" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN186" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AO186" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AP186" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ186" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR186" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AS186" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT186" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AU186" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV186" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW186" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX186" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ186" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA186" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB186" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC186" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD186" t="n">
+        <v>52</v>
+      </c>
+      <c r="BE186" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF186" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG186" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH186" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI186" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ186" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK186" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL186" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM186" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN186" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO186" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP186" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ186" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR186" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS186" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT186" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU186" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV186" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW186" t="n">
+        <v>36</v>
+      </c>
+      <c r="BX186" t="n">
+        <v>107</v>
+      </c>
+      <c r="BY186" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ186" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CA186" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="CB186" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="CC186" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD186" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE186" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF186" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG186" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH186" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI186" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ186" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK186" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL186" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM186" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN186" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO186" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP186" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ186" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR186" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS186" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT186" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU186" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV186" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW186" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX186" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY186" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ186" t="n">
+        <v>33</v>
+      </c>
+      <c r="DA186" t="n">
+        <v>86</v>
+      </c>
+      <c r="DB186" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC186" t="n">
+        <v>76</v>
+      </c>
+      <c r="DD186" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DE186" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DF186" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DG186" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="DH186" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="DI186" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DJ186" t="n">
+        <v>68</v>
+      </c>
+      <c r="DK186" t="n">
+        <v>14</v>
+      </c>
+      <c r="DL186" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="DM186" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DN186" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DO186" t="n">
+        <v>24</v>
+      </c>
+      <c r="DP186" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ186" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR186" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS186" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT186" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU186" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV186" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW186" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="DX186" t="inlineStr">
+        <is>
+          <t>3.87</t>
+        </is>
+      </c>
+      <c r="DY186" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="DZ186" t="inlineStr"/>
+      <c r="EA186" t="inlineStr"/>
+      <c r="EB186" t="inlineStr"/>
+      <c r="EC186" t="inlineStr"/>
+      <c r="ED186" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="EE186" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="EF186" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="EG186" t="inlineStr"/>
+      <c r="EH186" t="inlineStr"/>
+      <c r="EI186" t="inlineStr"/>
+      <c r="EJ186" t="inlineStr"/>
+      <c r="EK186" t="inlineStr"/>
+      <c r="EL186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>24</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Orenburg</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="n">
+        <v>46123.5625</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0</v>
+      </c>
+      <c r="I187" t="n">
+        <v>0</v>
+      </c>
+      <c r="J187" t="n">
+        <v>2</v>
+      </c>
+      <c r="K187" t="n">
+        <v>5</v>
+      </c>
+      <c r="L187" t="n">
+        <v>7</v>
+      </c>
+      <c r="M187" t="n">
+        <v>1</v>
+      </c>
+      <c r="N187" t="n">
+        <v>3</v>
+      </c>
+      <c r="O187" t="n">
+        <v>0</v>
+      </c>
+      <c r="P187" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>1</v>
+      </c>
+      <c r="R187" t="n">
+        <v>3</v>
+      </c>
+      <c r="S187" t="n">
+        <v>4</v>
+      </c>
+      <c r="T187" t="n">
+        <v>11</v>
+      </c>
+      <c r="U187" t="n">
+        <v>5</v>
+      </c>
+      <c r="V187" t="n">
+        <v>14</v>
+      </c>
+      <c r="W187" t="n">
+        <v>12</v>
+      </c>
+      <c r="X187" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y187" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z187" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>Kazan' Arena</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>Prospekt Husaina Yamasheva 115a, Kazan'</t>
+        </is>
+      </c>
+      <c r="AC187" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD187" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE187" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF187" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG187" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AH187" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI187" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AJ187" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AK187" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AL187" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM187" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN187" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AO187" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AP187" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AQ187" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR187" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AS187" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT187" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ187" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA187" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB187" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC187" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD187" t="n">
+        <v>41</v>
+      </c>
+      <c r="BE187" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF187" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG187" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH187" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI187" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ187" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK187" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL187" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM187" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN187" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO187" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP187" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ187" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR187" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS187" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT187" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU187" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV187" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW187" t="n">
+        <v>45</v>
+      </c>
+      <c r="BX187" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY187" t="n">
+        <v>85</v>
+      </c>
+      <c r="BZ187" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="CA187" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CB187" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CC187" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD187" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE187" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF187" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG187" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH187" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI187" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ187" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK187" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL187" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM187" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN187" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO187" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP187" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ187" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR187" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS187" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT187" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU187" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV187" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW187" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX187" t="n">
+        <v>14</v>
+      </c>
+      <c r="CY187" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ187" t="n">
+        <v>45</v>
+      </c>
+      <c r="DA187" t="n">
+        <v>64</v>
+      </c>
+      <c r="DB187" t="n">
+        <v>23</v>
+      </c>
+      <c r="DC187" t="n">
+        <v>64</v>
+      </c>
+      <c r="DD187" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE187" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF187" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="DG187" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="DH187" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DI187" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DJ187" t="n">
+        <v>55</v>
+      </c>
+      <c r="DK187" t="n">
+        <v>36</v>
+      </c>
+      <c r="DL187" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DM187" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DN187" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="DO187" t="n">
+        <v>24</v>
+      </c>
+      <c r="DP187" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ187" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR187" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS187" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT187" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU187" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV187" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW187" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="DX187" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="DY187" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="DZ187" t="inlineStr"/>
+      <c r="EA187" t="inlineStr"/>
+      <c r="EB187" t="inlineStr"/>
+      <c r="EC187" t="inlineStr"/>
+      <c r="ED187" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EE187" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EF187" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="EG187" t="inlineStr"/>
+      <c r="EH187" t="inlineStr"/>
+      <c r="EI187" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EJ187" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="EK187" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EL187" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Russian_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>24</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Baltika</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Olimpiyets</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="n">
+        <v>46123.6875</v>
+      </c>
+      <c r="G188" t="n">
+        <v>2</v>
+      </c>
+      <c r="H188" t="n">
+        <v>2</v>
+      </c>
+      <c r="I188" t="n">
+        <v>4</v>
+      </c>
+      <c r="J188" t="n">
+        <v>4</v>
+      </c>
+      <c r="K188" t="n">
+        <v>5</v>
+      </c>
+      <c r="L188" t="n">
+        <v>9</v>
+      </c>
+      <c r="M188" t="n">
+        <v>1</v>
+      </c>
+      <c r="N188" t="n">
+        <v>2</v>
+      </c>
+      <c r="O188" t="n">
+        <v>0</v>
+      </c>
+      <c r="P188" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>4</v>
+      </c>
+      <c r="R188" t="n">
+        <v>4</v>
+      </c>
+      <c r="S188" t="n">
+        <v>9</v>
+      </c>
+      <c r="T188" t="n">
+        <v>3</v>
+      </c>
+      <c r="U188" t="n">
+        <v>13</v>
+      </c>
+      <c r="V188" t="n">
+        <v>7</v>
+      </c>
+      <c r="W188" t="n">
+        <v>12</v>
+      </c>
+      <c r="X188" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y188" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z188" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>Complexe Sportif Jean Bianchi 1</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>21 Avenue Marechal Leclerc, Saint-André-les-Vergers</t>
+        </is>
+      </c>
+      <c r="AC188" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD188" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE188" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AF188" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG188" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AH188" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI188" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AJ188" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AK188" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AL188" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AM188" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN188" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AO188" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AP188" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ188" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR188" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AS188" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AT188" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU188" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW188" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX188" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY188" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ188" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA188" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB188" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC188" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD188" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE188" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF188" t="n">
+        <v>14514</v>
+      </c>
+      <c r="BG188" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH188" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI188" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ188" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK188" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL188" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM188" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN188" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO188" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP188" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ188" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR188" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS188" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT188" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU188" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV188" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW188" t="n">
+        <v>32</v>
+      </c>
+      <c r="BX188" t="n">
+        <v>91</v>
+      </c>
+      <c r="BY188" t="n">
+        <v>71</v>
+      </c>
+      <c r="BZ188" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="CA188" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="CB188" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="CC188" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD188" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE188" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF188" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG188" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH188" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI188" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ188" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK188" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL188" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM188" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN188" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO188" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP188" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ188" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR188" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS188" t="n">
+        <v>28</v>
+      </c>
+      <c r="CT188" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU188" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV188" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW188" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX188" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY188" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ188" t="n">
+        <v>37</v>
+      </c>
+      <c r="DA188" t="n">
+        <v>73</v>
+      </c>
+      <c r="DB188" t="n">
+        <v>27</v>
+      </c>
+      <c r="DC188" t="n">
+        <v>69</v>
+      </c>
+      <c r="DD188" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DE188" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="DF188" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="DG188" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="DH188" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="DI188" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="DJ188" t="n">
+        <v>64</v>
+      </c>
+      <c r="DK188" t="n">
+        <v>27</v>
+      </c>
+      <c r="DL188" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DM188" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DN188" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="DO188" t="n">
+        <v>24</v>
+      </c>
+      <c r="DP188" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ188" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR188" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS188" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT188" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU188" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV188" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW188" t="inlineStr"/>
+      <c r="DX188" t="inlineStr"/>
+      <c r="DY188" t="inlineStr"/>
+      <c r="DZ188" t="inlineStr"/>
+      <c r="EA188" t="inlineStr"/>
+      <c r="EB188" t="inlineStr"/>
+      <c r="EC188" t="inlineStr"/>
+      <c r="ED188" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EE188" t="inlineStr">
+        <is>
+          <t>6.13</t>
+        </is>
+      </c>
+      <c r="EF188" t="inlineStr">
+        <is>
+          <t>3.73</t>
+        </is>
+      </c>
+      <c r="EG188" t="inlineStr"/>
+      <c r="EH188" t="inlineStr"/>
+      <c r="EI188" t="inlineStr"/>
+      <c r="EJ188" t="inlineStr"/>
+      <c r="EK188" t="inlineStr"/>
+      <c r="EL188" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
